--- a/combined.xlsx
+++ b/combined.xlsx
@@ -218,11 +218,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -388,7 +387,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -409,10 +408,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -421,11 +416,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,7 +428,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -451,10 +442,6 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -485,10 +472,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -501,11 +484,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -778,17 +757,16 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16371" min="16336" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16372" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16336" style="1" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -799,279 +777,168 @@
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="4"/>
       <c r="H1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="XDH1" s="4"/>
-      <c r="XDI1" s="4"/>
-      <c r="XDJ1" s="4"/>
-      <c r="XDK1" s="4"/>
-      <c r="XDL1" s="4"/>
-      <c r="XDM1" s="4"/>
-      <c r="XDN1" s="4"/>
-      <c r="XDO1" s="4"/>
-      <c r="XDP1" s="4"/>
-      <c r="XDQ1" s="4"/>
-      <c r="XDR1" s="4"/>
-      <c r="XDS1" s="4"/>
-      <c r="XDT1" s="4"/>
-      <c r="XDU1" s="4"/>
-      <c r="XDV1" s="4"/>
-      <c r="XDW1" s="4"/>
-      <c r="XDX1" s="4"/>
-      <c r="XDY1" s="4"/>
-      <c r="XDZ1" s="4"/>
-      <c r="XEA1" s="4"/>
-      <c r="XEB1" s="4"/>
-      <c r="XEC1" s="4"/>
-      <c r="XED1" s="4"/>
-      <c r="XEE1" s="4"/>
-      <c r="XEF1" s="4"/>
-      <c r="XEG1" s="4"/>
-      <c r="XEH1" s="4"/>
-      <c r="XEI1" s="4"/>
-      <c r="XEJ1" s="4"/>
-      <c r="XEK1" s="4"/>
-      <c r="XEL1" s="4"/>
-      <c r="XEM1" s="4"/>
-      <c r="XEN1" s="4"/>
-      <c r="XEO1" s="4"/>
-      <c r="XEP1" s="4"/>
-      <c r="XEQ1" s="4"/>
-      <c r="XFD1" s="0"/>
-    </row>
-    <row r="2" s="8" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XFD1" s="1"/>
+    </row>
+    <row r="2" s="6" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="XDH2" s="7"/>
-      <c r="XDI2" s="7"/>
-      <c r="XDJ2" s="7"/>
-      <c r="XDK2" s="7"/>
-      <c r="XDL2" s="7"/>
-      <c r="XDM2" s="7"/>
-      <c r="XDN2" s="7"/>
-      <c r="XDO2" s="7"/>
-      <c r="XDP2" s="7"/>
-      <c r="XDQ2" s="7"/>
-      <c r="XDR2" s="7"/>
-      <c r="XDS2" s="7"/>
-      <c r="XDT2" s="7"/>
-      <c r="XDU2" s="7"/>
-      <c r="XDV2" s="7"/>
-      <c r="XDW2" s="7"/>
-      <c r="XDX2" s="7"/>
-      <c r="XDY2" s="7"/>
-      <c r="XDZ2" s="7"/>
-      <c r="XEA2" s="7"/>
-      <c r="XEB2" s="7"/>
-      <c r="XEC2" s="7"/>
-      <c r="XED2" s="7"/>
-      <c r="XEE2" s="7"/>
-      <c r="XEF2" s="7"/>
-      <c r="XEG2" s="7"/>
-      <c r="XEH2" s="7"/>
-      <c r="XEI2" s="7"/>
-      <c r="XEJ2" s="7"/>
-      <c r="XEK2" s="7"/>
-      <c r="XEL2" s="7"/>
-      <c r="XEM2" s="7"/>
-      <c r="XEN2" s="7"/>
-      <c r="XEO2" s="7"/>
-      <c r="XEP2" s="7"/>
-      <c r="XEQ2" s="7"/>
-      <c r="XFD2" s="0"/>
-    </row>
-    <row r="3" s="8" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XFD2" s="1"/>
+    </row>
+    <row r="3" s="6" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="8" t="s">
+      <c r="Q3" s="7"/>
+      <c r="R3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="T3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="XDH3" s="7"/>
-      <c r="XDI3" s="7"/>
-      <c r="XDJ3" s="7"/>
-      <c r="XDK3" s="7"/>
-      <c r="XDL3" s="7"/>
-      <c r="XDM3" s="7"/>
-      <c r="XDN3" s="7"/>
-      <c r="XDO3" s="7"/>
-      <c r="XDP3" s="7"/>
-      <c r="XDQ3" s="7"/>
-      <c r="XDR3" s="7"/>
-      <c r="XDS3" s="7"/>
-      <c r="XDT3" s="7"/>
-      <c r="XDU3" s="7"/>
-      <c r="XDV3" s="7"/>
-      <c r="XDW3" s="7"/>
-      <c r="XDX3" s="7"/>
-      <c r="XDY3" s="7"/>
-      <c r="XDZ3" s="7"/>
-      <c r="XEA3" s="7"/>
-      <c r="XEB3" s="7"/>
-      <c r="XEC3" s="7"/>
-      <c r="XED3" s="7"/>
-      <c r="XEE3" s="7"/>
-      <c r="XEF3" s="7"/>
-      <c r="XEG3" s="7"/>
-      <c r="XEH3" s="7"/>
-      <c r="XEI3" s="7"/>
-      <c r="XEJ3" s="7"/>
-      <c r="XEK3" s="7"/>
-      <c r="XEL3" s="7"/>
-      <c r="XEM3" s="7"/>
-      <c r="XEN3" s="7"/>
-      <c r="XEO3" s="7"/>
-      <c r="XEP3" s="7"/>
-      <c r="XEQ3" s="7"/>
-      <c r="XFD3" s="0"/>
-    </row>
-    <row r="4" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="s">
+      <c r="XFD3" s="1"/>
+    </row>
+    <row r="4" s="10" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="XDH4" s="11"/>
-      <c r="XDI4" s="11"/>
-      <c r="XDJ4" s="11"/>
-      <c r="XDK4" s="11"/>
-      <c r="XDL4" s="11"/>
-      <c r="XDM4" s="11"/>
-      <c r="XDN4" s="11"/>
-      <c r="XDO4" s="11"/>
-      <c r="XDP4" s="11"/>
-      <c r="XDQ4" s="11"/>
-      <c r="XDR4" s="11"/>
-      <c r="XDS4" s="11"/>
-      <c r="XDT4" s="11"/>
-      <c r="XDU4" s="11"/>
-      <c r="XDV4" s="11"/>
-      <c r="XDW4" s="11"/>
-      <c r="XDX4" s="11"/>
-      <c r="XDY4" s="11"/>
-      <c r="XDZ4" s="11"/>
-      <c r="XEA4" s="11"/>
-      <c r="XEB4" s="11"/>
-      <c r="XEC4" s="11"/>
-      <c r="XED4" s="11"/>
-      <c r="XEE4" s="11"/>
-      <c r="XEF4" s="11"/>
-      <c r="XEG4" s="11"/>
-      <c r="XEH4" s="11"/>
-      <c r="XEI4" s="11"/>
-      <c r="XEJ4" s="11"/>
-      <c r="XEK4" s="11"/>
-      <c r="XEL4" s="11"/>
-      <c r="XEM4" s="11"/>
-      <c r="XEN4" s="11"/>
-      <c r="XEO4" s="11"/>
-      <c r="XEP4" s="11"/>
-      <c r="XEQ4" s="11"/>
-      <c r="XFC4" s="0"/>
-      <c r="XFD4" s="0"/>
+      <c r="N4" s="9"/>
+      <c r="XDH4" s="9"/>
+      <c r="XDI4" s="9"/>
+      <c r="XDJ4" s="9"/>
+      <c r="XDK4" s="9"/>
+      <c r="XDL4" s="9"/>
+      <c r="XDM4" s="9"/>
+      <c r="XDN4" s="9"/>
+      <c r="XDO4" s="9"/>
+      <c r="XDP4" s="9"/>
+      <c r="XDQ4" s="9"/>
+      <c r="XDR4" s="9"/>
+      <c r="XDS4" s="9"/>
+      <c r="XDT4" s="9"/>
+      <c r="XDU4" s="9"/>
+      <c r="XDV4" s="9"/>
+      <c r="XDW4" s="9"/>
+      <c r="XDX4" s="9"/>
+      <c r="XDY4" s="9"/>
+      <c r="XDZ4" s="9"/>
+      <c r="XEA4" s="9"/>
+      <c r="XEB4" s="9"/>
+      <c r="XEC4" s="9"/>
+      <c r="XED4" s="9"/>
+      <c r="XEE4" s="9"/>
+      <c r="XEF4" s="9"/>
+      <c r="XEG4" s="9"/>
+      <c r="XEH4" s="9"/>
+      <c r="XEI4" s="9"/>
+      <c r="XEJ4" s="9"/>
+      <c r="XEK4" s="9"/>
+      <c r="XEL4" s="9"/>
+      <c r="XEM4" s="9"/>
+      <c r="XEN4" s="9"/>
+      <c r="XEO4" s="9"/>
+      <c r="XEP4" s="9"/>
+      <c r="XEQ4" s="9"/>
+      <c r="XFC4" s="1"/>
+      <c r="XFD4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="12" t="n">
         <v>446</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="13" t="n">
         <v>26.4</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="12" t="n">
         <v>920</v>
       </c>
       <c r="F5" s="1" t="n">
@@ -1106,37 +973,37 @@
       <c r="O5" s="1" t="n">
         <v>2.74</v>
       </c>
-      <c r="P5" s="16" t="n">
+      <c r="P5" s="1" t="n">
         <f aca="false">E5+D5+B5+0.8*C5+G5+J5</f>
         <v>4839.9</v>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="1" t="n">
         <f aca="false">P5-$Q$34*O5/100</f>
         <v>3332.9</v>
       </c>
-      <c r="R5" s="16" t="n">
+      <c r="R5" s="1" t="n">
         <f aca="false">Q5/N5</f>
         <v>6.48045887614233</v>
       </c>
-      <c r="T5" s="16" t="n">
+      <c r="T5" s="1" t="n">
         <f aca="false">O5*50000/100</f>
         <v>1370</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="15" t="n">
         <v>248</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="16" t="n">
         <v>61.1</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="15" t="n">
         <v>722</v>
       </c>
       <c r="F6" s="1" t="n">
@@ -1171,37 +1038,37 @@
       <c r="O6" s="1" t="n">
         <v>3.42</v>
       </c>
-      <c r="P6" s="16" t="n">
+      <c r="P6" s="1" t="n">
         <f aca="false">E6+D6+B6+0.8*C6+G6+J6</f>
         <v>5758.3</v>
       </c>
-      <c r="Q6" s="16" t="n">
+      <c r="Q6" s="1" t="n">
         <f aca="false">P6-$Q$34*O6/100</f>
         <v>3877.3</v>
       </c>
-      <c r="R6" s="16" t="n">
+      <c r="R6" s="1" t="n">
         <f aca="false">Q6/N6</f>
         <v>6.03940809968847</v>
       </c>
-      <c r="T6" s="16" t="n">
+      <c r="T6" s="1" t="n">
         <f aca="false">O6*50000/100</f>
         <v>1710</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="12" t="n">
         <v>40</v>
       </c>
       <c r="F7" s="1" t="n">
@@ -1236,37 +1103,37 @@
       <c r="O7" s="1" t="n">
         <v>0.62</v>
       </c>
-      <c r="P7" s="16" t="n">
+      <c r="P7" s="1" t="n">
         <f aca="false">E7+D7+B7+0.8*C7+G7+J7</f>
         <v>689.4</v>
       </c>
-      <c r="Q7" s="16" t="n">
+      <c r="Q7" s="1" t="n">
         <f aca="false">P7-$Q$34*O7/100</f>
         <v>348.4</v>
       </c>
-      <c r="R7" s="16" t="n">
+      <c r="R7" s="1" t="n">
         <f aca="false">Q7/N7</f>
         <v>3.00344827586207</v>
       </c>
-      <c r="T7" s="16" t="n">
+      <c r="T7" s="1" t="n">
         <f aca="false">O7*50000/100</f>
         <v>310</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="16" t="n">
         <v>0.3</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="15" t="n">
         <v>36</v>
       </c>
       <c r="F8" s="1" t="n">
@@ -1301,35 +1168,35 @@
       <c r="O8" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="P8" s="16" t="n">
+      <c r="P8" s="1" t="n">
         <f aca="false">E8+D8+B8+0.8*C8+G8+J8</f>
         <v>825.8</v>
       </c>
-      <c r="Q8" s="16" t="n">
+      <c r="Q8" s="1" t="n">
         <f aca="false">P8-$Q$34*O8/100</f>
         <v>556.3</v>
       </c>
-      <c r="R8" s="16" t="n">
+      <c r="R8" s="1" t="n">
         <f aca="false">ROUND(Q8/N8 *100/1000, 2)</f>
         <v>0.6</v>
       </c>
-      <c r="T8" s="16" t="n">
+      <c r="T8" s="1" t="n">
         <f aca="false">O8*50000/100</f>
         <v>245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="15" t="n">
+      <c r="C9" s="11"/>
+      <c r="D9" s="13" t="n">
         <v>0.8</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="12" t="n">
         <v>46</v>
       </c>
       <c r="F9" s="1" t="n">
@@ -1364,37 +1231,37 @@
       <c r="O9" s="1" t="n">
         <v>0.19</v>
       </c>
-      <c r="P9" s="16" t="n">
+      <c r="P9" s="1" t="n">
         <f aca="false">E9+D9+B9+0.8*C9+G9+J9</f>
         <v>1026.8</v>
       </c>
-      <c r="Q9" s="16" t="n">
+      <c r="Q9" s="1" t="n">
         <f aca="false">P9-$Q$34*O9/100</f>
         <v>922.3</v>
       </c>
-      <c r="R9" s="16" t="n">
+      <c r="R9" s="1" t="n">
         <f aca="false">ROUND(Q9/N9 *100/1000, 2)</f>
         <v>2.53</v>
       </c>
-      <c r="T9" s="16" t="n">
+      <c r="T9" s="1" t="n">
         <f aca="false">O9*50000/100</f>
         <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="15" t="n">
         <v>177</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="15" t="n">
         <v>355</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="16" t="n">
         <v>3.8</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="15" t="n">
         <v>348</v>
       </c>
       <c r="F10" s="1" t="n">
@@ -1429,37 +1296,37 @@
       <c r="O10" s="1" t="n">
         <v>1.85</v>
       </c>
-      <c r="P10" s="16" t="n">
+      <c r="P10" s="1" t="n">
         <f aca="false">E10+D10+B10+0.8*C10+G10+J10</f>
         <v>2114.5</v>
       </c>
-      <c r="Q10" s="16" t="n">
+      <c r="Q10" s="1" t="n">
         <f aca="false">P10-$Q$34*O10/100</f>
         <v>1097</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="1" t="n">
         <f aca="false">ROUND(Q10/N10 *100/1000, 2)</f>
         <v>0.32</v>
       </c>
-      <c r="T10" s="16" t="n">
+      <c r="T10" s="1" t="n">
         <f aca="false">O10*50000/100</f>
         <v>925</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="12" t="n">
         <v>350</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="13" t="n">
         <v>113.8</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="12" t="n">
         <v>533</v>
       </c>
       <c r="F11" s="1" t="n">
@@ -1494,37 +1361,37 @@
       <c r="O11" s="1" t="n">
         <v>2.22</v>
       </c>
-      <c r="P11" s="16" t="n">
+      <c r="P11" s="1" t="n">
         <f aca="false">E11+D11+B11+0.8*C11+G11+J11</f>
         <v>3369.3</v>
       </c>
-      <c r="Q11" s="16" t="n">
+      <c r="Q11" s="1" t="n">
         <f aca="false">P11-$Q$34*O11/100</f>
         <v>2148.3</v>
       </c>
-      <c r="R11" s="16" t="n">
+      <c r="R11" s="1" t="n">
         <f aca="false">ROUND(Q11/N11 *100/1000, 2)</f>
         <v>0.51</v>
       </c>
-      <c r="T11" s="16" t="n">
+      <c r="T11" s="1" t="n">
         <f aca="false">O11*50000/100</f>
         <v>1110</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="15" t="n">
         <v>29</v>
       </c>
       <c r="F12" s="1" t="n">
@@ -1559,37 +1426,37 @@
       <c r="O12" s="1" t="n">
         <v>0.22</v>
       </c>
-      <c r="P12" s="16" t="n">
+      <c r="P12" s="1" t="n">
         <f aca="false">E12+D12+B12+0.8*C12+G12+J12</f>
         <v>256.3</v>
       </c>
-      <c r="Q12" s="16" t="n">
+      <c r="Q12" s="1" t="n">
         <f aca="false">P12-$Q$34*O12/100</f>
         <v>135.3</v>
       </c>
-      <c r="R12" s="16" t="n">
+      <c r="R12" s="1" t="n">
         <f aca="false">ROUND(Q12/N12 *100/1000, 2)</f>
         <v>0.32</v>
       </c>
-      <c r="T12" s="16" t="n">
+      <c r="T12" s="1" t="n">
         <f aca="false">O12*50000/100</f>
         <v>110</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="13" t="n">
         <v>81.3</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="12" t="n">
         <v>152</v>
       </c>
       <c r="F13" s="1" t="n">
@@ -1624,37 +1491,37 @@
       <c r="O13" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="P13" s="16" t="n">
+      <c r="P13" s="1" t="n">
         <f aca="false">E13+D13+B13+0.8*C13+G13+J13</f>
         <v>2375.2</v>
       </c>
-      <c r="Q13" s="16" t="n">
+      <c r="Q13" s="1" t="n">
         <f aca="false">P13-$Q$34*O13/100</f>
         <v>1550.2</v>
       </c>
-      <c r="R13" s="16" t="n">
+      <c r="R13" s="1" t="n">
         <f aca="false">ROUND(Q13/N13 *100/1000, 2)</f>
         <v>0.55</v>
       </c>
-      <c r="T13" s="16" t="n">
+      <c r="T13" s="1" t="n">
         <f aca="false">O13*50000/100</f>
         <v>750</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="15" t="n">
         <v>1078</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="15" t="n">
         <v>2287</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="15" t="n">
         <v>3100</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="15" t="n">
         <v>6670</v>
       </c>
       <c r="F14" s="1" t="n">
@@ -1689,37 +1556,37 @@
       <c r="O14" s="1" t="n">
         <v>15.91</v>
       </c>
-      <c r="P14" s="16" t="n">
+      <c r="P14" s="1" t="n">
         <f aca="false">E14+D14+B14+0.8*C14+G14+J14</f>
         <v>37716.5</v>
       </c>
-      <c r="Q14" s="16" t="n">
+      <c r="Q14" s="1" t="n">
         <f aca="false">P14-$Q$34*O14/100</f>
         <v>28966</v>
       </c>
-      <c r="R14" s="16" t="n">
+      <c r="R14" s="1" t="n">
         <f aca="false">ROUND(Q14/N14 *100/1000, 2)</f>
         <v>0.97</v>
       </c>
-      <c r="T14" s="16" t="n">
+      <c r="T14" s="1" t="n">
         <f aca="false">O14*50000/100</f>
         <v>7955</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="12" t="n">
         <v>973</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="12" t="n">
         <v>3652</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="13" t="n">
         <v>1595.2</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="12" t="n">
         <v>8344</v>
       </c>
       <c r="F15" s="1" t="n">
@@ -1754,37 +1621,37 @@
       <c r="O15" s="1" t="n">
         <v>24.1</v>
       </c>
-      <c r="P15" s="16" t="n">
+      <c r="P15" s="1" t="n">
         <f aca="false">E15+D15+B15+0.8*C15+G15+J15</f>
         <v>41018.8</v>
       </c>
-      <c r="Q15" s="16" t="n">
+      <c r="Q15" s="1" t="n">
         <f aca="false">P15-$Q$34*O15/100</f>
         <v>27763.8</v>
       </c>
-      <c r="R15" s="16" t="n">
+      <c r="R15" s="1" t="n">
         <f aca="false">ROUND(Q15/N15 *100/1000, 2)</f>
         <v>0.61</v>
       </c>
-      <c r="T15" s="16" t="n">
+      <c r="T15" s="1" t="n">
         <f aca="false">O15*50000/100</f>
         <v>12050</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="15" t="n">
         <v>91</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="15" t="n">
         <v>74</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="16" t="n">
         <v>22.7</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="15" t="n">
         <v>118</v>
       </c>
       <c r="F16" s="1" t="n">
@@ -1819,37 +1686,37 @@
       <c r="O16" s="1" t="n">
         <v>1.32</v>
       </c>
-      <c r="P16" s="16" t="n">
+      <c r="P16" s="1" t="n">
         <f aca="false">E16+D16+B16+0.8*C16+G16+J16</f>
         <v>4088.6</v>
       </c>
-      <c r="Q16" s="16" t="n">
+      <c r="Q16" s="1" t="n">
         <f aca="false">P16-$Q$34*O16/100</f>
         <v>3362.6</v>
       </c>
-      <c r="R16" s="16" t="n">
+      <c r="R16" s="1" t="n">
         <f aca="false">ROUND(Q16/N16 *100/1000, 2)</f>
         <v>1.35</v>
       </c>
-      <c r="T16" s="16" t="n">
+      <c r="T16" s="1" t="n">
         <f aca="false">O16*50000/100</f>
         <v>660</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="13" t="n">
         <v>5.9</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="12" t="n">
         <v>208</v>
       </c>
       <c r="F17" s="1" t="n">
@@ -1884,37 +1751,37 @@
       <c r="O17" s="1" t="n">
         <v>1.16</v>
       </c>
-      <c r="P17" s="16" t="n">
+      <c r="P17" s="1" t="n">
         <f aca="false">E17+D17+B17+0.8*C17+G17+J17</f>
         <v>1578.1</v>
       </c>
-      <c r="Q17" s="16" t="n">
+      <c r="Q17" s="1" t="n">
         <f aca="false">P17-$Q$34*O17/100</f>
         <v>940.1</v>
       </c>
-      <c r="R17" s="16" t="n">
+      <c r="R17" s="1" t="n">
         <f aca="false">ROUND(Q17/N17 *100/1000, 2)</f>
         <v>0.43</v>
       </c>
-      <c r="T17" s="16" t="n">
+      <c r="T17" s="1" t="n">
         <f aca="false">O17*50000/100</f>
         <v>580</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="15" t="n">
         <v>97</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="15" t="n">
         <v>216</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="16" t="n">
         <v>241.4</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="15" t="n">
         <v>331</v>
       </c>
       <c r="F18" s="1" t="n">
@@ -1949,37 +1816,37 @@
       <c r="O18" s="1" t="n">
         <v>3.21</v>
       </c>
-      <c r="P18" s="16" t="n">
+      <c r="P18" s="1" t="n">
         <f aca="false">E18+D18+B18+0.8*C18+G18+J18</f>
         <v>3757.8</v>
       </c>
-      <c r="Q18" s="16" t="n">
+      <c r="Q18" s="1" t="n">
         <f aca="false">P18-$Q$34*O18/100</f>
         <v>1992.3</v>
       </c>
-      <c r="R18" s="16" t="n">
+      <c r="R18" s="1" t="n">
         <f aca="false">ROUND(Q18/N18 *100/1000, 2)</f>
         <v>0.33</v>
       </c>
-      <c r="T18" s="16" t="n">
+      <c r="T18" s="1" t="n">
         <f aca="false">O18*50000/100</f>
         <v>1605</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="12" t="n">
         <v>464</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="12" t="n">
         <v>1205</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="13" t="n">
         <v>544.5</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="12" t="n">
         <v>2618</v>
       </c>
       <c r="F19" s="1" t="n">
@@ -2014,37 +1881,37 @@
       <c r="O19" s="1" t="n">
         <v>12.01</v>
       </c>
-      <c r="P19" s="16" t="n">
+      <c r="P19" s="1" t="n">
         <f aca="false">E19+D19+B19+0.8*C19+G19+J19</f>
         <v>22215.8</v>
       </c>
-      <c r="Q19" s="16" t="n">
+      <c r="Q19" s="1" t="n">
         <f aca="false">P19-$Q$34*O19/100</f>
         <v>15610.3</v>
       </c>
-      <c r="R19" s="16" t="n">
+      <c r="R19" s="1" t="n">
         <f aca="false">ROUND(Q19/N19 *100/1000, 2)</f>
         <v>0.69</v>
       </c>
-      <c r="T19" s="16" t="n">
+      <c r="T19" s="1" t="n">
         <f aca="false">O19*50000/100</f>
         <v>6005</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="15" t="n">
         <v>20</v>
       </c>
       <c r="F20" s="1" t="n">
@@ -2079,37 +1946,37 @@
       <c r="O20" s="1" t="n">
         <v>0.23</v>
       </c>
-      <c r="P20" s="16" t="n">
+      <c r="P20" s="1" t="n">
         <f aca="false">E20+D20+B20+0.8*C20+G20+J20</f>
         <v>407.7</v>
       </c>
-      <c r="Q20" s="16" t="n">
+      <c r="Q20" s="1" t="n">
         <f aca="false">P20-$Q$34*O20/100</f>
         <v>281.2</v>
       </c>
-      <c r="R20" s="16" t="n">
+      <c r="R20" s="1" t="n">
         <f aca="false">ROUND(Q20/N20 *100/1000, 2)</f>
         <v>0.65</v>
       </c>
-      <c r="T20" s="16" t="n">
+      <c r="T20" s="1" t="n">
         <f aca="false">O20*50000/100</f>
         <v>115</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="12" t="n">
         <v>31</v>
       </c>
       <c r="F21" s="1" t="n">
@@ -2144,35 +2011,35 @@
       <c r="O21" s="1" t="n">
         <v>0.45</v>
       </c>
-      <c r="P21" s="16" t="n">
+      <c r="P21" s="1" t="n">
         <f aca="false">E21+D21+B21+0.8*C21+G21+J21</f>
         <v>425</v>
       </c>
-      <c r="Q21" s="16" t="n">
+      <c r="Q21" s="1" t="n">
         <f aca="false">P21-$Q$34*O21/100</f>
         <v>177.5</v>
       </c>
-      <c r="R21" s="16" t="n">
+      <c r="R21" s="1" t="n">
         <f aca="false">ROUND(Q21/N21 *100/1000, 2)</f>
         <v>0.21</v>
       </c>
-      <c r="T21" s="16" t="n">
+      <c r="T21" s="1" t="n">
         <f aca="false">O21*50000/100</f>
         <v>225</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18" t="n">
+      <c r="C22" s="14"/>
+      <c r="D22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="15" t="n">
         <v>208</v>
       </c>
       <c r="F22" s="1" t="n">
@@ -2207,35 +2074,35 @@
       <c r="O22" s="1" t="n">
         <v>0.48</v>
       </c>
-      <c r="P22" s="16" t="n">
+      <c r="P22" s="1" t="n">
         <f aca="false">E22+D22+B22+0.8*C22+G22+J22</f>
         <v>1923.5</v>
       </c>
-      <c r="Q22" s="16" t="n">
+      <c r="Q22" s="1" t="n">
         <f aca="false">P22-$Q$34*O22/100</f>
         <v>1659.5</v>
       </c>
-      <c r="R22" s="16" t="n">
+      <c r="R22" s="1" t="n">
         <f aca="false">ROUND(Q22/N22 *100/1000, 2)</f>
         <v>1.85</v>
       </c>
-      <c r="T22" s="16" t="n">
+      <c r="T22" s="1" t="n">
         <f aca="false">O22*50000/100</f>
         <v>240</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="14" t="n">
+      <c r="C23" s="11"/>
+      <c r="D23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="12" t="n">
         <v>9</v>
       </c>
       <c r="F23" s="1" t="n">
@@ -2270,37 +2137,37 @@
       <c r="O23" s="1" t="n">
         <v>0.13</v>
       </c>
-      <c r="P23" s="16" t="n">
+      <c r="P23" s="1" t="n">
         <f aca="false">E23+D23+B23+0.8*C23+G23+J23</f>
         <v>417.7</v>
       </c>
-      <c r="Q23" s="16" t="n">
+      <c r="Q23" s="1" t="n">
         <f aca="false">P23-$Q$34*O23/100</f>
         <v>346.2</v>
       </c>
-      <c r="R23" s="16" t="n">
+      <c r="R23" s="1" t="n">
         <f aca="false">ROUND(Q23/N23 *100/1000, 2)</f>
         <v>1.41</v>
       </c>
-      <c r="T23" s="16" t="n">
+      <c r="T23" s="1" t="n">
         <f aca="false">O23*50000/100</f>
         <v>65</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="15" t="n">
         <v>332</v>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="15" t="n">
         <v>882</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="15" t="n">
         <v>1961</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="15" t="n">
         <v>913</v>
       </c>
       <c r="F24" s="1" t="n">
@@ -2335,37 +2202,37 @@
       <c r="O24" s="1" t="n">
         <v>6.23</v>
       </c>
-      <c r="P24" s="16" t="n">
+      <c r="P24" s="1" t="n">
         <f aca="false">E24+D24+B24+0.8*C24+G24+J24</f>
         <v>13742.2</v>
       </c>
-      <c r="Q24" s="16" t="n">
+      <c r="Q24" s="1" t="n">
         <f aca="false">P24-$Q$34*O24/100</f>
         <v>10315.7</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="1" t="n">
         <f aca="false">ROUND(Q24/N24 *100/1000, 2)</f>
         <v>0.88</v>
       </c>
-      <c r="T24" s="16" t="n">
+      <c r="T24" s="1" t="n">
         <f aca="false">O24*50000/100</f>
         <v>3115</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="12" t="n">
         <v>494</v>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="12" t="n">
         <v>577</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="12" t="n">
         <v>560</v>
       </c>
       <c r="F25" s="1" t="n">
@@ -2400,37 +2267,37 @@
       <c r="O25" s="1" t="n">
         <v>4.91</v>
       </c>
-      <c r="P25" s="16" t="n">
+      <c r="P25" s="1" t="n">
         <f aca="false">E25+D25+B25+0.8*C25+G25+J25</f>
         <v>4766.1</v>
       </c>
-      <c r="Q25" s="16" t="n">
+      <c r="Q25" s="1" t="n">
         <f aca="false">P25-$Q$34*O25/100</f>
         <v>2065.6</v>
       </c>
-      <c r="R25" s="16" t="n">
+      <c r="R25" s="1" t="n">
         <f aca="false">ROUND(Q25/N25 *100/1000, 2)</f>
         <v>0.22</v>
       </c>
-      <c r="T25" s="16" t="n">
+      <c r="T25" s="1" t="n">
         <f aca="false">O25*50000/100</f>
         <v>2455</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="15" t="n">
         <v>136</v>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="15" t="n">
         <v>114</v>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="16" t="n">
         <v>24.9</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="15" t="n">
         <v>330</v>
       </c>
       <c r="F26" s="1" t="n">
@@ -2465,37 +2332,37 @@
       <c r="O26" s="1" t="n">
         <v>1.63</v>
       </c>
-      <c r="P26" s="16" t="n">
+      <c r="P26" s="1" t="n">
         <f aca="false">E26+D26+B26+0.8*C26+G26+J26</f>
         <v>5356.3</v>
       </c>
-      <c r="Q26" s="16" t="n">
+      <c r="Q26" s="1" t="n">
         <f aca="false">P26-$Q$34*O26/100</f>
         <v>4459.8</v>
       </c>
-      <c r="R26" s="16" t="n">
+      <c r="R26" s="1" t="n">
         <f aca="false">ROUND(Q26/N26 *100/1000, 2)</f>
         <v>1.45</v>
       </c>
-      <c r="T26" s="16" t="n">
+      <c r="T26" s="1" t="n">
         <f aca="false">O26*50000/100</f>
         <v>815</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="13" t="n">
         <v>1.9</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="12" t="n">
         <v>121</v>
       </c>
       <c r="F27" s="1" t="n">
@@ -2530,37 +2397,37 @@
       <c r="O27" s="1" t="n">
         <v>2.02</v>
       </c>
-      <c r="P27" s="16" t="n">
+      <c r="P27" s="1" t="n">
         <f aca="false">E27+D27+B27+0.8*C27+G27+J27</f>
         <v>1581</v>
       </c>
-      <c r="Q27" s="16" t="n">
+      <c r="Q27" s="1" t="n">
         <f aca="false">P27-$Q$34*O27/100</f>
         <v>470</v>
       </c>
-      <c r="R27" s="16" t="n">
+      <c r="R27" s="1" t="n">
         <f aca="false">ROUND(Q27/N27 *100/1000, 2)</f>
         <v>0.12</v>
       </c>
-      <c r="T27" s="16" t="n">
+      <c r="T27" s="1" t="n">
         <f aca="false">O27*50000/100</f>
         <v>1010</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="15" t="n">
         <v>51</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="15" t="n">
         <v>19</v>
       </c>
       <c r="F28" s="1" t="n">
@@ -2595,37 +2462,37 @@
       <c r="O28" s="1" t="n">
         <v>0.73</v>
       </c>
-      <c r="P28" s="16" t="n">
+      <c r="P28" s="1" t="n">
         <f aca="false">E28+D28+B28+0.8*C28+G28+J28</f>
         <v>395.5</v>
       </c>
-      <c r="Q28" s="16" t="n">
+      <c r="Q28" s="1" t="n">
         <f aca="false">P28-$Q$34*O28/100</f>
         <v>-6</v>
       </c>
-      <c r="R28" s="16" t="n">
+      <c r="R28" s="1" t="n">
         <f aca="false">ROUND(Q28/N28 *100/1000, 2)</f>
         <v>-0</v>
       </c>
-      <c r="T28" s="16" t="n">
+      <c r="T28" s="1" t="n">
         <f aca="false">O28*50000/100</f>
         <v>365</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="12" t="n">
         <v>75</v>
       </c>
       <c r="F29" s="1" t="n">
@@ -2660,37 +2527,37 @@
       <c r="O29" s="1" t="n">
         <v>0.38</v>
       </c>
-      <c r="P29" s="16" t="n">
+      <c r="P29" s="1" t="n">
         <f aca="false">E29+D29+B29+0.8*C29+G29+J29</f>
         <v>345.3</v>
       </c>
-      <c r="Q29" s="16" t="n">
+      <c r="Q29" s="1" t="n">
         <f aca="false">P29-$Q$34*O29/100</f>
         <v>136.3</v>
       </c>
-      <c r="R29" s="16" t="n">
+      <c r="R29" s="1" t="n">
         <f aca="false">ROUND(Q29/N29 *100/1000, 2)</f>
         <v>0.19</v>
       </c>
-      <c r="T29" s="16" t="n">
+      <c r="T29" s="1" t="n">
         <f aca="false">O29*50000/100</f>
         <v>190</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="15" t="n">
         <v>683</v>
       </c>
-      <c r="C30" s="18" t="n">
+      <c r="C30" s="15" t="n">
         <v>1122</v>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="16" t="n">
         <v>240.6</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="15" t="n">
         <v>2151</v>
       </c>
       <c r="F30" s="1" t="n">
@@ -2725,37 +2592,37 @@
       <c r="O30" s="1" t="n">
         <v>8.98</v>
       </c>
-      <c r="P30" s="16" t="n">
+      <c r="P30" s="1" t="n">
         <f aca="false">E30+D30+B30+0.8*C30+G30+J30</f>
         <v>22621.6</v>
       </c>
-      <c r="Q30" s="16" t="n">
+      <c r="Q30" s="1" t="n">
         <f aca="false">P30-$Q$34*O30/100</f>
         <v>17682.6</v>
       </c>
-      <c r="R30" s="16" t="n">
+      <c r="R30" s="1" t="n">
         <f aca="false">ROUND(Q30/N30 *100/1000, 2)</f>
         <v>1.05</v>
       </c>
-      <c r="T30" s="16" t="n">
+      <c r="T30" s="1" t="n">
         <f aca="false">O30*50000/100</f>
         <v>4490</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="12" t="n">
         <v>813</v>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="13" t="n">
         <v>245.1</v>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="12" t="n">
         <v>712</v>
       </c>
       <c r="F31" s="1" t="n">
@@ -2790,285 +2657,249 @@
       <c r="O31" s="1" t="n">
         <v>3.2</v>
       </c>
-      <c r="P31" s="16" t="n">
+      <c r="P31" s="1" t="n">
         <f aca="false">E31+D31+B31+0.8*C31+G31+J31</f>
         <v>4284.7</v>
       </c>
-      <c r="Q31" s="16" t="n">
+      <c r="Q31" s="1" t="n">
         <f aca="false">P31-$Q$34*O31/100</f>
         <v>2524.7</v>
       </c>
-      <c r="R31" s="16" t="n">
+      <c r="R31" s="1" t="n">
         <f aca="false">ROUND(Q31/N31 *100/1000, 2)</f>
         <v>0.42</v>
       </c>
-      <c r="T31" s="16" t="n">
+      <c r="T31" s="1" t="n">
         <f aca="false">O31*50000/100</f>
         <v>1600</v>
       </c>
     </row>
-    <row r="32" s="24" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+    <row r="32" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="21" t="n">
+      <c r="B32" s="18" t="n">
         <v>5847</v>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="18" t="n">
         <v>12930</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="19" t="n">
         <v>8334.6</v>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="18" t="n">
         <v>26264</v>
       </c>
-      <c r="F32" s="23" t="n">
+      <c r="F32" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="G32" s="23" t="n">
+      <c r="G32" s="20" t="n">
         <f aca="false">F32*F$34*1000/100</f>
         <v>93000</v>
       </c>
-      <c r="H32" s="23" t="n">
+      <c r="H32" s="20" t="n">
         <v>299</v>
       </c>
-      <c r="I32" s="23" t="n">
+      <c r="I32" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J32" s="23" t="n">
+      <c r="J32" s="20" t="n">
         <f aca="false">I32*I$34/100*1000</f>
         <v>44000</v>
       </c>
-      <c r="K32" s="23" t="n">
+      <c r="K32" s="20" t="n">
         <v>44</v>
       </c>
-      <c r="L32" s="23" t="n">
+      <c r="L32" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="N32" s="23" t="n">
+      <c r="N32" s="20" t="n">
         <v>18796</v>
       </c>
-      <c r="O32" s="23" t="n">
+      <c r="O32" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="P32" s="24" t="n">
+      <c r="P32" s="20" t="n">
         <f aca="false">E32+D32+B32+0.8*C32+G32+J32</f>
         <v>187789.6</v>
       </c>
-      <c r="Q32" s="24" t="n">
+      <c r="Q32" s="20" t="n">
         <f aca="false">P32-$Q$34*O32/100</f>
         <v>132789.6</v>
       </c>
-      <c r="R32" s="24" t="n">
+      <c r="R32" s="20" t="n">
         <f aca="false">ROUND(Q32/N32 *100/1000, 2)</f>
         <v>0.71</v>
       </c>
-      <c r="T32" s="24" t="n">
+      <c r="T32" s="20" t="n">
         <f aca="false">O32*50000/100</f>
         <v>50000</v>
       </c>
-      <c r="XDH32" s="23"/>
-      <c r="XDI32" s="23"/>
-      <c r="XDJ32" s="23"/>
-      <c r="XDK32" s="23"/>
-      <c r="XDL32" s="23"/>
-      <c r="XDM32" s="23"/>
-      <c r="XDN32" s="23"/>
-      <c r="XDO32" s="23"/>
-      <c r="XDP32" s="23"/>
-      <c r="XDQ32" s="23"/>
-      <c r="XDR32" s="23"/>
-      <c r="XDS32" s="23"/>
-      <c r="XDT32" s="23"/>
-      <c r="XDU32" s="23"/>
-      <c r="XDV32" s="23"/>
-      <c r="XDW32" s="23"/>
-      <c r="XDX32" s="23"/>
-      <c r="XDY32" s="23"/>
-      <c r="XDZ32" s="23"/>
-      <c r="XEA32" s="23"/>
-      <c r="XEB32" s="23"/>
-      <c r="XEC32" s="23"/>
-      <c r="XED32" s="23"/>
-      <c r="XEE32" s="23"/>
-      <c r="XEF32" s="23"/>
-      <c r="XEG32" s="23"/>
-      <c r="XEH32" s="23"/>
-      <c r="XEI32" s="23"/>
-      <c r="XEJ32" s="23"/>
-      <c r="XEK32" s="23"/>
-      <c r="XEL32" s="23"/>
-      <c r="XEM32" s="23"/>
-      <c r="XEN32" s="23"/>
-      <c r="XEO32" s="23"/>
-      <c r="XEP32" s="23"/>
-      <c r="XEQ32" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <f aca="false">SUM(B5:B31)</f>
         <v>5847</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="1" t="n">
         <f aca="false">SUM(C5:C31)</f>
         <v>12932</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33" s="1" t="n">
         <f aca="false">SUM(D5:D31)</f>
         <v>8334.5</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="1" t="n">
         <f aca="false">SUM(E5:E31)</f>
         <v>26264</v>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="G33" s="1" t="n">
         <f aca="false">SUM(G5:G31)</f>
         <v>93018.6</v>
       </c>
-      <c r="J33" s="0" t="n">
+      <c r="J33" s="1" t="n">
         <f aca="false">SUM(J5:J31)</f>
         <v>44088</v>
       </c>
-      <c r="P33" s="16" t="n">
+      <c r="P33" s="1" t="n">
         <f aca="false">SUM(P5:P31)</f>
         <v>187897.7</v>
       </c>
-      <c r="Q33" s="16" t="n">
+      <c r="Q33" s="1" t="n">
         <f aca="false">SUM(Q5:Q31)</f>
         <v>132716.2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F34" s="25" t="n">
+      <c r="F34" s="21" t="n">
         <v>93</v>
       </c>
-      <c r="I34" s="25" t="n">
+      <c r="I34" s="21" t="n">
         <v>44</v>
       </c>
-      <c r="Q34" s="0" t="n">
+      <c r="Q34" s="1" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N37" s="26" t="s">
+      <c r="N37" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="O37" s="27" t="n">
+      <c r="O37" s="23" t="n">
         <v>192.8</v>
       </c>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="24"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N38" s="26" t="s">
+      <c r="N38" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="O38" s="26" t="n">
+      <c r="O38" s="22" t="n">
         <f aca="false">O37*0.7</f>
         <v>134.96</v>
       </c>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N39" s="26"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="24"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N40" s="26" t="s">
+      <c r="N40" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="O40" s="29" t="n">
+      <c r="O40" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N41" s="26" t="s">
+      <c r="N41" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="O41" s="29" t="n">
+      <c r="O41" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
+      <c r="P41" s="24"/>
+      <c r="Q41" s="24"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="N42" s="26" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="N42" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="O42" s="26" t="n">
+      <c r="O42" s="22" t="n">
         <f aca="false">O37+O41</f>
         <v>211.8</v>
       </c>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="30"/>
-      <c r="C43" s="30" t="s">
+      <c r="B43" s="25"/>
+      <c r="C43" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="N43" s="26" t="s">
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="N43" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="O43" s="26" t="n">
+      <c r="O43" s="22" t="n">
         <f aca="false">O38-O40</f>
         <v>79.96</v>
       </c>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
+      <c r="P43" s="24"/>
+      <c r="Q43" s="24"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="N44" s="26" t="s">
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="N44" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="O44" s="26" t="n">
+      <c r="O44" s="22" t="n">
         <f aca="false">O43/O42</f>
         <v>0.37752596789424</v>
       </c>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
+      <c r="P44" s="24"/>
+      <c r="Q44" s="24"/>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="31"/>
-      <c r="B47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
       <c r="J47" s="1"/>
-      <c r="Q47" s="16" t="s">
+      <c r="Q47" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T47" s="16" t="s">
+      <c r="T47" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="31"/>
-      <c r="B49" s="32" t="s">
+      <c r="A49" s="26"/>
+      <c r="B49" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D49" s="32" t="s">
+      <c r="D49" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="E49" s="32" t="s">
+      <c r="E49" s="27" t="s">
         <v>25</v>
       </c>
       <c r="G49" s="1" t="s">

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -79,7 +79,10 @@
     <t xml:space="preserve">Share s</t>
   </si>
   <si>
-    <t xml:space="preserve">With reduced share (55)</t>
+    <t xml:space="preserve">Our scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario 0</t>
   </si>
   <si>
     <t xml:space="preserve">proj.</t>
@@ -292,10 +295,22 @@
     <t xml:space="preserve">share GNI</t>
   </si>
   <si>
+    <t xml:space="preserve">Reward fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ajustable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR</t>
+  </si>
+  <si>
     <t xml:space="preserve">GNI contrib reduction</t>
   </si>
   <si>
     <t xml:space="preserve">Ajout budg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remboursement </t>
   </si>
   <si>
     <t xml:space="preserve">New budg</t>
@@ -314,10 +329,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -399,12 +415,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8A65"/>
+        <bgColor rgb="FFFF9800"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -433,7 +455,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB4C7DC"/>
-        <bgColor rgb="FF99CCFF"/>
+        <bgColor rgb="FFD1C4E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -456,8 +478,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF333333"/>
-        <bgColor rgb="FF333300"/>
+        <fgColor rgb="FFD1C4E9"/>
+        <bgColor rgb="FFB4C7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCDD2"/>
+        <bgColor rgb="FFD1C4E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9800"/>
+        <bgColor rgb="FFFFBF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -495,7 +529,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -504,16 +538,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -524,19 +554,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -556,19 +598,19 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -580,51 +622,67 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -662,11 +720,11 @@
       <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF2F7FF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF650953"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFFF8A65"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFD1C4E9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -682,12 +740,12 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFCDD2"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFBF00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF9800"/>
       <rgbColor rgb="FFFF420E"/>
       <rgbColor rgb="FF5983B0"/>
       <rgbColor rgb="FFB3B3B3"/>
@@ -2115,11 +2173,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="10080540"/>
-        <c:axId val="73984353"/>
+        <c:axId val="36144290"/>
+        <c:axId val="94750663"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10080540"/>
+        <c:axId val="36144290"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2151,7 +2209,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73984353"/>
+        <c:crossAx val="94750663"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2159,7 +2217,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73984353"/>
+        <c:axId val="94750663"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2189,7 +2247,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10080540"/>
+        <c:crossAx val="36144290"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2245,14 +2303,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>700560</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>97200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1159200</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>40320</xdr:rowOff>
+      <xdr:colOff>1158480</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>39600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2260,8 +2318,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2460960" y="7635960"/>
-        <a:ext cx="10059840" cy="5658120"/>
+        <a:off x="2460960" y="7986600"/>
+        <a:ext cx="10059120" cy="5657400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2385,7 +2443,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD49"/>
+  <dimension ref="A1:XFD52"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
@@ -2394,238 +2452,244 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.25"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="10.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="2" width="10.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="14.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="11.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16341" style="1" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="5" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="U1" s="6"/>
+      <c r="AB1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="XFD1" s="1"/>
     </row>
-    <row r="2" s="6" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="5" t="s">
+    <row r="2" s="8" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="7"/>
+      <c r="H2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="6" t="s">
+      <c r="I2" s="7"/>
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="8" t="s">
         <v>17</v>
       </c>
       <c r="S2" s="1"/>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="U2" s="6"/>
+      <c r="V2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="Y2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="XFD2" s="1"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+    <row r="3" s="8" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="6" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>22</v>
+      <c r="M3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="S3" s="1"/>
-      <c r="T3" s="6" t="s">
-        <v>22</v>
+      <c r="T3" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="U3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="V3" s="9"/>
+      <c r="W3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB3" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="V3" s="7"/>
-      <c r="W3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="XFD3" s="1"/>
     </row>
-    <row r="4" s="10" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9" t="s">
+    <row r="4" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9" t="s">
+      <c r="C4" s="11"/>
+      <c r="D4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9" t="s">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="K4" s="9" t="s">
+      <c r="G4" s="11"/>
+      <c r="H4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="K4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="O4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="9"/>
+      <c r="L4" s="11"/>
+      <c r="O4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="11"/>
       <c r="S4" s="1"/>
-      <c r="AB4" s="9"/>
-      <c r="XDM4" s="9"/>
-      <c r="XDN4" s="9"/>
-      <c r="XDO4" s="9"/>
-      <c r="XDP4" s="9"/>
-      <c r="XDQ4" s="9"/>
-      <c r="XDR4" s="9"/>
-      <c r="XDS4" s="9"/>
-      <c r="XDT4" s="9"/>
-      <c r="XDU4" s="9"/>
-      <c r="XDV4" s="9"/>
-      <c r="XDW4" s="9"/>
-      <c r="XDX4" s="9"/>
-      <c r="XDY4" s="9"/>
-      <c r="XDZ4" s="9"/>
-      <c r="XEA4" s="9"/>
-      <c r="XEB4" s="9"/>
-      <c r="XEC4" s="9"/>
-      <c r="XED4" s="9"/>
-      <c r="XEE4" s="9"/>
-      <c r="XEF4" s="9"/>
-      <c r="XEG4" s="9"/>
-      <c r="XEH4" s="9"/>
-      <c r="XEI4" s="9"/>
-      <c r="XEJ4" s="9"/>
-      <c r="XEK4" s="9"/>
-      <c r="XEL4" s="9"/>
-      <c r="XEM4" s="9"/>
-      <c r="XEN4" s="9"/>
-      <c r="XEO4" s="9"/>
-      <c r="XEP4" s="9"/>
-      <c r="XEQ4" s="9"/>
-      <c r="XER4" s="9"/>
-      <c r="XES4" s="9"/>
-      <c r="XET4" s="9"/>
-      <c r="XEU4" s="9"/>
-      <c r="XEV4" s="9"/>
+      <c r="U4" s="2"/>
+      <c r="AB4" s="11"/>
+      <c r="XDM4" s="11"/>
+      <c r="XDN4" s="11"/>
+      <c r="XDO4" s="11"/>
+      <c r="XDP4" s="11"/>
+      <c r="XDQ4" s="11"/>
+      <c r="XDR4" s="11"/>
+      <c r="XDS4" s="11"/>
+      <c r="XDT4" s="11"/>
+      <c r="XDU4" s="11"/>
+      <c r="XDV4" s="11"/>
+      <c r="XDW4" s="11"/>
+      <c r="XDX4" s="11"/>
+      <c r="XDY4" s="11"/>
+      <c r="XDZ4" s="11"/>
+      <c r="XEA4" s="11"/>
+      <c r="XEB4" s="11"/>
+      <c r="XEC4" s="11"/>
+      <c r="XED4" s="11"/>
+      <c r="XEE4" s="11"/>
+      <c r="XEF4" s="11"/>
+      <c r="XEG4" s="11"/>
+      <c r="XEH4" s="11"/>
+      <c r="XEI4" s="11"/>
+      <c r="XEJ4" s="11"/>
+      <c r="XEK4" s="11"/>
+      <c r="XEL4" s="11"/>
+      <c r="XEM4" s="11"/>
+      <c r="XEN4" s="11"/>
+      <c r="XEO4" s="11"/>
+      <c r="XEP4" s="11"/>
+      <c r="XEQ4" s="11"/>
+      <c r="XER4" s="11"/>
+      <c r="XES4" s="11"/>
+      <c r="XET4" s="11"/>
+      <c r="XEU4" s="11"/>
+      <c r="XEV4" s="11"/>
       <c r="XFD4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="12" t="n">
+      <c r="A5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="14" t="n">
         <v>141</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="14" t="n">
         <f aca="false">1000*B5/$S5</f>
         <v>345.61025947732</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="15" t="n">
         <v>330</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="14" t="n">
         <f aca="false">1000*D5/$S5</f>
         <v>808.87507537245</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="16" t="n">
         <v>26.4</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="14" t="n">
         <f aca="false">1000*F5/$S5</f>
         <v>64.710006029796</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="14" t="n">
         <v>920</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="14" t="n">
         <f aca="false">1000*H5/$S5</f>
         <v>2255.04566467471</v>
       </c>
@@ -2635,7 +2699,7 @@
       <c r="K5" s="1" t="n">
         <v>1900</v>
       </c>
-      <c r="L5" s="12" t="n">
+      <c r="L5" s="14" t="n">
         <f aca="false">1000*K5/$S5</f>
         <v>4657.15952487168</v>
       </c>
@@ -2649,7 +2713,7 @@
         <f aca="false">N5*N$34/100*1000</f>
         <v>1452</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="P5" s="14" t="n">
         <f aca="false">1000*O5/$S5</f>
         <v>3559.05033163878</v>
       </c>
@@ -2665,17 +2729,17 @@
       <c r="T5" s="1" t="n">
         <v>2.74</v>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="U5" s="2" t="n">
         <f aca="false">H5+F5+B5+0.8*D5+K5+O5</f>
         <v>4703.4</v>
       </c>
       <c r="V5" s="1" t="n">
-        <f aca="false">U5-$V$34*T5/100</f>
-        <v>3196.4</v>
+        <f aca="false">U5-$T$42*1000*T5/100</f>
+        <v>3043.28606</v>
       </c>
       <c r="W5" s="1" t="n">
         <f aca="false">V5/S5</f>
-        <v>7.83481300278939</v>
+        <v>7.45950982170432</v>
       </c>
       <c r="Y5" s="1" t="n">
         <f aca="false">T5*50000/100</f>
@@ -2685,7 +2749,7 @@
         <v>514.3</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AH5" s="1" t="n">
         <v>1</v>
@@ -2703,34 +2767,34 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="16" t="n">
+      <c r="A6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">1000*B6/$S6</f>
         <v>394.508442480669</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="19" t="n">
         <v>184</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="14" t="n">
         <f aca="false">1000*D6/$S6</f>
         <v>362.947767082216</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="20" t="n">
         <v>61.1</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="14" t="n">
         <f aca="false">1000*F6/$S6</f>
         <v>120.522329177844</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="18" t="n">
         <v>722</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="14" t="n">
         <f aca="false">1000*H6/$S6</f>
         <v>1424.17547735522</v>
       </c>
@@ -2740,7 +2804,7 @@
       <c r="K6" s="1" t="n">
         <v>1100</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="14" t="n">
         <f aca="false">1000*K6/$S6</f>
         <v>2169.79643364368</v>
       </c>
@@ -2754,7 +2818,7 @@
         <f aca="false">N6*N$34/100*1000</f>
         <v>1452</v>
       </c>
-      <c r="P6" s="12" t="n">
+      <c r="P6" s="14" t="n">
         <f aca="false">1000*O6/$S6</f>
         <v>2864.13129240966</v>
       </c>
@@ -2770,17 +2834,17 @@
       <c r="T6" s="1" t="n">
         <v>3.42</v>
       </c>
-      <c r="U6" s="1" t="n">
+      <c r="U6" s="2" t="n">
         <f aca="false">H6+F6+B6+0.8*D6+K6+O6</f>
         <v>3682.3</v>
       </c>
       <c r="V6" s="1" t="n">
-        <f aca="false">U6-$V$34*T6/100</f>
-        <v>1801.3</v>
+        <f aca="false">U6-$T$42*1000*T6/100</f>
+        <v>1610.18698</v>
       </c>
       <c r="W6" s="1" t="n">
         <f aca="false">V6/S6</f>
-        <v>3.55314028720215</v>
+        <v>3.17616178791226</v>
       </c>
       <c r="Y6" s="1" t="n">
         <f aca="false">T6*50000/100</f>
@@ -2790,7 +2854,7 @@
         <v>642</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AH6" s="1" t="n">
         <v>1</v>
@@ -2808,34 +2872,34 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="12" t="n">
+      <c r="A7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">1000*B7/$S7</f>
         <v>726.008291778911</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="14" t="n">
         <f aca="false">1000*D7/$S7</f>
         <v>343.898664526853</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="14" t="n">
         <f aca="false">1000*F7/$S7</f>
         <v>3.82109627252059</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="14" t="n">
         <f aca="false">1000*H7/$S7</f>
         <v>764.219254504117</v>
       </c>
@@ -2845,7 +2909,7 @@
       <c r="K7" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="14" t="n">
         <f aca="false">1000*K7/$S7</f>
         <v>5158.47996790279</v>
       </c>
@@ -2859,7 +2923,7 @@
         <f aca="false">N7*N$34/100*1000</f>
         <v>220</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="14" t="n">
         <f aca="false">1000*O7/$S7</f>
         <v>4203.20589977264</v>
       </c>
@@ -2875,17 +2939,17 @@
       <c r="T7" s="1" t="n">
         <v>0.62</v>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="U7" s="2" t="n">
         <f aca="false">H7+F7+B7+0.8*D7+K7+O7</f>
         <v>582.6</v>
       </c>
       <c r="V7" s="1" t="n">
-        <f aca="false">U7-$V$34*T7/100</f>
-        <v>241.6</v>
+        <f aca="false">U7-$T$42*1000*T7/100</f>
+        <v>206.95378</v>
       </c>
       <c r="W7" s="1" t="n">
         <f aca="false">V7/S7</f>
-        <v>4.61588429720487</v>
+        <v>3.95395158671023</v>
       </c>
       <c r="Y7" s="1" t="n">
         <f aca="false">T7*50000/100</f>
@@ -2895,7 +2959,7 @@
         <v>116</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AH7" s="1" t="n">
         <v>0</v>
@@ -2913,34 +2977,34 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="A8" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <v>46</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="14" t="n">
         <f aca="false">1000*B8/$S8</f>
         <v>786.755148115208</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="19" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="14" t="n">
         <f aca="false">1000*D8/$S8</f>
         <v>444.687692412944</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="14" t="n">
         <f aca="false">1000*F8/$S8</f>
         <v>5.13101183553397</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="18" t="n">
         <v>36</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="14" t="n">
         <f aca="false">1000*H8/$S8</f>
         <v>615.721420264076</v>
       </c>
@@ -2950,7 +3014,7 @@
       <c r="K8" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" s="14" t="n">
         <f aca="false">1000*K8/$S8</f>
         <v>6499.28165834303</v>
       </c>
@@ -2964,7 +3028,7 @@
         <f aca="false">N8*N$34/100*1000</f>
         <v>352</v>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" s="14" t="n">
         <f aca="false">1000*O8/$S8</f>
         <v>6020.38722035986</v>
       </c>
@@ -2980,17 +3044,17 @@
       <c r="T8" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="U8" s="1" t="n">
-        <f aca="false">H8+F8+B8+0.8*D8+K8+O8</f>
-        <v>835.1</v>
+      <c r="U8" s="2" t="n">
+        <f aca="false">H8+F8+B8+D8+K8+O8</f>
+        <v>840.3</v>
       </c>
       <c r="V8" s="1" t="n">
-        <f aca="false">U8-$V$34*T8/100</f>
-        <v>565.6</v>
+        <f aca="false">U8-$T$42*1000*T8/100</f>
+        <v>543.41831</v>
       </c>
       <c r="W8" s="1" t="n">
         <f aca="false">ROUND(V8/S8 *100/1000, 2)</f>
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="Y8" s="1" t="n">
         <f aca="false">T8*50000/100</f>
@@ -3000,7 +3064,7 @@
         <v>93</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AH8" s="1" t="n">
         <v>0</v>
@@ -3018,32 +3082,32 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="12" t="n">
+      <c r="A9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="14" t="n">
         <f aca="false">1000*B9/$S9</f>
         <v>727.603456116417</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="12" t="n">
+      <c r="D9" s="21"/>
+      <c r="E9" s="14" t="n">
         <f aca="false">1000*D9/$S9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="14" t="n">
         <f aca="false">1000*F9/$S9</f>
         <v>36.3801728058208</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="14" t="n">
         <f aca="false">1000*H9/$S9</f>
         <v>2091.8599363347</v>
       </c>
@@ -3053,7 +3117,7 @@
       <c r="K9" s="1" t="n">
         <v>290</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="14" t="n">
         <f aca="false">1000*K9/$S9</f>
         <v>13187.8126421101</v>
       </c>
@@ -3067,7 +3131,7 @@
         <f aca="false">N9*N$34/100*1000</f>
         <v>220</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" s="14" t="n">
         <f aca="false">1000*O9/$S9</f>
         <v>10004.5475216007</v>
       </c>
@@ -3083,17 +3147,17 @@
       <c r="T9" s="1" t="n">
         <v>0.19</v>
       </c>
-      <c r="U9" s="1" t="n">
-        <f aca="false">H9+F9+B9+0.8*D9+K9+O9</f>
+      <c r="U9" s="2" t="n">
+        <f aca="false">H9+F9+B9+D9+K9+O9</f>
         <v>572.8</v>
       </c>
       <c r="V9" s="1" t="n">
-        <f aca="false">U9-$V$34*T9/100</f>
-        <v>468.3</v>
+        <f aca="false">U9-$T$42*1000*T9/100</f>
+        <v>457.68261</v>
       </c>
       <c r="W9" s="1" t="n">
         <f aca="false">ROUND(V9/S9 *100/1000, 2)</f>
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="Y9" s="1" t="n">
         <f aca="false">T9*50000/100</f>
@@ -3103,7 +3167,7 @@
         <v>36.5</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH9" s="1" t="n">
         <v>0</v>
@@ -3121,34 +3185,34 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="18" t="n">
         <v>177</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="14" t="n">
         <f aca="false">1000*B10/$S10</f>
         <v>777.772407095745</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="19" t="n">
         <v>263</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="14" t="n">
         <f aca="false">1000*D10/$S10</f>
         <v>1155.67312466769</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="20" t="n">
         <v>3.8</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="14" t="n">
         <f aca="false">1000*F10/$S10</f>
         <v>16.6979386834115</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="18" t="n">
         <v>348</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="14" t="n">
         <f aca="false">1000*H10/$S10</f>
         <v>1529.17964784926</v>
       </c>
@@ -3158,7 +3222,7 @@
       <c r="K10" s="1" t="n">
         <v>440</v>
       </c>
-      <c r="L10" s="12" t="n">
+      <c r="L10" s="14" t="n">
         <f aca="false">1000*K10/$S10</f>
         <v>1933.44553176343</v>
       </c>
@@ -3172,7 +3236,7 @@
         <f aca="false">N10*N$34/100*1000</f>
         <v>660</v>
       </c>
-      <c r="P10" s="12" t="n">
+      <c r="P10" s="14" t="n">
         <f aca="false">1000*O10/$S10</f>
         <v>2900.16829764515</v>
       </c>
@@ -3188,17 +3252,17 @@
       <c r="T10" s="1" t="n">
         <v>1.85</v>
       </c>
-      <c r="U10" s="1" t="n">
-        <f aca="false">H10+F10+B10+0.8*D10+K10+O10</f>
-        <v>1839.2</v>
+      <c r="U10" s="2" t="n">
+        <f aca="false">H10+F10+B10+D10+K10+O10</f>
+        <v>1891.8</v>
       </c>
       <c r="V10" s="1" t="n">
-        <f aca="false">U10-$V$34*T10/100</f>
-        <v>821.7</v>
+        <f aca="false">U10-$T$42*1000*T10/100</f>
+        <v>770.92015</v>
       </c>
       <c r="W10" s="1" t="n">
         <f aca="false">ROUND(V10/S10 *100/1000, 2)</f>
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="Y10" s="1" t="n">
         <f aca="false">T10*50000/100</f>
@@ -3208,7 +3272,7 @@
         <v>347.3</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH10" s="1" t="n">
         <v>0</v>
@@ -3226,34 +3290,34 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="12" t="n">
+      <c r="A11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="14" t="n">
         <v>106</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="14" t="n">
         <f aca="false">1000*B11/$S11</f>
         <v>304.277684963515</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="15" t="n">
         <v>258</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="14" t="n">
         <f aca="false">1000*D11/$S11</f>
         <v>740.600403024405</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="16" t="n">
         <v>113.8</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="14" t="n">
         <f aca="false">1000*F11/$S11</f>
         <v>326.667929706114</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="14" t="n">
         <v>533</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="14" t="n">
         <f aca="false">1000*H11/$S11</f>
         <v>1530.00005741088</v>
       </c>
@@ -3263,7 +3327,7 @@
       <c r="K11" s="1" t="n">
         <v>1130</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="L11" s="14" t="n">
         <f aca="false">1000*K11/$S11</f>
         <v>3243.71494347899</v>
       </c>
@@ -3277,7 +3341,7 @@
         <f aca="false">N11*N$34/100*1000</f>
         <v>616</v>
       </c>
-      <c r="P11" s="12" t="n">
+      <c r="P11" s="14" t="n">
         <f aca="false">1000*O11/$S11</f>
         <v>1768.25522582571</v>
       </c>
@@ -3293,17 +3357,17 @@
       <c r="T11" s="1" t="n">
         <v>2.22</v>
       </c>
-      <c r="U11" s="1" t="n">
-        <f aca="false">H11+F11+B11+0.8*D11+K11+O11</f>
-        <v>2705.2</v>
+      <c r="U11" s="2" t="n">
+        <f aca="false">H11+F11+B11+D11+K11+O11</f>
+        <v>2756.8</v>
       </c>
       <c r="V11" s="1" t="n">
-        <f aca="false">U11-$V$34*T11/100</f>
-        <v>1484.2</v>
+        <f aca="false">U11-$T$42*1000*T11/100</f>
+        <v>1411.74418</v>
       </c>
       <c r="W11" s="1" t="n">
         <f aca="false">ROUND(V11/S11 *100/1000, 2)</f>
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="Y11" s="1" t="n">
         <f aca="false">T11*50000/100</f>
@@ -3313,7 +3377,7 @@
         <v>417.8</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AH11" s="1" t="n">
         <v>1</v>
@@ -3331,34 +3395,34 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="16" t="n">
+      <c r="A12" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="14" t="n">
         <f aca="false">1000*B12/$S12</f>
         <v>744.360658921001</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="14" t="n">
         <f aca="false">1000*D12/$S12</f>
         <v>679.633645101783</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="14" t="n">
         <f aca="false">1000*F12/$S12</f>
         <v>3.23635069096087</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="14" t="n">
         <f aca="false">1000*H12/$S12</f>
         <v>938.541700378653</v>
       </c>
@@ -3368,7 +3432,7 @@
       <c r="K12" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" s="14" t="n">
         <f aca="false">1000*K12/$S12</f>
         <v>29127.1562186479</v>
       </c>
@@ -3382,7 +3446,7 @@
         <f aca="false">N12*N$34/100*1000</f>
         <v>88</v>
       </c>
-      <c r="P12" s="12" t="n">
+      <c r="P12" s="14" t="n">
         <f aca="false">1000*O12/$S12</f>
         <v>2847.98860804557</v>
       </c>
@@ -3398,17 +3462,17 @@
       <c r="T12" s="1" t="n">
         <v>0.22</v>
       </c>
-      <c r="U12" s="1" t="n">
-        <f aca="false">H12+F12+B12+0.8*D12+K12+O12</f>
-        <v>1056.9</v>
+      <c r="U12" s="2" t="n">
+        <f aca="false">H12+F12+B12+D12+K12+O12</f>
+        <v>1061.1</v>
       </c>
       <c r="V12" s="1" t="n">
-        <f aca="false">U12-$V$34*T12/100</f>
-        <v>935.9</v>
+        <f aca="false">U12-$T$42*1000*T12/100</f>
+        <v>927.80618</v>
       </c>
       <c r="W12" s="1" t="n">
         <f aca="false">ROUND(V12/S12 *100/1000, 2)</f>
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Y12" s="1" t="n">
         <f aca="false">T12*50000/100</f>
@@ -3418,7 +3482,7 @@
         <v>41.9</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AH12" s="1" t="n">
         <v>0</v>
@@ -3436,34 +3500,34 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="12" t="n">
+      <c r="A13" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="14" t="n">
         <v>97</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="14" t="n">
         <f aca="false">1000*B13/$S13</f>
         <v>379.785988637743</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="15" t="n">
         <v>133</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="14" t="n">
         <f aca="false">1000*D13/$S13</f>
         <v>520.737489575462</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="16" t="n">
         <v>81.3</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="14" t="n">
         <f aca="false">1000*F13/$S13</f>
         <v>318.315472951015</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="14" t="n">
         <v>152</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="14" t="n">
         <f aca="false">1000*H13/$S13</f>
         <v>595.128559514814</v>
       </c>
@@ -3473,7 +3537,7 @@
       <c r="K13" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="L13" s="14" t="n">
         <f aca="false">1000*K13/$S13</f>
         <v>2819.03001875438</v>
       </c>
@@ -3487,7 +3551,7 @@
         <f aca="false">N13*N$34/100*1000</f>
         <v>440</v>
       </c>
-      <c r="P13" s="12" t="n">
+      <c r="P13" s="14" t="n">
         <f aca="false">1000*O13/$S13</f>
         <v>1722.74056701657</v>
       </c>
@@ -3503,17 +3567,17 @@
       <c r="T13" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="U13" s="1" t="n">
-        <f aca="false">H13+F13+B13+0.8*D13+K13+O13</f>
-        <v>1596.7</v>
+      <c r="U13" s="2" t="n">
+        <f aca="false">H13+F13+B13+D13+K13+O13</f>
+        <v>1623.3</v>
       </c>
       <c r="V13" s="1" t="n">
-        <f aca="false">U13-$V$34*T13/100</f>
-        <v>771.7</v>
+        <f aca="false">U13-$T$42*1000*T13/100</f>
+        <v>714.4785</v>
       </c>
       <c r="W13" s="1" t="n">
         <f aca="false">ROUND(V13/S13 *100/1000, 2)</f>
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="Y13" s="1" t="n">
         <f aca="false">T13*50000/100</f>
@@ -3523,7 +3587,7 @@
         <v>281.7</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AH13" s="1" t="n">
         <v>0</v>
@@ -3541,34 +3605,34 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="16" t="n">
+      <c r="A14" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="18" t="n">
         <v>1078</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="14" t="n">
         <f aca="false">1000*B14/$S14</f>
         <v>418.692157950257</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="19" t="n">
         <v>1691</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="14" t="n">
         <f aca="false">1000*D14/$S14</f>
         <v>656.779628101934</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="18" t="n">
         <v>3100</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="14" t="n">
         <f aca="false">1000*F14/$S14</f>
         <v>1204.03125199054</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="18" t="n">
         <v>6670</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="14" t="n">
         <f aca="false">1000*H14/$S14</f>
         <v>2590.60917766996</v>
       </c>
@@ -3578,7 +3642,7 @@
       <c r="K14" s="1" t="n">
         <v>5380</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L14" s="14" t="n">
         <f aca="false">1000*K14/$S14</f>
         <v>2089.57681797067</v>
       </c>
@@ -3592,7 +3656,7 @@
         <f aca="false">N14*N$34/100*1000</f>
         <v>9108</v>
       </c>
-      <c r="P14" s="12" t="n">
+      <c r="P14" s="14" t="n">
         <f aca="false">1000*O14/$S14</f>
         <v>3537.5214977838</v>
       </c>
@@ -3608,17 +3672,17 @@
       <c r="T14" s="1" t="n">
         <v>15.91</v>
       </c>
-      <c r="U14" s="1" t="n">
-        <f aca="false">H14+F14+B14+0.8*D14+K14+O14</f>
-        <v>26688.8</v>
+      <c r="U14" s="2" t="n">
+        <f aca="false">H14+F14+B14+D14+K14+O14</f>
+        <v>27027</v>
       </c>
       <c r="V14" s="1" t="n">
-        <f aca="false">U14-$V$34*T14/100</f>
-        <v>17938.3</v>
+        <f aca="false">U14-$T$42*1000*T14/100</f>
+        <v>17387.43329</v>
       </c>
       <c r="W14" s="1" t="n">
         <f aca="false">ROUND(V14/S14 *100/1000, 2)</f>
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="Y14" s="1" t="n">
         <f aca="false">T14*50000/100</f>
@@ -3628,7 +3692,7 @@
         <v>2991.1</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AH14" s="1" t="n">
         <v>5</v>
@@ -3646,34 +3710,34 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="12" t="n">
+      <c r="A15" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="14" t="n">
         <v>973</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="14" t="n">
         <f aca="false">1000*B15/$S15</f>
         <v>260.893020991029</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="22" t="n">
         <v>2700</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="14" t="n">
         <f aca="false">1000*D15/$S15</f>
         <v>723.958023305013</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="16" t="n">
         <v>1595.2</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="14" t="n">
         <f aca="false">1000*F15/$S15</f>
         <v>427.725125472651</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="14" t="n">
         <v>8344</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="14" t="n">
         <f aca="false">1000*H15/$S15</f>
         <v>2237.29842461372</v>
       </c>
@@ -3683,7 +3747,7 @@
       <c r="K15" s="1" t="n">
         <v>6400</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="L15" s="14" t="n">
         <f aca="false">1000*K15/$S15</f>
         <v>1716.04864783411</v>
       </c>
@@ -3697,7 +3761,7 @@
         <f aca="false">N15*N$34/100*1000</f>
         <v>8492</v>
       </c>
-      <c r="P15" s="12" t="n">
+      <c r="P15" s="14" t="n">
         <f aca="false">1000*O15/$S15</f>
         <v>2276.98204959488</v>
       </c>
@@ -3713,17 +3777,17 @@
       <c r="T15" s="1" t="n">
         <v>24.1</v>
       </c>
-      <c r="U15" s="1" t="n">
-        <f aca="false">H15+F15+B15+0.8*D15+K15+O15</f>
-        <v>27964.2</v>
+      <c r="U15" s="2" t="n">
+        <f aca="false">H15+F15+B15+D15+K15+O15</f>
+        <v>28504.2</v>
       </c>
       <c r="V15" s="1" t="n">
-        <f aca="false">U15-$V$34*T15/100</f>
-        <v>14709.2</v>
+        <f aca="false">U15-$T$42*1000*T15/100</f>
+        <v>13902.4679</v>
       </c>
       <c r="W15" s="1" t="n">
         <f aca="false">ROUND(V15/S15 *100/1000, 2)</f>
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="Y15" s="1" t="n">
         <f aca="false">T15*50000/100</f>
@@ -3733,7 +3797,7 @@
         <v>4529.7</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AH15" s="1" t="n">
         <v>6</v>
@@ -3751,34 +3815,34 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="16" t="n">
+      <c r="A16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="18" t="n">
         <v>91</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="14" t="n">
         <f aca="false">1000*B16/$S16</f>
         <v>503.093193867792</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="19" t="n">
         <v>54</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="14" t="n">
         <f aca="false">1000*D16/$S16</f>
         <v>298.538818339129</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="20" t="n">
         <v>22.7</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="14" t="n">
         <f aca="false">1000*F16/$S16</f>
         <v>125.496873635152</v>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" s="18" t="n">
         <v>118</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="14" t="n">
         <f aca="false">1000*H16/$S16</f>
         <v>652.362603037356</v>
       </c>
@@ -3788,7 +3852,7 @@
       <c r="K16" s="1" t="n">
         <v>2540</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="L16" s="14" t="n">
         <f aca="false">1000*K16/$S16</f>
         <v>14042.3814552109</v>
       </c>
@@ -3802,7 +3866,7 @@
         <f aca="false">N16*N$34/100*1000</f>
         <v>924</v>
       </c>
-      <c r="P16" s="12" t="n">
+      <c r="P16" s="14" t="n">
         <f aca="false">1000*O16/$S16</f>
         <v>5108.33089158065</v>
       </c>
@@ -3818,17 +3882,17 @@
       <c r="T16" s="1" t="n">
         <v>1.32</v>
       </c>
-      <c r="U16" s="1" t="n">
-        <f aca="false">H16+F16+B16+0.8*D16+K16+O16</f>
-        <v>3738.9</v>
+      <c r="U16" s="2" t="n">
+        <f aca="false">H16+F16+B16+D16+K16+O16</f>
+        <v>3749.7</v>
       </c>
       <c r="V16" s="1" t="n">
-        <f aca="false">U16-$V$34*T16/100</f>
-        <v>3012.9</v>
+        <f aca="false">U16-$T$42*1000*T16/100</f>
+        <v>2949.93708</v>
       </c>
       <c r="W16" s="1" t="n">
         <f aca="false">ROUND(V16/S16 *100/1000, 2)</f>
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Y16" s="1" t="n">
         <f aca="false">T16*50000/100</f>
@@ -3838,7 +3902,7 @@
         <v>248.4</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AH16" s="1" t="n">
         <v>2</v>
@@ -3856,34 +3920,34 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="12" t="n">
+      <c r="A17" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="14" t="n">
         <v>139</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="14" t="n">
         <f aca="false">1000*B17/$S17</f>
         <v>933.361983293492</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="15" t="n">
         <v>113</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="14" t="n">
         <f aca="false">1000*D17/$S17</f>
         <v>758.776288576724</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="16" t="n">
         <v>5.9</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="14" t="n">
         <f aca="false">1000*F17/$S17</f>
         <v>39.617523031882</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" s="14" t="n">
         <v>208</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="I17" s="14" t="n">
         <f aca="false">1000*H17/$S17</f>
         <v>1396.68555773415</v>
       </c>
@@ -3893,7 +3957,7 @@
       <c r="K17" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="L17" s="14" t="n">
         <f aca="false">1000*K17/$S17</f>
         <v>2484.48873250786</v>
       </c>
@@ -3907,7 +3971,7 @@
         <f aca="false">N17*N$34/100*1000</f>
         <v>396</v>
       </c>
-      <c r="P17" s="12" t="n">
+      <c r="P17" s="14" t="n">
         <f aca="false">1000*O17/$S17</f>
         <v>2659.07442722462</v>
       </c>
@@ -3923,17 +3987,17 @@
       <c r="T17" s="1" t="n">
         <v>1.16</v>
       </c>
-      <c r="U17" s="1" t="n">
-        <f aca="false">H17+F17+B17+0.8*D17+K17+O17</f>
-        <v>1209.3</v>
+      <c r="U17" s="2" t="n">
+        <f aca="false">H17+F17+B17+D17+K17+O17</f>
+        <v>1231.9</v>
       </c>
       <c r="V17" s="1" t="n">
-        <f aca="false">U17-$V$34*T17/100</f>
-        <v>571.3</v>
+        <f aca="false">U17-$T$42*1000*T17/100</f>
+        <v>529.07804</v>
       </c>
       <c r="W17" s="1" t="n">
         <f aca="false">ROUND(V17/S17 *100/1000, 2)</f>
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="Y17" s="1" t="n">
         <f aca="false">T17*50000/100</f>
@@ -3943,7 +4007,7 @@
         <v>218.8</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AH17" s="1" t="n">
         <v>0</v>
@@ -3961,34 +4025,34 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="16" t="n">
+      <c r="A18" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="18" t="n">
         <v>97</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="14" t="n">
         <f aca="false">1000*B18/$S18</f>
         <v>299.863052234907</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="19" t="n">
         <v>160</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="14" t="n">
         <f aca="false">1000*D18/$S18</f>
         <v>494.619467603971</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="20" t="n">
         <v>241.4</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="14" t="n">
         <f aca="false">1000*F18/$S18</f>
         <v>746.257121747491</v>
       </c>
-      <c r="H18" s="16" t="n">
+      <c r="H18" s="18" t="n">
         <v>331</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="14" t="n">
         <f aca="false">1000*H18/$S18</f>
         <v>1023.24402360571</v>
       </c>
@@ -3998,7 +4062,7 @@
       <c r="K18" s="1" t="n">
         <v>940</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="L18" s="14" t="n">
         <f aca="false">1000*K18/$S18</f>
         <v>2905.88937217333</v>
       </c>
@@ -4012,7 +4076,7 @@
         <f aca="false">N18*N$34/100*1000</f>
         <v>572</v>
       </c>
-      <c r="P18" s="12" t="n">
+      <c r="P18" s="14" t="n">
         <f aca="false">1000*O18/$S18</f>
         <v>1768.2645966842</v>
       </c>
@@ -4028,17 +4092,17 @@
       <c r="T18" s="1" t="n">
         <v>3.21</v>
       </c>
-      <c r="U18" s="1" t="n">
-        <f aca="false">H18+F18+B18+0.8*D18+K18+O18</f>
-        <v>2309.4</v>
+      <c r="U18" s="2" t="n">
+        <f aca="false">H18+F18+B18+D18+K18+O18</f>
+        <v>2341.4</v>
       </c>
       <c r="V18" s="1" t="n">
-        <f aca="false">U18-$V$34*T18/100</f>
-        <v>543.9</v>
+        <f aca="false">U18-$T$42*1000*T18/100</f>
+        <v>396.52199</v>
       </c>
       <c r="W18" s="1" t="n">
         <f aca="false">ROUND(V18/S18 *100/1000, 2)</f>
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="Y18" s="1" t="n">
         <f aca="false">T18*50000/100</f>
@@ -4048,7 +4112,7 @@
         <v>602.4</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AH18" s="1" t="n">
         <v>0</v>
@@ -4066,34 +4130,34 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="12" t="n">
+      <c r="A19" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="14" t="n">
         <v>464</v>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="14" t="n">
         <f aca="false">1000*B19/$S19</f>
         <v>255.791133309077</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="15" t="n">
         <v>891</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="14" t="n">
         <f aca="false">1000*D19/$S19</f>
         <v>491.185128832732</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="16" t="n">
         <v>544.5</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="14" t="n">
         <f aca="false">1000*F19/$S19</f>
         <v>300.168689842225</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="H19" s="14" t="n">
         <v>2618</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="14" t="n">
         <f aca="false">1000*H19/$S19</f>
         <v>1443.23531681716</v>
       </c>
@@ -4103,7 +4167,7 @@
       <c r="K19" s="1" t="n">
         <v>7110</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="14" t="n">
         <f aca="false">1000*K19/$S19</f>
         <v>3919.55809876625</v>
       </c>
@@ -4117,7 +4181,7 @@
         <f aca="false">N19*N$34/100*1000</f>
         <v>8316</v>
       </c>
-      <c r="P19" s="12" t="n">
+      <c r="P19" s="14" t="n">
         <f aca="false">1000*O19/$S19</f>
         <v>4584.39453577217</v>
       </c>
@@ -4133,17 +4197,17 @@
       <c r="T19" s="1" t="n">
         <v>12.01</v>
       </c>
-      <c r="U19" s="1" t="n">
-        <f aca="false">H19+F19+B19+0.8*D19+K19+O19</f>
-        <v>19765.3</v>
+      <c r="U19" s="2" t="n">
+        <f aca="false">H19+F19+B19+D19+K19+O19</f>
+        <v>19943.5</v>
       </c>
       <c r="V19" s="1" t="n">
-        <f aca="false">U19-$V$34*T19/100</f>
-        <v>13159.8</v>
+        <f aca="false">U19-$T$42*1000*T19/100</f>
+        <v>12666.86919</v>
       </c>
       <c r="W19" s="1" t="n">
         <f aca="false">ROUND(V19/S19 *100/1000, 2)</f>
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="Y19" s="1" t="n">
         <f aca="false">T19*50000/100</f>
@@ -4153,7 +4217,7 @@
         <v>2258</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AH19" s="1" t="n">
         <v>7</v>
@@ -4171,34 +4235,34 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="16" t="n">
+      <c r="A20" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="18" t="n">
         <v>27</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="14" t="n">
         <f aca="false">1000*B20/$S20</f>
         <v>816.326530612245</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="14" t="n">
         <f aca="false">1000*D20/$S20</f>
         <v>604.686318972033</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="14" t="n">
         <f aca="false">1000*F20/$S20</f>
         <v>0</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="I20" s="14" t="n">
         <f aca="false">1000*H20/$S20</f>
         <v>604.686318972033</v>
       </c>
@@ -4208,7 +4272,7 @@
       <c r="K20" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="14" t="n">
         <f aca="false">1000*K20/$S20</f>
         <v>5442.1768707483</v>
       </c>
@@ -4222,7 +4286,7 @@
         <f aca="false">N20*N$34/100*1000</f>
         <v>88</v>
       </c>
-      <c r="P20" s="12" t="n">
+      <c r="P20" s="14" t="n">
         <f aca="false">1000*O20/$S20</f>
         <v>2660.61980347695</v>
       </c>
@@ -4238,17 +4302,17 @@
       <c r="T20" s="1" t="n">
         <v>0.23</v>
       </c>
-      <c r="U20" s="1" t="n">
-        <f aca="false">H20+F20+B20+0.8*D20+K20+O20</f>
-        <v>331</v>
+      <c r="U20" s="2" t="n">
+        <f aca="false">H20+F20+B20+D20+K20+O20</f>
+        <v>335</v>
       </c>
       <c r="V20" s="1" t="n">
-        <f aca="false">U20-$V$34*T20/100</f>
-        <v>204.5</v>
+        <f aca="false">U20-$T$42*1000*T20/100</f>
+        <v>195.64737</v>
       </c>
       <c r="W20" s="1" t="n">
         <f aca="false">ROUND(V20/S20 *100/1000, 2)</f>
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="Y20" s="1" t="n">
         <f aca="false">T20*50000/100</f>
@@ -4258,7 +4322,7 @@
         <v>43</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AH20" s="1" t="n">
         <v>0</v>
@@ -4276,34 +4340,34 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="12" t="n">
+      <c r="A21" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="14" t="n">
         <f aca="false">1000*B21/$S21</f>
         <v>759.034360189574</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="14" t="n">
         <f aca="false">1000*D21/$S21</f>
         <v>444.312796208531</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="14" t="n">
         <f aca="false">1000*F21/$S21</f>
         <v>1.85130331753555</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="H21" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="14" t="n">
         <f aca="false">1000*H21/$S21</f>
         <v>573.904028436019</v>
       </c>
@@ -4313,7 +4377,7 @@
       <c r="K21" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="14" t="n">
         <f aca="false">1000*K21/$S21</f>
         <v>2591.82464454976</v>
       </c>
@@ -4327,7 +4391,7 @@
         <f aca="false">N21*N$34/100*1000</f>
         <v>132</v>
       </c>
-      <c r="P21" s="12" t="n">
+      <c r="P21" s="14" t="n">
         <f aca="false">1000*O21/$S21</f>
         <v>2443.72037914692</v>
       </c>
@@ -4343,17 +4407,17 @@
       <c r="T21" s="1" t="n">
         <v>0.45</v>
       </c>
-      <c r="U21" s="1" t="n">
-        <f aca="false">H21+F21+B21+0.8*D21+K21+O21</f>
-        <v>363.3</v>
+      <c r="U21" s="2" t="n">
+        <f aca="false">H21+F21+B21+D21+K21+O21</f>
+        <v>368.1</v>
       </c>
       <c r="V21" s="1" t="n">
-        <f aca="false">U21-$V$34*T21/100</f>
-        <v>115.8</v>
+        <f aca="false">U21-$T$42*1000*T21/100</f>
+        <v>95.45355</v>
       </c>
       <c r="W21" s="1" t="n">
         <f aca="false">ROUND(V21/S21 *100/1000, 2)</f>
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="Y21" s="1" t="n">
         <f aca="false">T21*50000/100</f>
@@ -4363,7 +4427,7 @@
         <v>84.3</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AH21" s="1" t="n">
         <v>0</v>
@@ -4381,32 +4445,32 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="16" t="n">
+      <c r="A22" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="14" t="n">
         <f aca="false">1000*B22/$S22</f>
         <v>198.137507430157</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="12" t="n">
+      <c r="D22" s="23"/>
+      <c r="E22" s="14" t="n">
         <f aca="false">1000*D22/$S22</f>
         <v>0</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="14" t="n">
         <f aca="false">1000*F22/$S22</f>
         <v>0</v>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H22" s="18" t="n">
         <v>208</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" s="14" t="n">
         <f aca="false">1000*H22/$S22</f>
         <v>4121.26015454726</v>
       </c>
@@ -4416,7 +4480,7 @@
       <c r="K22" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="L22" s="14" t="n">
         <f aca="false">1000*K22/$S22</f>
         <v>4160.88765603329</v>
       </c>
@@ -4430,7 +4494,7 @@
         <f aca="false">N22*N$34/100*1000</f>
         <v>264</v>
       </c>
-      <c r="P22" s="12" t="n">
+      <c r="P22" s="14" t="n">
         <f aca="false">1000*O22/$S22</f>
         <v>5230.83019615613</v>
       </c>
@@ -4446,17 +4510,17 @@
       <c r="T22" s="1" t="n">
         <v>0.48</v>
       </c>
-      <c r="U22" s="1" t="n">
-        <f aca="false">H22+F22+B22+0.8*D22+K22+O22</f>
+      <c r="U22" s="2" t="n">
+        <f aca="false">H22+F22+B22+D22+K22+O22</f>
         <v>692</v>
       </c>
       <c r="V22" s="1" t="n">
-        <f aca="false">U22-$V$34*T22/100</f>
-        <v>428</v>
+        <f aca="false">U22-$T$42*1000*T22/100</f>
+        <v>401.17712</v>
       </c>
       <c r="W22" s="1" t="n">
         <f aca="false">ROUND(V22/S22 *100/1000, 2)</f>
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="Y22" s="1" t="n">
         <f aca="false">T22*50000/100</f>
@@ -4466,7 +4530,7 @@
         <v>89.5</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH22" s="1" t="n">
         <v>0</v>
@@ -4484,32 +4548,32 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="12" t="n">
+      <c r="A23" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="14" t="n">
         <f aca="false">1000*B23/$S23</f>
         <v>510.538983298082</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="12" t="n">
+      <c r="D23" s="21"/>
+      <c r="E23" s="14" t="n">
         <f aca="false">1000*D23/$S23</f>
         <v>0</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F23" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="14" t="n">
         <f aca="false">1000*F23/$S23</f>
         <v>0</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="H23" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="I23" s="14" t="n">
         <f aca="false">1000*H23/$S23</f>
         <v>656.407264240391</v>
       </c>
@@ -4519,7 +4583,7 @@
       <c r="K23" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="L23" s="14" t="n">
         <f aca="false">1000*K23/$S23</f>
         <v>19692.2179272117</v>
       </c>
@@ -4533,7 +4597,7 @@
         <f aca="false">N23*N$34/100*1000</f>
         <v>132</v>
       </c>
-      <c r="P23" s="12" t="n">
+      <c r="P23" s="14" t="n">
         <f aca="false">1000*O23/$S23</f>
         <v>9627.3065421924</v>
       </c>
@@ -4549,17 +4613,17 @@
       <c r="T23" s="1" t="n">
         <v>0.13</v>
       </c>
-      <c r="U23" s="1" t="n">
-        <f aca="false">H23+F23+B23+0.8*D23+K23+O23</f>
+      <c r="U23" s="2" t="n">
+        <f aca="false">H23+F23+B23+D23+K23+O23</f>
         <v>418</v>
       </c>
       <c r="V23" s="1" t="n">
-        <f aca="false">U23-$V$34*T23/100</f>
-        <v>346.5</v>
+        <f aca="false">U23-$T$42*1000*T23/100</f>
+        <v>339.23547</v>
       </c>
       <c r="W23" s="1" t="n">
         <f aca="false">ROUND(V23/S23 *100/1000, 2)</f>
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="Y23" s="1" t="n">
         <f aca="false">T23*50000/100</f>
@@ -4569,7 +4633,7 @@
         <v>24.6</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH23" s="1" t="n">
         <v>0</v>
@@ -4587,34 +4651,34 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="16" t="n">
+      <c r="A24" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="18" t="n">
         <v>332</v>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="14" t="n">
         <f aca="false">1000*B24/$S24</f>
         <v>396.580804533444</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="19" t="n">
         <v>652</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="14" t="n">
         <f aca="false">1000*D24/$S24</f>
         <v>778.827363119896</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="18" t="n">
         <v>1961</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="14" t="n">
         <f aca="false">1000*F24/$S24</f>
         <v>2342.4546918376</v>
       </c>
-      <c r="H24" s="16" t="n">
+      <c r="H24" s="18" t="n">
         <v>913</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="I24" s="14" t="n">
         <f aca="false">1000*H24/$S24</f>
         <v>1090.59721246697</v>
       </c>
@@ -4624,7 +4688,7 @@
       <c r="K24" s="1" t="n">
         <v>1980</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="L24" s="14" t="n">
         <f aca="false">1000*K24/$S24</f>
         <v>2365.15058125367</v>
       </c>
@@ -4638,7 +4702,7 @@
         <f aca="false">N24*N$34/100*1000</f>
         <v>1628</v>
       </c>
-      <c r="P24" s="12" t="n">
+      <c r="P24" s="14" t="n">
         <f aca="false">1000*O24/$S24</f>
         <v>1944.67936680858</v>
       </c>
@@ -4654,17 +4718,17 @@
       <c r="T24" s="1" t="n">
         <v>6.23</v>
       </c>
-      <c r="U24" s="1" t="n">
-        <f aca="false">H24+F24+B24+0.8*D24+K24+O24</f>
-        <v>7335.6</v>
+      <c r="U24" s="2" t="n">
+        <f aca="false">H24+F24+B24+D24+K24+O24</f>
+        <v>7466</v>
       </c>
       <c r="V24" s="1" t="n">
-        <f aca="false">U24-$V$34*T24/100</f>
-        <v>3909.1</v>
+        <f aca="false">U24-$T$42*1000*T24/100</f>
+        <v>3691.36137</v>
       </c>
       <c r="W24" s="1" t="n">
         <f aca="false">ROUND(V24/S24 *100/1000, 2)</f>
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="Y24" s="1" t="n">
         <f aca="false">T24*50000/100</f>
@@ -4674,7 +4738,7 @@
         <v>1170.6</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH24" s="1" t="n">
         <v>1</v>
@@ -4692,34 +4756,34 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="12" t="n">
+      <c r="A25" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="14" t="n">
         <v>494</v>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="14" t="n">
         <f aca="false">1000*B25/$S25</f>
         <v>901.606282772202</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="15" t="n">
         <v>427</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="14" t="n">
         <f aca="false">1000*D25/$S25</f>
         <v>779.323649278806</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="14" t="n">
         <v>63</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="14" t="n">
         <f aca="false">1000*F25/$S25</f>
         <v>114.982177762447</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="H25" s="14" t="n">
         <v>560</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="I25" s="14" t="n">
         <f aca="false">1000*H25/$S25</f>
         <v>1022.06380233286</v>
       </c>
@@ -4729,7 +4793,7 @@
       <c r="K25" s="1" t="n">
         <v>1190</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="L25" s="14" t="n">
         <f aca="false">1000*K25/$S25</f>
         <v>2171.88557995733</v>
       </c>
@@ -4743,7 +4807,7 @@
         <f aca="false">N25*N$34/100*1000</f>
         <v>1188</v>
       </c>
-      <c r="P25" s="12" t="n">
+      <c r="P25" s="14" t="n">
         <f aca="false">1000*O25/$S25</f>
         <v>2168.23535209186</v>
       </c>
@@ -4759,17 +4823,17 @@
       <c r="T25" s="1" t="n">
         <v>4.91</v>
       </c>
-      <c r="U25" s="1" t="n">
-        <f aca="false">H25+F25+B25+0.8*D25+K25+O25</f>
-        <v>3836.6</v>
+      <c r="U25" s="2" t="n">
+        <f aca="false">H25+F25+B25+D25+K25+O25</f>
+        <v>3922</v>
       </c>
       <c r="V25" s="1" t="n">
-        <f aca="false">U25-$V$34*T25/100</f>
-        <v>1136.1</v>
+        <f aca="false">U25-$T$42*1000*T25/100</f>
+        <v>947.12429</v>
       </c>
       <c r="W25" s="1" t="n">
         <f aca="false">ROUND(V25/S25 *100/1000, 2)</f>
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="Y25" s="1" t="n">
         <f aca="false">T25*50000/100</f>
@@ -4779,7 +4843,7 @@
         <v>922.9</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH25" s="1" t="n">
         <v>1</v>
@@ -4797,34 +4861,34 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" s="16" t="n">
+      <c r="A26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="18" t="n">
         <v>136</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="14" t="n">
         <f aca="false">1000*B26/$S26</f>
         <v>641.88790560472</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="19" t="n">
         <v>84</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="14" t="n">
         <f aca="false">1000*D26/$S26</f>
         <v>396.46017699115</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="20" t="n">
         <v>24.9</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="14" t="n">
         <f aca="false">1000*F26/$S26</f>
         <v>117.522123893805</v>
       </c>
-      <c r="H26" s="16" t="n">
+      <c r="H26" s="18" t="n">
         <v>330</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="I26" s="14" t="n">
         <f aca="false">1000*H26/$S26</f>
         <v>1557.52212389381</v>
       </c>
@@ -4834,7 +4898,7 @@
       <c r="K26" s="1" t="n">
         <v>1950</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="L26" s="14" t="n">
         <f aca="false">1000*K26/$S26</f>
         <v>9203.53982300885</v>
       </c>
@@ -4848,7 +4912,7 @@
         <f aca="false">N26*N$34/100*1000</f>
         <v>924</v>
       </c>
-      <c r="P26" s="12" t="n">
+      <c r="P26" s="14" t="n">
         <f aca="false">1000*O26/$S26</f>
         <v>4361.06194690266</v>
       </c>
@@ -4864,17 +4928,17 @@
       <c r="T26" s="1" t="n">
         <v>1.63</v>
       </c>
-      <c r="U26" s="1" t="n">
-        <f aca="false">H26+F26+B26+0.8*D26+K26+O26</f>
-        <v>3432.1</v>
+      <c r="U26" s="2" t="n">
+        <f aca="false">H26+F26+B26+D26+K26+O26</f>
+        <v>3448.9</v>
       </c>
       <c r="V26" s="1" t="n">
-        <f aca="false">U26-$V$34*T26/100</f>
-        <v>2535.6</v>
+        <f aca="false">U26-$T$42*1000*T26/100</f>
+        <v>2461.31397</v>
       </c>
       <c r="W26" s="1" t="n">
         <f aca="false">ROUND(V26/S26 *100/1000, 2)</f>
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Y26" s="1" t="n">
         <f aca="false">T26*50000/100</f>
@@ -4884,7 +4948,7 @@
         <v>306.8</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH26" s="1" t="n">
         <v>1</v>
@@ -4902,34 +4966,34 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="12" t="n">
+      <c r="A27" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="14" t="n">
         <v>133</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="14" t="n">
         <f aca="false">1000*B27/$S27</f>
         <v>617.708255926284</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="14" t="n">
         <f aca="false">1000*D27/$S27</f>
         <v>139.332689306681</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F27" s="16" t="n">
         <v>1.9</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="14" t="n">
         <f aca="false">1000*F27/$S27</f>
         <v>8.82440365608977</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="H27" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="I27" s="14" t="n">
         <f aca="false">1000*H27/$S27</f>
         <v>561.975180203611</v>
       </c>
@@ -4939,7 +5003,7 @@
       <c r="K27" s="1" t="n">
         <v>620</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="L27" s="14" t="n">
         <f aca="false">1000*K27/$S27</f>
         <v>2879.5422456714</v>
       </c>
@@ -4953,7 +5017,7 @@
         <f aca="false">N27*N$34/100*1000</f>
         <v>484</v>
       </c>
-      <c r="P27" s="12" t="n">
+      <c r="P27" s="14" t="n">
         <f aca="false">1000*O27/$S27</f>
         <v>2247.90072081445</v>
       </c>
@@ -4969,17 +5033,17 @@
       <c r="T27" s="1" t="n">
         <v>2.02</v>
       </c>
-      <c r="U27" s="1" t="n">
-        <f aca="false">H27+F27+B27+0.8*D27+K27+O27</f>
-        <v>1383.9</v>
+      <c r="U27" s="2" t="n">
+        <f aca="false">H27+F27+B27+D27+K27+O27</f>
+        <v>1389.9</v>
       </c>
       <c r="V27" s="1" t="n">
-        <f aca="false">U27-$V$34*T27/100</f>
-        <v>272.9</v>
+        <f aca="false">U27-$T$42*1000*T27/100</f>
+        <v>166.02038</v>
       </c>
       <c r="W27" s="1" t="n">
         <f aca="false">ROUND(V27/S27 *100/1000, 2)</f>
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="Y27" s="1" t="n">
         <f aca="false">T27*50000/100</f>
@@ -4989,7 +5053,7 @@
         <v>380.1</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH27" s="1" t="n">
         <v>0</v>
@@ -5007,34 +5071,34 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="16" t="n">
+      <c r="A28" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="18" t="n">
         <v>76</v>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="14" t="n">
         <f aca="false">1000*B28/$S28</f>
         <v>781.105469793829</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="14" t="n">
         <f aca="false">1000*D28/$S28</f>
         <v>380.275031346996</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="14" t="n">
         <f aca="false">1000*F28/$S28</f>
         <v>0</v>
       </c>
-      <c r="H28" s="16" t="n">
+      <c r="H28" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="I28" s="14" t="n">
         <f aca="false">1000*H28/$S28</f>
         <v>195.276367448457</v>
       </c>
@@ -5044,7 +5108,7 @@
       <c r="K28" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="L28" s="14" t="n">
         <f aca="false">1000*K28/$S28</f>
         <v>4111.08141996752</v>
       </c>
@@ -5058,7 +5122,7 @@
         <f aca="false">N28*N$34/100*1000</f>
         <v>176</v>
       </c>
-      <c r="P28" s="12" t="n">
+      <c r="P28" s="14" t="n">
         <f aca="false">1000*O28/$S28</f>
         <v>1808.87582478571</v>
       </c>
@@ -5074,17 +5138,17 @@
       <c r="T28" s="1" t="n">
         <v>0.73</v>
       </c>
-      <c r="U28" s="1" t="n">
-        <f aca="false">H28+F28+B28+0.8*D28+K28+O28</f>
-        <v>700.6</v>
+      <c r="U28" s="2" t="n">
+        <f aca="false">H28+F28+B28+D28+K28+O28</f>
+        <v>708</v>
       </c>
       <c r="V28" s="1" t="n">
-        <f aca="false">U28-$V$34*T28/100</f>
-        <v>299.1</v>
+        <f aca="false">U28-$T$42*1000*T28/100</f>
+        <v>265.70687</v>
       </c>
       <c r="W28" s="1" t="n">
         <f aca="false">ROUND(V28/S28 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="Y28" s="1" t="n">
         <f aca="false">T28*50000/100</f>
@@ -5094,7 +5158,7 @@
         <v>136.8</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH28" s="1" t="n">
         <v>0</v>
@@ -5112,34 +5176,34 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="12" t="n">
+      <c r="A29" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="14" t="n">
         <f aca="false">1000*B29/$S29</f>
         <v>641.137728041033</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="14" t="n">
         <f aca="false">1000*D29/$S29</f>
         <v>271.997824017408</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="14" t="n">
         <f aca="false">1000*F29/$S29</f>
         <v>7.77136640049737</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="H29" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="I29" s="14" t="n">
         <f aca="false">1000*H29/$S29</f>
         <v>1457.13120009326</v>
       </c>
@@ -5149,7 +5213,7 @@
       <c r="K29" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="L29" s="14" t="n">
         <f aca="false">1000*K29/$S29</f>
         <v>5828.52480037303</v>
       </c>
@@ -5163,7 +5227,7 @@
         <f aca="false">N29*N$34/100*1000</f>
         <v>176</v>
       </c>
-      <c r="P29" s="12" t="n">
+      <c r="P29" s="14" t="n">
         <f aca="false">1000*O29/$S29</f>
         <v>3419.40121621884</v>
       </c>
@@ -5179,17 +5243,17 @@
       <c r="T29" s="1" t="n">
         <v>0.38</v>
       </c>
-      <c r="U29" s="1" t="n">
-        <f aca="false">H29+F29+B29+0.8*D29+K29+O29</f>
-        <v>595.6</v>
+      <c r="U29" s="2" t="n">
+        <f aca="false">H29+F29+B29+D29+K29+O29</f>
+        <v>598.4</v>
       </c>
       <c r="V29" s="1" t="n">
-        <f aca="false">U29-$V$34*T29/100</f>
-        <v>386.6</v>
+        <f aca="false">U29-$T$42*1000*T29/100</f>
+        <v>368.16522</v>
       </c>
       <c r="W29" s="1" t="n">
         <f aca="false">ROUND(V29/S29 *100/1000, 2)</f>
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="Y29" s="1" t="n">
         <f aca="false">T29*50000/100</f>
@@ -5199,7 +5263,7 @@
         <v>70.5</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH29" s="1" t="n">
         <v>0</v>
@@ -5217,34 +5281,34 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="16" t="n">
+      <c r="A30" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="18" t="n">
         <v>683</v>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="14" t="n">
         <f aca="false">1000*B30/$S30</f>
         <v>562.985554433614</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="19" t="n">
         <v>830</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="14" t="n">
         <f aca="false">1000*D30/$S30</f>
         <v>684.155212562079</v>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="F30" s="20" t="n">
         <v>240.6</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="G30" s="14" t="n">
         <f aca="false">1000*F30/$S30</f>
         <v>198.32258330414</v>
       </c>
-      <c r="H30" s="16" t="n">
+      <c r="H30" s="18" t="n">
         <v>2151</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="I30" s="14" t="n">
         <f aca="false">1000*H30/$S30</f>
         <v>1773.033568941</v>
       </c>
@@ -5254,7 +5318,7 @@
       <c r="K30" s="1" t="n">
         <v>9330</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="L30" s="14" t="n">
         <f aca="false">1000*K30/$S30</f>
         <v>7690.56401590867</v>
       </c>
@@ -5268,7 +5332,7 @@
         <f aca="false">N30*N$34/100*1000</f>
         <v>4532</v>
       </c>
-      <c r="P30" s="12" t="n">
+      <c r="P30" s="14" t="n">
         <f aca="false">1000*O30/$S30</f>
         <v>3735.65231726668</v>
       </c>
@@ -5284,17 +5348,17 @@
       <c r="T30" s="1" t="n">
         <v>8.98</v>
       </c>
-      <c r="U30" s="1" t="n">
-        <f aca="false">H30+F30+B30+0.8*D30+K30+O30</f>
-        <v>17600.6</v>
+      <c r="U30" s="2" t="n">
+        <f aca="false">H30+F30+B30+D30+K30+O30</f>
+        <v>17766.6</v>
       </c>
       <c r="V30" s="1" t="n">
-        <f aca="false">U30-$V$34*T30/100</f>
-        <v>12661.6</v>
+        <f aca="false">U30-$T$42*1000*T30/100</f>
+        <v>12325.78862</v>
       </c>
       <c r="W30" s="1" t="n">
         <f aca="false">ROUND(V30/S30 *100/1000, 2)</f>
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" s="1" t="n">
         <f aca="false">T30*50000/100</f>
@@ -5304,7 +5368,7 @@
         <v>1687.2</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH30" s="1" t="n">
         <v>9</v>
@@ -5322,34 +5386,34 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="12" t="n">
+      <c r="A31" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="14" t="n">
         <v>189</v>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="14" t="n">
         <f aca="false">1000*B31/$S31</f>
         <v>341.958899796996</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="15" t="n">
         <v>601</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="14" t="n">
         <f aca="false">1000*D31/$S31</f>
         <v>1087.39311522748</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F31" s="16" t="n">
         <v>245.1</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="G31" s="14" t="n">
         <f aca="false">1000*F31/$S31</f>
         <v>443.460985927215</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="H31" s="14" t="n">
         <v>712</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="I31" s="14" t="n">
         <f aca="false">1000*H31/$S31</f>
         <v>1288.22611987016</v>
       </c>
@@ -5359,7 +5423,7 @@
       <c r="K31" s="1" t="n">
         <v>1160</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="L31" s="14" t="n">
         <f aca="false">1000*K31/$S31</f>
         <v>2098.79536383341</v>
       </c>
@@ -5373,7 +5437,7 @@
         <f aca="false">N31*N$34/100*1000</f>
         <v>1056</v>
       </c>
-      <c r="P31" s="12" t="n">
+      <c r="P31" s="14" t="n">
         <f aca="false">1000*O31/$S31</f>
         <v>1910.62750362766</v>
       </c>
@@ -5389,17 +5453,17 @@
       <c r="T31" s="1" t="n">
         <v>3.2</v>
       </c>
-      <c r="U31" s="1" t="n">
-        <f aca="false">H31+F31+B31+0.8*D31+K31+O31</f>
-        <v>3842.9</v>
+      <c r="U31" s="2" t="n">
+        <f aca="false">H31+F31+B31+D31+K31+O31</f>
+        <v>3963.1</v>
       </c>
       <c r="V31" s="1" t="n">
-        <f aca="false">U31-$V$34*T31/100</f>
-        <v>2082.9</v>
+        <f aca="false">U31-$T$42*1000*T31/100</f>
+        <v>2024.2808</v>
       </c>
       <c r="W31" s="1" t="n">
         <f aca="false">ROUND(V31/S31 *100/1000, 2)</f>
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="Y31" s="1" t="n">
         <f aca="false">T31*50000/100</f>
@@ -5409,7 +5473,7 @@
         <v>601.2</v>
       </c>
       <c r="AG31" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH31" s="1" t="n">
         <v>1</v>
@@ -5426,70 +5490,61 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="32" s="26" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="23" t="n">
+    <row r="32" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="25" t="n">
         <v>5847</v>
       </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="24" t="n">
+      <c r="C32" s="25"/>
+      <c r="D32" s="26" t="n">
         <v>9557</v>
       </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="25" t="n">
+      <c r="E32" s="25"/>
+      <c r="F32" s="27" t="n">
         <v>8334.6</v>
       </c>
-      <c r="G32" s="25"/>
-      <c r="H32" s="23" t="n">
+      <c r="G32" s="27"/>
+      <c r="H32" s="25" t="n">
         <v>26264</v>
       </c>
-      <c r="I32" s="23"/>
-      <c r="J32" s="26" t="n">
+      <c r="I32" s="25"/>
+      <c r="K32" s="1" t="n">
+        <f aca="false">SUM(K5:K31)</f>
+        <v>47600</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <f aca="false">SUM(O5:O31)</f>
+        <v>44088</v>
+      </c>
+      <c r="Q32" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="K32" s="26" t="n">
-        <f aca="false">J32*J$34*1000/100</f>
-        <v>93000</v>
-      </c>
-      <c r="M32" s="26" t="n">
-        <v>299</v>
-      </c>
-      <c r="N32" s="26" t="n">
+      <c r="S32" s="1"/>
+      <c r="T32" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="O32" s="26" t="n">
-        <f aca="false">N32*N$34/100*1000</f>
-        <v>44000</v>
-      </c>
-      <c r="Q32" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S32" s="1"/>
-      <c r="T32" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="U32" s="26" t="n">
-        <f aca="false">H32+F32+B32+0.8*D32+K32+O32</f>
-        <v>185091.2</v>
-      </c>
-      <c r="V32" s="26" t="n">
-        <f aca="false">U32-$V$34*T32/100</f>
-        <v>130091.2</v>
-      </c>
-      <c r="W32" s="26" t="e">
+      <c r="U32" s="2" t="n">
+        <f aca="false">H32+F32+B32+D32+K32+O32</f>
+        <v>141690.6</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <f aca="false">U32-$T$42*1000*T32/100</f>
+        <v>81102.5</v>
+      </c>
+      <c r="W32" s="28" t="e">
         <f aca="false">ROUND(V32/S32 *100/1000, 2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y32" s="26" t="n">
+      <c r="Y32" s="28" t="n">
         <f aca="false">T32*50000/100</f>
         <v>50000</v>
       </c>
-      <c r="AB32" s="26" t="n">
+      <c r="AB32" s="28" t="n">
         <v>18796</v>
       </c>
-      <c r="AK32" s="26" t="n">
+      <c r="AK32" s="28" t="n">
         <f aca="false">SUM(AK5:AK31)</f>
         <v>47600</v>
       </c>
@@ -5520,170 +5575,203 @@
         <f aca="false">SUM(O5:O31)</f>
         <v>44088</v>
       </c>
-      <c r="U33" s="1" t="n">
+      <c r="U33" s="2" t="n">
         <f aca="false">SUM(U5:U31)</f>
-        <v>139782.3</v>
+        <v>141588.1</v>
       </c>
       <c r="V33" s="1" t="n">
         <f aca="false">SUM(V5:V31)</f>
-        <v>84600.8</v>
+        <v>80800.05927</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J34" s="27" t="n">
+      <c r="J34" s="29" t="n">
         <v>93</v>
       </c>
-      <c r="N34" s="27" t="n">
+      <c r="N34" s="29" t="n">
         <v>44</v>
-      </c>
-      <c r="V34" s="1" t="n">
-        <v>55000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="29" t="n">
-        <v>103453.5</v>
-      </c>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
+      <c r="B35" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="31" t="n">
+        <f aca="false">SUM(B32:O32)</f>
+        <v>141690.6</v>
+      </c>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="28"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="28"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="S37" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="T37" s="31" t="n">
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="S37" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="T37" s="33" t="n">
         <v>192.8</v>
       </c>
-      <c r="U37" s="32"/>
-      <c r="V37" s="32"/>
+      <c r="U37" s="34"/>
+      <c r="V37" s="35"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S38" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="T38" s="30" t="n">
+      <c r="S38" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="T38" s="32" t="n">
         <f aca="false">T37*0.7</f>
         <v>134.96</v>
       </c>
-      <c r="U38" s="32"/>
-      <c r="V38" s="32"/>
+      <c r="U38" s="34"/>
+      <c r="V38" s="35"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S39" s="30"/>
-      <c r="T39" s="30"/>
-      <c r="U39" s="32"/>
-      <c r="V39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="34"/>
+      <c r="V39" s="35"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S40" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="T40" s="30" t="n">
-        <v>55</v>
-      </c>
-      <c r="U40" s="32"/>
-      <c r="V40" s="32"/>
+      <c r="S40" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="T40" s="37" t="n">
+        <v>20</v>
+      </c>
+      <c r="U40" s="34"/>
+      <c r="V40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S41" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="T41" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="U41" s="32"/>
-      <c r="V41" s="32"/>
+      <c r="Q41" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="S41" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="T41" s="36" t="n">
+        <f aca="false">U33/1000 -T40</f>
+        <v>121.5881</v>
+      </c>
+      <c r="U41" s="34"/>
+      <c r="V41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="S42" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="T42" s="30" t="n">
-        <f aca="false">T37+T41</f>
-        <v>211.8</v>
-      </c>
-      <c r="U42" s="32"/>
-      <c r="V42" s="32"/>
+      <c r="S42" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="T42" s="36" t="n">
+        <f aca="false">T41-T43-T44</f>
+        <v>60.5881</v>
+      </c>
+      <c r="U42" s="34"/>
+      <c r="V42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="S43" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="T43" s="30" t="n">
-        <f aca="false">T38-T40</f>
-        <v>79.96</v>
-      </c>
-      <c r="U43" s="32"/>
-      <c r="V43" s="32"/>
+      <c r="S43" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="T43" s="37" t="n">
+        <v>35</v>
+      </c>
+      <c r="U43" s="34"/>
+      <c r="V43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="S44" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="T44" s="30" t="n">
-        <f aca="false">T43/T42</f>
-        <v>0.37752596789424</v>
-      </c>
-      <c r="U44" s="32"/>
-      <c r="V44" s="32"/>
+      <c r="S44" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="T44" s="37" t="n">
+        <v>26</v>
+      </c>
+      <c r="U44" s="34"/>
+      <c r="V44" s="35"/>
     </row>
-    <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="33"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="V47" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y47" s="1" t="s">
-        <v>95</v>
-      </c>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="35"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+      <c r="S45" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="T45" s="36" t="n">
+        <f aca="false">T37+T43</f>
+        <v>227.8</v>
+      </c>
+      <c r="U45" s="34"/>
+      <c r="V45" s="35"/>
     </row>
-    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="33"/>
-      <c r="K49" s="1" t="s">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="35"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="S46" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="T46" s="36" t="n">
+        <f aca="false">T38-T42</f>
+        <v>74.3719</v>
+      </c>
+      <c r="U46" s="34"/>
+      <c r="V46" s="35"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="S47" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="T47" s="36" t="n">
+        <f aca="false">T46/T45</f>
+        <v>0.326478928884987</v>
+      </c>
+      <c r="U47" s="34"/>
+      <c r="V47" s="35"/>
+    </row>
+    <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="39"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="V50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y50" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="39"/>
+      <c r="K52" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O49" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P49" s="1"/>
+      <c r="O52" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P52" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="126">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -46,6 +46,9 @@
     <t xml:space="preserve">GNI</t>
   </si>
   <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
     <t xml:space="preserve">GDP 2025 (Eurostat)</t>
   </si>
   <si>
@@ -79,12 +82,18 @@
     <t xml:space="preserve">Share s</t>
   </si>
   <si>
+    <t xml:space="preserve">already NOR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Our scenario</t>
   </si>
   <si>
     <t xml:space="preserve">Scenario 0</t>
   </si>
   <si>
+    <t xml:space="preserve">+ externalité</t>
+  </si>
+  <si>
     <t xml:space="preserve">proj.</t>
   </si>
   <si>
@@ -94,6 +103,9 @@
     <t xml:space="preserve">(%)</t>
   </si>
   <si>
+    <t xml:space="preserve">base</t>
+  </si>
+  <si>
     <t xml:space="preserve">(EUR bn)</t>
   </si>
   <si>
@@ -106,6 +118,9 @@
     <t xml:space="preserve">50 bn répartis par s</t>
   </si>
   <si>
+    <t xml:space="preserve">table</t>
+  </si>
+  <si>
     <t xml:space="preserve">A 3\% DST</t>
   </si>
   <si>
@@ -121,18 +136,39 @@
     <t xml:space="preserve">Luxury VAT</t>
   </si>
   <si>
+    <t xml:space="preserve">table_s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 NOR scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status-quo scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_sscenario</t>
+  </si>
+  <si>
     <t xml:space="preserve">Austria</t>
   </si>
   <si>
     <t xml:space="preserve">Austria        </t>
   </si>
   <si>
+    <t xml:space="preserve">Austria     </t>
+  </si>
+  <si>
     <t xml:space="preserve">Belgium</t>
   </si>
   <si>
     <t xml:space="preserve">Belgium        </t>
   </si>
   <si>
+    <t xml:space="preserve">Belgium     </t>
+  </si>
+  <si>
     <t xml:space="preserve">Bulgaria</t>
   </si>
   <si>
@@ -157,12 +193,18 @@
     <t xml:space="preserve">Czechia        </t>
   </si>
   <si>
+    <t xml:space="preserve">Czechia     </t>
+  </si>
+  <si>
     <t xml:space="preserve">Denmark</t>
   </si>
   <si>
     <t xml:space="preserve">Denmark        </t>
   </si>
   <si>
+    <t xml:space="preserve">Denmark     </t>
+  </si>
+  <si>
     <t xml:space="preserve">Estonia</t>
   </si>
   <si>
@@ -181,18 +223,27 @@
     <t xml:space="preserve">France         </t>
   </si>
   <si>
+    <t xml:space="preserve">France      </t>
+  </si>
+  <si>
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
     <t xml:space="preserve">Germany        </t>
   </si>
   <si>
+    <t xml:space="preserve">Germany     </t>
+  </si>
+  <si>
     <t xml:space="preserve">Greece</t>
   </si>
   <si>
     <t xml:space="preserve">Greece         </t>
   </si>
   <si>
+    <t xml:space="preserve">Greece      </t>
+  </si>
+  <si>
     <t xml:space="preserve">Hungary</t>
   </si>
   <si>
@@ -205,12 +256,21 @@
     <t xml:space="preserve">Ireland        </t>
   </si>
   <si>
+    <t xml:space="preserve">Ireland     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t xml:space="preserve">Italy</t>
   </si>
   <si>
     <t xml:space="preserve">Italy          </t>
   </si>
   <si>
+    <t xml:space="preserve">Italy       </t>
+  </si>
+  <si>
     <t xml:space="preserve">Latvia</t>
   </si>
   <si>
@@ -241,18 +301,27 @@
     <t xml:space="preserve">Netherlands    </t>
   </si>
   <si>
+    <t xml:space="preserve">Netherlands </t>
+  </si>
+  <si>
     <t xml:space="preserve">Poland</t>
   </si>
   <si>
     <t xml:space="preserve">Poland         </t>
   </si>
   <si>
+    <t xml:space="preserve">Poland      </t>
+  </si>
+  <si>
     <t xml:space="preserve">Portugal</t>
   </si>
   <si>
     <t xml:space="preserve">Portugal       </t>
   </si>
   <si>
+    <t xml:space="preserve">Portugal    </t>
+  </si>
+  <si>
     <t xml:space="preserve">Romania</t>
   </si>
   <si>
@@ -277,10 +346,16 @@
     <t xml:space="preserve">Spain          </t>
   </si>
   <si>
+    <t xml:space="preserve">Spain       </t>
+  </si>
+  <si>
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
     <t xml:space="preserve">Sweden         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden      </t>
   </si>
   <si>
     <t xml:space="preserve">European Union</t>
@@ -329,11 +404,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="0.00E+00"/>
+    <numFmt numFmtId="168" formatCode="General"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -415,7 +491,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,7 +501,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8A65"/>
-        <bgColor rgb="FFFF9800"/>
+        <bgColor rgb="FFFFAB91"/>
       </patternFill>
     </fill>
     <fill>
@@ -468,6 +544,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00A933"/>
         <bgColor rgb="FF008000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFAB91"/>
+        <bgColor rgb="FFFF8A65"/>
       </patternFill>
     </fill>
     <fill>
@@ -529,7 +611,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -598,6 +680,10 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -614,6 +700,10 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -624,6 +714,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -650,19 +744,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -670,19 +768,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -738,7 +828,7 @@
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFFAB91"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCDD2"/>
       <rgbColor rgb="FF3366FF"/>
@@ -778,7 +868,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$C$1:$C$1</c:f>
+              <c:f>Combined_2!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -828,7 +918,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Combined_2!$A$5:$A$31</c:f>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
@@ -917,7 +1007,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Combined_2!$C$5:$C$31</c:f>
+              <c:f>Combined_2!$C$8:$C$34</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="27"/>
@@ -1011,7 +1101,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$E$1:$E$1</c:f>
+              <c:f>Combined_2!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1061,7 +1151,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Combined_2!$A$5:$A$31</c:f>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
@@ -1150,7 +1240,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Combined_2!$E$5:$E$31</c:f>
+              <c:f>Combined_2!$E$8:$E$34</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="27"/>
@@ -1244,7 +1334,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$G$1:$G$1</c:f>
+              <c:f>Combined_2!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1294,7 +1384,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Combined_2!$A$5:$A$31</c:f>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
@@ -1383,7 +1473,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Combined_2!$G$5:$G$31</c:f>
+              <c:f>Combined_2!$G$8:$G$34</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="27"/>
@@ -1477,7 +1567,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$I$1:$I$1</c:f>
+              <c:f>Combined_2!$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1527,7 +1617,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Combined_2!$A$5:$A$31</c:f>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
@@ -1616,7 +1706,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Combined_2!$I$5:$I$31</c:f>
+              <c:f>Combined_2!$I$8:$I$34</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="27"/>
@@ -1710,11 +1800,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$L$1:$L$1</c:f>
+              <c:f>Combined_2!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Aviation carbon tax</c:v>
+                  <c:v/>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1760,7 +1850,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Combined_2!$A$5:$A$31</c:f>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
@@ -1849,90 +1939,90 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Combined_2!$L$5:$L$31</c:f>
+              <c:f>Combined_2!$K$8:$K$34</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>4657.15952487168</c:v>
+                  <c:v>323</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2169.79643364368</c:v>
+                  <c:v>187</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5158.47996790279</c:v>
+                  <c:v>45.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6499.28165834303</c:v>
+                  <c:v>64.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13187.8126421101</c:v>
+                  <c:v>49.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1933.44553176343</c:v>
+                  <c:v>74.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3243.71494347899</c:v>
+                  <c:v>192.1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>29127.1562186479</c:v>
+                  <c:v>153</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2819.03001875438</c:v>
+                  <c:v>122.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2089.57681797067</c:v>
+                  <c:v>914.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1716.04864783411</c:v>
+                  <c:v>1088</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14042.3814552109</c:v>
+                  <c:v>431.8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2484.48873250786</c:v>
+                  <c:v>62.9</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2905.88937217333</c:v>
+                  <c:v>159.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3919.55809876625</c:v>
+                  <c:v>1208.7</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5442.1768707483</c:v>
+                  <c:v>30.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2591.82464454976</c:v>
+                  <c:v>23.8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4160.88765603329</c:v>
+                  <c:v>35.7</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19692.2179272117</c:v>
+                  <c:v>45.9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2365.15058125367</c:v>
+                  <c:v>336.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2171.88557995733</c:v>
+                  <c:v>202.3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9203.53982300885</c:v>
+                  <c:v>331.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2879.5422456714</c:v>
+                  <c:v>105.4</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4111.08141996752</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5828.52480037303</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7690.56401590867</c:v>
+                  <c:v>1586.1</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2098.79536383341</c:v>
+                  <c:v>197.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1943,7 +2033,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$P$1:$P$1</c:f>
+              <c:f>Combined_2!$R$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1993,7 +2083,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Combined_2!$A$5:$A$31</c:f>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
@@ -2082,90 +2172,90 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Combined_2!$P$5:$P$31</c:f>
+              <c:f>Combined_2!$R$8:$R$34</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>3559.05033163878</c:v>
+                  <c:v>3300.2103075196</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2864.13129240966</c:v>
+                  <c:v>2629.00426069118</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4203.20589977264</c:v>
+                  <c:v>4157.3527445024</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6020.38722035986</c:v>
+                  <c:v>5349.93500718342</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10004.5475216007</c:v>
+                  <c:v>9276.94406548431</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2900.16829764515</c:v>
+                  <c:v>2749.00801061637</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1768.25522582571</c:v>
+                  <c:v>1639.65484576566</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2847.98860804557</c:v>
+                  <c:v>2200.71846985339</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1722.74056701657</c:v>
+                  <c:v>1544.20199916212</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3537.5214977838</c:v>
+                  <c:v>3274.96500541426</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2276.98204959488</c:v>
+                  <c:v>2104.09014832559</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5108.33089158065</c:v>
+                  <c:v>4736.81591764751</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2659.07442722462</c:v>
+                  <c:v>2283.04370014235</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1768.2645966842</c:v>
+                  <c:v>1597.62088036082</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4584.39453577217</c:v>
+                  <c:v>4235.98937143739</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2660.61980347695</c:v>
+                  <c:v>2055.93348450491</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2443.72037914692</c:v>
+                  <c:v>2014.21800947867</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5230.83019615613</c:v>
+                  <c:v>4850.40618189023</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9627.3065421924</c:v>
+                  <c:v>8927.13879366932</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1944.67936680858</c:v>
+                  <c:v>1787.00266139166</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2168.23535209186</c:v>
+                  <c:v>1985.72395881813</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4361.06194690266</c:v>
+                  <c:v>4108.08259587021</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2247.90072081445</c:v>
+                  <c:v>2021.25287954225</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1808.87582478571</c:v>
+                  <c:v>1817.09798762565</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3419.40121621884</c:v>
+                  <c:v>2906.49103378602</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3735.65231726668</c:v>
+                  <c:v>3463.96851237455</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1910.62750362766</c:v>
+                  <c:v>1747.0662097565</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2173,11 +2263,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="36144290"/>
-        <c:axId val="94750663"/>
+        <c:axId val="98294469"/>
+        <c:axId val="91160820"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="36144290"/>
+        <c:axId val="98294469"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2209,7 +2299,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94750663"/>
+        <c:crossAx val="91160820"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2217,7 +2307,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94750663"/>
+        <c:axId val="91160820"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2247,7 +2337,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36144290"/>
+        <c:crossAx val="98294469"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2302,15 +2392,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>700560</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>97200</xdr:rowOff>
+      <xdr:colOff>713880</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>84240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1158480</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>39600</xdr:rowOff>
+      <xdr:colOff>1171440</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>26280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2318,8 +2408,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2460960" y="7986600"/>
-        <a:ext cx="10059120" cy="5657400"/>
+        <a:off x="2474280" y="9185040"/>
+        <a:ext cx="10058760" cy="5657040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2443,20 +2533,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD52"/>
+  <dimension ref="A1:XFA55"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="15.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="2" width="10.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="11.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16341" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="10.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="22.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="11.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" s="5" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2482,152 +2574,167 @@
       <c r="J1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="6"/>
-      <c r="AB1" s="5" t="s">
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="AF1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="XFD1" s="1"/>
+      <c r="AG1" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" s="8" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="8" t="s">
         <v>14</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="1"/>
       <c r="T2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="6"/>
+      <c r="U2" s="1"/>
       <c r="V2" s="8" t="s">
         <v>19</v>
       </c>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="Y2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="XFD2" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG2" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" s="8" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="B3" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="S3" s="1"/>
-      <c r="T3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="V3" s="9"/>
-      <c r="W3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="Y3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="XFD3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG3" s="8" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I4" s="11"/>
       <c r="K4" s="11" t="s">
         <v>5</v>
       </c>
       <c r="L4" s="11"/>
-      <c r="O4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" s="11"/>
-      <c r="S4" s="1"/>
-      <c r="U4" s="2"/>
-      <c r="AB4" s="11"/>
-      <c r="XDM4" s="11"/>
-      <c r="XDN4" s="11"/>
-      <c r="XDO4" s="11"/>
-      <c r="XDP4" s="11"/>
-      <c r="XDQ4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="P4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="U4" s="1"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="AG4" s="11"/>
       <c r="XDR4" s="11"/>
       <c r="XDS4" s="11"/>
       <c r="XDT4" s="11"/>
@@ -2659,3125 +2766,4293 @@
       <c r="XET4" s="11"/>
       <c r="XEU4" s="11"/>
       <c r="XEV4" s="11"/>
-      <c r="XFD4" s="1"/>
+      <c r="XEW4" s="11"/>
+      <c r="XEX4" s="11"/>
+      <c r="XEY4" s="11"/>
+      <c r="XEZ4" s="11"/>
+      <c r="XFA4" s="11"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>141</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <f aca="false">1000*B5/$S5</f>
-        <v>345.61025947732</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>330</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <f aca="false">1000*D5/$S5</f>
-        <v>808.87507537245</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <f aca="false">1000*F5/$S5</f>
-        <v>64.710006029796</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>920</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <f aca="false">1000*H5/$S5</f>
-        <v>2255.04566467471</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="L5" s="14" t="n">
-        <f aca="false">1000*K5/$S5</f>
-        <v>4657.15952487168</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <f aca="false">N5*N$34/100*1000</f>
-        <v>1452</v>
-      </c>
-      <c r="P5" s="14" t="n">
-        <f aca="false">1000*O5/$S5</f>
-        <v>3559.05033163878</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>407.974</v>
-      </c>
-      <c r="T5" s="1" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <f aca="false">H5+F5+B5+0.8*D5+K5+O5</f>
-        <v>4703.4</v>
-      </c>
-      <c r="V5" s="1" t="n">
-        <f aca="false">U5-$T$42*1000*T5/100</f>
-        <v>3043.28606</v>
-      </c>
-      <c r="W5" s="1" t="n">
-        <f aca="false">V5/S5</f>
-        <v>7.45950982170432</v>
-      </c>
-      <c r="Y5" s="1" t="n">
-        <f aca="false">T5*50000/100</f>
-        <v>1370</v>
-      </c>
-      <c r="AB5" s="1" t="n">
-        <v>514.3</v>
-      </c>
-      <c r="AG5" s="1" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="AH5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ5" s="1" t="n">
-        <f aca="false">AH5+AI5/100</f>
-        <v>1.9</v>
-      </c>
-      <c r="AK5" s="1" t="n">
-        <f aca="false">AJ5*1000</f>
-        <v>1900</v>
-      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="R5" s="11"/>
+      <c r="U5" s="1"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="AG5" s="11"/>
+      <c r="XDR5" s="11"/>
+      <c r="XDS5" s="11"/>
+      <c r="XDT5" s="11"/>
+      <c r="XDU5" s="11"/>
+      <c r="XDV5" s="11"/>
+      <c r="XDW5" s="11"/>
+      <c r="XDX5" s="11"/>
+      <c r="XDY5" s="11"/>
+      <c r="XDZ5" s="11"/>
+      <c r="XEA5" s="11"/>
+      <c r="XEB5" s="11"/>
+      <c r="XEC5" s="11"/>
+      <c r="XED5" s="11"/>
+      <c r="XEE5" s="11"/>
+      <c r="XEF5" s="11"/>
+      <c r="XEG5" s="11"/>
+      <c r="XEH5" s="11"/>
+      <c r="XEI5" s="11"/>
+      <c r="XEJ5" s="11"/>
+      <c r="XEK5" s="11"/>
+      <c r="XEL5" s="11"/>
+      <c r="XEM5" s="11"/>
+      <c r="XEN5" s="11"/>
+      <c r="XEO5" s="11"/>
+      <c r="XEP5" s="11"/>
+      <c r="XEQ5" s="11"/>
+      <c r="XER5" s="11"/>
+      <c r="XES5" s="11"/>
+      <c r="XET5" s="11"/>
+      <c r="XEU5" s="11"/>
+      <c r="XEV5" s="11"/>
+      <c r="XEW5" s="11"/>
+      <c r="XEX5" s="11"/>
+      <c r="XEY5" s="11"/>
+      <c r="XEZ5" s="11"/>
+      <c r="XFA5" s="11"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>200</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <f aca="false">1000*B6/$S6</f>
-        <v>394.508442480669</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>184</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <f aca="false">1000*D6/$S6</f>
-        <v>362.947767082216</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <f aca="false">1000*F6/$S6</f>
-        <v>120.522329177844</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>722</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <f aca="false">1000*H6/$S6</f>
-        <v>1424.17547735522</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>1100</v>
-      </c>
-      <c r="L6" s="14" t="n">
-        <f aca="false">1000*K6/$S6</f>
-        <v>2169.79643364368</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <f aca="false">N6*N$34/100*1000</f>
-        <v>1452</v>
-      </c>
-      <c r="P6" s="14" t="n">
-        <f aca="false">1000*O6/$S6</f>
-        <v>2864.13129240966</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="S6" s="1" t="n">
-        <v>506.96</v>
-      </c>
-      <c r="T6" s="1" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <f aca="false">H6+F6+B6+0.8*D6+K6+O6</f>
-        <v>3682.3</v>
-      </c>
-      <c r="V6" s="1" t="n">
-        <f aca="false">U6-$T$42*1000*T6/100</f>
-        <v>1610.18698</v>
-      </c>
-      <c r="W6" s="1" t="n">
-        <f aca="false">V6/S6</f>
-        <v>3.17616178791226</v>
-      </c>
-      <c r="Y6" s="1" t="n">
-        <f aca="false">T6*50000/100</f>
-        <v>1710</v>
-      </c>
-      <c r="AB6" s="1" t="n">
-        <v>642</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" s="1" t="n">
-        <f aca="false">AH6+AI6/100</f>
-        <v>1.1</v>
-      </c>
-      <c r="AK6" s="1" t="n">
-        <f aca="false">AJ6*1000</f>
-        <v>1100</v>
-      </c>
+    <row r="6" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="U6" s="1"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG6" s="11"/>
+      <c r="XDR6" s="11"/>
+      <c r="XDS6" s="11"/>
+      <c r="XDT6" s="11"/>
+      <c r="XDU6" s="11"/>
+      <c r="XDV6" s="11"/>
+      <c r="XDW6" s="11"/>
+      <c r="XDX6" s="11"/>
+      <c r="XDY6" s="11"/>
+      <c r="XDZ6" s="11"/>
+      <c r="XEA6" s="11"/>
+      <c r="XEB6" s="11"/>
+      <c r="XEC6" s="11"/>
+      <c r="XED6" s="11"/>
+      <c r="XEE6" s="11"/>
+      <c r="XEF6" s="11"/>
+      <c r="XEG6" s="11"/>
+      <c r="XEH6" s="11"/>
+      <c r="XEI6" s="11"/>
+      <c r="XEJ6" s="11"/>
+      <c r="XEK6" s="11"/>
+      <c r="XEL6" s="11"/>
+      <c r="XEM6" s="11"/>
+      <c r="XEN6" s="11"/>
+      <c r="XEO6" s="11"/>
+      <c r="XEP6" s="11"/>
+      <c r="XEQ6" s="11"/>
+      <c r="XER6" s="11"/>
+      <c r="XES6" s="11"/>
+      <c r="XET6" s="11"/>
+      <c r="XEU6" s="11"/>
+      <c r="XEV6" s="11"/>
+      <c r="XEW6" s="11"/>
+      <c r="XEX6" s="11"/>
+      <c r="XEY6" s="11"/>
+      <c r="XEZ6" s="11"/>
+      <c r="XFA6" s="11"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>38</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <f aca="false">1000*B7/$S7</f>
-        <v>726.008291778911</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <f aca="false">1000*D7/$S7</f>
-        <v>343.898664526853</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <f aca="false">1000*F7/$S7</f>
-        <v>3.82109627252059</v>
-      </c>
-      <c r="H7" s="14" t="n">
+    <row r="7" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="U7" s="1"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="0"/>
+      <c r="Z7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="14" t="n">
-        <f aca="false">1000*H7/$S7</f>
-        <v>764.219254504117</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>270</v>
-      </c>
-      <c r="L7" s="14" t="n">
-        <f aca="false">1000*K7/$S7</f>
-        <v>5158.47996790279</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <f aca="false">N7*N$34/100*1000</f>
-        <v>220</v>
-      </c>
-      <c r="P7" s="14" t="n">
-        <f aca="false">1000*O7/$S7</f>
-        <v>4203.20589977264</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>52.341</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <f aca="false">H7+F7+B7+0.8*D7+K7+O7</f>
-        <v>582.6</v>
-      </c>
-      <c r="V7" s="1" t="n">
-        <f aca="false">U7-$T$42*1000*T7/100</f>
-        <v>206.95378</v>
-      </c>
-      <c r="W7" s="1" t="n">
-        <f aca="false">V7/S7</f>
-        <v>3.95395158671023</v>
-      </c>
-      <c r="Y7" s="1" t="n">
-        <f aca="false">T7*50000/100</f>
-        <v>310</v>
-      </c>
-      <c r="AB7" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="AG7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ7" s="1" t="n">
-        <f aca="false">AH7+AI7/100</f>
-        <v>0.27</v>
-      </c>
-      <c r="AK7" s="1" t="n">
-        <f aca="false">AJ7*1000</f>
-        <v>270</v>
-      </c>
+      <c r="AC7" s="0"/>
+      <c r="AD7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG7" s="11"/>
+      <c r="XDR7" s="11"/>
+      <c r="XDS7" s="11"/>
+      <c r="XDT7" s="11"/>
+      <c r="XDU7" s="11"/>
+      <c r="XDV7" s="11"/>
+      <c r="XDW7" s="11"/>
+      <c r="XDX7" s="11"/>
+      <c r="XDY7" s="11"/>
+      <c r="XDZ7" s="11"/>
+      <c r="XEA7" s="11"/>
+      <c r="XEB7" s="11"/>
+      <c r="XEC7" s="11"/>
+      <c r="XED7" s="11"/>
+      <c r="XEE7" s="11"/>
+      <c r="XEF7" s="11"/>
+      <c r="XEG7" s="11"/>
+      <c r="XEH7" s="11"/>
+      <c r="XEI7" s="11"/>
+      <c r="XEJ7" s="11"/>
+      <c r="XEK7" s="11"/>
+      <c r="XEL7" s="11"/>
+      <c r="XEM7" s="11"/>
+      <c r="XEN7" s="11"/>
+      <c r="XEO7" s="11"/>
+      <c r="XEP7" s="11"/>
+      <c r="XEQ7" s="11"/>
+      <c r="XER7" s="11"/>
+      <c r="XES7" s="11"/>
+      <c r="XET7" s="11"/>
+      <c r="XEU7" s="11"/>
+      <c r="XEV7" s="11"/>
+      <c r="XEW7" s="11"/>
+      <c r="XEX7" s="11"/>
+      <c r="XEY7" s="11"/>
+      <c r="XEZ7" s="11"/>
+      <c r="XFA7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>46</v>
+      <c r="A8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>141</v>
       </c>
       <c r="C8" s="14" t="n">
-        <f aca="false">1000*B8/$S8</f>
-        <v>786.755148115208</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>26</v>
+        <f aca="false">1000*B8/$U8</f>
+        <v>345.61025947732</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>330</v>
       </c>
       <c r="E8" s="14" t="n">
-        <f aca="false">1000*D8/$S8</f>
-        <v>444.687692412944</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <v>0.3</v>
+        <f aca="false">1000*D8/$U8</f>
+        <v>808.87507537245</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>26.4</v>
       </c>
       <c r="G8" s="14" t="n">
-        <f aca="false">1000*F8/$S8</f>
-        <v>5.13101183553397</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>36</v>
+        <f aca="false">1000*F8/$U8</f>
+        <v>64.710006029796</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>920</v>
       </c>
       <c r="I8" s="14" t="n">
-        <f aca="false">1000*H8/$S8</f>
-        <v>615.721420264076</v>
+        <f aca="false">1000*H8/$U8</f>
+        <v>2255.04566467471</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.39</v>
+        <v>2.09</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>380</v>
-      </c>
-      <c r="L8" s="14" t="n">
-        <f aca="false">1000*K8/$S8</f>
-        <v>6499.28165834303</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>2.3</v>
+        <f aca="false">L8*$K$37/100</f>
+        <v>323</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M8" s="14" t="n">
+        <f aca="false">1000*L8/$U8</f>
+        <v>4657.15952487168</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>0.8</v>
+        <v>9.9</v>
       </c>
       <c r="O8" s="1" t="n">
-        <f aca="false">N8*N$34/100*1000</f>
-        <v>352</v>
-      </c>
-      <c r="P8" s="14" t="n">
-        <f aca="false">1000*O8/$S8</f>
-        <v>6020.38722035986</v>
+        <v>3.3</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <f aca="false">Q8*$P$37/100</f>
+        <v>1346.4</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>1.55</v>
+        <v>9900</v>
+      </c>
+      <c r="R8" s="14" t="n">
+        <f aca="false">1000*P8/$U8</f>
+        <v>3300.2103075196</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>58.468</v>
+        <v>2.8</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <f aca="false">H8+F8+B8+D8+K8+O8</f>
-        <v>840.3</v>
+        <v>1.18</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>407.974</v>
       </c>
       <c r="V8" s="1" t="n">
-        <f aca="false">U8-$T$42*1000*T8/100</f>
-        <v>543.41831</v>
-      </c>
-      <c r="W8" s="1" t="n">
-        <f aca="false">ROUND(V8/S8 *100/1000, 2)</f>
-        <v>0.93</v>
+        <f aca="false">100*U8/$U$36</f>
+        <v>2.80209736617656</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <f aca="false">H8+F8+B8+D8+K8+P8</f>
+        <v>3086.8</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <f aca="false">T8*50000/100</f>
-        <v>245</v>
-      </c>
-      <c r="AB8" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="AG8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ8" s="1" t="n">
-        <f aca="false">AH8+AI8/100</f>
-        <v>0.38</v>
-      </c>
-      <c r="AK8" s="1" t="n">
-        <f aca="false">AJ8*1000</f>
-        <v>380</v>
+        <f aca="false">-X8+($V$45 + $V$46)*1000*V8/100</f>
+        <v>1254.66991877658</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <f aca="false">Y8/U8/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <f aca="false">Y8/U8</f>
+        <v>3.07536734884228</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <f aca="false">-V8*($V$47)*10</f>
+        <v>-672.503367882374</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <f aca="false">AC8/U8/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG8" s="1" t="n">
+        <v>514.3</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO8" s="1" t="n">
+        <f aca="false">AM8+AN8/100</f>
+        <v>1.9</v>
+      </c>
+      <c r="AP8" s="1" t="n">
+        <f aca="false">AO8*1000</f>
+        <v>1900</v>
+      </c>
+      <c r="AS8" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV8" s="17" t="n">
+        <f aca="false">AT8+AU8/10</f>
+        <v>9.9</v>
+      </c>
+      <c r="AW8" s="17" t="n">
+        <f aca="false">1000*AV8</f>
+        <v>9900</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>16</v>
+      <c r="A9" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>200</v>
       </c>
       <c r="C9" s="14" t="n">
-        <f aca="false">1000*B9/$S9</f>
-        <v>727.603456116417</v>
-      </c>
-      <c r="D9" s="21"/>
+        <f aca="false">1000*B9/$U9</f>
+        <v>394.508442480669</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>184</v>
+      </c>
       <c r="E9" s="14" t="n">
-        <f aca="false">1000*D9/$S9</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.8</v>
+        <f aca="false">1000*D9/$U9</f>
+        <v>362.947767082216</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>61.1</v>
       </c>
       <c r="G9" s="14" t="n">
-        <f aca="false">1000*F9/$S9</f>
-        <v>36.3801728058208</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>46</v>
+        <f aca="false">1000*F9/$U9</f>
+        <v>120.522329177844</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>722</v>
       </c>
       <c r="I9" s="14" t="n">
-        <f aca="false">1000*H9/$S9</f>
-        <v>2091.8599363347</v>
+        <f aca="false">1000*H9/$U9</f>
+        <v>1424.17547735522</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.8</v>
+        <v>3.36</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>290</v>
-      </c>
-      <c r="L9" s="14" t="n">
-        <f aca="false">1000*K9/$S9</f>
-        <v>13187.8126421101</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>1.5</v>
+        <f aca="false">L9*$K$37/100</f>
+        <v>187</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <f aca="false">1000*L9/$U9</f>
+        <v>2169.79643364368</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>0.5</v>
+        <v>9.8</v>
       </c>
       <c r="O9" s="1" t="n">
-        <f aca="false">N9*N$34/100*1000</f>
-        <v>220</v>
-      </c>
-      <c r="P9" s="14" t="n">
-        <f aca="false">1000*O9/$S9</f>
-        <v>10004.5475216007</v>
+        <v>3.3</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <f aca="false">Q9*$P$37/100</f>
+        <v>1332.8</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>2.44</v>
+        <v>9800</v>
+      </c>
+      <c r="R9" s="14" t="n">
+        <f aca="false">1000*P9/$U9</f>
+        <v>2629.00426069118</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>21.99</v>
+        <v>3.5</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <f aca="false">H9+F9+B9+D9+K9+O9</f>
-        <v>572.8</v>
+        <v>0.93</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>506.96</v>
       </c>
       <c r="V9" s="1" t="n">
-        <f aca="false">U9-$T$42*1000*T9/100</f>
-        <v>457.68261</v>
-      </c>
-      <c r="W9" s="1" t="n">
-        <f aca="false">ROUND(V9/S9 *100/1000, 2)</f>
-        <v>2.08</v>
+        <f aca="false">100*U9/$U$36</f>
+        <v>3.48196522512922</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <f aca="false">H9+F9+B9+D9+K9+P9</f>
+        <v>2686.9</v>
+      </c>
+      <c r="X9" s="22" t="n">
+        <f aca="false">F9</f>
+        <v>61.1</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <f aca="false">T9*50000/100</f>
-        <v>95</v>
-      </c>
-      <c r="AB9" s="1" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="AG9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ9" s="1" t="n">
-        <f aca="false">AH9+AI9/100</f>
-        <v>0.29</v>
-      </c>
-      <c r="AK9" s="1" t="n">
-        <f aca="false">AJ9*1000</f>
-        <v>290</v>
+        <f aca="false">-X9+($V$45 + $V$46)*1000*V9/100</f>
+        <v>1497.98823116908</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <f aca="false">Y9/U9/10</f>
+        <v>0.295484501966444</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <f aca="false">Y9/U9</f>
+        <v>2.95484501966444</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <f aca="false">-V9*($V$47)*10</f>
+        <v>-835.671654031012</v>
+      </c>
+      <c r="AD9" s="1" t="n">
+        <f aca="false">AC9/U9/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG9" s="1" t="n">
+        <v>642</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO9" s="1" t="n">
+        <f aca="false">AM9+AN9/100</f>
+        <v>1.1</v>
+      </c>
+      <c r="AP9" s="1" t="n">
+        <f aca="false">AO9*1000</f>
+        <v>1100</v>
+      </c>
+      <c r="AS9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" s="17" t="n">
+        <f aca="false">AT9+AU9/10</f>
+        <v>9.8</v>
+      </c>
+      <c r="AW9" s="17" t="n">
+        <f aca="false">1000*AV9</f>
+        <v>9800</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>177</v>
+      <c r="A10" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>38</v>
       </c>
       <c r="C10" s="14" t="n">
-        <f aca="false">1000*B10/$S10</f>
-        <v>777.772407095745</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>263</v>
+        <f aca="false">1000*B10/$U10</f>
+        <v>726.008291778911</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>18</v>
       </c>
       <c r="E10" s="14" t="n">
-        <f aca="false">1000*D10/$S10</f>
-        <v>1155.67312466769</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>3.8</v>
+        <f aca="false">1000*D10/$U10</f>
+        <v>343.898664526853</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.2</v>
       </c>
       <c r="G10" s="14" t="n">
-        <f aca="false">1000*F10/$S10</f>
-        <v>16.6979386834115</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>348</v>
+        <f aca="false">1000*F10/$U10</f>
+        <v>3.82109627252059</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>40</v>
       </c>
       <c r="I10" s="14" t="n">
-        <f aca="false">1000*H10/$S10</f>
-        <v>1529.17964784926</v>
+        <f aca="false">1000*H10/$U10</f>
+        <v>764.219254504117</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.69</v>
+        <v>0.4</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>440</v>
-      </c>
-      <c r="L10" s="14" t="n">
-        <f aca="false">1000*K10/$S10</f>
-        <v>1933.44553176343</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>4.6</v>
+        <f aca="false">L10*$K$37/100</f>
+        <v>45.9</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="M10" s="14" t="n">
+        <f aca="false">1000*L10/$U10</f>
+        <v>5158.47996790279</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O10" s="1" t="n">
-        <f aca="false">N10*N$34/100*1000</f>
-        <v>660</v>
-      </c>
-      <c r="P10" s="14" t="n">
-        <f aca="false">1000*O10/$S10</f>
-        <v>2900.16829764515</v>
+        <v>0.5</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <f aca="false">Q10*$P$37/100</f>
+        <v>217.6</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>0.77</v>
+        <v>1600</v>
+      </c>
+      <c r="R10" s="14" t="n">
+        <f aca="false">1000*P10/$U10</f>
+        <v>4157.3527445024</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>227.573</v>
+        <v>0.6</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <f aca="false">H10+F10+B10+D10+K10+O10</f>
-        <v>1891.8</v>
+        <v>0.88</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>52.341</v>
       </c>
       <c r="V10" s="1" t="n">
-        <f aca="false">U10-$T$42*1000*T10/100</f>
-        <v>770.92015</v>
-      </c>
-      <c r="W10" s="1" t="n">
-        <f aca="false">ROUND(V10/S10 *100/1000, 2)</f>
-        <v>0.34</v>
+        <f aca="false">100*U10/$U$36</f>
+        <v>0.359494914487313</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <f aca="false">H10+F10+B10+D10+K10+P10</f>
+        <v>359.7</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <f aca="false">T10*50000/100</f>
-        <v>925</v>
-      </c>
-      <c r="AB10" s="1" t="n">
-        <v>347.3</v>
-      </c>
-      <c r="AG10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH10" s="1" t="n">
+        <f aca="false">-X10+($V$45 + $V$46)*1000*V10/100</f>
+        <v>160.967802405754</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <f aca="false">Y10/U10/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <f aca="false">Y10/U10</f>
+        <v>3.07536734884228</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <f aca="false">-V10*($V$47)*10</f>
+        <v>-86.2787794769552</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <f aca="false">AC10/U10/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG10" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="AL10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ10" s="1" t="n">
-        <f aca="false">AH10+AI10/100</f>
-        <v>0.44</v>
-      </c>
-      <c r="AK10" s="1" t="n">
-        <f aca="false">AJ10*1000</f>
-        <v>440</v>
+      <c r="AN10" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <f aca="false">AM10+AN10/100</f>
+        <v>0.27</v>
+      </c>
+      <c r="AP10" s="1" t="n">
+        <f aca="false">AO10*1000</f>
+        <v>270</v>
+      </c>
+      <c r="AS10" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV10" s="17" t="n">
+        <f aca="false">AT10+AU10/10</f>
+        <v>1.6</v>
+      </c>
+      <c r="AW10" s="17" t="n">
+        <f aca="false">1000*AV10</f>
+        <v>1600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>106</v>
+      <c r="A11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>46</v>
       </c>
       <c r="C11" s="14" t="n">
-        <f aca="false">1000*B11/$S11</f>
-        <v>304.277684963515</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>258</v>
+        <f aca="false">1000*B11/$U11</f>
+        <v>786.755148115208</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>26</v>
       </c>
       <c r="E11" s="14" t="n">
-        <f aca="false">1000*D11/$S11</f>
-        <v>740.600403024405</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>113.8</v>
+        <f aca="false">1000*D11/$U11</f>
+        <v>444.687692412944</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>0.3</v>
       </c>
       <c r="G11" s="14" t="n">
-        <f aca="false">1000*F11/$S11</f>
-        <v>326.667929706114</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>533</v>
+        <f aca="false">1000*F11/$U11</f>
+        <v>5.13101183553397</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>36</v>
       </c>
       <c r="I11" s="14" t="n">
-        <f aca="false">1000*H11/$S11</f>
-        <v>1530.00005741088</v>
+        <f aca="false">1000*H11/$U11</f>
+        <v>615.721420264076</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>1.85</v>
+        <v>0.39</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1130</v>
-      </c>
-      <c r="L11" s="14" t="n">
-        <f aca="false">1000*K11/$S11</f>
-        <v>3243.71494347899</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>4.2</v>
+        <f aca="false">L11*$K$37/100</f>
+        <v>64.6</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <f aca="false">1000*L11/$U11</f>
+        <v>6499.28165834303</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="O11" s="1" t="n">
-        <f aca="false">N11*N$34/100*1000</f>
-        <v>616</v>
-      </c>
-      <c r="P11" s="14" t="n">
-        <f aca="false">1000*O11/$S11</f>
-        <v>1768.25522582571</v>
+        <v>0.8</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <f aca="false">Q11*$P$37/100</f>
+        <v>312.8</v>
       </c>
       <c r="Q11" s="1" t="n">
+        <v>2300</v>
+      </c>
+      <c r="R11" s="14" t="n">
+        <f aca="false">1000*P11/$U11</f>
+        <v>5349.93500718342</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>58.468</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <f aca="false">100*U11/$U$36</f>
+        <v>0.401577131889804</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <f aca="false">H11+F11+B11+D11+K11+P11</f>
+        <v>485.7</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <f aca="false">-X11+($V$45 + $V$46)*1000*V11/100</f>
+        <v>179.810578152111</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <f aca="false">Y11/U11/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <f aca="false">ROUND(Y11/U11 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <f aca="false">-V11*($V$47)*10</f>
+        <v>-96.378511653553</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <f aca="false">AC11/U11/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG11" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="AL11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO11" s="1" t="n">
+        <f aca="false">AM11+AN11/100</f>
+        <v>0.38</v>
+      </c>
+      <c r="AP11" s="1" t="n">
+        <f aca="false">AO11*1000</f>
+        <v>380</v>
+      </c>
+      <c r="AS11" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="AT11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" s="17" t="n">
+        <f aca="false">AT11+AU11/10</f>
         <v>2.3</v>
       </c>
-      <c r="R11" s="1" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>348.366</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <f aca="false">H11+F11+B11+D11+K11+O11</f>
-        <v>2756.8</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <f aca="false">U11-$T$42*1000*T11/100</f>
-        <v>1411.74418</v>
-      </c>
-      <c r="W11" s="1" t="n">
-        <f aca="false">ROUND(V11/S11 *100/1000, 2)</f>
-        <v>0.41</v>
-      </c>
-      <c r="Y11" s="1" t="n">
-        <f aca="false">T11*50000/100</f>
-        <v>1110</v>
-      </c>
-      <c r="AB11" s="1" t="n">
-        <v>417.8</v>
-      </c>
-      <c r="AG11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI11" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ11" s="1" t="n">
-        <f aca="false">AH11+AI11/100</f>
-        <v>1.13</v>
-      </c>
-      <c r="AK11" s="1" t="n">
-        <f aca="false">AJ11*1000</f>
-        <v>1130</v>
+      <c r="AW11" s="17" t="n">
+        <f aca="false">1000*AV11</f>
+        <v>2300</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="18" t="n">
-        <v>23</v>
+      <c r="A12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="C12" s="14" t="n">
-        <f aca="false">1000*B12/$S12</f>
-        <v>744.360658921001</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>21</v>
-      </c>
+        <f aca="false">1000*B12/$U12</f>
+        <v>727.603456116417</v>
+      </c>
+      <c r="D12" s="23"/>
       <c r="E12" s="14" t="n">
-        <f aca="false">1000*D12/$S12</f>
-        <v>679.633645101783</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>0.1</v>
+        <f aca="false">1000*D12/$U12</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.8</v>
       </c>
       <c r="G12" s="14" t="n">
-        <f aca="false">1000*F12/$S12</f>
-        <v>3.23635069096087</v>
-      </c>
-      <c r="H12" s="18" t="n">
+        <f aca="false">1000*F12/$U12</f>
+        <v>36.3801728058208</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <f aca="false">1000*H12/$U12</f>
+        <v>2091.8599363347</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <f aca="false">L12*$K$37/100</f>
+        <v>49.3</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <f aca="false">1000*L12/$U12</f>
+        <v>13187.8126421101</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <f aca="false">Q12*$P$37/100</f>
+        <v>204</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R12" s="14" t="n">
+        <f aca="false">1000*P12/$U12</f>
+        <v>9276.94406548431</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <f aca="false">100*U12/$U$36</f>
+        <v>0.151034431317247</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <f aca="false">H12+F12+B12+D12+K12+P12</f>
+        <v>316.1</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <f aca="false">-X12+($V$45 + $V$46)*1000*V12/100</f>
+        <v>67.6273280010418</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <f aca="false">Y12/U12/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <f aca="false">ROUND(Y12/U12 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <f aca="false">-V12*($V$47)*10</f>
+        <v>-36.2482635161393</v>
+      </c>
+      <c r="AD12" s="1" t="n">
+        <f aca="false">AC12/U12/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG12" s="1" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AL12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="I12" s="14" t="n">
-        <f aca="false">1000*H12/$S12</f>
-        <v>938.541700378653</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="L12" s="14" t="n">
-        <f aca="false">1000*K12/$S12</f>
-        <v>29127.1562186479</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <f aca="false">N12*N$34/100*1000</f>
-        <v>88</v>
-      </c>
-      <c r="P12" s="14" t="n">
-        <f aca="false">1000*O12/$S12</f>
-        <v>2847.98860804557</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>30.899</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <f aca="false">H12+F12+B12+D12+K12+O12</f>
-        <v>1061.1</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <f aca="false">U12-$T$42*1000*T12/100</f>
-        <v>927.80618</v>
-      </c>
-      <c r="W12" s="1" t="n">
-        <f aca="false">ROUND(V12/S12 *100/1000, 2)</f>
-        <v>3</v>
-      </c>
-      <c r="Y12" s="1" t="n">
-        <f aca="false">T12*50000/100</f>
-        <v>110</v>
-      </c>
-      <c r="AB12" s="1" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="AG12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ12" s="1" t="n">
-        <f aca="false">AH12+AI12/100</f>
-        <v>0.9</v>
-      </c>
-      <c r="AK12" s="1" t="n">
-        <f aca="false">AJ12*1000</f>
-        <v>900</v>
+      <c r="AO12" s="1" t="n">
+        <f aca="false">AM12+AN12/100</f>
+        <v>0.29</v>
+      </c>
+      <c r="AP12" s="1" t="n">
+        <f aca="false">AO12*1000</f>
+        <v>290</v>
+      </c>
+      <c r="AS12" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="AT12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV12" s="17" t="n">
+        <f aca="false">AT12+AU12/10</f>
+        <v>1.5</v>
+      </c>
+      <c r="AW12" s="17" t="n">
+        <f aca="false">1000*AV12</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>97</v>
+      <c r="A13" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>177</v>
       </c>
       <c r="C13" s="14" t="n">
-        <f aca="false">1000*B13/$S13</f>
-        <v>379.785988637743</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>133</v>
+        <f aca="false">1000*B13/$U13</f>
+        <v>777.772407095745</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>263</v>
       </c>
       <c r="E13" s="14" t="n">
-        <f aca="false">1000*D13/$S13</f>
-        <v>520.737489575462</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>81.3</v>
+        <f aca="false">1000*D13/$U13</f>
+        <v>1155.67312466769</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>3.8</v>
       </c>
       <c r="G13" s="14" t="n">
-        <f aca="false">1000*F13/$S13</f>
-        <v>318.315472951015</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>152</v>
+        <f aca="false">1000*F13/$U13</f>
+        <v>16.6979386834115</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>348</v>
       </c>
       <c r="I13" s="14" t="n">
-        <f aca="false">1000*H13/$S13</f>
-        <v>595.128559514814</v>
+        <f aca="false">1000*H13/$U13</f>
+        <v>1529.17964784926</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>1.57</v>
+        <v>0.69</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>720</v>
-      </c>
-      <c r="L13" s="14" t="n">
-        <f aca="false">1000*K13/$S13</f>
-        <v>2819.03001875438</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>2.9</v>
+        <f aca="false">L13*$K$37/100</f>
+        <v>74.8</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>440</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <f aca="false">1000*L13/$U13</f>
+        <v>1933.44553176343</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="O13" s="1" t="n">
-        <f aca="false">N13*N$34/100*1000</f>
+        <v>1.5</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <f aca="false">Q13*$P$37/100</f>
+        <v>625.6</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4600</v>
+      </c>
+      <c r="R13" s="14" t="n">
+        <f aca="false">1000*P13/$U13</f>
+        <v>2749.00801061637</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>227.573</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <f aca="false">100*U13/$U$36</f>
+        <v>1.56304495853387</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <f aca="false">H13+F13+B13+D13+K13+P13</f>
+        <v>1492.2</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <f aca="false">-X13+($V$45 + $V$46)*1000*V13/100</f>
+        <v>699.870573678085</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <f aca="false">Y13/U13/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <f aca="false">ROUND(Y13/U13 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <f aca="false">-V13*($V$47)*10</f>
+        <v>-375.130790048129</v>
+      </c>
+      <c r="AD13" s="1" t="n">
+        <f aca="false">AC13/U13/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG13" s="1" t="n">
+        <v>347.3</v>
+      </c>
+      <c r="AL13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO13" s="1" t="n">
+        <f aca="false">AM13+AN13/100</f>
+        <v>0.44</v>
+      </c>
+      <c r="AP13" s="1" t="n">
+        <f aca="false">AO13*1000</f>
         <v>440</v>
       </c>
-      <c r="P13" s="14" t="n">
-        <f aca="false">1000*O13/$S13</f>
-        <v>1722.74056701657</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>255.407</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <f aca="false">H13+F13+B13+D13+K13+O13</f>
-        <v>1623.3</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <f aca="false">U13-$T$42*1000*T13/100</f>
-        <v>714.4785</v>
-      </c>
-      <c r="W13" s="1" t="n">
-        <f aca="false">ROUND(V13/S13 *100/1000, 2)</f>
-        <v>0.28</v>
-      </c>
-      <c r="Y13" s="1" t="n">
-        <f aca="false">T13*50000/100</f>
-        <v>750</v>
-      </c>
-      <c r="AB13" s="1" t="n">
-        <v>281.7</v>
-      </c>
-      <c r="AG13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="AJ13" s="1" t="n">
-        <f aca="false">AH13+AI13/100</f>
-        <v>0.72</v>
-      </c>
-      <c r="AK13" s="1" t="n">
-        <f aca="false">AJ13*1000</f>
-        <v>720</v>
+      <c r="AS13" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="AT13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV13" s="17" t="n">
+        <f aca="false">AT13+AU13/10</f>
+        <v>4.6</v>
+      </c>
+      <c r="AW13" s="17" t="n">
+        <f aca="false">1000*AV13</f>
+        <v>4600</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>1078</v>
+      <c r="A14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>106</v>
       </c>
       <c r="C14" s="14" t="n">
-        <f aca="false">1000*B14/$S14</f>
-        <v>418.692157950257</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>1691</v>
+        <f aca="false">1000*B14/$U14</f>
+        <v>304.277684963515</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>258</v>
       </c>
       <c r="E14" s="14" t="n">
-        <f aca="false">1000*D14/$S14</f>
-        <v>656.779628101934</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>3100</v>
+        <f aca="false">1000*D14/$U14</f>
+        <v>740.600403024405</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>113.8</v>
       </c>
       <c r="G14" s="14" t="n">
-        <f aca="false">1000*F14/$S14</f>
-        <v>1204.03125199054</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>6670</v>
+        <f aca="false">1000*F14/$U14</f>
+        <v>326.667929706114</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>533</v>
       </c>
       <c r="I14" s="14" t="n">
-        <f aca="false">1000*H14/$S14</f>
-        <v>2590.60917766996</v>
+        <f aca="false">1000*H14/$U14</f>
+        <v>1530.00005741088</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>17.13</v>
+        <v>1.85</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>5380</v>
-      </c>
-      <c r="L14" s="14" t="n">
-        <f aca="false">1000*K14/$S14</f>
-        <v>2089.57681797067</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>62</v>
+        <f aca="false">L14*$K$37/100</f>
+        <v>192.1</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>1130</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <f aca="false">1000*L14/$U14</f>
+        <v>3243.71494347899</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>20.7</v>
+        <v>4.2</v>
       </c>
       <c r="O14" s="1" t="n">
-        <f aca="false">N14*N$34/100*1000</f>
-        <v>9108</v>
-      </c>
-      <c r="P14" s="14" t="n">
-        <f aca="false">1000*O14/$S14</f>
-        <v>3537.5214977838</v>
+        <v>1.4</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <f aca="false">Q14*$P$37/100</f>
+        <v>571.2</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>1.27</v>
+        <v>4200</v>
+      </c>
+      <c r="R14" s="14" t="n">
+        <f aca="false">1000*P14/$U14</f>
+        <v>1639.65484576566</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>2574.684</v>
+        <v>2.3</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>15.91</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <f aca="false">H14+F14+B14+D14+K14+O14</f>
-        <v>27027</v>
+        <v>0.62</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>348.366</v>
       </c>
       <c r="V14" s="1" t="n">
-        <f aca="false">U14-$T$42*1000*T14/100</f>
-        <v>17387.43329</v>
-      </c>
-      <c r="W14" s="1" t="n">
-        <f aca="false">ROUND(V14/S14 *100/1000, 2)</f>
-        <v>0.68</v>
+        <f aca="false">100*U14/$U$36</f>
+        <v>2.39269034562365</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <f aca="false">H14+F14+B14+D14+K14+P14</f>
+        <v>1774.1</v>
       </c>
       <c r="Y14" s="1" t="n">
-        <f aca="false">T14*50000/100</f>
-        <v>7955</v>
-      </c>
-      <c r="AB14" s="1" t="n">
-        <v>2991.1</v>
-      </c>
-      <c r="AG14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH14" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI14" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ14" s="1" t="n">
-        <f aca="false">AH14+AI14/100</f>
-        <v>5.38</v>
-      </c>
-      <c r="AK14" s="1" t="n">
-        <f aca="false">AJ14*1000</f>
-        <v>5380</v>
+        <f aca="false">-X14+($V$45 + $V$46)*1000*V14/100</f>
+        <v>1071.35342184679</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <f aca="false">Y14/U14/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <f aca="false">ROUND(Y14/U14 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <f aca="false">-V14*($V$47)*10</f>
+        <v>-574.245682949676</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <f aca="false">AC14/U14/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO14" s="1" t="n">
+        <f aca="false">AM14+AN14/100</f>
+        <v>1.13</v>
+      </c>
+      <c r="AP14" s="1" t="n">
+        <f aca="false">AO14*1000</f>
+        <v>1130</v>
+      </c>
+      <c r="AS14" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV14" s="17" t="n">
+        <f aca="false">AT14+AU14/10</f>
+        <v>4.2</v>
+      </c>
+      <c r="AW14" s="17" t="n">
+        <f aca="false">1000*AV14</f>
+        <v>4200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>973</v>
+      <c r="A15" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>23</v>
       </c>
       <c r="C15" s="14" t="n">
-        <f aca="false">1000*B15/$S15</f>
-        <v>260.893020991029</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>2700</v>
+        <f aca="false">1000*B15/$U15</f>
+        <v>744.360658921001</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>21</v>
       </c>
       <c r="E15" s="14" t="n">
-        <f aca="false">1000*D15/$S15</f>
-        <v>723.958023305013</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>1595.2</v>
+        <f aca="false">1000*D15/$U15</f>
+        <v>679.633645101783</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0.1</v>
       </c>
       <c r="G15" s="14" t="n">
-        <f aca="false">1000*F15/$S15</f>
-        <v>427.725125472651</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>8344</v>
+        <f aca="false">1000*F15/$U15</f>
+        <v>3.23635069096087</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>29</v>
       </c>
       <c r="I15" s="14" t="n">
-        <f aca="false">1000*H15/$S15</f>
-        <v>2237.29842461372</v>
+        <f aca="false">1000*H15/$U15</f>
+        <v>938.541700378653</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>20.1</v>
+        <v>0.1</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>6400</v>
-      </c>
-      <c r="L15" s="14" t="n">
-        <f aca="false">1000*K15/$S15</f>
-        <v>1716.04864783411</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>57.7</v>
+        <f aca="false">L15*$K$37/100</f>
+        <v>153</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>900</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <f aca="false">1000*L15/$U15</f>
+        <v>29127.1562186479</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>19.3</v>
+        <v>0.5</v>
       </c>
       <c r="O15" s="1" t="n">
-        <f aca="false">N15*N$34/100*1000</f>
-        <v>8492</v>
-      </c>
-      <c r="P15" s="14" t="n">
-        <f aca="false">1000*O15/$S15</f>
-        <v>2276.98204959488</v>
+        <v>0.2</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <f aca="false">Q15*$P$37/100</f>
+        <v>68</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>0.79</v>
+        <v>500</v>
+      </c>
+      <c r="R15" s="14" t="n">
+        <f aca="false">1000*P15/$U15</f>
+        <v>2200.71846985339</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>3729.498</v>
+        <v>0.2</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <f aca="false">H15+F15+B15+D15+K15+O15</f>
-        <v>28504.2</v>
+        <v>0.91</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>30.899</v>
       </c>
       <c r="V15" s="1" t="n">
-        <f aca="false">U15-$T$42*1000*T15/100</f>
-        <v>13902.4679</v>
-      </c>
-      <c r="W15" s="1" t="n">
-        <f aca="false">ROUND(V15/S15 *100/1000, 2)</f>
-        <v>0.37</v>
+        <f aca="false">100*U15/$U$36</f>
+        <v>0.212224324387067</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <f aca="false">H15+F15+B15+D15+K15+P15</f>
+        <v>294.1</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <f aca="false">T15*50000/100</f>
-        <v>12050</v>
-      </c>
-      <c r="AB15" s="1" t="n">
-        <v>4529.7</v>
-      </c>
-      <c r="AG15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH15" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI15" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ15" s="1" t="n">
-        <f aca="false">AH15+AI15/100</f>
-        <v>6.4</v>
-      </c>
-      <c r="AK15" s="1" t="n">
-        <f aca="false">AJ15*1000</f>
-        <v>6400</v>
+        <f aca="false">-X15+($V$45 + $V$46)*1000*V15/100</f>
+        <v>95.0257757118777</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <f aca="false">Y15/U15/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <f aca="false">ROUND(Y15/U15 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <f aca="false">-V15*($V$47)*10</f>
+        <v>-50.9338378528962</v>
+      </c>
+      <c r="AD15" s="1" t="n">
+        <f aca="false">AC15/U15/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG15" s="1" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="AL15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO15" s="1" t="n">
+        <f aca="false">AM15+AN15/100</f>
+        <v>0.9</v>
+      </c>
+      <c r="AP15" s="1" t="n">
+        <f aca="false">AO15*1000</f>
+        <v>900</v>
+      </c>
+      <c r="AS15" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV15" s="17" t="n">
+        <f aca="false">AT15+AU15/10</f>
+        <v>0.5</v>
+      </c>
+      <c r="AW15" s="17" t="n">
+        <f aca="false">1000*AV15</f>
+        <v>500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="18" t="n">
-        <v>91</v>
+      <c r="A16" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>97</v>
       </c>
       <c r="C16" s="14" t="n">
-        <f aca="false">1000*B16/$S16</f>
-        <v>503.093193867792</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>54</v>
+        <f aca="false">1000*B16/$U16</f>
+        <v>379.785988637743</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>133</v>
       </c>
       <c r="E16" s="14" t="n">
-        <f aca="false">1000*D16/$S16</f>
-        <v>298.538818339129</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>22.7</v>
+        <f aca="false">1000*D16/$U16</f>
+        <v>520.737489575462</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>81.3</v>
       </c>
       <c r="G16" s="14" t="n">
-        <f aca="false">1000*F16/$S16</f>
-        <v>125.496873635152</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>118</v>
+        <f aca="false">1000*F16/$U16</f>
+        <v>318.315472951015</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>152</v>
       </c>
       <c r="I16" s="14" t="n">
-        <f aca="false">1000*H16/$S16</f>
-        <v>652.362603037356</v>
+        <f aca="false">1000*H16/$U16</f>
+        <v>595.128559514814</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>3.09</v>
+        <v>1.57</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>2540</v>
-      </c>
-      <c r="L16" s="14" t="n">
-        <f aca="false">1000*K16/$S16</f>
-        <v>14042.3814552109</v>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>6.3</v>
+        <f aca="false">L16*$K$37/100</f>
+        <v>122.4</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>720</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <f aca="false">1000*L16/$U16</f>
+        <v>2819.03001875438</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O16" s="1" t="n">
-        <f aca="false">N16*N$34/100*1000</f>
-        <v>924</v>
-      </c>
-      <c r="P16" s="14" t="n">
-        <f aca="false">1000*O16/$S16</f>
-        <v>5108.33089158065</v>
+        <v>1</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <f aca="false">Q16*$P$37/100</f>
+        <v>394.4</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>1.61</v>
+        <v>2900</v>
+      </c>
+      <c r="R16" s="14" t="n">
+        <f aca="false">1000*P16/$U16</f>
+        <v>1544.20199916212</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>180.881</v>
+        <v>1.6</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <f aca="false">H16+F16+B16+D16+K16+O16</f>
-        <v>3749.7</v>
+        <v>0.61</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>255.407</v>
       </c>
       <c r="V16" s="1" t="n">
-        <f aca="false">U16-$T$42*1000*T16/100</f>
-        <v>2949.93708</v>
-      </c>
-      <c r="W16" s="1" t="n">
-        <f aca="false">ROUND(V16/S16 *100/1000, 2)</f>
-        <v>1.63</v>
+        <f aca="false">100*U16/$U$36</f>
+        <v>1.75421787173461</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <f aca="false">H16+F16+B16+D16+K16+P16</f>
+        <v>980.1</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <f aca="false">T16*50000/100</f>
-        <v>660</v>
-      </c>
-      <c r="AB16" s="1" t="n">
-        <v>248.4</v>
-      </c>
-      <c r="AG16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH16" s="1" t="n">
+        <f aca="false">-X16+($V$45 + $V$46)*1000*V16/100</f>
+        <v>785.470348465761</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <f aca="false">Y16/U16/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <f aca="false">ROUND(Y16/U16 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <f aca="false">-V16*($V$47)*10</f>
+        <v>-421.012289216306</v>
+      </c>
+      <c r="AD16" s="1" t="n">
+        <f aca="false">AC16/U16/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG16" s="1" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="AL16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO16" s="1" t="n">
+        <f aca="false">AM16+AN16/100</f>
+        <v>0.72</v>
+      </c>
+      <c r="AP16" s="1" t="n">
+        <f aca="false">AO16*1000</f>
+        <v>720</v>
+      </c>
+      <c r="AS16" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AI16" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="AJ16" s="1" t="n">
-        <f aca="false">AH16+AI16/100</f>
-        <v>2.54</v>
-      </c>
-      <c r="AK16" s="1" t="n">
-        <f aca="false">AJ16*1000</f>
-        <v>2540</v>
+      <c r="AU16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV16" s="17" t="n">
+        <f aca="false">AT16+AU16/10</f>
+        <v>2.9</v>
+      </c>
+      <c r="AW16" s="17" t="n">
+        <f aca="false">1000*AV16</f>
+        <v>2900</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>139</v>
+      <c r="A17" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>1078</v>
       </c>
       <c r="C17" s="14" t="n">
-        <f aca="false">1000*B17/$S17</f>
-        <v>933.361983293492</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>113</v>
+        <f aca="false">1000*B17/$U17</f>
+        <v>418.692157950257</v>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>1691</v>
       </c>
       <c r="E17" s="14" t="n">
-        <f aca="false">1000*D17/$S17</f>
-        <v>758.776288576724</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>5.9</v>
+        <f aca="false">1000*D17/$U17</f>
+        <v>656.779628101934</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>3100</v>
       </c>
       <c r="G17" s="14" t="n">
-        <f aca="false">1000*F17/$S17</f>
-        <v>39.617523031882</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>208</v>
+        <f aca="false">1000*F17/$U17</f>
+        <v>1204.03125199054</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>6670</v>
       </c>
       <c r="I17" s="14" t="n">
-        <f aca="false">1000*H17/$S17</f>
-        <v>1396.68555773415</v>
+        <f aca="false">1000*H17/$U17</f>
+        <v>2590.60917766996</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.76</v>
+        <v>17.13</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>370</v>
-      </c>
-      <c r="L17" s="14" t="n">
-        <f aca="false">1000*K17/$S17</f>
-        <v>2484.48873250786</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>2.5</v>
+        <f aca="false">L17*$K$37/100</f>
+        <v>914.6</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>5380</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <f aca="false">1000*L17/$U17</f>
+        <v>2089.57681797067</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>0.9</v>
+        <v>62</v>
       </c>
       <c r="O17" s="1" t="n">
-        <f aca="false">N17*N$34/100*1000</f>
-        <v>396</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <f aca="false">1000*O17/$S17</f>
-        <v>2659.07442722462</v>
+        <v>20.7</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <f aca="false">Q17*$P$37/100</f>
+        <v>8432</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>0.78</v>
+        <v>62000</v>
+      </c>
+      <c r="R17" s="14" t="n">
+        <f aca="false">1000*P17/$U17</f>
+        <v>3274.96500541426</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>148.924</v>
+        <v>16.3</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="U17" s="2" t="n">
-        <f aca="false">H17+F17+B17+D17+K17+O17</f>
-        <v>1231.9</v>
+        <v>1.27</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>2574.684</v>
       </c>
       <c r="V17" s="1" t="n">
-        <f aca="false">U17-$T$42*1000*T17/100</f>
-        <v>529.07804</v>
-      </c>
-      <c r="W17" s="1" t="n">
-        <f aca="false">ROUND(V17/S17 *100/1000, 2)</f>
-        <v>0.36</v>
+        <f aca="false">100*U17/$U$36</f>
+        <v>17.6837623356805</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <f aca="false">H17+F17+B17+D17+K17+P17</f>
+        <v>21885.6</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <f aca="false">B17+F17</f>
+        <v>4178</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <f aca="false">T17*50000/100</f>
-        <v>580</v>
-      </c>
-      <c r="AB17" s="1" t="n">
-        <v>218.8</v>
-      </c>
-      <c r="AG17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH17" s="1" t="n">
+        <f aca="false">-X17+($V$45 + $V$46)*1000*V17/100</f>
+        <v>3740.09910718664</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <f aca="false">Y17/U17/10</f>
+        <v>0.145264393890149</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <f aca="false">ROUND(Y17/U17 *100/1000, 2)</f>
+        <v>0.15</v>
+      </c>
+      <c r="AC17" s="1" t="n">
+        <f aca="false">-V17*($V$47)*10</f>
+        <v>-4244.10296056332</v>
+      </c>
+      <c r="AD17" s="1" t="n">
+        <f aca="false">AC17/U17/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG17" s="1" t="n">
+        <v>2991.1</v>
+      </c>
+      <c r="AL17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO17" s="1" t="n">
+        <f aca="false">AM17+AN17/100</f>
+        <v>5.38</v>
+      </c>
+      <c r="AP17" s="1" t="n">
+        <f aca="false">AO17*1000</f>
+        <v>5380</v>
+      </c>
+      <c r="AS17" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT17" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="AU17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="AJ17" s="1" t="n">
-        <f aca="false">AH17+AI17/100</f>
-        <v>0.37</v>
-      </c>
-      <c r="AK17" s="1" t="n">
-        <f aca="false">AJ17*1000</f>
-        <v>370</v>
+      <c r="AV17" s="17" t="n">
+        <f aca="false">AT17+AU17/10</f>
+        <v>62</v>
+      </c>
+      <c r="AW17" s="17" t="n">
+        <f aca="false">1000*AV17</f>
+        <v>62000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="18" t="n">
-        <v>97</v>
+      <c r="A18" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>973</v>
       </c>
       <c r="C18" s="14" t="n">
-        <f aca="false">1000*B18/$S18</f>
-        <v>299.863052234907</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>160</v>
+        <f aca="false">1000*B18/$U18</f>
+        <v>260.893020991029</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>2700</v>
       </c>
       <c r="E18" s="14" t="n">
-        <f aca="false">1000*D18/$S18</f>
-        <v>494.619467603971</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <v>241.4</v>
+        <f aca="false">1000*D18/$U18</f>
+        <v>723.958023305013</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>1595.2</v>
       </c>
       <c r="G18" s="14" t="n">
-        <f aca="false">1000*F18/$S18</f>
-        <v>746.257121747491</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <v>331</v>
+        <f aca="false">1000*F18/$U18</f>
+        <v>427.725125472651</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>8344</v>
       </c>
       <c r="I18" s="14" t="n">
-        <f aca="false">1000*H18/$S18</f>
-        <v>1023.24402360571</v>
+        <f aca="false">1000*H18/$U18</f>
+        <v>2237.29842461372</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>2.52</v>
+        <v>20.1</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>940</v>
-      </c>
-      <c r="L18" s="14" t="n">
-        <f aca="false">1000*K18/$S18</f>
-        <v>2905.88937217333</v>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>3.8</v>
+        <f aca="false">L18*$K$37/100</f>
+        <v>1088</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>6400</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <f aca="false">1000*L18/$U18</f>
+        <v>1716.04864783411</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>1.3</v>
+        <v>57.7</v>
       </c>
       <c r="O18" s="1" t="n">
-        <f aca="false">N18*N$34/100*1000</f>
-        <v>572</v>
-      </c>
-      <c r="P18" s="14" t="n">
-        <f aca="false">1000*O18/$S18</f>
-        <v>1768.2645966842</v>
+        <v>19.3</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <f aca="false">Q18*$P$37/100</f>
+        <v>7847.2</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>0.43</v>
+        <v>57700</v>
+      </c>
+      <c r="R18" s="14" t="n">
+        <f aca="false">1000*P18/$U18</f>
+        <v>2104.09014832559</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>323.481</v>
+        <v>24.5</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <f aca="false">H18+F18+B18+D18+K18+O18</f>
-        <v>2341.4</v>
+        <v>0.79</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>3729.498</v>
       </c>
       <c r="V18" s="1" t="n">
-        <f aca="false">U18-$T$42*1000*T18/100</f>
-        <v>396.52199</v>
-      </c>
-      <c r="W18" s="1" t="n">
-        <f aca="false">ROUND(V18/S18 *100/1000, 2)</f>
-        <v>0.12</v>
+        <f aca="false">100*U18/$U$36</f>
+        <v>25.6153983414647</v>
+      </c>
+      <c r="W18" s="2" t="n">
+        <f aca="false">H18+F18+B18+D18+K18+P18</f>
+        <v>22547.4</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <f aca="false">T18*50000/100</f>
-        <v>1605</v>
-      </c>
-      <c r="AB18" s="1" t="n">
-        <v>602.4</v>
-      </c>
-      <c r="AG18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="AJ18" s="1" t="n">
-        <f aca="false">AH18+AI18/100</f>
-        <v>0.94</v>
-      </c>
-      <c r="AK18" s="1" t="n">
-        <f aca="false">AJ18*1000</f>
-        <v>940</v>
+        <f aca="false">-X18+($V$45 + $V$46)*1000*V18/100</f>
+        <v>11469.5763767726</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <f aca="false">Y18/U18/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <f aca="false">ROUND(Y18/U18 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC18" s="1" t="n">
+        <f aca="false">-V18*($V$47)*10</f>
+        <v>-6147.69560195154</v>
+      </c>
+      <c r="AD18" s="1" t="n">
+        <f aca="false">AC18/U18/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG18" s="1" t="n">
+        <v>4529.7</v>
+      </c>
+      <c r="AL18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN18" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO18" s="1" t="n">
+        <f aca="false">AM18+AN18/100</f>
+        <v>6.4</v>
+      </c>
+      <c r="AP18" s="1" t="n">
+        <f aca="false">AO18*1000</f>
+        <v>6400</v>
+      </c>
+      <c r="AS18" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT18" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="AU18" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" s="17" t="n">
+        <f aca="false">AT18+AU18/10</f>
+        <v>57.7</v>
+      </c>
+      <c r="AW18" s="17" t="n">
+        <f aca="false">1000*AV18</f>
+        <v>57700</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="14" t="n">
-        <v>464</v>
+      <c r="A19" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>91</v>
       </c>
       <c r="C19" s="14" t="n">
-        <f aca="false">1000*B19/$S19</f>
-        <v>255.791133309077</v>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>891</v>
+        <f aca="false">1000*B19/$U19</f>
+        <v>503.093193867792</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>54</v>
       </c>
       <c r="E19" s="14" t="n">
-        <f aca="false">1000*D19/$S19</f>
-        <v>491.185128832732</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>544.5</v>
+        <f aca="false">1000*D19/$U19</f>
+        <v>298.538818339129</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>22.7</v>
       </c>
       <c r="G19" s="14" t="n">
-        <f aca="false">1000*F19/$S19</f>
-        <v>300.168689842225</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>2618</v>
+        <f aca="false">1000*F19/$U19</f>
+        <v>125.496873635152</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>118</v>
       </c>
       <c r="I19" s="14" t="n">
-        <f aca="false">1000*H19/$S19</f>
-        <v>1443.23531681716</v>
+        <f aca="false">1000*H19/$U19</f>
+        <v>652.362603037356</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>10.01</v>
+        <v>3.09</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>7110</v>
-      </c>
-      <c r="L19" s="14" t="n">
-        <f aca="false">1000*K19/$S19</f>
-        <v>3919.55809876625</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>56.5</v>
+        <f aca="false">L19*$K$37/100</f>
+        <v>431.8</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>2540</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <f aca="false">1000*L19/$U19</f>
+        <v>14042.3814552109</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>18.9</v>
+        <v>6.3</v>
       </c>
       <c r="O19" s="1" t="n">
-        <f aca="false">N19*N$34/100*1000</f>
-        <v>8316</v>
-      </c>
-      <c r="P19" s="14" t="n">
-        <f aca="false">1000*O19/$S19</f>
-        <v>4584.39453577217</v>
+        <v>2.1</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <f aca="false">Q19*$P$37/100</f>
+        <v>856.8</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="R19" s="1" t="n">
-        <v>1.54</v>
+        <v>6300</v>
+      </c>
+      <c r="R19" s="14" t="n">
+        <f aca="false">1000*P19/$U19</f>
+        <v>4736.81591764751</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>1813.98</v>
+        <v>1.3</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <f aca="false">H19+F19+B19+D19+K19+O19</f>
-        <v>19943.5</v>
+        <v>1.61</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>180.881</v>
       </c>
       <c r="V19" s="1" t="n">
-        <f aca="false">U19-$T$42*1000*T19/100</f>
-        <v>12666.86919</v>
-      </c>
-      <c r="W19" s="1" t="n">
-        <f aca="false">ROUND(V19/S19 *100/1000, 2)</f>
-        <v>0.7</v>
+        <f aca="false">100*U19/$U$36</f>
+        <v>1.24234920286926</v>
+      </c>
+      <c r="W19" s="2" t="n">
+        <f aca="false">H19+F19+B19+D19+K19+P19</f>
+        <v>1574.3</v>
+      </c>
+      <c r="X19" s="22" t="n">
+        <f aca="false">F19</f>
+        <v>22.7</v>
       </c>
       <c r="Y19" s="1" t="n">
-        <f aca="false">T19*50000/100</f>
-        <v>6005</v>
-      </c>
-      <c r="AB19" s="1" t="n">
-        <v>2258</v>
-      </c>
-      <c r="AG19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AH19" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI19" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ19" s="1" t="n">
-        <f aca="false">AH19+AI19/100</f>
-        <v>7.11</v>
-      </c>
-      <c r="AK19" s="1" t="n">
-        <f aca="false">AJ19*1000</f>
-        <v>7110</v>
+        <f aca="false">-X19+($V$45 + $V$46)*1000*V19/100</f>
+        <v>533.575521425941</v>
+      </c>
+      <c r="Z19" s="1" t="n">
+        <f aca="false">Y19/U19/10</f>
+        <v>0.294987047520713</v>
+      </c>
+      <c r="AA19" s="1" t="n">
+        <f aca="false">ROUND(Y19/U19 *100/1000, 2)</f>
+        <v>0.29</v>
+      </c>
+      <c r="AC19" s="1" t="n">
+        <f aca="false">-V19*($V$47)*10</f>
+        <v>-298.163808688621</v>
+      </c>
+      <c r="AD19" s="1" t="n">
+        <f aca="false">AC19/U19/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG19" s="1" t="n">
+        <v>248.4</v>
+      </c>
+      <c r="AL19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN19" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="AO19" s="1" t="n">
+        <f aca="false">AM19+AN19/100</f>
+        <v>2.54</v>
+      </c>
+      <c r="AP19" s="1" t="n">
+        <f aca="false">AO19*1000</f>
+        <v>2540</v>
+      </c>
+      <c r="AS19" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV19" s="17" t="n">
+        <f aca="false">AT19+AU19/10</f>
+        <v>6.3</v>
+      </c>
+      <c r="AW19" s="17" t="n">
+        <f aca="false">1000*AV19</f>
+        <v>6300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="18" t="n">
-        <v>27</v>
+      <c r="A20" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>139</v>
       </c>
       <c r="C20" s="14" t="n">
-        <f aca="false">1000*B20/$S20</f>
-        <v>816.326530612245</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>20</v>
+        <f aca="false">1000*B20/$U20</f>
+        <v>933.361983293492</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>113</v>
       </c>
       <c r="E20" s="14" t="n">
-        <f aca="false">1000*D20/$S20</f>
-        <v>604.686318972033</v>
-      </c>
-      <c r="F20" s="18" t="n">
+        <f aca="false">1000*D20/$U20</f>
+        <v>758.776288576724</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <f aca="false">1000*F20/$U20</f>
+        <v>39.617523031882</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>208</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <f aca="false">1000*H20/$U20</f>
+        <v>1396.68555773415</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <f aca="false">L20*$K$37/100</f>
+        <v>62.9</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>370</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <f aca="false">1000*L20/$U20</f>
+        <v>2484.48873250786</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <f aca="false">Q20*$P$37/100</f>
+        <v>340</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R20" s="14" t="n">
+        <f aca="false">1000*P20/$U20</f>
+        <v>2283.04370014235</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>148.924</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <f aca="false">100*U20/$U$36</f>
+        <v>1.02285819233696</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <f aca="false">H20+F20+B20+D20+K20+P20</f>
+        <v>868.8</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <f aca="false">-X20+($V$45 + $V$46)*1000*V20/100</f>
+        <v>457.996007058988</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <f aca="false">Y20/U20/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <f aca="false">ROUND(Y20/U20 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC20" s="1" t="n">
+        <f aca="false">-V20*($V$47)*10</f>
+        <v>-245.48596616087</v>
+      </c>
+      <c r="AD20" s="1" t="n">
+        <f aca="false">AC20/U20/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG20" s="1" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="14" t="n">
-        <f aca="false">1000*F20/$S20</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <f aca="false">1000*H20/$S20</f>
-        <v>604.686318972033</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="K20" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="L20" s="14" t="n">
-        <f aca="false">1000*K20/$S20</f>
-        <v>5442.1768707483</v>
-      </c>
-      <c r="M20" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <f aca="false">N20*N$34/100*1000</f>
-        <v>88</v>
-      </c>
-      <c r="P20" s="14" t="n">
-        <f aca="false">1000*O20/$S20</f>
-        <v>2660.61980347695</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>33.075</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="U20" s="2" t="n">
-        <f aca="false">H20+F20+B20+D20+K20+O20</f>
-        <v>335</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <f aca="false">U20-$T$42*1000*T20/100</f>
-        <v>195.64737</v>
-      </c>
-      <c r="W20" s="1" t="n">
-        <f aca="false">ROUND(V20/S20 *100/1000, 2)</f>
-        <v>0.59</v>
-      </c>
-      <c r="Y20" s="1" t="n">
-        <f aca="false">T20*50000/100</f>
-        <v>115</v>
-      </c>
-      <c r="AB20" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="AG20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ20" s="1" t="n">
-        <f aca="false">AH20+AI20/100</f>
-        <v>0.18</v>
-      </c>
-      <c r="AK20" s="1" t="n">
-        <f aca="false">AJ20*1000</f>
-        <v>180</v>
+      <c r="AN20" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO20" s="1" t="n">
+        <f aca="false">AM20+AN20/100</f>
+        <v>0.37</v>
+      </c>
+      <c r="AP20" s="1" t="n">
+        <f aca="false">AO20*1000</f>
+        <v>370</v>
+      </c>
+      <c r="AS20" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV20" s="17" t="n">
+        <f aca="false">AT20+AU20/10</f>
+        <v>2.5</v>
+      </c>
+      <c r="AW20" s="17" t="n">
+        <f aca="false">1000*AV20</f>
+        <v>2500</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="14" t="n">
-        <v>41</v>
+      <c r="A21" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>97</v>
       </c>
       <c r="C21" s="14" t="n">
-        <f aca="false">1000*B21/$S21</f>
-        <v>759.034360189574</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>24</v>
+        <f aca="false">1000*B21/$U21</f>
+        <v>299.863052234907</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>160</v>
       </c>
       <c r="E21" s="14" t="n">
-        <f aca="false">1000*D21/$S21</f>
-        <v>444.312796208531</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>0.1</v>
+        <f aca="false">1000*D21/$U21</f>
+        <v>494.619467603971</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>241.4</v>
       </c>
       <c r="G21" s="14" t="n">
-        <f aca="false">1000*F21/$S21</f>
-        <v>1.85130331753555</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>31</v>
+        <f aca="false">1000*F21/$U21</f>
+        <v>746.257121747491</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>331</v>
       </c>
       <c r="I21" s="14" t="n">
-        <f aca="false">1000*H21/$S21</f>
-        <v>573.904028436019</v>
+        <f aca="false">1000*H21/$U21</f>
+        <v>1023.24402360571</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.21</v>
+        <v>2.52</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="L21" s="14" t="n">
-        <f aca="false">1000*K21/$S21</f>
-        <v>2591.82464454976</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>0.8</v>
+        <f aca="false">L21*$K$37/100</f>
+        <v>159.8</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>940</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <f aca="false">1000*L21/$U21</f>
+        <v>2905.88937217333</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="O21" s="1" t="n">
-        <f aca="false">N21*N$34/100*1000</f>
-        <v>132</v>
-      </c>
-      <c r="P21" s="14" t="n">
-        <f aca="false">1000*O21/$S21</f>
-        <v>2443.72037914692</v>
+        <v>1.3</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <f aca="false">Q21*$P$37/100</f>
+        <v>516.8</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R21" s="1" t="n">
-        <v>0.53</v>
+        <v>3800</v>
+      </c>
+      <c r="R21" s="14" t="n">
+        <f aca="false">1000*P21/$U21</f>
+        <v>1597.62088036082</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>54.016</v>
+        <v>3</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <f aca="false">H21+F21+B21+D21+K21+O21</f>
-        <v>368.1</v>
+        <v>0.43</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>323.481</v>
       </c>
       <c r="V21" s="1" t="n">
-        <f aca="false">U21-$T$42*1000*T21/100</f>
-        <v>95.45355</v>
-      </c>
-      <c r="W21" s="1" t="n">
-        <f aca="false">ROUND(V21/S21 *100/1000, 2)</f>
-        <v>0.18</v>
+        <f aca="false">100*U21/$U$36</f>
+        <v>2.22177211809615</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <f aca="false">H21+F21+B21+D21+K21+P21</f>
+        <v>1506</v>
+      </c>
+      <c r="X21" s="22" t="n">
+        <f aca="false">F21</f>
+        <v>241.4</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <f aca="false">T21*50000/100</f>
-        <v>225</v>
-      </c>
-      <c r="AB21" s="1" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="AG21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH21" s="1" t="n">
+        <f aca="false">-X21+($V$45 + $V$46)*1000*V21/100</f>
+        <v>753.42290537085</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <f aca="false">Y21/U21/10</f>
+        <v>0.232911022709479</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <f aca="false">ROUND(Y21/U21 *100/1000, 2)</f>
+        <v>0.23</v>
+      </c>
+      <c r="AC21" s="1" t="n">
+        <f aca="false">-V21*($V$47)*10</f>
+        <v>-533.225308343076</v>
+      </c>
+      <c r="AD21" s="1" t="n">
+        <f aca="false">AC21/U21/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG21" s="1" t="n">
+        <v>602.4</v>
+      </c>
+      <c r="AL21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ21" s="1" t="n">
-        <f aca="false">AH21+AI21/100</f>
-        <v>0.14</v>
-      </c>
-      <c r="AK21" s="1" t="n">
-        <f aca="false">AJ21*1000</f>
-        <v>140</v>
+      <c r="AN21" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="AO21" s="1" t="n">
+        <f aca="false">AM21+AN21/100</f>
+        <v>0.94</v>
+      </c>
+      <c r="AP21" s="1" t="n">
+        <f aca="false">AO21*1000</f>
+        <v>940</v>
+      </c>
+      <c r="AS21" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV21" s="17" t="n">
+        <f aca="false">AT21+AU21/10</f>
+        <v>3.8</v>
+      </c>
+      <c r="AW21" s="17" t="n">
+        <f aca="false">1000*AV21</f>
+        <v>3800</v>
+      </c>
+      <c r="AX21" s="17" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="18" t="n">
-        <v>10</v>
+      <c r="A22" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>464</v>
       </c>
       <c r="C22" s="14" t="n">
-        <f aca="false">1000*B22/$S22</f>
-        <v>198.137507430157</v>
-      </c>
-      <c r="D22" s="23"/>
+        <f aca="false">1000*B22/$U22</f>
+        <v>255.791133309077</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>891</v>
+      </c>
       <c r="E22" s="14" t="n">
-        <f aca="false">1000*D22/$S22</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>0</v>
+        <f aca="false">1000*D22/$U22</f>
+        <v>491.185128832732</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>544.5</v>
       </c>
       <c r="G22" s="14" t="n">
-        <f aca="false">1000*F22/$S22</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>208</v>
+        <f aca="false">1000*F22/$U22</f>
+        <v>300.168689842225</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>2618</v>
       </c>
       <c r="I22" s="14" t="n">
-        <f aca="false">1000*H22/$S22</f>
-        <v>4121.26015454726</v>
+        <f aca="false">1000*H22/$U22</f>
+        <v>1443.23531681716</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1.55</v>
+        <v>10.01</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>210</v>
-      </c>
-      <c r="L22" s="14" t="n">
-        <f aca="false">1000*K22/$S22</f>
-        <v>4160.88765603329</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>1.8</v>
+        <f aca="false">L22*$K$37/100</f>
+        <v>1208.7</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>7110</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <f aca="false">1000*L22/$U22</f>
+        <v>3919.55809876625</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>0.6</v>
+        <v>56.5</v>
       </c>
       <c r="O22" s="1" t="n">
-        <f aca="false">N22*N$34/100*1000</f>
-        <v>264</v>
-      </c>
-      <c r="P22" s="14" t="n">
-        <f aca="false">1000*O22/$S22</f>
-        <v>5230.83019615613</v>
+        <v>18.9</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <f aca="false">Q22*$P$37/100</f>
+        <v>7684</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>1.21</v>
+        <v>56500</v>
+      </c>
+      <c r="R22" s="14" t="n">
+        <f aca="false">1000*P22/$U22</f>
+        <v>4235.98937143739</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>50.47</v>
+        <v>12.3</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="U22" s="2" t="n">
-        <f aca="false">H22+F22+B22+D22+K22+O22</f>
-        <v>692</v>
+        <v>1.54</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>1813.98</v>
       </c>
       <c r="V22" s="1" t="n">
-        <f aca="false">U22-$T$42*1000*T22/100</f>
-        <v>401.17712</v>
-      </c>
-      <c r="W22" s="1" t="n">
-        <f aca="false">ROUND(V22/S22 *100/1000, 2)</f>
-        <v>0.79</v>
+        <f aca="false">100*U22/$U$36</f>
+        <v>12.4590012606121</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <f aca="false">H22+F22+B22+D22+K22+P22</f>
+        <v>13410.2</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <f aca="false">B22+F22</f>
+        <v>1008.5</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <f aca="false">T22*50000/100</f>
-        <v>240</v>
-      </c>
-      <c r="AB22" s="1" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="AG22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AH22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ22" s="1" t="n">
-        <f aca="false">AH22+AI22/100</f>
-        <v>0.21</v>
-      </c>
-      <c r="AK22" s="1" t="n">
-        <f aca="false">AJ22*1000</f>
-        <v>210</v>
+        <f aca="false">-X22+($V$45 + $V$46)*1000*V22/100</f>
+        <v>4570.15486345292</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <f aca="false">Y22/U22/10</f>
+        <v>0.251940752569098</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <f aca="false">ROUND(Y22/U22 *100/1000, 2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="AC22" s="1" t="n">
+        <f aca="false">-V22*($V$47)*10</f>
+        <v>-2990.1603025469</v>
+      </c>
+      <c r="AD22" s="1" t="n">
+        <f aca="false">AC22/U22/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG22" s="1" t="n">
+        <v>2258</v>
+      </c>
+      <c r="AL22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN22" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO22" s="1" t="n">
+        <f aca="false">AM22+AN22/100</f>
+        <v>7.11</v>
+      </c>
+      <c r="AP22" s="1" t="n">
+        <f aca="false">AO22*1000</f>
+        <v>7110</v>
+      </c>
+      <c r="AS22" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT22" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="AU22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV22" s="17" t="n">
+        <f aca="false">AT22+AU22/10</f>
+        <v>56.5</v>
+      </c>
+      <c r="AW22" s="17" t="n">
+        <f aca="false">1000*AV22</f>
+        <v>56500</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>7</v>
+      <c r="A23" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>27</v>
       </c>
       <c r="C23" s="14" t="n">
-        <f aca="false">1000*B23/$S23</f>
-        <v>510.538983298082</v>
-      </c>
-      <c r="D23" s="21"/>
+        <f aca="false">1000*B23/$U23</f>
+        <v>816.326530612245</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>20</v>
+      </c>
       <c r="E23" s="14" t="n">
-        <f aca="false">1000*D23/$S23</f>
+        <f aca="false">1000*D23/$U23</f>
+        <v>604.686318972033</v>
+      </c>
+      <c r="F23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="14" t="n">
+      <c r="G23" s="14" t="n">
+        <f aca="false">1000*F23/$U23</f>
         <v>0</v>
       </c>
-      <c r="G23" s="14" t="n">
-        <f aca="false">1000*F23/$S23</f>
+      <c r="H23" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <f aca="false">1000*H23/$U23</f>
+        <v>604.686318972033</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <f aca="false">L23*$K$37/100</f>
+        <v>30.6</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <f aca="false">1000*L23/$U23</f>
+        <v>5442.1768707483</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <f aca="false">Q23*$P$37/100</f>
+        <v>68</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="R23" s="14" t="n">
+        <f aca="false">1000*P23/$U23</f>
+        <v>2055.93348450491</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>33.075</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <f aca="false">100*U23/$U$36</f>
+        <v>0.227169796080852</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <f aca="false">H23+F23+B23+D23+K23+P23</f>
+        <v>165.6</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <f aca="false">-X23+($V$45 + $V$46)*1000*V23/100</f>
+        <v>101.717775062959</v>
+      </c>
+      <c r="Z23" s="1" t="n">
+        <f aca="false">Y23/U23/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA23" s="1" t="n">
+        <f aca="false">ROUND(Y23/U23 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC23" s="1" t="n">
+        <f aca="false">-V23*($V$47)*10</f>
+        <v>-54.5207510594045</v>
+      </c>
+      <c r="AD23" s="1" t="n">
+        <f aca="false">AC23/U23/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG23" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="AL23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <f aca="false">1000*H23/$S23</f>
-        <v>656.407264240391</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>270</v>
-      </c>
-      <c r="L23" s="14" t="n">
-        <f aca="false">1000*K23/$S23</f>
-        <v>19692.2179272117</v>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <f aca="false">N23*N$34/100*1000</f>
-        <v>132</v>
-      </c>
-      <c r="P23" s="14" t="n">
-        <f aca="false">1000*O23/$S23</f>
-        <v>9627.3065421924</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>13.711</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="U23" s="2" t="n">
-        <f aca="false">H23+F23+B23+D23+K23+O23</f>
-        <v>418</v>
-      </c>
-      <c r="V23" s="1" t="n">
-        <f aca="false">U23-$T$42*1000*T23/100</f>
-        <v>339.23547</v>
-      </c>
-      <c r="W23" s="1" t="n">
-        <f aca="false">ROUND(V23/S23 *100/1000, 2)</f>
-        <v>2.47</v>
-      </c>
-      <c r="Y23" s="1" t="n">
-        <f aca="false">T23*50000/100</f>
-        <v>65</v>
-      </c>
-      <c r="AB23" s="1" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="AG23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH23" s="1" t="n">
+      <c r="AN23" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO23" s="1" t="n">
+        <f aca="false">AM23+AN23/100</f>
+        <v>0.18</v>
+      </c>
+      <c r="AP23" s="1" t="n">
+        <f aca="false">AO23*1000</f>
+        <v>180</v>
+      </c>
+      <c r="AS23" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ23" s="1" t="n">
-        <f aca="false">AH23+AI23/100</f>
-        <v>0.27</v>
-      </c>
-      <c r="AK23" s="1" t="n">
-        <f aca="false">AJ23*1000</f>
-        <v>270</v>
+      <c r="AU23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV23" s="17" t="n">
+        <f aca="false">AT23+AU23/10</f>
+        <v>0.5</v>
+      </c>
+      <c r="AW23" s="17" t="n">
+        <f aca="false">1000*AV23</f>
+        <v>500</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="18" t="n">
-        <v>332</v>
+      <c r="A24" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>41</v>
       </c>
       <c r="C24" s="14" t="n">
-        <f aca="false">1000*B24/$S24</f>
-        <v>396.580804533444</v>
-      </c>
-      <c r="D24" s="19" t="n">
-        <v>652</v>
+        <f aca="false">1000*B24/$U24</f>
+        <v>759.034360189574</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>24</v>
       </c>
       <c r="E24" s="14" t="n">
-        <f aca="false">1000*D24/$S24</f>
-        <v>778.827363119896</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1961</v>
+        <f aca="false">1000*D24/$U24</f>
+        <v>444.312796208531</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>0.1</v>
       </c>
       <c r="G24" s="14" t="n">
-        <f aca="false">1000*F24/$S24</f>
-        <v>2342.4546918376</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>913</v>
+        <f aca="false">1000*F24/$U24</f>
+        <v>1.85130331753555</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>31</v>
       </c>
       <c r="I24" s="14" t="n">
-        <f aca="false">1000*H24/$S24</f>
-        <v>1090.59721246697</v>
+        <f aca="false">1000*H24/$U24</f>
+        <v>573.904028436019</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>8.82</v>
+        <v>0.21</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>1980</v>
-      </c>
-      <c r="L24" s="14" t="n">
-        <f aca="false">1000*K24/$S24</f>
-        <v>2365.15058125367</v>
-      </c>
-      <c r="M24" s="1" t="n">
-        <v>11</v>
+        <f aca="false">L24*$K$37/100</f>
+        <v>23.8</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <f aca="false">1000*L24/$U24</f>
+        <v>2591.82464454976</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="O24" s="1" t="n">
-        <f aca="false">N24*N$34/100*1000</f>
-        <v>1628</v>
-      </c>
-      <c r="P24" s="14" t="n">
-        <f aca="false">1000*O24/$S24</f>
-        <v>1944.67936680858</v>
+        <v>0.3</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <f aca="false">Q24*$P$37/100</f>
+        <v>108.8</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>0.61</v>
+        <v>800</v>
+      </c>
+      <c r="R24" s="14" t="n">
+        <f aca="false">1000*P24/$U24</f>
+        <v>2014.21800947867</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>837.156</v>
+        <v>0.5</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="U24" s="2" t="n">
-        <f aca="false">H24+F24+B24+D24+K24+O24</f>
-        <v>7466</v>
+        <v>0.53</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>54.016</v>
       </c>
       <c r="V24" s="1" t="n">
-        <f aca="false">U24-$T$42*1000*T24/100</f>
-        <v>3691.36137</v>
-      </c>
-      <c r="W24" s="1" t="n">
-        <f aca="false">ROUND(V24/S24 *100/1000, 2)</f>
-        <v>0.44</v>
+        <f aca="false">100*U24/$U$36</f>
+        <v>0.370999356163366</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <f aca="false">H24+F24+B24+D24+K24+P24</f>
+        <v>228.7</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <f aca="false">T24*50000/100</f>
-        <v>3115</v>
-      </c>
-      <c r="AB24" s="1" t="n">
-        <v>1170.6</v>
-      </c>
-      <c r="AG24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI24" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="AJ24" s="1" t="n">
-        <f aca="false">AH24+AI24/100</f>
-        <v>1.98</v>
-      </c>
-      <c r="AK24" s="1" t="n">
-        <f aca="false">AJ24*1000</f>
-        <v>1980</v>
+        <f aca="false">-X24+($V$45 + $V$46)*1000*V24/100</f>
+        <v>166.119042715065</v>
+      </c>
+      <c r="Z24" s="1" t="n">
+        <f aca="false">Y24/U24/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA24" s="1" t="n">
+        <f aca="false">ROUND(Y24/U24 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC24" s="1" t="n">
+        <f aca="false">-V24*($V$47)*10</f>
+        <v>-89.0398454792077</v>
+      </c>
+      <c r="AD24" s="1" t="n">
+        <f aca="false">AC24/U24/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG24" s="1" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AL24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO24" s="1" t="n">
+        <f aca="false">AM24+AN24/100</f>
+        <v>0.14</v>
+      </c>
+      <c r="AP24" s="1" t="n">
+        <f aca="false">AO24*1000</f>
+        <v>140</v>
+      </c>
+      <c r="AS24" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV24" s="17" t="n">
+        <f aca="false">AT24+AU24/10</f>
+        <v>0.8</v>
+      </c>
+      <c r="AW24" s="17" t="n">
+        <f aca="false">1000*AV24</f>
+        <v>800</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="14" t="n">
-        <v>494</v>
+      <c r="A25" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="C25" s="14" t="n">
-        <f aca="false">1000*B25/$S25</f>
-        <v>901.606282772202</v>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>427</v>
-      </c>
+        <f aca="false">1000*B25/$U25</f>
+        <v>198.137507430157</v>
+      </c>
+      <c r="D25" s="25"/>
       <c r="E25" s="14" t="n">
-        <f aca="false">1000*D25/$S25</f>
-        <v>779.323649278806</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>63</v>
+        <f aca="false">1000*D25/$U25</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="G25" s="14" t="n">
-        <f aca="false">1000*F25/$S25</f>
-        <v>114.982177762447</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>560</v>
+        <f aca="false">1000*F25/$U25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>208</v>
       </c>
       <c r="I25" s="14" t="n">
-        <f aca="false">1000*H25/$S25</f>
-        <v>1022.06380233286</v>
+        <f aca="false">1000*H25/$U25</f>
+        <v>4121.26015454726</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1190</v>
-      </c>
-      <c r="L25" s="14" t="n">
-        <f aca="false">1000*K25/$S25</f>
-        <v>2171.88557995733</v>
-      </c>
-      <c r="M25" s="1" t="n">
+        <f aca="false">L25*$K$37/100</f>
+        <v>35.7</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <f aca="false">1000*L25/$U25</f>
+        <v>4160.88765603329</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <f aca="false">Q25*$P$37/100</f>
+        <v>244.8</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>1800</v>
+      </c>
+      <c r="R25" s="14" t="n">
+        <f aca="false">1000*P25/$U25</f>
+        <v>4850.40618189023</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <f aca="false">100*U25/$U$36</f>
+        <v>0.346644281427078</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <f aca="false">H25+F25+B25+D25+K25+P25</f>
+        <v>498.5</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <f aca="false">-X25+($V$45 + $V$46)*1000*V25/100</f>
+        <v>155.21379009607</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <f aca="false">Y25/U25/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA25" s="1" t="n">
+        <f aca="false">ROUND(Y25/U25 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC25" s="1" t="n">
+        <f aca="false">-V25*($V$47)*10</f>
+        <v>-83.1946275424988</v>
+      </c>
+      <c r="AD25" s="1" t="n">
+        <f aca="false">AC25/U25/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG25" s="1" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="AL25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AM25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO25" s="1" t="n">
+        <f aca="false">AM25+AN25/100</f>
+        <v>0.21</v>
+      </c>
+      <c r="AP25" s="1" t="n">
+        <f aca="false">AO25*1000</f>
+        <v>210</v>
+      </c>
+      <c r="AS25" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="N25" s="1" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O25" s="1" t="n">
-        <f aca="false">N25*N$34/100*1000</f>
-        <v>1188</v>
-      </c>
-      <c r="P25" s="14" t="n">
-        <f aca="false">1000*O25/$S25</f>
-        <v>2168.23535209186</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R25" s="1" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>547.911</v>
-      </c>
-      <c r="T25" s="1" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="U25" s="2" t="n">
-        <f aca="false">H25+F25+B25+D25+K25+O25</f>
-        <v>3922</v>
-      </c>
-      <c r="V25" s="1" t="n">
-        <f aca="false">U25-$T$42*1000*T25/100</f>
-        <v>947.12429</v>
-      </c>
-      <c r="W25" s="1" t="n">
-        <f aca="false">ROUND(V25/S25 *100/1000, 2)</f>
-        <v>0.17</v>
-      </c>
-      <c r="Y25" s="1" t="n">
-        <f aca="false">T25*50000/100</f>
-        <v>2455</v>
-      </c>
-      <c r="AB25" s="1" t="n">
-        <v>922.9</v>
-      </c>
-      <c r="AG25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI25" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ25" s="1" t="n">
-        <f aca="false">AH25+AI25/100</f>
-        <v>1.19</v>
-      </c>
-      <c r="AK25" s="1" t="n">
-        <f aca="false">AJ25*1000</f>
-        <v>1190</v>
+      <c r="AV25" s="17" t="n">
+        <f aca="false">AT25+AU25/10</f>
+        <v>1.8</v>
+      </c>
+      <c r="AW25" s="17" t="n">
+        <f aca="false">1000*AV25</f>
+        <v>1800</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="18" t="n">
-        <v>136</v>
+      <c r="A26" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="C26" s="14" t="n">
-        <f aca="false">1000*B26/$S26</f>
-        <v>641.88790560472</v>
-      </c>
-      <c r="D26" s="19" t="n">
-        <v>84</v>
-      </c>
+        <f aca="false">1000*B26/$U26</f>
+        <v>510.538983298082</v>
+      </c>
+      <c r="D26" s="23"/>
       <c r="E26" s="14" t="n">
-        <f aca="false">1000*D26/$S26</f>
-        <v>396.46017699115</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>24.9</v>
+        <f aca="false">1000*D26/$U26</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G26" s="14" t="n">
-        <f aca="false">1000*F26/$S26</f>
-        <v>117.522123893805</v>
-      </c>
-      <c r="H26" s="18" t="n">
-        <v>330</v>
+        <f aca="false">1000*F26/$U26</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>9</v>
       </c>
       <c r="I26" s="14" t="n">
-        <f aca="false">1000*H26/$S26</f>
-        <v>1557.52212389381</v>
+        <f aca="false">1000*H26/$U26</f>
+        <v>656.407264240391</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>4.14</v>
+        <v>0.29</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>1950</v>
-      </c>
-      <c r="L26" s="14" t="n">
-        <f aca="false">1000*K26/$S26</f>
-        <v>9203.53982300885</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>6.4</v>
+        <f aca="false">L26*$K$37/100</f>
+        <v>45.9</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <f aca="false">1000*L26/$U26</f>
+        <v>19692.2179272117</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="O26" s="1" t="n">
-        <f aca="false">N26*N$34/100*1000</f>
-        <v>924</v>
-      </c>
-      <c r="P26" s="14" t="n">
-        <f aca="false">1000*O26/$S26</f>
-        <v>4361.06194690266</v>
+        <v>0.3</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <f aca="false">Q26*$P$37/100</f>
+        <v>122.4</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R26" s="1" t="n">
-        <v>1.34</v>
+        <v>900</v>
+      </c>
+      <c r="R26" s="14" t="n">
+        <f aca="false">1000*P26/$U26</f>
+        <v>8927.13879366932</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>211.875</v>
+        <v>0.1</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U26" s="2" t="n">
-        <f aca="false">H26+F26+B26+D26+K26+O26</f>
-        <v>3448.9</v>
+        <v>3.11</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>13.711</v>
       </c>
       <c r="V26" s="1" t="n">
-        <f aca="false">U26-$T$42*1000*T26/100</f>
-        <v>2461.31397</v>
-      </c>
-      <c r="W26" s="1" t="n">
-        <f aca="false">ROUND(V26/S26 *100/1000, 2)</f>
-        <v>1.16</v>
+        <f aca="false">100*U26/$U$36</f>
+        <v>0.0941715819822998</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <f aca="false">H26+F26+B26+D26+K26+P26</f>
+        <v>184.3</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <f aca="false">T26*50000/100</f>
-        <v>815</v>
-      </c>
-      <c r="AB26" s="1" t="n">
-        <v>306.8</v>
-      </c>
-      <c r="AG26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI26" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ26" s="1" t="n">
-        <f aca="false">AH26+AI26/100</f>
-        <v>1.95</v>
-      </c>
-      <c r="AK26" s="1" t="n">
-        <f aca="false">AJ26*1000</f>
-        <v>1950</v>
+        <f aca="false">-X26+($V$45 + $V$46)*1000*V26/100</f>
+        <v>42.1663617199765</v>
+      </c>
+      <c r="Z26" s="1" t="n">
+        <f aca="false">Y26/U26/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA26" s="1" t="n">
+        <f aca="false">ROUND(Y26/U26 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC26" s="1" t="n">
+        <f aca="false">-V26*($V$47)*10</f>
+        <v>-22.6011796757519</v>
+      </c>
+      <c r="AD26" s="1" t="n">
+        <f aca="false">AC26/U26/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG26" s="1" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AL26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO26" s="1" t="n">
+        <f aca="false">AM26+AN26/100</f>
+        <v>0.27</v>
+      </c>
+      <c r="AP26" s="1" t="n">
+        <f aca="false">AO26*1000</f>
+        <v>270</v>
+      </c>
+      <c r="AS26" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV26" s="17" t="n">
+        <f aca="false">AT26+AU26/10</f>
+        <v>0.9</v>
+      </c>
+      <c r="AW26" s="17" t="n">
+        <f aca="false">1000*AV26</f>
+        <v>900</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="14" t="n">
-        <v>133</v>
+      <c r="A27" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>332</v>
       </c>
       <c r="C27" s="14" t="n">
-        <f aca="false">1000*B27/$S27</f>
-        <v>617.708255926284</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>30</v>
+        <f aca="false">1000*B27/$U27</f>
+        <v>396.580804533444</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>652</v>
       </c>
       <c r="E27" s="14" t="n">
-        <f aca="false">1000*D27/$S27</f>
-        <v>139.332689306681</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>1.9</v>
+        <f aca="false">1000*D27/$U27</f>
+        <v>778.827363119896</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>1961</v>
       </c>
       <c r="G27" s="14" t="n">
-        <f aca="false">1000*F27/$S27</f>
-        <v>8.82440365608977</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <v>121</v>
+        <f aca="false">1000*F27/$U27</f>
+        <v>2342.4546918376</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>913</v>
       </c>
       <c r="I27" s="14" t="n">
-        <f aca="false">1000*H27/$S27</f>
-        <v>561.975180203611</v>
+        <f aca="false">1000*H27/$U27</f>
+        <v>1090.59721246697</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.87</v>
+        <v>8.82</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>620</v>
-      </c>
-      <c r="L27" s="14" t="n">
-        <f aca="false">1000*K27/$S27</f>
-        <v>2879.5422456714</v>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>3.2</v>
+        <f aca="false">L27*$K$37/100</f>
+        <v>336.6</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <f aca="false">1000*L27/$U27</f>
+        <v>2365.15058125367</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="O27" s="1" t="n">
-        <f aca="false">N27*N$34/100*1000</f>
-        <v>484</v>
-      </c>
-      <c r="P27" s="14" t="n">
-        <f aca="false">1000*O27/$S27</f>
-        <v>2247.90072081445</v>
+        <v>3.7</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <f aca="false">Q27*$P$37/100</f>
+        <v>1496</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>0.49</v>
+        <v>11000</v>
+      </c>
+      <c r="R27" s="14" t="n">
+        <f aca="false">1000*P27/$U27</f>
+        <v>1787.00266139166</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>215.312</v>
+        <v>6</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U27" s="2" t="n">
-        <f aca="false">H27+F27+B27+D27+K27+O27</f>
-        <v>1389.9</v>
+        <v>0.61</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>837.156</v>
       </c>
       <c r="V27" s="1" t="n">
-        <f aca="false">U27-$T$42*1000*T27/100</f>
-        <v>166.02038</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <f aca="false">ROUND(V27/S27 *100/1000, 2)</f>
-        <v>0.08</v>
+        <f aca="false">100*U27/$U$36</f>
+        <v>5.74985813478041</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <f aca="false">H27+F27+B27+D27+K27+P27</f>
+        <v>5690.6</v>
       </c>
       <c r="Y27" s="1" t="n">
-        <f aca="false">T27*50000/100</f>
-        <v>1010</v>
-      </c>
-      <c r="AB27" s="1" t="n">
-        <v>380.1</v>
-      </c>
-      <c r="AG27" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH27" s="1" t="n">
+        <f aca="false">-X27+($V$45 + $V$46)*1000*V27/100</f>
+        <v>2574.56222828741</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <f aca="false">Y27/U27/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA27" s="1" t="n">
+        <f aca="false">ROUND(Y27/U27 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC27" s="1" t="n">
+        <f aca="false">-V27*($V$47)*10</f>
+        <v>-1379.9659523473</v>
+      </c>
+      <c r="AD27" s="1" t="n">
+        <f aca="false">AC27/U27/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG27" s="1" t="n">
+        <v>1170.6</v>
+      </c>
+      <c r="AL27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN27" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="AO27" s="1" t="n">
+        <f aca="false">AM27+AN27/100</f>
+        <v>1.98</v>
+      </c>
+      <c r="AP27" s="1" t="n">
+        <f aca="false">AO27*1000</f>
+        <v>1980</v>
+      </c>
+      <c r="AS27" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="AJ27" s="1" t="n">
-        <f aca="false">AH27+AI27/100</f>
-        <v>0.62</v>
-      </c>
-      <c r="AK27" s="1" t="n">
-        <f aca="false">AJ27*1000</f>
-        <v>620</v>
+      <c r="AV27" s="17" t="n">
+        <f aca="false">AT27+AU27/10</f>
+        <v>11</v>
+      </c>
+      <c r="AW27" s="17" t="n">
+        <f aca="false">1000*AV27</f>
+        <v>11000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="18" t="n">
-        <v>76</v>
+      <c r="A28" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>494</v>
       </c>
       <c r="C28" s="14" t="n">
-        <f aca="false">1000*B28/$S28</f>
-        <v>781.105469793829</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <v>37</v>
+        <f aca="false">1000*B28/$U28</f>
+        <v>901.606282772202</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>427</v>
       </c>
       <c r="E28" s="14" t="n">
-        <f aca="false">1000*D28/$S28</f>
-        <v>380.275031346996</v>
-      </c>
-      <c r="F28" s="18" t="n">
+        <f aca="false">1000*D28/$U28</f>
+        <v>779.323649278806</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <f aca="false">1000*F28/$U28</f>
+        <v>114.982177762447</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>560</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <f aca="false">1000*H28/$U28</f>
+        <v>1022.06380233286</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <f aca="false">L28*$K$37/100</f>
+        <v>202.3</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>1190</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <f aca="false">1000*L28/$U28</f>
+        <v>2171.88557995733</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <f aca="false">Q28*$P$37/100</f>
+        <v>1088</v>
+      </c>
+      <c r="Q28" s="1" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R28" s="14" t="n">
+        <f aca="false">1000*P28/$U28</f>
+        <v>1985.72395881813</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>547.911</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <f aca="false">100*U28/$U$36</f>
+        <v>3.76322993621937</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <f aca="false">H28+F28+B28+D28+K28+P28</f>
+        <v>2834.3</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <f aca="false">-X28+($V$45 + $V$46)*1000*V28/100</f>
+        <v>1685.02759947152</v>
+      </c>
+      <c r="Z28" s="1" t="n">
+        <f aca="false">Y28/U28/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA28" s="1" t="n">
+        <f aca="false">ROUND(Y28/U28 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC28" s="1" t="n">
+        <f aca="false">-V28*($V$47)*10</f>
+        <v>-903.17518469265</v>
+      </c>
+      <c r="AD28" s="1" t="n">
+        <f aca="false">AC28/U28/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG28" s="1" t="n">
+        <v>922.9</v>
+      </c>
+      <c r="AL28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO28" s="1" t="n">
+        <f aca="false">AM28+AN28/100</f>
+        <v>1.19</v>
+      </c>
+      <c r="AP28" s="1" t="n">
+        <f aca="false">AO28*1000</f>
+        <v>1190</v>
+      </c>
+      <c r="AS28" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="14" t="n">
-        <f aca="false">1000*F28/$S28</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <f aca="false">1000*H28/$S28</f>
-        <v>195.276367448457</v>
-      </c>
-      <c r="J28" s="1" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K28" s="1" t="n">
-        <v>400</v>
-      </c>
-      <c r="L28" s="14" t="n">
-        <f aca="false">1000*K28/$S28</f>
-        <v>4111.08141996752</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N28" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O28" s="1" t="n">
-        <f aca="false">N28*N$34/100*1000</f>
-        <v>176</v>
-      </c>
-      <c r="P28" s="14" t="n">
-        <f aca="false">1000*O28/$S28</f>
-        <v>1808.87582478571</v>
-      </c>
-      <c r="Q28" s="1" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R28" s="1" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>97.298</v>
-      </c>
-      <c r="T28" s="1" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="U28" s="2" t="n">
-        <f aca="false">H28+F28+B28+D28+K28+O28</f>
-        <v>708</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <f aca="false">U28-$T$42*1000*T28/100</f>
-        <v>265.70687</v>
-      </c>
-      <c r="W28" s="1" t="n">
-        <f aca="false">ROUND(V28/S28 *100/1000, 2)</f>
-        <v>0.27</v>
-      </c>
-      <c r="Y28" s="1" t="n">
-        <f aca="false">T28*50000/100</f>
-        <v>365</v>
-      </c>
-      <c r="AB28" s="1" t="n">
-        <v>136.8</v>
-      </c>
-      <c r="AG28" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ28" s="1" t="n">
-        <f aca="false">AH28+AI28/100</f>
-        <v>0.4</v>
-      </c>
-      <c r="AK28" s="1" t="n">
-        <f aca="false">AJ28*1000</f>
-        <v>400</v>
+      <c r="AV28" s="17" t="n">
+        <f aca="false">AT28+AU28/10</f>
+        <v>8</v>
+      </c>
+      <c r="AW28" s="17" t="n">
+        <f aca="false">1000*AV28</f>
+        <v>8000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="14" t="n">
-        <v>33</v>
+      <c r="A29" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>136</v>
       </c>
       <c r="C29" s="14" t="n">
-        <f aca="false">1000*B29/$S29</f>
-        <v>641.137728041033</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>14</v>
+        <f aca="false">1000*B29/$U29</f>
+        <v>641.88790560472</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>84</v>
       </c>
       <c r="E29" s="14" t="n">
-        <f aca="false">1000*D29/$S29</f>
-        <v>271.997824017408</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>0.4</v>
+        <f aca="false">1000*D29/$U29</f>
+        <v>396.46017699115</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>24.9</v>
       </c>
       <c r="G29" s="14" t="n">
-        <f aca="false">1000*F29/$S29</f>
-        <v>7.77136640049737</v>
-      </c>
-      <c r="H29" s="14" t="n">
-        <v>75</v>
+        <f aca="false">1000*F29/$U29</f>
+        <v>117.522123893805</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>330</v>
       </c>
       <c r="I29" s="14" t="n">
-        <f aca="false">1000*H29/$S29</f>
-        <v>1457.13120009326</v>
+        <f aca="false">1000*H29/$U29</f>
+        <v>1557.52212389381</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.05</v>
+        <v>4.14</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="L29" s="14" t="n">
-        <f aca="false">1000*K29/$S29</f>
-        <v>5828.52480037303</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>1.1</v>
+        <f aca="false">L29*$K$37/100</f>
+        <v>331.5</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <f aca="false">1000*L29/$U29</f>
+        <v>9203.53982300885</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="O29" s="1" t="n">
-        <f aca="false">N29*N$34/100*1000</f>
-        <v>176</v>
-      </c>
-      <c r="P29" s="14" t="n">
-        <f aca="false">1000*O29/$S29</f>
-        <v>3419.40121621884</v>
+        <v>2.1</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <f aca="false">Q29*$P$37/100</f>
+        <v>870.4</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R29" s="1" t="n">
-        <v>0.93</v>
+        <v>6400</v>
+      </c>
+      <c r="R29" s="14" t="n">
+        <f aca="false">1000*P29/$U29</f>
+        <v>4108.08259587021</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>51.471</v>
+        <v>1.6</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="U29" s="2" t="n">
-        <f aca="false">H29+F29+B29+D29+K29+O29</f>
-        <v>598.4</v>
+        <v>1.34</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>211.875</v>
       </c>
       <c r="V29" s="1" t="n">
-        <f aca="false">U29-$T$42*1000*T29/100</f>
-        <v>368.16522</v>
-      </c>
-      <c r="W29" s="1" t="n">
-        <f aca="false">ROUND(V29/S29 *100/1000, 2)</f>
-        <v>0.72</v>
+        <f aca="false">100*U29/$U$36</f>
+        <v>1.45522601797825</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <f aca="false">H29+F29+B29+D29+K29+P29</f>
+        <v>1776.8</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <f aca="false">T29*50000/100</f>
-        <v>190</v>
-      </c>
-      <c r="AB29" s="1" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="AG29" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ29" s="1" t="n">
-        <f aca="false">AH29+AI29/100</f>
-        <v>0.3</v>
-      </c>
-      <c r="AK29" s="1" t="n">
-        <f aca="false">AJ29*1000</f>
-        <v>300</v>
+        <f aca="false">-X29+($V$45 + $V$46)*1000*V29/100</f>
+        <v>651.593457035959</v>
+      </c>
+      <c r="Z29" s="1" t="n">
+        <f aca="false">Y29/U29/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <f aca="false">ROUND(Y29/U29 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC29" s="1" t="n">
+        <f aca="false">-V29*($V$47)*10</f>
+        <v>-349.25424431478</v>
+      </c>
+      <c r="AD29" s="1" t="n">
+        <f aca="false">AC29/U29/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG29" s="1" t="n">
+        <v>306.8</v>
+      </c>
+      <c r="AL29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO29" s="1" t="n">
+        <f aca="false">AM29+AN29/100</f>
+        <v>1.95</v>
+      </c>
+      <c r="AP29" s="1" t="n">
+        <f aca="false">AO29*1000</f>
+        <v>1950</v>
+      </c>
+      <c r="AS29" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU29" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV29" s="17" t="n">
+        <f aca="false">AT29+AU29/10</f>
+        <v>6.4</v>
+      </c>
+      <c r="AW29" s="17" t="n">
+        <f aca="false">1000*AV29</f>
+        <v>6400</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="18" t="n">
-        <v>683</v>
+      <c r="A30" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>133</v>
       </c>
       <c r="C30" s="14" t="n">
-        <f aca="false">1000*B30/$S30</f>
-        <v>562.985554433614</v>
-      </c>
-      <c r="D30" s="19" t="n">
-        <v>830</v>
+        <f aca="false">1000*B30/$U30</f>
+        <v>617.708255926284</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>30</v>
       </c>
       <c r="E30" s="14" t="n">
-        <f aca="false">1000*D30/$S30</f>
-        <v>684.155212562079</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>240.6</v>
+        <f aca="false">1000*D30/$U30</f>
+        <v>139.332689306681</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>1.9</v>
       </c>
       <c r="G30" s="14" t="n">
-        <f aca="false">1000*F30/$S30</f>
-        <v>198.32258330414</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>2151</v>
+        <f aca="false">1000*F30/$U30</f>
+        <v>8.82440365608977</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>121</v>
       </c>
       <c r="I30" s="14" t="n">
-        <f aca="false">1000*H30/$S30</f>
-        <v>1773.033568941</v>
+        <f aca="false">1000*H30/$U30</f>
+        <v>561.975180203611</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>15.18</v>
+        <v>0.87</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>9330</v>
-      </c>
-      <c r="L30" s="14" t="n">
-        <f aca="false">1000*K30/$S30</f>
-        <v>7690.56401590867</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>30.9</v>
+        <f aca="false">L30*$K$37/100</f>
+        <v>105.4</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>620</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <f aca="false">1000*L30/$U30</f>
+        <v>2879.5422456714</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>10.3</v>
+        <v>3.2</v>
       </c>
       <c r="O30" s="1" t="n">
-        <f aca="false">N30*N$34/100*1000</f>
-        <v>4532</v>
-      </c>
-      <c r="P30" s="14" t="n">
-        <f aca="false">1000*O30/$S30</f>
-        <v>3735.65231726668</v>
+        <v>1.1</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <f aca="false">Q30*$P$37/100</f>
+        <v>435.2</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="R30" s="1" t="n">
-        <v>1.19</v>
+        <v>3200</v>
+      </c>
+      <c r="R30" s="14" t="n">
+        <f aca="false">1000*P30/$U30</f>
+        <v>2021.25287954225</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>1213.175</v>
+        <v>2.2</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="U30" s="2" t="n">
-        <f aca="false">H30+F30+B30+D30+K30+O30</f>
-        <v>17766.6</v>
+        <v>0.49</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>215.312</v>
       </c>
       <c r="V30" s="1" t="n">
-        <f aca="false">U30-$T$42*1000*T30/100</f>
-        <v>12325.78862</v>
-      </c>
-      <c r="W30" s="1" t="n">
-        <f aca="false">ROUND(V30/S30 *100/1000, 2)</f>
-        <v>1.02</v>
+        <f aca="false">100*U30/$U$36</f>
+        <v>1.47883244546517</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <f aca="false">H30+F30+B30+D30+K30+P30</f>
+        <v>826.5</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <f aca="false">T30*50000/100</f>
-        <v>4490</v>
-      </c>
-      <c r="AB30" s="1" t="n">
-        <v>1687.2</v>
-      </c>
-      <c r="AG30" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH30" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI30" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="AJ30" s="1" t="n">
-        <f aca="false">AH30+AI30/100</f>
-        <v>9.33</v>
-      </c>
-      <c r="AK30" s="1" t="n">
-        <f aca="false">AJ30*1000</f>
-        <v>9330</v>
+        <f aca="false">-X30+($V$45 + $V$46)*1000*V30/100</f>
+        <v>662.16349461393</v>
+      </c>
+      <c r="Z30" s="1" t="n">
+        <f aca="false">Y30/U30/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA30" s="1" t="n">
+        <f aca="false">ROUND(Y30/U30 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC30" s="1" t="n">
+        <f aca="false">-V30*($V$47)*10</f>
+        <v>-354.919786911641</v>
+      </c>
+      <c r="AD30" s="1" t="n">
+        <f aca="false">AC30/U30/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG30" s="1" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="AL30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="AO30" s="1" t="n">
+        <f aca="false">AM30+AN30/100</f>
+        <v>0.62</v>
+      </c>
+      <c r="AP30" s="1" t="n">
+        <f aca="false">AO30*1000</f>
+        <v>620</v>
+      </c>
+      <c r="AS30" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV30" s="17" t="n">
+        <f aca="false">AT30+AU30/10</f>
+        <v>3.2</v>
+      </c>
+      <c r="AW30" s="17" t="n">
+        <f aca="false">1000*AV30</f>
+        <v>3200</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="14" t="n">
-        <v>189</v>
+      <c r="A31" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>76</v>
       </c>
       <c r="C31" s="14" t="n">
-        <f aca="false">1000*B31/$S31</f>
-        <v>341.958899796996</v>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>601</v>
+        <f aca="false">1000*B31/$U31</f>
+        <v>781.105469793829</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>37</v>
       </c>
       <c r="E31" s="14" t="n">
-        <f aca="false">1000*D31/$S31</f>
-        <v>1087.39311522748</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>245.1</v>
+        <f aca="false">1000*D31/$U31</f>
+        <v>380.275031346996</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="G31" s="14" t="n">
-        <f aca="false">1000*F31/$S31</f>
-        <v>443.460985927215</v>
-      </c>
-      <c r="H31" s="14" t="n">
-        <v>712</v>
+        <f aca="false">1000*F31/$U31</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>19</v>
       </c>
       <c r="I31" s="14" t="n">
-        <f aca="false">1000*H31/$S31</f>
-        <v>1288.22611987016</v>
+        <f aca="false">1000*H31/$U31</f>
+        <v>195.276367448457</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>1.54</v>
+        <v>0.09</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>1160</v>
-      </c>
-      <c r="L31" s="14" t="n">
-        <f aca="false">1000*K31/$S31</f>
-        <v>2098.79536383341</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>7.1</v>
+        <f aca="false">L31*$K$37/100</f>
+        <v>68</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <f aca="false">1000*L31/$U31</f>
+        <v>4111.08141996752</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="O31" s="1" t="n">
-        <f aca="false">N31*N$34/100*1000</f>
-        <v>1056</v>
-      </c>
-      <c r="P31" s="14" t="n">
-        <f aca="false">1000*O31/$S31</f>
-        <v>1910.62750362766</v>
+        <v>0.4</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <f aca="false">Q31*$P$37/100</f>
+        <v>176.8</v>
       </c>
       <c r="Q31" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R31" s="14" t="n">
+        <f aca="false">1000*P31/$U31</f>
+        <v>1817.09798762565</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>97.298</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <f aca="false">100*U31/$U$36</f>
+        <v>0.668274129072555</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <f aca="false">H31+F31+B31+D31+K31+P31</f>
+        <v>376.8</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <f aca="false">-X31+($V$45 + $V$46)*1000*V31/100</f>
+        <v>299.227092307656</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <f aca="false">Y31/U31/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA31" s="1" t="n">
+        <f aca="false">ROUND(Y31/U31 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC31" s="1" t="n">
+        <f aca="false">-V31*($V$47)*10</f>
+        <v>-160.385790977413</v>
+      </c>
+      <c r="AD31" s="1" t="n">
+        <f aca="false">AC31/U31/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AE31" s="26"/>
+      <c r="AG31" s="1" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="AL31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO31" s="1" t="n">
+        <f aca="false">AM31+AN31/100</f>
+        <v>0.4</v>
+      </c>
+      <c r="AP31" s="1" t="n">
+        <f aca="false">AO31*1000</f>
+        <v>400</v>
+      </c>
+      <c r="AS31" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="R31" s="1" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="S31" s="1" t="n">
-        <v>552.698</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U31" s="2" t="n">
-        <f aca="false">H31+F31+B31+D31+K31+O31</f>
-        <v>3963.1</v>
-      </c>
-      <c r="V31" s="1" t="n">
-        <f aca="false">U31-$T$42*1000*T31/100</f>
-        <v>2024.2808</v>
-      </c>
-      <c r="W31" s="1" t="n">
-        <f aca="false">ROUND(V31/S31 *100/1000, 2)</f>
-        <v>0.37</v>
-      </c>
-      <c r="Y31" s="1" t="n">
-        <f aca="false">T31*50000/100</f>
-        <v>1600</v>
-      </c>
-      <c r="AB31" s="1" t="n">
-        <v>601.2</v>
-      </c>
-      <c r="AG31" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH31" s="1" t="n">
+      <c r="AV31" s="17" t="n">
+        <f aca="false">AT31+AU31/10</f>
+        <v>1.3</v>
+      </c>
+      <c r="AW31" s="17" t="n">
+        <f aca="false">1000*AV31</f>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <f aca="false">1000*B32/$U32</f>
+        <v>641.137728041033</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <f aca="false">1000*D32/$U32</f>
+        <v>271.997824017408</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <f aca="false">1000*F32/$U32</f>
+        <v>7.77136640049737</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <f aca="false">1000*H32/$U32</f>
+        <v>1457.13120009326</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <f aca="false">L32*$K$37/100</f>
+        <v>51</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="M32" s="14" t="n">
+        <f aca="false">1000*L32/$U32</f>
+        <v>5828.52480037303</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <f aca="false">Q32*$P$37/100</f>
+        <v>149.6</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>1100</v>
+      </c>
+      <c r="R32" s="14" t="n">
+        <f aca="false">1000*P32/$U32</f>
+        <v>2906.49103378602</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>51.471</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <f aca="false">100*U32/$U$36</f>
+        <v>0.353519473139155</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <f aca="false">H32+F32+B32+D32+K32+P32</f>
+        <v>323</v>
+      </c>
+      <c r="Y32" s="1" t="n">
+        <f aca="false">-X32+($V$45 + $V$46)*1000*V32/100</f>
+        <v>158.292232812261</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <f aca="false">Y32/U32/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA32" s="1" t="n">
+        <f aca="false">ROUND(Y32/U32 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC32" s="1" t="n">
+        <f aca="false">-V32*($V$47)*10</f>
+        <v>-84.8446735533971</v>
+      </c>
+      <c r="AD32" s="1" t="n">
+        <f aca="false">AC32/U32/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG32" s="1" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AL32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO32" s="1" t="n">
+        <f aca="false">AM32+AN32/100</f>
+        <v>0.3</v>
+      </c>
+      <c r="AP32" s="1" t="n">
+        <f aca="false">AO32*1000</f>
+        <v>300</v>
+      </c>
+      <c r="AS32" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="AT32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AI31" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ31" s="1" t="n">
-        <f aca="false">AH31+AI31/100</f>
-        <v>1.16</v>
-      </c>
-      <c r="AK31" s="1" t="n">
-        <f aca="false">AJ31*1000</f>
-        <v>1160</v>
+      <c r="AU32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" s="17" t="n">
+        <f aca="false">AT32+AU32/10</f>
+        <v>1.1</v>
+      </c>
+      <c r="AW32" s="17" t="n">
+        <f aca="false">1000*AV32</f>
+        <v>1100</v>
       </c>
     </row>
-    <row r="32" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" s="25" t="n">
-        <v>5847</v>
-      </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="26" t="n">
-        <v>9557</v>
-      </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="27" t="n">
-        <v>8334.6</v>
-      </c>
-      <c r="G32" s="27"/>
-      <c r="H32" s="25" t="n">
-        <v>26264</v>
-      </c>
-      <c r="I32" s="25"/>
-      <c r="K32" s="1" t="n">
-        <f aca="false">SUM(K5:K31)</f>
-        <v>47600</v>
-      </c>
-      <c r="O32" s="1" t="n">
-        <f aca="false">SUM(O5:O31)</f>
-        <v>44088</v>
-      </c>
-      <c r="Q32" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="S32" s="1"/>
-      <c r="T32" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="U32" s="2" t="n">
-        <f aca="false">H32+F32+B32+D32+K32+O32</f>
-        <v>141690.6</v>
-      </c>
-      <c r="V32" s="1" t="n">
-        <f aca="false">U32-$T$42*1000*T32/100</f>
-        <v>81102.5</v>
-      </c>
-      <c r="W32" s="28" t="e">
-        <f aca="false">ROUND(V32/S32 *100/1000, 2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y32" s="28" t="n">
-        <f aca="false">T32*50000/100</f>
-        <v>50000</v>
-      </c>
-      <c r="AB32" s="28" t="n">
-        <v>18796</v>
-      </c>
-      <c r="AK32" s="28" t="n">
-        <f aca="false">SUM(AK5:AK31)</f>
-        <v>47600</v>
-      </c>
-      <c r="XFD32" s="1"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="1" t="n">
-        <f aca="false">SUM(B5:B31)</f>
-        <v>5847</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <f aca="false">SUM(D5:D31)</f>
-        <v>9561</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <f aca="false">SUM(F5:F31)</f>
-        <v>8334.5</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <f aca="false">SUM(H5:H31)</f>
-        <v>26264</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>683</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <f aca="false">1000*B33/$U33</f>
+        <v>562.985554433614</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>830</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <f aca="false">1000*D33/$U33</f>
+        <v>684.155212562079</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>240.6</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <f aca="false">1000*F33/$U33</f>
+        <v>198.32258330414</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>2151</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <f aca="false">1000*H33/$U33</f>
+        <v>1773.033568941</v>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>15.18</v>
       </c>
       <c r="K33" s="1" t="n">
-        <f aca="false">SUM(K5:K31)</f>
-        <v>47600</v>
+        <f aca="false">L33*$K$37/100</f>
+        <v>1586.1</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>9330</v>
+      </c>
+      <c r="M33" s="14" t="n">
+        <f aca="false">1000*L33/$U33</f>
+        <v>7690.56401590867</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>30.9</v>
       </c>
       <c r="O33" s="1" t="n">
-        <f aca="false">SUM(O5:O31)</f>
-        <v>44088</v>
-      </c>
-      <c r="U33" s="2" t="n">
-        <f aca="false">SUM(U5:U31)</f>
-        <v>141588.1</v>
+        <v>10.3</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <f aca="false">Q33*$P$37/100</f>
+        <v>4202.4</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>30900</v>
+      </c>
+      <c r="R33" s="14" t="n">
+        <f aca="false">1000*P33/$U33</f>
+        <v>3463.96851237455</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U33" s="1" t="n">
+        <v>1213.175</v>
       </c>
       <c r="V33" s="1" t="n">
-        <f aca="false">SUM(V5:V31)</f>
-        <v>80800.05927</v>
+        <f aca="false">100*U33/$U$36</f>
+        <v>8.33247822707144</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <f aca="false">H33+F33+B33+D33+K33+P33</f>
+        <v>9693.1</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <f aca="false">B33+F33</f>
+        <v>923.6</v>
+      </c>
+      <c r="Y33" s="1" t="n">
+        <f aca="false">-X33+($V$45 + $V$46)*1000*V33/100</f>
+        <v>2807.35878343174</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <f aca="false">Y33/U33/10</f>
+        <v>0.231405921110453</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <f aca="false">ROUND(Y33/U33 *100/1000, 2)</f>
+        <v>0.23</v>
+      </c>
+      <c r="AC33" s="1" t="n">
+        <f aca="false">-V33*($V$47)*10</f>
+        <v>-1999.79477449715</v>
+      </c>
+      <c r="AD33" s="1" t="n">
+        <f aca="false">AC33/U33/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG33" s="1" t="n">
+        <v>1687.2</v>
+      </c>
+      <c r="AL33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AM33" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN33" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="AO33" s="1" t="n">
+        <f aca="false">AM33+AN33/100</f>
+        <v>9.33</v>
+      </c>
+      <c r="AP33" s="1" t="n">
+        <f aca="false">AO33*1000</f>
+        <v>9330</v>
+      </c>
+      <c r="AS33" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT33" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU33" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV33" s="17" t="n">
+        <f aca="false">AT33+AU33/10</f>
+        <v>30.9</v>
+      </c>
+      <c r="AW33" s="17" t="n">
+        <f aca="false">1000*AV33</f>
+        <v>30900</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J34" s="29" t="n">
-        <v>93</v>
-      </c>
-      <c r="N34" s="29" t="n">
-        <v>44</v>
+      <c r="A34" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>189</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <f aca="false">1000*B34/$U34</f>
+        <v>341.958899796996</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>601</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <f aca="false">1000*D34/$U34</f>
+        <v>1087.39311522748</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>245.1</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <f aca="false">1000*F34/$U34</f>
+        <v>443.460985927215</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>712</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <f aca="false">1000*H34/$U34</f>
+        <v>1288.22611987016</v>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <f aca="false">L34*$K$37/100</f>
+        <v>197.2</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>1160</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <f aca="false">1000*L34/$U34</f>
+        <v>2098.79536383341</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O34" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <f aca="false">Q34*$P$37/100</f>
+        <v>965.6</v>
+      </c>
+      <c r="Q34" s="1" t="n">
+        <v>7100</v>
+      </c>
+      <c r="R34" s="14" t="n">
+        <f aca="false">1000*P34/$U34</f>
+        <v>1747.0662097565</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="U34" s="1" t="n">
+        <v>552.698</v>
+      </c>
+      <c r="V34" s="1" t="n">
+        <f aca="false">100*U34/$U$36</f>
+        <v>3.79610860028102</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <f aca="false">H34+F34+B34+D34+K34+P34</f>
+        <v>2909.9</v>
+      </c>
+      <c r="Y34" s="1" t="n">
+        <f aca="false">-X34+($V$45 + $V$46)*1000*V34/100</f>
+        <v>1699.74938297043</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <f aca="false">Y34/U34/10</f>
+        <v>0.307536734884228</v>
+      </c>
+      <c r="AA34" s="1" t="n">
+        <f aca="false">ROUND(Y34/U34 *100/1000, 2)</f>
+        <v>0.31</v>
+      </c>
+      <c r="AC34" s="1" t="n">
+        <f aca="false">-V34*($V$47)*10</f>
+        <v>-911.066064067446</v>
+      </c>
+      <c r="AD34" s="1" t="n">
+        <f aca="false">AC34/U34/10</f>
+        <v>-0.16483976132851</v>
+      </c>
+      <c r="AG34" s="1" t="n">
+        <v>601.2</v>
+      </c>
+      <c r="AL34" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO34" s="1" t="n">
+        <f aca="false">AM34+AN34/100</f>
+        <v>1.16</v>
+      </c>
+      <c r="AP34" s="1" t="n">
+        <f aca="false">AO34*1000</f>
+        <v>1160</v>
+      </c>
+      <c r="AS34" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AT34" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV34" s="17" t="n">
+        <f aca="false">AT34+AU34/10</f>
+        <v>7.1</v>
+      </c>
+      <c r="AW34" s="17" t="n">
+        <f aca="false">1000*AV34</f>
+        <v>7100</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="31" t="n">
-        <f aca="false">SUM(B32:O32)</f>
-        <v>141690.6</v>
-      </c>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
+    <row r="35" s="31" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="28" t="n">
+        <v>5847</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="29" t="n">
+        <v>9557</v>
+      </c>
+      <c r="E35" s="28"/>
+      <c r="F35" s="30" t="n">
+        <v>8334.6</v>
+      </c>
+      <c r="G35" s="30"/>
+      <c r="H35" s="28" t="n">
+        <v>26264</v>
+      </c>
+      <c r="I35" s="28"/>
+      <c r="K35" s="1" t="n">
+        <f aca="false">SUM(K8:K34)</f>
+        <v>8092</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="P35" s="1" t="n">
+        <f aca="false">SUM(P8:P34)</f>
+        <v>40677.6</v>
+      </c>
+      <c r="Q35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <f aca="false">H35+F35+B35+D35+L35+P35</f>
+        <v>90680.2</v>
+      </c>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="1" t="n">
+        <f aca="false">SUM(Y8:Y34)</f>
+        <v>38340.8</v>
+      </c>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="31" t="e">
+        <f aca="false">ROUND(Y35/U35 *100/1000, 2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC35" s="1" t="n">
+        <f aca="false">-V35*($V$47)*10</f>
+        <v>-24000</v>
+      </c>
+      <c r="AD35" s="1"/>
+      <c r="AG35" s="31" t="n">
+        <v>18796</v>
+      </c>
+      <c r="AP35" s="31" t="n">
+        <f aca="false">SUM(AP8:AP34)</f>
+        <v>47600</v>
+      </c>
+      <c r="AV35" s="31" t="n">
+        <f aca="false">SUM(AV8:AV34)</f>
+        <v>299.1</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="30"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
+      <c r="B36" s="1" t="n">
+        <f aca="false">SUM(B8:B34)</f>
+        <v>5847</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <f aca="false">SUM(D8:D34)</f>
+        <v>9561</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <f aca="false">SUM(F8:F34)</f>
+        <v>8334.5</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <f aca="false">SUM(H8:H34)</f>
+        <v>26264</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <f aca="false">SUM(L8:L34)</f>
+        <v>47600</v>
+      </c>
+      <c r="P36" s="1" t="n">
+        <f aca="false">SUM(P8:P34)</f>
+        <v>40677.6</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <f aca="false">SUM(Q8:Q34)</f>
+        <v>299100</v>
+      </c>
+      <c r="U36" s="1" t="n">
+        <f aca="false">SUM(U8:U34)</f>
+        <v>14559.594</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <f aca="false">SUM(W8:W34)</f>
+        <v>98776.1</v>
+      </c>
+      <c r="Y36" s="0"/>
+      <c r="Z36" s="0"/>
     </row>
-    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="30"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="S37" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="T37" s="33" t="n">
-        <v>192.8</v>
-      </c>
-      <c r="U37" s="34"/>
-      <c r="V37" s="35"/>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J37" s="32" t="n">
+        <v>93</v>
+      </c>
+      <c r="K37" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="O37" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="P37" s="33" t="n">
+        <v>13.6</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S38" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="T38" s="32" t="n">
-        <f aca="false">T37*0.7</f>
-        <v>134.96</v>
-      </c>
-      <c r="U38" s="34"/>
-      <c r="V38" s="35"/>
+      <c r="B38" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="35" t="n">
+        <f aca="false">SUM(B35:P35)</f>
+        <v>98772.2</v>
+      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S39" s="32"/>
-      <c r="T39" s="32"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="35"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S40" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="T40" s="37" t="n">
-        <v>20</v>
-      </c>
-      <c r="U40" s="34"/>
-      <c r="V40" s="35"/>
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="34"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="U40" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="V40" s="37" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="W40" s="38"/>
+      <c r="X40" s="38"/>
+      <c r="Y40" s="17"/>
+      <c r="Z40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q41" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="S41" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="T41" s="36" t="n">
-        <f aca="false">U33/1000 -T40</f>
-        <v>121.5881</v>
-      </c>
-      <c r="U41" s="34"/>
-      <c r="V41" s="35"/>
+      <c r="U41" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="V41" s="36" t="n">
+        <f aca="false">V40*0.7</f>
+        <v>134.96</v>
+      </c>
+      <c r="W41" s="38"/>
+      <c r="X41" s="38"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S42" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="T42" s="36" t="n">
-        <f aca="false">T41-T43-T44</f>
-        <v>60.5881</v>
-      </c>
-      <c r="U42" s="34"/>
-      <c r="V42" s="35"/>
+      <c r="U42" s="36"/>
+      <c r="V42" s="36"/>
+      <c r="W42" s="38"/>
+      <c r="X42" s="38"/>
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="17"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S43" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="T43" s="37" t="n">
-        <v>35</v>
-      </c>
-      <c r="U43" s="34"/>
-      <c r="V43" s="35"/>
+      <c r="U43" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="V43" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="W43" s="38"/>
+      <c r="X43" s="38"/>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S44" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="T44" s="37" t="n">
-        <v>26</v>
-      </c>
-      <c r="U44" s="34"/>
-      <c r="V44" s="35"/>
+      <c r="S44" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="U44" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="V44" s="39" t="n">
+        <f aca="false">W36/1000 -V43</f>
+        <v>68.7761</v>
+      </c>
+      <c r="W44" s="38"/>
+      <c r="X44" s="38"/>
+      <c r="Y44" s="17"/>
+      <c r="Z44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="35"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="S45" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="T45" s="36" t="n">
-        <f aca="false">T37+T43</f>
-        <v>227.8</v>
-      </c>
-      <c r="U45" s="34"/>
-      <c r="V45" s="35"/>
+      <c r="U45" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="V45" s="39" t="n">
+        <f aca="false">V44-V46-V47</f>
+        <v>30.7761</v>
+      </c>
+      <c r="W45" s="38"/>
+      <c r="X45" s="38"/>
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="35"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="S46" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="T46" s="36" t="n">
-        <f aca="false">T38-T42</f>
-        <v>74.3719</v>
-      </c>
-      <c r="U46" s="34"/>
-      <c r="V46" s="35"/>
+      <c r="U46" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="V46" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="W46" s="38"/>
+      <c r="X46" s="38"/>
+      <c r="Y46" s="17"/>
+      <c r="Z46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="35"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="S47" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="T47" s="36" t="n">
-        <f aca="false">T46/T45</f>
-        <v>0.326478928884987</v>
-      </c>
-      <c r="U47" s="34"/>
-      <c r="V47" s="35"/>
+      <c r="U47" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="V47" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="W47" s="38"/>
+      <c r="X47" s="38"/>
+      <c r="Y47" s="17"/>
+      <c r="Z47" s="17"/>
     </row>
-    <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="39"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="V50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y50" s="1" t="s">
-        <v>100</v>
-      </c>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="U48" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="V48" s="39" t="n">
+        <f aca="false">V40+V46</f>
+        <v>206.8</v>
+      </c>
+      <c r="W48" s="38"/>
+      <c r="X48" s="38"/>
+      <c r="Y48" s="17"/>
+      <c r="Z48" s="17"/>
     </row>
-    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="39"/>
-      <c r="K52" s="1" t="s">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="U49" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="V49" s="39" t="n">
+        <f aca="false">V41-V45</f>
+        <v>104.1839</v>
+      </c>
+      <c r="W49" s="38"/>
+      <c r="X49" s="38"/>
+      <c r="Y49" s="17"/>
+      <c r="Z49" s="17"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="U50" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="V50" s="39" t="n">
+        <f aca="false">V49/V48</f>
+        <v>0.503790618955513</v>
+      </c>
+      <c r="W50" s="38"/>
+      <c r="X50" s="38"/>
+      <c r="Y50" s="17"/>
+      <c r="Z50" s="17"/>
+    </row>
+    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="41"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="Y53" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC53" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD53" s="1"/>
+    </row>
+    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="41"/>
+      <c r="K55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P52" s="1"/>
+      <c r="P55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:E37"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:E40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="124">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -52,16 +52,7 @@
     <t xml:space="preserve">GDP 2025 (Eurostat)</t>
   </si>
   <si>
-    <t xml:space="preserve">M3 (2028)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yield (EUR m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimated revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central</t>
+    <t xml:space="preserve">revenues</t>
   </si>
   <si>
     <t xml:space="preserve">Rev. share</t>
@@ -94,18 +85,15 @@
     <t xml:space="preserve">+ externalité</t>
   </si>
   <si>
-    <t xml:space="preserve">proj.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR million, 0.5% rate</t>
+    <t xml:space="preserve">Millions EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/GNI</t>
   </si>
   <si>
     <t xml:space="preserve">(%)</t>
   </si>
   <si>
-    <t xml:space="preserve">base</t>
-  </si>
-  <si>
     <t xml:space="preserve">(EUR bn)</t>
   </si>
   <si>
@@ -362,6 +350,12 @@
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux effectif (inclus elasticité)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux effectif</t>
   </si>
   <si>
     <t xml:space="preserve">Budget 2026 </t>
@@ -491,7 +485,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,7 +495,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8A65"/>
-        <bgColor rgb="FFFFAB91"/>
+        <bgColor rgb="FFDF979A"/>
       </patternFill>
     </fill>
     <fill>
@@ -512,8 +506,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCF4069"/>
+        <bgColor rgb="FF993366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF979A"/>
+        <bgColor rgb="FFFFAB91"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5983B0"/>
         <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBABC"/>
+        <bgColor rgb="FF729FCF"/>
       </patternFill>
     </fill>
     <fill>
@@ -549,7 +561,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFAB91"/>
-        <bgColor rgb="FFFF8A65"/>
+        <bgColor rgb="FFDF979A"/>
       </patternFill>
     </fill>
     <fill>
@@ -611,7 +623,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -628,11 +640,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -640,27 +664,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -684,19 +716,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -712,7 +744,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -720,47 +752,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -768,11 +804,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -808,7 +844,7 @@
       <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF729FCF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFCF4069"/>
       <rgbColor rgb="FFF2F7FF"/>
       <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF650953"/>
@@ -829,10 +865,10 @@
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFFAB91"/>
-      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFDF979A"/>
       <rgbColor rgb="FFFFCDD2"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF5EBABC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9800"/>
@@ -2263,11 +2299,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="98294469"/>
-        <c:axId val="91160820"/>
+        <c:axId val="84957813"/>
+        <c:axId val="13308638"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="98294469"/>
+        <c:axId val="84957813"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2299,7 +2335,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91160820"/>
+        <c:crossAx val="13308638"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2307,7 +2343,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91160820"/>
+        <c:axId val="13308638"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2337,7 +2373,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98294469"/>
+        <c:crossAx val="84957813"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2398,9 +2434,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1171440</xdr:colOff>
+      <xdr:colOff>1171080</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>26280</xdr:rowOff>
+      <xdr:rowOff>25920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2409,7 +2445,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="2474280" y="9185040"/>
-        <a:ext cx="10058760" cy="5657040"/>
+        <a:ext cx="10058400" cy="5656680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2540,9 +2576,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="15.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.93"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="10.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="14.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="14.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="14.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="22.7"/>
@@ -2551,7 +2590,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.16"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="10" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2559,451 +2598,494 @@
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="6"/>
+      <c r="I1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" s="7"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="AF1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG1" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" s="13" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG2" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="13" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="12"/>
+      <c r="V3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG3" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" s="17" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="16"/>
+      <c r="K4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="AF1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG1" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" s="8" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
-      <c r="B2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="1"/>
-      <c r="V2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG2" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" s="8" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="U3" s="1"/>
-      <c r="V3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG3" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="P4" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="K4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="P4" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="U4" s="1"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="AG4" s="11"/>
-      <c r="XDR4" s="11"/>
-      <c r="XDS4" s="11"/>
-      <c r="XDT4" s="11"/>
-      <c r="XDU4" s="11"/>
-      <c r="XDV4" s="11"/>
-      <c r="XDW4" s="11"/>
-      <c r="XDX4" s="11"/>
-      <c r="XDY4" s="11"/>
-      <c r="XDZ4" s="11"/>
-      <c r="XEA4" s="11"/>
-      <c r="XEB4" s="11"/>
-      <c r="XEC4" s="11"/>
-      <c r="XED4" s="11"/>
-      <c r="XEE4" s="11"/>
-      <c r="XEF4" s="11"/>
-      <c r="XEG4" s="11"/>
-      <c r="XEH4" s="11"/>
-      <c r="XEI4" s="11"/>
-      <c r="XEJ4" s="11"/>
-      <c r="XEK4" s="11"/>
-      <c r="XEL4" s="11"/>
-      <c r="XEM4" s="11"/>
-      <c r="XEN4" s="11"/>
-      <c r="XEO4" s="11"/>
-      <c r="XEP4" s="11"/>
-      <c r="XEQ4" s="11"/>
-      <c r="XER4" s="11"/>
-      <c r="XES4" s="11"/>
-      <c r="XET4" s="11"/>
-      <c r="XEU4" s="11"/>
-      <c r="XEV4" s="11"/>
-      <c r="XEW4" s="11"/>
-      <c r="XEX4" s="11"/>
-      <c r="XEY4" s="11"/>
-      <c r="XEZ4" s="11"/>
-      <c r="XFA4" s="11"/>
+      <c r="AG4" s="16"/>
+      <c r="XDR4" s="16"/>
+      <c r="XDS4" s="16"/>
+      <c r="XDT4" s="16"/>
+      <c r="XDU4" s="16"/>
+      <c r="XDV4" s="16"/>
+      <c r="XDW4" s="16"/>
+      <c r="XDX4" s="16"/>
+      <c r="XDY4" s="16"/>
+      <c r="XDZ4" s="16"/>
+      <c r="XEA4" s="16"/>
+      <c r="XEB4" s="16"/>
+      <c r="XEC4" s="16"/>
+      <c r="XED4" s="16"/>
+      <c r="XEE4" s="16"/>
+      <c r="XEF4" s="16"/>
+      <c r="XEG4" s="16"/>
+      <c r="XEH4" s="16"/>
+      <c r="XEI4" s="16"/>
+      <c r="XEJ4" s="16"/>
+      <c r="XEK4" s="16"/>
+      <c r="XEL4" s="16"/>
+      <c r="XEM4" s="16"/>
+      <c r="XEN4" s="16"/>
+      <c r="XEO4" s="16"/>
+      <c r="XEP4" s="16"/>
+      <c r="XEQ4" s="16"/>
+      <c r="XER4" s="16"/>
+      <c r="XES4" s="16"/>
+      <c r="XET4" s="16"/>
+      <c r="XEU4" s="16"/>
+      <c r="XEV4" s="16"/>
+      <c r="XEW4" s="16"/>
+      <c r="XEX4" s="16"/>
+      <c r="XEY4" s="16"/>
+      <c r="XEZ4" s="16"/>
+      <c r="XFA4" s="16"/>
     </row>
-    <row r="5" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11" t="s">
+    <row r="5" s="17" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="M5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" s="11"/>
-      <c r="U5" s="1"/>
+      <c r="R5" s="16"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
-      <c r="AG5" s="11"/>
-      <c r="XDR5" s="11"/>
-      <c r="XDS5" s="11"/>
-      <c r="XDT5" s="11"/>
-      <c r="XDU5" s="11"/>
-      <c r="XDV5" s="11"/>
-      <c r="XDW5" s="11"/>
-      <c r="XDX5" s="11"/>
-      <c r="XDY5" s="11"/>
-      <c r="XDZ5" s="11"/>
-      <c r="XEA5" s="11"/>
-      <c r="XEB5" s="11"/>
-      <c r="XEC5" s="11"/>
-      <c r="XED5" s="11"/>
-      <c r="XEE5" s="11"/>
-      <c r="XEF5" s="11"/>
-      <c r="XEG5" s="11"/>
-      <c r="XEH5" s="11"/>
-      <c r="XEI5" s="11"/>
-      <c r="XEJ5" s="11"/>
-      <c r="XEK5" s="11"/>
-      <c r="XEL5" s="11"/>
-      <c r="XEM5" s="11"/>
-      <c r="XEN5" s="11"/>
-      <c r="XEO5" s="11"/>
-      <c r="XEP5" s="11"/>
-      <c r="XEQ5" s="11"/>
-      <c r="XER5" s="11"/>
-      <c r="XES5" s="11"/>
-      <c r="XET5" s="11"/>
-      <c r="XEU5" s="11"/>
-      <c r="XEV5" s="11"/>
-      <c r="XEW5" s="11"/>
-      <c r="XEX5" s="11"/>
-      <c r="XEY5" s="11"/>
-      <c r="XEZ5" s="11"/>
-      <c r="XFA5" s="11"/>
+      <c r="AG5" s="16"/>
+      <c r="XDR5" s="16"/>
+      <c r="XDS5" s="16"/>
+      <c r="XDT5" s="16"/>
+      <c r="XDU5" s="16"/>
+      <c r="XDV5" s="16"/>
+      <c r="XDW5" s="16"/>
+      <c r="XDX5" s="16"/>
+      <c r="XDY5" s="16"/>
+      <c r="XDZ5" s="16"/>
+      <c r="XEA5" s="16"/>
+      <c r="XEB5" s="16"/>
+      <c r="XEC5" s="16"/>
+      <c r="XED5" s="16"/>
+      <c r="XEE5" s="16"/>
+      <c r="XEF5" s="16"/>
+      <c r="XEG5" s="16"/>
+      <c r="XEH5" s="16"/>
+      <c r="XEI5" s="16"/>
+      <c r="XEJ5" s="16"/>
+      <c r="XEK5" s="16"/>
+      <c r="XEL5" s="16"/>
+      <c r="XEM5" s="16"/>
+      <c r="XEN5" s="16"/>
+      <c r="XEO5" s="16"/>
+      <c r="XEP5" s="16"/>
+      <c r="XEQ5" s="16"/>
+      <c r="XER5" s="16"/>
+      <c r="XES5" s="16"/>
+      <c r="XET5" s="16"/>
+      <c r="XEU5" s="16"/>
+      <c r="XEV5" s="16"/>
+      <c r="XEW5" s="16"/>
+      <c r="XEX5" s="16"/>
+      <c r="XEY5" s="16"/>
+      <c r="XEZ5" s="16"/>
+      <c r="XFA5" s="16"/>
     </row>
-    <row r="6" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="U6" s="1"/>
+    <row r="6" s="17" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC6" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG6" s="11"/>
-      <c r="XDR6" s="11"/>
-      <c r="XDS6" s="11"/>
-      <c r="XDT6" s="11"/>
-      <c r="XDU6" s="11"/>
-      <c r="XDV6" s="11"/>
-      <c r="XDW6" s="11"/>
-      <c r="XDX6" s="11"/>
-      <c r="XDY6" s="11"/>
-      <c r="XDZ6" s="11"/>
-      <c r="XEA6" s="11"/>
-      <c r="XEB6" s="11"/>
-      <c r="XEC6" s="11"/>
-      <c r="XED6" s="11"/>
-      <c r="XEE6" s="11"/>
-      <c r="XEF6" s="11"/>
-      <c r="XEG6" s="11"/>
-      <c r="XEH6" s="11"/>
-      <c r="XEI6" s="11"/>
-      <c r="XEJ6" s="11"/>
-      <c r="XEK6" s="11"/>
-      <c r="XEL6" s="11"/>
-      <c r="XEM6" s="11"/>
-      <c r="XEN6" s="11"/>
-      <c r="XEO6" s="11"/>
-      <c r="XEP6" s="11"/>
-      <c r="XEQ6" s="11"/>
-      <c r="XER6" s="11"/>
-      <c r="XES6" s="11"/>
-      <c r="XET6" s="11"/>
-      <c r="XEU6" s="11"/>
-      <c r="XEV6" s="11"/>
-      <c r="XEW6" s="11"/>
-      <c r="XEX6" s="11"/>
-      <c r="XEY6" s="11"/>
-      <c r="XEZ6" s="11"/>
-      <c r="XFA6" s="11"/>
+      <c r="Y6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC6" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG6" s="16"/>
+      <c r="XDR6" s="16"/>
+      <c r="XDS6" s="16"/>
+      <c r="XDT6" s="16"/>
+      <c r="XDU6" s="16"/>
+      <c r="XDV6" s="16"/>
+      <c r="XDW6" s="16"/>
+      <c r="XDX6" s="16"/>
+      <c r="XDY6" s="16"/>
+      <c r="XDZ6" s="16"/>
+      <c r="XEA6" s="16"/>
+      <c r="XEB6" s="16"/>
+      <c r="XEC6" s="16"/>
+      <c r="XED6" s="16"/>
+      <c r="XEE6" s="16"/>
+      <c r="XEF6" s="16"/>
+      <c r="XEG6" s="16"/>
+      <c r="XEH6" s="16"/>
+      <c r="XEI6" s="16"/>
+      <c r="XEJ6" s="16"/>
+      <c r="XEK6" s="16"/>
+      <c r="XEL6" s="16"/>
+      <c r="XEM6" s="16"/>
+      <c r="XEN6" s="16"/>
+      <c r="XEO6" s="16"/>
+      <c r="XEP6" s="16"/>
+      <c r="XEQ6" s="16"/>
+      <c r="XER6" s="16"/>
+      <c r="XES6" s="16"/>
+      <c r="XET6" s="16"/>
+      <c r="XEU6" s="16"/>
+      <c r="XEV6" s="16"/>
+      <c r="XEW6" s="16"/>
+      <c r="XEX6" s="16"/>
+      <c r="XEY6" s="16"/>
+      <c r="XEZ6" s="16"/>
+      <c r="XFA6" s="16"/>
     </row>
-    <row r="7" s="12" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="U7" s="1"/>
+    <row r="7" s="17" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-      <c r="Y7" s="0"/>
-      <c r="Z7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC7" s="0"/>
-      <c r="AD7" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG7" s="11"/>
-      <c r="XDR7" s="11"/>
-      <c r="XDS7" s="11"/>
-      <c r="XDT7" s="11"/>
-      <c r="XDU7" s="11"/>
-      <c r="XDV7" s="11"/>
-      <c r="XDW7" s="11"/>
-      <c r="XDX7" s="11"/>
-      <c r="XDY7" s="11"/>
-      <c r="XDZ7" s="11"/>
-      <c r="XEA7" s="11"/>
-      <c r="XEB7" s="11"/>
-      <c r="XEC7" s="11"/>
-      <c r="XED7" s="11"/>
-      <c r="XEE7" s="11"/>
-      <c r="XEF7" s="11"/>
-      <c r="XEG7" s="11"/>
-      <c r="XEH7" s="11"/>
-      <c r="XEI7" s="11"/>
-      <c r="XEJ7" s="11"/>
-      <c r="XEK7" s="11"/>
-      <c r="XEL7" s="11"/>
-      <c r="XEM7" s="11"/>
-      <c r="XEN7" s="11"/>
-      <c r="XEO7" s="11"/>
-      <c r="XEP7" s="11"/>
-      <c r="XEQ7" s="11"/>
-      <c r="XER7" s="11"/>
-      <c r="XES7" s="11"/>
-      <c r="XET7" s="11"/>
-      <c r="XEU7" s="11"/>
-      <c r="XEV7" s="11"/>
-      <c r="XEW7" s="11"/>
-      <c r="XEX7" s="11"/>
-      <c r="XEY7" s="11"/>
-      <c r="XEZ7" s="11"/>
-      <c r="XFA7" s="11"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG7" s="16"/>
+      <c r="XDR7" s="16"/>
+      <c r="XDS7" s="16"/>
+      <c r="XDT7" s="16"/>
+      <c r="XDU7" s="16"/>
+      <c r="XDV7" s="16"/>
+      <c r="XDW7" s="16"/>
+      <c r="XDX7" s="16"/>
+      <c r="XDY7" s="16"/>
+      <c r="XDZ7" s="16"/>
+      <c r="XEA7" s="16"/>
+      <c r="XEB7" s="16"/>
+      <c r="XEC7" s="16"/>
+      <c r="XED7" s="16"/>
+      <c r="XEE7" s="16"/>
+      <c r="XEF7" s="16"/>
+      <c r="XEG7" s="16"/>
+      <c r="XEH7" s="16"/>
+      <c r="XEI7" s="16"/>
+      <c r="XEJ7" s="16"/>
+      <c r="XEK7" s="16"/>
+      <c r="XEL7" s="16"/>
+      <c r="XEM7" s="16"/>
+      <c r="XEN7" s="16"/>
+      <c r="XEO7" s="16"/>
+      <c r="XEP7" s="16"/>
+      <c r="XEQ7" s="16"/>
+      <c r="XER7" s="16"/>
+      <c r="XES7" s="16"/>
+      <c r="XET7" s="16"/>
+      <c r="XEU7" s="16"/>
+      <c r="XEV7" s="16"/>
+      <c r="XEW7" s="16"/>
+      <c r="XEX7" s="16"/>
+      <c r="XEY7" s="16"/>
+      <c r="XEZ7" s="16"/>
+      <c r="XFA7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="14" t="n">
+      <c r="A8" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="19" t="n">
         <v>141</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="19" t="n">
         <f aca="false">1000*B8/$U8</f>
         <v>345.61025947732</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="20" t="n">
         <v>330</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="19" t="n">
         <f aca="false">1000*D8/$U8</f>
         <v>808.87507537245</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="21" t="n">
         <v>26.4</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="19" t="n">
         <f aca="false">1000*F8/$U8</f>
         <v>64.710006029796</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="19" t="n">
         <v>920</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="19" t="n">
         <f aca="false">1000*H8/$U8</f>
         <v>2255.04566467471</v>
       </c>
@@ -3017,7 +3099,7 @@
       <c r="L8" s="1" t="n">
         <v>1900</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="19" t="n">
         <f aca="false">1000*L8/$U8</f>
         <v>4657.15952487168</v>
       </c>
@@ -3034,7 +3116,7 @@
       <c r="Q8" s="1" t="n">
         <v>9900</v>
       </c>
-      <c r="R8" s="14" t="n">
+      <c r="R8" s="19" t="n">
         <f aca="false">1000*P8/$U8</f>
         <v>3300.2103075196</v>
       </c>
@@ -3079,7 +3161,7 @@
         <v>514.3</v>
       </c>
       <c r="AL8" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM8" s="1" t="n">
         <v>1</v>
@@ -3095,8 +3177,8 @@
         <f aca="false">AO8*1000</f>
         <v>1900</v>
       </c>
-      <c r="AS8" s="17" t="s">
-        <v>45</v>
+      <c r="AS8" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="AT8" s="1" t="n">
         <v>9</v>
@@ -3104,44 +3186,44 @@
       <c r="AU8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV8" s="17" t="n">
+      <c r="AV8" s="22" t="n">
         <f aca="false">AT8+AU8/10</f>
         <v>9.9</v>
       </c>
-      <c r="AW8" s="17" t="n">
+      <c r="AW8" s="22" t="n">
         <f aca="false">1000*AV8</f>
         <v>9900</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="19" t="n">
+      <c r="A9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="24" t="n">
         <v>200</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="19" t="n">
         <f aca="false">1000*B9/$U9</f>
         <v>394.508442480669</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="25" t="n">
         <v>184</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">1000*D9/$U9</f>
         <v>362.947767082216</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="26" t="n">
         <v>61.1</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="19" t="n">
         <f aca="false">1000*F9/$U9</f>
         <v>120.522329177844</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="24" t="n">
         <v>722</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="19" t="n">
         <f aca="false">1000*H9/$U9</f>
         <v>1424.17547735522</v>
       </c>
@@ -3155,7 +3237,7 @@
       <c r="L9" s="1" t="n">
         <v>1100</v>
       </c>
-      <c r="M9" s="14" t="n">
+      <c r="M9" s="19" t="n">
         <f aca="false">1000*L9/$U9</f>
         <v>2169.79643364368</v>
       </c>
@@ -3172,7 +3254,7 @@
       <c r="Q9" s="1" t="n">
         <v>9800</v>
       </c>
-      <c r="R9" s="14" t="n">
+      <c r="R9" s="19" t="n">
         <f aca="false">1000*P9/$U9</f>
         <v>2629.00426069118</v>
       </c>
@@ -3193,7 +3275,7 @@
         <f aca="false">H9+F9+B9+D9+K9+P9</f>
         <v>2686.9</v>
       </c>
-      <c r="X9" s="22" t="n">
+      <c r="X9" s="27" t="n">
         <f aca="false">F9</f>
         <v>61.1</v>
       </c>
@@ -3221,7 +3303,7 @@
         <v>642</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="AM9" s="1" t="n">
         <v>1</v>
@@ -3237,8 +3319,8 @@
         <f aca="false">AO9*1000</f>
         <v>1100</v>
       </c>
-      <c r="AS9" s="17" t="s">
-        <v>48</v>
+      <c r="AS9" s="22" t="s">
+        <v>44</v>
       </c>
       <c r="AT9" s="1" t="n">
         <v>9</v>
@@ -3246,44 +3328,44 @@
       <c r="AU9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AV9" s="17" t="n">
+      <c r="AV9" s="22" t="n">
         <f aca="false">AT9+AU9/10</f>
         <v>9.8</v>
       </c>
-      <c r="AW9" s="17" t="n">
+      <c r="AW9" s="22" t="n">
         <f aca="false">1000*AV9</f>
         <v>9800</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="14" t="n">
+      <c r="A10" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="19" t="n">
         <f aca="false">1000*B10/$U10</f>
         <v>726.008291778911</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="19" t="n">
         <f aca="false">1000*D10/$U10</f>
         <v>343.898664526853</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="19" t="n">
         <f aca="false">1000*F10/$U10</f>
         <v>3.82109627252059</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="19" t="n">
         <f aca="false">1000*H10/$U10</f>
         <v>764.219254504117</v>
       </c>
@@ -3297,7 +3379,7 @@
       <c r="L10" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="M10" s="19" t="n">
         <f aca="false">1000*L10/$U10</f>
         <v>5158.47996790279</v>
       </c>
@@ -3314,7 +3396,7 @@
       <c r="Q10" s="1" t="n">
         <v>1600</v>
       </c>
-      <c r="R10" s="14" t="n">
+      <c r="R10" s="19" t="n">
         <f aca="false">1000*P10/$U10</f>
         <v>4157.3527445024</v>
       </c>
@@ -3359,7 +3441,7 @@
         <v>116</v>
       </c>
       <c r="AL10" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM10" s="1" t="n">
         <v>0</v>
@@ -3375,8 +3457,8 @@
         <f aca="false">AO10*1000</f>
         <v>270</v>
       </c>
-      <c r="AS10" s="17" t="s">
-        <v>49</v>
+      <c r="AS10" s="22" t="s">
+        <v>45</v>
       </c>
       <c r="AT10" s="1" t="n">
         <v>1</v>
@@ -3384,44 +3466,44 @@
       <c r="AU10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AV10" s="17" t="n">
+      <c r="AV10" s="22" t="n">
         <f aca="false">AT10+AU10/10</f>
         <v>1.6</v>
       </c>
-      <c r="AW10" s="17" t="n">
+      <c r="AW10" s="22" t="n">
         <f aca="false">1000*AV10</f>
         <v>1600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="19" t="n">
+      <c r="A11" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="24" t="n">
         <v>46</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="19" t="n">
         <f aca="false">1000*B11/$U11</f>
         <v>786.755148115208</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">1000*D11/$U11</f>
         <v>444.687692412944</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="19" t="n">
         <f aca="false">1000*F11/$U11</f>
         <v>5.13101183553397</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="24" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="19" t="n">
         <f aca="false">1000*H11/$U11</f>
         <v>615.721420264076</v>
       </c>
@@ -3435,7 +3517,7 @@
       <c r="L11" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M11" s="19" t="n">
         <f aca="false">1000*L11/$U11</f>
         <v>6499.28165834303</v>
       </c>
@@ -3452,7 +3534,7 @@
       <c r="Q11" s="1" t="n">
         <v>2300</v>
       </c>
-      <c r="R11" s="14" t="n">
+      <c r="R11" s="19" t="n">
         <f aca="false">1000*P11/$U11</f>
         <v>5349.93500718342</v>
       </c>
@@ -3497,7 +3579,7 @@
         <v>93</v>
       </c>
       <c r="AL11" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AM11" s="1" t="n">
         <v>0</v>
@@ -3513,8 +3595,8 @@
         <f aca="false">AO11*1000</f>
         <v>380</v>
       </c>
-      <c r="AS11" s="17" t="s">
-        <v>51</v>
+      <c r="AS11" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="AT11" s="1" t="n">
         <v>2</v>
@@ -3522,42 +3604,42 @@
       <c r="AU11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AV11" s="17" t="n">
+      <c r="AV11" s="22" t="n">
         <f aca="false">AT11+AU11/10</f>
         <v>2.3</v>
       </c>
-      <c r="AW11" s="17" t="n">
+      <c r="AW11" s="22" t="n">
         <f aca="false">1000*AV11</f>
         <v>2300</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="14" t="n">
+      <c r="A12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="19" t="n">
         <f aca="false">1000*B12/$U12</f>
         <v>727.603456116417</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="14" t="n">
+      <c r="D12" s="28"/>
+      <c r="E12" s="19" t="n">
         <f aca="false">1000*D12/$U12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="19" t="n">
         <f aca="false">1000*F12/$U12</f>
         <v>36.3801728058208</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="19" t="n">
         <v>46</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="19" t="n">
         <f aca="false">1000*H12/$U12</f>
         <v>2091.8599363347</v>
       </c>
@@ -3571,7 +3653,7 @@
       <c r="L12" s="1" t="n">
         <v>290</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="19" t="n">
         <f aca="false">1000*L12/$U12</f>
         <v>13187.8126421101</v>
       </c>
@@ -3588,7 +3670,7 @@
       <c r="Q12" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="R12" s="14" t="n">
+      <c r="R12" s="19" t="n">
         <f aca="false">1000*P12/$U12</f>
         <v>9276.94406548431</v>
       </c>
@@ -3633,7 +3715,7 @@
         <v>36.5</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AM12" s="1" t="n">
         <v>0</v>
@@ -3649,8 +3731,8 @@
         <f aca="false">AO12*1000</f>
         <v>290</v>
       </c>
-      <c r="AS12" s="17" t="s">
-        <v>53</v>
+      <c r="AS12" s="22" t="s">
+        <v>49</v>
       </c>
       <c r="AT12" s="1" t="n">
         <v>1</v>
@@ -3658,44 +3740,44 @@
       <c r="AU12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV12" s="17" t="n">
+      <c r="AV12" s="22" t="n">
         <f aca="false">AT12+AU12/10</f>
         <v>1.5</v>
       </c>
-      <c r="AW12" s="17" t="n">
+      <c r="AW12" s="22" t="n">
         <f aca="false">1000*AV12</f>
         <v>1500</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="19" t="n">
+      <c r="A13" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <v>177</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="19" t="n">
         <f aca="false">1000*B13/$U13</f>
         <v>777.772407095745</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="25" t="n">
         <v>263</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">1000*D13/$U13</f>
         <v>1155.67312466769</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="26" t="n">
         <v>3.8</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="19" t="n">
         <f aca="false">1000*F13/$U13</f>
         <v>16.6979386834115</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="24" t="n">
         <v>348</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="19" t="n">
         <f aca="false">1000*H13/$U13</f>
         <v>1529.17964784926</v>
       </c>
@@ -3709,7 +3791,7 @@
       <c r="L13" s="1" t="n">
         <v>440</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="19" t="n">
         <f aca="false">1000*L13/$U13</f>
         <v>1933.44553176343</v>
       </c>
@@ -3726,7 +3808,7 @@
       <c r="Q13" s="1" t="n">
         <v>4600</v>
       </c>
-      <c r="R13" s="14" t="n">
+      <c r="R13" s="19" t="n">
         <f aca="false">1000*P13/$U13</f>
         <v>2749.00801061637</v>
       </c>
@@ -3771,7 +3853,7 @@
         <v>347.3</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AM13" s="1" t="n">
         <v>0</v>
@@ -3787,8 +3869,8 @@
         <f aca="false">AO13*1000</f>
         <v>440</v>
       </c>
-      <c r="AS13" s="17" t="s">
-        <v>57</v>
+      <c r="AS13" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="AT13" s="1" t="n">
         <v>4</v>
@@ -3796,44 +3878,44 @@
       <c r="AU13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AV13" s="17" t="n">
+      <c r="AV13" s="22" t="n">
         <f aca="false">AT13+AU13/10</f>
         <v>4.6</v>
       </c>
-      <c r="AW13" s="17" t="n">
+      <c r="AW13" s="22" t="n">
         <f aca="false">1000*AV13</f>
         <v>4600</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="14" t="n">
+      <c r="A14" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="19" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="19" t="n">
         <f aca="false">1000*B14/$U14</f>
         <v>304.277684963515</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="20" t="n">
         <v>258</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="19" t="n">
         <f aca="false">1000*D14/$U14</f>
         <v>740.600403024405</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="21" t="n">
         <v>113.8</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="19" t="n">
         <f aca="false">1000*F14/$U14</f>
         <v>326.667929706114</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="19" t="n">
         <v>533</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="19" t="n">
         <f aca="false">1000*H14/$U14</f>
         <v>1530.00005741088</v>
       </c>
@@ -3847,7 +3929,7 @@
       <c r="L14" s="1" t="n">
         <v>1130</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="19" t="n">
         <f aca="false">1000*L14/$U14</f>
         <v>3243.71494347899</v>
       </c>
@@ -3864,7 +3946,7 @@
       <c r="Q14" s="1" t="n">
         <v>4200</v>
       </c>
-      <c r="R14" s="14" t="n">
+      <c r="R14" s="19" t="n">
         <f aca="false">1000*P14/$U14</f>
         <v>1639.65484576566</v>
       </c>
@@ -3909,7 +3991,7 @@
         <v>417.8</v>
       </c>
       <c r="AL14" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AM14" s="1" t="n">
         <v>1</v>
@@ -3925,8 +4007,8 @@
         <f aca="false">AO14*1000</f>
         <v>1130</v>
       </c>
-      <c r="AS14" s="17" t="s">
-        <v>60</v>
+      <c r="AS14" s="22" t="s">
+        <v>56</v>
       </c>
       <c r="AT14" s="1" t="n">
         <v>4</v>
@@ -3934,44 +4016,44 @@
       <c r="AU14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AV14" s="17" t="n">
+      <c r="AV14" s="22" t="n">
         <f aca="false">AT14+AU14/10</f>
         <v>4.2</v>
       </c>
-      <c r="AW14" s="17" t="n">
+      <c r="AW14" s="22" t="n">
         <f aca="false">1000*AV14</f>
         <v>4200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="19" t="n">
+      <c r="A15" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="24" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="19" t="n">
         <f aca="false">1000*B15/$U15</f>
         <v>744.360658921001</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="19" t="n">
         <f aca="false">1000*D15/$U15</f>
         <v>679.633645101783</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="19" t="n">
         <f aca="false">1000*F15/$U15</f>
         <v>3.23635069096087</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="19" t="n">
         <f aca="false">1000*H15/$U15</f>
         <v>938.541700378653</v>
       </c>
@@ -3985,7 +4067,7 @@
       <c r="L15" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="M15" s="19" t="n">
         <f aca="false">1000*L15/$U15</f>
         <v>29127.1562186479</v>
       </c>
@@ -4002,7 +4084,7 @@
       <c r="Q15" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="R15" s="14" t="n">
+      <c r="R15" s="19" t="n">
         <f aca="false">1000*P15/$U15</f>
         <v>2200.71846985339</v>
       </c>
@@ -4047,7 +4129,7 @@
         <v>41.9</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AM15" s="1" t="n">
         <v>0</v>
@@ -4063,8 +4145,8 @@
         <f aca="false">AO15*1000</f>
         <v>900</v>
       </c>
-      <c r="AS15" s="17" t="s">
-        <v>61</v>
+      <c r="AS15" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="AT15" s="1" t="n">
         <v>0</v>
@@ -4072,44 +4154,44 @@
       <c r="AU15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV15" s="17" t="n">
+      <c r="AV15" s="22" t="n">
         <f aca="false">AT15+AU15/10</f>
         <v>0.5</v>
       </c>
-      <c r="AW15" s="17" t="n">
+      <c r="AW15" s="22" t="n">
         <f aca="false">1000*AV15</f>
         <v>500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="14" t="n">
+      <c r="A16" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="19" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="19" t="n">
         <f aca="false">1000*B16/$U16</f>
         <v>379.785988637743</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="20" t="n">
         <v>133</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="19" t="n">
         <f aca="false">1000*D16/$U16</f>
         <v>520.737489575462</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="21" t="n">
         <v>81.3</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="19" t="n">
         <f aca="false">1000*F16/$U16</f>
         <v>318.315472951015</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="19" t="n">
         <v>152</v>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="I16" s="19" t="n">
         <f aca="false">1000*H16/$U16</f>
         <v>595.128559514814</v>
       </c>
@@ -4123,7 +4205,7 @@
       <c r="L16" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="19" t="n">
         <f aca="false">1000*L16/$U16</f>
         <v>2819.03001875438</v>
       </c>
@@ -4140,7 +4222,7 @@
       <c r="Q16" s="1" t="n">
         <v>2900</v>
       </c>
-      <c r="R16" s="14" t="n">
+      <c r="R16" s="19" t="n">
         <f aca="false">1000*P16/$U16</f>
         <v>1544.20199916212</v>
       </c>
@@ -4185,7 +4267,7 @@
         <v>281.7</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM16" s="1" t="n">
         <v>0</v>
@@ -4201,8 +4283,8 @@
         <f aca="false">AO16*1000</f>
         <v>720</v>
       </c>
-      <c r="AS16" s="17" t="s">
-        <v>63</v>
+      <c r="AS16" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="AT16" s="1" t="n">
         <v>2</v>
@@ -4210,44 +4292,44 @@
       <c r="AU16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV16" s="17" t="n">
+      <c r="AV16" s="22" t="n">
         <f aca="false">AT16+AU16/10</f>
         <v>2.9</v>
       </c>
-      <c r="AW16" s="17" t="n">
+      <c r="AW16" s="22" t="n">
         <f aca="false">1000*AV16</f>
         <v>2900</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="19" t="n">
+      <c r="A17" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="24" t="n">
         <v>1078</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="19" t="n">
         <f aca="false">1000*B17/$U17</f>
         <v>418.692157950257</v>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="25" t="n">
         <v>1691</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="19" t="n">
         <f aca="false">1000*D17/$U17</f>
         <v>656.779628101934</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="24" t="n">
         <v>3100</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="19" t="n">
         <f aca="false">1000*F17/$U17</f>
         <v>1204.03125199054</v>
       </c>
-      <c r="H17" s="19" t="n">
+      <c r="H17" s="24" t="n">
         <v>6670</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="I17" s="19" t="n">
         <f aca="false">1000*H17/$U17</f>
         <v>2590.60917766996</v>
       </c>
@@ -4261,7 +4343,7 @@
       <c r="L17" s="1" t="n">
         <v>5380</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="19" t="n">
         <f aca="false">1000*L17/$U17</f>
         <v>2089.57681797067</v>
       </c>
@@ -4278,7 +4360,7 @@
       <c r="Q17" s="1" t="n">
         <v>62000</v>
       </c>
-      <c r="R17" s="14" t="n">
+      <c r="R17" s="19" t="n">
         <f aca="false">1000*P17/$U17</f>
         <v>3274.96500541426</v>
       </c>
@@ -4327,7 +4409,7 @@
         <v>2991.1</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AM17" s="1" t="n">
         <v>5</v>
@@ -4343,8 +4425,8 @@
         <f aca="false">AO17*1000</f>
         <v>5380</v>
       </c>
-      <c r="AS17" s="17" t="s">
-        <v>67</v>
+      <c r="AS17" s="22" t="s">
+        <v>63</v>
       </c>
       <c r="AT17" s="1" t="n">
         <v>62</v>
@@ -4352,44 +4434,44 @@
       <c r="AU17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AV17" s="17" t="n">
+      <c r="AV17" s="22" t="n">
         <f aca="false">AT17+AU17/10</f>
         <v>62</v>
       </c>
-      <c r="AW17" s="17" t="n">
+      <c r="AW17" s="22" t="n">
         <f aca="false">1000*AV17</f>
         <v>62000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="14" t="n">
+      <c r="A18" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="19" t="n">
         <v>973</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="19" t="n">
         <f aca="false">1000*B18/$U18</f>
         <v>260.893020991029</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="29" t="n">
         <v>2700</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="19" t="n">
         <f aca="false">1000*D18/$U18</f>
         <v>723.958023305013</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="21" t="n">
         <v>1595.2</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="19" t="n">
         <f aca="false">1000*F18/$U18</f>
         <v>427.725125472651</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="19" t="n">
         <v>8344</v>
       </c>
-      <c r="I18" s="14" t="n">
+      <c r="I18" s="19" t="n">
         <f aca="false">1000*H18/$U18</f>
         <v>2237.29842461372</v>
       </c>
@@ -4403,7 +4485,7 @@
       <c r="L18" s="1" t="n">
         <v>6400</v>
       </c>
-      <c r="M18" s="14" t="n">
+      <c r="M18" s="19" t="n">
         <f aca="false">1000*L18/$U18</f>
         <v>1716.04864783411</v>
       </c>
@@ -4420,7 +4502,7 @@
       <c r="Q18" s="1" t="n">
         <v>57700</v>
       </c>
-      <c r="R18" s="14" t="n">
+      <c r="R18" s="19" t="n">
         <f aca="false">1000*P18/$U18</f>
         <v>2104.09014832559</v>
       </c>
@@ -4465,7 +4547,7 @@
         <v>4529.7</v>
       </c>
       <c r="AL18" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AM18" s="1" t="n">
         <v>6</v>
@@ -4481,8 +4563,8 @@
         <f aca="false">AO18*1000</f>
         <v>6400</v>
       </c>
-      <c r="AS18" s="17" t="s">
-        <v>70</v>
+      <c r="AS18" s="22" t="s">
+        <v>66</v>
       </c>
       <c r="AT18" s="1" t="n">
         <v>57</v>
@@ -4490,44 +4572,44 @@
       <c r="AU18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AV18" s="17" t="n">
+      <c r="AV18" s="22" t="n">
         <f aca="false">AT18+AU18/10</f>
         <v>57.7</v>
       </c>
-      <c r="AW18" s="17" t="n">
+      <c r="AW18" s="22" t="n">
         <f aca="false">1000*AV18</f>
         <v>57700</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="19" t="n">
+      <c r="A19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="24" t="n">
         <v>91</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="19" t="n">
         <f aca="false">1000*B19/$U19</f>
         <v>503.093193867792</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="25" t="n">
         <v>54</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="19" t="n">
         <f aca="false">1000*D19/$U19</f>
         <v>298.538818339129</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="26" t="n">
         <v>22.7</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="19" t="n">
         <f aca="false">1000*F19/$U19</f>
         <v>125.496873635152</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="24" t="n">
         <v>118</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="19" t="n">
         <f aca="false">1000*H19/$U19</f>
         <v>652.362603037356</v>
       </c>
@@ -4541,7 +4623,7 @@
       <c r="L19" s="1" t="n">
         <v>2540</v>
       </c>
-      <c r="M19" s="14" t="n">
+      <c r="M19" s="19" t="n">
         <f aca="false">1000*L19/$U19</f>
         <v>14042.3814552109</v>
       </c>
@@ -4558,7 +4640,7 @@
       <c r="Q19" s="1" t="n">
         <v>6300</v>
       </c>
-      <c r="R19" s="14" t="n">
+      <c r="R19" s="19" t="n">
         <f aca="false">1000*P19/$U19</f>
         <v>4736.81591764751</v>
       </c>
@@ -4579,7 +4661,7 @@
         <f aca="false">H19+F19+B19+D19+K19+P19</f>
         <v>1574.3</v>
       </c>
-      <c r="X19" s="22" t="n">
+      <c r="X19" s="27" t="n">
         <f aca="false">F19</f>
         <v>22.7</v>
       </c>
@@ -4607,7 +4689,7 @@
         <v>248.4</v>
       </c>
       <c r="AL19" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="AM19" s="1" t="n">
         <v>2</v>
@@ -4623,8 +4705,8 @@
         <f aca="false">AO19*1000</f>
         <v>2540</v>
       </c>
-      <c r="AS19" s="17" t="s">
-        <v>73</v>
+      <c r="AS19" s="22" t="s">
+        <v>69</v>
       </c>
       <c r="AT19" s="1" t="n">
         <v>6</v>
@@ -4632,44 +4714,44 @@
       <c r="AU19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AV19" s="17" t="n">
+      <c r="AV19" s="22" t="n">
         <f aca="false">AT19+AU19/10</f>
         <v>6.3</v>
       </c>
-      <c r="AW19" s="17" t="n">
+      <c r="AW19" s="22" t="n">
         <f aca="false">1000*AV19</f>
         <v>6300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="14" t="n">
+      <c r="A20" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="19" t="n">
         <v>139</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="19" t="n">
         <f aca="false">1000*B20/$U20</f>
         <v>933.361983293492</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="20" t="n">
         <v>113</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="19" t="n">
         <f aca="false">1000*D20/$U20</f>
         <v>758.776288576724</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="21" t="n">
         <v>5.9</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="19" t="n">
         <f aca="false">1000*F20/$U20</f>
         <v>39.617523031882</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="19" t="n">
         <v>208</v>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="I20" s="19" t="n">
         <f aca="false">1000*H20/$U20</f>
         <v>1396.68555773415</v>
       </c>
@@ -4683,7 +4765,7 @@
       <c r="L20" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="M20" s="14" t="n">
+      <c r="M20" s="19" t="n">
         <f aca="false">1000*L20/$U20</f>
         <v>2484.48873250786</v>
       </c>
@@ -4700,7 +4782,7 @@
       <c r="Q20" s="1" t="n">
         <v>2500</v>
       </c>
-      <c r="R20" s="14" t="n">
+      <c r="R20" s="19" t="n">
         <f aca="false">1000*P20/$U20</f>
         <v>2283.04370014235</v>
       </c>
@@ -4745,7 +4827,7 @@
         <v>218.8</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AM20" s="1" t="n">
         <v>0</v>
@@ -4761,8 +4843,8 @@
         <f aca="false">AO20*1000</f>
         <v>370</v>
       </c>
-      <c r="AS20" s="17" t="s">
-        <v>74</v>
+      <c r="AS20" s="22" t="s">
+        <v>70</v>
       </c>
       <c r="AT20" s="1" t="n">
         <v>2</v>
@@ -4770,44 +4852,44 @@
       <c r="AU20" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV20" s="17" t="n">
+      <c r="AV20" s="22" t="n">
         <f aca="false">AT20+AU20/10</f>
         <v>2.5</v>
       </c>
-      <c r="AW20" s="17" t="n">
+      <c r="AW20" s="22" t="n">
         <f aca="false">1000*AV20</f>
         <v>2500</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" s="19" t="n">
+      <c r="A21" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="24" t="n">
         <v>97</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="19" t="n">
         <f aca="false">1000*B21/$U21</f>
         <v>299.863052234907</v>
       </c>
-      <c r="D21" s="20" t="n">
+      <c r="D21" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="19" t="n">
         <f aca="false">1000*D21/$U21</f>
         <v>494.619467603971</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="26" t="n">
         <v>241.4</v>
       </c>
-      <c r="G21" s="14" t="n">
+      <c r="G21" s="19" t="n">
         <f aca="false">1000*F21/$U21</f>
         <v>746.257121747491</v>
       </c>
-      <c r="H21" s="19" t="n">
+      <c r="H21" s="24" t="n">
         <v>331</v>
       </c>
-      <c r="I21" s="14" t="n">
+      <c r="I21" s="19" t="n">
         <f aca="false">1000*H21/$U21</f>
         <v>1023.24402360571</v>
       </c>
@@ -4821,7 +4903,7 @@
       <c r="L21" s="1" t="n">
         <v>940</v>
       </c>
-      <c r="M21" s="14" t="n">
+      <c r="M21" s="19" t="n">
         <f aca="false">1000*L21/$U21</f>
         <v>2905.88937217333</v>
       </c>
@@ -4838,7 +4920,7 @@
       <c r="Q21" s="1" t="n">
         <v>3800</v>
       </c>
-      <c r="R21" s="14" t="n">
+      <c r="R21" s="19" t="n">
         <f aca="false">1000*P21/$U21</f>
         <v>1597.62088036082</v>
       </c>
@@ -4859,7 +4941,7 @@
         <f aca="false">H21+F21+B21+D21+K21+P21</f>
         <v>1506</v>
       </c>
-      <c r="X21" s="22" t="n">
+      <c r="X21" s="27" t="n">
         <f aca="false">F21</f>
         <v>241.4</v>
       </c>
@@ -4887,7 +4969,7 @@
         <v>602.4</v>
       </c>
       <c r="AL21" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AM21" s="1" t="n">
         <v>0</v>
@@ -4903,8 +4985,8 @@
         <f aca="false">AO21*1000</f>
         <v>940</v>
       </c>
-      <c r="AS21" s="17" t="s">
-        <v>78</v>
+      <c r="AS21" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="AT21" s="1" t="n">
         <v>3</v>
@@ -4912,47 +4994,47 @@
       <c r="AU21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AV21" s="17" t="n">
+      <c r="AV21" s="22" t="n">
         <f aca="false">AT21+AU21/10</f>
         <v>3.8</v>
       </c>
-      <c r="AW21" s="17" t="n">
+      <c r="AW21" s="22" t="n">
         <f aca="false">1000*AV21</f>
         <v>3800</v>
       </c>
-      <c r="AX21" s="17" t="s">
-        <v>79</v>
+      <c r="AX21" s="22" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="14" t="n">
+      <c r="A22" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="19" t="n">
         <v>464</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="19" t="n">
         <f aca="false">1000*B22/$U22</f>
         <v>255.791133309077</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="20" t="n">
         <v>891</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="19" t="n">
         <f aca="false">1000*D22/$U22</f>
         <v>491.185128832732</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="21" t="n">
         <v>544.5</v>
       </c>
-      <c r="G22" s="14" t="n">
+      <c r="G22" s="19" t="n">
         <f aca="false">1000*F22/$U22</f>
         <v>300.168689842225</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="19" t="n">
         <v>2618</v>
       </c>
-      <c r="I22" s="14" t="n">
+      <c r="I22" s="19" t="n">
         <f aca="false">1000*H22/$U22</f>
         <v>1443.23531681716</v>
       </c>
@@ -4966,7 +5048,7 @@
       <c r="L22" s="1" t="n">
         <v>7110</v>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="M22" s="19" t="n">
         <f aca="false">1000*L22/$U22</f>
         <v>3919.55809876625</v>
       </c>
@@ -4983,7 +5065,7 @@
       <c r="Q22" s="1" t="n">
         <v>56500</v>
       </c>
-      <c r="R22" s="14" t="n">
+      <c r="R22" s="19" t="n">
         <f aca="false">1000*P22/$U22</f>
         <v>4235.98937143739</v>
       </c>
@@ -5032,7 +5114,7 @@
         <v>2258</v>
       </c>
       <c r="AL22" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AM22" s="1" t="n">
         <v>7</v>
@@ -5048,8 +5130,8 @@
         <f aca="false">AO22*1000</f>
         <v>7110</v>
       </c>
-      <c r="AS22" s="17" t="s">
-        <v>82</v>
+      <c r="AS22" s="22" t="s">
+        <v>78</v>
       </c>
       <c r="AT22" s="1" t="n">
         <v>56</v>
@@ -5057,44 +5139,44 @@
       <c r="AU22" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV22" s="17" t="n">
+      <c r="AV22" s="22" t="n">
         <f aca="false">AT22+AU22/10</f>
         <v>56.5</v>
       </c>
-      <c r="AW22" s="17" t="n">
+      <c r="AW22" s="22" t="n">
         <f aca="false">1000*AV22</f>
         <v>56500</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="19" t="n">
+      <c r="A23" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="19" t="n">
         <f aca="false">1000*B23/$U23</f>
         <v>816.326530612245</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="19" t="n">
         <f aca="false">1000*D23/$U23</f>
         <v>604.686318972033</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="14" t="n">
+      <c r="G23" s="19" t="n">
         <f aca="false">1000*F23/$U23</f>
         <v>0</v>
       </c>
-      <c r="H23" s="19" t="n">
+      <c r="H23" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="I23" s="19" t="n">
         <f aca="false">1000*H23/$U23</f>
         <v>604.686318972033</v>
       </c>
@@ -5108,7 +5190,7 @@
       <c r="L23" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="M23" s="14" t="n">
+      <c r="M23" s="19" t="n">
         <f aca="false">1000*L23/$U23</f>
         <v>5442.1768707483</v>
       </c>
@@ -5125,7 +5207,7 @@
       <c r="Q23" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="R23" s="14" t="n">
+      <c r="R23" s="19" t="n">
         <f aca="false">1000*P23/$U23</f>
         <v>2055.93348450491</v>
       </c>
@@ -5170,7 +5252,7 @@
         <v>43</v>
       </c>
       <c r="AL23" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AM23" s="1" t="n">
         <v>0</v>
@@ -5186,8 +5268,8 @@
         <f aca="false">AO23*1000</f>
         <v>180</v>
       </c>
-      <c r="AS23" s="17" t="s">
-        <v>83</v>
+      <c r="AS23" s="22" t="s">
+        <v>79</v>
       </c>
       <c r="AT23" s="1" t="n">
         <v>0</v>
@@ -5195,44 +5277,44 @@
       <c r="AU23" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV23" s="17" t="n">
+      <c r="AV23" s="22" t="n">
         <f aca="false">AT23+AU23/10</f>
         <v>0.5</v>
       </c>
-      <c r="AW23" s="17" t="n">
+      <c r="AW23" s="22" t="n">
         <f aca="false">1000*AV23</f>
         <v>500</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="14" t="n">
+      <c r="A24" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="19" t="n">
         <f aca="false">1000*B24/$U24</f>
         <v>759.034360189574</v>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="19" t="n">
         <f aca="false">1000*D24/$U24</f>
         <v>444.312796208531</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="G24" s="14" t="n">
+      <c r="G24" s="19" t="n">
         <f aca="false">1000*F24/$U24</f>
         <v>1.85130331753555</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H24" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="I24" s="14" t="n">
+      <c r="I24" s="19" t="n">
         <f aca="false">1000*H24/$U24</f>
         <v>573.904028436019</v>
       </c>
@@ -5246,7 +5328,7 @@
       <c r="L24" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="M24" s="14" t="n">
+      <c r="M24" s="19" t="n">
         <f aca="false">1000*L24/$U24</f>
         <v>2591.82464454976</v>
       </c>
@@ -5263,7 +5345,7 @@
       <c r="Q24" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="R24" s="14" t="n">
+      <c r="R24" s="19" t="n">
         <f aca="false">1000*P24/$U24</f>
         <v>2014.21800947867</v>
       </c>
@@ -5308,7 +5390,7 @@
         <v>84.3</v>
       </c>
       <c r="AL24" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AM24" s="1" t="n">
         <v>0</v>
@@ -5324,8 +5406,8 @@
         <f aca="false">AO24*1000</f>
         <v>140</v>
       </c>
-      <c r="AS24" s="17" t="s">
-        <v>85</v>
+      <c r="AS24" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="AT24" s="1" t="n">
         <v>0</v>
@@ -5333,42 +5415,42 @@
       <c r="AU24" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AV24" s="17" t="n">
+      <c r="AV24" s="22" t="n">
         <f aca="false">AT24+AU24/10</f>
         <v>0.8</v>
       </c>
-      <c r="AW24" s="17" t="n">
+      <c r="AW24" s="22" t="n">
         <f aca="false">1000*AV24</f>
         <v>800</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="19" t="n">
+      <c r="A25" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="19" t="n">
         <f aca="false">1000*B25/$U25</f>
         <v>198.137507430157</v>
       </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="14" t="n">
+      <c r="D25" s="30"/>
+      <c r="E25" s="19" t="n">
         <f aca="false">1000*D25/$U25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="19" t="n">
         <f aca="false">1000*F25/$U25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="19" t="n">
+      <c r="H25" s="24" t="n">
         <v>208</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="I25" s="19" t="n">
         <f aca="false">1000*H25/$U25</f>
         <v>4121.26015454726</v>
       </c>
@@ -5382,7 +5464,7 @@
       <c r="L25" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="M25" s="14" t="n">
+      <c r="M25" s="19" t="n">
         <f aca="false">1000*L25/$U25</f>
         <v>4160.88765603329</v>
       </c>
@@ -5399,7 +5481,7 @@
       <c r="Q25" s="1" t="n">
         <v>1800</v>
       </c>
-      <c r="R25" s="14" t="n">
+      <c r="R25" s="19" t="n">
         <f aca="false">1000*P25/$U25</f>
         <v>4850.40618189023</v>
       </c>
@@ -5444,7 +5526,7 @@
         <v>89.5</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AM25" s="1" t="n">
         <v>0</v>
@@ -5460,8 +5542,8 @@
         <f aca="false">AO25*1000</f>
         <v>210</v>
       </c>
-      <c r="AS25" s="17" t="s">
-        <v>87</v>
+      <c r="AS25" s="22" t="s">
+        <v>83</v>
       </c>
       <c r="AT25" s="1" t="n">
         <v>1</v>
@@ -5469,42 +5551,42 @@
       <c r="AU25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AV25" s="17" t="n">
+      <c r="AV25" s="22" t="n">
         <f aca="false">AT25+AU25/10</f>
         <v>1.8</v>
       </c>
-      <c r="AW25" s="17" t="n">
+      <c r="AW25" s="22" t="n">
         <f aca="false">1000*AV25</f>
         <v>1800</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="14" t="n">
+      <c r="A26" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="19" t="n">
         <f aca="false">1000*B26/$U26</f>
         <v>510.538983298082</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="14" t="n">
+      <c r="D26" s="28"/>
+      <c r="E26" s="19" t="n">
         <f aca="false">1000*D26/$U26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="14" t="n">
+      <c r="G26" s="19" t="n">
         <f aca="false">1000*F26/$U26</f>
         <v>0</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H26" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="I26" s="14" t="n">
+      <c r="I26" s="19" t="n">
         <f aca="false">1000*H26/$U26</f>
         <v>656.407264240391</v>
       </c>
@@ -5518,7 +5600,7 @@
       <c r="L26" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="M26" s="14" t="n">
+      <c r="M26" s="19" t="n">
         <f aca="false">1000*L26/$U26</f>
         <v>19692.2179272117</v>
       </c>
@@ -5535,7 +5617,7 @@
       <c r="Q26" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="R26" s="14" t="n">
+      <c r="R26" s="19" t="n">
         <f aca="false">1000*P26/$U26</f>
         <v>8927.13879366932</v>
       </c>
@@ -5580,7 +5662,7 @@
         <v>24.6</v>
       </c>
       <c r="AL26" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AM26" s="1" t="n">
         <v>0</v>
@@ -5596,8 +5678,8 @@
         <f aca="false">AO26*1000</f>
         <v>270</v>
       </c>
-      <c r="AS26" s="17" t="s">
-        <v>89</v>
+      <c r="AS26" s="22" t="s">
+        <v>85</v>
       </c>
       <c r="AT26" s="1" t="n">
         <v>0</v>
@@ -5605,44 +5687,44 @@
       <c r="AU26" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV26" s="17" t="n">
+      <c r="AV26" s="22" t="n">
         <f aca="false">AT26+AU26/10</f>
         <v>0.9</v>
       </c>
-      <c r="AW26" s="17" t="n">
+      <c r="AW26" s="22" t="n">
         <f aca="false">1000*AV26</f>
         <v>900</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="19" t="n">
+      <c r="A27" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="24" t="n">
         <v>332</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="19" t="n">
         <f aca="false">1000*B27/$U27</f>
         <v>396.580804533444</v>
       </c>
-      <c r="D27" s="20" t="n">
+      <c r="D27" s="25" t="n">
         <v>652</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="19" t="n">
         <f aca="false">1000*D27/$U27</f>
         <v>778.827363119896</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="24" t="n">
         <v>1961</v>
       </c>
-      <c r="G27" s="14" t="n">
+      <c r="G27" s="19" t="n">
         <f aca="false">1000*F27/$U27</f>
         <v>2342.4546918376</v>
       </c>
-      <c r="H27" s="19" t="n">
+      <c r="H27" s="24" t="n">
         <v>913</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="I27" s="19" t="n">
         <f aca="false">1000*H27/$U27</f>
         <v>1090.59721246697</v>
       </c>
@@ -5656,7 +5738,7 @@
       <c r="L27" s="1" t="n">
         <v>1980</v>
       </c>
-      <c r="M27" s="14" t="n">
+      <c r="M27" s="19" t="n">
         <f aca="false">1000*L27/$U27</f>
         <v>2365.15058125367</v>
       </c>
@@ -5673,7 +5755,7 @@
       <c r="Q27" s="1" t="n">
         <v>11000</v>
       </c>
-      <c r="R27" s="14" t="n">
+      <c r="R27" s="19" t="n">
         <f aca="false">1000*P27/$U27</f>
         <v>1787.00266139166</v>
       </c>
@@ -5718,7 +5800,7 @@
         <v>1170.6</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AM27" s="1" t="n">
         <v>1</v>
@@ -5734,8 +5816,8 @@
         <f aca="false">AO27*1000</f>
         <v>1980</v>
       </c>
-      <c r="AS27" s="17" t="s">
-        <v>93</v>
+      <c r="AS27" s="22" t="s">
+        <v>89</v>
       </c>
       <c r="AT27" s="1" t="n">
         <v>11</v>
@@ -5743,44 +5825,44 @@
       <c r="AU27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AV27" s="17" t="n">
+      <c r="AV27" s="22" t="n">
         <f aca="false">AT27+AU27/10</f>
         <v>11</v>
       </c>
-      <c r="AW27" s="17" t="n">
+      <c r="AW27" s="22" t="n">
         <f aca="false">1000*AV27</f>
         <v>11000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28" s="14" t="n">
+      <c r="A28" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="19" t="n">
         <v>494</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="19" t="n">
         <f aca="false">1000*B28/$U28</f>
         <v>901.606282772202</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="20" t="n">
         <v>427</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="19" t="n">
         <f aca="false">1000*D28/$U28</f>
         <v>779.323649278806</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="19" t="n">
         <v>63</v>
       </c>
-      <c r="G28" s="14" t="n">
+      <c r="G28" s="19" t="n">
         <f aca="false">1000*F28/$U28</f>
         <v>114.982177762447</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="19" t="n">
         <v>560</v>
       </c>
-      <c r="I28" s="14" t="n">
+      <c r="I28" s="19" t="n">
         <f aca="false">1000*H28/$U28</f>
         <v>1022.06380233286</v>
       </c>
@@ -5794,7 +5876,7 @@
       <c r="L28" s="1" t="n">
         <v>1190</v>
       </c>
-      <c r="M28" s="14" t="n">
+      <c r="M28" s="19" t="n">
         <f aca="false">1000*L28/$U28</f>
         <v>2171.88557995733</v>
       </c>
@@ -5811,7 +5893,7 @@
       <c r="Q28" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="R28" s="14" t="n">
+      <c r="R28" s="19" t="n">
         <f aca="false">1000*P28/$U28</f>
         <v>1985.72395881813</v>
       </c>
@@ -5856,7 +5938,7 @@
         <v>922.9</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AM28" s="1" t="n">
         <v>1</v>
@@ -5872,8 +5954,8 @@
         <f aca="false">AO28*1000</f>
         <v>1190</v>
       </c>
-      <c r="AS28" s="17" t="s">
-        <v>96</v>
+      <c r="AS28" s="22" t="s">
+        <v>92</v>
       </c>
       <c r="AT28" s="1" t="n">
         <v>8</v>
@@ -5881,44 +5963,44 @@
       <c r="AU28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AV28" s="17" t="n">
+      <c r="AV28" s="22" t="n">
         <f aca="false">AT28+AU28/10</f>
         <v>8</v>
       </c>
-      <c r="AW28" s="17" t="n">
+      <c r="AW28" s="22" t="n">
         <f aca="false">1000*AV28</f>
         <v>8000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="19" t="n">
+      <c r="A29" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="24" t="n">
         <v>136</v>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="19" t="n">
         <f aca="false">1000*B29/$U29</f>
         <v>641.88790560472</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="25" t="n">
         <v>84</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="19" t="n">
         <f aca="false">1000*D29/$U29</f>
         <v>396.46017699115</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="F29" s="26" t="n">
         <v>24.9</v>
       </c>
-      <c r="G29" s="14" t="n">
+      <c r="G29" s="19" t="n">
         <f aca="false">1000*F29/$U29</f>
         <v>117.522123893805</v>
       </c>
-      <c r="H29" s="19" t="n">
+      <c r="H29" s="24" t="n">
         <v>330</v>
       </c>
-      <c r="I29" s="14" t="n">
+      <c r="I29" s="19" t="n">
         <f aca="false">1000*H29/$U29</f>
         <v>1557.52212389381</v>
       </c>
@@ -5932,7 +6014,7 @@
       <c r="L29" s="1" t="n">
         <v>1950</v>
       </c>
-      <c r="M29" s="14" t="n">
+      <c r="M29" s="19" t="n">
         <f aca="false">1000*L29/$U29</f>
         <v>9203.53982300885</v>
       </c>
@@ -5949,7 +6031,7 @@
       <c r="Q29" s="1" t="n">
         <v>6400</v>
       </c>
-      <c r="R29" s="14" t="n">
+      <c r="R29" s="19" t="n">
         <f aca="false">1000*P29/$U29</f>
         <v>4108.08259587021</v>
       </c>
@@ -5994,7 +6076,7 @@
         <v>306.8</v>
       </c>
       <c r="AL29" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AM29" s="1" t="n">
         <v>1</v>
@@ -6010,8 +6092,8 @@
         <f aca="false">AO29*1000</f>
         <v>1950</v>
       </c>
-      <c r="AS29" s="17" t="s">
-        <v>99</v>
+      <c r="AS29" s="22" t="s">
+        <v>95</v>
       </c>
       <c r="AT29" s="1" t="n">
         <v>6</v>
@@ -6019,44 +6101,44 @@
       <c r="AU29" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AV29" s="17" t="n">
+      <c r="AV29" s="22" t="n">
         <f aca="false">AT29+AU29/10</f>
         <v>6.4</v>
       </c>
-      <c r="AW29" s="17" t="n">
+      <c r="AW29" s="22" t="n">
         <f aca="false">1000*AV29</f>
         <v>6400</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="14" t="n">
+      <c r="A30" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="19" t="n">
         <v>133</v>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="19" t="n">
         <f aca="false">1000*B30/$U30</f>
         <v>617.708255926284</v>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="19" t="n">
         <f aca="false">1000*D30/$U30</f>
         <v>139.332689306681</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="21" t="n">
         <v>1.9</v>
       </c>
-      <c r="G30" s="14" t="n">
+      <c r="G30" s="19" t="n">
         <f aca="false">1000*F30/$U30</f>
         <v>8.82440365608977</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="H30" s="19" t="n">
         <v>121</v>
       </c>
-      <c r="I30" s="14" t="n">
+      <c r="I30" s="19" t="n">
         <f aca="false">1000*H30/$U30</f>
         <v>561.975180203611</v>
       </c>
@@ -6070,7 +6152,7 @@
       <c r="L30" s="1" t="n">
         <v>620</v>
       </c>
-      <c r="M30" s="14" t="n">
+      <c r="M30" s="19" t="n">
         <f aca="false">1000*L30/$U30</f>
         <v>2879.5422456714</v>
       </c>
@@ -6087,7 +6169,7 @@
       <c r="Q30" s="1" t="n">
         <v>3200</v>
       </c>
-      <c r="R30" s="14" t="n">
+      <c r="R30" s="19" t="n">
         <f aca="false">1000*P30/$U30</f>
         <v>2021.25287954225</v>
       </c>
@@ -6132,7 +6214,7 @@
         <v>380.1</v>
       </c>
       <c r="AL30" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="AM30" s="1" t="n">
         <v>0</v>
@@ -6148,8 +6230,8 @@
         <f aca="false">AO30*1000</f>
         <v>620</v>
       </c>
-      <c r="AS30" s="17" t="s">
-        <v>100</v>
+      <c r="AS30" s="22" t="s">
+        <v>96</v>
       </c>
       <c r="AT30" s="1" t="n">
         <v>3</v>
@@ -6157,44 +6239,44 @@
       <c r="AU30" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AV30" s="17" t="n">
+      <c r="AV30" s="22" t="n">
         <f aca="false">AT30+AU30/10</f>
         <v>3.2</v>
       </c>
-      <c r="AW30" s="17" t="n">
+      <c r="AW30" s="22" t="n">
         <f aca="false">1000*AV30</f>
         <v>3200</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B31" s="19" t="n">
+      <c r="A31" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="24" t="n">
         <v>76</v>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="19" t="n">
         <f aca="false">1000*B31/$U31</f>
         <v>781.105469793829</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="19" t="n">
         <f aca="false">1000*D31/$U31</f>
         <v>380.275031346996</v>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="14" t="n">
+      <c r="G31" s="19" t="n">
         <f aca="false">1000*F31/$U31</f>
         <v>0</v>
       </c>
-      <c r="H31" s="19" t="n">
+      <c r="H31" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="I31" s="14" t="n">
+      <c r="I31" s="19" t="n">
         <f aca="false">1000*H31/$U31</f>
         <v>195.276367448457</v>
       </c>
@@ -6208,7 +6290,7 @@
       <c r="L31" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="M31" s="14" t="n">
+      <c r="M31" s="19" t="n">
         <f aca="false">1000*L31/$U31</f>
         <v>4111.08141996752</v>
       </c>
@@ -6225,7 +6307,7 @@
       <c r="Q31" s="1" t="n">
         <v>1300</v>
       </c>
-      <c r="R31" s="14" t="n">
+      <c r="R31" s="19" t="n">
         <f aca="false">1000*P31/$U31</f>
         <v>1817.09798762565</v>
       </c>
@@ -6266,12 +6348,12 @@
         <f aca="false">AC31/U31/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AE31" s="26"/>
+      <c r="AE31" s="31"/>
       <c r="AG31" s="1" t="n">
         <v>136.8</v>
       </c>
       <c r="AL31" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AM31" s="1" t="n">
         <v>0</v>
@@ -6287,8 +6369,8 @@
         <f aca="false">AO31*1000</f>
         <v>400</v>
       </c>
-      <c r="AS31" s="17" t="s">
-        <v>102</v>
+      <c r="AS31" s="22" t="s">
+        <v>98</v>
       </c>
       <c r="AT31" s="1" t="n">
         <v>1</v>
@@ -6296,44 +6378,44 @@
       <c r="AU31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AV31" s="17" t="n">
+      <c r="AV31" s="22" t="n">
         <f aca="false">AT31+AU31/10</f>
         <v>1.3</v>
       </c>
-      <c r="AW31" s="17" t="n">
+      <c r="AW31" s="22" t="n">
         <f aca="false">1000*AV31</f>
         <v>1300</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="14" t="n">
+      <c r="A32" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="19" t="n">
         <v>33</v>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C32" s="19" t="n">
         <f aca="false">1000*B32/$U32</f>
         <v>641.137728041033</v>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E32" s="19" t="n">
         <f aca="false">1000*D32/$U32</f>
         <v>271.997824017408</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="G32" s="14" t="n">
+      <c r="G32" s="19" t="n">
         <f aca="false">1000*F32/$U32</f>
         <v>7.77136640049737</v>
       </c>
-      <c r="H32" s="14" t="n">
+      <c r="H32" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="I32" s="14" t="n">
+      <c r="I32" s="19" t="n">
         <f aca="false">1000*H32/$U32</f>
         <v>1457.13120009326</v>
       </c>
@@ -6347,7 +6429,7 @@
       <c r="L32" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="M32" s="14" t="n">
+      <c r="M32" s="19" t="n">
         <f aca="false">1000*L32/$U32</f>
         <v>5828.52480037303</v>
       </c>
@@ -6364,7 +6446,7 @@
       <c r="Q32" s="1" t="n">
         <v>1100</v>
       </c>
-      <c r="R32" s="14" t="n">
+      <c r="R32" s="19" t="n">
         <f aca="false">1000*P32/$U32</f>
         <v>2906.49103378602</v>
       </c>
@@ -6409,7 +6491,7 @@
         <v>70.5</v>
       </c>
       <c r="AL32" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AM32" s="1" t="n">
         <v>0</v>
@@ -6425,8 +6507,8 @@
         <f aca="false">AO32*1000</f>
         <v>300</v>
       </c>
-      <c r="AS32" s="17" t="s">
-        <v>104</v>
+      <c r="AS32" s="22" t="s">
+        <v>100</v>
       </c>
       <c r="AT32" s="1" t="n">
         <v>1</v>
@@ -6434,44 +6516,44 @@
       <c r="AU32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV32" s="17" t="n">
+      <c r="AV32" s="22" t="n">
         <f aca="false">AT32+AU32/10</f>
         <v>1.1</v>
       </c>
-      <c r="AW32" s="17" t="n">
+      <c r="AW32" s="22" t="n">
         <f aca="false">1000*AV32</f>
         <v>1100</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" s="19" t="n">
+      <c r="A33" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="24" t="n">
         <v>683</v>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="19" t="n">
         <f aca="false">1000*B33/$U33</f>
         <v>562.985554433614</v>
       </c>
-      <c r="D33" s="20" t="n">
+      <c r="D33" s="25" t="n">
         <v>830</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="19" t="n">
         <f aca="false">1000*D33/$U33</f>
         <v>684.155212562079</v>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="F33" s="26" t="n">
         <v>240.6</v>
       </c>
-      <c r="G33" s="14" t="n">
+      <c r="G33" s="19" t="n">
         <f aca="false">1000*F33/$U33</f>
         <v>198.32258330414</v>
       </c>
-      <c r="H33" s="19" t="n">
+      <c r="H33" s="24" t="n">
         <v>2151</v>
       </c>
-      <c r="I33" s="14" t="n">
+      <c r="I33" s="19" t="n">
         <f aca="false">1000*H33/$U33</f>
         <v>1773.033568941</v>
       </c>
@@ -6485,7 +6567,7 @@
       <c r="L33" s="1" t="n">
         <v>9330</v>
       </c>
-      <c r="M33" s="14" t="n">
+      <c r="M33" s="19" t="n">
         <f aca="false">1000*L33/$U33</f>
         <v>7690.56401590867</v>
       </c>
@@ -6502,7 +6584,7 @@
       <c r="Q33" s="1" t="n">
         <v>30900</v>
       </c>
-      <c r="R33" s="14" t="n">
+      <c r="R33" s="19" t="n">
         <f aca="false">1000*P33/$U33</f>
         <v>3463.96851237455</v>
       </c>
@@ -6551,7 +6633,7 @@
         <v>1687.2</v>
       </c>
       <c r="AL33" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AM33" s="1" t="n">
         <v>9</v>
@@ -6567,8 +6649,8 @@
         <f aca="false">AO33*1000</f>
         <v>9330</v>
       </c>
-      <c r="AS33" s="17" t="s">
-        <v>108</v>
+      <c r="AS33" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="AT33" s="1" t="n">
         <v>30</v>
@@ -6576,44 +6658,44 @@
       <c r="AU33" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV33" s="17" t="n">
+      <c r="AV33" s="22" t="n">
         <f aca="false">AT33+AU33/10</f>
         <v>30.9</v>
       </c>
-      <c r="AW33" s="17" t="n">
+      <c r="AW33" s="22" t="n">
         <f aca="false">1000*AV33</f>
         <v>30900</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B34" s="14" t="n">
+      <c r="A34" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="19" t="n">
         <v>189</v>
       </c>
-      <c r="C34" s="14" t="n">
+      <c r="C34" s="19" t="n">
         <f aca="false">1000*B34/$U34</f>
         <v>341.958899796996</v>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="20" t="n">
         <v>601</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="19" t="n">
         <f aca="false">1000*D34/$U34</f>
         <v>1087.39311522748</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="21" t="n">
         <v>245.1</v>
       </c>
-      <c r="G34" s="14" t="n">
+      <c r="G34" s="19" t="n">
         <f aca="false">1000*F34/$U34</f>
         <v>443.460985927215</v>
       </c>
-      <c r="H34" s="14" t="n">
+      <c r="H34" s="19" t="n">
         <v>712</v>
       </c>
-      <c r="I34" s="14" t="n">
+      <c r="I34" s="19" t="n">
         <f aca="false">1000*H34/$U34</f>
         <v>1288.22611987016</v>
       </c>
@@ -6627,7 +6709,7 @@
       <c r="L34" s="1" t="n">
         <v>1160</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="19" t="n">
         <f aca="false">1000*L34/$U34</f>
         <v>2098.79536383341</v>
       </c>
@@ -6644,7 +6726,7 @@
       <c r="Q34" s="1" t="n">
         <v>7100</v>
       </c>
-      <c r="R34" s="14" t="n">
+      <c r="R34" s="19" t="n">
         <f aca="false">1000*P34/$U34</f>
         <v>1747.0662097565</v>
       </c>
@@ -6689,7 +6771,7 @@
         <v>601.2</v>
       </c>
       <c r="AL34" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AM34" s="1" t="n">
         <v>1</v>
@@ -6705,8 +6787,8 @@
         <f aca="false">AO34*1000</f>
         <v>1160</v>
       </c>
-      <c r="AS34" s="17" t="s">
-        <v>111</v>
+      <c r="AS34" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="AT34" s="1" t="n">
         <v>7</v>
@@ -6714,35 +6796,35 @@
       <c r="AU34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV34" s="17" t="n">
+      <c r="AV34" s="22" t="n">
         <f aca="false">AT34+AU34/10</f>
         <v>7.1</v>
       </c>
-      <c r="AW34" s="17" t="n">
+      <c r="AW34" s="22" t="n">
         <f aca="false">1000*AV34</f>
         <v>7100</v>
       </c>
     </row>
-    <row r="35" s="31" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35" s="28" t="n">
+    <row r="35" s="36" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="33" t="n">
         <v>5847</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="29" t="n">
+      <c r="C35" s="33"/>
+      <c r="D35" s="34" t="n">
         <v>9557</v>
       </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="30" t="n">
+      <c r="E35" s="33"/>
+      <c r="F35" s="35" t="n">
         <v>8334.6</v>
       </c>
-      <c r="G35" s="30"/>
-      <c r="H35" s="28" t="n">
+      <c r="G35" s="35"/>
+      <c r="H35" s="33" t="n">
         <v>26264</v>
       </c>
-      <c r="I35" s="28"/>
+      <c r="I35" s="33"/>
       <c r="K35" s="1" t="n">
         <f aca="false">SUM(K8:K34)</f>
         <v>8092</v>
@@ -6754,7 +6836,7 @@
       </c>
       <c r="Q35" s="1"/>
       <c r="U35" s="1"/>
-      <c r="V35" s="31" t="n">
+      <c r="V35" s="36" t="n">
         <v>100</v>
       </c>
       <c r="W35" s="2" t="n">
@@ -6767,7 +6849,7 @@
         <v>38340.8</v>
       </c>
       <c r="Z35" s="1"/>
-      <c r="AA35" s="31" t="e">
+      <c r="AA35" s="36" t="e">
         <f aca="false">ROUND(Y35/U35 *100/1000, 2)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6776,14 +6858,14 @@
         <v>-24000</v>
       </c>
       <c r="AD35" s="1"/>
-      <c r="AG35" s="31" t="n">
+      <c r="AG35" s="36" t="n">
         <v>18796</v>
       </c>
-      <c r="AP35" s="31" t="n">
+      <c r="AP35" s="36" t="n">
         <f aca="false">SUM(AP8:AP34)</f>
         <v>47600</v>
       </c>
-      <c r="AV35" s="31" t="n">
+      <c r="AV35" s="36" t="n">
         <f aca="false">SUM(AV8:AV34)</f>
         <v>299.1</v>
       </c>
@@ -6825,225 +6907,229 @@
         <f aca="false">SUM(W8:W34)</f>
         <v>98776.1</v>
       </c>
-      <c r="Y36" s="0"/>
-      <c r="Z36" s="0"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="32" t="n">
+      <c r="J37" s="37" t="n">
         <v>93</v>
       </c>
-      <c r="K37" s="33" t="n">
+      <c r="K37" s="38" t="n">
         <v>17</v>
       </c>
-      <c r="O37" s="32" t="n">
+      <c r="O37" s="37" t="n">
         <v>44</v>
       </c>
-      <c r="P37" s="33" t="n">
+      <c r="P37" s="38" t="n">
         <v>13.6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="35" t="n">
+      <c r="B38" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="40" t="n">
         <f aca="false">SUM(B35:P35)</f>
         <v>98772.2</v>
       </c>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="K38" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="P38" s="41" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="34"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="34"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="U40" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="V40" s="37" t="n">
+      <c r="B40" s="39"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="U40" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="V40" s="43" t="n">
         <v>192.8</v>
       </c>
-      <c r="W40" s="38"/>
-      <c r="X40" s="38"/>
-      <c r="Y40" s="17"/>
-      <c r="Z40" s="17"/>
+      <c r="W40" s="44"/>
+      <c r="X40" s="44"/>
+      <c r="Y40" s="22"/>
+      <c r="Z40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U41" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="V41" s="36" t="n">
+      <c r="U41" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="V41" s="42" t="n">
         <f aca="false">V40*0.7</f>
         <v>134.96</v>
       </c>
-      <c r="W41" s="38"/>
-      <c r="X41" s="38"/>
-      <c r="Y41" s="17"/>
-      <c r="Z41" s="17"/>
+      <c r="W41" s="44"/>
+      <c r="X41" s="44"/>
+      <c r="Y41" s="22"/>
+      <c r="Z41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U42" s="36"/>
-      <c r="V42" s="36"/>
-      <c r="W42" s="38"/>
-      <c r="X42" s="38"/>
-      <c r="Y42" s="17"/>
-      <c r="Z42" s="17"/>
+      <c r="U42" s="42"/>
+      <c r="V42" s="42"/>
+      <c r="W42" s="44"/>
+      <c r="X42" s="44"/>
+      <c r="Y42" s="22"/>
+      <c r="Z42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U43" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="V43" s="40" t="n">
+      <c r="U43" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="V43" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="W43" s="38"/>
-      <c r="X43" s="38"/>
-      <c r="Y43" s="17"/>
-      <c r="Z43" s="17"/>
+      <c r="W43" s="44"/>
+      <c r="X43" s="44"/>
+      <c r="Y43" s="22"/>
+      <c r="Z43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S44" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="U44" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="V44" s="39" t="n">
+      <c r="S44" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="U44" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="V44" s="45" t="n">
         <f aca="false">W36/1000 -V43</f>
         <v>68.7761</v>
       </c>
-      <c r="W44" s="38"/>
-      <c r="X44" s="38"/>
-      <c r="Y44" s="17"/>
-      <c r="Z44" s="17"/>
+      <c r="W44" s="44"/>
+      <c r="X44" s="44"/>
+      <c r="Y44" s="22"/>
+      <c r="Z44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U45" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="V45" s="39" t="n">
+      <c r="U45" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="V45" s="45" t="n">
         <f aca="false">V44-V46-V47</f>
         <v>30.7761</v>
       </c>
-      <c r="W45" s="38"/>
-      <c r="X45" s="38"/>
-      <c r="Y45" s="17"/>
-      <c r="Z45" s="17"/>
+      <c r="W45" s="44"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="22"/>
+      <c r="Z45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U46" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="V46" s="40" t="n">
+      <c r="U46" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="V46" s="46" t="n">
         <v>14</v>
       </c>
-      <c r="W46" s="38"/>
-      <c r="X46" s="38"/>
-      <c r="Y46" s="17"/>
-      <c r="Z46" s="17"/>
+      <c r="W46" s="44"/>
+      <c r="X46" s="44"/>
+      <c r="Y46" s="22"/>
+      <c r="Z46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U47" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="V47" s="40" t="n">
+      <c r="U47" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="V47" s="46" t="n">
         <v>24</v>
       </c>
-      <c r="W47" s="38"/>
-      <c r="X47" s="38"/>
-      <c r="Y47" s="17"/>
-      <c r="Z47" s="17"/>
+      <c r="W47" s="44"/>
+      <c r="X47" s="44"/>
+      <c r="Y47" s="22"/>
+      <c r="Z47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="U48" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="V48" s="39" t="n">
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="U48" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="V48" s="45" t="n">
         <f aca="false">V40+V46</f>
         <v>206.8</v>
       </c>
-      <c r="W48" s="38"/>
-      <c r="X48" s="38"/>
-      <c r="Y48" s="17"/>
-      <c r="Z48" s="17"/>
+      <c r="W48" s="44"/>
+      <c r="X48" s="44"/>
+      <c r="Y48" s="22"/>
+      <c r="Z48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="U49" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="V49" s="39" t="n">
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="U49" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="V49" s="45" t="n">
         <f aca="false">V41-V45</f>
         <v>104.1839</v>
       </c>
-      <c r="W49" s="38"/>
-      <c r="X49" s="38"/>
-      <c r="Y49" s="17"/>
-      <c r="Z49" s="17"/>
+      <c r="W49" s="44"/>
+      <c r="X49" s="44"/>
+      <c r="Y49" s="22"/>
+      <c r="Z49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="U50" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="V50" s="39" t="n">
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
+      <c r="U50" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="V50" s="45" t="n">
         <f aca="false">V49/V48</f>
         <v>0.503790618955513</v>
       </c>
-      <c r="W50" s="38"/>
-      <c r="X50" s="38"/>
-      <c r="Y50" s="17"/>
-      <c r="Z50" s="17"/>
+      <c r="W50" s="44"/>
+      <c r="X50" s="44"/>
+      <c r="Y50" s="22"/>
+      <c r="Z50" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="41"/>
+      <c r="A53" s="47"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="Y53" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AC53" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AD53" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="41"/>
+      <c r="A55" s="47"/>
       <c r="K55" s="1" t="s">
         <v>5</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -904,7 +904,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$C$1</c:f>
+              <c:f>Combined_2!$C$1:$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1137,7 +1137,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$E$1</c:f>
+              <c:f>Combined_2!$E$1:$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1370,7 +1370,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$G$1</c:f>
+              <c:f>Combined_2!$G$1:$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1603,7 +1603,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$I$1</c:f>
+              <c:f>Combined_2!$I$1:$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1836,7 +1836,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$K$1</c:f>
+              <c:f>Combined_2!$K$1:$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2069,7 +2069,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$R$1</c:f>
+              <c:f>Combined_2!$R$1:$R$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2299,11 +2299,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="84957813"/>
-        <c:axId val="13308638"/>
+        <c:axId val="15868000"/>
+        <c:axId val="69750484"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84957813"/>
+        <c:axId val="15868000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2335,7 +2335,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13308638"/>
+        <c:crossAx val="69750484"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2343,7 +2343,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13308638"/>
+        <c:axId val="69750484"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2373,8 +2373,1543 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84957813"/>
+        <c:crossAx val="15868000"/>
         <c:crossesAt val="0"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_2!$C$1:$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DST</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>Austria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Belgium</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bulgaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Croatia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Cyprus</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Czechia</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Denmark</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Estonia</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Finland</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Greece</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hungary</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ireland</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Italy</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Latvia</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lithuania</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Luxembourg</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Malta</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Netherlands</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Poland</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Portugal</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Romania</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Slovakia</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Slovenia</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Spain</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Sweden</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Combined_2!$C$8:$C$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>345.61025947732</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>394.508442480669</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>726.008291778911</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>786.755148115208</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>727.603456116417</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>777.772407095745</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>304.277684963515</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>744.360658921001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>379.785988637743</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>418.692157950257</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>260.893020991029</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>503.093193867792</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>933.361983293492</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>299.863052234907</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>255.791133309077</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>816.326530612245</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>759.034360189574</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>198.137507430157</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>510.538983298082</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>396.580804533444</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>901.606282772202</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>641.88790560472</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>617.708255926284</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>781.105469793829</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>641.137728041033</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>562.985554433614</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>341.958899796996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_2!$E$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ad Tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>Austria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Belgium</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bulgaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Croatia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Cyprus</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Czechia</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Denmark</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Estonia</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Finland</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Greece</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hungary</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ireland</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Italy</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Latvia</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lithuania</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Luxembourg</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Malta</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Netherlands</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Poland</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Portugal</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Romania</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Slovakia</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Slovenia</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Spain</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Sweden</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Combined_2!$E$8:$E$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>808.87507537245</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>362.947767082216</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>343.898664526853</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>444.687692412944</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1155.67312466769</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>740.600403024405</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>679.633645101783</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>520.737489575462</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>656.779628101934</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>723.958023305013</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>298.538818339129</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>758.776288576724</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>494.619467603971</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>491.185128832732</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>604.686318972033</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>444.312796208531</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>778.827363119896</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>779.323649278806</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>396.46017699115</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>139.332689306681</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>380.275031346996</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>271.997824017408</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>684.155212562079</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1087.39311522748</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_2!$G$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FTT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>Austria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Belgium</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bulgaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Croatia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Cyprus</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Czechia</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Denmark</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Estonia</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Finland</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Greece</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hungary</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ireland</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Italy</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Latvia</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lithuania</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Luxembourg</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Malta</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Netherlands</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Poland</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Portugal</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Romania</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Slovakia</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Slovenia</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Spain</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Sweden</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Combined_2!$G$8:$G$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>64.710006029796</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>120.522329177844</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.82109627252059</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.13101183553397</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.3801728058208</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.6979386834115</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>326.667929706114</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.23635069096087</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>318.315472951015</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1204.03125199054</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>427.725125472651</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>125.496873635152</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39.617523031882</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>746.257121747491</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>300.168689842225</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.85130331753555</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2342.4546918376</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>114.982177762447</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>117.522123893805</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.82440365608977</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.77136640049737</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>198.32258330414</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>443.460985927215</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_2!$I$1:$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Wealth Tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="800080"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>Austria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Belgium</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bulgaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Croatia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Cyprus</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Czechia</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Denmark</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Estonia</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Finland</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Greece</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hungary</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ireland</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Italy</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Latvia</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lithuania</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Luxembourg</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Malta</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Netherlands</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Poland</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Portugal</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Romania</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Slovakia</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Slovenia</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Spain</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Sweden</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Combined_2!$I$8:$I$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>2255.04566467471</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1424.17547735522</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>764.219254504117</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>615.721420264076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2091.8599363347</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1529.17964784926</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1530.00005741088</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>938.541700378653</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>595.128559514814</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2590.60917766996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2237.29842461372</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>652.362603037356</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1396.68555773415</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1023.24402360571</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1443.23531681716</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>604.686318972033</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>573.904028436019</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4121.26015454726</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>656.407264240391</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1090.59721246697</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1022.06380233286</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1557.52212389381</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>561.975180203611</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>195.276367448457</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1457.13120009326</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1773.033568941</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1288.22611987016</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_2!$K$1:$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="729fcf"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>Austria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Belgium</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bulgaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Croatia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Cyprus</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Czechia</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Denmark</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Estonia</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Finland</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Greece</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hungary</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ireland</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Italy</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Latvia</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lithuania</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Luxembourg</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Malta</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Netherlands</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Poland</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Portugal</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Romania</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Slovakia</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Slovenia</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Spain</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Sweden</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Combined_2!$K$8:$K$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>323</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>64.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>74.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>192.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>122.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>914.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1088</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>431.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>62.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>159.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1208.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>35.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>336.6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>202.3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>331.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>105.4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1586.1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>197.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Combined_2!$R$1:$R$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Luxury tax</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="b85c00"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Combined_2!$A$8:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>Austria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Belgium</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bulgaria</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Croatia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Cyprus</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Czechia</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Denmark</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Estonia</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Finland</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Greece</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Hungary</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ireland</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Italy</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Latvia</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Lithuania</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Luxembourg</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Malta</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Netherlands</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Poland</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Portugal</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Romania</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Slovakia</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Slovenia</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Spain</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Sweden</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Combined_2!$R$8:$R$34</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>3300.2103075196</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2629.00426069118</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4157.3527445024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5349.93500718342</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9276.94406548431</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2749.00801061637</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1639.65484576566</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2200.71846985339</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1544.20199916212</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3274.96500541426</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2104.09014832559</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4736.81591764751</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2283.04370014235</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1597.62088036082</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4235.98937143739</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2055.93348450491</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2014.21800947867</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4850.40618189023</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8927.13879366932</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1787.00266139166</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1985.72395881813</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4108.08259587021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2021.25287954225</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1817.09798762565</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2906.49103378602</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3463.96851237455</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1747.0662097565</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="100"/>
+        <c:axId val="85549976"/>
+        <c:axId val="45664579"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="85549976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="45664579"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="45664579"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="85549976"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -2450,6 +3985,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>935640</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>147960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>330120</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>89640</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="13897440" y="9073440"/>
+        <a:ext cx="10058400" cy="5656680"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2569,7 +4134,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFA55"/>
+  <dimension ref="A1:XFD55"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
@@ -2582,12 +4147,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="18.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="14.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="22.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="11.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="11.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="2" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="22.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="11.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16347" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" s="10" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2633,12 +4200,15 @@
       <c r="V1" s="7"/>
       <c r="W1" s="9"/>
       <c r="X1" s="9"/>
-      <c r="AF1" s="10" t="s">
+      <c r="Y1" s="9"/>
+      <c r="AG1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AH1" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="XFC1" s="0"/>
+      <c r="XFD1" s="0"/>
     </row>
     <row r="2" s="13" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
@@ -2699,21 +4269,24 @@
         <v>16</v>
       </c>
       <c r="W2" s="9"/>
-      <c r="X2" s="9" t="s">
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Z2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="AC2" s="13" t="s">
+      <c r="AD2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" s="13" t="s">
+      <c r="AG2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AG2" s="13" t="s">
+      <c r="AH2" s="13" t="s">
         <v>14</v>
       </c>
+      <c r="XFC2" s="0"/>
+      <c r="XFD2" s="0"/>
     </row>
     <row r="3" s="13" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
@@ -2775,17 +4348,20 @@
         <v>25</v>
       </c>
       <c r="X3" s="9"/>
-      <c r="Y3" s="14"/>
+      <c r="Y3" s="9"/>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="13" t="s">
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AD3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="AG3" s="13" t="s">
+      <c r="AH3" s="13" t="s">
         <v>24</v>
       </c>
+      <c r="XFC3" s="0"/>
+      <c r="XFD3" s="0"/>
     </row>
     <row r="4" s="17" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
@@ -2819,8 +4395,8 @@
       <c r="R4" s="16"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="AG4" s="16"/>
-      <c r="XDR4" s="16"/>
+      <c r="Y4" s="2"/>
+      <c r="AH4" s="16"/>
       <c r="XDS4" s="16"/>
       <c r="XDT4" s="16"/>
       <c r="XDU4" s="16"/>
@@ -2856,6 +4432,9 @@
       <c r="XEY4" s="16"/>
       <c r="XEZ4" s="16"/>
       <c r="XFA4" s="16"/>
+      <c r="XFB4" s="16"/>
+      <c r="XFC4" s="0"/>
+      <c r="XFD4" s="0"/>
     </row>
     <row r="5" s="17" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
@@ -2889,8 +4468,8 @@
       <c r="R5" s="16"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
-      <c r="AG5" s="16"/>
-      <c r="XDR5" s="16"/>
+      <c r="Y5" s="2"/>
+      <c r="AH5" s="16"/>
       <c r="XDS5" s="16"/>
       <c r="XDT5" s="16"/>
       <c r="XDU5" s="16"/>
@@ -2926,6 +4505,9 @@
       <c r="XEY5" s="16"/>
       <c r="XEZ5" s="16"/>
       <c r="XFA5" s="16"/>
+      <c r="XFB5" s="16"/>
+      <c r="XFC5" s="0"/>
+      <c r="XFD5" s="0"/>
     </row>
     <row r="6" s="17" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
@@ -2947,14 +4529,14 @@
       <c r="R6" s="16"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6" s="17" t="s">
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="AC6" s="17" t="s">
+      <c r="AD6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="AG6" s="16"/>
-      <c r="XDR6" s="16"/>
+      <c r="AH6" s="16"/>
       <c r="XDS6" s="16"/>
       <c r="XDT6" s="16"/>
       <c r="XDU6" s="16"/>
@@ -2990,6 +4572,9 @@
       <c r="XEY6" s="16"/>
       <c r="XEZ6" s="16"/>
       <c r="XFA6" s="16"/>
+      <c r="XFB6" s="16"/>
+      <c r="XFC6" s="0"/>
+      <c r="XFD6" s="0"/>
     </row>
     <row r="7" s="17" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
@@ -3011,16 +4596,16 @@
       <c r="R7" s="16"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="17" t="s">
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="17" t="s">
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="AG7" s="16"/>
-      <c r="XDR7" s="16"/>
+      <c r="AH7" s="16"/>
       <c r="XDS7" s="16"/>
       <c r="XDT7" s="16"/>
       <c r="XDU7" s="16"/>
@@ -3056,6 +4641,9 @@
       <c r="XEY7" s="16"/>
       <c r="XEZ7" s="16"/>
       <c r="XFA7" s="16"/>
+      <c r="XFB7" s="16"/>
+      <c r="XFC7" s="0"/>
+      <c r="XFD7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
@@ -3137,61 +4725,65 @@
         <f aca="false">H8+F8+B8+D8+K8+P8</f>
         <v>3086.8</v>
       </c>
-      <c r="Y8" s="1" t="n">
-        <f aca="false">-X8+($V$45 + $V$46)*1000*V8/100</f>
+      <c r="X8" s="2" t="n">
+        <f aca="false">W8/U8</f>
+        <v>7.56616843230206</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <f aca="false">-Y8+($V$45 + $V$46)*1000*V8/100</f>
         <v>1254.66991877658</v>
       </c>
-      <c r="Z8" s="1" t="n">
-        <f aca="false">Y8/U8/10</f>
+      <c r="AA8" s="1" t="n">
+        <f aca="false">Z8/U8/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA8" s="1" t="n">
-        <f aca="false">Y8/U8</f>
+      <c r="AB8" s="1" t="n">
+        <f aca="false">Z8/U8</f>
         <v>3.07536734884228</v>
       </c>
-      <c r="AC8" s="1" t="n">
+      <c r="AD8" s="1" t="n">
         <f aca="false">-V8*($V$47)*10</f>
         <v>-672.503367882374</v>
       </c>
-      <c r="AD8" s="1" t="n">
-        <f aca="false">AC8/U8/10</f>
+      <c r="AE8" s="1" t="n">
+        <f aca="false">AD8/U8/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG8" s="1" t="n">
+      <c r="AH8" s="1" t="n">
         <v>514.3</v>
       </c>
-      <c r="AL8" s="1" t="s">
+      <c r="AM8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AM8" s="1" t="n">
+      <c r="AN8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN8" s="1" t="n">
+      <c r="AO8" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="AO8" s="1" t="n">
-        <f aca="false">AM8+AN8/100</f>
+      <c r="AP8" s="1" t="n">
+        <f aca="false">AN8+AO8/100</f>
         <v>1.9</v>
       </c>
-      <c r="AP8" s="1" t="n">
-        <f aca="false">AO8*1000</f>
+      <c r="AQ8" s="1" t="n">
+        <f aca="false">AP8*1000</f>
         <v>1900</v>
       </c>
-      <c r="AS8" s="22" t="s">
+      <c r="AT8" s="22" t="s">
         <v>41</v>
-      </c>
-      <c r="AT8" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="AU8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV8" s="22" t="n">
-        <f aca="false">AT8+AU8/10</f>
+      <c r="AV8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW8" s="22" t="n">
+        <f aca="false">AU8+AV8/10</f>
         <v>9.9</v>
       </c>
-      <c r="AW8" s="22" t="n">
-        <f aca="false">1000*AV8</f>
+      <c r="AX8" s="22" t="n">
+        <f aca="false">1000*AW8</f>
         <v>9900</v>
       </c>
     </row>
@@ -3275,65 +4867,69 @@
         <f aca="false">H9+F9+B9+D9+K9+P9</f>
         <v>2686.9</v>
       </c>
-      <c r="X9" s="27" t="n">
+      <c r="X9" s="2" t="n">
+        <f aca="false">W9/U9</f>
+        <v>5.30002367050655</v>
+      </c>
+      <c r="Y9" s="27" t="n">
         <f aca="false">F9</f>
         <v>61.1</v>
       </c>
-      <c r="Y9" s="1" t="n">
-        <f aca="false">-X9+($V$45 + $V$46)*1000*V9/100</f>
+      <c r="Z9" s="1" t="n">
+        <f aca="false">-Y9+($V$45 + $V$46)*1000*V9/100</f>
         <v>1497.98823116908</v>
       </c>
-      <c r="Z9" s="1" t="n">
-        <f aca="false">Y9/U9/10</f>
+      <c r="AA9" s="1" t="n">
+        <f aca="false">Z9/U9/10</f>
         <v>0.295484501966444</v>
       </c>
-      <c r="AA9" s="1" t="n">
-        <f aca="false">Y9/U9</f>
+      <c r="AB9" s="1" t="n">
+        <f aca="false">Z9/U9</f>
         <v>2.95484501966444</v>
       </c>
-      <c r="AC9" s="1" t="n">
+      <c r="AD9" s="1" t="n">
         <f aca="false">-V9*($V$47)*10</f>
         <v>-835.671654031012</v>
       </c>
-      <c r="AD9" s="1" t="n">
-        <f aca="false">AC9/U9/10</f>
+      <c r="AE9" s="1" t="n">
+        <f aca="false">AD9/U9/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG9" s="1" t="n">
+      <c r="AH9" s="1" t="n">
         <v>642</v>
       </c>
-      <c r="AL9" s="1" t="s">
+      <c r="AM9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AM9" s="1" t="n">
+      <c r="AN9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN9" s="1" t="n">
+      <c r="AO9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AO9" s="1" t="n">
-        <f aca="false">AM9+AN9/100</f>
+      <c r="AP9" s="1" t="n">
+        <f aca="false">AN9+AO9/100</f>
         <v>1.1</v>
       </c>
-      <c r="AP9" s="1" t="n">
-        <f aca="false">AO9*1000</f>
+      <c r="AQ9" s="1" t="n">
+        <f aca="false">AP9*1000</f>
         <v>1100</v>
       </c>
-      <c r="AS9" s="22" t="s">
+      <c r="AT9" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="AT9" s="1" t="n">
+      <c r="AU9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AU9" s="1" t="n">
+      <c r="AV9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AV9" s="22" t="n">
-        <f aca="false">AT9+AU9/10</f>
+      <c r="AW9" s="22" t="n">
+        <f aca="false">AU9+AV9/10</f>
         <v>9.8</v>
       </c>
-      <c r="AW9" s="22" t="n">
-        <f aca="false">1000*AV9</f>
+      <c r="AX9" s="22" t="n">
+        <f aca="false">1000*AW9</f>
         <v>9800</v>
       </c>
     </row>
@@ -3417,61 +5013,65 @@
         <f aca="false">H10+F10+B10+D10+K10+P10</f>
         <v>359.7</v>
       </c>
-      <c r="Y10" s="1" t="n">
-        <f aca="false">-X10+($V$45 + $V$46)*1000*V10/100</f>
+      <c r="X10" s="2" t="n">
+        <f aca="false">W10/U10</f>
+        <v>6.87224164612827</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <f aca="false">-Y10+($V$45 + $V$46)*1000*V10/100</f>
         <v>160.967802405754</v>
       </c>
-      <c r="Z10" s="1" t="n">
-        <f aca="false">Y10/U10/10</f>
+      <c r="AA10" s="1" t="n">
+        <f aca="false">Z10/U10/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA10" s="1" t="n">
-        <f aca="false">Y10/U10</f>
+      <c r="AB10" s="1" t="n">
+        <f aca="false">Z10/U10</f>
         <v>3.07536734884228</v>
       </c>
-      <c r="AC10" s="1" t="n">
+      <c r="AD10" s="1" t="n">
         <f aca="false">-V10*($V$47)*10</f>
         <v>-86.2787794769552</v>
       </c>
-      <c r="AD10" s="1" t="n">
-        <f aca="false">AC10/U10/10</f>
+      <c r="AE10" s="1" t="n">
+        <f aca="false">AD10/U10/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG10" s="1" t="n">
+      <c r="AH10" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="AL10" s="1" t="s">
+      <c r="AM10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AM10" s="1" t="n">
+      <c r="AN10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN10" s="1" t="n">
+      <c r="AO10" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AO10" s="1" t="n">
-        <f aca="false">AM10+AN10/100</f>
+      <c r="AP10" s="1" t="n">
+        <f aca="false">AN10+AO10/100</f>
         <v>0.27</v>
       </c>
-      <c r="AP10" s="1" t="n">
-        <f aca="false">AO10*1000</f>
+      <c r="AQ10" s="1" t="n">
+        <f aca="false">AP10*1000</f>
         <v>270</v>
       </c>
-      <c r="AS10" s="22" t="s">
+      <c r="AT10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="AT10" s="1" t="n">
+      <c r="AU10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AU10" s="1" t="n">
+      <c r="AV10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AV10" s="22" t="n">
-        <f aca="false">AT10+AU10/10</f>
+      <c r="AW10" s="22" t="n">
+        <f aca="false">AU10+AV10/10</f>
         <v>1.6</v>
       </c>
-      <c r="AW10" s="22" t="n">
-        <f aca="false">1000*AV10</f>
+      <c r="AX10" s="22" t="n">
+        <f aca="false">1000*AW10</f>
         <v>1600</v>
       </c>
     </row>
@@ -3555,61 +5155,65 @@
         <f aca="false">H11+F11+B11+D11+K11+P11</f>
         <v>485.7</v>
       </c>
-      <c r="Y11" s="1" t="n">
-        <f aca="false">-X11+($V$45 + $V$46)*1000*V11/100</f>
-        <v>179.810578152111</v>
+      <c r="X11" s="2" t="n">
+        <f aca="false">W11/U11</f>
+        <v>8.30710816172949</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <f aca="false">Y11/U11/10</f>
+        <f aca="false">-Y11+($V$45 + $V$46)*1000*V11/100</f>
+        <v>179.81057815211</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <f aca="false">Z11/U11/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA11" s="1" t="n">
-        <f aca="false">ROUND(Y11/U11 *100/1000, 2)</f>
+      <c r="AB11" s="1" t="n">
+        <f aca="false">ROUND(Z11/U11 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC11" s="1" t="n">
+      <c r="AD11" s="1" t="n">
         <f aca="false">-V11*($V$47)*10</f>
         <v>-96.378511653553</v>
       </c>
-      <c r="AD11" s="1" t="n">
-        <f aca="false">AC11/U11/10</f>
+      <c r="AE11" s="1" t="n">
+        <f aca="false">AD11/U11/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG11" s="1" t="n">
+      <c r="AH11" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="AL11" s="1" t="s">
+      <c r="AM11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AM11" s="1" t="n">
+      <c r="AN11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN11" s="1" t="n">
+      <c r="AO11" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="AO11" s="1" t="n">
-        <f aca="false">AM11+AN11/100</f>
+      <c r="AP11" s="1" t="n">
+        <f aca="false">AN11+AO11/100</f>
         <v>0.38</v>
       </c>
-      <c r="AP11" s="1" t="n">
-        <f aca="false">AO11*1000</f>
+      <c r="AQ11" s="1" t="n">
+        <f aca="false">AP11*1000</f>
         <v>380</v>
       </c>
-      <c r="AS11" s="22" t="s">
+      <c r="AT11" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="AT11" s="1" t="n">
+      <c r="AU11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AU11" s="1" t="n">
+      <c r="AV11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AV11" s="22" t="n">
-        <f aca="false">AT11+AU11/10</f>
+      <c r="AW11" s="22" t="n">
+        <f aca="false">AU11+AV11/10</f>
         <v>2.3</v>
       </c>
-      <c r="AW11" s="22" t="n">
-        <f aca="false">1000*AV11</f>
+      <c r="AX11" s="22" t="n">
+        <f aca="false">1000*AW11</f>
         <v>2300</v>
       </c>
     </row>
@@ -3691,61 +5295,65 @@
         <f aca="false">H12+F12+B12+D12+K12+P12</f>
         <v>316.1</v>
       </c>
-      <c r="Y12" s="1" t="n">
-        <f aca="false">-X12+($V$45 + $V$46)*1000*V12/100</f>
+      <c r="X12" s="2" t="n">
+        <f aca="false">W12/U12</f>
+        <v>14.3747157799</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <f aca="false">-Y12+($V$45 + $V$46)*1000*V12/100</f>
         <v>67.6273280010418</v>
       </c>
-      <c r="Z12" s="1" t="n">
-        <f aca="false">Y12/U12/10</f>
+      <c r="AA12" s="1" t="n">
+        <f aca="false">Z12/U12/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA12" s="1" t="n">
-        <f aca="false">ROUND(Y12/U12 *100/1000, 2)</f>
+      <c r="AB12" s="1" t="n">
+        <f aca="false">ROUND(Z12/U12 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC12" s="1" t="n">
+      <c r="AD12" s="1" t="n">
         <f aca="false">-V12*($V$47)*10</f>
         <v>-36.2482635161393</v>
       </c>
-      <c r="AD12" s="1" t="n">
-        <f aca="false">AC12/U12/10</f>
+      <c r="AE12" s="1" t="n">
+        <f aca="false">AD12/U12/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG12" s="1" t="n">
+      <c r="AH12" s="1" t="n">
         <v>36.5</v>
       </c>
-      <c r="AL12" s="1" t="s">
+      <c r="AM12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AM12" s="1" t="n">
+      <c r="AN12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN12" s="1" t="n">
+      <c r="AO12" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="AO12" s="1" t="n">
-        <f aca="false">AM12+AN12/100</f>
+      <c r="AP12" s="1" t="n">
+        <f aca="false">AN12+AO12/100</f>
         <v>0.29</v>
       </c>
-      <c r="AP12" s="1" t="n">
-        <f aca="false">AO12*1000</f>
+      <c r="AQ12" s="1" t="n">
+        <f aca="false">AP12*1000</f>
         <v>290</v>
       </c>
-      <c r="AS12" s="22" t="s">
+      <c r="AT12" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="AT12" s="1" t="n">
+      <c r="AU12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AU12" s="1" t="n">
+      <c r="AV12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV12" s="22" t="n">
-        <f aca="false">AT12+AU12/10</f>
+      <c r="AW12" s="22" t="n">
+        <f aca="false">AU12+AV12/10</f>
         <v>1.5</v>
       </c>
-      <c r="AW12" s="22" t="n">
-        <f aca="false">1000*AV12</f>
+      <c r="AX12" s="22" t="n">
+        <f aca="false">1000*AW12</f>
         <v>1500</v>
       </c>
     </row>
@@ -3829,61 +5437,65 @@
         <f aca="false">H13+F13+B13+D13+K13+P13</f>
         <v>1492.2</v>
       </c>
-      <c r="Y13" s="1" t="n">
-        <f aca="false">-X13+($V$45 + $V$46)*1000*V13/100</f>
-        <v>699.870573678085</v>
+      <c r="X13" s="2" t="n">
+        <f aca="false">W13/U13</f>
+        <v>6.55701686931226</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <f aca="false">Y13/U13/10</f>
+        <f aca="false">-Y13+($V$45 + $V$46)*1000*V13/100</f>
+        <v>699.870573678084</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <f aca="false">Z13/U13/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA13" s="1" t="n">
-        <f aca="false">ROUND(Y13/U13 *100/1000, 2)</f>
+      <c r="AB13" s="1" t="n">
+        <f aca="false">ROUND(Z13/U13 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC13" s="1" t="n">
+      <c r="AD13" s="1" t="n">
         <f aca="false">-V13*($V$47)*10</f>
         <v>-375.130790048129</v>
       </c>
-      <c r="AD13" s="1" t="n">
-        <f aca="false">AC13/U13/10</f>
+      <c r="AE13" s="1" t="n">
+        <f aca="false">AD13/U13/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG13" s="1" t="n">
+      <c r="AH13" s="1" t="n">
         <v>347.3</v>
       </c>
-      <c r="AL13" s="1" t="s">
+      <c r="AM13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AM13" s="1" t="n">
+      <c r="AN13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN13" s="1" t="n">
+      <c r="AO13" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="AO13" s="1" t="n">
-        <f aca="false">AM13+AN13/100</f>
+      <c r="AP13" s="1" t="n">
+        <f aca="false">AN13+AO13/100</f>
         <v>0.44</v>
       </c>
-      <c r="AP13" s="1" t="n">
-        <f aca="false">AO13*1000</f>
+      <c r="AQ13" s="1" t="n">
+        <f aca="false">AP13*1000</f>
         <v>440</v>
       </c>
-      <c r="AS13" s="22" t="s">
+      <c r="AT13" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="AT13" s="1" t="n">
+      <c r="AU13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AU13" s="1" t="n">
+      <c r="AV13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AV13" s="22" t="n">
-        <f aca="false">AT13+AU13/10</f>
+      <c r="AW13" s="22" t="n">
+        <f aca="false">AU13+AV13/10</f>
         <v>4.6</v>
       </c>
-      <c r="AW13" s="22" t="n">
-        <f aca="false">1000*AV13</f>
+      <c r="AX13" s="22" t="n">
+        <f aca="false">1000*AW13</f>
         <v>4600</v>
       </c>
     </row>
@@ -3967,61 +5579,65 @@
         <f aca="false">H14+F14+B14+D14+K14+P14</f>
         <v>1774.1</v>
       </c>
-      <c r="Y14" s="1" t="n">
-        <f aca="false">-X14+($V$45 + $V$46)*1000*V14/100</f>
+      <c r="X14" s="2" t="n">
+        <f aca="false">W14/U14</f>
+        <v>5.09263246126201</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <f aca="false">-Y14+($V$45 + $V$46)*1000*V14/100</f>
         <v>1071.35342184679</v>
       </c>
-      <c r="Z14" s="1" t="n">
-        <f aca="false">Y14/U14/10</f>
+      <c r="AA14" s="1" t="n">
+        <f aca="false">Z14/U14/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA14" s="1" t="n">
-        <f aca="false">ROUND(Y14/U14 *100/1000, 2)</f>
+      <c r="AB14" s="1" t="n">
+        <f aca="false">ROUND(Z14/U14 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC14" s="1" t="n">
+      <c r="AD14" s="1" t="n">
         <f aca="false">-V14*($V$47)*10</f>
         <v>-574.245682949676</v>
       </c>
-      <c r="AD14" s="1" t="n">
-        <f aca="false">AC14/U14/10</f>
+      <c r="AE14" s="1" t="n">
+        <f aca="false">AD14/U14/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG14" s="1" t="n">
+      <c r="AH14" s="1" t="n">
         <v>417.8</v>
       </c>
-      <c r="AL14" s="1" t="s">
+      <c r="AM14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AM14" s="1" t="n">
+      <c r="AN14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN14" s="1" t="n">
+      <c r="AO14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="AO14" s="1" t="n">
-        <f aca="false">AM14+AN14/100</f>
+      <c r="AP14" s="1" t="n">
+        <f aca="false">AN14+AO14/100</f>
         <v>1.13</v>
       </c>
-      <c r="AP14" s="1" t="n">
-        <f aca="false">AO14*1000</f>
+      <c r="AQ14" s="1" t="n">
+        <f aca="false">AP14*1000</f>
         <v>1130</v>
       </c>
-      <c r="AS14" s="22" t="s">
+      <c r="AT14" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="AT14" s="1" t="n">
+      <c r="AU14" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AU14" s="1" t="n">
+      <c r="AV14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AV14" s="22" t="n">
-        <f aca="false">AT14+AU14/10</f>
+      <c r="AW14" s="22" t="n">
+        <f aca="false">AU14+AV14/10</f>
         <v>4.2</v>
       </c>
-      <c r="AW14" s="22" t="n">
-        <f aca="false">1000*AV14</f>
+      <c r="AX14" s="22" t="n">
+        <f aca="false">1000*AW14</f>
         <v>4200</v>
       </c>
     </row>
@@ -4105,61 +5721,65 @@
         <f aca="false">H15+F15+B15+D15+K15+P15</f>
         <v>294.1</v>
       </c>
-      <c r="Y15" s="1" t="n">
-        <f aca="false">-X15+($V$45 + $V$46)*1000*V15/100</f>
-        <v>95.0257757118777</v>
+      <c r="X15" s="2" t="n">
+        <f aca="false">W15/U15</f>
+        <v>9.51810738211593</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <f aca="false">Y15/U15/10</f>
+        <f aca="false">-Y15+($V$45 + $V$46)*1000*V15/100</f>
+        <v>95.0257757118776</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <f aca="false">Z15/U15/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA15" s="1" t="n">
-        <f aca="false">ROUND(Y15/U15 *100/1000, 2)</f>
+      <c r="AB15" s="1" t="n">
+        <f aca="false">ROUND(Z15/U15 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC15" s="1" t="n">
+      <c r="AD15" s="1" t="n">
         <f aca="false">-V15*($V$47)*10</f>
         <v>-50.9338378528962</v>
       </c>
-      <c r="AD15" s="1" t="n">
-        <f aca="false">AC15/U15/10</f>
+      <c r="AE15" s="1" t="n">
+        <f aca="false">AD15/U15/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG15" s="1" t="n">
+      <c r="AH15" s="1" t="n">
         <v>41.9</v>
       </c>
-      <c r="AL15" s="1" t="s">
+      <c r="AM15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AM15" s="1" t="n">
+      <c r="AN15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN15" s="1" t="n">
+      <c r="AO15" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="AO15" s="1" t="n">
-        <f aca="false">AM15+AN15/100</f>
+      <c r="AP15" s="1" t="n">
+        <f aca="false">AN15+AO15/100</f>
         <v>0.9</v>
       </c>
-      <c r="AP15" s="1" t="n">
-        <f aca="false">AO15*1000</f>
+      <c r="AQ15" s="1" t="n">
+        <f aca="false">AP15*1000</f>
         <v>900</v>
       </c>
-      <c r="AS15" s="22" t="s">
+      <c r="AT15" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="AT15" s="1" t="n">
+      <c r="AU15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" s="1" t="n">
+      <c r="AV15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV15" s="22" t="n">
-        <f aca="false">AT15+AU15/10</f>
+      <c r="AW15" s="22" t="n">
+        <f aca="false">AU15+AV15/10</f>
         <v>0.5</v>
       </c>
-      <c r="AW15" s="22" t="n">
-        <f aca="false">1000*AV15</f>
+      <c r="AX15" s="22" t="n">
+        <f aca="false">1000*AW15</f>
         <v>500</v>
       </c>
     </row>
@@ -4243,61 +5863,65 @@
         <f aca="false">H16+F16+B16+D16+K16+P16</f>
         <v>980.1</v>
       </c>
-      <c r="Y16" s="1" t="n">
-        <f aca="false">-X16+($V$45 + $V$46)*1000*V16/100</f>
+      <c r="X16" s="2" t="n">
+        <f aca="false">W16/U16</f>
+        <v>3.8374046130294</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <f aca="false">-Y16+($V$45 + $V$46)*1000*V16/100</f>
         <v>785.470348465761</v>
       </c>
-      <c r="Z16" s="1" t="n">
-        <f aca="false">Y16/U16/10</f>
+      <c r="AA16" s="1" t="n">
+        <f aca="false">Z16/U16/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA16" s="1" t="n">
-        <f aca="false">ROUND(Y16/U16 *100/1000, 2)</f>
+      <c r="AB16" s="1" t="n">
+        <f aca="false">ROUND(Z16/U16 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC16" s="1" t="n">
+      <c r="AD16" s="1" t="n">
         <f aca="false">-V16*($V$47)*10</f>
         <v>-421.012289216306</v>
       </c>
-      <c r="AD16" s="1" t="n">
-        <f aca="false">AC16/U16/10</f>
+      <c r="AE16" s="1" t="n">
+        <f aca="false">AD16/U16/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG16" s="1" t="n">
+      <c r="AH16" s="1" t="n">
         <v>281.7</v>
       </c>
-      <c r="AL16" s="1" t="s">
+      <c r="AM16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AM16" s="1" t="n">
+      <c r="AN16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN16" s="1" t="n">
+      <c r="AO16" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="AO16" s="1" t="n">
-        <f aca="false">AM16+AN16/100</f>
+      <c r="AP16" s="1" t="n">
+        <f aca="false">AN16+AO16/100</f>
         <v>0.72</v>
       </c>
-      <c r="AP16" s="1" t="n">
-        <f aca="false">AO16*1000</f>
+      <c r="AQ16" s="1" t="n">
+        <f aca="false">AP16*1000</f>
         <v>720</v>
       </c>
-      <c r="AS16" s="22" t="s">
+      <c r="AT16" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="AT16" s="1" t="n">
+      <c r="AU16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AU16" s="1" t="n">
+      <c r="AV16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV16" s="22" t="n">
-        <f aca="false">AT16+AU16/10</f>
+      <c r="AW16" s="22" t="n">
+        <f aca="false">AU16+AV16/10</f>
         <v>2.9</v>
       </c>
-      <c r="AW16" s="22" t="n">
-        <f aca="false">1000*AV16</f>
+      <c r="AX16" s="22" t="n">
+        <f aca="false">1000*AW16</f>
         <v>2900</v>
       </c>
     </row>
@@ -4382,64 +6006,68 @@
         <v>21885.6</v>
       </c>
       <c r="X17" s="2" t="n">
+        <f aca="false">W17/U17</f>
+        <v>8.50030528018196</v>
+      </c>
+      <c r="Y17" s="2" t="n">
         <f aca="false">B17+F17</f>
         <v>4178</v>
       </c>
-      <c r="Y17" s="1" t="n">
-        <f aca="false">-X17+($V$45 + $V$46)*1000*V17/100</f>
+      <c r="Z17" s="1" t="n">
+        <f aca="false">-Y17+($V$45 + $V$46)*1000*V17/100</f>
         <v>3740.09910718664</v>
       </c>
-      <c r="Z17" s="1" t="n">
-        <f aca="false">Y17/U17/10</f>
+      <c r="AA17" s="1" t="n">
+        <f aca="false">Z17/U17/10</f>
         <v>0.145264393890149</v>
       </c>
-      <c r="AA17" s="1" t="n">
-        <f aca="false">ROUND(Y17/U17 *100/1000, 2)</f>
+      <c r="AB17" s="1" t="n">
+        <f aca="false">ROUND(Z17/U17 *100/1000, 2)</f>
         <v>0.15</v>
       </c>
-      <c r="AC17" s="1" t="n">
+      <c r="AD17" s="1" t="n">
         <f aca="false">-V17*($V$47)*10</f>
         <v>-4244.10296056332</v>
       </c>
-      <c r="AD17" s="1" t="n">
-        <f aca="false">AC17/U17/10</f>
+      <c r="AE17" s="1" t="n">
+        <f aca="false">AD17/U17/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG17" s="1" t="n">
+      <c r="AH17" s="1" t="n">
         <v>2991.1</v>
       </c>
-      <c r="AL17" s="1" t="s">
+      <c r="AM17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AM17" s="1" t="n">
+      <c r="AN17" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AN17" s="1" t="n">
+      <c r="AO17" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="AO17" s="1" t="n">
-        <f aca="false">AM17+AN17/100</f>
+      <c r="AP17" s="1" t="n">
+        <f aca="false">AN17+AO17/100</f>
         <v>5.38</v>
       </c>
-      <c r="AP17" s="1" t="n">
-        <f aca="false">AO17*1000</f>
+      <c r="AQ17" s="1" t="n">
+        <f aca="false">AP17*1000</f>
         <v>5380</v>
       </c>
-      <c r="AS17" s="22" t="s">
+      <c r="AT17" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="AT17" s="1" t="n">
+      <c r="AU17" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="AU17" s="1" t="n">
+      <c r="AV17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AV17" s="22" t="n">
-        <f aca="false">AT17+AU17/10</f>
+      <c r="AW17" s="22" t="n">
+        <f aca="false">AU17+AV17/10</f>
         <v>62</v>
       </c>
-      <c r="AW17" s="22" t="n">
-        <f aca="false">1000*AV17</f>
+      <c r="AX17" s="22" t="n">
+        <f aca="false">1000*AW17</f>
         <v>62000</v>
       </c>
     </row>
@@ -4523,61 +6151,65 @@
         <f aca="false">H18+F18+B18+D18+K18+P18</f>
         <v>22547.4</v>
       </c>
-      <c r="Y18" s="1" t="n">
-        <f aca="false">-X18+($V$45 + $V$46)*1000*V18/100</f>
+      <c r="X18" s="2" t="n">
+        <f aca="false">W18/U18</f>
+        <v>6.0456930128398</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <f aca="false">-Y18+($V$45 + $V$46)*1000*V18/100</f>
         <v>11469.5763767726</v>
       </c>
-      <c r="Z18" s="1" t="n">
-        <f aca="false">Y18/U18/10</f>
+      <c r="AA18" s="1" t="n">
+        <f aca="false">Z18/U18/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA18" s="1" t="n">
-        <f aca="false">ROUND(Y18/U18 *100/1000, 2)</f>
+      <c r="AB18" s="1" t="n">
+        <f aca="false">ROUND(Z18/U18 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC18" s="1" t="n">
+      <c r="AD18" s="1" t="n">
         <f aca="false">-V18*($V$47)*10</f>
         <v>-6147.69560195154</v>
       </c>
-      <c r="AD18" s="1" t="n">
-        <f aca="false">AC18/U18/10</f>
+      <c r="AE18" s="1" t="n">
+        <f aca="false">AD18/U18/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG18" s="1" t="n">
+      <c r="AH18" s="1" t="n">
         <v>4529.7</v>
       </c>
-      <c r="AL18" s="1" t="s">
+      <c r="AM18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AM18" s="1" t="n">
+      <c r="AN18" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AN18" s="1" t="n">
+      <c r="AO18" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AO18" s="1" t="n">
-        <f aca="false">AM18+AN18/100</f>
+      <c r="AP18" s="1" t="n">
+        <f aca="false">AN18+AO18/100</f>
         <v>6.4</v>
       </c>
-      <c r="AP18" s="1" t="n">
-        <f aca="false">AO18*1000</f>
+      <c r="AQ18" s="1" t="n">
+        <f aca="false">AP18*1000</f>
         <v>6400</v>
       </c>
-      <c r="AS18" s="22" t="s">
+      <c r="AT18" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="AT18" s="1" t="n">
+      <c r="AU18" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="AU18" s="1" t="n">
+      <c r="AV18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AV18" s="22" t="n">
-        <f aca="false">AT18+AU18/10</f>
+      <c r="AW18" s="22" t="n">
+        <f aca="false">AU18+AV18/10</f>
         <v>57.7</v>
       </c>
-      <c r="AW18" s="22" t="n">
-        <f aca="false">1000*AV18</f>
+      <c r="AX18" s="22" t="n">
+        <f aca="false">1000*AW18</f>
         <v>57700</v>
       </c>
     </row>
@@ -4661,65 +6293,69 @@
         <f aca="false">H19+F19+B19+D19+K19+P19</f>
         <v>1574.3</v>
       </c>
-      <c r="X19" s="27" t="n">
+      <c r="X19" s="2" t="n">
+        <f aca="false">W19/U19</f>
+        <v>8.70351225391279</v>
+      </c>
+      <c r="Y19" s="27" t="n">
         <f aca="false">F19</f>
         <v>22.7</v>
       </c>
-      <c r="Y19" s="1" t="n">
-        <f aca="false">-X19+($V$45 + $V$46)*1000*V19/100</f>
+      <c r="Z19" s="1" t="n">
+        <f aca="false">-Y19+($V$45 + $V$46)*1000*V19/100</f>
         <v>533.575521425941</v>
       </c>
-      <c r="Z19" s="1" t="n">
-        <f aca="false">Y19/U19/10</f>
+      <c r="AA19" s="1" t="n">
+        <f aca="false">Z19/U19/10</f>
         <v>0.294987047520713</v>
       </c>
-      <c r="AA19" s="1" t="n">
-        <f aca="false">ROUND(Y19/U19 *100/1000, 2)</f>
+      <c r="AB19" s="1" t="n">
+        <f aca="false">ROUND(Z19/U19 *100/1000, 2)</f>
         <v>0.29</v>
       </c>
-      <c r="AC19" s="1" t="n">
+      <c r="AD19" s="1" t="n">
         <f aca="false">-V19*($V$47)*10</f>
         <v>-298.163808688621</v>
       </c>
-      <c r="AD19" s="1" t="n">
-        <f aca="false">AC19/U19/10</f>
+      <c r="AE19" s="1" t="n">
+        <f aca="false">AD19/U19/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG19" s="1" t="n">
+      <c r="AH19" s="1" t="n">
         <v>248.4</v>
       </c>
-      <c r="AL19" s="1" t="s">
+      <c r="AM19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AM19" s="1" t="n">
+      <c r="AN19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AN19" s="1" t="n">
+      <c r="AO19" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="AO19" s="1" t="n">
-        <f aca="false">AM19+AN19/100</f>
+      <c r="AP19" s="1" t="n">
+        <f aca="false">AN19+AO19/100</f>
         <v>2.54</v>
       </c>
-      <c r="AP19" s="1" t="n">
-        <f aca="false">AO19*1000</f>
+      <c r="AQ19" s="1" t="n">
+        <f aca="false">AP19*1000</f>
         <v>2540</v>
       </c>
-      <c r="AS19" s="22" t="s">
+      <c r="AT19" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="AT19" s="1" t="n">
+      <c r="AU19" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AU19" s="1" t="n">
+      <c r="AV19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AV19" s="22" t="n">
-        <f aca="false">AT19+AU19/10</f>
+      <c r="AW19" s="22" t="n">
+        <f aca="false">AU19+AV19/10</f>
         <v>6.3</v>
       </c>
-      <c r="AW19" s="22" t="n">
-        <f aca="false">1000*AV19</f>
+      <c r="AX19" s="22" t="n">
+        <f aca="false">1000*AW19</f>
         <v>6300</v>
       </c>
     </row>
@@ -4803,61 +6439,65 @@
         <f aca="false">H20+F20+B20+D20+K20+P20</f>
         <v>868.8</v>
       </c>
-      <c r="Y20" s="1" t="n">
-        <f aca="false">-X20+($V$45 + $V$46)*1000*V20/100</f>
+      <c r="X20" s="2" t="n">
+        <f aca="false">W20/U20</f>
+        <v>5.83384813730493</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <f aca="false">-Y20+($V$45 + $V$46)*1000*V20/100</f>
         <v>457.996007058988</v>
       </c>
-      <c r="Z20" s="1" t="n">
-        <f aca="false">Y20/U20/10</f>
+      <c r="AA20" s="1" t="n">
+        <f aca="false">Z20/U20/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA20" s="1" t="n">
-        <f aca="false">ROUND(Y20/U20 *100/1000, 2)</f>
+      <c r="AB20" s="1" t="n">
+        <f aca="false">ROUND(Z20/U20 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC20" s="1" t="n">
+      <c r="AD20" s="1" t="n">
         <f aca="false">-V20*($V$47)*10</f>
         <v>-245.48596616087</v>
       </c>
-      <c r="AD20" s="1" t="n">
-        <f aca="false">AC20/U20/10</f>
+      <c r="AE20" s="1" t="n">
+        <f aca="false">AD20/U20/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG20" s="1" t="n">
+      <c r="AH20" s="1" t="n">
         <v>218.8</v>
       </c>
-      <c r="AL20" s="1" t="s">
+      <c r="AM20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AM20" s="1" t="n">
+      <c r="AN20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN20" s="1" t="n">
+      <c r="AO20" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="AO20" s="1" t="n">
-        <f aca="false">AM20+AN20/100</f>
+      <c r="AP20" s="1" t="n">
+        <f aca="false">AN20+AO20/100</f>
         <v>0.37</v>
       </c>
-      <c r="AP20" s="1" t="n">
-        <f aca="false">AO20*1000</f>
+      <c r="AQ20" s="1" t="n">
+        <f aca="false">AP20*1000</f>
         <v>370</v>
       </c>
-      <c r="AS20" s="22" t="s">
+      <c r="AT20" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="AT20" s="1" t="n">
+      <c r="AU20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AU20" s="1" t="n">
+      <c r="AV20" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV20" s="22" t="n">
-        <f aca="false">AT20+AU20/10</f>
+      <c r="AW20" s="22" t="n">
+        <f aca="false">AU20+AV20/10</f>
         <v>2.5</v>
       </c>
-      <c r="AW20" s="22" t="n">
-        <f aca="false">1000*AV20</f>
+      <c r="AX20" s="22" t="n">
+        <f aca="false">1000*AW20</f>
         <v>2500</v>
       </c>
     </row>
@@ -4941,68 +6581,72 @@
         <f aca="false">H21+F21+B21+D21+K21+P21</f>
         <v>1506</v>
       </c>
-      <c r="X21" s="27" t="n">
+      <c r="X21" s="2" t="n">
+        <f aca="false">W21/U21</f>
+        <v>4.65560573882237</v>
+      </c>
+      <c r="Y21" s="27" t="n">
         <f aca="false">F21</f>
         <v>241.4</v>
       </c>
-      <c r="Y21" s="1" t="n">
-        <f aca="false">-X21+($V$45 + $V$46)*1000*V21/100</f>
+      <c r="Z21" s="1" t="n">
+        <f aca="false">-Y21+($V$45 + $V$46)*1000*V21/100</f>
         <v>753.42290537085</v>
       </c>
-      <c r="Z21" s="1" t="n">
-        <f aca="false">Y21/U21/10</f>
+      <c r="AA21" s="1" t="n">
+        <f aca="false">Z21/U21/10</f>
         <v>0.232911022709479</v>
       </c>
-      <c r="AA21" s="1" t="n">
-        <f aca="false">ROUND(Y21/U21 *100/1000, 2)</f>
+      <c r="AB21" s="1" t="n">
+        <f aca="false">ROUND(Z21/U21 *100/1000, 2)</f>
         <v>0.23</v>
       </c>
-      <c r="AC21" s="1" t="n">
+      <c r="AD21" s="1" t="n">
         <f aca="false">-V21*($V$47)*10</f>
         <v>-533.225308343076</v>
       </c>
-      <c r="AD21" s="1" t="n">
-        <f aca="false">AC21/U21/10</f>
+      <c r="AE21" s="1" t="n">
+        <f aca="false">AD21/U21/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG21" s="1" t="n">
+      <c r="AH21" s="1" t="n">
         <v>602.4</v>
       </c>
-      <c r="AL21" s="1" t="s">
+      <c r="AM21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AM21" s="1" t="n">
+      <c r="AN21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN21" s="1" t="n">
+      <c r="AO21" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="AO21" s="1" t="n">
-        <f aca="false">AM21+AN21/100</f>
+      <c r="AP21" s="1" t="n">
+        <f aca="false">AN21+AO21/100</f>
         <v>0.94</v>
       </c>
-      <c r="AP21" s="1" t="n">
-        <f aca="false">AO21*1000</f>
+      <c r="AQ21" s="1" t="n">
+        <f aca="false">AP21*1000</f>
         <v>940</v>
       </c>
-      <c r="AS21" s="22" t="s">
+      <c r="AT21" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="AT21" s="1" t="n">
+      <c r="AU21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AU21" s="1" t="n">
+      <c r="AV21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AV21" s="22" t="n">
-        <f aca="false">AT21+AU21/10</f>
+      <c r="AW21" s="22" t="n">
+        <f aca="false">AU21+AV21/10</f>
         <v>3.8</v>
       </c>
-      <c r="AW21" s="22" t="n">
-        <f aca="false">1000*AV21</f>
+      <c r="AX21" s="22" t="n">
+        <f aca="false">1000*AW21</f>
         <v>3800</v>
       </c>
-      <c r="AX21" s="22" t="s">
+      <c r="AY21" s="22" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5087,64 +6731,68 @@
         <v>13410.2</v>
       </c>
       <c r="X22" s="2" t="n">
+        <f aca="false">W22/U22</f>
+        <v>7.39269451702885</v>
+      </c>
+      <c r="Y22" s="2" t="n">
         <f aca="false">B22+F22</f>
         <v>1008.5</v>
       </c>
-      <c r="Y22" s="1" t="n">
-        <f aca="false">-X22+($V$45 + $V$46)*1000*V22/100</f>
+      <c r="Z22" s="1" t="n">
+        <f aca="false">-Y22+($V$45 + $V$46)*1000*V22/100</f>
         <v>4570.15486345292</v>
       </c>
-      <c r="Z22" s="1" t="n">
-        <f aca="false">Y22/U22/10</f>
+      <c r="AA22" s="1" t="n">
+        <f aca="false">Z22/U22/10</f>
         <v>0.251940752569098</v>
       </c>
-      <c r="AA22" s="1" t="n">
-        <f aca="false">ROUND(Y22/U22 *100/1000, 2)</f>
+      <c r="AB22" s="1" t="n">
+        <f aca="false">ROUND(Z22/U22 *100/1000, 2)</f>
         <v>0.25</v>
       </c>
-      <c r="AC22" s="1" t="n">
+      <c r="AD22" s="1" t="n">
         <f aca="false">-V22*($V$47)*10</f>
         <v>-2990.1603025469</v>
       </c>
-      <c r="AD22" s="1" t="n">
-        <f aca="false">AC22/U22/10</f>
+      <c r="AE22" s="1" t="n">
+        <f aca="false">AD22/U22/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG22" s="1" t="n">
+      <c r="AH22" s="1" t="n">
         <v>2258</v>
       </c>
-      <c r="AL22" s="1" t="s">
+      <c r="AM22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AM22" s="1" t="n">
+      <c r="AN22" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AN22" s="1" t="n">
+      <c r="AO22" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AO22" s="1" t="n">
-        <f aca="false">AM22+AN22/100</f>
+      <c r="AP22" s="1" t="n">
+        <f aca="false">AN22+AO22/100</f>
         <v>7.11</v>
       </c>
-      <c r="AP22" s="1" t="n">
-        <f aca="false">AO22*1000</f>
+      <c r="AQ22" s="1" t="n">
+        <f aca="false">AP22*1000</f>
         <v>7110</v>
       </c>
-      <c r="AS22" s="22" t="s">
+      <c r="AT22" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="AT22" s="1" t="n">
+      <c r="AU22" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="AU22" s="1" t="n">
+      <c r="AV22" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV22" s="22" t="n">
-        <f aca="false">AT22+AU22/10</f>
+      <c r="AW22" s="22" t="n">
+        <f aca="false">AU22+AV22/10</f>
         <v>56.5</v>
       </c>
-      <c r="AW22" s="22" t="n">
-        <f aca="false">1000*AV22</f>
+      <c r="AX22" s="22" t="n">
+        <f aca="false">1000*AW22</f>
         <v>56500</v>
       </c>
     </row>
@@ -5228,61 +6876,65 @@
         <f aca="false">H23+F23+B23+D23+K23+P23</f>
         <v>165.6</v>
       </c>
-      <c r="Y23" s="1" t="n">
-        <f aca="false">-X23+($V$45 + $V$46)*1000*V23/100</f>
-        <v>101.717775062959</v>
+      <c r="X23" s="2" t="n">
+        <f aca="false">W23/U23</f>
+        <v>5.00680272108844</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <f aca="false">Y23/U23/10</f>
+        <f aca="false">-Y23+($V$45 + $V$46)*1000*V23/100</f>
+        <v>101.717775062958</v>
+      </c>
+      <c r="AA23" s="1" t="n">
+        <f aca="false">Z23/U23/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA23" s="1" t="n">
-        <f aca="false">ROUND(Y23/U23 *100/1000, 2)</f>
+      <c r="AB23" s="1" t="n">
+        <f aca="false">ROUND(Z23/U23 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC23" s="1" t="n">
+      <c r="AD23" s="1" t="n">
         <f aca="false">-V23*($V$47)*10</f>
         <v>-54.5207510594045</v>
       </c>
-      <c r="AD23" s="1" t="n">
-        <f aca="false">AC23/U23/10</f>
+      <c r="AE23" s="1" t="n">
+        <f aca="false">AD23/U23/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG23" s="1" t="n">
+      <c r="AH23" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="AL23" s="1" t="s">
+      <c r="AM23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AM23" s="1" t="n">
+      <c r="AN23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN23" s="1" t="n">
+      <c r="AO23" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="AO23" s="1" t="n">
-        <f aca="false">AM23+AN23/100</f>
+      <c r="AP23" s="1" t="n">
+        <f aca="false">AN23+AO23/100</f>
         <v>0.18</v>
       </c>
-      <c r="AP23" s="1" t="n">
-        <f aca="false">AO23*1000</f>
+      <c r="AQ23" s="1" t="n">
+        <f aca="false">AP23*1000</f>
         <v>180</v>
       </c>
-      <c r="AS23" s="22" t="s">
+      <c r="AT23" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="AT23" s="1" t="n">
+      <c r="AU23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" s="1" t="n">
+      <c r="AV23" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AV23" s="22" t="n">
-        <f aca="false">AT23+AU23/10</f>
+      <c r="AW23" s="22" t="n">
+        <f aca="false">AU23+AV23/10</f>
         <v>0.5</v>
       </c>
-      <c r="AW23" s="22" t="n">
-        <f aca="false">1000*AV23</f>
+      <c r="AX23" s="22" t="n">
+        <f aca="false">1000*AW23</f>
         <v>500</v>
       </c>
     </row>
@@ -5366,61 +7018,65 @@
         <f aca="false">H24+F24+B24+D24+K24+P24</f>
         <v>228.7</v>
       </c>
-      <c r="Y24" s="1" t="n">
-        <f aca="false">-X24+($V$45 + $V$46)*1000*V24/100</f>
+      <c r="X24" s="2" t="n">
+        <f aca="false">W24/U24</f>
+        <v>4.23393068720379</v>
+      </c>
+      <c r="Z24" s="1" t="n">
+        <f aca="false">-Y24+($V$45 + $V$46)*1000*V24/100</f>
         <v>166.119042715065</v>
       </c>
-      <c r="Z24" s="1" t="n">
-        <f aca="false">Y24/U24/10</f>
+      <c r="AA24" s="1" t="n">
+        <f aca="false">Z24/U24/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA24" s="1" t="n">
-        <f aca="false">ROUND(Y24/U24 *100/1000, 2)</f>
+      <c r="AB24" s="1" t="n">
+        <f aca="false">ROUND(Z24/U24 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC24" s="1" t="n">
+      <c r="AD24" s="1" t="n">
         <f aca="false">-V24*($V$47)*10</f>
         <v>-89.0398454792077</v>
       </c>
-      <c r="AD24" s="1" t="n">
-        <f aca="false">AC24/U24/10</f>
+      <c r="AE24" s="1" t="n">
+        <f aca="false">AD24/U24/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG24" s="1" t="n">
+      <c r="AH24" s="1" t="n">
         <v>84.3</v>
       </c>
-      <c r="AL24" s="1" t="s">
+      <c r="AM24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AM24" s="1" t="n">
+      <c r="AN24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN24" s="1" t="n">
+      <c r="AO24" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="AO24" s="1" t="n">
-        <f aca="false">AM24+AN24/100</f>
+      <c r="AP24" s="1" t="n">
+        <f aca="false">AN24+AO24/100</f>
         <v>0.14</v>
       </c>
-      <c r="AP24" s="1" t="n">
-        <f aca="false">AO24*1000</f>
+      <c r="AQ24" s="1" t="n">
+        <f aca="false">AP24*1000</f>
         <v>140</v>
       </c>
-      <c r="AS24" s="22" t="s">
+      <c r="AT24" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="AT24" s="1" t="n">
+      <c r="AU24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" s="1" t="n">
+      <c r="AV24" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AV24" s="22" t="n">
-        <f aca="false">AT24+AU24/10</f>
+      <c r="AW24" s="22" t="n">
+        <f aca="false">AU24+AV24/10</f>
         <v>0.8</v>
       </c>
-      <c r="AW24" s="22" t="n">
-        <f aca="false">1000*AV24</f>
+      <c r="AX24" s="22" t="n">
+        <f aca="false">1000*AW24</f>
         <v>800</v>
       </c>
     </row>
@@ -5502,61 +7158,65 @@
         <f aca="false">H25+F25+B25+D25+K25+P25</f>
         <v>498.5</v>
       </c>
-      <c r="Y25" s="1" t="n">
-        <f aca="false">-X25+($V$45 + $V$46)*1000*V25/100</f>
+      <c r="X25" s="2" t="n">
+        <f aca="false">W25/U25</f>
+        <v>9.8771547453933</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <f aca="false">-Y25+($V$45 + $V$46)*1000*V25/100</f>
         <v>155.21379009607</v>
       </c>
-      <c r="Z25" s="1" t="n">
-        <f aca="false">Y25/U25/10</f>
+      <c r="AA25" s="1" t="n">
+        <f aca="false">Z25/U25/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA25" s="1" t="n">
-        <f aca="false">ROUND(Y25/U25 *100/1000, 2)</f>
+      <c r="AB25" s="1" t="n">
+        <f aca="false">ROUND(Z25/U25 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC25" s="1" t="n">
+      <c r="AD25" s="1" t="n">
         <f aca="false">-V25*($V$47)*10</f>
         <v>-83.1946275424988</v>
       </c>
-      <c r="AD25" s="1" t="n">
-        <f aca="false">AC25/U25/10</f>
+      <c r="AE25" s="1" t="n">
+        <f aca="false">AD25/U25/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG25" s="1" t="n">
+      <c r="AH25" s="1" t="n">
         <v>89.5</v>
       </c>
-      <c r="AL25" s="1" t="s">
+      <c r="AM25" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AM25" s="1" t="n">
+      <c r="AN25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN25" s="1" t="n">
+      <c r="AO25" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="AO25" s="1" t="n">
-        <f aca="false">AM25+AN25/100</f>
+      <c r="AP25" s="1" t="n">
+        <f aca="false">AN25+AO25/100</f>
         <v>0.21</v>
       </c>
-      <c r="AP25" s="1" t="n">
-        <f aca="false">AO25*1000</f>
+      <c r="AQ25" s="1" t="n">
+        <f aca="false">AP25*1000</f>
         <v>210</v>
       </c>
-      <c r="AS25" s="22" t="s">
+      <c r="AT25" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="AT25" s="1" t="n">
+      <c r="AU25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AU25" s="1" t="n">
+      <c r="AV25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AV25" s="22" t="n">
-        <f aca="false">AT25+AU25/10</f>
+      <c r="AW25" s="22" t="n">
+        <f aca="false">AU25+AV25/10</f>
         <v>1.8</v>
       </c>
-      <c r="AW25" s="22" t="n">
-        <f aca="false">1000*AV25</f>
+      <c r="AX25" s="22" t="n">
+        <f aca="false">1000*AW25</f>
         <v>1800</v>
       </c>
     </row>
@@ -5638,61 +7298,65 @@
         <f aca="false">H26+F26+B26+D26+K26+P26</f>
         <v>184.3</v>
       </c>
-      <c r="Y26" s="1" t="n">
-        <f aca="false">-X26+($V$45 + $V$46)*1000*V26/100</f>
+      <c r="X26" s="2" t="n">
+        <f aca="false">W26/U26</f>
+        <v>13.4417620888338</v>
+      </c>
+      <c r="Z26" s="1" t="n">
+        <f aca="false">-Y26+($V$45 + $V$46)*1000*V26/100</f>
         <v>42.1663617199765</v>
       </c>
-      <c r="Z26" s="1" t="n">
-        <f aca="false">Y26/U26/10</f>
+      <c r="AA26" s="1" t="n">
+        <f aca="false">Z26/U26/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA26" s="1" t="n">
-        <f aca="false">ROUND(Y26/U26 *100/1000, 2)</f>
+      <c r="AB26" s="1" t="n">
+        <f aca="false">ROUND(Z26/U26 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC26" s="1" t="n">
+      <c r="AD26" s="1" t="n">
         <f aca="false">-V26*($V$47)*10</f>
         <v>-22.6011796757519</v>
       </c>
-      <c r="AD26" s="1" t="n">
-        <f aca="false">AC26/U26/10</f>
+      <c r="AE26" s="1" t="n">
+        <f aca="false">AD26/U26/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG26" s="1" t="n">
+      <c r="AH26" s="1" t="n">
         <v>24.6</v>
       </c>
-      <c r="AL26" s="1" t="s">
+      <c r="AM26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AM26" s="1" t="n">
+      <c r="AN26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN26" s="1" t="n">
+      <c r="AO26" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="AO26" s="1" t="n">
-        <f aca="false">AM26+AN26/100</f>
+      <c r="AP26" s="1" t="n">
+        <f aca="false">AN26+AO26/100</f>
         <v>0.27</v>
       </c>
-      <c r="AP26" s="1" t="n">
-        <f aca="false">AO26*1000</f>
+      <c r="AQ26" s="1" t="n">
+        <f aca="false">AP26*1000</f>
         <v>270</v>
       </c>
-      <c r="AS26" s="22" t="s">
+      <c r="AT26" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="AT26" s="1" t="n">
+      <c r="AU26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" s="1" t="n">
+      <c r="AV26" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV26" s="22" t="n">
-        <f aca="false">AT26+AU26/10</f>
+      <c r="AW26" s="22" t="n">
+        <f aca="false">AU26+AV26/10</f>
         <v>0.9</v>
       </c>
-      <c r="AW26" s="22" t="n">
-        <f aca="false">1000*AV26</f>
+      <c r="AX26" s="22" t="n">
+        <f aca="false">1000*AW26</f>
         <v>900</v>
       </c>
     </row>
@@ -5776,61 +7440,65 @@
         <f aca="false">H27+F27+B27+D27+K27+P27</f>
         <v>5690.6</v>
       </c>
-      <c r="Y27" s="1" t="n">
-        <f aca="false">-X27+($V$45 + $V$46)*1000*V27/100</f>
+      <c r="X27" s="2" t="n">
+        <f aca="false">W27/U27</f>
+        <v>6.7975383321627</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <f aca="false">-Y27+($V$45 + $V$46)*1000*V27/100</f>
         <v>2574.56222828741</v>
       </c>
-      <c r="Z27" s="1" t="n">
-        <f aca="false">Y27/U27/10</f>
+      <c r="AA27" s="1" t="n">
+        <f aca="false">Z27/U27/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA27" s="1" t="n">
-        <f aca="false">ROUND(Y27/U27 *100/1000, 2)</f>
+      <c r="AB27" s="1" t="n">
+        <f aca="false">ROUND(Z27/U27 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC27" s="1" t="n">
+      <c r="AD27" s="1" t="n">
         <f aca="false">-V27*($V$47)*10</f>
         <v>-1379.9659523473</v>
       </c>
-      <c r="AD27" s="1" t="n">
-        <f aca="false">AC27/U27/10</f>
+      <c r="AE27" s="1" t="n">
+        <f aca="false">AD27/U27/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG27" s="1" t="n">
+      <c r="AH27" s="1" t="n">
         <v>1170.6</v>
       </c>
-      <c r="AL27" s="1" t="s">
+      <c r="AM27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AM27" s="1" t="n">
+      <c r="AN27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN27" s="1" t="n">
+      <c r="AO27" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="AO27" s="1" t="n">
-        <f aca="false">AM27+AN27/100</f>
+      <c r="AP27" s="1" t="n">
+        <f aca="false">AN27+AO27/100</f>
         <v>1.98</v>
       </c>
-      <c r="AP27" s="1" t="n">
-        <f aca="false">AO27*1000</f>
+      <c r="AQ27" s="1" t="n">
+        <f aca="false">AP27*1000</f>
         <v>1980</v>
       </c>
-      <c r="AS27" s="22" t="s">
+      <c r="AT27" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="AT27" s="1" t="n">
+      <c r="AU27" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AU27" s="1" t="n">
+      <c r="AV27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AV27" s="22" t="n">
-        <f aca="false">AT27+AU27/10</f>
+      <c r="AW27" s="22" t="n">
+        <f aca="false">AU27+AV27/10</f>
         <v>11</v>
       </c>
-      <c r="AW27" s="22" t="n">
-        <f aca="false">1000*AV27</f>
+      <c r="AX27" s="22" t="n">
+        <f aca="false">1000*AW27</f>
         <v>11000</v>
       </c>
     </row>
@@ -5914,61 +7582,65 @@
         <f aca="false">H28+F28+B28+D28+K28+P28</f>
         <v>2834.3</v>
       </c>
-      <c r="Y28" s="1" t="n">
-        <f aca="false">-X28+($V$45 + $V$46)*1000*V28/100</f>
+      <c r="X28" s="2" t="n">
+        <f aca="false">W28/U28</f>
+        <v>5.17292041955719</v>
+      </c>
+      <c r="Z28" s="1" t="n">
+        <f aca="false">-Y28+($V$45 + $V$46)*1000*V28/100</f>
         <v>1685.02759947152</v>
       </c>
-      <c r="Z28" s="1" t="n">
-        <f aca="false">Y28/U28/10</f>
+      <c r="AA28" s="1" t="n">
+        <f aca="false">Z28/U28/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA28" s="1" t="n">
-        <f aca="false">ROUND(Y28/U28 *100/1000, 2)</f>
+      <c r="AB28" s="1" t="n">
+        <f aca="false">ROUND(Z28/U28 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC28" s="1" t="n">
+      <c r="AD28" s="1" t="n">
         <f aca="false">-V28*($V$47)*10</f>
         <v>-903.17518469265</v>
       </c>
-      <c r="AD28" s="1" t="n">
-        <f aca="false">AC28/U28/10</f>
+      <c r="AE28" s="1" t="n">
+        <f aca="false">AD28/U28/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG28" s="1" t="n">
+      <c r="AH28" s="1" t="n">
         <v>922.9</v>
       </c>
-      <c r="AL28" s="1" t="s">
+      <c r="AM28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AM28" s="1" t="n">
+      <c r="AN28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN28" s="1" t="n">
+      <c r="AO28" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="AO28" s="1" t="n">
-        <f aca="false">AM28+AN28/100</f>
+      <c r="AP28" s="1" t="n">
+        <f aca="false">AN28+AO28/100</f>
         <v>1.19</v>
       </c>
-      <c r="AP28" s="1" t="n">
-        <f aca="false">AO28*1000</f>
+      <c r="AQ28" s="1" t="n">
+        <f aca="false">AP28*1000</f>
         <v>1190</v>
       </c>
-      <c r="AS28" s="22" t="s">
+      <c r="AT28" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AT28" s="1" t="n">
+      <c r="AU28" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AU28" s="1" t="n">
+      <c r="AV28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AV28" s="22" t="n">
-        <f aca="false">AT28+AU28/10</f>
+      <c r="AW28" s="22" t="n">
+        <f aca="false">AU28+AV28/10</f>
         <v>8</v>
       </c>
-      <c r="AW28" s="22" t="n">
-        <f aca="false">1000*AV28</f>
+      <c r="AX28" s="22" t="n">
+        <f aca="false">1000*AW28</f>
         <v>8000</v>
       </c>
     </row>
@@ -6052,61 +7724,65 @@
         <f aca="false">H29+F29+B29+D29+K29+P29</f>
         <v>1776.8</v>
       </c>
-      <c r="Y29" s="1" t="n">
-        <f aca="false">-X29+($V$45 + $V$46)*1000*V29/100</f>
-        <v>651.593457035959</v>
+      <c r="X29" s="2" t="n">
+        <f aca="false">W29/U29</f>
+        <v>8.38607669616519</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <f aca="false">Y29/U29/10</f>
+        <f aca="false">-Y29+($V$45 + $V$46)*1000*V29/100</f>
+        <v>651.593457035958</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <f aca="false">Z29/U29/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA29" s="1" t="n">
-        <f aca="false">ROUND(Y29/U29 *100/1000, 2)</f>
+      <c r="AB29" s="1" t="n">
+        <f aca="false">ROUND(Z29/U29 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC29" s="1" t="n">
+      <c r="AD29" s="1" t="n">
         <f aca="false">-V29*($V$47)*10</f>
         <v>-349.25424431478</v>
       </c>
-      <c r="AD29" s="1" t="n">
-        <f aca="false">AC29/U29/10</f>
+      <c r="AE29" s="1" t="n">
+        <f aca="false">AD29/U29/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG29" s="1" t="n">
+      <c r="AH29" s="1" t="n">
         <v>306.8</v>
       </c>
-      <c r="AL29" s="1" t="s">
+      <c r="AM29" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AM29" s="1" t="n">
+      <c r="AN29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN29" s="1" t="n">
+      <c r="AO29" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="AO29" s="1" t="n">
-        <f aca="false">AM29+AN29/100</f>
+      <c r="AP29" s="1" t="n">
+        <f aca="false">AN29+AO29/100</f>
         <v>1.95</v>
       </c>
-      <c r="AP29" s="1" t="n">
-        <f aca="false">AO29*1000</f>
+      <c r="AQ29" s="1" t="n">
+        <f aca="false">AP29*1000</f>
         <v>1950</v>
       </c>
-      <c r="AS29" s="22" t="s">
+      <c r="AT29" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="AT29" s="1" t="n">
+      <c r="AU29" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AU29" s="1" t="n">
+      <c r="AV29" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AV29" s="22" t="n">
-        <f aca="false">AT29+AU29/10</f>
+      <c r="AW29" s="22" t="n">
+        <f aca="false">AU29+AV29/10</f>
         <v>6.4</v>
       </c>
-      <c r="AW29" s="22" t="n">
-        <f aca="false">1000*AV29</f>
+      <c r="AX29" s="22" t="n">
+        <f aca="false">1000*AW29</f>
         <v>6400</v>
       </c>
     </row>
@@ -6190,61 +7866,65 @@
         <f aca="false">H30+F30+B30+D30+K30+P30</f>
         <v>826.5</v>
       </c>
-      <c r="Y30" s="1" t="n">
-        <f aca="false">-X30+($V$45 + $V$46)*1000*V30/100</f>
-        <v>662.16349461393</v>
+      <c r="X30" s="2" t="n">
+        <f aca="false">W30/U30</f>
+        <v>3.83861559039905</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <f aca="false">Y30/U30/10</f>
+        <f aca="false">-Y30+($V$45 + $V$46)*1000*V30/100</f>
+        <v>662.163494613929</v>
+      </c>
+      <c r="AA30" s="1" t="n">
+        <f aca="false">Z30/U30/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA30" s="1" t="n">
-        <f aca="false">ROUND(Y30/U30 *100/1000, 2)</f>
+      <c r="AB30" s="1" t="n">
+        <f aca="false">ROUND(Z30/U30 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC30" s="1" t="n">
+      <c r="AD30" s="1" t="n">
         <f aca="false">-V30*($V$47)*10</f>
         <v>-354.919786911641</v>
       </c>
-      <c r="AD30" s="1" t="n">
-        <f aca="false">AC30/U30/10</f>
+      <c r="AE30" s="1" t="n">
+        <f aca="false">AD30/U30/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG30" s="1" t="n">
+      <c r="AH30" s="1" t="n">
         <v>380.1</v>
       </c>
-      <c r="AL30" s="1" t="s">
+      <c r="AM30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AM30" s="1" t="n">
+      <c r="AN30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN30" s="1" t="n">
+      <c r="AO30" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="AO30" s="1" t="n">
-        <f aca="false">AM30+AN30/100</f>
+      <c r="AP30" s="1" t="n">
+        <f aca="false">AN30+AO30/100</f>
         <v>0.62</v>
       </c>
-      <c r="AP30" s="1" t="n">
-        <f aca="false">AO30*1000</f>
+      <c r="AQ30" s="1" t="n">
+        <f aca="false">AP30*1000</f>
         <v>620</v>
       </c>
-      <c r="AS30" s="22" t="s">
+      <c r="AT30" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="AT30" s="1" t="n">
+      <c r="AU30" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AU30" s="1" t="n">
+      <c r="AV30" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AV30" s="22" t="n">
-        <f aca="false">AT30+AU30/10</f>
+      <c r="AW30" s="22" t="n">
+        <f aca="false">AU30+AV30/10</f>
         <v>3.2</v>
       </c>
-      <c r="AW30" s="22" t="n">
-        <f aca="false">1000*AV30</f>
+      <c r="AX30" s="22" t="n">
+        <f aca="false">1000*AW30</f>
         <v>3200</v>
       </c>
     </row>
@@ -6328,62 +8008,66 @@
         <f aca="false">H31+F31+B31+D31+K31+P31</f>
         <v>376.8</v>
       </c>
-      <c r="Y31" s="1" t="n">
-        <f aca="false">-X31+($V$45 + $V$46)*1000*V31/100</f>
+      <c r="X31" s="2" t="n">
+        <f aca="false">W31/U31</f>
+        <v>3.87263869760941</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <f aca="false">-Y31+($V$45 + $V$46)*1000*V31/100</f>
         <v>299.227092307656</v>
       </c>
-      <c r="Z31" s="1" t="n">
-        <f aca="false">Y31/U31/10</f>
+      <c r="AA31" s="1" t="n">
+        <f aca="false">Z31/U31/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA31" s="1" t="n">
-        <f aca="false">ROUND(Y31/U31 *100/1000, 2)</f>
+      <c r="AB31" s="1" t="n">
+        <f aca="false">ROUND(Z31/U31 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC31" s="1" t="n">
+      <c r="AD31" s="1" t="n">
         <f aca="false">-V31*($V$47)*10</f>
         <v>-160.385790977413</v>
       </c>
-      <c r="AD31" s="1" t="n">
-        <f aca="false">AC31/U31/10</f>
+      <c r="AE31" s="1" t="n">
+        <f aca="false">AD31/U31/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AE31" s="31"/>
-      <c r="AG31" s="1" t="n">
+      <c r="AF31" s="31"/>
+      <c r="AH31" s="1" t="n">
         <v>136.8</v>
       </c>
-      <c r="AL31" s="1" t="s">
+      <c r="AM31" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AM31" s="1" t="n">
+      <c r="AN31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN31" s="1" t="n">
+      <c r="AO31" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="AO31" s="1" t="n">
-        <f aca="false">AM31+AN31/100</f>
+      <c r="AP31" s="1" t="n">
+        <f aca="false">AN31+AO31/100</f>
         <v>0.4</v>
       </c>
-      <c r="AP31" s="1" t="n">
-        <f aca="false">AO31*1000</f>
+      <c r="AQ31" s="1" t="n">
+        <f aca="false">AP31*1000</f>
         <v>400</v>
       </c>
-      <c r="AS31" s="22" t="s">
+      <c r="AT31" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="AT31" s="1" t="n">
+      <c r="AU31" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AU31" s="1" t="n">
+      <c r="AV31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AV31" s="22" t="n">
-        <f aca="false">AT31+AU31/10</f>
+      <c r="AW31" s="22" t="n">
+        <f aca="false">AU31+AV31/10</f>
         <v>1.3</v>
       </c>
-      <c r="AW31" s="22" t="n">
-        <f aca="false">1000*AV31</f>
+      <c r="AX31" s="22" t="n">
+        <f aca="false">1000*AW31</f>
         <v>1300</v>
       </c>
     </row>
@@ -6467,61 +8151,65 @@
         <f aca="false">H32+F32+B32+D32+K32+P32</f>
         <v>323</v>
       </c>
-      <c r="Y32" s="1" t="n">
-        <f aca="false">-X32+($V$45 + $V$46)*1000*V32/100</f>
+      <c r="X32" s="2" t="n">
+        <f aca="false">W32/U32</f>
+        <v>6.27537836840163</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <f aca="false">-Y32+($V$45 + $V$46)*1000*V32/100</f>
         <v>158.292232812261</v>
       </c>
-      <c r="Z32" s="1" t="n">
-        <f aca="false">Y32/U32/10</f>
+      <c r="AA32" s="1" t="n">
+        <f aca="false">Z32/U32/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA32" s="1" t="n">
-        <f aca="false">ROUND(Y32/U32 *100/1000, 2)</f>
+      <c r="AB32" s="1" t="n">
+        <f aca="false">ROUND(Z32/U32 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC32" s="1" t="n">
+      <c r="AD32" s="1" t="n">
         <f aca="false">-V32*($V$47)*10</f>
         <v>-84.8446735533971</v>
       </c>
-      <c r="AD32" s="1" t="n">
-        <f aca="false">AC32/U32/10</f>
+      <c r="AE32" s="1" t="n">
+        <f aca="false">AD32/U32/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG32" s="1" t="n">
+      <c r="AH32" s="1" t="n">
         <v>70.5</v>
       </c>
-      <c r="AL32" s="1" t="s">
+      <c r="AM32" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AM32" s="1" t="n">
+      <c r="AN32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AN32" s="1" t="n">
+      <c r="AO32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AO32" s="1" t="n">
-        <f aca="false">AM32+AN32/100</f>
+      <c r="AP32" s="1" t="n">
+        <f aca="false">AN32+AO32/100</f>
         <v>0.3</v>
       </c>
-      <c r="AP32" s="1" t="n">
-        <f aca="false">AO32*1000</f>
+      <c r="AQ32" s="1" t="n">
+        <f aca="false">AP32*1000</f>
         <v>300</v>
       </c>
-      <c r="AS32" s="22" t="s">
+      <c r="AT32" s="22" t="s">
         <v>100</v>
-      </c>
-      <c r="AT32" s="1" t="n">
-        <v>1</v>
       </c>
       <c r="AU32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV32" s="22" t="n">
-        <f aca="false">AT32+AU32/10</f>
+      <c r="AV32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW32" s="22" t="n">
+        <f aca="false">AU32+AV32/10</f>
         <v>1.1</v>
       </c>
-      <c r="AW32" s="22" t="n">
-        <f aca="false">1000*AV32</f>
+      <c r="AX32" s="22" t="n">
+        <f aca="false">1000*AW32</f>
         <v>1100</v>
       </c>
     </row>
@@ -6606,64 +8294,68 @@
         <v>9693.1</v>
       </c>
       <c r="X33" s="2" t="n">
+        <f aca="false">W33/U33</f>
+        <v>7.98986131431986</v>
+      </c>
+      <c r="Y33" s="2" t="n">
         <f aca="false">B33+F33</f>
         <v>923.6</v>
       </c>
-      <c r="Y33" s="1" t="n">
-        <f aca="false">-X33+($V$45 + $V$46)*1000*V33/100</f>
-        <v>2807.35878343174</v>
-      </c>
       <c r="Z33" s="1" t="n">
-        <f aca="false">Y33/U33/10</f>
+        <f aca="false">-Y33+($V$45 + $V$46)*1000*V33/100</f>
+        <v>2807.35878343173</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <f aca="false">Z33/U33/10</f>
         <v>0.231405921110453</v>
       </c>
-      <c r="AA33" s="1" t="n">
-        <f aca="false">ROUND(Y33/U33 *100/1000, 2)</f>
+      <c r="AB33" s="1" t="n">
+        <f aca="false">ROUND(Z33/U33 *100/1000, 2)</f>
         <v>0.23</v>
       </c>
-      <c r="AC33" s="1" t="n">
+      <c r="AD33" s="1" t="n">
         <f aca="false">-V33*($V$47)*10</f>
         <v>-1999.79477449715</v>
       </c>
-      <c r="AD33" s="1" t="n">
-        <f aca="false">AC33/U33/10</f>
+      <c r="AE33" s="1" t="n">
+        <f aca="false">AD33/U33/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG33" s="1" t="n">
+      <c r="AH33" s="1" t="n">
         <v>1687.2</v>
       </c>
-      <c r="AL33" s="1" t="s">
+      <c r="AM33" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AM33" s="1" t="n">
+      <c r="AN33" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AN33" s="1" t="n">
+      <c r="AO33" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="AO33" s="1" t="n">
-        <f aca="false">AM33+AN33/100</f>
+      <c r="AP33" s="1" t="n">
+        <f aca="false">AN33+AO33/100</f>
         <v>9.33</v>
       </c>
-      <c r="AP33" s="1" t="n">
-        <f aca="false">AO33*1000</f>
+      <c r="AQ33" s="1" t="n">
+        <f aca="false">AP33*1000</f>
         <v>9330</v>
       </c>
-      <c r="AS33" s="22" t="s">
+      <c r="AT33" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="AT33" s="1" t="n">
+      <c r="AU33" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="AU33" s="1" t="n">
+      <c r="AV33" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AV33" s="22" t="n">
-        <f aca="false">AT33+AU33/10</f>
+      <c r="AW33" s="22" t="n">
+        <f aca="false">AU33+AV33/10</f>
         <v>30.9</v>
       </c>
-      <c r="AW33" s="22" t="n">
-        <f aca="false">1000*AV33</f>
+      <c r="AX33" s="22" t="n">
+        <f aca="false">1000*AW33</f>
         <v>30900</v>
       </c>
     </row>
@@ -6747,61 +8439,65 @@
         <f aca="false">H34+F34+B34+D34+K34+P34</f>
         <v>2909.9</v>
       </c>
-      <c r="Y34" s="1" t="n">
-        <f aca="false">-X34+($V$45 + $V$46)*1000*V34/100</f>
+      <c r="X34" s="2" t="n">
+        <f aca="false">W34/U34</f>
+        <v>5.26490054243004</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <f aca="false">-Y34+($V$45 + $V$46)*1000*V34/100</f>
         <v>1699.74938297043</v>
       </c>
-      <c r="Z34" s="1" t="n">
-        <f aca="false">Y34/U34/10</f>
+      <c r="AA34" s="1" t="n">
+        <f aca="false">Z34/U34/10</f>
         <v>0.307536734884228</v>
       </c>
-      <c r="AA34" s="1" t="n">
-        <f aca="false">ROUND(Y34/U34 *100/1000, 2)</f>
+      <c r="AB34" s="1" t="n">
+        <f aca="false">ROUND(Z34/U34 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AC34" s="1" t="n">
+      <c r="AD34" s="1" t="n">
         <f aca="false">-V34*($V$47)*10</f>
         <v>-911.066064067446</v>
       </c>
-      <c r="AD34" s="1" t="n">
-        <f aca="false">AC34/U34/10</f>
+      <c r="AE34" s="1" t="n">
+        <f aca="false">AD34/U34/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG34" s="1" t="n">
+      <c r="AH34" s="1" t="n">
         <v>601.2</v>
       </c>
-      <c r="AL34" s="1" t="s">
+      <c r="AM34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AM34" s="1" t="n">
+      <c r="AN34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN34" s="1" t="n">
+      <c r="AO34" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="AO34" s="1" t="n">
-        <f aca="false">AM34+AN34/100</f>
+      <c r="AP34" s="1" t="n">
+        <f aca="false">AN34+AO34/100</f>
         <v>1.16</v>
       </c>
-      <c r="AP34" s="1" t="n">
-        <f aca="false">AO34*1000</f>
+      <c r="AQ34" s="1" t="n">
+        <f aca="false">AP34*1000</f>
         <v>1160</v>
       </c>
-      <c r="AS34" s="22" t="s">
+      <c r="AT34" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="AT34" s="1" t="n">
+      <c r="AU34" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AU34" s="1" t="n">
+      <c r="AV34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AV34" s="22" t="n">
-        <f aca="false">AT34+AU34/10</f>
+      <c r="AW34" s="22" t="n">
+        <f aca="false">AU34+AV34/10</f>
         <v>7.1</v>
       </c>
-      <c r="AW34" s="22" t="n">
-        <f aca="false">1000*AV34</f>
+      <c r="AX34" s="22" t="n">
+        <f aca="false">1000*AW34</f>
         <v>7100</v>
       </c>
     </row>
@@ -6844,31 +8540,34 @@
         <v>90680.2</v>
       </c>
       <c r="X35" s="2"/>
-      <c r="Y35" s="1" t="n">
-        <f aca="false">SUM(Y8:Y34)</f>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="1" t="n">
+        <f aca="false">SUM(Z8:Z34)</f>
         <v>38340.8</v>
       </c>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="36" t="e">
-        <f aca="false">ROUND(Y35/U35 *100/1000, 2)</f>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="36" t="e">
+        <f aca="false">ROUND(Z35/U35 *100/1000, 2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC35" s="1" t="n">
+      <c r="AD35" s="1" t="n">
         <f aca="false">-V35*($V$47)*10</f>
         <v>-24000</v>
       </c>
-      <c r="AD35" s="1"/>
-      <c r="AG35" s="36" t="n">
+      <c r="AE35" s="1"/>
+      <c r="AH35" s="36" t="n">
         <v>18796</v>
       </c>
-      <c r="AP35" s="36" t="n">
-        <f aca="false">SUM(AP8:AP34)</f>
+      <c r="AQ35" s="36" t="n">
+        <f aca="false">SUM(AQ8:AQ34)</f>
         <v>47600</v>
       </c>
-      <c r="AV35" s="36" t="n">
-        <f aca="false">SUM(AV8:AV34)</f>
+      <c r="AW35" s="36" t="n">
+        <f aca="false">SUM(AW8:AW34)</f>
         <v>299.1</v>
       </c>
+      <c r="XFC35" s="0"/>
+      <c r="XFD35" s="0"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="n">
@@ -6958,8 +8657,9 @@
       </c>
       <c r="W40" s="44"/>
       <c r="X40" s="44"/>
-      <c r="Y40" s="22"/>
+      <c r="Y40" s="44"/>
       <c r="Z40" s="22"/>
+      <c r="AA40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U41" s="42" t="s">
@@ -6971,16 +8671,18 @@
       </c>
       <c r="W41" s="44"/>
       <c r="X41" s="44"/>
-      <c r="Y41" s="22"/>
+      <c r="Y41" s="44"/>
       <c r="Z41" s="22"/>
+      <c r="AA41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U42" s="42"/>
       <c r="V42" s="42"/>
       <c r="W42" s="44"/>
       <c r="X42" s="44"/>
-      <c r="Y42" s="22"/>
+      <c r="Y42" s="44"/>
       <c r="Z42" s="22"/>
+      <c r="AA42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U43" s="45" t="s">
@@ -6991,8 +8693,9 @@
       </c>
       <c r="W43" s="44"/>
       <c r="X43" s="44"/>
-      <c r="Y43" s="22"/>
+      <c r="Y43" s="44"/>
       <c r="Z43" s="22"/>
+      <c r="AA43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S44" s="46" t="s">
@@ -7007,8 +8710,9 @@
       </c>
       <c r="W44" s="44"/>
       <c r="X44" s="44"/>
-      <c r="Y44" s="22"/>
+      <c r="Y44" s="44"/>
       <c r="Z44" s="22"/>
+      <c r="AA44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U45" s="45" t="s">
@@ -7020,8 +8724,9 @@
       </c>
       <c r="W45" s="44"/>
       <c r="X45" s="44"/>
-      <c r="Y45" s="22"/>
+      <c r="Y45" s="44"/>
       <c r="Z45" s="22"/>
+      <c r="AA45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U46" s="45" t="s">
@@ -7032,8 +8737,9 @@
       </c>
       <c r="W46" s="44"/>
       <c r="X46" s="44"/>
-      <c r="Y46" s="22"/>
+      <c r="Y46" s="44"/>
       <c r="Z46" s="22"/>
+      <c r="AA46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U47" s="45" t="s">
@@ -7044,8 +8750,9 @@
       </c>
       <c r="W47" s="44"/>
       <c r="X47" s="44"/>
-      <c r="Y47" s="22"/>
+      <c r="Y47" s="44"/>
       <c r="Z47" s="22"/>
+      <c r="AA47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="22"/>
@@ -7065,8 +8772,9 @@
       </c>
       <c r="W48" s="44"/>
       <c r="X48" s="44"/>
-      <c r="Y48" s="22"/>
+      <c r="Y48" s="44"/>
       <c r="Z48" s="22"/>
+      <c r="AA48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="22"/>
@@ -7086,8 +8794,9 @@
       </c>
       <c r="W49" s="44"/>
       <c r="X49" s="44"/>
-      <c r="Y49" s="22"/>
+      <c r="Y49" s="44"/>
       <c r="Z49" s="22"/>
+      <c r="AA49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="22"/>
@@ -7107,21 +8816,22 @@
       </c>
       <c r="W50" s="44"/>
       <c r="X50" s="44"/>
-      <c r="Y50" s="22"/>
+      <c r="Y50" s="44"/>
       <c r="Z50" s="22"/>
+      <c r="AA50" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="47"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
-      <c r="Y53" s="1" t="s">
+      <c r="Z53" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="AC53" s="1" t="s">
+      <c r="AD53" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="AD53" s="1"/>
+      <c r="AE53" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="47"/>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -1923,7 +1923,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$K$1</c:f>
+              <c:f>Combined_2!$L$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2057,90 +2057,90 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Combined_2!$K$8:$K$34</c:f>
+              <c:f>Combined_2!$L$8:$L$34</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>791.717119228186</c:v>
+                  <c:v>1900</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>368.865393719426</c:v>
+                  <c:v>1100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>876.941594543475</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1104.87788191831</c:v>
+                  <c:v>380</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2241.92814915871</c:v>
+                  <c:v>290</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>328.685740399784</c:v>
+                  <c:v>440</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>551.431540391428</c:v>
+                  <c:v>1130</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4951.61655717014</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>479.235103188245</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>355.228059055014</c:v>
+                  <c:v>5380</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>291.728270131798</c:v>
+                  <c:v>6400</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2387.20484738585</c:v>
+                  <c:v>2540</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>422.363084526336</c:v>
+                  <c:v>370</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>494.001193269466</c:v>
+                  <c:v>940</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>666.324876790262</c:v>
+                  <c:v>7110</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>925.170068027211</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>440.61018957346</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>707.350901525659</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3347.67704762599</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>402.075598813125</c:v>
+                  <c:v>1980</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>369.220548592746</c:v>
+                  <c:v>1190</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1564.6017699115</c:v>
+                  <c:v>1950</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>489.522181764138</c:v>
+                  <c:v>620</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>698.883841394479</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>990.849216063414</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1307.39588270447</c:v>
+                  <c:v>9330</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>356.79521185168</c:v>
+                  <c:v>1160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2376,11 +2376,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="58971359"/>
-        <c:axId val="74152583"/>
+        <c:axId val="90354791"/>
+        <c:axId val="91786331"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58971359"/>
+        <c:axId val="90354791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2408,7 +2408,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74152583"/>
+        <c:crossAx val="91786331"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2416,7 +2416,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74152583"/>
+        <c:axId val="91786331"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2453,7 +2453,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58971359"/>
+        <c:crossAx val="90354791"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">revenues</t>
   </si>
   <si>
-    <t xml:space="preserve">sources</t>
+    <t xml:space="preserve">source</t>
   </si>
   <si>
     <t xml:space="preserve">Share s</t>
@@ -686,7 +686,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -740,10 +740,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1923,7 +1919,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Combined_2!$L$1</c:f>
+              <c:f>Combined_2!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2057,90 +2053,90 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Combined_2!$L$8:$L$34</c:f>
+              <c:f>Combined_2!$K$8:$K$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>1900</c:v>
+                  <c:v>791.717119228186</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1100</c:v>
+                  <c:v>368.865393719426</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>270</c:v>
+                  <c:v>876.941594543475</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>380</c:v>
+                  <c:v>1104.87788191831</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>290</c:v>
+                  <c:v>2241.92814915871</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>440</c:v>
+                  <c:v>328.685740399784</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1130</c:v>
+                  <c:v>551.431540391428</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>900</c:v>
+                  <c:v>4951.61655717014</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>720</c:v>
+                  <c:v>479.235103188245</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5380</c:v>
+                  <c:v>355.228059055014</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6400</c:v>
+                  <c:v>291.728270131798</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2540</c:v>
+                  <c:v>2387.20484738585</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>370</c:v>
+                  <c:v>422.363084526336</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>940</c:v>
+                  <c:v>494.001193269466</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7110</c:v>
+                  <c:v>666.324876790262</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>180</c:v>
+                  <c:v>925.170068027211</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>140</c:v>
+                  <c:v>440.61018957346</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>210</c:v>
+                  <c:v>707.350901525659</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>270</c:v>
+                  <c:v>3347.67704762599</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1980</c:v>
+                  <c:v>402.075598813125</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1190</c:v>
+                  <c:v>369.220548592746</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1950</c:v>
+                  <c:v>1564.6017699115</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>620</c:v>
+                  <c:v>489.522181764138</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>400</c:v>
+                  <c:v>698.883841394479</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>300</c:v>
+                  <c:v>990.849216063414</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9330</c:v>
+                  <c:v>1307.39588270447</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1160</c:v>
+                  <c:v>356.79521185168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2376,11 +2372,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="90354791"/>
-        <c:axId val="91786331"/>
+        <c:axId val="31480390"/>
+        <c:axId val="55153828"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="90354791"/>
+        <c:axId val="31480390"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2408,7 +2404,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91786331"/>
+        <c:crossAx val="55153828"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2416,7 +2412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91786331"/>
+        <c:axId val="55153828"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2453,7 +2449,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90354791"/>
+        <c:crossAx val="31480390"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2726,7 +2722,7 @@
       <c r="XFC1" s="0"/>
       <c r="XFD1" s="0"/>
     </row>
-    <row r="2" s="15" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="13" t="s">
         <v>10</v>
@@ -2755,22 +2751,22 @@
       <c r="J2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>11</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>10</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="14" t="s">
         <v>12</v>
       </c>
       <c r="R2" s="11"/>
@@ -2778,16 +2774,16 @@
       <c r="T2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="15" t="s">
+      <c r="U2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="Y2" s="15" t="s">
+      <c r="Y2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AB2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="14" t="s">
         <v>17</v>
       </c>
       <c r="XEX2" s="0"/>
@@ -2798,7 +2794,7 @@
       <c r="XFC2" s="0"/>
       <c r="XFD2" s="0"/>
     </row>
-    <row r="3" s="15" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="14" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="13" t="s">
         <v>18</v>
@@ -2827,18 +2823,16 @@
       <c r="J3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="13" t="s">
+      <c r="K3" s="13" t="s">
         <v>19</v>
       </c>
       <c r="M3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="13" t="s">
+      <c r="N3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="R3" s="11" t="s">
@@ -2846,15 +2840,15 @@
       </c>
       <c r="S3" s="11"/>
       <c r="T3" s="11"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="15" t="s">
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="15" t="s">
+      <c r="Y3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AC3" s="15" t="s">
+      <c r="AC3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="XEX3" s="0"/>
@@ -2865,76 +2859,76 @@
       <c r="XFC3" s="0"/>
       <c r="XFD3" s="0"/>
     </row>
-    <row r="4" s="20" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18" t="s">
+      <c r="I4" s="17"/>
+      <c r="J4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="19"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18" t="s">
+      <c r="K4" s="18"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="17"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="AC4" s="18"/>
-      <c r="XDN4" s="18"/>
-      <c r="XDO4" s="18"/>
-      <c r="XDP4" s="18"/>
-      <c r="XDQ4" s="18"/>
-      <c r="XDR4" s="18"/>
-      <c r="XDS4" s="18"/>
-      <c r="XDT4" s="18"/>
-      <c r="XDU4" s="18"/>
-      <c r="XDV4" s="18"/>
-      <c r="XDW4" s="18"/>
-      <c r="XDX4" s="18"/>
-      <c r="XDY4" s="18"/>
-      <c r="XDZ4" s="18"/>
-      <c r="XEA4" s="18"/>
-      <c r="XEB4" s="18"/>
-      <c r="XEC4" s="18"/>
-      <c r="XED4" s="18"/>
-      <c r="XEE4" s="18"/>
-      <c r="XEF4" s="18"/>
-      <c r="XEG4" s="18"/>
-      <c r="XEH4" s="18"/>
-      <c r="XEI4" s="18"/>
-      <c r="XEJ4" s="18"/>
-      <c r="XEK4" s="18"/>
-      <c r="XEL4" s="18"/>
-      <c r="XEM4" s="18"/>
-      <c r="XEN4" s="18"/>
-      <c r="XEO4" s="18"/>
-      <c r="XEP4" s="18"/>
-      <c r="XEQ4" s="18"/>
-      <c r="XER4" s="18"/>
-      <c r="XES4" s="18"/>
-      <c r="XET4" s="18"/>
-      <c r="XEU4" s="18"/>
-      <c r="XEV4" s="18"/>
-      <c r="XEW4" s="18"/>
+      <c r="AC4" s="17"/>
+      <c r="XDN4" s="17"/>
+      <c r="XDO4" s="17"/>
+      <c r="XDP4" s="17"/>
+      <c r="XDQ4" s="17"/>
+      <c r="XDR4" s="17"/>
+      <c r="XDS4" s="17"/>
+      <c r="XDT4" s="17"/>
+      <c r="XDU4" s="17"/>
+      <c r="XDV4" s="17"/>
+      <c r="XDW4" s="17"/>
+      <c r="XDX4" s="17"/>
+      <c r="XDY4" s="17"/>
+      <c r="XDZ4" s="17"/>
+      <c r="XEA4" s="17"/>
+      <c r="XEB4" s="17"/>
+      <c r="XEC4" s="17"/>
+      <c r="XED4" s="17"/>
+      <c r="XEE4" s="17"/>
+      <c r="XEF4" s="17"/>
+      <c r="XEG4" s="17"/>
+      <c r="XEH4" s="17"/>
+      <c r="XEI4" s="17"/>
+      <c r="XEJ4" s="17"/>
+      <c r="XEK4" s="17"/>
+      <c r="XEL4" s="17"/>
+      <c r="XEM4" s="17"/>
+      <c r="XEN4" s="17"/>
+      <c r="XEO4" s="17"/>
+      <c r="XEP4" s="17"/>
+      <c r="XEQ4" s="17"/>
+      <c r="XER4" s="17"/>
+      <c r="XES4" s="17"/>
+      <c r="XET4" s="17"/>
+      <c r="XEU4" s="17"/>
+      <c r="XEV4" s="17"/>
+      <c r="XEW4" s="17"/>
       <c r="XEX4" s="0"/>
       <c r="XEY4" s="0"/>
       <c r="XEZ4" s="0"/>
@@ -2943,76 +2937,76 @@
       <c r="XFC4" s="0"/>
       <c r="XFD4" s="0"/>
     </row>
-    <row r="5" s="20" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+    <row r="5" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18" t="s">
+      <c r="H5" s="17"/>
+      <c r="I5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="18" t="s">
+      <c r="J5" s="17"/>
+      <c r="K5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18" t="s">
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="18"/>
+      <c r="O5" s="17"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="AC5" s="18"/>
-      <c r="XDN5" s="18"/>
-      <c r="XDO5" s="18"/>
-      <c r="XDP5" s="18"/>
-      <c r="XDQ5" s="18"/>
-      <c r="XDR5" s="18"/>
-      <c r="XDS5" s="18"/>
-      <c r="XDT5" s="18"/>
-      <c r="XDU5" s="18"/>
-      <c r="XDV5" s="18"/>
-      <c r="XDW5" s="18"/>
-      <c r="XDX5" s="18"/>
-      <c r="XDY5" s="18"/>
-      <c r="XDZ5" s="18"/>
-      <c r="XEA5" s="18"/>
-      <c r="XEB5" s="18"/>
-      <c r="XEC5" s="18"/>
-      <c r="XED5" s="18"/>
-      <c r="XEE5" s="18"/>
-      <c r="XEF5" s="18"/>
-      <c r="XEG5" s="18"/>
-      <c r="XEH5" s="18"/>
-      <c r="XEI5" s="18"/>
-      <c r="XEJ5" s="18"/>
-      <c r="XEK5" s="18"/>
-      <c r="XEL5" s="18"/>
-      <c r="XEM5" s="18"/>
-      <c r="XEN5" s="18"/>
-      <c r="XEO5" s="18"/>
-      <c r="XEP5" s="18"/>
-      <c r="XEQ5" s="18"/>
-      <c r="XER5" s="18"/>
-      <c r="XES5" s="18"/>
-      <c r="XET5" s="18"/>
-      <c r="XEU5" s="18"/>
-      <c r="XEV5" s="18"/>
-      <c r="XEW5" s="18"/>
+      <c r="AC5" s="17"/>
+      <c r="XDN5" s="17"/>
+      <c r="XDO5" s="17"/>
+      <c r="XDP5" s="17"/>
+      <c r="XDQ5" s="17"/>
+      <c r="XDR5" s="17"/>
+      <c r="XDS5" s="17"/>
+      <c r="XDT5" s="17"/>
+      <c r="XDU5" s="17"/>
+      <c r="XDV5" s="17"/>
+      <c r="XDW5" s="17"/>
+      <c r="XDX5" s="17"/>
+      <c r="XDY5" s="17"/>
+      <c r="XDZ5" s="17"/>
+      <c r="XEA5" s="17"/>
+      <c r="XEB5" s="17"/>
+      <c r="XEC5" s="17"/>
+      <c r="XED5" s="17"/>
+      <c r="XEE5" s="17"/>
+      <c r="XEF5" s="17"/>
+      <c r="XEG5" s="17"/>
+      <c r="XEH5" s="17"/>
+      <c r="XEI5" s="17"/>
+      <c r="XEJ5" s="17"/>
+      <c r="XEK5" s="17"/>
+      <c r="XEL5" s="17"/>
+      <c r="XEM5" s="17"/>
+      <c r="XEN5" s="17"/>
+      <c r="XEO5" s="17"/>
+      <c r="XEP5" s="17"/>
+      <c r="XEQ5" s="17"/>
+      <c r="XER5" s="17"/>
+      <c r="XES5" s="17"/>
+      <c r="XET5" s="17"/>
+      <c r="XEU5" s="17"/>
+      <c r="XEV5" s="17"/>
+      <c r="XEW5" s="17"/>
       <c r="XEX5" s="0"/>
       <c r="XEY5" s="0"/>
       <c r="XEZ5" s="0"/>
@@ -3021,70 +3015,70 @@
       <c r="XFC5" s="0"/>
       <c r="XFD5" s="0"/>
     </row>
-    <row r="6" s="20" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+    <row r="6" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="18"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="17"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-      <c r="U6" s="20" t="s">
+      <c r="U6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="Y6" s="20" t="s">
+      <c r="Y6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AC6" s="18"/>
-      <c r="XDN6" s="18"/>
-      <c r="XDO6" s="18"/>
-      <c r="XDP6" s="18"/>
-      <c r="XDQ6" s="18"/>
-      <c r="XDR6" s="18"/>
-      <c r="XDS6" s="18"/>
-      <c r="XDT6" s="18"/>
-      <c r="XDU6" s="18"/>
-      <c r="XDV6" s="18"/>
-      <c r="XDW6" s="18"/>
-      <c r="XDX6" s="18"/>
-      <c r="XDY6" s="18"/>
-      <c r="XDZ6" s="18"/>
-      <c r="XEA6" s="18"/>
-      <c r="XEB6" s="18"/>
-      <c r="XEC6" s="18"/>
-      <c r="XED6" s="18"/>
-      <c r="XEE6" s="18"/>
-      <c r="XEF6" s="18"/>
-      <c r="XEG6" s="18"/>
-      <c r="XEH6" s="18"/>
-      <c r="XEI6" s="18"/>
-      <c r="XEJ6" s="18"/>
-      <c r="XEK6" s="18"/>
-      <c r="XEL6" s="18"/>
-      <c r="XEM6" s="18"/>
-      <c r="XEN6" s="18"/>
-      <c r="XEO6" s="18"/>
-      <c r="XEP6" s="18"/>
-      <c r="XEQ6" s="18"/>
-      <c r="XER6" s="18"/>
-      <c r="XES6" s="18"/>
-      <c r="XET6" s="18"/>
-      <c r="XEU6" s="18"/>
-      <c r="XEV6" s="18"/>
-      <c r="XEW6" s="18"/>
+      <c r="AC6" s="17"/>
+      <c r="XDN6" s="17"/>
+      <c r="XDO6" s="17"/>
+      <c r="XDP6" s="17"/>
+      <c r="XDQ6" s="17"/>
+      <c r="XDR6" s="17"/>
+      <c r="XDS6" s="17"/>
+      <c r="XDT6" s="17"/>
+      <c r="XDU6" s="17"/>
+      <c r="XDV6" s="17"/>
+      <c r="XDW6" s="17"/>
+      <c r="XDX6" s="17"/>
+      <c r="XDY6" s="17"/>
+      <c r="XDZ6" s="17"/>
+      <c r="XEA6" s="17"/>
+      <c r="XEB6" s="17"/>
+      <c r="XEC6" s="17"/>
+      <c r="XED6" s="17"/>
+      <c r="XEE6" s="17"/>
+      <c r="XEF6" s="17"/>
+      <c r="XEG6" s="17"/>
+      <c r="XEH6" s="17"/>
+      <c r="XEI6" s="17"/>
+      <c r="XEJ6" s="17"/>
+      <c r="XEK6" s="17"/>
+      <c r="XEL6" s="17"/>
+      <c r="XEM6" s="17"/>
+      <c r="XEN6" s="17"/>
+      <c r="XEO6" s="17"/>
+      <c r="XEP6" s="17"/>
+      <c r="XEQ6" s="17"/>
+      <c r="XER6" s="17"/>
+      <c r="XES6" s="17"/>
+      <c r="XET6" s="17"/>
+      <c r="XEU6" s="17"/>
+      <c r="XEV6" s="17"/>
+      <c r="XEW6" s="17"/>
       <c r="XEX6" s="0"/>
       <c r="XEY6" s="0"/>
       <c r="XEZ6" s="0"/>
@@ -3093,81 +3087,81 @@
       <c r="XFC6" s="0"/>
       <c r="XFD6" s="0"/>
     </row>
-    <row r="7" s="20" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+    <row r="7" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="18"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="17"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="1"/>
-      <c r="V7" s="20" t="s">
+      <c r="V7" s="19" t="s">
         <v>32</v>
       </c>
       <c r="Y7" s="1"/>
-      <c r="Z7" s="20" t="s">
+      <c r="Z7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AC7" s="18"/>
-      <c r="AV7" s="20" t="s">
+      <c r="AC7" s="17"/>
+      <c r="AV7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AW7" s="20" t="s">
+      <c r="AW7" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AZ7" s="20" t="s">
+      <c r="AZ7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="XDN7" s="18"/>
-      <c r="XDO7" s="18"/>
-      <c r="XDP7" s="18"/>
-      <c r="XDQ7" s="18"/>
-      <c r="XDR7" s="18"/>
-      <c r="XDS7" s="18"/>
-      <c r="XDT7" s="18"/>
-      <c r="XDU7" s="18"/>
-      <c r="XDV7" s="18"/>
-      <c r="XDW7" s="18"/>
-      <c r="XDX7" s="18"/>
-      <c r="XDY7" s="18"/>
-      <c r="XDZ7" s="18"/>
-      <c r="XEA7" s="18"/>
-      <c r="XEB7" s="18"/>
-      <c r="XEC7" s="18"/>
-      <c r="XED7" s="18"/>
-      <c r="XEE7" s="18"/>
-      <c r="XEF7" s="18"/>
-      <c r="XEG7" s="18"/>
-      <c r="XEH7" s="18"/>
-      <c r="XEI7" s="18"/>
-      <c r="XEJ7" s="18"/>
-      <c r="XEK7" s="18"/>
-      <c r="XEL7" s="18"/>
-      <c r="XEM7" s="18"/>
-      <c r="XEN7" s="18"/>
-      <c r="XEO7" s="18"/>
-      <c r="XEP7" s="18"/>
-      <c r="XEQ7" s="18"/>
-      <c r="XER7" s="18"/>
-      <c r="XES7" s="18"/>
-      <c r="XET7" s="18"/>
-      <c r="XEU7" s="18"/>
-      <c r="XEV7" s="18"/>
-      <c r="XEW7" s="18"/>
+      <c r="XDN7" s="17"/>
+      <c r="XDO7" s="17"/>
+      <c r="XDP7" s="17"/>
+      <c r="XDQ7" s="17"/>
+      <c r="XDR7" s="17"/>
+      <c r="XDS7" s="17"/>
+      <c r="XDT7" s="17"/>
+      <c r="XDU7" s="17"/>
+      <c r="XDV7" s="17"/>
+      <c r="XDW7" s="17"/>
+      <c r="XDX7" s="17"/>
+      <c r="XDY7" s="17"/>
+      <c r="XDZ7" s="17"/>
+      <c r="XEA7" s="17"/>
+      <c r="XEB7" s="17"/>
+      <c r="XEC7" s="17"/>
+      <c r="XED7" s="17"/>
+      <c r="XEE7" s="17"/>
+      <c r="XEF7" s="17"/>
+      <c r="XEG7" s="17"/>
+      <c r="XEH7" s="17"/>
+      <c r="XEI7" s="17"/>
+      <c r="XEJ7" s="17"/>
+      <c r="XEK7" s="17"/>
+      <c r="XEL7" s="17"/>
+      <c r="XEM7" s="17"/>
+      <c r="XEN7" s="17"/>
+      <c r="XEO7" s="17"/>
+      <c r="XEP7" s="17"/>
+      <c r="XEQ7" s="17"/>
+      <c r="XER7" s="17"/>
+      <c r="XES7" s="17"/>
+      <c r="XET7" s="17"/>
+      <c r="XEU7" s="17"/>
+      <c r="XEV7" s="17"/>
+      <c r="XEW7" s="17"/>
       <c r="XEX7" s="0"/>
       <c r="XEY7" s="0"/>
       <c r="XEZ7" s="0"/>
@@ -3177,34 +3171,34 @@
       <c r="XFD7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="21" t="n">
         <v>141</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="21" t="n">
         <f aca="false">1000*B8/$P8</f>
         <v>345.61025947732</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="22" t="n">
         <v>330</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="21" t="n">
         <f aca="false">1000*D8/$P8</f>
         <v>808.87507537245</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="23" t="n">
         <v>26.4</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="21" t="n">
         <f aca="false">1000*F8/$P8</f>
         <v>64.710006029796</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="21" t="n">
         <v>920</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="21" t="n">
         <f aca="false">1000*H8/$P8</f>
         <v>2255.04566467471</v>
       </c>
@@ -3285,7 +3279,7 @@
         <f aca="false">AK8*1000</f>
         <v>1900</v>
       </c>
-      <c r="AO8" s="25" t="s">
+      <c r="AO8" s="24" t="s">
         <v>40</v>
       </c>
       <c r="AP8" s="1" t="n">
@@ -3294,15 +3288,15 @@
       <c r="AQ8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AR8" s="25" t="n">
+      <c r="AR8" s="24" t="n">
         <f aca="false">AP8+AQ8/10</f>
         <v>9.9</v>
       </c>
-      <c r="AS8" s="25" t="n">
+      <c r="AS8" s="24" t="n">
         <f aca="false">1000*AR8</f>
         <v>9900</v>
       </c>
-      <c r="AU8" s="26" t="s">
+      <c r="AU8" s="25" t="s">
         <v>39</v>
       </c>
       <c r="AV8" s="0" t="n">
@@ -3320,43 +3314,43 @@
       <c r="AZ8" s="0" t="n">
         <v>1.17</v>
       </c>
-      <c r="BA8" s="26" t="s">
+      <c r="BA8" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="BC8" s="26" t="n">
+      <c r="BC8" s="25" t="n">
         <f aca="false">AV8*1000</f>
         <v>1090</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="21" t="n">
         <f aca="false">1000*B9/$P9</f>
         <v>394.508442480669</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="28" t="n">
         <v>184</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">1000*D9/$P9</f>
         <v>362.947767082216</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="29" t="n">
         <v>61.1</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="21" t="n">
         <f aca="false">1000*F9/$P9</f>
         <v>120.522329177844</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="27" t="n">
         <v>722</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="I9" s="21" t="n">
         <f aca="false">1000*H9/$P9</f>
         <v>1424.17547735522</v>
       </c>
@@ -3397,7 +3391,7 @@
         <f aca="false">R9/P9</f>
         <v>5.30002367050655</v>
       </c>
-      <c r="T9" s="31" t="n">
+      <c r="T9" s="30" t="n">
         <f aca="false">F9</f>
         <v>61.1</v>
       </c>
@@ -3441,7 +3435,7 @@
         <f aca="false">AK9*1000</f>
         <v>1100</v>
       </c>
-      <c r="AO9" s="25" t="s">
+      <c r="AO9" s="24" t="s">
         <v>44</v>
       </c>
       <c r="AP9" s="1" t="n">
@@ -3450,15 +3444,15 @@
       <c r="AQ9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AR9" s="25" t="n">
+      <c r="AR9" s="24" t="n">
         <f aca="false">AP9+AQ9/10</f>
         <v>9.8</v>
       </c>
-      <c r="AS9" s="25" t="n">
+      <c r="AS9" s="24" t="n">
         <f aca="false">1000*AR9</f>
         <v>9800</v>
       </c>
-      <c r="AU9" s="26" t="s">
+      <c r="AU9" s="25" t="s">
         <v>43</v>
       </c>
       <c r="AV9" s="0" t="n">
@@ -3476,43 +3470,43 @@
       <c r="AZ9" s="0" t="n">
         <v>0.96</v>
       </c>
-      <c r="BA9" s="26" t="s">
+      <c r="BA9" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="BC9" s="26" t="n">
+      <c r="BC9" s="25" t="n">
         <f aca="false">AV9*1000</f>
         <v>1100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="21" t="n">
         <v>38</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="21" t="n">
         <f aca="false">1000*B10/$P10</f>
         <v>726.008291778911</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="21" t="n">
         <f aca="false">1000*D10/$P10</f>
         <v>343.898664526853</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="21" t="n">
         <f aca="false">1000*F10/$P10</f>
         <v>3.82109627252059</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="21" t="n">
         <f aca="false">1000*H10/$P10</f>
         <v>764.219254504117</v>
       </c>
@@ -3593,7 +3587,7 @@
         <f aca="false">AK10*1000</f>
         <v>270</v>
       </c>
-      <c r="AO10" s="25" t="s">
+      <c r="AO10" s="24" t="s">
         <v>46</v>
       </c>
       <c r="AP10" s="1" t="n">
@@ -3602,15 +3596,15 @@
       <c r="AQ10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AR10" s="25" t="n">
+      <c r="AR10" s="24" t="n">
         <f aca="false">AP10+AQ10/10</f>
         <v>1.6</v>
       </c>
-      <c r="AS10" s="25" t="n">
+      <c r="AS10" s="24" t="n">
         <f aca="false">1000*AR10</f>
         <v>1600</v>
       </c>
-      <c r="AU10" s="26" t="s">
+      <c r="AU10" s="25" t="s">
         <v>47</v>
       </c>
       <c r="AV10" s="0" t="n">
@@ -3628,43 +3622,43 @@
       <c r="AZ10" s="0" t="n">
         <v>1.48</v>
       </c>
-      <c r="BA10" s="26" t="s">
+      <c r="BA10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="BC10" s="26" t="n">
+      <c r="BC10" s="25" t="n">
         <f aca="false">AV10*1000</f>
         <v>270</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="27" t="n">
         <v>46</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="21" t="n">
         <f aca="false">1000*B11/$P11</f>
         <v>786.755148115208</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="21" t="n">
         <f aca="false">1000*D11/$P11</f>
         <v>444.687692412944</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="29" t="n">
         <v>0.3</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="21" t="n">
         <f aca="false">1000*F11/$P11</f>
         <v>5.13101183553397</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="21" t="n">
         <f aca="false">1000*H11/$P11</f>
         <v>615.721420264076</v>
       </c>
@@ -3745,7 +3739,7 @@
         <f aca="false">AK11*1000</f>
         <v>380</v>
       </c>
-      <c r="AO11" s="25" t="s">
+      <c r="AO11" s="24" t="s">
         <v>49</v>
       </c>
       <c r="AP11" s="1" t="n">
@@ -3754,15 +3748,15 @@
       <c r="AQ11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AR11" s="25" t="n">
+      <c r="AR11" s="24" t="n">
         <f aca="false">AP11+AQ11/10</f>
         <v>2.3</v>
       </c>
-      <c r="AS11" s="25" t="n">
+      <c r="AS11" s="24" t="n">
         <f aca="false">1000*AR11</f>
         <v>2300</v>
       </c>
-      <c r="AU11" s="26" t="s">
+      <c r="AU11" s="25" t="s">
         <v>50</v>
       </c>
       <c r="AV11" s="0" t="n">
@@ -3780,41 +3774,41 @@
       <c r="AZ11" s="0" t="n">
         <v>2.39</v>
       </c>
-      <c r="BA11" s="26" t="s">
+      <c r="BA11" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="BC11" s="26" t="n">
+      <c r="BC11" s="25" t="n">
         <f aca="false">AV11*1000</f>
         <v>380</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="21" t="n">
         <f aca="false">1000*B12/$P12</f>
         <v>727.603456116417</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="22" t="n">
+      <c r="D12" s="31"/>
+      <c r="E12" s="21" t="n">
         <f aca="false">1000*D12/$P12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="23" t="n">
         <v>0.8</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="21" t="n">
         <f aca="false">1000*F12/$P12</f>
         <v>36.3801728058208</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="I12" s="22" t="n">
+      <c r="I12" s="21" t="n">
         <f aca="false">1000*H12/$P12</f>
         <v>2091.8599363347</v>
       </c>
@@ -3895,7 +3889,7 @@
         <f aca="false">AK12*1000</f>
         <v>290</v>
       </c>
-      <c r="AO12" s="25" t="s">
+      <c r="AO12" s="24" t="s">
         <v>52</v>
       </c>
       <c r="AP12" s="1" t="n">
@@ -3904,15 +3898,15 @@
       <c r="AQ12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AR12" s="25" t="n">
+      <c r="AR12" s="24" t="n">
         <f aca="false">AP12+AQ12/10</f>
         <v>1.5</v>
       </c>
-      <c r="AS12" s="25" t="n">
+      <c r="AS12" s="24" t="n">
         <f aca="false">1000*AR12</f>
         <v>1500</v>
       </c>
-      <c r="AU12" s="26" t="s">
+      <c r="AU12" s="25" t="s">
         <v>53</v>
       </c>
       <c r="AV12" s="0" t="n">
@@ -3930,43 +3924,43 @@
       <c r="AZ12" s="0" t="n">
         <v>5.29</v>
       </c>
-      <c r="BA12" s="26" t="s">
+      <c r="BA12" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="BC12" s="26" t="n">
+      <c r="BC12" s="25" t="n">
         <f aca="false">AV12*1000</f>
         <v>290</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="28" t="n">
+      <c r="B13" s="27" t="n">
         <v>177</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="21" t="n">
         <f aca="false">1000*B13/$P13</f>
         <v>777.772407095745</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="28" t="n">
         <v>263</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="21" t="n">
         <f aca="false">1000*D13/$P13</f>
         <v>1155.67312466769</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="29" t="n">
         <v>3.8</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="21" t="n">
         <f aca="false">1000*F13/$P13</f>
         <v>16.6979386834115</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="27" t="n">
         <v>348</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="21" t="n">
         <f aca="false">1000*H13/$P13</f>
         <v>1529.17964784926</v>
       </c>
@@ -4047,7 +4041,7 @@
         <f aca="false">AK13*1000</f>
         <v>440</v>
       </c>
-      <c r="AO13" s="25" t="s">
+      <c r="AO13" s="24" t="s">
         <v>57</v>
       </c>
       <c r="AP13" s="1" t="n">
@@ -4056,15 +4050,15 @@
       <c r="AQ13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AR13" s="25" t="n">
+      <c r="AR13" s="24" t="n">
         <f aca="false">AP13+AQ13/10</f>
         <v>4.6</v>
       </c>
-      <c r="AS13" s="25" t="n">
+      <c r="AS13" s="24" t="n">
         <f aca="false">1000*AR13</f>
         <v>4600</v>
       </c>
-      <c r="AU13" s="26" t="s">
+      <c r="AU13" s="25" t="s">
         <v>56</v>
       </c>
       <c r="AV13" s="0" t="n">
@@ -4082,43 +4076,43 @@
       <c r="AZ13" s="0" t="n">
         <v>0.79</v>
       </c>
-      <c r="BA13" s="26" t="s">
+      <c r="BA13" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="BC13" s="26" t="n">
+      <c r="BC13" s="25" t="n">
         <f aca="false">AV13*1000</f>
         <v>440</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="21" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="21" t="n">
         <f aca="false">1000*B14/$P14</f>
         <v>304.277684963515</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="22" t="n">
         <v>258</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="21" t="n">
         <f aca="false">1000*D14/$P14</f>
         <v>740.600403024405</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="23" t="n">
         <v>113.8</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="21" t="n">
         <f aca="false">1000*F14/$P14</f>
         <v>326.667929706114</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="21" t="n">
         <v>533</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="21" t="n">
         <f aca="false">1000*H14/$P14</f>
         <v>1530.00005741088</v>
       </c>
@@ -4199,7 +4193,7 @@
         <f aca="false">AK14*1000</f>
         <v>1130</v>
       </c>
-      <c r="AO14" s="25" t="s">
+      <c r="AO14" s="24" t="s">
         <v>61</v>
       </c>
       <c r="AP14" s="1" t="n">
@@ -4208,15 +4202,15 @@
       <c r="AQ14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AR14" s="25" t="n">
+      <c r="AR14" s="24" t="n">
         <f aca="false">AP14+AQ14/10</f>
         <v>4.2</v>
       </c>
-      <c r="AS14" s="25" t="n">
+      <c r="AS14" s="24" t="n">
         <f aca="false">1000*AR14</f>
         <v>4200</v>
       </c>
-      <c r="AU14" s="26" t="s">
+      <c r="AU14" s="25" t="s">
         <v>60</v>
       </c>
       <c r="AV14" s="0" t="n">
@@ -4234,43 +4228,43 @@
       <c r="AZ14" s="0" t="n">
         <v>1.49</v>
       </c>
-      <c r="BA14" s="26" t="s">
+      <c r="BA14" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="BC14" s="26" t="n">
+      <c r="BC14" s="25" t="n">
         <f aca="false">AV14*1000</f>
         <v>1130</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="21" t="n">
         <f aca="false">1000*B15/$P15</f>
         <v>744.360658921001</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="21" t="n">
         <f aca="false">1000*D15/$P15</f>
         <v>679.633645101783</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="21" t="n">
         <f aca="false">1000*F15/$P15</f>
         <v>3.23635069096087</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="I15" s="21" t="n">
         <f aca="false">1000*H15/$P15</f>
         <v>938.541700378653</v>
       </c>
@@ -4351,7 +4345,7 @@
         <f aca="false">AK15*1000</f>
         <v>900</v>
       </c>
-      <c r="AO15" s="25" t="s">
+      <c r="AO15" s="24" t="s">
         <v>63</v>
       </c>
       <c r="AP15" s="1" t="n">
@@ -4360,15 +4354,15 @@
       <c r="AQ15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AR15" s="25" t="n">
+      <c r="AR15" s="24" t="n">
         <f aca="false">AP15+AQ15/10</f>
         <v>0.5</v>
       </c>
-      <c r="AS15" s="25" t="n">
+      <c r="AS15" s="24" t="n">
         <f aca="false">1000*AR15</f>
         <v>500</v>
       </c>
-      <c r="AU15" s="26" t="s">
+      <c r="AU15" s="25" t="s">
         <v>64</v>
       </c>
       <c r="AV15" s="0" t="n">
@@ -4386,43 +4380,43 @@
       <c r="AZ15" s="0" t="n">
         <v>1.3</v>
       </c>
-      <c r="BA15" s="26" t="s">
+      <c r="BA15" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="BC15" s="26" t="n">
+      <c r="BC15" s="25" t="n">
         <f aca="false">AV15*1000</f>
         <v>90</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="21" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="21" t="n">
         <f aca="false">1000*B16/$P16</f>
         <v>379.785988637743</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="22" t="n">
         <v>133</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="21" t="n">
         <f aca="false">1000*D16/$P16</f>
         <v>520.737489575462</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="23" t="n">
         <v>81.3</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="21" t="n">
         <f aca="false">1000*F16/$P16</f>
         <v>318.315472951015</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="21" t="n">
         <v>152</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="21" t="n">
         <f aca="false">1000*H16/$P16</f>
         <v>595.128559514814</v>
       </c>
@@ -4503,7 +4497,7 @@
         <f aca="false">AK16*1000</f>
         <v>720</v>
       </c>
-      <c r="AO16" s="25" t="s">
+      <c r="AO16" s="24" t="s">
         <v>66</v>
       </c>
       <c r="AP16" s="1" t="n">
@@ -4512,15 +4506,15 @@
       <c r="AQ16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AR16" s="25" t="n">
+      <c r="AR16" s="24" t="n">
         <f aca="false">AP16+AQ16/10</f>
         <v>2.9</v>
       </c>
-      <c r="AS16" s="25" t="n">
+      <c r="AS16" s="24" t="n">
         <f aca="false">1000*AR16</f>
         <v>2900</v>
       </c>
-      <c r="AU16" s="26" t="s">
+      <c r="AU16" s="25" t="s">
         <v>67</v>
       </c>
       <c r="AV16" s="0" t="n">
@@ -4538,43 +4532,43 @@
       <c r="AZ16" s="0" t="n">
         <v>1.36</v>
       </c>
-      <c r="BA16" s="26" t="s">
+      <c r="BA16" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="BC16" s="26" t="n">
+      <c r="BC16" s="25" t="n">
         <f aca="false">AV16*1000</f>
         <v>720</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="28" t="n">
+      <c r="B17" s="27" t="n">
         <v>1078</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="21" t="n">
         <f aca="false">1000*B17/$P17</f>
         <v>418.692157950257</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="28" t="n">
         <v>1691</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="21" t="n">
         <f aca="false">1000*D17/$P17</f>
         <v>656.779628101934</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="27" t="n">
         <v>3100</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="21" t="n">
         <f aca="false">1000*F17/$P17</f>
         <v>1204.03125199054</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="27" t="n">
         <v>6670</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="21" t="n">
         <f aca="false">1000*H17/$P17</f>
         <v>2590.60917766996</v>
       </c>
@@ -4659,7 +4653,7 @@
         <f aca="false">AK17*1000</f>
         <v>5380</v>
       </c>
-      <c r="AO17" s="25" t="s">
+      <c r="AO17" s="24" t="s">
         <v>71</v>
       </c>
       <c r="AP17" s="1" t="n">
@@ -4668,15 +4662,15 @@
       <c r="AQ17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AR17" s="25" t="n">
+      <c r="AR17" s="24" t="n">
         <f aca="false">AP17+AQ17/10</f>
         <v>62</v>
       </c>
-      <c r="AS17" s="25" t="n">
+      <c r="AS17" s="24" t="n">
         <f aca="false">1000*AR17</f>
         <v>62000</v>
       </c>
-      <c r="AU17" s="26" t="s">
+      <c r="AU17" s="25" t="s">
         <v>70</v>
       </c>
       <c r="AV17" s="0" t="n">
@@ -4694,43 +4688,43 @@
       <c r="AZ17" s="0" t="n">
         <v>0.98</v>
       </c>
-      <c r="BA17" s="26" t="s">
+      <c r="BA17" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="BC17" s="26" t="n">
+      <c r="BC17" s="25" t="n">
         <f aca="false">AV17*1000</f>
         <v>5380</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="21" t="n">
         <v>973</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="21" t="n">
         <f aca="false">1000*B18/$P18</f>
         <v>260.893020991029</v>
       </c>
-      <c r="D18" s="33" t="n">
+      <c r="D18" s="32" t="n">
         <v>2700</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="21" t="n">
         <f aca="false">1000*D18/$P18</f>
         <v>723.958023305013</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="23" t="n">
         <v>1595.2</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="21" t="n">
         <f aca="false">1000*F18/$P18</f>
         <v>427.725125472651</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="21" t="n">
         <v>8344</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="I18" s="21" t="n">
         <f aca="false">1000*H18/$P18</f>
         <v>2237.29842461372</v>
       </c>
@@ -4811,7 +4805,7 @@
         <f aca="false">AK18*1000</f>
         <v>6400</v>
       </c>
-      <c r="AO18" s="25" t="s">
+      <c r="AO18" s="24" t="s">
         <v>75</v>
       </c>
       <c r="AP18" s="1" t="n">
@@ -4820,15 +4814,15 @@
       <c r="AQ18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AR18" s="25" t="n">
+      <c r="AR18" s="24" t="n">
         <f aca="false">AP18+AQ18/10</f>
         <v>57.7</v>
       </c>
-      <c r="AS18" s="25" t="n">
+      <c r="AS18" s="24" t="n">
         <f aca="false">1000*AR18</f>
         <v>57700</v>
       </c>
-      <c r="AU18" s="26" t="s">
+      <c r="AU18" s="25" t="s">
         <v>74</v>
       </c>
       <c r="AV18" s="0" t="n">
@@ -4846,43 +4840,43 @@
       <c r="AZ18" s="0" t="n">
         <v>0.73</v>
       </c>
-      <c r="BA18" s="26" t="s">
+      <c r="BA18" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="BC18" s="26" t="n">
+      <c r="BC18" s="25" t="n">
         <f aca="false">AV18*1000</f>
         <v>6040</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="27" t="n">
         <v>91</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="21" t="n">
         <f aca="false">1000*B19/$P19</f>
         <v>503.093193867792</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="28" t="n">
         <v>54</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="21" t="n">
         <f aca="false">1000*D19/$P19</f>
         <v>298.538818339129</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="29" t="n">
         <v>22.7</v>
       </c>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="21" t="n">
         <f aca="false">1000*F19/$P19</f>
         <v>125.496873635152</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="27" t="n">
         <v>118</v>
       </c>
-      <c r="I19" s="22" t="n">
+      <c r="I19" s="21" t="n">
         <f aca="false">1000*H19/$P19</f>
         <v>652.362603037356</v>
       </c>
@@ -4923,7 +4917,7 @@
         <f aca="false">R19/P19</f>
         <v>8.70351225391279</v>
       </c>
-      <c r="T19" s="31" t="n">
+      <c r="T19" s="30" t="n">
         <f aca="false">F19</f>
         <v>22.7</v>
       </c>
@@ -4967,7 +4961,7 @@
         <f aca="false">AK19*1000</f>
         <v>2540</v>
       </c>
-      <c r="AO19" s="25" t="s">
+      <c r="AO19" s="24" t="s">
         <v>79</v>
       </c>
       <c r="AP19" s="1" t="n">
@@ -4976,15 +4970,15 @@
       <c r="AQ19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AR19" s="25" t="n">
+      <c r="AR19" s="24" t="n">
         <f aca="false">AP19+AQ19/10</f>
         <v>6.3</v>
       </c>
-      <c r="AS19" s="25" t="n">
+      <c r="AS19" s="24" t="n">
         <f aca="false">1000*AR19</f>
         <v>6300</v>
       </c>
-      <c r="AU19" s="26" t="s">
+      <c r="AU19" s="25" t="s">
         <v>78</v>
       </c>
       <c r="AV19" s="0" t="n">
@@ -5002,43 +4996,43 @@
       <c r="AZ19" s="0" t="n">
         <v>5.88</v>
       </c>
-      <c r="BA19" s="26" t="s">
+      <c r="BA19" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="BC19" s="26" t="n">
+      <c r="BC19" s="25" t="n">
         <f aca="false">AV19*1000</f>
         <v>2540</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="21" t="n">
         <v>139</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="21" t="n">
         <f aca="false">1000*B20/$P20</f>
         <v>933.361983293492</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="E20" s="22" t="n">
+      <c r="E20" s="21" t="n">
         <f aca="false">1000*D20/$P20</f>
         <v>758.776288576724</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="23" t="n">
         <v>5.9</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G20" s="21" t="n">
         <f aca="false">1000*F20/$P20</f>
         <v>39.617523031882</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="21" t="n">
         <f aca="false">1000*H20/$P20</f>
         <v>1396.68555773415</v>
       </c>
@@ -5119,7 +5113,7 @@
         <f aca="false">AK20*1000</f>
         <v>370</v>
       </c>
-      <c r="AO20" s="25" t="s">
+      <c r="AO20" s="24" t="s">
         <v>81</v>
       </c>
       <c r="AP20" s="1" t="n">
@@ -5128,15 +5122,15 @@
       <c r="AQ20" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AR20" s="25" t="n">
+      <c r="AR20" s="24" t="n">
         <f aca="false">AP20+AQ20/10</f>
         <v>2.5</v>
       </c>
-      <c r="AS20" s="25" t="n">
+      <c r="AS20" s="24" t="n">
         <f aca="false">1000*AR20</f>
         <v>2500</v>
       </c>
-      <c r="AU20" s="26" t="s">
+      <c r="AU20" s="25" t="s">
         <v>82</v>
       </c>
       <c r="AV20" s="0" t="n">
@@ -5154,43 +5148,43 @@
       <c r="AZ20" s="0" t="n">
         <v>0.95</v>
       </c>
-      <c r="BA20" s="26" t="s">
+      <c r="BA20" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="BC20" s="26" t="n">
+      <c r="BC20" s="25" t="n">
         <f aca="false">AV20*1000</f>
         <v>370</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="27" t="n">
         <v>97</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="21" t="n">
         <f aca="false">1000*B21/$P21</f>
         <v>299.863052234907</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="28" t="n">
         <v>160</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="21" t="n">
         <f aca="false">1000*D21/$P21</f>
         <v>494.619467603971</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="29" t="n">
         <v>241.4</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="21" t="n">
         <f aca="false">1000*F21/$P21</f>
         <v>746.257121747491</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="27" t="n">
         <v>331</v>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="I21" s="21" t="n">
         <f aca="false">1000*H21/$P21</f>
         <v>1023.24402360571</v>
       </c>
@@ -5231,7 +5225,7 @@
         <f aca="false">R21/P21</f>
         <v>4.65560573882237</v>
       </c>
-      <c r="T21" s="31" t="n">
+      <c r="T21" s="30" t="n">
         <f aca="false">F21</f>
         <v>241.4</v>
       </c>
@@ -5275,7 +5269,7 @@
         <f aca="false">AK21*1000</f>
         <v>940</v>
       </c>
-      <c r="AO21" s="25" t="s">
+      <c r="AO21" s="24" t="s">
         <v>86</v>
       </c>
       <c r="AP21" s="1" t="n">
@@ -5284,18 +5278,18 @@
       <c r="AQ21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AR21" s="25" t="n">
+      <c r="AR21" s="24" t="n">
         <f aca="false">AP21+AQ21/10</f>
         <v>3.8</v>
       </c>
-      <c r="AS21" s="25" t="n">
+      <c r="AS21" s="24" t="n">
         <f aca="false">1000*AR21</f>
         <v>3800</v>
       </c>
-      <c r="AT21" s="25" t="s">
+      <c r="AT21" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="AU21" s="26" t="s">
+      <c r="AU21" s="25" t="s">
         <v>85</v>
       </c>
       <c r="AV21" s="0" t="n">
@@ -5313,43 +5307,43 @@
       <c r="AZ21" s="0" t="n">
         <v>1.22</v>
       </c>
-      <c r="BA21" s="26" t="s">
+      <c r="BA21" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="BC21" s="26" t="n">
+      <c r="BC21" s="25" t="n">
         <f aca="false">AV21*1000</f>
         <v>940</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="21" t="n">
         <v>464</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="21" t="n">
         <f aca="false">1000*B22/$P22</f>
         <v>255.791133309077</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="22" t="n">
         <v>891</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="21" t="n">
         <f aca="false">1000*D22/$P22</f>
         <v>491.185128832732</v>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="F22" s="23" t="n">
         <v>544.5</v>
       </c>
-      <c r="G22" s="22" t="n">
+      <c r="G22" s="21" t="n">
         <f aca="false">1000*F22/$P22</f>
         <v>300.168689842225</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="21" t="n">
         <v>2618</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="21" t="n">
         <f aca="false">1000*H22/$P22</f>
         <v>1443.23531681716</v>
       </c>
@@ -5434,7 +5428,7 @@
         <f aca="false">AK22*1000</f>
         <v>7110</v>
       </c>
-      <c r="AO22" s="25" t="s">
+      <c r="AO22" s="24" t="s">
         <v>91</v>
       </c>
       <c r="AP22" s="1" t="n">
@@ -5443,15 +5437,15 @@
       <c r="AQ22" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AR22" s="25" t="n">
+      <c r="AR22" s="24" t="n">
         <f aca="false">AP22+AQ22/10</f>
         <v>56.5</v>
       </c>
-      <c r="AS22" s="25" t="n">
+      <c r="AS22" s="24" t="n">
         <f aca="false">1000*AR22</f>
         <v>56500</v>
       </c>
-      <c r="AU22" s="26" t="s">
+      <c r="AU22" s="25" t="s">
         <v>90</v>
       </c>
       <c r="AV22" s="0" t="n">
@@ -5469,43 +5463,43 @@
       <c r="AZ22" s="0" t="n">
         <v>1.78</v>
       </c>
-      <c r="BA22" s="26" t="s">
+      <c r="BA22" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="BC22" s="26" t="n">
+      <c r="BC22" s="25" t="n">
         <f aca="false">AV22*1000</f>
         <v>7110</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="27" t="n">
         <v>27</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="21" t="n">
         <f aca="false">1000*B23/$P23</f>
         <v>816.326530612245</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E23" s="21" t="n">
         <f aca="false">1000*D23/$P23</f>
         <v>604.686318972033</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="22" t="n">
+      <c r="G23" s="21" t="n">
         <f aca="false">1000*F23/$P23</f>
         <v>0</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="I23" s="21" t="n">
         <f aca="false">1000*H23/$P23</f>
         <v>604.686318972033</v>
       </c>
@@ -5586,7 +5580,7 @@
         <f aca="false">AK23*1000</f>
         <v>180</v>
       </c>
-      <c r="AO23" s="25" t="s">
+      <c r="AO23" s="24" t="s">
         <v>93</v>
       </c>
       <c r="AP23" s="1" t="n">
@@ -5595,15 +5589,15 @@
       <c r="AQ23" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AR23" s="25" t="n">
+      <c r="AR23" s="24" t="n">
         <f aca="false">AP23+AQ23/10</f>
         <v>0.5</v>
       </c>
-      <c r="AS23" s="25" t="n">
+      <c r="AS23" s="24" t="n">
         <f aca="false">1000*AR23</f>
         <v>500</v>
       </c>
-      <c r="AU23" s="26" t="s">
+      <c r="AU23" s="25" t="s">
         <v>94</v>
       </c>
       <c r="AV23" s="0" t="n">
@@ -5621,43 +5615,43 @@
       <c r="AZ23" s="0" t="n">
         <v>2.26</v>
       </c>
-      <c r="BA23" s="26" t="s">
+      <c r="BA23" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="BC23" s="26" t="n">
+      <c r="BC23" s="25" t="n">
         <f aca="false">AV23*1000</f>
         <v>180</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="21" t="n">
         <f aca="false">1000*B24/$P24</f>
         <v>759.034360189574</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="E24" s="22" t="n">
+      <c r="E24" s="21" t="n">
         <f aca="false">1000*D24/$P24</f>
         <v>444.312796208531</v>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="G24" s="22" t="n">
+      <c r="G24" s="21" t="n">
         <f aca="false">1000*F24/$P24</f>
         <v>1.85130331753555</v>
       </c>
-      <c r="H24" s="22" t="n">
+      <c r="H24" s="21" t="n">
         <v>31</v>
       </c>
-      <c r="I24" s="22" t="n">
+      <c r="I24" s="21" t="n">
         <f aca="false">1000*H24/$P24</f>
         <v>573.904028436019</v>
       </c>
@@ -5738,7 +5732,7 @@
         <f aca="false">AK24*1000</f>
         <v>140</v>
       </c>
-      <c r="AO24" s="25" t="s">
+      <c r="AO24" s="24" t="s">
         <v>96</v>
       </c>
       <c r="AP24" s="1" t="n">
@@ -5747,15 +5741,15 @@
       <c r="AQ24" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AR24" s="25" t="n">
+      <c r="AR24" s="24" t="n">
         <f aca="false">AP24+AQ24/10</f>
         <v>0.8</v>
       </c>
-      <c r="AS24" s="25" t="n">
+      <c r="AS24" s="24" t="n">
         <f aca="false">1000*AR24</f>
         <v>800</v>
       </c>
-      <c r="AU24" s="26" t="s">
+      <c r="AU24" s="25" t="s">
         <v>97</v>
       </c>
       <c r="AV24" s="0" t="n">
@@ -5773,41 +5767,41 @@
       <c r="AZ24" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BA24" s="26" t="s">
+      <c r="BA24" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="BC24" s="26" t="n">
+      <c r="BC24" s="25" t="n">
         <f aca="false">AV24*1000</f>
         <v>140</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="21" t="n">
         <f aca="false">1000*B25/$P25</f>
         <v>198.137507430157</v>
       </c>
-      <c r="D25" s="34"/>
-      <c r="E25" s="22" t="n">
+      <c r="D25" s="33"/>
+      <c r="E25" s="21" t="n">
         <f aca="false">1000*D25/$P25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="28" t="n">
+      <c r="F25" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="22" t="n">
+      <c r="G25" s="21" t="n">
         <f aca="false">1000*F25/$P25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="27" t="n">
         <v>208</v>
       </c>
-      <c r="I25" s="22" t="n">
+      <c r="I25" s="21" t="n">
         <f aca="false">1000*H25/$P25</f>
         <v>4121.26015454726</v>
       </c>
@@ -5888,7 +5882,7 @@
         <f aca="false">AK25*1000</f>
         <v>210</v>
       </c>
-      <c r="AO25" s="25" t="s">
+      <c r="AO25" s="24" t="s">
         <v>99</v>
       </c>
       <c r="AP25" s="1" t="n">
@@ -5897,15 +5891,15 @@
       <c r="AQ25" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AR25" s="25" t="n">
+      <c r="AR25" s="24" t="n">
         <f aca="false">AP25+AQ25/10</f>
         <v>1.8</v>
       </c>
-      <c r="AS25" s="25" t="n">
+      <c r="AS25" s="24" t="n">
         <f aca="false">1000*AR25</f>
         <v>1800</v>
       </c>
-      <c r="AU25" s="26" t="s">
+      <c r="AU25" s="25" t="s">
         <v>100</v>
       </c>
       <c r="AV25" s="0" t="n">
@@ -5923,41 +5917,41 @@
       <c r="AZ25" s="0" t="n">
         <v>2.01</v>
       </c>
-      <c r="BA25" s="26" t="s">
+      <c r="BA25" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="BC25" s="26" t="n">
+      <c r="BC25" s="25" t="n">
         <f aca="false">AV25*1000</f>
         <v>210</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="21" t="n">
         <f aca="false">1000*B26/$P26</f>
         <v>510.538983298082</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="22" t="n">
+      <c r="D26" s="31"/>
+      <c r="E26" s="21" t="n">
         <f aca="false">1000*D26/$P26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="22" t="n">
+      <c r="F26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="22" t="n">
+      <c r="G26" s="21" t="n">
         <f aca="false">1000*F26/$P26</f>
         <v>0</v>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="H26" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="I26" s="22" t="n">
+      <c r="I26" s="21" t="n">
         <f aca="false">1000*H26/$P26</f>
         <v>656.407264240391</v>
       </c>
@@ -6038,7 +6032,7 @@
         <f aca="false">AK26*1000</f>
         <v>270</v>
       </c>
-      <c r="AO26" s="25" t="s">
+      <c r="AO26" s="24" t="s">
         <v>102</v>
       </c>
       <c r="AP26" s="1" t="n">
@@ -6047,15 +6041,15 @@
       <c r="AQ26" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AR26" s="25" t="n">
+      <c r="AR26" s="24" t="n">
         <f aca="false">AP26+AQ26/10</f>
         <v>0.9</v>
       </c>
-      <c r="AS26" s="25" t="n">
+      <c r="AS26" s="24" t="n">
         <f aca="false">1000*AR26</f>
         <v>900</v>
       </c>
-      <c r="AU26" s="26" t="s">
+      <c r="AU26" s="25" t="s">
         <v>103</v>
       </c>
       <c r="AV26" s="0" t="n">
@@ -6073,43 +6067,43 @@
       <c r="AZ26" s="0" t="n">
         <v>7.59</v>
       </c>
-      <c r="BA26" s="26" t="s">
+      <c r="BA26" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="BC26" s="26" t="n">
+      <c r="BC26" s="25" t="n">
         <f aca="false">AV26*1000</f>
         <v>270</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="27" t="n">
         <v>332</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="21" t="n">
         <f aca="false">1000*B27/$P27</f>
         <v>396.580804533444</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="28" t="n">
         <v>652</v>
       </c>
-      <c r="E27" s="22" t="n">
+      <c r="E27" s="21" t="n">
         <f aca="false">1000*D27/$P27</f>
         <v>778.827363119896</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="F27" s="27" t="n">
         <v>1961</v>
       </c>
-      <c r="G27" s="22" t="n">
+      <c r="G27" s="21" t="n">
         <f aca="false">1000*F27/$P27</f>
         <v>2342.4546918376</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="27" t="n">
         <v>913</v>
       </c>
-      <c r="I27" s="22" t="n">
+      <c r="I27" s="21" t="n">
         <f aca="false">1000*H27/$P27</f>
         <v>1090.59721246697</v>
       </c>
@@ -6190,7 +6184,7 @@
         <f aca="false">AK27*1000</f>
         <v>1980</v>
       </c>
-      <c r="AO27" s="25" t="s">
+      <c r="AO27" s="24" t="s">
         <v>107</v>
       </c>
       <c r="AP27" s="1" t="n">
@@ -6199,15 +6193,15 @@
       <c r="AQ27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AR27" s="25" t="n">
+      <c r="AR27" s="24" t="n">
         <f aca="false">AP27+AQ27/10</f>
         <v>11</v>
       </c>
-      <c r="AS27" s="25" t="n">
+      <c r="AS27" s="24" t="n">
         <f aca="false">1000*AR27</f>
         <v>11000</v>
       </c>
-      <c r="AU27" s="26" t="s">
+      <c r="AU27" s="25" t="s">
         <v>106</v>
       </c>
       <c r="AV27" s="0" t="n">
@@ -6225,43 +6219,43 @@
       <c r="AZ27" s="0" t="n">
         <v>0.99</v>
       </c>
-      <c r="BA27" s="26" t="s">
+      <c r="BA27" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="BC27" s="26" t="n">
+      <c r="BC27" s="25" t="n">
         <f aca="false">AV27*1000</f>
         <v>1980</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="21" t="n">
         <v>494</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="21" t="n">
         <f aca="false">1000*B28/$P28</f>
         <v>901.606282772202</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="22" t="n">
         <v>427</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="21" t="n">
         <f aca="false">1000*D28/$P28</f>
         <v>779.323649278806</v>
       </c>
-      <c r="F28" s="22" t="n">
+      <c r="F28" s="21" t="n">
         <v>63</v>
       </c>
-      <c r="G28" s="22" t="n">
+      <c r="G28" s="21" t="n">
         <f aca="false">1000*F28/$P28</f>
         <v>114.982177762447</v>
       </c>
-      <c r="H28" s="22" t="n">
+      <c r="H28" s="21" t="n">
         <v>560</v>
       </c>
-      <c r="I28" s="22" t="n">
+      <c r="I28" s="21" t="n">
         <f aca="false">1000*H28/$P28</f>
         <v>1022.06380233286</v>
       </c>
@@ -6342,7 +6336,7 @@
         <f aca="false">AK28*1000</f>
         <v>1190</v>
       </c>
-      <c r="AO28" s="25" t="s">
+      <c r="AO28" s="24" t="s">
         <v>111</v>
       </c>
       <c r="AP28" s="1" t="n">
@@ -6351,15 +6345,15 @@
       <c r="AQ28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AR28" s="25" t="n">
+      <c r="AR28" s="24" t="n">
         <f aca="false">AP28+AQ28/10</f>
         <v>8</v>
       </c>
-      <c r="AS28" s="25" t="n">
+      <c r="AS28" s="24" t="n">
         <f aca="false">1000*AR28</f>
         <v>8000</v>
       </c>
-      <c r="AU28" s="26" t="s">
+      <c r="AU28" s="25" t="s">
         <v>110</v>
       </c>
       <c r="AV28" s="0" t="n">
@@ -6377,43 +6371,43 @@
       <c r="AZ28" s="0" t="n">
         <v>0.76</v>
       </c>
-      <c r="BA28" s="26" t="s">
+      <c r="BA28" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="BC28" s="26" t="n">
+      <c r="BC28" s="25" t="n">
         <f aca="false">AV28*1000</f>
         <v>1190</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="28" t="n">
+      <c r="B29" s="27" t="n">
         <v>136</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="21" t="n">
         <f aca="false">1000*B29/$P29</f>
         <v>641.88790560472</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="28" t="n">
         <v>84</v>
       </c>
-      <c r="E29" s="22" t="n">
+      <c r="E29" s="21" t="n">
         <f aca="false">1000*D29/$P29</f>
         <v>396.46017699115</v>
       </c>
-      <c r="F29" s="30" t="n">
+      <c r="F29" s="29" t="n">
         <v>24.9</v>
       </c>
-      <c r="G29" s="22" t="n">
+      <c r="G29" s="21" t="n">
         <f aca="false">1000*F29/$P29</f>
         <v>117.522123893805</v>
       </c>
-      <c r="H29" s="28" t="n">
+      <c r="H29" s="27" t="n">
         <v>330</v>
       </c>
-      <c r="I29" s="22" t="n">
+      <c r="I29" s="21" t="n">
         <f aca="false">1000*H29/$P29</f>
         <v>1557.52212389381</v>
       </c>
@@ -6494,7 +6488,7 @@
         <f aca="false">AK29*1000</f>
         <v>1950</v>
       </c>
-      <c r="AO29" s="25" t="s">
+      <c r="AO29" s="24" t="s">
         <v>115</v>
       </c>
       <c r="AP29" s="1" t="n">
@@ -6503,15 +6497,15 @@
       <c r="AQ29" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AR29" s="25" t="n">
+      <c r="AR29" s="24" t="n">
         <f aca="false">AP29+AQ29/10</f>
         <v>6.4</v>
       </c>
-      <c r="AS29" s="25" t="n">
+      <c r="AS29" s="24" t="n">
         <f aca="false">1000*AR29</f>
         <v>6400</v>
       </c>
-      <c r="AU29" s="26" t="s">
+      <c r="AU29" s="25" t="s">
         <v>114</v>
       </c>
       <c r="AV29" s="0" t="n">
@@ -6529,43 +6523,43 @@
       <c r="AZ29" s="0" t="n">
         <v>3.8</v>
       </c>
-      <c r="BA29" s="26" t="s">
+      <c r="BA29" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="BC29" s="26" t="n">
+      <c r="BC29" s="25" t="n">
         <f aca="false">AV29*1000</f>
         <v>1950</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="21" t="n">
         <v>133</v>
       </c>
-      <c r="C30" s="22" t="n">
+      <c r="C30" s="21" t="n">
         <f aca="false">1000*B30/$P30</f>
         <v>617.708255926284</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="21" t="n">
         <f aca="false">1000*D30/$P30</f>
         <v>139.332689306681</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="23" t="n">
         <v>1.9</v>
       </c>
-      <c r="G30" s="22" t="n">
+      <c r="G30" s="21" t="n">
         <f aca="false">1000*F30/$P30</f>
         <v>8.82440365608977</v>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="H30" s="21" t="n">
         <v>121</v>
       </c>
-      <c r="I30" s="22" t="n">
+      <c r="I30" s="21" t="n">
         <f aca="false">1000*H30/$P30</f>
         <v>561.975180203611</v>
       </c>
@@ -6646,7 +6640,7 @@
         <f aca="false">AK30*1000</f>
         <v>620</v>
       </c>
-      <c r="AO30" s="25" t="s">
+      <c r="AO30" s="24" t="s">
         <v>117</v>
       </c>
       <c r="AP30" s="1" t="n">
@@ -6655,15 +6649,15 @@
       <c r="AQ30" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AR30" s="25" t="n">
+      <c r="AR30" s="24" t="n">
         <f aca="false">AP30+AQ30/10</f>
         <v>3.2</v>
       </c>
-      <c r="AS30" s="25" t="n">
+      <c r="AS30" s="24" t="n">
         <f aca="false">1000*AR30</f>
         <v>3200</v>
       </c>
-      <c r="AU30" s="26" t="s">
+      <c r="AU30" s="25" t="s">
         <v>118</v>
       </c>
       <c r="AV30" s="0" t="n">
@@ -6681,43 +6675,43 @@
       <c r="AZ30" s="0" t="n">
         <v>0.92</v>
       </c>
-      <c r="BA30" s="26" t="s">
+      <c r="BA30" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="BC30" s="26" t="n">
+      <c r="BC30" s="25" t="n">
         <f aca="false">AV30*1000</f>
         <v>620</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="28" t="n">
+      <c r="B31" s="27" t="n">
         <v>76</v>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C31" s="21" t="n">
         <f aca="false">1000*B31/$P31</f>
         <v>781.105469793829</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="28" t="n">
         <v>37</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="21" t="n">
         <f aca="false">1000*D31/$P31</f>
         <v>380.275031346996</v>
       </c>
-      <c r="F31" s="28" t="n">
+      <c r="F31" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="22" t="n">
+      <c r="G31" s="21" t="n">
         <f aca="false">1000*F31/$P31</f>
         <v>0</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="I31" s="22" t="n">
+      <c r="I31" s="21" t="n">
         <f aca="false">1000*H31/$P31</f>
         <v>195.276367448457</v>
       </c>
@@ -6778,7 +6772,7 @@
         <f aca="false">Y31/P31/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AA31" s="35"/>
+      <c r="AA31" s="34"/>
       <c r="AC31" s="1" t="n">
         <v>136.8</v>
       </c>
@@ -6799,7 +6793,7 @@
         <f aca="false">AK31*1000</f>
         <v>400</v>
       </c>
-      <c r="AO31" s="25" t="s">
+      <c r="AO31" s="24" t="s">
         <v>120</v>
       </c>
       <c r="AP31" s="1" t="n">
@@ -6808,15 +6802,15 @@
       <c r="AQ31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AR31" s="25" t="n">
+      <c r="AR31" s="24" t="n">
         <f aca="false">AP31+AQ31/10</f>
         <v>1.3</v>
       </c>
-      <c r="AS31" s="25" t="n">
+      <c r="AS31" s="24" t="n">
         <f aca="false">1000*AR31</f>
         <v>1300</v>
       </c>
-      <c r="AU31" s="26" t="s">
+      <c r="AU31" s="25" t="s">
         <v>121</v>
       </c>
       <c r="AV31" s="0" t="n">
@@ -6834,43 +6828,43 @@
       <c r="AZ31" s="0" t="n">
         <v>0.19</v>
       </c>
-      <c r="BA31" s="26" t="s">
+      <c r="BA31" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="BC31" s="26" t="n">
+      <c r="BC31" s="25" t="n">
         <f aca="false">AV31*1000</f>
         <v>50</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C32" s="21" t="n">
         <f aca="false">1000*B32/$P32</f>
         <v>641.137728041033</v>
       </c>
-      <c r="D32" s="23" t="n">
+      <c r="D32" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="22" t="n">
+      <c r="E32" s="21" t="n">
         <f aca="false">1000*D32/$P32</f>
         <v>271.997824017408</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="23" t="n">
         <v>0.4</v>
       </c>
-      <c r="G32" s="22" t="n">
+      <c r="G32" s="21" t="n">
         <f aca="false">1000*F32/$P32</f>
         <v>7.77136640049737</v>
       </c>
-      <c r="H32" s="22" t="n">
+      <c r="H32" s="21" t="n">
         <v>75</v>
       </c>
-      <c r="I32" s="22" t="n">
+      <c r="I32" s="21" t="n">
         <f aca="false">1000*H32/$P32</f>
         <v>1457.13120009326</v>
       </c>
@@ -6951,7 +6945,7 @@
         <f aca="false">AK32*1000</f>
         <v>300</v>
       </c>
-      <c r="AO32" s="25" t="s">
+      <c r="AO32" s="24" t="s">
         <v>123</v>
       </c>
       <c r="AP32" s="1" t="n">
@@ -6960,15 +6954,15 @@
       <c r="AQ32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AR32" s="25" t="n">
+      <c r="AR32" s="24" t="n">
         <f aca="false">AP32+AQ32/10</f>
         <v>1.1</v>
       </c>
-      <c r="AS32" s="25" t="n">
+      <c r="AS32" s="24" t="n">
         <f aca="false">1000*AR32</f>
         <v>1100</v>
       </c>
-      <c r="AU32" s="26" t="s">
+      <c r="AU32" s="25" t="s">
         <v>124</v>
       </c>
       <c r="AV32" s="0" t="n">
@@ -6986,43 +6980,43 @@
       <c r="AZ32" s="0" t="n">
         <v>0.22</v>
       </c>
-      <c r="BA32" s="26" t="s">
+      <c r="BA32" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="BC32" s="26" t="n">
+      <c r="BC32" s="25" t="n">
         <f aca="false">AV32*1000</f>
         <v>30</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="27" t="n">
         <v>683</v>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="21" t="n">
         <f aca="false">1000*B33/$P33</f>
         <v>562.985554433614</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="28" t="n">
         <v>830</v>
       </c>
-      <c r="E33" s="22" t="n">
+      <c r="E33" s="21" t="n">
         <f aca="false">1000*D33/$P33</f>
         <v>684.155212562079</v>
       </c>
-      <c r="F33" s="30" t="n">
+      <c r="F33" s="29" t="n">
         <v>240.6</v>
       </c>
-      <c r="G33" s="22" t="n">
+      <c r="G33" s="21" t="n">
         <f aca="false">1000*F33/$P33</f>
         <v>198.32258330414</v>
       </c>
-      <c r="H33" s="28" t="n">
+      <c r="H33" s="27" t="n">
         <v>2151</v>
       </c>
-      <c r="I33" s="22" t="n">
+      <c r="I33" s="21" t="n">
         <f aca="false">1000*H33/$P33</f>
         <v>1773.033568941</v>
       </c>
@@ -7107,7 +7101,7 @@
         <f aca="false">AK33*1000</f>
         <v>9330</v>
       </c>
-      <c r="AO33" s="25" t="s">
+      <c r="AO33" s="24" t="s">
         <v>128</v>
       </c>
       <c r="AP33" s="1" t="n">
@@ -7116,15 +7110,15 @@
       <c r="AQ33" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AR33" s="25" t="n">
+      <c r="AR33" s="24" t="n">
         <f aca="false">AP33+AQ33/10</f>
         <v>30.9</v>
       </c>
-      <c r="AS33" s="25" t="n">
+      <c r="AS33" s="24" t="n">
         <f aca="false">1000*AR33</f>
         <v>30900</v>
       </c>
-      <c r="AU33" s="26" t="s">
+      <c r="AU33" s="25" t="s">
         <v>127</v>
       </c>
       <c r="AV33" s="0" t="n">
@@ -7142,43 +7136,43 @@
       <c r="AZ33" s="0" t="n">
         <v>3.24</v>
       </c>
-      <c r="BA33" s="26" t="s">
+      <c r="BA33" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="BC33" s="26" t="n">
+      <c r="BC33" s="25" t="n">
         <f aca="false">AV33*1000</f>
         <v>9330</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="21" t="n">
         <v>189</v>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="21" t="n">
         <f aca="false">1000*B34/$P34</f>
         <v>341.958899796996</v>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D34" s="22" t="n">
         <v>601</v>
       </c>
-      <c r="E34" s="22" t="n">
+      <c r="E34" s="21" t="n">
         <f aca="false">1000*D34/$P34</f>
         <v>1087.39311522748</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="23" t="n">
         <v>245.1</v>
       </c>
-      <c r="G34" s="22" t="n">
+      <c r="G34" s="21" t="n">
         <f aca="false">1000*F34/$P34</f>
         <v>443.460985927215</v>
       </c>
-      <c r="H34" s="22" t="n">
+      <c r="H34" s="21" t="n">
         <v>712</v>
       </c>
-      <c r="I34" s="22" t="n">
+      <c r="I34" s="21" t="n">
         <f aca="false">1000*H34/$P34</f>
         <v>1288.22611987016</v>
       </c>
@@ -7259,7 +7253,7 @@
         <f aca="false">AK34*1000</f>
         <v>1160</v>
       </c>
-      <c r="AO34" s="25" t="s">
+      <c r="AO34" s="24" t="s">
         <v>132</v>
       </c>
       <c r="AP34" s="1" t="n">
@@ -7268,15 +7262,15 @@
       <c r="AQ34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AR34" s="25" t="n">
+      <c r="AR34" s="24" t="n">
         <f aca="false">AP34+AQ34/10</f>
         <v>7.1</v>
       </c>
-      <c r="AS34" s="25" t="n">
+      <c r="AS34" s="24" t="n">
         <f aca="false">1000*AR34</f>
         <v>7100</v>
       </c>
-      <c r="AU34" s="26" t="s">
+      <c r="AU34" s="25" t="s">
         <v>131</v>
       </c>
       <c r="AV34" s="0" t="n">
@@ -7294,34 +7288,34 @@
       <c r="AZ34" s="0" t="n">
         <v>1.08</v>
       </c>
-      <c r="BA34" s="26" t="s">
+      <c r="BA34" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="BC34" s="26" t="n">
+      <c r="BC34" s="25" t="n">
         <f aca="false">AV34*1000</f>
         <v>1160</v>
       </c>
     </row>
-    <row r="35" s="40" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="36" t="s">
+    <row r="35" s="39" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="37" t="n">
+      <c r="B35" s="36" t="n">
         <v>5847</v>
       </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="38" t="n">
+      <c r="C35" s="36"/>
+      <c r="D35" s="37" t="n">
         <v>9557</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="39" t="n">
+      <c r="E35" s="36"/>
+      <c r="F35" s="38" t="n">
         <v>8334.6</v>
       </c>
-      <c r="G35" s="39"/>
-      <c r="H35" s="37" t="n">
+      <c r="G35" s="38"/>
+      <c r="H35" s="36" t="n">
         <v>26264</v>
       </c>
-      <c r="I35" s="37"/>
+      <c r="I35" s="36"/>
       <c r="J35" s="1" t="n">
         <f aca="false">SUM(J8:J34)</f>
         <v>8092</v>
@@ -7335,7 +7329,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="40" t="n">
+      <c r="Q35" s="39" t="n">
         <v>100</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -7349,7 +7343,7 @@
         <v>38340.8</v>
       </c>
       <c r="V35" s="1"/>
-      <c r="W35" s="40" t="e">
+      <c r="W35" s="39" t="e">
         <f aca="false">ROUND(U35/P35 *100/1000, 2)</f>
         <v>#DIV/0!</v>
       </c>
@@ -7358,14 +7352,14 @@
         <v>-24000</v>
       </c>
       <c r="Z35" s="1"/>
-      <c r="AC35" s="40" t="n">
+      <c r="AC35" s="39" t="n">
         <v>18796</v>
       </c>
-      <c r="AL35" s="40" t="n">
+      <c r="AL35" s="39" t="n">
         <f aca="false">SUM(AL8:AL34)</f>
         <v>47600</v>
       </c>
-      <c r="AR35" s="40" t="n">
+      <c r="AR35" s="39" t="n">
         <f aca="false">SUM(AR8:AR34)</f>
         <v>299.1</v>
       </c>
@@ -7416,214 +7410,214 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="41" t="n">
+      <c r="J37" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="K37" s="42"/>
-      <c r="M37" s="41" t="n">
+      <c r="K37" s="41"/>
+      <c r="M37" s="40" t="n">
         <v>13.6</v>
       </c>
-      <c r="N37" s="42"/>
+      <c r="N37" s="41"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="44" t="n">
+      <c r="C38" s="43" t="n">
         <f aca="false">SUM(B35:M35)</f>
         <v>98772.2</v>
       </c>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
       <c r="J38" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="N38" s="45"/>
+      <c r="N38" s="44"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="43"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="43"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="P40" s="46" t="s">
+      <c r="B40" s="42"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="P40" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="Q40" s="47" t="n">
+      <c r="Q40" s="46" t="n">
         <v>192.8</v>
       </c>
-      <c r="R40" s="48"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="48"/>
-      <c r="U40" s="25"/>
-      <c r="V40" s="25"/>
+      <c r="R40" s="47"/>
+      <c r="S40" s="47"/>
+      <c r="T40" s="47"/>
+      <c r="U40" s="24"/>
+      <c r="V40" s="24"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P41" s="46" t="s">
+      <c r="P41" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="Q41" s="46" t="n">
+      <c r="Q41" s="45" t="n">
         <f aca="false">Q40*0.7</f>
         <v>134.96</v>
       </c>
-      <c r="R41" s="48"/>
-      <c r="S41" s="48"/>
-      <c r="T41" s="48"/>
-      <c r="U41" s="25"/>
-      <c r="V41" s="25"/>
+      <c r="R41" s="47"/>
+      <c r="S41" s="47"/>
+      <c r="T41" s="47"/>
+      <c r="U41" s="24"/>
+      <c r="V41" s="24"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P42" s="46"/>
-      <c r="Q42" s="46"/>
-      <c r="R42" s="48"/>
-      <c r="S42" s="48"/>
-      <c r="T42" s="48"/>
-      <c r="U42" s="25"/>
-      <c r="V42" s="25"/>
+      <c r="P42" s="45"/>
+      <c r="Q42" s="45"/>
+      <c r="R42" s="47"/>
+      <c r="S42" s="47"/>
+      <c r="T42" s="47"/>
+      <c r="U42" s="24"/>
+      <c r="V42" s="24"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P43" s="49" t="s">
+      <c r="P43" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="Q43" s="50" t="n">
+      <c r="Q43" s="49" t="n">
         <v>30</v>
       </c>
-      <c r="R43" s="48"/>
-      <c r="S43" s="48"/>
-      <c r="T43" s="48"/>
-      <c r="U43" s="25"/>
-      <c r="V43" s="25"/>
+      <c r="R43" s="47"/>
+      <c r="S43" s="47"/>
+      <c r="T43" s="47"/>
+      <c r="U43" s="24"/>
+      <c r="V43" s="24"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P44" s="49" t="s">
+      <c r="P44" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="Q44" s="49" t="n">
+      <c r="Q44" s="48" t="n">
         <f aca="false">R36/1000 -Q43</f>
         <v>68.7761</v>
       </c>
-      <c r="R44" s="48"/>
-      <c r="S44" s="48"/>
-      <c r="T44" s="48"/>
-      <c r="U44" s="25"/>
-      <c r="V44" s="25"/>
+      <c r="R44" s="47"/>
+      <c r="S44" s="47"/>
+      <c r="T44" s="47"/>
+      <c r="U44" s="24"/>
+      <c r="V44" s="24"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P45" s="49" t="s">
+      <c r="P45" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="Q45" s="49" t="n">
+      <c r="Q45" s="48" t="n">
         <f aca="false">Q44-Q46-Q47</f>
         <v>30.7761</v>
       </c>
-      <c r="R45" s="48"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="25"/>
-      <c r="V45" s="25"/>
+      <c r="R45" s="47"/>
+      <c r="S45" s="47"/>
+      <c r="T45" s="47"/>
+      <c r="U45" s="24"/>
+      <c r="V45" s="24"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P46" s="49" t="s">
+      <c r="P46" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="Q46" s="50" t="n">
+      <c r="Q46" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="R46" s="48"/>
-      <c r="S46" s="48"/>
-      <c r="T46" s="48"/>
-      <c r="U46" s="25"/>
-      <c r="V46" s="25"/>
+      <c r="R46" s="47"/>
+      <c r="S46" s="47"/>
+      <c r="T46" s="47"/>
+      <c r="U46" s="24"/>
+      <c r="V46" s="24"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P47" s="49" t="s">
+      <c r="P47" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="Q47" s="50" t="n">
+      <c r="Q47" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="R47" s="48"/>
-      <c r="S47" s="48"/>
-      <c r="T47" s="48"/>
-      <c r="U47" s="25"/>
-      <c r="V47" s="25"/>
+      <c r="R47" s="47"/>
+      <c r="S47" s="47"/>
+      <c r="T47" s="47"/>
+      <c r="U47" s="24"/>
+      <c r="V47" s="24"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25"/>
-      <c r="P48" s="49" t="s">
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="P48" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="Q48" s="49" t="n">
+      <c r="Q48" s="48" t="n">
         <f aca="false">Q40+Q46</f>
         <v>206.8</v>
       </c>
-      <c r="R48" s="48"/>
-      <c r="S48" s="48"/>
-      <c r="T48" s="48"/>
-      <c r="U48" s="25"/>
-      <c r="V48" s="25"/>
+      <c r="R48" s="47"/>
+      <c r="S48" s="47"/>
+      <c r="T48" s="47"/>
+      <c r="U48" s="24"/>
+      <c r="V48" s="24"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="25"/>
-      <c r="I49" s="25"/>
-      <c r="P49" s="49" t="s">
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="P49" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="Q49" s="49" t="n">
+      <c r="Q49" s="48" t="n">
         <f aca="false">Q41-Q45</f>
         <v>104.1839</v>
       </c>
-      <c r="R49" s="48"/>
-      <c r="S49" s="48"/>
-      <c r="T49" s="48"/>
-      <c r="U49" s="25"/>
-      <c r="V49" s="25"/>
+      <c r="R49" s="47"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="47"/>
+      <c r="U49" s="24"/>
+      <c r="V49" s="24"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25"/>
-      <c r="I50" s="25"/>
-      <c r="P50" s="49" t="s">
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="P50" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="Q50" s="49" t="n">
+      <c r="Q50" s="48" t="n">
         <f aca="false">Q49/Q48</f>
         <v>0.503790618955513</v>
       </c>
-      <c r="R50" s="48"/>
-      <c r="S50" s="48"/>
-      <c r="T50" s="48"/>
-      <c r="U50" s="25"/>
-      <c r="V50" s="25"/>
+      <c r="R50" s="47"/>
+      <c r="S50" s="47"/>
+      <c r="T50" s="47"/>
+      <c r="U50" s="24"/>
+      <c r="V50" s="24"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="51"/>
+      <c r="A53" s="50"/>
       <c r="U53" s="1" t="s">
         <v>147</v>
       </c>
@@ -7633,7 +7627,7 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="51"/>
+      <c r="A55" s="50"/>
       <c r="J55" s="1" t="s">
         <v>5</v>
       </c>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -2372,11 +2372,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="31480390"/>
-        <c:axId val="55153828"/>
+        <c:axId val="594606"/>
+        <c:axId val="46595793"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="31480390"/>
+        <c:axId val="594606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2404,7 +2404,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55153828"/>
+        <c:crossAx val="46595793"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2412,7 +2412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55153828"/>
+        <c:axId val="46595793"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2449,7 +2449,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31480390"/>
+        <c:crossAx val="594606"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -476,10 +476,10 @@
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.00E+00"/>
-    <numFmt numFmtId="169" formatCode="General"/>
+    <numFmt numFmtId="169" formatCode="#,##0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -556,22 +556,17 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF8A65"/>
-        <bgColor rgb="FFDF979A"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -686,7 +681,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -699,11 +694,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -711,23 +710,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -735,15 +734,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -751,119 +762,139 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -871,19 +902,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -900,23 +919,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -940,7 +942,7 @@
       <rgbColor rgb="FFF2F7FF"/>
       <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF650953"/>
-      <rgbColor rgb="FFFF8A65"/>
+      <rgbColor rgb="FFDF979A"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFD1C4E9"/>
       <rgbColor rgb="FF000080"/>
@@ -957,7 +959,7 @@
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF83CAFF"/>
       <rgbColor rgb="FFFFAB91"/>
-      <rgbColor rgb="FFDF979A"/>
+      <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCDD2"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -992,10 +994,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.120695043440215"/>
-          <c:y val="0.0304478275363929"/>
-          <c:w val="0.693168323020189"/>
-          <c:h val="0.776752972552506"/>
+          <c:x val="0.120692041522491"/>
+          <c:y val="0.0304310380182914"/>
+          <c:w val="0.693148788927336"/>
+          <c:h val="0.776729688717549"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -1032,11 +1034,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1143,7 +1150,7 @@
             <c:numRef>
               <c:f>Combined_2!$C$8:$C$34</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>345.61025947732</c:v>
@@ -1260,11 +1267,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1371,7 +1383,7 @@
             <c:numRef>
               <c:f>Combined_2!$E$8:$E$34</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>808.87507537245</c:v>
@@ -1488,11 +1500,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1599,7 +1616,7 @@
             <c:numRef>
               <c:f>Combined_2!$G$8:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>64.710006029796</c:v>
@@ -1716,11 +1733,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1827,7 +1849,7 @@
             <c:numRef>
               <c:f>Combined_2!$I$8:$I$34</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>2255.04566467471</c:v>
@@ -1944,11 +1966,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -2058,7 +2085,7 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>791.717119228186</c:v>
+                  <c:v>454.195610504591</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>368.865393719426</c:v>
@@ -2079,7 +2106,7 @@
                   <c:v>551.431540391428</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4951.61655717014</c:v>
+                  <c:v>495.161655717014</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>479.235103188245</c:v>
@@ -2088,7 +2115,7 @@
                   <c:v>355.228059055014</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>291.728270131798</c:v>
+                  <c:v>275.318554936884</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2387.20484738585</c:v>
@@ -2127,10 +2154,10 @@
                   <c:v>489.522181764138</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>698.883841394479</c:v>
+                  <c:v>87.3604801743099</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>990.849216063414</c:v>
+                  <c:v>99.0849216063414</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>1307.39588270447</c:v>
@@ -2172,11 +2199,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -2372,17 +2404,17 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="594606"/>
-        <c:axId val="46595793"/>
+        <c:axId val="29288581"/>
+        <c:axId val="48883956"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="594606"/>
+        <c:axId val="29288581"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2399,12 +2431,16 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46595793"/>
+        <c:crossAx val="48883956"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2412,7 +2448,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46595793"/>
+        <c:axId val="48883956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2427,7 +2463,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2444,12 +2480,16 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="594606"/>
+        <c:crossAx val="29288581"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2477,7 +2517,11 @@
         <a:p>
           <a:pPr>
             <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
               <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -2508,9 +2552,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>219960</xdr:colOff>
+      <xdr:colOff>219600</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>117720</xdr:rowOff>
+      <xdr:rowOff>117360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2519,7 +2563,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3526200" y="8258760"/>
-        <a:ext cx="15606000" cy="8777880"/>
+        <a:ext cx="15605640" cy="8777520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2660,11 +2704,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="3" width="17.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="3" width="14.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="22.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="14.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="11.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16377" min="16342" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16378" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16342" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" s="12" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2714,13 +2757,13 @@
       <c r="AC1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="XEX1" s="0"/>
-      <c r="XEY1" s="0"/>
-      <c r="XEZ1" s="0"/>
-      <c r="XFA1" s="0"/>
-      <c r="XFB1" s="0"/>
-      <c r="XFC1" s="0"/>
-      <c r="XFD1" s="0"/>
+      <c r="XEX1" s="1"/>
+      <c r="XEY1" s="1"/>
+      <c r="XEZ1" s="1"/>
+      <c r="XFA1" s="1"/>
+      <c r="XFB1" s="1"/>
+      <c r="XFC1" s="1"/>
+      <c r="XFD1" s="1"/>
     </row>
     <row r="2" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
@@ -2786,13 +2829,13 @@
       <c r="AC2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="XEX2" s="0"/>
-      <c r="XEY2" s="0"/>
-      <c r="XEZ2" s="0"/>
-      <c r="XFA2" s="0"/>
-      <c r="XFB2" s="0"/>
-      <c r="XFC2" s="0"/>
-      <c r="XFD2" s="0"/>
+      <c r="XEX2" s="1"/>
+      <c r="XEY2" s="1"/>
+      <c r="XEZ2" s="1"/>
+      <c r="XFA2" s="1"/>
+      <c r="XFB2" s="1"/>
+      <c r="XFC2" s="1"/>
+      <c r="XFD2" s="1"/>
     </row>
     <row r="3" s="14" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
@@ -2851,13 +2894,13 @@
       <c r="AC3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="XEX3" s="0"/>
-      <c r="XEY3" s="0"/>
-      <c r="XEZ3" s="0"/>
-      <c r="XFA3" s="0"/>
-      <c r="XFB3" s="0"/>
-      <c r="XFC3" s="0"/>
-      <c r="XFD3" s="0"/>
+      <c r="XEX3" s="1"/>
+      <c r="XEY3" s="1"/>
+      <c r="XEZ3" s="1"/>
+      <c r="XFA3" s="1"/>
+      <c r="XFB3" s="1"/>
+      <c r="XFC3" s="1"/>
+      <c r="XFD3" s="1"/>
     </row>
     <row r="4" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
@@ -2929,13 +2972,13 @@
       <c r="XEU4" s="17"/>
       <c r="XEV4" s="17"/>
       <c r="XEW4" s="17"/>
-      <c r="XEX4" s="0"/>
-      <c r="XEY4" s="0"/>
-      <c r="XEZ4" s="0"/>
-      <c r="XFA4" s="0"/>
-      <c r="XFB4" s="0"/>
-      <c r="XFC4" s="0"/>
-      <c r="XFD4" s="0"/>
+      <c r="XEX4" s="1"/>
+      <c r="XEY4" s="1"/>
+      <c r="XEZ4" s="1"/>
+      <c r="XFA4" s="1"/>
+      <c r="XFB4" s="1"/>
+      <c r="XFC4" s="1"/>
+      <c r="XFD4" s="1"/>
     </row>
     <row r="5" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
@@ -3007,13 +3050,13 @@
       <c r="XEU5" s="17"/>
       <c r="XEV5" s="17"/>
       <c r="XEW5" s="17"/>
-      <c r="XEX5" s="0"/>
-      <c r="XEY5" s="0"/>
-      <c r="XEZ5" s="0"/>
-      <c r="XFA5" s="0"/>
-      <c r="XFB5" s="0"/>
-      <c r="XFC5" s="0"/>
-      <c r="XFD5" s="0"/>
+      <c r="XEX5" s="1"/>
+      <c r="XEY5" s="1"/>
+      <c r="XEZ5" s="1"/>
+      <c r="XFA5" s="1"/>
+      <c r="XFB5" s="1"/>
+      <c r="XFC5" s="1"/>
+      <c r="XFD5" s="1"/>
     </row>
     <row r="6" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
@@ -3079,13 +3122,13 @@
       <c r="XEU6" s="17"/>
       <c r="XEV6" s="17"/>
       <c r="XEW6" s="17"/>
-      <c r="XEX6" s="0"/>
-      <c r="XEY6" s="0"/>
-      <c r="XEZ6" s="0"/>
-      <c r="XFA6" s="0"/>
-      <c r="XFB6" s="0"/>
-      <c r="XFC6" s="0"/>
-      <c r="XFD6" s="0"/>
+      <c r="XEX6" s="1"/>
+      <c r="XEY6" s="1"/>
+      <c r="XEZ6" s="1"/>
+      <c r="XFA6" s="1"/>
+      <c r="XFB6" s="1"/>
+      <c r="XFC6" s="1"/>
+      <c r="XFD6" s="1"/>
     </row>
     <row r="7" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
@@ -3162,4235 +3205,5422 @@
       <c r="XEU7" s="17"/>
       <c r="XEV7" s="17"/>
       <c r="XEW7" s="17"/>
-      <c r="XEX7" s="0"/>
-      <c r="XEY7" s="0"/>
-      <c r="XEZ7" s="0"/>
-      <c r="XFA7" s="0"/>
-      <c r="XFB7" s="0"/>
-      <c r="XFC7" s="0"/>
-      <c r="XFD7" s="0"/>
+      <c r="XEX7" s="1"/>
+      <c r="XEY7" s="1"/>
+      <c r="XEZ7" s="1"/>
+      <c r="XFA7" s="1"/>
+      <c r="XFB7" s="1"/>
+      <c r="XFC7" s="1"/>
+      <c r="XFD7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>141</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="22" t="n">
         <f aca="false">1000*B8/$P8</f>
         <v>345.61025947732</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>330</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="22" t="n">
         <f aca="false">1000*D8/$P8</f>
         <v>808.87507537245</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="21" t="n">
         <v>26.4</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="22" t="n">
         <f aca="false">1000*F8/$P8</f>
         <v>64.710006029796</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>920</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="22" t="n">
         <f aca="false">1000*H8/$P8</f>
         <v>2255.04566467471</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="24" t="n">
         <f aca="false">L8*$J$37/100</f>
-        <v>323</v>
-      </c>
-      <c r="K8" s="2" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="K8" s="25" t="n">
         <f aca="false">1000*J8/P8</f>
-        <v>791.717119228186</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="M8" s="1" t="n">
+        <v>454.195610504591</v>
+      </c>
+      <c r="L8" s="24" t="n">
+        <v>1090</v>
+      </c>
+      <c r="M8" s="24" t="n">
         <f aca="false">O8*$M$37/100</f>
         <v>1346.4</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="25" t="n">
         <f aca="false">1000*M8/P8</f>
         <v>3300.2103075196</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="O8" s="24" t="n">
         <v>9900</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="P8" s="25" t="n">
         <v>407.974</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="Q8" s="25" t="n">
         <f aca="false">100*P8/$P$36</f>
         <v>2.80209736617656</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="26" t="n">
         <f aca="false">H8+F8+B8+D8+J8+M8</f>
-        <v>3086.8</v>
-      </c>
-      <c r="S8" s="3" t="n">
+        <v>2949.1</v>
+      </c>
+      <c r="S8" s="27" t="n">
         <f aca="false">R8/P8</f>
-        <v>7.56616843230206</v>
-      </c>
-      <c r="U8" s="1" t="n">
+        <v>7.22864692357847</v>
+      </c>
+      <c r="T8" s="26"/>
+      <c r="U8" s="25" t="n">
         <f aca="false">-T8+($Q$45 + $Q$46)*1000*Q8/100</f>
-        <v>1254.66991877658</v>
-      </c>
-      <c r="V8" s="1" t="n">
+        <v>1242.28464841808</v>
+      </c>
+      <c r="V8" s="25" t="n">
         <f aca="false">U8/P8/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W8" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W8" s="25" t="n">
         <f aca="false">U8/P8</f>
-        <v>3.07536734884228</v>
-      </c>
-      <c r="Y8" s="1" t="n">
+        <v>3.04500935946429</v>
+      </c>
+      <c r="Y8" s="25" t="n">
         <f aca="false">-Q8*($Q$47)*10</f>
         <v>-672.503367882374</v>
       </c>
-      <c r="Z8" s="1" t="n">
+      <c r="Z8" s="25" t="n">
         <f aca="false">Y8/P8/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC8" s="1" t="n">
+      <c r="AC8" s="24" t="n">
         <v>514.3</v>
       </c>
-      <c r="AH8" s="1" t="s">
+      <c r="AH8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="AI8" s="1" t="n">
+      <c r="AI8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AJ8" s="1" t="n">
+      <c r="AJ8" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="AK8" s="1" t="n">
+      <c r="AK8" s="24" t="n">
         <f aca="false">AI8+AJ8/100</f>
         <v>1.9</v>
       </c>
-      <c r="AL8" s="1" t="n">
+      <c r="AL8" s="24" t="n">
         <f aca="false">AK8*1000</f>
         <v>1900</v>
       </c>
-      <c r="AO8" s="24" t="s">
+      <c r="AO8" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="AP8" s="1" t="n">
+      <c r="AP8" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="AQ8" s="1" t="n">
+      <c r="AQ8" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="AR8" s="24" t="n">
+      <c r="AR8" s="29" t="n">
         <f aca="false">AP8+AQ8/10</f>
         <v>9.9</v>
       </c>
-      <c r="AS8" s="24" t="n">
+      <c r="AS8" s="29" t="n">
         <f aca="false">1000*AR8</f>
         <v>9900</v>
       </c>
-      <c r="AU8" s="25" t="s">
+      <c r="AU8" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="AV8" s="0" t="n">
+      <c r="AV8" s="24" t="n">
         <v>1.09</v>
       </c>
-      <c r="AW8" s="0" t="n">
+      <c r="AW8" s="24" t="n">
         <v>2.43</v>
       </c>
-      <c r="AX8" s="0" t="n">
+      <c r="AX8" s="24" t="n">
         <v>2.81</v>
       </c>
-      <c r="AY8" s="0" t="n">
+      <c r="AY8" s="24" t="n">
         <v>0.86</v>
       </c>
-      <c r="AZ8" s="0" t="n">
+      <c r="AZ8" s="24" t="n">
         <v>1.17</v>
       </c>
-      <c r="BA8" s="25" t="s">
+      <c r="BA8" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="BC8" s="25" t="n">
+      <c r="BC8" s="29" t="n">
         <f aca="false">AV8*1000</f>
         <v>1090</v>
       </c>
+      <c r="XDN8" s="24"/>
+      <c r="XDO8" s="24"/>
+      <c r="XDP8" s="24"/>
+      <c r="XDQ8" s="24"/>
+      <c r="XDR8" s="24"/>
+      <c r="XDS8" s="24"/>
+      <c r="XDT8" s="24"/>
+      <c r="XDU8" s="24"/>
+      <c r="XDV8" s="24"/>
+      <c r="XDW8" s="24"/>
+      <c r="XDX8" s="24"/>
+      <c r="XDY8" s="24"/>
+      <c r="XDZ8" s="24"/>
+      <c r="XEA8" s="24"/>
+      <c r="XEB8" s="24"/>
+      <c r="XEC8" s="24"/>
+      <c r="XED8" s="24"/>
+      <c r="XEE8" s="24"/>
+      <c r="XEF8" s="24"/>
+      <c r="XEG8" s="24"/>
+      <c r="XEH8" s="24"/>
+      <c r="XEI8" s="24"/>
+      <c r="XEJ8" s="24"/>
+      <c r="XEK8" s="24"/>
+      <c r="XEL8" s="24"/>
+      <c r="XEM8" s="24"/>
+      <c r="XEN8" s="24"/>
+      <c r="XEO8" s="24"/>
+      <c r="XEP8" s="24"/>
+      <c r="XEQ8" s="24"/>
+      <c r="XER8" s="24"/>
+      <c r="XES8" s="24"/>
+      <c r="XET8" s="24"/>
+      <c r="XEU8" s="24"/>
+      <c r="XEV8" s="24"/>
+      <c r="XEW8" s="24"/>
+      <c r="XEX8" s="24"/>
+      <c r="XEY8" s="24"/>
+      <c r="XEZ8" s="24"/>
+      <c r="XFA8" s="24"/>
+      <c r="XFB8" s="24"/>
+      <c r="XFC8" s="24"/>
+      <c r="XFD8" s="24"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
+    <row r="9" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="31" t="n">
         <v>200</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="22" t="n">
         <f aca="false">1000*B9/$P9</f>
         <v>394.508442480669</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="32" t="n">
         <v>184</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="22" t="n">
         <f aca="false">1000*D9/$P9</f>
         <v>362.947767082216</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="31" t="n">
         <v>61.1</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="22" t="n">
         <f aca="false">1000*F9/$P9</f>
         <v>120.522329177844</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="31" t="n">
         <v>722</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="22" t="n">
         <f aca="false">1000*H9/$P9</f>
         <v>1424.17547735522</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="24" t="n">
         <f aca="false">L9*$J$37/100</f>
         <v>187</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="25" t="n">
         <f aca="false">1000*J9/P9</f>
         <v>368.865393719426</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="L9" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9" s="24" t="n">
         <f aca="false">O9*$M$37/100</f>
         <v>1332.8</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="25" t="n">
         <f aca="false">1000*M9/P9</f>
         <v>2629.00426069118</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="O9" s="24" t="n">
         <v>9800</v>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="P9" s="25" t="n">
         <v>506.96</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="Q9" s="25" t="n">
         <f aca="false">100*P9/$P$36</f>
         <v>3.48196522512922</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="26" t="n">
         <f aca="false">H9+F9+B9+D9+J9+M9</f>
         <v>2686.9</v>
       </c>
-      <c r="S9" s="3" t="n">
+      <c r="S9" s="27" t="n">
         <f aca="false">R9/P9</f>
         <v>5.30002367050655</v>
       </c>
-      <c r="T9" s="30" t="n">
+      <c r="T9" s="33" t="n">
         <f aca="false">F9</f>
         <v>61.1</v>
       </c>
-      <c r="U9" s="1" t="n">
+      <c r="U9" s="25" t="n">
         <f aca="false">-T9+($Q$45 + $Q$46)*1000*Q9/100</f>
-        <v>1497.98823116908</v>
-      </c>
-      <c r="V9" s="1" t="n">
+        <v>1482.59794487401</v>
+      </c>
+      <c r="V9" s="25" t="n">
         <f aca="false">U9/P9/10</f>
-        <v>0.295484501966444</v>
-      </c>
-      <c r="W9" s="1" t="n">
+        <v>0.292448703028644</v>
+      </c>
+      <c r="W9" s="25" t="n">
         <f aca="false">U9/P9</f>
-        <v>2.95484501966444</v>
-      </c>
-      <c r="Y9" s="1" t="n">
+        <v>2.92448703028644</v>
+      </c>
+      <c r="Y9" s="25" t="n">
         <f aca="false">-Q9*($Q$47)*10</f>
         <v>-835.671654031012</v>
       </c>
-      <c r="Z9" s="1" t="n">
+      <c r="Z9" s="25" t="n">
         <f aca="false">Y9/P9/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC9" s="1" t="n">
+      <c r="AC9" s="24" t="n">
         <v>642</v>
       </c>
-      <c r="AH9" s="1" t="s">
+      <c r="AH9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="AI9" s="1" t="n">
+      <c r="AI9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AJ9" s="1" t="n">
+      <c r="AJ9" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="AK9" s="1" t="n">
+      <c r="AK9" s="24" t="n">
         <f aca="false">AI9+AJ9/100</f>
         <v>1.1</v>
       </c>
-      <c r="AL9" s="1" t="n">
+      <c r="AL9" s="24" t="n">
         <f aca="false">AK9*1000</f>
         <v>1100</v>
       </c>
-      <c r="AO9" s="24" t="s">
+      <c r="AO9" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="AP9" s="1" t="n">
+      <c r="AP9" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="AQ9" s="1" t="n">
+      <c r="AQ9" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="AR9" s="24" t="n">
+      <c r="AR9" s="29" t="n">
         <f aca="false">AP9+AQ9/10</f>
         <v>9.8</v>
       </c>
-      <c r="AS9" s="24" t="n">
+      <c r="AS9" s="29" t="n">
         <f aca="false">1000*AR9</f>
         <v>9800</v>
       </c>
-      <c r="AU9" s="25" t="s">
+      <c r="AU9" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="AV9" s="0" t="n">
+      <c r="AV9" s="24" t="n">
         <v>1.1</v>
       </c>
-      <c r="AW9" s="0" t="n">
+      <c r="AW9" s="24" t="n">
         <v>2.45</v>
       </c>
-      <c r="AX9" s="0" t="n">
+      <c r="AX9" s="24" t="n">
         <v>3.46</v>
       </c>
-      <c r="AY9" s="0" t="n">
+      <c r="AY9" s="24" t="n">
         <v>0.71</v>
       </c>
-      <c r="AZ9" s="0" t="n">
+      <c r="AZ9" s="24" t="n">
         <v>0.96</v>
       </c>
-      <c r="BA9" s="25" t="s">
+      <c r="BA9" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="BC9" s="25" t="n">
+      <c r="BC9" s="29" t="n">
         <f aca="false">AV9*1000</f>
         <v>1100</v>
       </c>
+      <c r="XDN9" s="24"/>
+      <c r="XDO9" s="24"/>
+      <c r="XDP9" s="24"/>
+      <c r="XDQ9" s="24"/>
+      <c r="XDR9" s="24"/>
+      <c r="XDS9" s="24"/>
+      <c r="XDT9" s="24"/>
+      <c r="XDU9" s="24"/>
+      <c r="XDV9" s="24"/>
+      <c r="XDW9" s="24"/>
+      <c r="XDX9" s="24"/>
+      <c r="XDY9" s="24"/>
+      <c r="XDZ9" s="24"/>
+      <c r="XEA9" s="24"/>
+      <c r="XEB9" s="24"/>
+      <c r="XEC9" s="24"/>
+      <c r="XED9" s="24"/>
+      <c r="XEE9" s="24"/>
+      <c r="XEF9" s="24"/>
+      <c r="XEG9" s="24"/>
+      <c r="XEH9" s="24"/>
+      <c r="XEI9" s="24"/>
+      <c r="XEJ9" s="24"/>
+      <c r="XEK9" s="24"/>
+      <c r="XEL9" s="24"/>
+      <c r="XEM9" s="24"/>
+      <c r="XEN9" s="24"/>
+      <c r="XEO9" s="24"/>
+      <c r="XEP9" s="24"/>
+      <c r="XEQ9" s="24"/>
+      <c r="XER9" s="24"/>
+      <c r="XES9" s="24"/>
+      <c r="XET9" s="24"/>
+      <c r="XEU9" s="24"/>
+      <c r="XEV9" s="24"/>
+      <c r="XEW9" s="24"/>
+      <c r="XEX9" s="24"/>
+      <c r="XEY9" s="24"/>
+      <c r="XEZ9" s="24"/>
+      <c r="XFA9" s="24"/>
+      <c r="XFB9" s="24"/>
+      <c r="XFC9" s="24"/>
+      <c r="XFD9" s="24"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
         <v>46</v>
       </c>
       <c r="B10" s="21" t="n">
         <v>38</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="22" t="n">
         <f aca="false">1000*B10/$P10</f>
         <v>726.008291778911</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="22" t="n">
         <f aca="false">1000*D10/$P10</f>
         <v>343.898664526853</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="22" t="n">
         <f aca="false">1000*F10/$P10</f>
         <v>3.82109627252059</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="22" t="n">
         <f aca="false">1000*H10/$P10</f>
         <v>764.219254504117</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="24" t="n">
         <f aca="false">L10*$J$37/100</f>
         <v>45.9</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="25" t="n">
         <f aca="false">1000*J10/P10</f>
         <v>876.941594543475</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="L10" s="24" t="n">
         <v>270</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="24" t="n">
         <f aca="false">O10*$M$37/100</f>
         <v>217.6</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="25" t="n">
         <f aca="false">1000*M10/P10</f>
         <v>4157.3527445024</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="O10" s="24" t="n">
         <v>1600</v>
       </c>
-      <c r="P10" s="1" t="n">
+      <c r="P10" s="25" t="n">
         <v>52.341</v>
       </c>
-      <c r="Q10" s="1" t="n">
+      <c r="Q10" s="25" t="n">
         <f aca="false">100*P10/$P$36</f>
         <v>0.359494914487313</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="26" t="n">
         <f aca="false">H10+F10+B10+D10+J10+M10</f>
         <v>359.7</v>
       </c>
-      <c r="S10" s="3" t="n">
+      <c r="S10" s="27" t="n">
         <f aca="false">R10/P10</f>
         <v>6.87224164612827</v>
       </c>
-      <c r="U10" s="1" t="n">
+      <c r="T10" s="26"/>
+      <c r="U10" s="25" t="n">
         <f aca="false">-T10+($Q$45 + $Q$46)*1000*Q10/100</f>
-        <v>160.967802405754</v>
-      </c>
-      <c r="V10" s="1" t="n">
+        <v>159.37883488372</v>
+      </c>
+      <c r="V10" s="25" t="n">
         <f aca="false">U10/P10/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W10" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W10" s="25" t="n">
         <f aca="false">U10/P10</f>
-        <v>3.07536734884228</v>
-      </c>
-      <c r="Y10" s="1" t="n">
+        <v>3.04500935946428</v>
+      </c>
+      <c r="Y10" s="25" t="n">
         <f aca="false">-Q10*($Q$47)*10</f>
         <v>-86.2787794769552</v>
       </c>
-      <c r="Z10" s="1" t="n">
+      <c r="Z10" s="25" t="n">
         <f aca="false">Y10/P10/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC10" s="1" t="n">
+      <c r="AC10" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="AH10" s="1" t="s">
+      <c r="AH10" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="AI10" s="1" t="n">
+      <c r="AI10" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" s="1" t="n">
+      <c r="AJ10" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="AK10" s="1" t="n">
+      <c r="AK10" s="24" t="n">
         <f aca="false">AI10+AJ10/100</f>
         <v>0.27</v>
       </c>
-      <c r="AL10" s="1" t="n">
+      <c r="AL10" s="24" t="n">
         <f aca="false">AK10*1000</f>
         <v>270</v>
       </c>
-      <c r="AO10" s="24" t="s">
+      <c r="AO10" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="AP10" s="1" t="n">
+      <c r="AP10" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AQ10" s="1" t="n">
+      <c r="AQ10" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="AR10" s="24" t="n">
+      <c r="AR10" s="29" t="n">
         <f aca="false">AP10+AQ10/10</f>
         <v>1.6</v>
       </c>
-      <c r="AS10" s="24" t="n">
+      <c r="AS10" s="29" t="n">
         <f aca="false">1000*AR10</f>
         <v>1600</v>
       </c>
-      <c r="AU10" s="25" t="s">
+      <c r="AU10" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AV10" s="0" t="n">
+      <c r="AV10" s="24" t="n">
         <v>0.27</v>
       </c>
-      <c r="AW10" s="0" t="n">
+      <c r="AW10" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="AX10" s="0" t="n">
+      <c r="AX10" s="24" t="n">
         <v>0.55</v>
       </c>
-      <c r="AY10" s="0" t="n">
+      <c r="AY10" s="24" t="n">
         <v>1.09</v>
       </c>
-      <c r="AZ10" s="0" t="n">
+      <c r="AZ10" s="24" t="n">
         <v>1.48</v>
       </c>
-      <c r="BA10" s="25" t="s">
+      <c r="BA10" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="BC10" s="25" t="n">
+      <c r="BC10" s="29" t="n">
         <f aca="false">AV10*1000</f>
         <v>270</v>
       </c>
+      <c r="XDN10" s="24"/>
+      <c r="XDO10" s="24"/>
+      <c r="XDP10" s="24"/>
+      <c r="XDQ10" s="24"/>
+      <c r="XDR10" s="24"/>
+      <c r="XDS10" s="24"/>
+      <c r="XDT10" s="24"/>
+      <c r="XDU10" s="24"/>
+      <c r="XDV10" s="24"/>
+      <c r="XDW10" s="24"/>
+      <c r="XDX10" s="24"/>
+      <c r="XDY10" s="24"/>
+      <c r="XDZ10" s="24"/>
+      <c r="XEA10" s="24"/>
+      <c r="XEB10" s="24"/>
+      <c r="XEC10" s="24"/>
+      <c r="XED10" s="24"/>
+      <c r="XEE10" s="24"/>
+      <c r="XEF10" s="24"/>
+      <c r="XEG10" s="24"/>
+      <c r="XEH10" s="24"/>
+      <c r="XEI10" s="24"/>
+      <c r="XEJ10" s="24"/>
+      <c r="XEK10" s="24"/>
+      <c r="XEL10" s="24"/>
+      <c r="XEM10" s="24"/>
+      <c r="XEN10" s="24"/>
+      <c r="XEO10" s="24"/>
+      <c r="XEP10" s="24"/>
+      <c r="XEQ10" s="24"/>
+      <c r="XER10" s="24"/>
+      <c r="XES10" s="24"/>
+      <c r="XET10" s="24"/>
+      <c r="XEU10" s="24"/>
+      <c r="XEV10" s="24"/>
+      <c r="XEW10" s="24"/>
+      <c r="XEX10" s="24"/>
+      <c r="XEY10" s="24"/>
+      <c r="XEZ10" s="24"/>
+      <c r="XFA10" s="24"/>
+      <c r="XFB10" s="24"/>
+      <c r="XFC10" s="24"/>
+      <c r="XFD10" s="24"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
+    <row r="11" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="22" t="n">
         <f aca="false">1000*B11/$P11</f>
         <v>786.755148115208</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="22" t="n">
         <f aca="false">1000*D11/$P11</f>
         <v>444.687692412944</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="22" t="n">
         <f aca="false">1000*F11/$P11</f>
         <v>5.13101183553397</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="22" t="n">
         <f aca="false">1000*H11/$P11</f>
         <v>615.721420264076</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="24" t="n">
         <f aca="false">L11*$J$37/100</f>
         <v>64.6</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="25" t="n">
         <f aca="false">1000*J11/P11</f>
         <v>1104.87788191831</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="L11" s="24" t="n">
         <v>380</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11" s="24" t="n">
         <f aca="false">O11*$M$37/100</f>
         <v>312.8</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" s="25" t="n">
         <f aca="false">1000*M11/P11</f>
         <v>5349.93500718342</v>
       </c>
-      <c r="O11" s="1" t="n">
+      <c r="O11" s="24" t="n">
         <v>2300</v>
       </c>
-      <c r="P11" s="1" t="n">
+      <c r="P11" s="25" t="n">
         <v>58.468</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="Q11" s="25" t="n">
         <f aca="false">100*P11/$P$36</f>
         <v>0.401577131889804</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="26" t="n">
         <f aca="false">H11+F11+B11+D11+J11+M11</f>
         <v>485.7</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="27" t="n">
         <f aca="false">R11/P11</f>
         <v>8.30710816172949</v>
       </c>
-      <c r="U11" s="1" t="n">
+      <c r="T11" s="26"/>
+      <c r="U11" s="25" t="n">
         <f aca="false">-T11+($Q$45 + $Q$46)*1000*Q11/100</f>
-        <v>179.81057815211</v>
-      </c>
-      <c r="V11" s="1" t="n">
+        <v>178.035607229158</v>
+      </c>
+      <c r="V11" s="25" t="n">
         <f aca="false">U11/P11/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W11" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W11" s="25" t="n">
         <f aca="false">ROUND(U11/P11 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y11" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y11" s="25" t="n">
         <f aca="false">-Q11*($Q$47)*10</f>
         <v>-96.378511653553</v>
       </c>
-      <c r="Z11" s="1" t="n">
+      <c r="Z11" s="25" t="n">
         <f aca="false">Y11/P11/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC11" s="1" t="n">
+      <c r="AC11" s="24" t="n">
         <v>93</v>
       </c>
-      <c r="AH11" s="1" t="s">
+      <c r="AH11" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="AI11" s="1" t="n">
+      <c r="AI11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" s="1" t="n">
+      <c r="AJ11" s="24" t="n">
         <v>38</v>
       </c>
-      <c r="AK11" s="1" t="n">
+      <c r="AK11" s="24" t="n">
         <f aca="false">AI11+AJ11/100</f>
         <v>0.38</v>
       </c>
-      <c r="AL11" s="1" t="n">
+      <c r="AL11" s="24" t="n">
         <f aca="false">AK11*1000</f>
         <v>380</v>
       </c>
-      <c r="AO11" s="24" t="s">
+      <c r="AO11" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AP11" s="1" t="n">
+      <c r="AP11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="AQ11" s="1" t="n">
+      <c r="AQ11" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="AR11" s="24" t="n">
+      <c r="AR11" s="29" t="n">
         <f aca="false">AP11+AQ11/10</f>
         <v>2.3</v>
       </c>
-      <c r="AS11" s="24" t="n">
+      <c r="AS11" s="29" t="n">
         <f aca="false">1000*AR11</f>
         <v>2300</v>
       </c>
-      <c r="AU11" s="25" t="s">
+      <c r="AU11" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="AV11" s="0" t="n">
+      <c r="AV11" s="24" t="n">
         <v>0.38</v>
       </c>
-      <c r="AW11" s="0" t="n">
+      <c r="AW11" s="24" t="n">
         <v>0.84</v>
       </c>
-      <c r="AX11" s="0" t="n">
+      <c r="AX11" s="24" t="n">
         <v>0.48</v>
       </c>
-      <c r="AY11" s="0" t="n">
+      <c r="AY11" s="24" t="n">
         <v>1.76</v>
       </c>
-      <c r="AZ11" s="0" t="n">
+      <c r="AZ11" s="24" t="n">
         <v>2.39</v>
       </c>
-      <c r="BA11" s="25" t="s">
+      <c r="BA11" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="BC11" s="25" t="n">
+      <c r="BC11" s="29" t="n">
         <f aca="false">AV11*1000</f>
         <v>380</v>
       </c>
+      <c r="XDN11" s="24"/>
+      <c r="XDO11" s="24"/>
+      <c r="XDP11" s="24"/>
+      <c r="XDQ11" s="24"/>
+      <c r="XDR11" s="24"/>
+      <c r="XDS11" s="24"/>
+      <c r="XDT11" s="24"/>
+      <c r="XDU11" s="24"/>
+      <c r="XDV11" s="24"/>
+      <c r="XDW11" s="24"/>
+      <c r="XDX11" s="24"/>
+      <c r="XDY11" s="24"/>
+      <c r="XDZ11" s="24"/>
+      <c r="XEA11" s="24"/>
+      <c r="XEB11" s="24"/>
+      <c r="XEC11" s="24"/>
+      <c r="XED11" s="24"/>
+      <c r="XEE11" s="24"/>
+      <c r="XEF11" s="24"/>
+      <c r="XEG11" s="24"/>
+      <c r="XEH11" s="24"/>
+      <c r="XEI11" s="24"/>
+      <c r="XEJ11" s="24"/>
+      <c r="XEK11" s="24"/>
+      <c r="XEL11" s="24"/>
+      <c r="XEM11" s="24"/>
+      <c r="XEN11" s="24"/>
+      <c r="XEO11" s="24"/>
+      <c r="XEP11" s="24"/>
+      <c r="XEQ11" s="24"/>
+      <c r="XER11" s="24"/>
+      <c r="XES11" s="24"/>
+      <c r="XET11" s="24"/>
+      <c r="XEU11" s="24"/>
+      <c r="XEV11" s="24"/>
+      <c r="XEW11" s="24"/>
+      <c r="XEX11" s="24"/>
+      <c r="XEY11" s="24"/>
+      <c r="XEZ11" s="24"/>
+      <c r="XFA11" s="24"/>
+      <c r="XFB11" s="24"/>
+      <c r="XFC11" s="24"/>
+      <c r="XFD11" s="24"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="22" t="n">
         <f aca="false">1000*B12/$P12</f>
         <v>727.603456116417</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="21" t="n">
+      <c r="D12" s="34"/>
+      <c r="E12" s="22" t="n">
         <f aca="false">1000*D12/$P12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="22" t="n">
         <f aca="false">1000*F12/$P12</f>
         <v>36.3801728058208</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="22" t="n">
         <f aca="false">1000*H12/$P12</f>
         <v>2091.8599363347</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="24" t="n">
         <f aca="false">L12*$J$37/100</f>
         <v>49.3</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="25" t="n">
         <f aca="false">1000*J12/P12</f>
         <v>2241.92814915871</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="L12" s="24" t="n">
         <v>290</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="24" t="n">
         <f aca="false">O12*$M$37/100</f>
         <v>204</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="25" t="n">
         <f aca="false">1000*M12/P12</f>
         <v>9276.94406548431</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="O12" s="24" t="n">
         <v>1500</v>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="P12" s="25" t="n">
         <v>21.99</v>
       </c>
-      <c r="Q12" s="1" t="n">
+      <c r="Q12" s="25" t="n">
         <f aca="false">100*P12/$P$36</f>
         <v>0.151034431317247</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="26" t="n">
         <f aca="false">H12+F12+B12+D12+J12+M12</f>
         <v>316.1</v>
       </c>
-      <c r="S12" s="3" t="n">
+      <c r="S12" s="27" t="n">
         <f aca="false">R12/P12</f>
         <v>14.3747157799</v>
       </c>
-      <c r="U12" s="1" t="n">
+      <c r="T12" s="26"/>
+      <c r="U12" s="25" t="n">
         <f aca="false">-T12+($Q$45 + $Q$46)*1000*Q12/100</f>
-        <v>67.6273280010418</v>
-      </c>
-      <c r="V12" s="1" t="n">
+        <v>66.9597558146196</v>
+      </c>
+      <c r="V12" s="25" t="n">
         <f aca="false">U12/P12/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W12" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W12" s="25" t="n">
         <f aca="false">ROUND(U12/P12 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y12" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y12" s="25" t="n">
         <f aca="false">-Q12*($Q$47)*10</f>
         <v>-36.2482635161393</v>
       </c>
-      <c r="Z12" s="1" t="n">
+      <c r="Z12" s="25" t="n">
         <f aca="false">Y12/P12/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC12" s="1" t="n">
+      <c r="AC12" s="24" t="n">
         <v>36.5</v>
       </c>
-      <c r="AH12" s="1" t="s">
+      <c r="AH12" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="AI12" s="1" t="n">
+      <c r="AI12" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ12" s="1" t="n">
+      <c r="AJ12" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="AK12" s="1" t="n">
+      <c r="AK12" s="24" t="n">
         <f aca="false">AI12+AJ12/100</f>
         <v>0.29</v>
       </c>
-      <c r="AL12" s="1" t="n">
+      <c r="AL12" s="24" t="n">
         <f aca="false">AK12*1000</f>
         <v>290</v>
       </c>
-      <c r="AO12" s="24" t="s">
+      <c r="AO12" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AP12" s="1" t="n">
+      <c r="AP12" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AQ12" s="1" t="n">
+      <c r="AQ12" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="AR12" s="24" t="n">
+      <c r="AR12" s="29" t="n">
         <f aca="false">AP12+AQ12/10</f>
         <v>1.5</v>
       </c>
-      <c r="AS12" s="24" t="n">
+      <c r="AS12" s="29" t="n">
         <f aca="false">1000*AR12</f>
         <v>1500</v>
       </c>
-      <c r="AU12" s="25" t="s">
+      <c r="AU12" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="AV12" s="0" t="n">
+      <c r="AV12" s="24" t="n">
         <v>0.29</v>
       </c>
-      <c r="AW12" s="0" t="n">
+      <c r="AW12" s="24" t="n">
         <v>0.64</v>
       </c>
-      <c r="AX12" s="0" t="n">
+      <c r="AX12" s="24" t="n">
         <v>0.16</v>
       </c>
-      <c r="AY12" s="0" t="n">
+      <c r="AY12" s="24" t="n">
         <v>3.9</v>
       </c>
-      <c r="AZ12" s="0" t="n">
+      <c r="AZ12" s="24" t="n">
         <v>5.29</v>
       </c>
-      <c r="BA12" s="25" t="s">
+      <c r="BA12" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="BC12" s="25" t="n">
+      <c r="BC12" s="29" t="n">
         <f aca="false">AV12*1000</f>
         <v>290</v>
       </c>
+      <c r="XDN12" s="24"/>
+      <c r="XDO12" s="24"/>
+      <c r="XDP12" s="24"/>
+      <c r="XDQ12" s="24"/>
+      <c r="XDR12" s="24"/>
+      <c r="XDS12" s="24"/>
+      <c r="XDT12" s="24"/>
+      <c r="XDU12" s="24"/>
+      <c r="XDV12" s="24"/>
+      <c r="XDW12" s="24"/>
+      <c r="XDX12" s="24"/>
+      <c r="XDY12" s="24"/>
+      <c r="XDZ12" s="24"/>
+      <c r="XEA12" s="24"/>
+      <c r="XEB12" s="24"/>
+      <c r="XEC12" s="24"/>
+      <c r="XED12" s="24"/>
+      <c r="XEE12" s="24"/>
+      <c r="XEF12" s="24"/>
+      <c r="XEG12" s="24"/>
+      <c r="XEH12" s="24"/>
+      <c r="XEI12" s="24"/>
+      <c r="XEJ12" s="24"/>
+      <c r="XEK12" s="24"/>
+      <c r="XEL12" s="24"/>
+      <c r="XEM12" s="24"/>
+      <c r="XEN12" s="24"/>
+      <c r="XEO12" s="24"/>
+      <c r="XEP12" s="24"/>
+      <c r="XEQ12" s="24"/>
+      <c r="XER12" s="24"/>
+      <c r="XES12" s="24"/>
+      <c r="XET12" s="24"/>
+      <c r="XEU12" s="24"/>
+      <c r="XEV12" s="24"/>
+      <c r="XEW12" s="24"/>
+      <c r="XEX12" s="24"/>
+      <c r="XEY12" s="24"/>
+      <c r="XEZ12" s="24"/>
+      <c r="XFA12" s="24"/>
+      <c r="XFB12" s="24"/>
+      <c r="XFC12" s="24"/>
+      <c r="XFD12" s="24"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
+    <row r="13" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="31" t="n">
         <v>177</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="22" t="n">
         <f aca="false">1000*B13/$P13</f>
         <v>777.772407095745</v>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="32" t="n">
         <v>263</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="22" t="n">
         <f aca="false">1000*D13/$P13</f>
         <v>1155.67312466769</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="31" t="n">
         <v>3.8</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="22" t="n">
         <f aca="false">1000*F13/$P13</f>
         <v>16.6979386834115</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="31" t="n">
         <v>348</v>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="22" t="n">
         <f aca="false">1000*H13/$P13</f>
         <v>1529.17964784926</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="24" t="n">
         <f aca="false">L13*$J$37/100</f>
         <v>74.8</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="25" t="n">
         <f aca="false">1000*J13/P13</f>
         <v>328.685740399784</v>
       </c>
-      <c r="L13" s="1" t="n">
+      <c r="L13" s="24" t="n">
         <v>440</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="24" t="n">
         <f aca="false">O13*$M$37/100</f>
         <v>625.6</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" s="25" t="n">
         <f aca="false">1000*M13/P13</f>
         <v>2749.00801061637</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="O13" s="24" t="n">
         <v>4600</v>
       </c>
-      <c r="P13" s="1" t="n">
+      <c r="P13" s="25" t="n">
         <v>227.573</v>
       </c>
-      <c r="Q13" s="1" t="n">
+      <c r="Q13" s="25" t="n">
         <f aca="false">100*P13/$P$36</f>
         <v>1.56304495853387</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="26" t="n">
         <f aca="false">H13+F13+B13+D13+J13+M13</f>
         <v>1492.2</v>
       </c>
-      <c r="S13" s="3" t="n">
+      <c r="S13" s="27" t="n">
         <f aca="false">R13/P13</f>
         <v>6.55701686931226</v>
       </c>
-      <c r="U13" s="1" t="n">
+      <c r="T13" s="26"/>
+      <c r="U13" s="25" t="n">
         <f aca="false">-T13+($Q$45 + $Q$46)*1000*Q13/100</f>
-        <v>699.870573678084</v>
-      </c>
-      <c r="V13" s="1" t="n">
+        <v>692.961914961364</v>
+      </c>
+      <c r="V13" s="25" t="n">
         <f aca="false">U13/P13/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W13" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W13" s="25" t="n">
         <f aca="false">ROUND(U13/P13 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y13" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y13" s="25" t="n">
         <f aca="false">-Q13*($Q$47)*10</f>
         <v>-375.130790048129</v>
       </c>
-      <c r="Z13" s="1" t="n">
+      <c r="Z13" s="25" t="n">
         <f aca="false">Y13/P13/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC13" s="1" t="n">
+      <c r="AC13" s="24" t="n">
         <v>347.3</v>
       </c>
-      <c r="AH13" s="1" t="s">
+      <c r="AH13" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="AI13" s="1" t="n">
+      <c r="AI13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ13" s="1" t="n">
+      <c r="AJ13" s="24" t="n">
         <v>44</v>
       </c>
-      <c r="AK13" s="1" t="n">
+      <c r="AK13" s="24" t="n">
         <f aca="false">AI13+AJ13/100</f>
         <v>0.44</v>
       </c>
-      <c r="AL13" s="1" t="n">
+      <c r="AL13" s="24" t="n">
         <f aca="false">AK13*1000</f>
         <v>440</v>
       </c>
-      <c r="AO13" s="24" t="s">
+      <c r="AO13" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="AP13" s="1" t="n">
+      <c r="AP13" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="AQ13" s="1" t="n">
+      <c r="AQ13" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="AR13" s="24" t="n">
+      <c r="AR13" s="29" t="n">
         <f aca="false">AP13+AQ13/10</f>
         <v>4.6</v>
       </c>
-      <c r="AS13" s="24" t="n">
+      <c r="AS13" s="29" t="n">
         <f aca="false">1000*AR13</f>
         <v>4600</v>
       </c>
-      <c r="AU13" s="25" t="s">
+      <c r="AU13" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="AV13" s="0" t="n">
+      <c r="AV13" s="24" t="n">
         <v>0.44</v>
       </c>
-      <c r="AW13" s="0" t="n">
+      <c r="AW13" s="24" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX13" s="0" t="n">
+      <c r="AX13" s="24" t="n">
         <v>1.68</v>
       </c>
-      <c r="AY13" s="0" t="n">
+      <c r="AY13" s="24" t="n">
         <v>0.58</v>
       </c>
-      <c r="AZ13" s="0" t="n">
+      <c r="AZ13" s="24" t="n">
         <v>0.79</v>
       </c>
-      <c r="BA13" s="25" t="s">
+      <c r="BA13" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="BC13" s="25" t="n">
+      <c r="BC13" s="29" t="n">
         <f aca="false">AV13*1000</f>
         <v>440</v>
       </c>
+      <c r="XDN13" s="24"/>
+      <c r="XDO13" s="24"/>
+      <c r="XDP13" s="24"/>
+      <c r="XDQ13" s="24"/>
+      <c r="XDR13" s="24"/>
+      <c r="XDS13" s="24"/>
+      <c r="XDT13" s="24"/>
+      <c r="XDU13" s="24"/>
+      <c r="XDV13" s="24"/>
+      <c r="XDW13" s="24"/>
+      <c r="XDX13" s="24"/>
+      <c r="XDY13" s="24"/>
+      <c r="XDZ13" s="24"/>
+      <c r="XEA13" s="24"/>
+      <c r="XEB13" s="24"/>
+      <c r="XEC13" s="24"/>
+      <c r="XED13" s="24"/>
+      <c r="XEE13" s="24"/>
+      <c r="XEF13" s="24"/>
+      <c r="XEG13" s="24"/>
+      <c r="XEH13" s="24"/>
+      <c r="XEI13" s="24"/>
+      <c r="XEJ13" s="24"/>
+      <c r="XEK13" s="24"/>
+      <c r="XEL13" s="24"/>
+      <c r="XEM13" s="24"/>
+      <c r="XEN13" s="24"/>
+      <c r="XEO13" s="24"/>
+      <c r="XEP13" s="24"/>
+      <c r="XEQ13" s="24"/>
+      <c r="XER13" s="24"/>
+      <c r="XES13" s="24"/>
+      <c r="XET13" s="24"/>
+      <c r="XEU13" s="24"/>
+      <c r="XEV13" s="24"/>
+      <c r="XEW13" s="24"/>
+      <c r="XEX13" s="24"/>
+      <c r="XEY13" s="24"/>
+      <c r="XEZ13" s="24"/>
+      <c r="XFA13" s="24"/>
+      <c r="XFB13" s="24"/>
+      <c r="XFC13" s="24"/>
+      <c r="XFD13" s="24"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
         <v>59</v>
       </c>
       <c r="B14" s="21" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="22" t="n">
         <f aca="false">1000*B14/$P14</f>
         <v>304.277684963515</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>258</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="22" t="n">
         <f aca="false">1000*D14/$P14</f>
         <v>740.600403024405</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="21" t="n">
         <v>113.8</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="22" t="n">
         <f aca="false">1000*F14/$P14</f>
         <v>326.667929706114</v>
       </c>
       <c r="H14" s="21" t="n">
         <v>533</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <f aca="false">1000*H14/$P14</f>
         <v>1530.00005741088</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="24" t="n">
         <f aca="false">L14*$J$37/100</f>
         <v>192.1</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="25" t="n">
         <f aca="false">1000*J14/P14</f>
         <v>551.431540391428</v>
       </c>
-      <c r="L14" s="1" t="n">
+      <c r="L14" s="24" t="n">
         <v>1130</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14" s="24" t="n">
         <f aca="false">O14*$M$37/100</f>
         <v>571.2</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" s="25" t="n">
         <f aca="false">1000*M14/P14</f>
         <v>1639.65484576566</v>
       </c>
-      <c r="O14" s="1" t="n">
+      <c r="O14" s="24" t="n">
         <v>4200</v>
       </c>
-      <c r="P14" s="1" t="n">
+      <c r="P14" s="25" t="n">
         <v>348.366</v>
       </c>
-      <c r="Q14" s="1" t="n">
+      <c r="Q14" s="25" t="n">
         <f aca="false">100*P14/$P$36</f>
         <v>2.39269034562365</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="26" t="n">
         <f aca="false">H14+F14+B14+D14+J14+M14</f>
         <v>1774.1</v>
       </c>
-      <c r="S14" s="3" t="n">
+      <c r="S14" s="27" t="n">
         <f aca="false">R14/P14</f>
         <v>5.09263246126201</v>
       </c>
-      <c r="U14" s="1" t="n">
+      <c r="T14" s="26"/>
+      <c r="U14" s="25" t="n">
         <f aca="false">-T14+($Q$45 + $Q$46)*1000*Q14/100</f>
-        <v>1071.35342184679</v>
-      </c>
-      <c r="V14" s="1" t="n">
+        <v>1060.77773051913</v>
+      </c>
+      <c r="V14" s="25" t="n">
         <f aca="false">U14/P14/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W14" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W14" s="25" t="n">
         <f aca="false">ROUND(U14/P14 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y14" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y14" s="25" t="n">
         <f aca="false">-Q14*($Q$47)*10</f>
         <v>-574.245682949676</v>
       </c>
-      <c r="Z14" s="1" t="n">
+      <c r="Z14" s="25" t="n">
         <f aca="false">Y14/P14/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC14" s="1" t="n">
+      <c r="AC14" s="24" t="n">
         <v>417.8</v>
       </c>
-      <c r="AH14" s="1" t="s">
+      <c r="AH14" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="AI14" s="1" t="n">
+      <c r="AI14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AJ14" s="1" t="n">
+      <c r="AJ14" s="24" t="n">
         <v>13</v>
       </c>
-      <c r="AK14" s="1" t="n">
+      <c r="AK14" s="24" t="n">
         <f aca="false">AI14+AJ14/100</f>
         <v>1.13</v>
       </c>
-      <c r="AL14" s="1" t="n">
+      <c r="AL14" s="24" t="n">
         <f aca="false">AK14*1000</f>
         <v>1130</v>
       </c>
-      <c r="AO14" s="24" t="s">
+      <c r="AO14" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="AP14" s="1" t="n">
+      <c r="AP14" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="AQ14" s="1" t="n">
+      <c r="AQ14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="AR14" s="24" t="n">
+      <c r="AR14" s="29" t="n">
         <f aca="false">AP14+AQ14/10</f>
         <v>4.2</v>
       </c>
-      <c r="AS14" s="24" t="n">
+      <c r="AS14" s="29" t="n">
         <f aca="false">1000*AR14</f>
         <v>4200</v>
       </c>
-      <c r="AU14" s="25" t="s">
+      <c r="AU14" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="AV14" s="0" t="n">
+      <c r="AV14" s="24" t="n">
         <v>1.13</v>
       </c>
-      <c r="AW14" s="0" t="n">
+      <c r="AW14" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="AX14" s="0" t="n">
+      <c r="AX14" s="24" t="n">
         <v>2.27</v>
       </c>
-      <c r="AY14" s="0" t="n">
+      <c r="AY14" s="24" t="n">
         <v>1.1</v>
       </c>
-      <c r="AZ14" s="0" t="n">
+      <c r="AZ14" s="24" t="n">
         <v>1.49</v>
       </c>
-      <c r="BA14" s="25" t="s">
+      <c r="BA14" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="BC14" s="25" t="n">
+      <c r="BC14" s="29" t="n">
         <f aca="false">AV14*1000</f>
         <v>1130</v>
       </c>
+      <c r="XDN14" s="24"/>
+      <c r="XDO14" s="24"/>
+      <c r="XDP14" s="24"/>
+      <c r="XDQ14" s="24"/>
+      <c r="XDR14" s="24"/>
+      <c r="XDS14" s="24"/>
+      <c r="XDT14" s="24"/>
+      <c r="XDU14" s="24"/>
+      <c r="XDV14" s="24"/>
+      <c r="XDW14" s="24"/>
+      <c r="XDX14" s="24"/>
+      <c r="XDY14" s="24"/>
+      <c r="XDZ14" s="24"/>
+      <c r="XEA14" s="24"/>
+      <c r="XEB14" s="24"/>
+      <c r="XEC14" s="24"/>
+      <c r="XED14" s="24"/>
+      <c r="XEE14" s="24"/>
+      <c r="XEF14" s="24"/>
+      <c r="XEG14" s="24"/>
+      <c r="XEH14" s="24"/>
+      <c r="XEI14" s="24"/>
+      <c r="XEJ14" s="24"/>
+      <c r="XEK14" s="24"/>
+      <c r="XEL14" s="24"/>
+      <c r="XEM14" s="24"/>
+      <c r="XEN14" s="24"/>
+      <c r="XEO14" s="24"/>
+      <c r="XEP14" s="24"/>
+      <c r="XEQ14" s="24"/>
+      <c r="XER14" s="24"/>
+      <c r="XES14" s="24"/>
+      <c r="XET14" s="24"/>
+      <c r="XEU14" s="24"/>
+      <c r="XEV14" s="24"/>
+      <c r="XEW14" s="24"/>
+      <c r="XEX14" s="24"/>
+      <c r="XEY14" s="24"/>
+      <c r="XEZ14" s="24"/>
+      <c r="XFA14" s="24"/>
+      <c r="XFB14" s="24"/>
+      <c r="XFC14" s="24"/>
+      <c r="XFD14" s="24"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
+    <row r="15" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="22" t="n">
         <f aca="false">1000*B15/$P15</f>
         <v>744.360658921001</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="32" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="22" t="n">
         <f aca="false">1000*D15/$P15</f>
         <v>679.633645101783</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="22" t="n">
         <f aca="false">1000*F15/$P15</f>
         <v>3.23635069096087</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="22" t="n">
         <f aca="false">1000*H15/$P15</f>
         <v>938.541700378653</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="24" t="n">
         <f aca="false">L15*$J$37/100</f>
-        <v>153</v>
-      </c>
-      <c r="K15" s="2" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K15" s="25" t="n">
         <f aca="false">1000*J15/P15</f>
-        <v>4951.61655717014</v>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="M15" s="1" t="n">
+        <v>495.161655717014</v>
+      </c>
+      <c r="L15" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="M15" s="24" t="n">
         <f aca="false">O15*$M$37/100</f>
         <v>68</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" s="25" t="n">
         <f aca="false">1000*M15/P15</f>
         <v>2200.71846985339</v>
       </c>
-      <c r="O15" s="1" t="n">
+      <c r="O15" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="P15" s="1" t="n">
+      <c r="P15" s="25" t="n">
         <v>30.899</v>
       </c>
-      <c r="Q15" s="1" t="n">
+      <c r="Q15" s="25" t="n">
         <f aca="false">100*P15/$P$36</f>
         <v>0.212224324387067</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="26" t="n">
         <f aca="false">H15+F15+B15+D15+J15+M15</f>
-        <v>294.1</v>
-      </c>
-      <c r="S15" s="3" t="n">
+        <v>156.4</v>
+      </c>
+      <c r="S15" s="27" t="n">
         <f aca="false">R15/P15</f>
-        <v>9.51810738211593</v>
-      </c>
-      <c r="U15" s="1" t="n">
+        <v>5.0616524806628</v>
+      </c>
+      <c r="T15" s="26"/>
+      <c r="U15" s="25" t="n">
         <f aca="false">-T15+($Q$45 + $Q$46)*1000*Q15/100</f>
-        <v>95.0257757118776</v>
-      </c>
-      <c r="V15" s="1" t="n">
+        <v>94.0877441980867</v>
+      </c>
+      <c r="V15" s="25" t="n">
         <f aca="false">U15/P15/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W15" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W15" s="25" t="n">
         <f aca="false">ROUND(U15/P15 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y15" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y15" s="25" t="n">
         <f aca="false">-Q15*($Q$47)*10</f>
         <v>-50.9338378528962</v>
       </c>
-      <c r="Z15" s="1" t="n">
+      <c r="Z15" s="25" t="n">
         <f aca="false">Y15/P15/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC15" s="1" t="n">
+      <c r="AC15" s="24" t="n">
         <v>41.9</v>
       </c>
-      <c r="AH15" s="1" t="s">
+      <c r="AH15" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="AI15" s="1" t="n">
+      <c r="AI15" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" s="1" t="n">
+      <c r="AJ15" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="AK15" s="1" t="n">
+      <c r="AK15" s="24" t="n">
         <f aca="false">AI15+AJ15/100</f>
         <v>0.9</v>
       </c>
-      <c r="AL15" s="1" t="n">
+      <c r="AL15" s="24" t="n">
         <f aca="false">AK15*1000</f>
         <v>900</v>
       </c>
-      <c r="AO15" s="24" t="s">
+      <c r="AO15" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="AP15" s="1" t="n">
+      <c r="AP15" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AQ15" s="1" t="n">
+      <c r="AQ15" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="AR15" s="24" t="n">
+      <c r="AR15" s="29" t="n">
         <f aca="false">AP15+AQ15/10</f>
         <v>0.5</v>
       </c>
-      <c r="AS15" s="24" t="n">
+      <c r="AS15" s="29" t="n">
         <f aca="false">1000*AR15</f>
         <v>500</v>
       </c>
-      <c r="AU15" s="25" t="s">
+      <c r="AU15" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="AV15" s="0" t="n">
+      <c r="AV15" s="24" t="n">
         <v>0.09</v>
       </c>
-      <c r="AW15" s="0" t="n">
+      <c r="AW15" s="24" t="n">
         <v>0.22</v>
       </c>
-      <c r="AX15" s="0" t="n">
+      <c r="AX15" s="24" t="n">
         <v>0.22</v>
       </c>
-      <c r="AY15" s="0" t="n">
+      <c r="AY15" s="24" t="n">
         <v>0.96</v>
       </c>
-      <c r="AZ15" s="0" t="n">
+      <c r="AZ15" s="24" t="n">
         <v>1.3</v>
       </c>
-      <c r="BA15" s="25" t="s">
+      <c r="BA15" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="BC15" s="25" t="n">
+      <c r="BC15" s="29" t="n">
         <f aca="false">AV15*1000</f>
         <v>90</v>
       </c>
+      <c r="XDN15" s="24"/>
+      <c r="XDO15" s="24"/>
+      <c r="XDP15" s="24"/>
+      <c r="XDQ15" s="24"/>
+      <c r="XDR15" s="24"/>
+      <c r="XDS15" s="24"/>
+      <c r="XDT15" s="24"/>
+      <c r="XDU15" s="24"/>
+      <c r="XDV15" s="24"/>
+      <c r="XDW15" s="24"/>
+      <c r="XDX15" s="24"/>
+      <c r="XDY15" s="24"/>
+      <c r="XDZ15" s="24"/>
+      <c r="XEA15" s="24"/>
+      <c r="XEB15" s="24"/>
+      <c r="XEC15" s="24"/>
+      <c r="XED15" s="24"/>
+      <c r="XEE15" s="24"/>
+      <c r="XEF15" s="24"/>
+      <c r="XEG15" s="24"/>
+      <c r="XEH15" s="24"/>
+      <c r="XEI15" s="24"/>
+      <c r="XEJ15" s="24"/>
+      <c r="XEK15" s="24"/>
+      <c r="XEL15" s="24"/>
+      <c r="XEM15" s="24"/>
+      <c r="XEN15" s="24"/>
+      <c r="XEO15" s="24"/>
+      <c r="XEP15" s="24"/>
+      <c r="XEQ15" s="24"/>
+      <c r="XER15" s="24"/>
+      <c r="XES15" s="24"/>
+      <c r="XET15" s="24"/>
+      <c r="XEU15" s="24"/>
+      <c r="XEV15" s="24"/>
+      <c r="XEW15" s="24"/>
+      <c r="XEX15" s="24"/>
+      <c r="XEY15" s="24"/>
+      <c r="XEZ15" s="24"/>
+      <c r="XFA15" s="24"/>
+      <c r="XFB15" s="24"/>
+      <c r="XFC15" s="24"/>
+      <c r="XFD15" s="24"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
         <v>66</v>
       </c>
       <c r="B16" s="21" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="22" t="n">
         <f aca="false">1000*B16/$P16</f>
         <v>379.785988637743</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>133</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="22" t="n">
         <f aca="false">1000*D16/$P16</f>
         <v>520.737489575462</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="21" t="n">
         <v>81.3</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="22" t="n">
         <f aca="false">1000*F16/$P16</f>
         <v>318.315472951015</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>152</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="22" t="n">
         <f aca="false">1000*H16/$P16</f>
         <v>595.128559514814</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="24" t="n">
         <f aca="false">L16*$J$37/100</f>
         <v>122.4</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="25" t="n">
         <f aca="false">1000*J16/P16</f>
         <v>479.235103188245</v>
       </c>
-      <c r="L16" s="1" t="n">
+      <c r="L16" s="24" t="n">
         <v>720</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="24" t="n">
         <f aca="false">O16*$M$37/100</f>
         <v>394.4</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" s="25" t="n">
         <f aca="false">1000*M16/P16</f>
         <v>1544.20199916212</v>
       </c>
-      <c r="O16" s="1" t="n">
+      <c r="O16" s="24" t="n">
         <v>2900</v>
       </c>
-      <c r="P16" s="1" t="n">
+      <c r="P16" s="25" t="n">
         <v>255.407</v>
       </c>
-      <c r="Q16" s="1" t="n">
+      <c r="Q16" s="25" t="n">
         <f aca="false">100*P16/$P$36</f>
         <v>1.75421787173461</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="26" t="n">
         <f aca="false">H16+F16+B16+D16+J16+M16</f>
         <v>980.1</v>
       </c>
-      <c r="S16" s="3" t="n">
+      <c r="S16" s="27" t="n">
         <f aca="false">R16/P16</f>
         <v>3.8374046130294</v>
       </c>
-      <c r="U16" s="1" t="n">
+      <c r="T16" s="26"/>
+      <c r="U16" s="25" t="n">
         <f aca="false">-T16+($Q$45 + $Q$46)*1000*Q16/100</f>
-        <v>785.470348465761</v>
-      </c>
-      <c r="V16" s="1" t="n">
+        <v>777.716705472694</v>
+      </c>
+      <c r="V16" s="25" t="n">
         <f aca="false">U16/P16/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W16" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W16" s="25" t="n">
         <f aca="false">ROUND(U16/P16 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y16" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y16" s="25" t="n">
         <f aca="false">-Q16*($Q$47)*10</f>
         <v>-421.012289216306</v>
       </c>
-      <c r="Z16" s="1" t="n">
+      <c r="Z16" s="25" t="n">
         <f aca="false">Y16/P16/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC16" s="1" t="n">
+      <c r="AC16" s="24" t="n">
         <v>281.7</v>
       </c>
-      <c r="AH16" s="1" t="s">
+      <c r="AH16" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="AI16" s="1" t="n">
+      <c r="AI16" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ16" s="1" t="n">
+      <c r="AJ16" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="AK16" s="1" t="n">
+      <c r="AK16" s="24" t="n">
         <f aca="false">AI16+AJ16/100</f>
         <v>0.72</v>
       </c>
-      <c r="AL16" s="1" t="n">
+      <c r="AL16" s="24" t="n">
         <f aca="false">AK16*1000</f>
         <v>720</v>
       </c>
-      <c r="AO16" s="24" t="s">
+      <c r="AO16" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="AP16" s="1" t="n">
+      <c r="AP16" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="AQ16" s="1" t="n">
+      <c r="AQ16" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="AR16" s="24" t="n">
+      <c r="AR16" s="29" t="n">
         <f aca="false">AP16+AQ16/10</f>
         <v>2.9</v>
       </c>
-      <c r="AS16" s="24" t="n">
+      <c r="AS16" s="29" t="n">
         <f aca="false">1000*AR16</f>
         <v>2900</v>
       </c>
-      <c r="AU16" s="25" t="s">
+      <c r="AU16" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="AV16" s="0" t="n">
+      <c r="AV16" s="24" t="n">
         <v>0.72</v>
       </c>
-      <c r="AW16" s="0" t="n">
+      <c r="AW16" s="24" t="n">
         <v>1.59</v>
       </c>
-      <c r="AX16" s="0" t="n">
+      <c r="AX16" s="24" t="n">
         <v>1.6</v>
       </c>
-      <c r="AY16" s="0" t="n">
+      <c r="AY16" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AZ16" s="0" t="n">
+      <c r="AZ16" s="24" t="n">
         <v>1.36</v>
       </c>
-      <c r="BA16" s="25" t="s">
+      <c r="BA16" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="BC16" s="25" t="n">
+      <c r="BC16" s="29" t="n">
         <f aca="false">AV16*1000</f>
         <v>720</v>
       </c>
+      <c r="XDN16" s="24"/>
+      <c r="XDO16" s="24"/>
+      <c r="XDP16" s="24"/>
+      <c r="XDQ16" s="24"/>
+      <c r="XDR16" s="24"/>
+      <c r="XDS16" s="24"/>
+      <c r="XDT16" s="24"/>
+      <c r="XDU16" s="24"/>
+      <c r="XDV16" s="24"/>
+      <c r="XDW16" s="24"/>
+      <c r="XDX16" s="24"/>
+      <c r="XDY16" s="24"/>
+      <c r="XDZ16" s="24"/>
+      <c r="XEA16" s="24"/>
+      <c r="XEB16" s="24"/>
+      <c r="XEC16" s="24"/>
+      <c r="XED16" s="24"/>
+      <c r="XEE16" s="24"/>
+      <c r="XEF16" s="24"/>
+      <c r="XEG16" s="24"/>
+      <c r="XEH16" s="24"/>
+      <c r="XEI16" s="24"/>
+      <c r="XEJ16" s="24"/>
+      <c r="XEK16" s="24"/>
+      <c r="XEL16" s="24"/>
+      <c r="XEM16" s="24"/>
+      <c r="XEN16" s="24"/>
+      <c r="XEO16" s="24"/>
+      <c r="XEP16" s="24"/>
+      <c r="XEQ16" s="24"/>
+      <c r="XER16" s="24"/>
+      <c r="XES16" s="24"/>
+      <c r="XET16" s="24"/>
+      <c r="XEU16" s="24"/>
+      <c r="XEV16" s="24"/>
+      <c r="XEW16" s="24"/>
+      <c r="XEX16" s="24"/>
+      <c r="XEY16" s="24"/>
+      <c r="XEZ16" s="24"/>
+      <c r="XFA16" s="24"/>
+      <c r="XFB16" s="24"/>
+      <c r="XFC16" s="24"/>
+      <c r="XFD16" s="24"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
+    <row r="17" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="31" t="n">
         <v>1078</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="22" t="n">
         <f aca="false">1000*B17/$P17</f>
         <v>418.692157950257</v>
       </c>
-      <c r="D17" s="28" t="n">
+      <c r="D17" s="32" t="n">
         <v>1691</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="22" t="n">
         <f aca="false">1000*D17/$P17</f>
         <v>656.779628101934</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="31" t="n">
         <v>3100</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="22" t="n">
         <f aca="false">1000*F17/$P17</f>
         <v>1204.03125199054</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="31" t="n">
         <v>6670</v>
       </c>
-      <c r="I17" s="21" t="n">
+      <c r="I17" s="22" t="n">
         <f aca="false">1000*H17/$P17</f>
         <v>2590.60917766996</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="24" t="n">
         <f aca="false">L17*$J$37/100</f>
         <v>914.6</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="25" t="n">
         <f aca="false">1000*J17/P17</f>
         <v>355.228059055014</v>
       </c>
-      <c r="L17" s="1" t="n">
+      <c r="L17" s="24" t="n">
         <v>5380</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="24" t="n">
         <f aca="false">O17*$M$37/100</f>
         <v>8432</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="N17" s="25" t="n">
         <f aca="false">1000*M17/P17</f>
         <v>3274.96500541426</v>
       </c>
-      <c r="O17" s="1" t="n">
+      <c r="O17" s="24" t="n">
         <v>62000</v>
       </c>
-      <c r="P17" s="1" t="n">
+      <c r="P17" s="25" t="n">
         <v>2574.684</v>
       </c>
-      <c r="Q17" s="1" t="n">
+      <c r="Q17" s="25" t="n">
         <f aca="false">100*P17/$P$36</f>
         <v>17.6837623356805</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="26" t="n">
         <f aca="false">H17+F17+B17+D17+J17+M17</f>
         <v>21885.6</v>
       </c>
-      <c r="S17" s="3" t="n">
+      <c r="S17" s="27" t="n">
         <f aca="false">R17/P17</f>
         <v>8.50030528018196</v>
       </c>
-      <c r="T17" s="3" t="n">
+      <c r="T17" s="26" t="n">
         <f aca="false">B17+F17</f>
         <v>4178</v>
       </c>
-      <c r="U17" s="1" t="n">
+      <c r="U17" s="25" t="n">
         <f aca="false">-T17+($Q$45 + $Q$46)*1000*Q17/100</f>
-        <v>3740.09910718664</v>
-      </c>
-      <c r="V17" s="1" t="n">
+        <v>3661.93687766293</v>
+      </c>
+      <c r="V17" s="25" t="n">
         <f aca="false">U17/P17/10</f>
-        <v>0.145264393890149</v>
-      </c>
-      <c r="W17" s="1" t="n">
+        <v>0.142228594952349</v>
+      </c>
+      <c r="W17" s="25" t="n">
         <f aca="false">ROUND(U17/P17 *100/1000, 2)</f>
-        <v>0.15</v>
-      </c>
-      <c r="Y17" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Y17" s="25" t="n">
         <f aca="false">-Q17*($Q$47)*10</f>
         <v>-4244.10296056332</v>
       </c>
-      <c r="Z17" s="1" t="n">
+      <c r="Z17" s="25" t="n">
         <f aca="false">Y17/P17/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC17" s="1" t="n">
+      <c r="AC17" s="24" t="n">
         <v>2991.1</v>
       </c>
-      <c r="AH17" s="1" t="s">
+      <c r="AH17" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="AI17" s="1" t="n">
+      <c r="AI17" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="AJ17" s="1" t="n">
+      <c r="AJ17" s="24" t="n">
         <v>38</v>
       </c>
-      <c r="AK17" s="1" t="n">
+      <c r="AK17" s="24" t="n">
         <f aca="false">AI17+AJ17/100</f>
         <v>5.38</v>
       </c>
-      <c r="AL17" s="1" t="n">
+      <c r="AL17" s="24" t="n">
         <f aca="false">AK17*1000</f>
         <v>5380</v>
       </c>
-      <c r="AO17" s="24" t="s">
+      <c r="AO17" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="AP17" s="1" t="n">
+      <c r="AP17" s="24" t="n">
         <v>62</v>
       </c>
-      <c r="AQ17" s="1" t="n">
+      <c r="AQ17" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AR17" s="24" t="n">
+      <c r="AR17" s="29" t="n">
         <f aca="false">AP17+AQ17/10</f>
         <v>62</v>
       </c>
-      <c r="AS17" s="24" t="n">
+      <c r="AS17" s="29" t="n">
         <f aca="false">1000*AR17</f>
         <v>62000</v>
       </c>
-      <c r="AU17" s="25" t="s">
+      <c r="AU17" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="AV17" s="0" t="n">
+      <c r="AV17" s="24" t="n">
         <v>5.38</v>
       </c>
-      <c r="AW17" s="0" t="n">
+      <c r="AW17" s="24" t="n">
         <v>11.96</v>
       </c>
-      <c r="AX17" s="0" t="n">
+      <c r="AX17" s="24" t="n">
         <v>16.61</v>
       </c>
-      <c r="AY17" s="0" t="n">
+      <c r="AY17" s="24" t="n">
         <v>0.72</v>
       </c>
-      <c r="AZ17" s="0" t="n">
+      <c r="AZ17" s="24" t="n">
         <v>0.98</v>
       </c>
-      <c r="BA17" s="25" t="s">
+      <c r="BA17" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="BC17" s="25" t="n">
+      <c r="BC17" s="29" t="n">
         <f aca="false">AV17*1000</f>
         <v>5380</v>
       </c>
+      <c r="XDN17" s="24"/>
+      <c r="XDO17" s="24"/>
+      <c r="XDP17" s="24"/>
+      <c r="XDQ17" s="24"/>
+      <c r="XDR17" s="24"/>
+      <c r="XDS17" s="24"/>
+      <c r="XDT17" s="24"/>
+      <c r="XDU17" s="24"/>
+      <c r="XDV17" s="24"/>
+      <c r="XDW17" s="24"/>
+      <c r="XDX17" s="24"/>
+      <c r="XDY17" s="24"/>
+      <c r="XDZ17" s="24"/>
+      <c r="XEA17" s="24"/>
+      <c r="XEB17" s="24"/>
+      <c r="XEC17" s="24"/>
+      <c r="XED17" s="24"/>
+      <c r="XEE17" s="24"/>
+      <c r="XEF17" s="24"/>
+      <c r="XEG17" s="24"/>
+      <c r="XEH17" s="24"/>
+      <c r="XEI17" s="24"/>
+      <c r="XEJ17" s="24"/>
+      <c r="XEK17" s="24"/>
+      <c r="XEL17" s="24"/>
+      <c r="XEM17" s="24"/>
+      <c r="XEN17" s="24"/>
+      <c r="XEO17" s="24"/>
+      <c r="XEP17" s="24"/>
+      <c r="XEQ17" s="24"/>
+      <c r="XER17" s="24"/>
+      <c r="XES17" s="24"/>
+      <c r="XET17" s="24"/>
+      <c r="XEU17" s="24"/>
+      <c r="XEV17" s="24"/>
+      <c r="XEW17" s="24"/>
+      <c r="XEX17" s="24"/>
+      <c r="XEY17" s="24"/>
+      <c r="XEZ17" s="24"/>
+      <c r="XFA17" s="24"/>
+      <c r="XFB17" s="24"/>
+      <c r="XFC17" s="24"/>
+      <c r="XFD17" s="24"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
         <v>73</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>973</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="22" t="n">
         <f aca="false">1000*B18/$P18</f>
         <v>260.893020991029</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="23" t="n">
         <v>2700</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="22" t="n">
         <f aca="false">1000*D18/$P18</f>
         <v>723.958023305013</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="21" t="n">
         <v>1595.2</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="22" t="n">
         <f aca="false">1000*F18/$P18</f>
         <v>427.725125472651</v>
       </c>
       <c r="H18" s="21" t="n">
         <v>8344</v>
       </c>
-      <c r="I18" s="21" t="n">
+      <c r="I18" s="22" t="n">
         <f aca="false">1000*H18/$P18</f>
         <v>2237.29842461372</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="24" t="n">
         <f aca="false">L18*$J$37/100</f>
-        <v>1088</v>
-      </c>
-      <c r="K18" s="2" t="n">
+        <v>1026.8</v>
+      </c>
+      <c r="K18" s="25" t="n">
         <f aca="false">1000*J18/P18</f>
-        <v>291.728270131798</v>
-      </c>
-      <c r="L18" s="1" t="n">
-        <v>6400</v>
-      </c>
-      <c r="M18" s="1" t="n">
+        <v>275.318554936884</v>
+      </c>
+      <c r="L18" s="24" t="n">
+        <v>6040</v>
+      </c>
+      <c r="M18" s="24" t="n">
         <f aca="false">O18*$M$37/100</f>
         <v>7847.2</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" s="25" t="n">
         <f aca="false">1000*M18/P18</f>
         <v>2104.09014832559</v>
       </c>
-      <c r="O18" s="1" t="n">
+      <c r="O18" s="24" t="n">
         <v>57700</v>
       </c>
-      <c r="P18" s="1" t="n">
+      <c r="P18" s="25" t="n">
         <v>3729.498</v>
       </c>
-      <c r="Q18" s="1" t="n">
+      <c r="Q18" s="25" t="n">
         <f aca="false">100*P18/$P$36</f>
         <v>25.6153983414647</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="26" t="n">
         <f aca="false">H18+F18+B18+D18+J18+M18</f>
-        <v>22547.4</v>
-      </c>
-      <c r="S18" s="3" t="n">
+        <v>22486.2</v>
+      </c>
+      <c r="S18" s="27" t="n">
         <f aca="false">R18/P18</f>
-        <v>6.0456930128398</v>
-      </c>
-      <c r="U18" s="1" t="n">
+        <v>6.02928329764488</v>
+      </c>
+      <c r="T18" s="26"/>
+      <c r="U18" s="25" t="n">
         <f aca="false">-T18+($Q$45 + $Q$46)*1000*Q18/100</f>
-        <v>11469.5763767726</v>
-      </c>
-      <c r="V18" s="1" t="n">
+        <v>11356.3563161033</v>
+      </c>
+      <c r="V18" s="25" t="n">
         <f aca="false">U18/P18/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W18" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W18" s="25" t="n">
         <f aca="false">ROUND(U18/P18 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y18" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y18" s="25" t="n">
         <f aca="false">-Q18*($Q$47)*10</f>
         <v>-6147.69560195154</v>
       </c>
-      <c r="Z18" s="1" t="n">
+      <c r="Z18" s="25" t="n">
         <f aca="false">Y18/P18/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC18" s="1" t="n">
+      <c r="AC18" s="24" t="n">
         <v>4529.7</v>
       </c>
-      <c r="AH18" s="1" t="s">
+      <c r="AH18" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="AI18" s="1" t="n">
+      <c r="AI18" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="AJ18" s="1" t="n">
+      <c r="AJ18" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="AK18" s="1" t="n">
+      <c r="AK18" s="24" t="n">
         <f aca="false">AI18+AJ18/100</f>
         <v>6.4</v>
       </c>
-      <c r="AL18" s="1" t="n">
+      <c r="AL18" s="24" t="n">
         <f aca="false">AK18*1000</f>
         <v>6400</v>
       </c>
-      <c r="AO18" s="24" t="s">
+      <c r="AO18" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="AP18" s="1" t="n">
+      <c r="AP18" s="24" t="n">
         <v>57</v>
       </c>
-      <c r="AQ18" s="1" t="n">
+      <c r="AQ18" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="AR18" s="24" t="n">
+      <c r="AR18" s="29" t="n">
         <f aca="false">AP18+AQ18/10</f>
         <v>57.7</v>
       </c>
-      <c r="AS18" s="24" t="n">
+      <c r="AS18" s="29" t="n">
         <f aca="false">1000*AR18</f>
         <v>57700</v>
       </c>
-      <c r="AU18" s="25" t="s">
+      <c r="AU18" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="AV18" s="0" t="n">
+      <c r="AV18" s="24" t="n">
         <v>6.04</v>
       </c>
-      <c r="AW18" s="0" t="n">
+      <c r="AW18" s="24" t="n">
         <v>13.43</v>
       </c>
-      <c r="AX18" s="0" t="n">
+      <c r="AX18" s="24" t="n">
         <v>24.81</v>
       </c>
-      <c r="AY18" s="0" t="n">
+      <c r="AY18" s="24" t="n">
         <v>0.54</v>
       </c>
-      <c r="AZ18" s="0" t="n">
+      <c r="AZ18" s="24" t="n">
         <v>0.73</v>
       </c>
-      <c r="BA18" s="25" t="s">
+      <c r="BA18" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="BC18" s="25" t="n">
+      <c r="BC18" s="29" t="n">
         <f aca="false">AV18*1000</f>
         <v>6040</v>
       </c>
+      <c r="XDN18" s="24"/>
+      <c r="XDO18" s="24"/>
+      <c r="XDP18" s="24"/>
+      <c r="XDQ18" s="24"/>
+      <c r="XDR18" s="24"/>
+      <c r="XDS18" s="24"/>
+      <c r="XDT18" s="24"/>
+      <c r="XDU18" s="24"/>
+      <c r="XDV18" s="24"/>
+      <c r="XDW18" s="24"/>
+      <c r="XDX18" s="24"/>
+      <c r="XDY18" s="24"/>
+      <c r="XDZ18" s="24"/>
+      <c r="XEA18" s="24"/>
+      <c r="XEB18" s="24"/>
+      <c r="XEC18" s="24"/>
+      <c r="XED18" s="24"/>
+      <c r="XEE18" s="24"/>
+      <c r="XEF18" s="24"/>
+      <c r="XEG18" s="24"/>
+      <c r="XEH18" s="24"/>
+      <c r="XEI18" s="24"/>
+      <c r="XEJ18" s="24"/>
+      <c r="XEK18" s="24"/>
+      <c r="XEL18" s="24"/>
+      <c r="XEM18" s="24"/>
+      <c r="XEN18" s="24"/>
+      <c r="XEO18" s="24"/>
+      <c r="XEP18" s="24"/>
+      <c r="XEQ18" s="24"/>
+      <c r="XER18" s="24"/>
+      <c r="XES18" s="24"/>
+      <c r="XET18" s="24"/>
+      <c r="XEU18" s="24"/>
+      <c r="XEV18" s="24"/>
+      <c r="XEW18" s="24"/>
+      <c r="XEX18" s="24"/>
+      <c r="XEY18" s="24"/>
+      <c r="XEZ18" s="24"/>
+      <c r="XFA18" s="24"/>
+      <c r="XFB18" s="24"/>
+      <c r="XFC18" s="24"/>
+      <c r="XFD18" s="24"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
+    <row r="19" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="31" t="n">
         <v>91</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="22" t="n">
         <f aca="false">1000*B19/$P19</f>
         <v>503.093193867792</v>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D19" s="32" t="n">
         <v>54</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="22" t="n">
         <f aca="false">1000*D19/$P19</f>
         <v>298.538818339129</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="31" t="n">
         <v>22.7</v>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="22" t="n">
         <f aca="false">1000*F19/$P19</f>
         <v>125.496873635152</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="31" t="n">
         <v>118</v>
       </c>
-      <c r="I19" s="21" t="n">
+      <c r="I19" s="22" t="n">
         <f aca="false">1000*H19/$P19</f>
         <v>652.362603037356</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="24" t="n">
         <f aca="false">L19*$J$37/100</f>
         <v>431.8</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="25" t="n">
         <f aca="false">1000*J19/P19</f>
         <v>2387.20484738585</v>
       </c>
-      <c r="L19" s="1" t="n">
+      <c r="L19" s="24" t="n">
         <v>2540</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="24" t="n">
         <f aca="false">O19*$M$37/100</f>
         <v>856.8</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" s="25" t="n">
         <f aca="false">1000*M19/P19</f>
         <v>4736.81591764751</v>
       </c>
-      <c r="O19" s="1" t="n">
+      <c r="O19" s="24" t="n">
         <v>6300</v>
       </c>
-      <c r="P19" s="1" t="n">
+      <c r="P19" s="25" t="n">
         <v>180.881</v>
       </c>
-      <c r="Q19" s="1" t="n">
+      <c r="Q19" s="25" t="n">
         <f aca="false">100*P19/$P$36</f>
         <v>1.24234920286926</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="26" t="n">
         <f aca="false">H19+F19+B19+D19+J19+M19</f>
         <v>1574.3</v>
       </c>
-      <c r="S19" s="3" t="n">
+      <c r="S19" s="27" t="n">
         <f aca="false">R19/P19</f>
         <v>8.70351225391279</v>
       </c>
-      <c r="T19" s="30" t="n">
+      <c r="T19" s="33" t="n">
         <f aca="false">F19</f>
         <v>22.7</v>
       </c>
-      <c r="U19" s="1" t="n">
+      <c r="U19" s="25" t="n">
         <f aca="false">-T19+($Q$45 + $Q$46)*1000*Q19/100</f>
-        <v>533.575521425941</v>
-      </c>
-      <c r="V19" s="1" t="n">
+        <v>528.08433794926</v>
+      </c>
+      <c r="V19" s="25" t="n">
         <f aca="false">U19/P19/10</f>
-        <v>0.294987047520713</v>
-      </c>
-      <c r="W19" s="1" t="n">
+        <v>0.291951248582914</v>
+      </c>
+      <c r="W19" s="25" t="n">
         <f aca="false">ROUND(U19/P19 *100/1000, 2)</f>
         <v>0.29</v>
       </c>
-      <c r="Y19" s="1" t="n">
+      <c r="Y19" s="25" t="n">
         <f aca="false">-Q19*($Q$47)*10</f>
         <v>-298.163808688621</v>
       </c>
-      <c r="Z19" s="1" t="n">
+      <c r="Z19" s="25" t="n">
         <f aca="false">Y19/P19/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC19" s="1" t="n">
+      <c r="AC19" s="24" t="n">
         <v>248.4</v>
       </c>
-      <c r="AH19" s="1" t="s">
+      <c r="AH19" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="AI19" s="1" t="n">
+      <c r="AI19" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="AJ19" s="1" t="n">
+      <c r="AJ19" s="24" t="n">
         <v>54</v>
       </c>
-      <c r="AK19" s="1" t="n">
+      <c r="AK19" s="24" t="n">
         <f aca="false">AI19+AJ19/100</f>
         <v>2.54</v>
       </c>
-      <c r="AL19" s="1" t="n">
+      <c r="AL19" s="24" t="n">
         <f aca="false">AK19*1000</f>
         <v>2540</v>
       </c>
-      <c r="AO19" s="24" t="s">
+      <c r="AO19" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="AP19" s="1" t="n">
+      <c r="AP19" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="AQ19" s="1" t="n">
+      <c r="AQ19" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="AR19" s="24" t="n">
+      <c r="AR19" s="29" t="n">
         <f aca="false">AP19+AQ19/10</f>
         <v>6.3</v>
       </c>
-      <c r="AS19" s="24" t="n">
+      <c r="AS19" s="29" t="n">
         <f aca="false">1000*AR19</f>
         <v>6300</v>
       </c>
-      <c r="AU19" s="25" t="s">
+      <c r="AU19" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="AV19" s="0" t="n">
+      <c r="AV19" s="24" t="n">
         <v>2.54</v>
       </c>
-      <c r="AW19" s="0" t="n">
+      <c r="AW19" s="24" t="n">
         <v>5.64</v>
       </c>
-      <c r="AX19" s="0" t="n">
+      <c r="AX19" s="24" t="n">
         <v>1.3</v>
       </c>
-      <c r="AY19" s="0" t="n">
+      <c r="AY19" s="24" t="n">
         <v>4.34</v>
       </c>
-      <c r="AZ19" s="0" t="n">
+      <c r="AZ19" s="24" t="n">
         <v>5.88</v>
       </c>
-      <c r="BA19" s="25" t="s">
+      <c r="BA19" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="BC19" s="25" t="n">
+      <c r="BC19" s="29" t="n">
         <f aca="false">AV19*1000</f>
         <v>2540</v>
       </c>
+      <c r="XDN19" s="24"/>
+      <c r="XDO19" s="24"/>
+      <c r="XDP19" s="24"/>
+      <c r="XDQ19" s="24"/>
+      <c r="XDR19" s="24"/>
+      <c r="XDS19" s="24"/>
+      <c r="XDT19" s="24"/>
+      <c r="XDU19" s="24"/>
+      <c r="XDV19" s="24"/>
+      <c r="XDW19" s="24"/>
+      <c r="XDX19" s="24"/>
+      <c r="XDY19" s="24"/>
+      <c r="XDZ19" s="24"/>
+      <c r="XEA19" s="24"/>
+      <c r="XEB19" s="24"/>
+      <c r="XEC19" s="24"/>
+      <c r="XED19" s="24"/>
+      <c r="XEE19" s="24"/>
+      <c r="XEF19" s="24"/>
+      <c r="XEG19" s="24"/>
+      <c r="XEH19" s="24"/>
+      <c r="XEI19" s="24"/>
+      <c r="XEJ19" s="24"/>
+      <c r="XEK19" s="24"/>
+      <c r="XEL19" s="24"/>
+      <c r="XEM19" s="24"/>
+      <c r="XEN19" s="24"/>
+      <c r="XEO19" s="24"/>
+      <c r="XEP19" s="24"/>
+      <c r="XEQ19" s="24"/>
+      <c r="XER19" s="24"/>
+      <c r="XES19" s="24"/>
+      <c r="XET19" s="24"/>
+      <c r="XEU19" s="24"/>
+      <c r="XEV19" s="24"/>
+      <c r="XEW19" s="24"/>
+      <c r="XEX19" s="24"/>
+      <c r="XEY19" s="24"/>
+      <c r="XEZ19" s="24"/>
+      <c r="XFA19" s="24"/>
+      <c r="XFB19" s="24"/>
+      <c r="XFC19" s="24"/>
+      <c r="XFD19" s="24"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
         <v>81</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>139</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="22" t="n">
         <f aca="false">1000*B20/$P20</f>
         <v>933.361983293492</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>113</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E20" s="22" t="n">
         <f aca="false">1000*D20/$P20</f>
         <v>758.776288576724</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="21" t="n">
         <v>5.9</v>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="G20" s="22" t="n">
         <f aca="false">1000*F20/$P20</f>
         <v>39.617523031882</v>
       </c>
       <c r="H20" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="I20" s="21" t="n">
+      <c r="I20" s="22" t="n">
         <f aca="false">1000*H20/$P20</f>
         <v>1396.68555773415</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="24" t="n">
         <f aca="false">L20*$J$37/100</f>
         <v>62.9</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="25" t="n">
         <f aca="false">1000*J20/P20</f>
         <v>422.363084526336</v>
       </c>
-      <c r="L20" s="1" t="n">
+      <c r="L20" s="24" t="n">
         <v>370</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="24" t="n">
         <f aca="false">O20*$M$37/100</f>
         <v>340</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N20" s="25" t="n">
         <f aca="false">1000*M20/P20</f>
         <v>2283.04370014235</v>
       </c>
-      <c r="O20" s="1" t="n">
+      <c r="O20" s="24" t="n">
         <v>2500</v>
       </c>
-      <c r="P20" s="1" t="n">
+      <c r="P20" s="25" t="n">
         <v>148.924</v>
       </c>
-      <c r="Q20" s="1" t="n">
+      <c r="Q20" s="25" t="n">
         <f aca="false">100*P20/$P$36</f>
         <v>1.02285819233696</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="26" t="n">
         <f aca="false">H20+F20+B20+D20+J20+M20</f>
         <v>868.8</v>
       </c>
-      <c r="S20" s="3" t="n">
+      <c r="S20" s="27" t="n">
         <f aca="false">R20/P20</f>
         <v>5.83384813730493</v>
       </c>
-      <c r="U20" s="1" t="n">
+      <c r="T20" s="26"/>
+      <c r="U20" s="25" t="n">
         <f aca="false">-T20+($Q$45 + $Q$46)*1000*Q20/100</f>
-        <v>457.996007058988</v>
-      </c>
-      <c r="V20" s="1" t="n">
+        <v>453.47497384886</v>
+      </c>
+      <c r="V20" s="25" t="n">
         <f aca="false">U20/P20/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W20" s="1" t="n">
+        <v>0.304500935946429</v>
+      </c>
+      <c r="W20" s="25" t="n">
         <f aca="false">ROUND(U20/P20 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y20" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y20" s="25" t="n">
         <f aca="false">-Q20*($Q$47)*10</f>
         <v>-245.48596616087</v>
       </c>
-      <c r="Z20" s="1" t="n">
+      <c r="Z20" s="25" t="n">
         <f aca="false">Y20/P20/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC20" s="1" t="n">
+      <c r="AC20" s="24" t="n">
         <v>218.8</v>
       </c>
-      <c r="AH20" s="1" t="s">
+      <c r="AH20" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="AI20" s="1" t="n">
+      <c r="AI20" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" s="1" t="n">
+      <c r="AJ20" s="24" t="n">
         <v>37</v>
       </c>
-      <c r="AK20" s="1" t="n">
+      <c r="AK20" s="24" t="n">
         <f aca="false">AI20+AJ20/100</f>
         <v>0.37</v>
       </c>
-      <c r="AL20" s="1" t="n">
+      <c r="AL20" s="24" t="n">
         <f aca="false">AK20*1000</f>
         <v>370</v>
       </c>
-      <c r="AO20" s="24" t="s">
+      <c r="AO20" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="AP20" s="1" t="n">
+      <c r="AP20" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="AQ20" s="1" t="n">
+      <c r="AQ20" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="AR20" s="24" t="n">
+      <c r="AR20" s="29" t="n">
         <f aca="false">AP20+AQ20/10</f>
         <v>2.5</v>
       </c>
-      <c r="AS20" s="24" t="n">
+      <c r="AS20" s="29" t="n">
         <f aca="false">1000*AR20</f>
         <v>2500</v>
       </c>
-      <c r="AU20" s="25" t="s">
+      <c r="AU20" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="AV20" s="0" t="n">
+      <c r="AV20" s="24" t="n">
         <v>0.37</v>
       </c>
-      <c r="AW20" s="0" t="n">
+      <c r="AW20" s="24" t="n">
         <v>0.82</v>
       </c>
-      <c r="AX20" s="0" t="n">
+      <c r="AX20" s="24" t="n">
         <v>1.18</v>
       </c>
-      <c r="AY20" s="0" t="n">
+      <c r="AY20" s="24" t="n">
         <v>0.7</v>
       </c>
-      <c r="AZ20" s="0" t="n">
+      <c r="AZ20" s="24" t="n">
         <v>0.95</v>
       </c>
-      <c r="BA20" s="25" t="s">
+      <c r="BA20" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="BC20" s="25" t="n">
+      <c r="BC20" s="29" t="n">
         <f aca="false">AV20*1000</f>
         <v>370</v>
       </c>
+      <c r="XDN20" s="24"/>
+      <c r="XDO20" s="24"/>
+      <c r="XDP20" s="24"/>
+      <c r="XDQ20" s="24"/>
+      <c r="XDR20" s="24"/>
+      <c r="XDS20" s="24"/>
+      <c r="XDT20" s="24"/>
+      <c r="XDU20" s="24"/>
+      <c r="XDV20" s="24"/>
+      <c r="XDW20" s="24"/>
+      <c r="XDX20" s="24"/>
+      <c r="XDY20" s="24"/>
+      <c r="XDZ20" s="24"/>
+      <c r="XEA20" s="24"/>
+      <c r="XEB20" s="24"/>
+      <c r="XEC20" s="24"/>
+      <c r="XED20" s="24"/>
+      <c r="XEE20" s="24"/>
+      <c r="XEF20" s="24"/>
+      <c r="XEG20" s="24"/>
+      <c r="XEH20" s="24"/>
+      <c r="XEI20" s="24"/>
+      <c r="XEJ20" s="24"/>
+      <c r="XEK20" s="24"/>
+      <c r="XEL20" s="24"/>
+      <c r="XEM20" s="24"/>
+      <c r="XEN20" s="24"/>
+      <c r="XEO20" s="24"/>
+      <c r="XEP20" s="24"/>
+      <c r="XEQ20" s="24"/>
+      <c r="XER20" s="24"/>
+      <c r="XES20" s="24"/>
+      <c r="XET20" s="24"/>
+      <c r="XEU20" s="24"/>
+      <c r="XEV20" s="24"/>
+      <c r="XEW20" s="24"/>
+      <c r="XEX20" s="24"/>
+      <c r="XEY20" s="24"/>
+      <c r="XEZ20" s="24"/>
+      <c r="XFA20" s="24"/>
+      <c r="XFB20" s="24"/>
+      <c r="XFC20" s="24"/>
+      <c r="XFD20" s="24"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
+    <row r="21" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="27" t="n">
+      <c r="B21" s="31" t="n">
         <v>97</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="22" t="n">
         <f aca="false">1000*B21/$P21</f>
         <v>299.863052234907</v>
       </c>
-      <c r="D21" s="28" t="n">
+      <c r="D21" s="32" t="n">
         <v>160</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="22" t="n">
         <f aca="false">1000*D21/$P21</f>
         <v>494.619467603971</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="31" t="n">
         <v>241.4</v>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="G21" s="22" t="n">
         <f aca="false">1000*F21/$P21</f>
         <v>746.257121747491</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="31" t="n">
         <v>331</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="22" t="n">
         <f aca="false">1000*H21/$P21</f>
         <v>1023.24402360571</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="24" t="n">
         <f aca="false">L21*$J$37/100</f>
         <v>159.8</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="25" t="n">
         <f aca="false">1000*J21/P21</f>
         <v>494.001193269466</v>
       </c>
-      <c r="L21" s="1" t="n">
+      <c r="L21" s="24" t="n">
         <v>940</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="M21" s="24" t="n">
         <f aca="false">O21*$M$37/100</f>
         <v>516.8</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="N21" s="25" t="n">
         <f aca="false">1000*M21/P21</f>
         <v>1597.62088036082</v>
       </c>
-      <c r="O21" s="1" t="n">
+      <c r="O21" s="24" t="n">
         <v>3800</v>
       </c>
-      <c r="P21" s="1" t="n">
+      <c r="P21" s="25" t="n">
         <v>323.481</v>
       </c>
-      <c r="Q21" s="1" t="n">
+      <c r="Q21" s="25" t="n">
         <f aca="false">100*P21/$P$36</f>
         <v>2.22177211809615</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="26" t="n">
         <f aca="false">H21+F21+B21+D21+J21+M21</f>
         <v>1506</v>
       </c>
-      <c r="S21" s="3" t="n">
+      <c r="S21" s="27" t="n">
         <f aca="false">R21/P21</f>
         <v>4.65560573882237</v>
       </c>
-      <c r="T21" s="30" t="n">
+      <c r="T21" s="33" t="n">
         <f aca="false">F21</f>
         <v>241.4</v>
       </c>
-      <c r="U21" s="1" t="n">
+      <c r="U21" s="25" t="n">
         <f aca="false">-T21+($Q$45 + $Q$46)*1000*Q21/100</f>
-        <v>753.42290537085</v>
-      </c>
-      <c r="V21" s="1" t="n">
+        <v>743.602672608865</v>
+      </c>
+      <c r="V21" s="25" t="n">
         <f aca="false">U21/P21/10</f>
-        <v>0.232911022709479</v>
-      </c>
-      <c r="W21" s="1" t="n">
+        <v>0.229875223771679</v>
+      </c>
+      <c r="W21" s="25" t="n">
         <f aca="false">ROUND(U21/P21 *100/1000, 2)</f>
         <v>0.23</v>
       </c>
-      <c r="Y21" s="1" t="n">
+      <c r="Y21" s="25" t="n">
         <f aca="false">-Q21*($Q$47)*10</f>
         <v>-533.225308343076</v>
       </c>
-      <c r="Z21" s="1" t="n">
+      <c r="Z21" s="25" t="n">
         <f aca="false">Y21/P21/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC21" s="1" t="n">
+      <c r="AC21" s="24" t="n">
         <v>602.4</v>
       </c>
-      <c r="AH21" s="1" t="s">
+      <c r="AH21" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="AI21" s="1" t="n">
+      <c r="AI21" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" s="1" t="n">
+      <c r="AJ21" s="24" t="n">
         <v>94</v>
       </c>
-      <c r="AK21" s="1" t="n">
+      <c r="AK21" s="24" t="n">
         <f aca="false">AI21+AJ21/100</f>
         <v>0.94</v>
       </c>
-      <c r="AL21" s="1" t="n">
+      <c r="AL21" s="24" t="n">
         <f aca="false">AK21*1000</f>
         <v>940</v>
       </c>
-      <c r="AO21" s="24" t="s">
+      <c r="AO21" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="AP21" s="1" t="n">
+      <c r="AP21" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="AQ21" s="1" t="n">
+      <c r="AQ21" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="AR21" s="24" t="n">
+      <c r="AR21" s="29" t="n">
         <f aca="false">AP21+AQ21/10</f>
         <v>3.8</v>
       </c>
-      <c r="AS21" s="24" t="n">
+      <c r="AS21" s="29" t="n">
         <f aca="false">1000*AR21</f>
         <v>3800</v>
       </c>
-      <c r="AT21" s="24" t="s">
+      <c r="AT21" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="AU21" s="25" t="s">
+      <c r="AU21" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="AV21" s="0" t="n">
+      <c r="AV21" s="24" t="n">
         <v>0.94</v>
       </c>
-      <c r="AW21" s="0" t="n">
+      <c r="AW21" s="24" t="n">
         <v>2.1</v>
       </c>
-      <c r="AX21" s="0" t="n">
+      <c r="AX21" s="24" t="n">
         <v>2.33</v>
       </c>
-      <c r="AY21" s="0" t="n">
+      <c r="AY21" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="AZ21" s="0" t="n">
+      <c r="AZ21" s="24" t="n">
         <v>1.22</v>
       </c>
-      <c r="BA21" s="25" t="s">
+      <c r="BA21" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="BC21" s="25" t="n">
+      <c r="BC21" s="29" t="n">
         <f aca="false">AV21*1000</f>
         <v>940</v>
       </c>
+      <c r="XDN21" s="24"/>
+      <c r="XDO21" s="24"/>
+      <c r="XDP21" s="24"/>
+      <c r="XDQ21" s="24"/>
+      <c r="XDR21" s="24"/>
+      <c r="XDS21" s="24"/>
+      <c r="XDT21" s="24"/>
+      <c r="XDU21" s="24"/>
+      <c r="XDV21" s="24"/>
+      <c r="XDW21" s="24"/>
+      <c r="XDX21" s="24"/>
+      <c r="XDY21" s="24"/>
+      <c r="XDZ21" s="24"/>
+      <c r="XEA21" s="24"/>
+      <c r="XEB21" s="24"/>
+      <c r="XEC21" s="24"/>
+      <c r="XED21" s="24"/>
+      <c r="XEE21" s="24"/>
+      <c r="XEF21" s="24"/>
+      <c r="XEG21" s="24"/>
+      <c r="XEH21" s="24"/>
+      <c r="XEI21" s="24"/>
+      <c r="XEJ21" s="24"/>
+      <c r="XEK21" s="24"/>
+      <c r="XEL21" s="24"/>
+      <c r="XEM21" s="24"/>
+      <c r="XEN21" s="24"/>
+      <c r="XEO21" s="24"/>
+      <c r="XEP21" s="24"/>
+      <c r="XEQ21" s="24"/>
+      <c r="XER21" s="24"/>
+      <c r="XES21" s="24"/>
+      <c r="XET21" s="24"/>
+      <c r="XEU21" s="24"/>
+      <c r="XEV21" s="24"/>
+      <c r="XEW21" s="24"/>
+      <c r="XEX21" s="24"/>
+      <c r="XEY21" s="24"/>
+      <c r="XEZ21" s="24"/>
+      <c r="XFA21" s="24"/>
+      <c r="XFB21" s="24"/>
+      <c r="XFC21" s="24"/>
+      <c r="XFD21" s="24"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B22" s="21" t="n">
         <v>464</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="22" t="n">
         <f aca="false">1000*B22/$P22</f>
         <v>255.791133309077</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <v>891</v>
       </c>
-      <c r="E22" s="21" t="n">
+      <c r="E22" s="22" t="n">
         <f aca="false">1000*D22/$P22</f>
         <v>491.185128832732</v>
       </c>
-      <c r="F22" s="23" t="n">
+      <c r="F22" s="21" t="n">
         <v>544.5</v>
       </c>
-      <c r="G22" s="21" t="n">
+      <c r="G22" s="22" t="n">
         <f aca="false">1000*F22/$P22</f>
         <v>300.168689842225</v>
       </c>
       <c r="H22" s="21" t="n">
         <v>2618</v>
       </c>
-      <c r="I22" s="21" t="n">
+      <c r="I22" s="22" t="n">
         <f aca="false">1000*H22/$P22</f>
         <v>1443.23531681716</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="24" t="n">
         <f aca="false">L22*$J$37/100</f>
         <v>1208.7</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="25" t="n">
         <f aca="false">1000*J22/P22</f>
         <v>666.324876790262</v>
       </c>
-      <c r="L22" s="1" t="n">
+      <c r="L22" s="24" t="n">
         <v>7110</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M22" s="24" t="n">
         <f aca="false">O22*$M$37/100</f>
         <v>7684</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="N22" s="25" t="n">
         <f aca="false">1000*M22/P22</f>
         <v>4235.98937143739</v>
       </c>
-      <c r="O22" s="1" t="n">
+      <c r="O22" s="24" t="n">
         <v>56500</v>
       </c>
-      <c r="P22" s="1" t="n">
+      <c r="P22" s="25" t="n">
         <v>1813.98</v>
       </c>
-      <c r="Q22" s="1" t="n">
+      <c r="Q22" s="25" t="n">
         <f aca="false">100*P22/$P$36</f>
         <v>12.4590012606121</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="26" t="n">
         <f aca="false">H22+F22+B22+D22+J22+M22</f>
         <v>13410.2</v>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="S22" s="27" t="n">
         <f aca="false">R22/P22</f>
         <v>7.39269451702885</v>
       </c>
-      <c r="T22" s="3" t="n">
+      <c r="T22" s="26" t="n">
         <f aca="false">B22+F22</f>
         <v>1008.5</v>
       </c>
-      <c r="U22" s="1" t="n">
+      <c r="U22" s="25" t="n">
         <f aca="false">-T22+($Q$45 + $Q$46)*1000*Q22/100</f>
-        <v>4570.15486345292</v>
-      </c>
-      <c r="V22" s="1" t="n">
+        <v>4515.08607788103</v>
+      </c>
+      <c r="V22" s="25" t="n">
         <f aca="false">U22/P22/10</f>
-        <v>0.251940752569098</v>
-      </c>
-      <c r="W22" s="1" t="n">
+        <v>0.248904953631298</v>
+      </c>
+      <c r="W22" s="25" t="n">
         <f aca="false">ROUND(U22/P22 *100/1000, 2)</f>
         <v>0.25</v>
       </c>
-      <c r="Y22" s="1" t="n">
+      <c r="Y22" s="25" t="n">
         <f aca="false">-Q22*($Q$47)*10</f>
         <v>-2990.1603025469</v>
       </c>
-      <c r="Z22" s="1" t="n">
+      <c r="Z22" s="25" t="n">
         <f aca="false">Y22/P22/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC22" s="1" t="n">
+      <c r="AC22" s="24" t="n">
         <v>2258</v>
       </c>
-      <c r="AH22" s="1" t="s">
+      <c r="AH22" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="AI22" s="1" t="n">
+      <c r="AI22" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="AJ22" s="1" t="n">
+      <c r="AJ22" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="AK22" s="1" t="n">
+      <c r="AK22" s="24" t="n">
         <f aca="false">AI22+AJ22/100</f>
         <v>7.11</v>
       </c>
-      <c r="AL22" s="1" t="n">
+      <c r="AL22" s="24" t="n">
         <f aca="false">AK22*1000</f>
         <v>7110</v>
       </c>
-      <c r="AO22" s="24" t="s">
+      <c r="AO22" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AP22" s="1" t="n">
+      <c r="AP22" s="24" t="n">
         <v>56</v>
       </c>
-      <c r="AQ22" s="1" t="n">
+      <c r="AQ22" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="AR22" s="24" t="n">
+      <c r="AR22" s="29" t="n">
         <f aca="false">AP22+AQ22/10</f>
         <v>56.5</v>
       </c>
-      <c r="AS22" s="24" t="n">
+      <c r="AS22" s="29" t="n">
         <f aca="false">1000*AR22</f>
         <v>56500</v>
       </c>
-      <c r="AU22" s="25" t="s">
+      <c r="AU22" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AV22" s="0" t="n">
+      <c r="AV22" s="24" t="n">
         <v>7.11</v>
       </c>
-      <c r="AW22" s="0" t="n">
+      <c r="AW22" s="24" t="n">
         <v>15.81</v>
       </c>
-      <c r="AX22" s="0" t="n">
+      <c r="AX22" s="24" t="n">
         <v>12.06</v>
       </c>
-      <c r="AY22" s="0" t="n">
+      <c r="AY22" s="24" t="n">
         <v>1.31</v>
       </c>
-      <c r="AZ22" s="0" t="n">
+      <c r="AZ22" s="24" t="n">
         <v>1.78</v>
       </c>
-      <c r="BA22" s="25" t="s">
+      <c r="BA22" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="BC22" s="25" t="n">
+      <c r="BC22" s="29" t="n">
         <f aca="false">AV22*1000</f>
         <v>7110</v>
       </c>
+      <c r="XDN22" s="24"/>
+      <c r="XDO22" s="24"/>
+      <c r="XDP22" s="24"/>
+      <c r="XDQ22" s="24"/>
+      <c r="XDR22" s="24"/>
+      <c r="XDS22" s="24"/>
+      <c r="XDT22" s="24"/>
+      <c r="XDU22" s="24"/>
+      <c r="XDV22" s="24"/>
+      <c r="XDW22" s="24"/>
+      <c r="XDX22" s="24"/>
+      <c r="XDY22" s="24"/>
+      <c r="XDZ22" s="24"/>
+      <c r="XEA22" s="24"/>
+      <c r="XEB22" s="24"/>
+      <c r="XEC22" s="24"/>
+      <c r="XED22" s="24"/>
+      <c r="XEE22" s="24"/>
+      <c r="XEF22" s="24"/>
+      <c r="XEG22" s="24"/>
+      <c r="XEH22" s="24"/>
+      <c r="XEI22" s="24"/>
+      <c r="XEJ22" s="24"/>
+      <c r="XEK22" s="24"/>
+      <c r="XEL22" s="24"/>
+      <c r="XEM22" s="24"/>
+      <c r="XEN22" s="24"/>
+      <c r="XEO22" s="24"/>
+      <c r="XEP22" s="24"/>
+      <c r="XEQ22" s="24"/>
+      <c r="XER22" s="24"/>
+      <c r="XES22" s="24"/>
+      <c r="XET22" s="24"/>
+      <c r="XEU22" s="24"/>
+      <c r="XEV22" s="24"/>
+      <c r="XEW22" s="24"/>
+      <c r="XEX22" s="24"/>
+      <c r="XEY22" s="24"/>
+      <c r="XEZ22" s="24"/>
+      <c r="XFA22" s="24"/>
+      <c r="XFB22" s="24"/>
+      <c r="XFC22" s="24"/>
+      <c r="XFD22" s="24"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
+    <row r="23" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="22" t="n">
         <f aca="false">1000*B23/$P23</f>
         <v>816.326530612245</v>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E23" s="22" t="n">
         <f aca="false">1000*D23/$P23</f>
         <v>604.686318972033</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="22" t="n">
         <f aca="false">1000*F23/$P23</f>
         <v>0</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="21" t="n">
+      <c r="I23" s="22" t="n">
         <f aca="false">1000*H23/$P23</f>
         <v>604.686318972033</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="24" t="n">
         <f aca="false">L23*$J$37/100</f>
         <v>30.6</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="25" t="n">
         <f aca="false">1000*J23/P23</f>
         <v>925.170068027211</v>
       </c>
-      <c r="L23" s="1" t="n">
+      <c r="L23" s="24" t="n">
         <v>180</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="M23" s="24" t="n">
         <f aca="false">O23*$M$37/100</f>
         <v>68</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="N23" s="25" t="n">
         <f aca="false">1000*M23/P23</f>
         <v>2055.93348450491</v>
       </c>
-      <c r="O23" s="1" t="n">
+      <c r="O23" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="P23" s="1" t="n">
+      <c r="P23" s="25" t="n">
         <v>33.075</v>
       </c>
-      <c r="Q23" s="1" t="n">
+      <c r="Q23" s="25" t="n">
         <f aca="false">100*P23/$P$36</f>
         <v>0.227169796080852</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="26" t="n">
         <f aca="false">H23+F23+B23+D23+J23+M23</f>
         <v>165.6</v>
       </c>
-      <c r="S23" s="3" t="n">
+      <c r="S23" s="27" t="n">
         <f aca="false">R23/P23</f>
         <v>5.00680272108844</v>
       </c>
-      <c r="U23" s="1" t="n">
+      <c r="T23" s="26"/>
+      <c r="U23" s="25" t="n">
         <f aca="false">-T23+($Q$45 + $Q$46)*1000*Q23/100</f>
-        <v>101.717775062958</v>
-      </c>
-      <c r="V23" s="1" t="n">
+        <v>100.713684564281</v>
+      </c>
+      <c r="V23" s="25" t="n">
         <f aca="false">U23/P23/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W23" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W23" s="25" t="n">
         <f aca="false">ROUND(U23/P23 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y23" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y23" s="25" t="n">
         <f aca="false">-Q23*($Q$47)*10</f>
         <v>-54.5207510594045</v>
       </c>
-      <c r="Z23" s="1" t="n">
+      <c r="Z23" s="25" t="n">
         <f aca="false">Y23/P23/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC23" s="1" t="n">
+      <c r="AC23" s="24" t="n">
         <v>43</v>
       </c>
-      <c r="AH23" s="1" t="s">
+      <c r="AH23" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="AI23" s="1" t="n">
+      <c r="AI23" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" s="1" t="n">
+      <c r="AJ23" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="AK23" s="1" t="n">
+      <c r="AK23" s="24" t="n">
         <f aca="false">AI23+AJ23/100</f>
         <v>0.18</v>
       </c>
-      <c r="AL23" s="1" t="n">
+      <c r="AL23" s="24" t="n">
         <f aca="false">AK23*1000</f>
         <v>180</v>
       </c>
-      <c r="AO23" s="24" t="s">
+      <c r="AO23" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="AP23" s="1" t="n">
+      <c r="AP23" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AQ23" s="1" t="n">
+      <c r="AQ23" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="AR23" s="24" t="n">
+      <c r="AR23" s="29" t="n">
         <f aca="false">AP23+AQ23/10</f>
         <v>0.5</v>
       </c>
-      <c r="AS23" s="24" t="n">
+      <c r="AS23" s="29" t="n">
         <f aca="false">1000*AR23</f>
         <v>500</v>
       </c>
-      <c r="AU23" s="25" t="s">
+      <c r="AU23" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="AV23" s="0" t="n">
+      <c r="AV23" s="24" t="n">
         <v>0.18</v>
       </c>
-      <c r="AW23" s="0" t="n">
+      <c r="AW23" s="24" t="n">
         <v>0.4</v>
       </c>
-      <c r="AX23" s="0" t="n">
+      <c r="AX23" s="24" t="n">
         <v>0.24</v>
       </c>
-      <c r="AY23" s="0" t="n">
+      <c r="AY23" s="24" t="n">
         <v>1.67</v>
       </c>
-      <c r="AZ23" s="0" t="n">
+      <c r="AZ23" s="24" t="n">
         <v>2.26</v>
       </c>
-      <c r="BA23" s="25" t="s">
+      <c r="BA23" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="BC23" s="25" t="n">
+      <c r="BC23" s="29" t="n">
         <f aca="false">AV23*1000</f>
         <v>180</v>
       </c>
+      <c r="XDN23" s="24"/>
+      <c r="XDO23" s="24"/>
+      <c r="XDP23" s="24"/>
+      <c r="XDQ23" s="24"/>
+      <c r="XDR23" s="24"/>
+      <c r="XDS23" s="24"/>
+      <c r="XDT23" s="24"/>
+      <c r="XDU23" s="24"/>
+      <c r="XDV23" s="24"/>
+      <c r="XDW23" s="24"/>
+      <c r="XDX23" s="24"/>
+      <c r="XDY23" s="24"/>
+      <c r="XDZ23" s="24"/>
+      <c r="XEA23" s="24"/>
+      <c r="XEB23" s="24"/>
+      <c r="XEC23" s="24"/>
+      <c r="XED23" s="24"/>
+      <c r="XEE23" s="24"/>
+      <c r="XEF23" s="24"/>
+      <c r="XEG23" s="24"/>
+      <c r="XEH23" s="24"/>
+      <c r="XEI23" s="24"/>
+      <c r="XEJ23" s="24"/>
+      <c r="XEK23" s="24"/>
+      <c r="XEL23" s="24"/>
+      <c r="XEM23" s="24"/>
+      <c r="XEN23" s="24"/>
+      <c r="XEO23" s="24"/>
+      <c r="XEP23" s="24"/>
+      <c r="XEQ23" s="24"/>
+      <c r="XER23" s="24"/>
+      <c r="XES23" s="24"/>
+      <c r="XET23" s="24"/>
+      <c r="XEU23" s="24"/>
+      <c r="XEV23" s="24"/>
+      <c r="XEW23" s="24"/>
+      <c r="XEX23" s="24"/>
+      <c r="XEY23" s="24"/>
+      <c r="XEZ23" s="24"/>
+      <c r="XFA23" s="24"/>
+      <c r="XFB23" s="24"/>
+      <c r="XFC23" s="24"/>
+      <c r="XFD23" s="24"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
         <v>96</v>
       </c>
       <c r="B24" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="22" t="n">
         <f aca="false">1000*B24/$P24</f>
         <v>759.034360189574</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E24" s="22" t="n">
         <f aca="false">1000*D24/$P24</f>
         <v>444.312796208531</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F24" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="22" t="n">
         <f aca="false">1000*F24/$P24</f>
         <v>1.85130331753555</v>
       </c>
       <c r="H24" s="21" t="n">
         <v>31</v>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="I24" s="22" t="n">
         <f aca="false">1000*H24/$P24</f>
         <v>573.904028436019</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="24" t="n">
         <f aca="false">L24*$J$37/100</f>
         <v>23.8</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="25" t="n">
         <f aca="false">1000*J24/P24</f>
         <v>440.61018957346</v>
       </c>
-      <c r="L24" s="1" t="n">
+      <c r="L24" s="24" t="n">
         <v>140</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M24" s="24" t="n">
         <f aca="false">O24*$M$37/100</f>
         <v>108.8</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="N24" s="25" t="n">
         <f aca="false">1000*M24/P24</f>
         <v>2014.21800947867</v>
       </c>
-      <c r="O24" s="1" t="n">
+      <c r="O24" s="24" t="n">
         <v>800</v>
       </c>
-      <c r="P24" s="1" t="n">
+      <c r="P24" s="25" t="n">
         <v>54.016</v>
       </c>
-      <c r="Q24" s="1" t="n">
+      <c r="Q24" s="25" t="n">
         <f aca="false">100*P24/$P$36</f>
         <v>0.370999356163366</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="26" t="n">
         <f aca="false">H24+F24+B24+D24+J24+M24</f>
         <v>228.7</v>
       </c>
-      <c r="S24" s="3" t="n">
+      <c r="S24" s="27" t="n">
         <f aca="false">R24/P24</f>
         <v>4.23393068720379</v>
       </c>
-      <c r="U24" s="1" t="n">
+      <c r="T24" s="26"/>
+      <c r="U24" s="25" t="n">
         <f aca="false">-T24+($Q$45 + $Q$46)*1000*Q24/100</f>
-        <v>166.119042715065</v>
-      </c>
-      <c r="V24" s="1" t="n">
+        <v>164.479225560823</v>
+      </c>
+      <c r="V24" s="25" t="n">
         <f aca="false">U24/P24/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W24" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W24" s="25" t="n">
         <f aca="false">ROUND(U24/P24 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y24" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y24" s="25" t="n">
         <f aca="false">-Q24*($Q$47)*10</f>
         <v>-89.0398454792077</v>
       </c>
-      <c r="Z24" s="1" t="n">
+      <c r="Z24" s="25" t="n">
         <f aca="false">Y24/P24/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC24" s="1" t="n">
+      <c r="AC24" s="24" t="n">
         <v>84.3</v>
       </c>
-      <c r="AH24" s="1" t="s">
+      <c r="AH24" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="AI24" s="1" t="n">
+      <c r="AI24" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" s="1" t="n">
+      <c r="AJ24" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="AK24" s="1" t="n">
+      <c r="AK24" s="24" t="n">
         <f aca="false">AI24+AJ24/100</f>
         <v>0.14</v>
       </c>
-      <c r="AL24" s="1" t="n">
+      <c r="AL24" s="24" t="n">
         <f aca="false">AK24*1000</f>
         <v>140</v>
       </c>
-      <c r="AO24" s="24" t="s">
+      <c r="AO24" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AP24" s="1" t="n">
+      <c r="AP24" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AQ24" s="1" t="n">
+      <c r="AQ24" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="AR24" s="24" t="n">
+      <c r="AR24" s="29" t="n">
         <f aca="false">AP24+AQ24/10</f>
         <v>0.8</v>
       </c>
-      <c r="AS24" s="24" t="n">
+      <c r="AS24" s="29" t="n">
         <f aca="false">1000*AR24</f>
         <v>800</v>
       </c>
-      <c r="AU24" s="25" t="s">
+      <c r="AU24" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="AV24" s="0" t="n">
+      <c r="AV24" s="24" t="n">
         <v>0.14</v>
       </c>
-      <c r="AW24" s="0" t="n">
+      <c r="AW24" s="24" t="n">
         <v>0.31</v>
       </c>
-      <c r="AX24" s="0" t="n">
+      <c r="AX24" s="24" t="n">
         <v>0.42</v>
       </c>
-      <c r="AY24" s="0" t="n">
+      <c r="AY24" s="24" t="n">
         <v>0.74</v>
       </c>
-      <c r="AZ24" s="0" t="n">
+      <c r="AZ24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="BA24" s="25" t="s">
+      <c r="BA24" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="BC24" s="25" t="n">
+      <c r="BC24" s="29" t="n">
         <f aca="false">AV24*1000</f>
         <v>140</v>
       </c>
+      <c r="XDN24" s="24"/>
+      <c r="XDO24" s="24"/>
+      <c r="XDP24" s="24"/>
+      <c r="XDQ24" s="24"/>
+      <c r="XDR24" s="24"/>
+      <c r="XDS24" s="24"/>
+      <c r="XDT24" s="24"/>
+      <c r="XDU24" s="24"/>
+      <c r="XDV24" s="24"/>
+      <c r="XDW24" s="24"/>
+      <c r="XDX24" s="24"/>
+      <c r="XDY24" s="24"/>
+      <c r="XDZ24" s="24"/>
+      <c r="XEA24" s="24"/>
+      <c r="XEB24" s="24"/>
+      <c r="XEC24" s="24"/>
+      <c r="XED24" s="24"/>
+      <c r="XEE24" s="24"/>
+      <c r="XEF24" s="24"/>
+      <c r="XEG24" s="24"/>
+      <c r="XEH24" s="24"/>
+      <c r="XEI24" s="24"/>
+      <c r="XEJ24" s="24"/>
+      <c r="XEK24" s="24"/>
+      <c r="XEL24" s="24"/>
+      <c r="XEM24" s="24"/>
+      <c r="XEN24" s="24"/>
+      <c r="XEO24" s="24"/>
+      <c r="XEP24" s="24"/>
+      <c r="XEQ24" s="24"/>
+      <c r="XER24" s="24"/>
+      <c r="XES24" s="24"/>
+      <c r="XET24" s="24"/>
+      <c r="XEU24" s="24"/>
+      <c r="XEV24" s="24"/>
+      <c r="XEW24" s="24"/>
+      <c r="XEX24" s="24"/>
+      <c r="XEY24" s="24"/>
+      <c r="XEZ24" s="24"/>
+      <c r="XFA24" s="24"/>
+      <c r="XFB24" s="24"/>
+      <c r="XFC24" s="24"/>
+      <c r="XFD24" s="24"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
+    <row r="25" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="27" t="n">
+      <c r="B25" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="22" t="n">
         <f aca="false">1000*B25/$P25</f>
         <v>198.137507430157</v>
       </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="21" t="n">
+      <c r="D25" s="35"/>
+      <c r="E25" s="22" t="n">
         <f aca="false">1000*D25/$P25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="22" t="n">
         <f aca="false">1000*F25/$P25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="27" t="n">
+      <c r="H25" s="31" t="n">
         <v>208</v>
       </c>
-      <c r="I25" s="21" t="n">
+      <c r="I25" s="22" t="n">
         <f aca="false">1000*H25/$P25</f>
         <v>4121.26015454726</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="24" t="n">
         <f aca="false">L25*$J$37/100</f>
         <v>35.7</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="25" t="n">
         <f aca="false">1000*J25/P25</f>
         <v>707.350901525659</v>
       </c>
-      <c r="L25" s="1" t="n">
+      <c r="L25" s="24" t="n">
         <v>210</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="M25" s="24" t="n">
         <f aca="false">O25*$M$37/100</f>
         <v>244.8</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="N25" s="25" t="n">
         <f aca="false">1000*M25/P25</f>
         <v>4850.40618189023</v>
       </c>
-      <c r="O25" s="1" t="n">
+      <c r="O25" s="24" t="n">
         <v>1800</v>
       </c>
-      <c r="P25" s="1" t="n">
+      <c r="P25" s="25" t="n">
         <v>50.47</v>
       </c>
-      <c r="Q25" s="1" t="n">
+      <c r="Q25" s="25" t="n">
         <f aca="false">100*P25/$P$36</f>
         <v>0.346644281427078</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="26" t="n">
         <f aca="false">H25+F25+B25+D25+J25+M25</f>
         <v>498.5</v>
       </c>
-      <c r="S25" s="3" t="n">
+      <c r="S25" s="27" t="n">
         <f aca="false">R25/P25</f>
         <v>9.8771547453933</v>
       </c>
-      <c r="U25" s="1" t="n">
+      <c r="T25" s="26"/>
+      <c r="U25" s="25" t="n">
         <f aca="false">-T25+($Q$45 + $Q$46)*1000*Q25/100</f>
-        <v>155.21379009607</v>
-      </c>
-      <c r="V25" s="1" t="n">
+        <v>153.681622372162</v>
+      </c>
+      <c r="V25" s="25" t="n">
         <f aca="false">U25/P25/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W25" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W25" s="25" t="n">
         <f aca="false">ROUND(U25/P25 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y25" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y25" s="25" t="n">
         <f aca="false">-Q25*($Q$47)*10</f>
         <v>-83.1946275424988</v>
       </c>
-      <c r="Z25" s="1" t="n">
+      <c r="Z25" s="25" t="n">
         <f aca="false">Y25/P25/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC25" s="1" t="n">
+      <c r="AC25" s="24" t="n">
         <v>89.5</v>
       </c>
-      <c r="AH25" s="1" t="s">
+      <c r="AH25" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="AI25" s="1" t="n">
+      <c r="AI25" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" s="1" t="n">
+      <c r="AJ25" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="AK25" s="1" t="n">
+      <c r="AK25" s="24" t="n">
         <f aca="false">AI25+AJ25/100</f>
         <v>0.21</v>
       </c>
-      <c r="AL25" s="1" t="n">
+      <c r="AL25" s="24" t="n">
         <f aca="false">AK25*1000</f>
         <v>210</v>
       </c>
-      <c r="AO25" s="24" t="s">
+      <c r="AO25" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="AP25" s="1" t="n">
+      <c r="AP25" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AQ25" s="1" t="n">
+      <c r="AQ25" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="AR25" s="24" t="n">
+      <c r="AR25" s="29" t="n">
         <f aca="false">AP25+AQ25/10</f>
         <v>1.8</v>
       </c>
-      <c r="AS25" s="24" t="n">
+      <c r="AS25" s="29" t="n">
         <f aca="false">1000*AR25</f>
         <v>1800</v>
       </c>
-      <c r="AU25" s="25" t="s">
+      <c r="AU25" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="AV25" s="0" t="n">
+      <c r="AV25" s="24" t="n">
         <v>0.21</v>
       </c>
-      <c r="AW25" s="0" t="n">
+      <c r="AW25" s="24" t="n">
         <v>0.46</v>
       </c>
-      <c r="AX25" s="0" t="n">
+      <c r="AX25" s="24" t="n">
         <v>0.31</v>
       </c>
-      <c r="AY25" s="0" t="n">
+      <c r="AY25" s="24" t="n">
         <v>1.48</v>
       </c>
-      <c r="AZ25" s="0" t="n">
+      <c r="AZ25" s="24" t="n">
         <v>2.01</v>
       </c>
-      <c r="BA25" s="25" t="s">
+      <c r="BA25" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="BC25" s="25" t="n">
+      <c r="BC25" s="29" t="n">
         <f aca="false">AV25*1000</f>
         <v>210</v>
       </c>
+      <c r="XDN25" s="24"/>
+      <c r="XDO25" s="24"/>
+      <c r="XDP25" s="24"/>
+      <c r="XDQ25" s="24"/>
+      <c r="XDR25" s="24"/>
+      <c r="XDS25" s="24"/>
+      <c r="XDT25" s="24"/>
+      <c r="XDU25" s="24"/>
+      <c r="XDV25" s="24"/>
+      <c r="XDW25" s="24"/>
+      <c r="XDX25" s="24"/>
+      <c r="XDY25" s="24"/>
+      <c r="XDZ25" s="24"/>
+      <c r="XEA25" s="24"/>
+      <c r="XEB25" s="24"/>
+      <c r="XEC25" s="24"/>
+      <c r="XED25" s="24"/>
+      <c r="XEE25" s="24"/>
+      <c r="XEF25" s="24"/>
+      <c r="XEG25" s="24"/>
+      <c r="XEH25" s="24"/>
+      <c r="XEI25" s="24"/>
+      <c r="XEJ25" s="24"/>
+      <c r="XEK25" s="24"/>
+      <c r="XEL25" s="24"/>
+      <c r="XEM25" s="24"/>
+      <c r="XEN25" s="24"/>
+      <c r="XEO25" s="24"/>
+      <c r="XEP25" s="24"/>
+      <c r="XEQ25" s="24"/>
+      <c r="XER25" s="24"/>
+      <c r="XES25" s="24"/>
+      <c r="XET25" s="24"/>
+      <c r="XEU25" s="24"/>
+      <c r="XEV25" s="24"/>
+      <c r="XEW25" s="24"/>
+      <c r="XEX25" s="24"/>
+      <c r="XEY25" s="24"/>
+      <c r="XEZ25" s="24"/>
+      <c r="XFA25" s="24"/>
+      <c r="XFB25" s="24"/>
+      <c r="XFC25" s="24"/>
+      <c r="XFD25" s="24"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
         <v>102</v>
       </c>
       <c r="B26" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="22" t="n">
         <f aca="false">1000*B26/$P26</f>
         <v>510.538983298082</v>
       </c>
-      <c r="D26" s="31"/>
-      <c r="E26" s="21" t="n">
+      <c r="D26" s="34"/>
+      <c r="E26" s="22" t="n">
         <f aca="false">1000*D26/$P26</f>
         <v>0</v>
       </c>
       <c r="F26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="22" t="n">
         <f aca="false">1000*F26/$P26</f>
         <v>0</v>
       </c>
       <c r="H26" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="I26" s="21" t="n">
+      <c r="I26" s="22" t="n">
         <f aca="false">1000*H26/$P26</f>
         <v>656.407264240391</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="24" t="n">
         <f aca="false">L26*$J$37/100</f>
         <v>45.9</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="25" t="n">
         <f aca="false">1000*J26/P26</f>
         <v>3347.67704762599</v>
       </c>
-      <c r="L26" s="1" t="n">
+      <c r="L26" s="24" t="n">
         <v>270</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="M26" s="24" t="n">
         <f aca="false">O26*$M$37/100</f>
         <v>122.4</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="N26" s="25" t="n">
         <f aca="false">1000*M26/P26</f>
         <v>8927.13879366932</v>
       </c>
-      <c r="O26" s="1" t="n">
+      <c r="O26" s="24" t="n">
         <v>900</v>
       </c>
-      <c r="P26" s="1" t="n">
+      <c r="P26" s="25" t="n">
         <v>13.711</v>
       </c>
-      <c r="Q26" s="1" t="n">
+      <c r="Q26" s="25" t="n">
         <f aca="false">100*P26/$P$36</f>
         <v>0.0941715819822998</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="26" t="n">
         <f aca="false">H26+F26+B26+D26+J26+M26</f>
         <v>184.3</v>
       </c>
-      <c r="S26" s="3" t="n">
+      <c r="S26" s="27" t="n">
         <f aca="false">R26/P26</f>
         <v>13.4417620888338</v>
       </c>
-      <c r="U26" s="1" t="n">
+      <c r="T26" s="26"/>
+      <c r="U26" s="25" t="n">
         <f aca="false">-T26+($Q$45 + $Q$46)*1000*Q26/100</f>
-        <v>42.1663617199765</v>
-      </c>
-      <c r="V26" s="1" t="n">
+        <v>41.7501233276148</v>
+      </c>
+      <c r="V26" s="25" t="n">
         <f aca="false">U26/P26/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W26" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W26" s="25" t="n">
         <f aca="false">ROUND(U26/P26 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y26" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y26" s="25" t="n">
         <f aca="false">-Q26*($Q$47)*10</f>
         <v>-22.6011796757519</v>
       </c>
-      <c r="Z26" s="1" t="n">
+      <c r="Z26" s="25" t="n">
         <f aca="false">Y26/P26/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC26" s="1" t="n">
+      <c r="AC26" s="24" t="n">
         <v>24.6</v>
       </c>
-      <c r="AH26" s="1" t="s">
+      <c r="AH26" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="AI26" s="1" t="n">
+      <c r="AI26" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ26" s="1" t="n">
+      <c r="AJ26" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="AK26" s="1" t="n">
+      <c r="AK26" s="24" t="n">
         <f aca="false">AI26+AJ26/100</f>
         <v>0.27</v>
       </c>
-      <c r="AL26" s="1" t="n">
+      <c r="AL26" s="24" t="n">
         <f aca="false">AK26*1000</f>
         <v>270</v>
       </c>
-      <c r="AO26" s="24" t="s">
+      <c r="AO26" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="AP26" s="1" t="n">
+      <c r="AP26" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AQ26" s="1" t="n">
+      <c r="AQ26" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="AR26" s="24" t="n">
+      <c r="AR26" s="29" t="n">
         <f aca="false">AP26+AQ26/10</f>
         <v>0.9</v>
       </c>
-      <c r="AS26" s="24" t="n">
+      <c r="AS26" s="29" t="n">
         <f aca="false">1000*AR26</f>
         <v>900</v>
       </c>
-      <c r="AU26" s="25" t="s">
+      <c r="AU26" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="AV26" s="0" t="n">
+      <c r="AV26" s="24" t="n">
         <v>0.27</v>
       </c>
-      <c r="AW26" s="0" t="n">
+      <c r="AW26" s="24" t="n">
         <v>0.61</v>
       </c>
-      <c r="AX26" s="0" t="n">
+      <c r="AX26" s="24" t="n">
         <v>0.11</v>
       </c>
-      <c r="AY26" s="0" t="n">
+      <c r="AY26" s="24" t="n">
         <v>5.6</v>
       </c>
-      <c r="AZ26" s="0" t="n">
+      <c r="AZ26" s="24" t="n">
         <v>7.59</v>
       </c>
-      <c r="BA26" s="25" t="s">
+      <c r="BA26" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="BC26" s="25" t="n">
+      <c r="BC26" s="29" t="n">
         <f aca="false">AV26*1000</f>
         <v>270</v>
       </c>
+      <c r="XDN26" s="24"/>
+      <c r="XDO26" s="24"/>
+      <c r="XDP26" s="24"/>
+      <c r="XDQ26" s="24"/>
+      <c r="XDR26" s="24"/>
+      <c r="XDS26" s="24"/>
+      <c r="XDT26" s="24"/>
+      <c r="XDU26" s="24"/>
+      <c r="XDV26" s="24"/>
+      <c r="XDW26" s="24"/>
+      <c r="XDX26" s="24"/>
+      <c r="XDY26" s="24"/>
+      <c r="XDZ26" s="24"/>
+      <c r="XEA26" s="24"/>
+      <c r="XEB26" s="24"/>
+      <c r="XEC26" s="24"/>
+      <c r="XED26" s="24"/>
+      <c r="XEE26" s="24"/>
+      <c r="XEF26" s="24"/>
+      <c r="XEG26" s="24"/>
+      <c r="XEH26" s="24"/>
+      <c r="XEI26" s="24"/>
+      <c r="XEJ26" s="24"/>
+      <c r="XEK26" s="24"/>
+      <c r="XEL26" s="24"/>
+      <c r="XEM26" s="24"/>
+      <c r="XEN26" s="24"/>
+      <c r="XEO26" s="24"/>
+      <c r="XEP26" s="24"/>
+      <c r="XEQ26" s="24"/>
+      <c r="XER26" s="24"/>
+      <c r="XES26" s="24"/>
+      <c r="XET26" s="24"/>
+      <c r="XEU26" s="24"/>
+      <c r="XEV26" s="24"/>
+      <c r="XEW26" s="24"/>
+      <c r="XEX26" s="24"/>
+      <c r="XEY26" s="24"/>
+      <c r="XEZ26" s="24"/>
+      <c r="XFA26" s="24"/>
+      <c r="XFB26" s="24"/>
+      <c r="XFC26" s="24"/>
+      <c r="XFD26" s="24"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="s">
+    <row r="27" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="31" t="n">
         <v>332</v>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="22" t="n">
         <f aca="false">1000*B27/$P27</f>
         <v>396.580804533444</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D27" s="32" t="n">
         <v>652</v>
       </c>
-      <c r="E27" s="21" t="n">
+      <c r="E27" s="22" t="n">
         <f aca="false">1000*D27/$P27</f>
         <v>778.827363119896</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="31" t="n">
         <v>1961</v>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="22" t="n">
         <f aca="false">1000*F27/$P27</f>
         <v>2342.4546918376</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="31" t="n">
         <v>913</v>
       </c>
-      <c r="I27" s="21" t="n">
+      <c r="I27" s="22" t="n">
         <f aca="false">1000*H27/$P27</f>
         <v>1090.59721246697</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="24" t="n">
         <f aca="false">L27*$J$37/100</f>
         <v>336.6</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="25" t="n">
         <f aca="false">1000*J27/P27</f>
         <v>402.075598813125</v>
       </c>
-      <c r="L27" s="1" t="n">
+      <c r="L27" s="24" t="n">
         <v>1980</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="M27" s="24" t="n">
         <f aca="false">O27*$M$37/100</f>
         <v>1496</v>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="N27" s="25" t="n">
         <f aca="false">1000*M27/P27</f>
         <v>1787.00266139166</v>
       </c>
-      <c r="O27" s="1" t="n">
+      <c r="O27" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="P27" s="1" t="n">
+      <c r="P27" s="25" t="n">
         <v>837.156</v>
       </c>
-      <c r="Q27" s="1" t="n">
+      <c r="Q27" s="25" t="n">
         <f aca="false">100*P27/$P$36</f>
         <v>5.74985813478041</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="26" t="n">
         <f aca="false">H27+F27+B27+D27+J27+M27</f>
         <v>5690.6</v>
       </c>
-      <c r="S27" s="3" t="n">
+      <c r="S27" s="27" t="n">
         <f aca="false">R27/P27</f>
         <v>6.7975383321627</v>
       </c>
-      <c r="U27" s="1" t="n">
+      <c r="T27" s="26"/>
+      <c r="U27" s="25" t="n">
         <f aca="false">-T27+($Q$45 + $Q$46)*1000*Q27/100</f>
-        <v>2574.56222828741</v>
-      </c>
-      <c r="V27" s="1" t="n">
+        <v>2549.14785533168</v>
+      </c>
+      <c r="V27" s="25" t="n">
         <f aca="false">U27/P27/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W27" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W27" s="25" t="n">
         <f aca="false">ROUND(U27/P27 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y27" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y27" s="25" t="n">
         <f aca="false">-Q27*($Q$47)*10</f>
         <v>-1379.9659523473</v>
       </c>
-      <c r="Z27" s="1" t="n">
+      <c r="Z27" s="25" t="n">
         <f aca="false">Y27/P27/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC27" s="1" t="n">
+      <c r="AC27" s="24" t="n">
         <v>1170.6</v>
       </c>
-      <c r="AH27" s="1" t="s">
+      <c r="AH27" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="AI27" s="1" t="n">
+      <c r="AI27" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AJ27" s="1" t="n">
+      <c r="AJ27" s="24" t="n">
         <v>98</v>
       </c>
-      <c r="AK27" s="1" t="n">
+      <c r="AK27" s="24" t="n">
         <f aca="false">AI27+AJ27/100</f>
         <v>1.98</v>
       </c>
-      <c r="AL27" s="1" t="n">
+      <c r="AL27" s="24" t="n">
         <f aca="false">AK27*1000</f>
         <v>1980</v>
       </c>
-      <c r="AO27" s="24" t="s">
+      <c r="AO27" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="AP27" s="1" t="n">
+      <c r="AP27" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="AQ27" s="1" t="n">
+      <c r="AQ27" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AR27" s="24" t="n">
+      <c r="AR27" s="29" t="n">
         <f aca="false">AP27+AQ27/10</f>
         <v>11</v>
       </c>
-      <c r="AS27" s="24" t="n">
+      <c r="AS27" s="29" t="n">
         <f aca="false">1000*AR27</f>
         <v>11000</v>
       </c>
-      <c r="AU27" s="25" t="s">
+      <c r="AU27" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="AV27" s="0" t="n">
+      <c r="AV27" s="24" t="n">
         <v>1.98</v>
       </c>
-      <c r="AW27" s="0" t="n">
+      <c r="AW27" s="24" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX27" s="0" t="n">
+      <c r="AX27" s="24" t="n">
         <v>6.06</v>
       </c>
-      <c r="AY27" s="0" t="n">
+      <c r="AY27" s="24" t="n">
         <v>0.73</v>
       </c>
-      <c r="AZ27" s="0" t="n">
+      <c r="AZ27" s="24" t="n">
         <v>0.99</v>
       </c>
-      <c r="BA27" s="25" t="s">
+      <c r="BA27" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="BC27" s="25" t="n">
+      <c r="BC27" s="29" t="n">
         <f aca="false">AV27*1000</f>
         <v>1980</v>
       </c>
+      <c r="XDN27" s="24"/>
+      <c r="XDO27" s="24"/>
+      <c r="XDP27" s="24"/>
+      <c r="XDQ27" s="24"/>
+      <c r="XDR27" s="24"/>
+      <c r="XDS27" s="24"/>
+      <c r="XDT27" s="24"/>
+      <c r="XDU27" s="24"/>
+      <c r="XDV27" s="24"/>
+      <c r="XDW27" s="24"/>
+      <c r="XDX27" s="24"/>
+      <c r="XDY27" s="24"/>
+      <c r="XDZ27" s="24"/>
+      <c r="XEA27" s="24"/>
+      <c r="XEB27" s="24"/>
+      <c r="XEC27" s="24"/>
+      <c r="XED27" s="24"/>
+      <c r="XEE27" s="24"/>
+      <c r="XEF27" s="24"/>
+      <c r="XEG27" s="24"/>
+      <c r="XEH27" s="24"/>
+      <c r="XEI27" s="24"/>
+      <c r="XEJ27" s="24"/>
+      <c r="XEK27" s="24"/>
+      <c r="XEL27" s="24"/>
+      <c r="XEM27" s="24"/>
+      <c r="XEN27" s="24"/>
+      <c r="XEO27" s="24"/>
+      <c r="XEP27" s="24"/>
+      <c r="XEQ27" s="24"/>
+      <c r="XER27" s="24"/>
+      <c r="XES27" s="24"/>
+      <c r="XET27" s="24"/>
+      <c r="XEU27" s="24"/>
+      <c r="XEV27" s="24"/>
+      <c r="XEW27" s="24"/>
+      <c r="XEX27" s="24"/>
+      <c r="XEY27" s="24"/>
+      <c r="XEZ27" s="24"/>
+      <c r="XFA27" s="24"/>
+      <c r="XFB27" s="24"/>
+      <c r="XFC27" s="24"/>
+      <c r="XFD27" s="24"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="21" t="n">
         <v>494</v>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="22" t="n">
         <f aca="false">1000*B28/$P28</f>
         <v>901.606282772202</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="23" t="n">
         <v>427</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="22" t="n">
         <f aca="false">1000*D28/$P28</f>
         <v>779.323649278806</v>
       </c>
       <c r="F28" s="21" t="n">
         <v>63</v>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="G28" s="22" t="n">
         <f aca="false">1000*F28/$P28</f>
         <v>114.982177762447</v>
       </c>
       <c r="H28" s="21" t="n">
         <v>560</v>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="I28" s="22" t="n">
         <f aca="false">1000*H28/$P28</f>
         <v>1022.06380233286</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="24" t="n">
         <f aca="false">L28*$J$37/100</f>
         <v>202.3</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="25" t="n">
         <f aca="false">1000*J28/P28</f>
         <v>369.220548592746</v>
       </c>
-      <c r="L28" s="1" t="n">
+      <c r="L28" s="24" t="n">
         <v>1190</v>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="M28" s="24" t="n">
         <f aca="false">O28*$M$37/100</f>
         <v>1088</v>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="N28" s="25" t="n">
         <f aca="false">1000*M28/P28</f>
         <v>1985.72395881813</v>
       </c>
-      <c r="O28" s="1" t="n">
+      <c r="O28" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="P28" s="1" t="n">
+      <c r="P28" s="25" t="n">
         <v>547.911</v>
       </c>
-      <c r="Q28" s="1" t="n">
+      <c r="Q28" s="25" t="n">
         <f aca="false">100*P28/$P$36</f>
         <v>3.76322993621937</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="26" t="n">
         <f aca="false">H28+F28+B28+D28+J28+M28</f>
         <v>2834.3</v>
       </c>
-      <c r="S28" s="3" t="n">
+      <c r="S28" s="27" t="n">
         <f aca="false">R28/P28</f>
         <v>5.17292041955719</v>
       </c>
-      <c r="U28" s="1" t="n">
+      <c r="T28" s="26"/>
+      <c r="U28" s="25" t="n">
         <f aca="false">-T28+($Q$45 + $Q$46)*1000*Q28/100</f>
-        <v>1685.02759947152</v>
-      </c>
-      <c r="V28" s="1" t="n">
+        <v>1668.39412315343</v>
+      </c>
+      <c r="V28" s="25" t="n">
         <f aca="false">U28/P28/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W28" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W28" s="25" t="n">
         <f aca="false">ROUND(U28/P28 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y28" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y28" s="25" t="n">
         <f aca="false">-Q28*($Q$47)*10</f>
         <v>-903.17518469265</v>
       </c>
-      <c r="Z28" s="1" t="n">
+      <c r="Z28" s="25" t="n">
         <f aca="false">Y28/P28/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC28" s="1" t="n">
+      <c r="AC28" s="24" t="n">
         <v>922.9</v>
       </c>
-      <c r="AH28" s="1" t="s">
+      <c r="AH28" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="AI28" s="1" t="n">
+      <c r="AI28" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AJ28" s="1" t="n">
+      <c r="AJ28" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="AK28" s="1" t="n">
+      <c r="AK28" s="24" t="n">
         <f aca="false">AI28+AJ28/100</f>
         <v>1.19</v>
       </c>
-      <c r="AL28" s="1" t="n">
+      <c r="AL28" s="24" t="n">
         <f aca="false">AK28*1000</f>
         <v>1190</v>
       </c>
-      <c r="AO28" s="24" t="s">
+      <c r="AO28" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="AP28" s="1" t="n">
+      <c r="AP28" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="AQ28" s="1" t="n">
+      <c r="AQ28" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AR28" s="24" t="n">
+      <c r="AR28" s="29" t="n">
         <f aca="false">AP28+AQ28/10</f>
         <v>8</v>
       </c>
-      <c r="AS28" s="24" t="n">
+      <c r="AS28" s="29" t="n">
         <f aca="false">1000*AR28</f>
         <v>8000</v>
       </c>
-      <c r="AU28" s="25" t="s">
+      <c r="AU28" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="AV28" s="0" t="n">
+      <c r="AV28" s="24" t="n">
         <v>1.19</v>
       </c>
-      <c r="AW28" s="0" t="n">
+      <c r="AW28" s="24" t="n">
         <v>2.65</v>
       </c>
-      <c r="AX28" s="0" t="n">
+      <c r="AX28" s="24" t="n">
         <v>4.77</v>
       </c>
-      <c r="AY28" s="0" t="n">
+      <c r="AY28" s="24" t="n">
         <v>0.56</v>
       </c>
-      <c r="AZ28" s="0" t="n">
+      <c r="AZ28" s="24" t="n">
         <v>0.76</v>
       </c>
-      <c r="BA28" s="25" t="s">
+      <c r="BA28" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="BC28" s="25" t="n">
+      <c r="BC28" s="29" t="n">
         <f aca="false">AV28*1000</f>
         <v>1190</v>
       </c>
+      <c r="XDN28" s="24"/>
+      <c r="XDO28" s="24"/>
+      <c r="XDP28" s="24"/>
+      <c r="XDQ28" s="24"/>
+      <c r="XDR28" s="24"/>
+      <c r="XDS28" s="24"/>
+      <c r="XDT28" s="24"/>
+      <c r="XDU28" s="24"/>
+      <c r="XDV28" s="24"/>
+      <c r="XDW28" s="24"/>
+      <c r="XDX28" s="24"/>
+      <c r="XDY28" s="24"/>
+      <c r="XDZ28" s="24"/>
+      <c r="XEA28" s="24"/>
+      <c r="XEB28" s="24"/>
+      <c r="XEC28" s="24"/>
+      <c r="XED28" s="24"/>
+      <c r="XEE28" s="24"/>
+      <c r="XEF28" s="24"/>
+      <c r="XEG28" s="24"/>
+      <c r="XEH28" s="24"/>
+      <c r="XEI28" s="24"/>
+      <c r="XEJ28" s="24"/>
+      <c r="XEK28" s="24"/>
+      <c r="XEL28" s="24"/>
+      <c r="XEM28" s="24"/>
+      <c r="XEN28" s="24"/>
+      <c r="XEO28" s="24"/>
+      <c r="XEP28" s="24"/>
+      <c r="XEQ28" s="24"/>
+      <c r="XER28" s="24"/>
+      <c r="XES28" s="24"/>
+      <c r="XET28" s="24"/>
+      <c r="XEU28" s="24"/>
+      <c r="XEV28" s="24"/>
+      <c r="XEW28" s="24"/>
+      <c r="XEX28" s="24"/>
+      <c r="XEY28" s="24"/>
+      <c r="XEZ28" s="24"/>
+      <c r="XFA28" s="24"/>
+      <c r="XFB28" s="24"/>
+      <c r="XFC28" s="24"/>
+      <c r="XFD28" s="24"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="s">
+    <row r="29" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="31" t="n">
         <v>136</v>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="22" t="n">
         <f aca="false">1000*B29/$P29</f>
         <v>641.88790560472</v>
       </c>
-      <c r="D29" s="28" t="n">
+      <c r="D29" s="32" t="n">
         <v>84</v>
       </c>
-      <c r="E29" s="21" t="n">
+      <c r="E29" s="22" t="n">
         <f aca="false">1000*D29/$P29</f>
         <v>396.46017699115</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="31" t="n">
         <v>24.9</v>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="G29" s="22" t="n">
         <f aca="false">1000*F29/$P29</f>
         <v>117.522123893805</v>
       </c>
-      <c r="H29" s="27" t="n">
+      <c r="H29" s="31" t="n">
         <v>330</v>
       </c>
-      <c r="I29" s="21" t="n">
+      <c r="I29" s="22" t="n">
         <f aca="false">1000*H29/$P29</f>
         <v>1557.52212389381</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="24" t="n">
         <f aca="false">L29*$J$37/100</f>
         <v>331.5</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="25" t="n">
         <f aca="false">1000*J29/P29</f>
         <v>1564.6017699115</v>
       </c>
-      <c r="L29" s="1" t="n">
+      <c r="L29" s="24" t="n">
         <v>1950</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="M29" s="24" t="n">
         <f aca="false">O29*$M$37/100</f>
         <v>870.4</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="N29" s="25" t="n">
         <f aca="false">1000*M29/P29</f>
         <v>4108.08259587021</v>
       </c>
-      <c r="O29" s="1" t="n">
+      <c r="O29" s="24" t="n">
         <v>6400</v>
       </c>
-      <c r="P29" s="1" t="n">
+      <c r="P29" s="25" t="n">
         <v>211.875</v>
       </c>
-      <c r="Q29" s="1" t="n">
+      <c r="Q29" s="25" t="n">
         <f aca="false">100*P29/$P$36</f>
         <v>1.45522601797825</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="26" t="n">
         <f aca="false">H29+F29+B29+D29+J29+M29</f>
         <v>1776.8</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="27" t="n">
         <f aca="false">R29/P29</f>
         <v>8.38607669616519</v>
       </c>
-      <c r="U29" s="1" t="n">
+      <c r="T29" s="26"/>
+      <c r="U29" s="25" t="n">
         <f aca="false">-T29+($Q$45 + $Q$46)*1000*Q29/100</f>
-        <v>651.593457035958</v>
-      </c>
-      <c r="V29" s="1" t="n">
+        <v>645.161358036495</v>
+      </c>
+      <c r="V29" s="25" t="n">
         <f aca="false">U29/P29/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W29" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W29" s="25" t="n">
         <f aca="false">ROUND(U29/P29 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y29" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y29" s="25" t="n">
         <f aca="false">-Q29*($Q$47)*10</f>
         <v>-349.25424431478</v>
       </c>
-      <c r="Z29" s="1" t="n">
+      <c r="Z29" s="25" t="n">
         <f aca="false">Y29/P29/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC29" s="1" t="n">
+      <c r="AC29" s="24" t="n">
         <v>306.8</v>
       </c>
-      <c r="AH29" s="1" t="s">
+      <c r="AH29" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="AI29" s="1" t="n">
+      <c r="AI29" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AJ29" s="1" t="n">
+      <c r="AJ29" s="24" t="n">
         <v>95</v>
       </c>
-      <c r="AK29" s="1" t="n">
+      <c r="AK29" s="24" t="n">
         <f aca="false">AI29+AJ29/100</f>
         <v>1.95</v>
       </c>
-      <c r="AL29" s="1" t="n">
+      <c r="AL29" s="24" t="n">
         <f aca="false">AK29*1000</f>
         <v>1950</v>
       </c>
-      <c r="AO29" s="24" t="s">
+      <c r="AO29" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="AP29" s="1" t="n">
+      <c r="AP29" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="AQ29" s="1" t="n">
+      <c r="AQ29" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="AR29" s="24" t="n">
+      <c r="AR29" s="29" t="n">
         <f aca="false">AP29+AQ29/10</f>
         <v>6.4</v>
       </c>
-      <c r="AS29" s="24" t="n">
+      <c r="AS29" s="29" t="n">
         <f aca="false">1000*AR29</f>
         <v>6400</v>
       </c>
-      <c r="AU29" s="25" t="s">
+      <c r="AU29" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="AV29" s="0" t="n">
+      <c r="AV29" s="24" t="n">
         <v>1.95</v>
       </c>
-      <c r="AW29" s="0" t="n">
+      <c r="AW29" s="24" t="n">
         <v>4.33</v>
       </c>
-      <c r="AX29" s="0" t="n">
+      <c r="AX29" s="24" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY29" s="0" t="n">
+      <c r="AY29" s="24" t="n">
         <v>2.8</v>
       </c>
-      <c r="AZ29" s="0" t="n">
+      <c r="AZ29" s="24" t="n">
         <v>3.8</v>
       </c>
-      <c r="BA29" s="25" t="s">
+      <c r="BA29" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="BC29" s="25" t="n">
+      <c r="BC29" s="29" t="n">
         <f aca="false">AV29*1000</f>
         <v>1950</v>
       </c>
+      <c r="XDN29" s="24"/>
+      <c r="XDO29" s="24"/>
+      <c r="XDP29" s="24"/>
+      <c r="XDQ29" s="24"/>
+      <c r="XDR29" s="24"/>
+      <c r="XDS29" s="24"/>
+      <c r="XDT29" s="24"/>
+      <c r="XDU29" s="24"/>
+      <c r="XDV29" s="24"/>
+      <c r="XDW29" s="24"/>
+      <c r="XDX29" s="24"/>
+      <c r="XDY29" s="24"/>
+      <c r="XDZ29" s="24"/>
+      <c r="XEA29" s="24"/>
+      <c r="XEB29" s="24"/>
+      <c r="XEC29" s="24"/>
+      <c r="XED29" s="24"/>
+      <c r="XEE29" s="24"/>
+      <c r="XEF29" s="24"/>
+      <c r="XEG29" s="24"/>
+      <c r="XEH29" s="24"/>
+      <c r="XEI29" s="24"/>
+      <c r="XEJ29" s="24"/>
+      <c r="XEK29" s="24"/>
+      <c r="XEL29" s="24"/>
+      <c r="XEM29" s="24"/>
+      <c r="XEN29" s="24"/>
+      <c r="XEO29" s="24"/>
+      <c r="XEP29" s="24"/>
+      <c r="XEQ29" s="24"/>
+      <c r="XER29" s="24"/>
+      <c r="XES29" s="24"/>
+      <c r="XET29" s="24"/>
+      <c r="XEU29" s="24"/>
+      <c r="XEV29" s="24"/>
+      <c r="XEW29" s="24"/>
+      <c r="XEX29" s="24"/>
+      <c r="XEY29" s="24"/>
+      <c r="XEZ29" s="24"/>
+      <c r="XFA29" s="24"/>
+      <c r="XFB29" s="24"/>
+      <c r="XFC29" s="24"/>
+      <c r="XFD29" s="24"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B30" s="21" t="n">
         <v>133</v>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="22" t="n">
         <f aca="false">1000*B30/$P30</f>
         <v>617.708255926284</v>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="E30" s="21" t="n">
+      <c r="E30" s="22" t="n">
         <f aca="false">1000*D30/$P30</f>
         <v>139.332689306681</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F30" s="21" t="n">
         <v>1.9</v>
       </c>
-      <c r="G30" s="21" t="n">
+      <c r="G30" s="22" t="n">
         <f aca="false">1000*F30/$P30</f>
         <v>8.82440365608977</v>
       </c>
       <c r="H30" s="21" t="n">
         <v>121</v>
       </c>
-      <c r="I30" s="21" t="n">
+      <c r="I30" s="22" t="n">
         <f aca="false">1000*H30/$P30</f>
         <v>561.975180203611</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="24" t="n">
         <f aca="false">L30*$J$37/100</f>
         <v>105.4</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="25" t="n">
         <f aca="false">1000*J30/P30</f>
         <v>489.522181764138</v>
       </c>
-      <c r="L30" s="1" t="n">
+      <c r="L30" s="24" t="n">
         <v>620</v>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="M30" s="24" t="n">
         <f aca="false">O30*$M$37/100</f>
         <v>435.2</v>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="N30" s="25" t="n">
         <f aca="false">1000*M30/P30</f>
         <v>2021.25287954225</v>
       </c>
-      <c r="O30" s="1" t="n">
+      <c r="O30" s="24" t="n">
         <v>3200</v>
       </c>
-      <c r="P30" s="1" t="n">
+      <c r="P30" s="25" t="n">
         <v>215.312</v>
       </c>
-      <c r="Q30" s="1" t="n">
+      <c r="Q30" s="25" t="n">
         <f aca="false">100*P30/$P$36</f>
         <v>1.47883244546517</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="26" t="n">
         <f aca="false">H30+F30+B30+D30+J30+M30</f>
         <v>826.5</v>
       </c>
-      <c r="S30" s="3" t="n">
+      <c r="S30" s="27" t="n">
         <f aca="false">R30/P30</f>
         <v>3.83861559039905</v>
       </c>
-      <c r="U30" s="1" t="n">
+      <c r="T30" s="26"/>
+      <c r="U30" s="25" t="n">
         <f aca="false">-T30+($Q$45 + $Q$46)*1000*Q30/100</f>
-        <v>662.163494613929</v>
-      </c>
-      <c r="V30" s="1" t="n">
+        <v>655.627055204974</v>
+      </c>
+      <c r="V30" s="25" t="n">
         <f aca="false">U30/P30/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W30" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W30" s="25" t="n">
         <f aca="false">ROUND(U30/P30 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y30" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y30" s="25" t="n">
         <f aca="false">-Q30*($Q$47)*10</f>
         <v>-354.919786911641</v>
       </c>
-      <c r="Z30" s="1" t="n">
+      <c r="Z30" s="25" t="n">
         <f aca="false">Y30/P30/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC30" s="1" t="n">
+      <c r="AC30" s="24" t="n">
         <v>380.1</v>
       </c>
-      <c r="AH30" s="1" t="s">
+      <c r="AH30" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="AI30" s="1" t="n">
+      <c r="AI30" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" s="1" t="n">
+      <c r="AJ30" s="24" t="n">
         <v>62</v>
       </c>
-      <c r="AK30" s="1" t="n">
+      <c r="AK30" s="24" t="n">
         <f aca="false">AI30+AJ30/100</f>
         <v>0.62</v>
       </c>
-      <c r="AL30" s="1" t="n">
+      <c r="AL30" s="24" t="n">
         <f aca="false">AK30*1000</f>
         <v>620</v>
       </c>
-      <c r="AO30" s="24" t="s">
+      <c r="AO30" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="AP30" s="1" t="n">
+      <c r="AP30" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="AQ30" s="1" t="n">
+      <c r="AQ30" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="AR30" s="24" t="n">
+      <c r="AR30" s="29" t="n">
         <f aca="false">AP30+AQ30/10</f>
         <v>3.2</v>
       </c>
-      <c r="AS30" s="24" t="n">
+      <c r="AS30" s="29" t="n">
         <f aca="false">1000*AR30</f>
         <v>3200</v>
       </c>
-      <c r="AU30" s="25" t="s">
+      <c r="AU30" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="AV30" s="0" t="n">
+      <c r="AV30" s="24" t="n">
         <v>0.62</v>
       </c>
-      <c r="AW30" s="0" t="n">
+      <c r="AW30" s="24" t="n">
         <v>1.37</v>
       </c>
-      <c r="AX30" s="0" t="n">
+      <c r="AX30" s="24" t="n">
         <v>2.03</v>
       </c>
-      <c r="AY30" s="0" t="n">
+      <c r="AY30" s="24" t="n">
         <v>0.68</v>
       </c>
-      <c r="AZ30" s="0" t="n">
+      <c r="AZ30" s="24" t="n">
         <v>0.92</v>
       </c>
-      <c r="BA30" s="25" t="s">
+      <c r="BA30" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="BC30" s="25" t="n">
+      <c r="BC30" s="29" t="n">
         <f aca="false">AV30*1000</f>
         <v>620</v>
       </c>
+      <c r="XDN30" s="24"/>
+      <c r="XDO30" s="24"/>
+      <c r="XDP30" s="24"/>
+      <c r="XDQ30" s="24"/>
+      <c r="XDR30" s="24"/>
+      <c r="XDS30" s="24"/>
+      <c r="XDT30" s="24"/>
+      <c r="XDU30" s="24"/>
+      <c r="XDV30" s="24"/>
+      <c r="XDW30" s="24"/>
+      <c r="XDX30" s="24"/>
+      <c r="XDY30" s="24"/>
+      <c r="XDZ30" s="24"/>
+      <c r="XEA30" s="24"/>
+      <c r="XEB30" s="24"/>
+      <c r="XEC30" s="24"/>
+      <c r="XED30" s="24"/>
+      <c r="XEE30" s="24"/>
+      <c r="XEF30" s="24"/>
+      <c r="XEG30" s="24"/>
+      <c r="XEH30" s="24"/>
+      <c r="XEI30" s="24"/>
+      <c r="XEJ30" s="24"/>
+      <c r="XEK30" s="24"/>
+      <c r="XEL30" s="24"/>
+      <c r="XEM30" s="24"/>
+      <c r="XEN30" s="24"/>
+      <c r="XEO30" s="24"/>
+      <c r="XEP30" s="24"/>
+      <c r="XEQ30" s="24"/>
+      <c r="XER30" s="24"/>
+      <c r="XES30" s="24"/>
+      <c r="XET30" s="24"/>
+      <c r="XEU30" s="24"/>
+      <c r="XEV30" s="24"/>
+      <c r="XEW30" s="24"/>
+      <c r="XEX30" s="24"/>
+      <c r="XEY30" s="24"/>
+      <c r="XEZ30" s="24"/>
+      <c r="XFA30" s="24"/>
+      <c r="XFB30" s="24"/>
+      <c r="XFC30" s="24"/>
+      <c r="XFD30" s="24"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="s">
+    <row r="31" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="31" t="n">
         <v>76</v>
       </c>
-      <c r="C31" s="21" t="n">
+      <c r="C31" s="22" t="n">
         <f aca="false">1000*B31/$P31</f>
         <v>781.105469793829</v>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D31" s="32" t="n">
         <v>37</v>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="22" t="n">
         <f aca="false">1000*D31/$P31</f>
         <v>380.275031346996</v>
       </c>
-      <c r="F31" s="27" t="n">
+      <c r="F31" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="21" t="n">
+      <c r="G31" s="22" t="n">
         <f aca="false">1000*F31/$P31</f>
         <v>0</v>
       </c>
-      <c r="H31" s="27" t="n">
+      <c r="H31" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="I31" s="21" t="n">
+      <c r="I31" s="22" t="n">
         <f aca="false">1000*H31/$P31</f>
         <v>195.276367448457</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="24" t="n">
         <f aca="false">L31*$J$37/100</f>
-        <v>68</v>
-      </c>
-      <c r="K31" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K31" s="25" t="n">
         <f aca="false">1000*J31/P31</f>
-        <v>698.883841394479</v>
-      </c>
-      <c r="L31" s="1" t="n">
-        <v>400</v>
-      </c>
-      <c r="M31" s="1" t="n">
+        <v>87.3604801743099</v>
+      </c>
+      <c r="L31" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="M31" s="24" t="n">
         <f aca="false">O31*$M$37/100</f>
         <v>176.8</v>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="N31" s="25" t="n">
         <f aca="false">1000*M31/P31</f>
         <v>1817.09798762565</v>
       </c>
-      <c r="O31" s="1" t="n">
+      <c r="O31" s="24" t="n">
         <v>1300</v>
       </c>
-      <c r="P31" s="1" t="n">
+      <c r="P31" s="25" t="n">
         <v>97.298</v>
       </c>
-      <c r="Q31" s="1" t="n">
+      <c r="Q31" s="25" t="n">
         <f aca="false">100*P31/$P$36</f>
         <v>0.668274129072555</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="26" t="n">
         <f aca="false">H31+F31+B31+D31+J31+M31</f>
-        <v>376.8</v>
-      </c>
-      <c r="S31" s="3" t="n">
+        <v>317.3</v>
+      </c>
+      <c r="S31" s="27" t="n">
         <f aca="false">R31/P31</f>
-        <v>3.87263869760941</v>
-      </c>
-      <c r="U31" s="1" t="n">
+        <v>3.26111533638924</v>
+      </c>
+      <c r="T31" s="26"/>
+      <c r="U31" s="25" t="n">
         <f aca="false">-T31+($Q$45 + $Q$46)*1000*Q31/100</f>
-        <v>299.227092307656</v>
-      </c>
-      <c r="V31" s="1" t="n">
+        <v>296.273320657156</v>
+      </c>
+      <c r="V31" s="25" t="n">
         <f aca="false">U31/P31/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W31" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W31" s="25" t="n">
         <f aca="false">ROUND(U31/P31 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y31" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y31" s="25" t="n">
         <f aca="false">-Q31*($Q$47)*10</f>
         <v>-160.385790977413</v>
       </c>
-      <c r="Z31" s="1" t="n">
+      <c r="Z31" s="25" t="n">
         <f aca="false">Y31/P31/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AA31" s="34"/>
-      <c r="AC31" s="1" t="n">
+      <c r="AA31" s="36"/>
+      <c r="AC31" s="24" t="n">
         <v>136.8</v>
       </c>
-      <c r="AH31" s="1" t="s">
+      <c r="AH31" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="AI31" s="1" t="n">
+      <c r="AI31" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" s="1" t="n">
+      <c r="AJ31" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="AK31" s="1" t="n">
+      <c r="AK31" s="24" t="n">
         <f aca="false">AI31+AJ31/100</f>
         <v>0.4</v>
       </c>
-      <c r="AL31" s="1" t="n">
+      <c r="AL31" s="24" t="n">
         <f aca="false">AK31*1000</f>
         <v>400</v>
       </c>
-      <c r="AO31" s="24" t="s">
+      <c r="AO31" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="AP31" s="1" t="n">
+      <c r="AP31" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AQ31" s="1" t="n">
+      <c r="AQ31" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="AR31" s="24" t="n">
+      <c r="AR31" s="29" t="n">
         <f aca="false">AP31+AQ31/10</f>
         <v>1.3</v>
       </c>
-      <c r="AS31" s="24" t="n">
+      <c r="AS31" s="29" t="n">
         <f aca="false">1000*AR31</f>
         <v>1300</v>
       </c>
-      <c r="AU31" s="25" t="s">
+      <c r="AU31" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="AV31" s="0" t="n">
+      <c r="AV31" s="24" t="n">
         <v>0.05</v>
       </c>
-      <c r="AW31" s="0" t="n">
+      <c r="AW31" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="AX31" s="0" t="n">
+      <c r="AX31" s="24" t="n">
         <v>0.73</v>
       </c>
-      <c r="AY31" s="0" t="n">
+      <c r="AY31" s="24" t="n">
         <v>0.14</v>
       </c>
-      <c r="AZ31" s="0" t="n">
+      <c r="AZ31" s="24" t="n">
         <v>0.19</v>
       </c>
-      <c r="BA31" s="25" t="s">
+      <c r="BA31" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BC31" s="25" t="n">
+      <c r="BC31" s="29" t="n">
         <f aca="false">AV31*1000</f>
         <v>50</v>
       </c>
+      <c r="XDN31" s="24"/>
+      <c r="XDO31" s="24"/>
+      <c r="XDP31" s="24"/>
+      <c r="XDQ31" s="24"/>
+      <c r="XDR31" s="24"/>
+      <c r="XDS31" s="24"/>
+      <c r="XDT31" s="24"/>
+      <c r="XDU31" s="24"/>
+      <c r="XDV31" s="24"/>
+      <c r="XDW31" s="24"/>
+      <c r="XDX31" s="24"/>
+      <c r="XDY31" s="24"/>
+      <c r="XDZ31" s="24"/>
+      <c r="XEA31" s="24"/>
+      <c r="XEB31" s="24"/>
+      <c r="XEC31" s="24"/>
+      <c r="XED31" s="24"/>
+      <c r="XEE31" s="24"/>
+      <c r="XEF31" s="24"/>
+      <c r="XEG31" s="24"/>
+      <c r="XEH31" s="24"/>
+      <c r="XEI31" s="24"/>
+      <c r="XEJ31" s="24"/>
+      <c r="XEK31" s="24"/>
+      <c r="XEL31" s="24"/>
+      <c r="XEM31" s="24"/>
+      <c r="XEN31" s="24"/>
+      <c r="XEO31" s="24"/>
+      <c r="XEP31" s="24"/>
+      <c r="XEQ31" s="24"/>
+      <c r="XER31" s="24"/>
+      <c r="XES31" s="24"/>
+      <c r="XET31" s="24"/>
+      <c r="XEU31" s="24"/>
+      <c r="XEV31" s="24"/>
+      <c r="XEW31" s="24"/>
+      <c r="XEX31" s="24"/>
+      <c r="XEY31" s="24"/>
+      <c r="XEZ31" s="24"/>
+      <c r="XFA31" s="24"/>
+      <c r="XFB31" s="24"/>
+      <c r="XFC31" s="24"/>
+      <c r="XFD31" s="24"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
         <v>123</v>
       </c>
       <c r="B32" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="22" t="n">
         <f aca="false">1000*B32/$P32</f>
         <v>641.137728041033</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="22" t="n">
         <f aca="false">1000*D32/$P32</f>
         <v>271.997824017408</v>
       </c>
-      <c r="F32" s="23" t="n">
+      <c r="F32" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="G32" s="21" t="n">
+      <c r="G32" s="22" t="n">
         <f aca="false">1000*F32/$P32</f>
         <v>7.77136640049737</v>
       </c>
       <c r="H32" s="21" t="n">
         <v>75</v>
       </c>
-      <c r="I32" s="21" t="n">
+      <c r="I32" s="22" t="n">
         <f aca="false">1000*H32/$P32</f>
         <v>1457.13120009326</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="24" t="n">
         <f aca="false">L32*$J$37/100</f>
-        <v>51</v>
-      </c>
-      <c r="K32" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K32" s="25" t="n">
         <f aca="false">1000*J32/P32</f>
-        <v>990.849216063414</v>
-      </c>
-      <c r="L32" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="M32" s="1" t="n">
+        <v>99.0849216063414</v>
+      </c>
+      <c r="L32" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="M32" s="24" t="n">
         <f aca="false">O32*$M$37/100</f>
         <v>149.6</v>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="N32" s="25" t="n">
         <f aca="false">1000*M32/P32</f>
         <v>2906.49103378602</v>
       </c>
-      <c r="O32" s="1" t="n">
+      <c r="O32" s="24" t="n">
         <v>1100</v>
       </c>
-      <c r="P32" s="1" t="n">
+      <c r="P32" s="25" t="n">
         <v>51.471</v>
       </c>
-      <c r="Q32" s="1" t="n">
+      <c r="Q32" s="25" t="n">
         <f aca="false">100*P32/$P$36</f>
         <v>0.353519473139155</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="26" t="n">
         <f aca="false">H32+F32+B32+D32+J32+M32</f>
-        <v>323</v>
-      </c>
-      <c r="S32" s="3" t="n">
+        <v>277.1</v>
+      </c>
+      <c r="S32" s="27" t="n">
         <f aca="false">R32/P32</f>
-        <v>6.27537836840163</v>
-      </c>
-      <c r="U32" s="1" t="n">
+        <v>5.38361407394455</v>
+      </c>
+      <c r="T32" s="26"/>
+      <c r="U32" s="25" t="n">
         <f aca="false">-T32+($Q$45 + $Q$46)*1000*Q32/100</f>
-        <v>158.292232812261</v>
-      </c>
-      <c r="V32" s="1" t="n">
+        <v>156.729676740986</v>
+      </c>
+      <c r="V32" s="25" t="n">
         <f aca="false">U32/P32/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W32" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W32" s="25" t="n">
         <f aca="false">ROUND(U32/P32 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y32" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y32" s="25" t="n">
         <f aca="false">-Q32*($Q$47)*10</f>
         <v>-84.8446735533971</v>
       </c>
-      <c r="Z32" s="1" t="n">
+      <c r="Z32" s="25" t="n">
         <f aca="false">Y32/P32/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC32" s="1" t="n">
+      <c r="AC32" s="24" t="n">
         <v>70.5</v>
       </c>
-      <c r="AH32" s="1" t="s">
+      <c r="AH32" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="AI32" s="1" t="n">
+      <c r="AI32" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ32" s="1" t="n">
+      <c r="AJ32" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="AK32" s="1" t="n">
+      <c r="AK32" s="24" t="n">
         <f aca="false">AI32+AJ32/100</f>
         <v>0.3</v>
       </c>
-      <c r="AL32" s="1" t="n">
+      <c r="AL32" s="24" t="n">
         <f aca="false">AK32*1000</f>
         <v>300</v>
       </c>
-      <c r="AO32" s="24" t="s">
+      <c r="AO32" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="AP32" s="1" t="n">
+      <c r="AP32" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AQ32" s="1" t="n">
+      <c r="AQ32" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AR32" s="24" t="n">
+      <c r="AR32" s="29" t="n">
         <f aca="false">AP32+AQ32/10</f>
         <v>1.1</v>
       </c>
-      <c r="AS32" s="24" t="n">
+      <c r="AS32" s="29" t="n">
         <f aca="false">1000*AR32</f>
         <v>1100</v>
       </c>
-      <c r="AU32" s="25" t="s">
+      <c r="AU32" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="AV32" s="0" t="n">
+      <c r="AV32" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="AW32" s="0" t="n">
+      <c r="AW32" s="24" t="n">
         <v>0.06</v>
       </c>
-      <c r="AX32" s="0" t="n">
+      <c r="AX32" s="24" t="n">
         <v>0.38</v>
       </c>
-      <c r="AY32" s="0" t="n">
+      <c r="AY32" s="24" t="n">
         <v>0.16</v>
       </c>
-      <c r="AZ32" s="0" t="n">
+      <c r="AZ32" s="24" t="n">
         <v>0.22</v>
       </c>
-      <c r="BA32" s="25" t="s">
+      <c r="BA32" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="BC32" s="25" t="n">
+      <c r="BC32" s="29" t="n">
         <f aca="false">AV32*1000</f>
         <v>30</v>
       </c>
+      <c r="XDN32" s="24"/>
+      <c r="XDO32" s="24"/>
+      <c r="XDP32" s="24"/>
+      <c r="XDQ32" s="24"/>
+      <c r="XDR32" s="24"/>
+      <c r="XDS32" s="24"/>
+      <c r="XDT32" s="24"/>
+      <c r="XDU32" s="24"/>
+      <c r="XDV32" s="24"/>
+      <c r="XDW32" s="24"/>
+      <c r="XDX32" s="24"/>
+      <c r="XDY32" s="24"/>
+      <c r="XDZ32" s="24"/>
+      <c r="XEA32" s="24"/>
+      <c r="XEB32" s="24"/>
+      <c r="XEC32" s="24"/>
+      <c r="XED32" s="24"/>
+      <c r="XEE32" s="24"/>
+      <c r="XEF32" s="24"/>
+      <c r="XEG32" s="24"/>
+      <c r="XEH32" s="24"/>
+      <c r="XEI32" s="24"/>
+      <c r="XEJ32" s="24"/>
+      <c r="XEK32" s="24"/>
+      <c r="XEL32" s="24"/>
+      <c r="XEM32" s="24"/>
+      <c r="XEN32" s="24"/>
+      <c r="XEO32" s="24"/>
+      <c r="XEP32" s="24"/>
+      <c r="XEQ32" s="24"/>
+      <c r="XER32" s="24"/>
+      <c r="XES32" s="24"/>
+      <c r="XET32" s="24"/>
+      <c r="XEU32" s="24"/>
+      <c r="XEV32" s="24"/>
+      <c r="XEW32" s="24"/>
+      <c r="XEX32" s="24"/>
+      <c r="XEY32" s="24"/>
+      <c r="XEZ32" s="24"/>
+      <c r="XFA32" s="24"/>
+      <c r="XFB32" s="24"/>
+      <c r="XFC32" s="24"/>
+      <c r="XFD32" s="24"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="s">
+    <row r="33" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B33" s="31" t="n">
         <v>683</v>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="22" t="n">
         <f aca="false">1000*B33/$P33</f>
         <v>562.985554433614</v>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D33" s="32" t="n">
         <v>830</v>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="E33" s="22" t="n">
         <f aca="false">1000*D33/$P33</f>
         <v>684.155212562079</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="31" t="n">
         <v>240.6</v>
       </c>
-      <c r="G33" s="21" t="n">
+      <c r="G33" s="22" t="n">
         <f aca="false">1000*F33/$P33</f>
         <v>198.32258330414</v>
       </c>
-      <c r="H33" s="27" t="n">
+      <c r="H33" s="31" t="n">
         <v>2151</v>
       </c>
-      <c r="I33" s="21" t="n">
+      <c r="I33" s="22" t="n">
         <f aca="false">1000*H33/$P33</f>
         <v>1773.033568941</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="24" t="n">
         <f aca="false">L33*$J$37/100</f>
         <v>1586.1</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="25" t="n">
         <f aca="false">1000*J33/P33</f>
         <v>1307.39588270447</v>
       </c>
-      <c r="L33" s="1" t="n">
+      <c r="L33" s="24" t="n">
         <v>9330</v>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="M33" s="24" t="n">
         <f aca="false">O33*$M$37/100</f>
         <v>4202.4</v>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="N33" s="25" t="n">
         <f aca="false">1000*M33/P33</f>
         <v>3463.96851237455</v>
       </c>
-      <c r="O33" s="1" t="n">
+      <c r="O33" s="24" t="n">
         <v>30900</v>
       </c>
-      <c r="P33" s="1" t="n">
+      <c r="P33" s="25" t="n">
         <v>1213.175</v>
       </c>
-      <c r="Q33" s="1" t="n">
+      <c r="Q33" s="25" t="n">
         <f aca="false">100*P33/$P$36</f>
         <v>8.33247822707144</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="26" t="n">
         <f aca="false">H33+F33+B33+D33+J33+M33</f>
         <v>9693.1</v>
       </c>
-      <c r="S33" s="3" t="n">
+      <c r="S33" s="27" t="n">
         <f aca="false">R33/P33</f>
         <v>7.98986131431986</v>
       </c>
-      <c r="T33" s="3" t="n">
+      <c r="T33" s="26" t="n">
         <f aca="false">B33+F33</f>
         <v>923.6</v>
       </c>
-      <c r="U33" s="1" t="n">
+      <c r="U33" s="25" t="n">
         <f aca="false">-T33+($Q$45 + $Q$46)*1000*Q33/100</f>
-        <v>2807.35878343173</v>
-      </c>
-      <c r="V33" s="1" t="n">
+        <v>2770.52922966808</v>
+      </c>
+      <c r="V33" s="25" t="n">
         <f aca="false">U33/P33/10</f>
-        <v>0.231405921110453</v>
-      </c>
-      <c r="W33" s="1" t="n">
+        <v>0.228370122172653</v>
+      </c>
+      <c r="W33" s="25" t="n">
         <f aca="false">ROUND(U33/P33 *100/1000, 2)</f>
         <v>0.23</v>
       </c>
-      <c r="Y33" s="1" t="n">
+      <c r="Y33" s="25" t="n">
         <f aca="false">-Q33*($Q$47)*10</f>
         <v>-1999.79477449715</v>
       </c>
-      <c r="Z33" s="1" t="n">
+      <c r="Z33" s="25" t="n">
         <f aca="false">Y33/P33/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC33" s="1" t="n">
+      <c r="AC33" s="24" t="n">
         <v>1687.2</v>
       </c>
-      <c r="AH33" s="1" t="s">
+      <c r="AH33" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="AI33" s="1" t="n">
+      <c r="AI33" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="AJ33" s="1" t="n">
+      <c r="AJ33" s="24" t="n">
         <v>33</v>
       </c>
-      <c r="AK33" s="1" t="n">
+      <c r="AK33" s="24" t="n">
         <f aca="false">AI33+AJ33/100</f>
         <v>9.33</v>
       </c>
-      <c r="AL33" s="1" t="n">
+      <c r="AL33" s="24" t="n">
         <f aca="false">AK33*1000</f>
         <v>9330</v>
       </c>
-      <c r="AO33" s="24" t="s">
+      <c r="AO33" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AP33" s="1" t="n">
+      <c r="AP33" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="AQ33" s="1" t="n">
+      <c r="AQ33" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="AR33" s="24" t="n">
+      <c r="AR33" s="29" t="n">
         <f aca="false">AP33+AQ33/10</f>
         <v>30.9</v>
       </c>
-      <c r="AS33" s="24" t="n">
+      <c r="AS33" s="29" t="n">
         <f aca="false">1000*AR33</f>
         <v>30900</v>
       </c>
-      <c r="AU33" s="25" t="s">
+      <c r="AU33" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="AV33" s="0" t="n">
+      <c r="AV33" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="AW33" s="0" t="n">
+      <c r="AW33" s="24" t="n">
         <v>20.74</v>
       </c>
-      <c r="AX33" s="0" t="n">
+      <c r="AX33" s="24" t="n">
         <v>8.68</v>
       </c>
-      <c r="AY33" s="0" t="n">
+      <c r="AY33" s="24" t="n">
         <v>2.39</v>
       </c>
-      <c r="AZ33" s="0" t="n">
+      <c r="AZ33" s="24" t="n">
         <v>3.24</v>
       </c>
-      <c r="BA33" s="25" t="s">
+      <c r="BA33" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="BC33" s="25" t="n">
+      <c r="BC33" s="29" t="n">
         <f aca="false">AV33*1000</f>
         <v>9330</v>
       </c>
+      <c r="XDN33" s="24"/>
+      <c r="XDO33" s="24"/>
+      <c r="XDP33" s="24"/>
+      <c r="XDQ33" s="24"/>
+      <c r="XDR33" s="24"/>
+      <c r="XDS33" s="24"/>
+      <c r="XDT33" s="24"/>
+      <c r="XDU33" s="24"/>
+      <c r="XDV33" s="24"/>
+      <c r="XDW33" s="24"/>
+      <c r="XDX33" s="24"/>
+      <c r="XDY33" s="24"/>
+      <c r="XDZ33" s="24"/>
+      <c r="XEA33" s="24"/>
+      <c r="XEB33" s="24"/>
+      <c r="XEC33" s="24"/>
+      <c r="XED33" s="24"/>
+      <c r="XEE33" s="24"/>
+      <c r="XEF33" s="24"/>
+      <c r="XEG33" s="24"/>
+      <c r="XEH33" s="24"/>
+      <c r="XEI33" s="24"/>
+      <c r="XEJ33" s="24"/>
+      <c r="XEK33" s="24"/>
+      <c r="XEL33" s="24"/>
+      <c r="XEM33" s="24"/>
+      <c r="XEN33" s="24"/>
+      <c r="XEO33" s="24"/>
+      <c r="XEP33" s="24"/>
+      <c r="XEQ33" s="24"/>
+      <c r="XER33" s="24"/>
+      <c r="XES33" s="24"/>
+      <c r="XET33" s="24"/>
+      <c r="XEU33" s="24"/>
+      <c r="XEV33" s="24"/>
+      <c r="XEW33" s="24"/>
+      <c r="XEX33" s="24"/>
+      <c r="XEY33" s="24"/>
+      <c r="XEZ33" s="24"/>
+      <c r="XFA33" s="24"/>
+      <c r="XFB33" s="24"/>
+      <c r="XFC33" s="24"/>
+      <c r="XFD33" s="24"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" s="28" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
         <v>130</v>
       </c>
       <c r="B34" s="21" t="n">
         <v>189</v>
       </c>
-      <c r="C34" s="21" t="n">
+      <c r="C34" s="22" t="n">
         <f aca="false">1000*B34/$P34</f>
         <v>341.958899796996</v>
       </c>
-      <c r="D34" s="22" t="n">
+      <c r="D34" s="23" t="n">
         <v>601</v>
       </c>
-      <c r="E34" s="21" t="n">
+      <c r="E34" s="22" t="n">
         <f aca="false">1000*D34/$P34</f>
         <v>1087.39311522748</v>
       </c>
-      <c r="F34" s="23" t="n">
+      <c r="F34" s="21" t="n">
         <v>245.1</v>
       </c>
-      <c r="G34" s="21" t="n">
+      <c r="G34" s="22" t="n">
         <f aca="false">1000*F34/$P34</f>
         <v>443.460985927215</v>
       </c>
       <c r="H34" s="21" t="n">
         <v>712</v>
       </c>
-      <c r="I34" s="21" t="n">
+      <c r="I34" s="22" t="n">
         <f aca="false">1000*H34/$P34</f>
         <v>1288.22611987016</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="24" t="n">
         <f aca="false">L34*$J$37/100</f>
         <v>197.2</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="25" t="n">
         <f aca="false">1000*J34/P34</f>
         <v>356.79521185168</v>
       </c>
-      <c r="L34" s="1" t="n">
+      <c r="L34" s="24" t="n">
         <v>1160</v>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="M34" s="24" t="n">
         <f aca="false">O34*$M$37/100</f>
         <v>965.6</v>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="N34" s="25" t="n">
         <f aca="false">1000*M34/P34</f>
         <v>1747.0662097565</v>
       </c>
-      <c r="O34" s="1" t="n">
+      <c r="O34" s="24" t="n">
         <v>7100</v>
       </c>
-      <c r="P34" s="1" t="n">
+      <c r="P34" s="25" t="n">
         <v>552.698</v>
       </c>
-      <c r="Q34" s="1" t="n">
+      <c r="Q34" s="25" t="n">
         <f aca="false">100*P34/$P$36</f>
         <v>3.79610860028102</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="26" t="n">
         <f aca="false">H34+F34+B34+D34+J34+M34</f>
         <v>2909.9</v>
       </c>
-      <c r="S34" s="3" t="n">
+      <c r="S34" s="27" t="n">
         <f aca="false">R34/P34</f>
         <v>5.26490054243004</v>
       </c>
-      <c r="U34" s="1" t="n">
+      <c r="T34" s="26"/>
+      <c r="U34" s="25" t="n">
         <f aca="false">-T34+($Q$45 + $Q$46)*1000*Q34/100</f>
-        <v>1699.74938297043</v>
-      </c>
-      <c r="V34" s="1" t="n">
+        <v>1682.97058295719</v>
+      </c>
+      <c r="V34" s="25" t="n">
         <f aca="false">U34/P34/10</f>
-        <v>0.307536734884228</v>
-      </c>
-      <c r="W34" s="1" t="n">
+        <v>0.304500935946428</v>
+      </c>
+      <c r="W34" s="25" t="n">
         <f aca="false">ROUND(U34/P34 *100/1000, 2)</f>
-        <v>0.31</v>
-      </c>
-      <c r="Y34" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y34" s="25" t="n">
         <f aca="false">-Q34*($Q$47)*10</f>
         <v>-911.066064067446</v>
       </c>
-      <c r="Z34" s="1" t="n">
+      <c r="Z34" s="25" t="n">
         <f aca="false">Y34/P34/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC34" s="1" t="n">
+      <c r="AC34" s="24" t="n">
         <v>601.2</v>
       </c>
-      <c r="AH34" s="1" t="s">
+      <c r="AH34" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="AI34" s="1" t="n">
+      <c r="AI34" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AJ34" s="1" t="n">
+      <c r="AJ34" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="AK34" s="1" t="n">
+      <c r="AK34" s="24" t="n">
         <f aca="false">AI34+AJ34/100</f>
         <v>1.16</v>
       </c>
-      <c r="AL34" s="1" t="n">
+      <c r="AL34" s="24" t="n">
         <f aca="false">AK34*1000</f>
         <v>1160</v>
       </c>
-      <c r="AO34" s="24" t="s">
+      <c r="AO34" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="AP34" s="1" t="n">
+      <c r="AP34" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="AQ34" s="1" t="n">
+      <c r="AQ34" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AR34" s="24" t="n">
+      <c r="AR34" s="29" t="n">
         <f aca="false">AP34+AQ34/10</f>
         <v>7.1</v>
       </c>
-      <c r="AS34" s="24" t="n">
+      <c r="AS34" s="29" t="n">
         <f aca="false">1000*AR34</f>
         <v>7100</v>
       </c>
-      <c r="AU34" s="25" t="s">
+      <c r="AU34" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="AV34" s="0" t="n">
+      <c r="AV34" s="24" t="n">
         <v>1.16</v>
       </c>
-      <c r="AW34" s="0" t="n">
+      <c r="AW34" s="24" t="n">
         <v>2.58</v>
       </c>
-      <c r="AX34" s="0" t="n">
+      <c r="AX34" s="24" t="n">
         <v>3.23</v>
       </c>
-      <c r="AY34" s="0" t="n">
+      <c r="AY34" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="AZ34" s="0" t="n">
+      <c r="AZ34" s="24" t="n">
         <v>1.08</v>
       </c>
-      <c r="BA34" s="25" t="s">
+      <c r="BA34" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="BC34" s="25" t="n">
+      <c r="BC34" s="29" t="n">
         <f aca="false">AV34*1000</f>
         <v>1160</v>
       </c>
+      <c r="XDN34" s="24"/>
+      <c r="XDO34" s="24"/>
+      <c r="XDP34" s="24"/>
+      <c r="XDQ34" s="24"/>
+      <c r="XDR34" s="24"/>
+      <c r="XDS34" s="24"/>
+      <c r="XDT34" s="24"/>
+      <c r="XDU34" s="24"/>
+      <c r="XDV34" s="24"/>
+      <c r="XDW34" s="24"/>
+      <c r="XDX34" s="24"/>
+      <c r="XDY34" s="24"/>
+      <c r="XDZ34" s="24"/>
+      <c r="XEA34" s="24"/>
+      <c r="XEB34" s="24"/>
+      <c r="XEC34" s="24"/>
+      <c r="XED34" s="24"/>
+      <c r="XEE34" s="24"/>
+      <c r="XEF34" s="24"/>
+      <c r="XEG34" s="24"/>
+      <c r="XEH34" s="24"/>
+      <c r="XEI34" s="24"/>
+      <c r="XEJ34" s="24"/>
+      <c r="XEK34" s="24"/>
+      <c r="XEL34" s="24"/>
+      <c r="XEM34" s="24"/>
+      <c r="XEN34" s="24"/>
+      <c r="XEO34" s="24"/>
+      <c r="XEP34" s="24"/>
+      <c r="XEQ34" s="24"/>
+      <c r="XER34" s="24"/>
+      <c r="XES34" s="24"/>
+      <c r="XET34" s="24"/>
+      <c r="XEU34" s="24"/>
+      <c r="XEV34" s="24"/>
+      <c r="XEW34" s="24"/>
+      <c r="XEX34" s="24"/>
+      <c r="XEY34" s="24"/>
+      <c r="XEZ34" s="24"/>
+      <c r="XFA34" s="24"/>
+      <c r="XFB34" s="24"/>
+      <c r="XFC34" s="24"/>
+      <c r="XFD34" s="24"/>
     </row>
-    <row r="35" s="39" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="35" t="s">
+    <row r="35" s="42" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="36" t="n">
+      <c r="B35" s="38" t="n">
         <v>5847</v>
       </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="37" t="n">
+      <c r="C35" s="39"/>
+      <c r="D35" s="40" t="n">
         <v>9557</v>
       </c>
-      <c r="E35" s="36"/>
+      <c r="E35" s="39"/>
       <c r="F35" s="38" t="n">
         <v>8334.6</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="36" t="n">
+      <c r="G35" s="39"/>
+      <c r="H35" s="38" t="n">
         <v>26264</v>
       </c>
-      <c r="I35" s="36"/>
-      <c r="J35" s="1" t="n">
+      <c r="I35" s="39"/>
+      <c r="J35" s="24" t="n">
         <f aca="false">SUM(J8:J34)</f>
-        <v>8092</v>
-      </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1" t="n">
+        <v>7650</v>
+      </c>
+      <c r="K35" s="25"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24" t="n">
         <f aca="false">SUM(M8:M34)</f>
         <v>40677.6</v>
       </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="39" t="n">
+      <c r="N35" s="25"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="26" t="n">
         <f aca="false">H35+F35+B35+D35+L35+M35</f>
         <v>90680.2</v>
       </c>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="1" t="n">
+      <c r="S35" s="27"/>
+      <c r="T35" s="26"/>
+      <c r="U35" s="24" t="n">
         <f aca="false">SUM(U8:U34)</f>
-        <v>38340.8</v>
-      </c>
-      <c r="V35" s="1"/>
-      <c r="W35" s="39" t="e">
+        <v>37898.8</v>
+      </c>
+      <c r="V35" s="24"/>
+      <c r="W35" s="42" t="e">
         <f aca="false">ROUND(U35/P35 *100/1000, 2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y35" s="1" t="n">
+      <c r="Y35" s="25" t="n">
         <f aca="false">-Q35*($Q$47)*10</f>
         <v>-24000</v>
       </c>
-      <c r="Z35" s="1"/>
-      <c r="AC35" s="39" t="n">
+      <c r="Z35" s="25"/>
+      <c r="AC35" s="42" t="n">
         <v>18796</v>
       </c>
-      <c r="AL35" s="39" t="n">
+      <c r="AL35" s="42" t="n">
         <f aca="false">SUM(AL8:AL34)</f>
         <v>47600</v>
       </c>
-      <c r="AR35" s="39" t="n">
+      <c r="AR35" s="42" t="n">
         <f aca="false">SUM(AR8:AR34)</f>
         <v>299.1</v>
       </c>
-      <c r="XEX35" s="0"/>
-      <c r="XEY35" s="0"/>
-      <c r="XEZ35" s="0"/>
-      <c r="XFA35" s="0"/>
-      <c r="XFB35" s="0"/>
-      <c r="XFC35" s="0"/>
-      <c r="XFD35" s="0"/>
+      <c r="XEX35" s="24"/>
+      <c r="XEY35" s="24"/>
+      <c r="XEZ35" s="24"/>
+      <c r="XFA35" s="24"/>
+      <c r="XFB35" s="24"/>
+      <c r="XFC35" s="24"/>
+      <c r="XFD35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="n">
         <f aca="false">SUM(B8:B34)</f>
         <v>5847</v>
       </c>
+      <c r="C36" s="2"/>
       <c r="D36" s="1" t="n">
         <f aca="false">SUM(D8:D34)</f>
         <v>9561</v>
       </c>
+      <c r="E36" s="2"/>
       <c r="F36" s="1" t="n">
         <f aca="false">SUM(F8:F34)</f>
         <v>8334.5</v>
       </c>
+      <c r="G36" s="2"/>
       <c r="H36" s="1" t="n">
         <f aca="false">SUM(H8:H34)</f>
         <v>26264</v>
       </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
       <c r="L36" s="1" t="n">
         <f aca="false">SUM(L8:L34)</f>
-        <v>47600</v>
+        <v>45000</v>
       </c>
       <c r="M36" s="1" t="n">
         <f aca="false">SUM(M8:M34)</f>
@@ -7400,224 +8630,226 @@
         <f aca="false">SUM(O8:O34)</f>
         <v>299100</v>
       </c>
-      <c r="P36" s="1" t="n">
+      <c r="P36" s="2" t="n">
         <f aca="false">SUM(P8:P34)</f>
         <v>14559.594</v>
       </c>
+      <c r="Q36" s="43"/>
       <c r="R36" s="3" t="n">
         <f aca="false">SUM(R8:R34)</f>
-        <v>98776.1</v>
-      </c>
+        <v>98334.1</v>
+      </c>
+      <c r="S36" s="44"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="40" t="n">
+      <c r="J37" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="K37" s="41"/>
-      <c r="M37" s="40" t="n">
+      <c r="K37" s="46"/>
+      <c r="M37" s="45" t="n">
         <v>13.6</v>
       </c>
-      <c r="N37" s="41"/>
+      <c r="N37" s="46"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="43" t="n">
+      <c r="C38" s="48" t="n">
         <f aca="false">SUM(B35:M35)</f>
-        <v>98772.2</v>
-      </c>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
+        <v>98330.2</v>
+      </c>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
       <c r="J38" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="M38" s="24" t="s">
+      <c r="M38" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="N38" s="44"/>
+      <c r="N38" s="50"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="42"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="42"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="P40" s="45" t="s">
+      <c r="B40" s="47"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="P40" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="Q40" s="46" t="n">
+      <c r="Q40" s="52" t="n">
         <v>192.8</v>
       </c>
-      <c r="R40" s="47"/>
-      <c r="S40" s="47"/>
-      <c r="T40" s="47"/>
-      <c r="U40" s="24"/>
-      <c r="V40" s="24"/>
+      <c r="R40" s="53"/>
+      <c r="S40" s="53"/>
+      <c r="T40" s="53"/>
+      <c r="U40" s="49"/>
+      <c r="V40" s="49"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P41" s="45" t="s">
+      <c r="P41" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="Q41" s="45" t="n">
+      <c r="Q41" s="51" t="n">
         <f aca="false">Q40*0.7</f>
         <v>134.96</v>
       </c>
-      <c r="R41" s="47"/>
-      <c r="S41" s="47"/>
-      <c r="T41" s="47"/>
-      <c r="U41" s="24"/>
-      <c r="V41" s="24"/>
+      <c r="R41" s="53"/>
+      <c r="S41" s="53"/>
+      <c r="T41" s="53"/>
+      <c r="U41" s="49"/>
+      <c r="V41" s="49"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P42" s="45"/>
-      <c r="Q42" s="45"/>
-      <c r="R42" s="47"/>
-      <c r="S42" s="47"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="24"/>
-      <c r="V42" s="24"/>
+      <c r="P42" s="51"/>
+      <c r="Q42" s="51"/>
+      <c r="R42" s="53"/>
+      <c r="S42" s="53"/>
+      <c r="T42" s="53"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="49"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P43" s="48" t="s">
+      <c r="P43" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="Q43" s="49" t="n">
+      <c r="Q43" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="R43" s="47"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
+      <c r="R43" s="53"/>
+      <c r="S43" s="53"/>
+      <c r="T43" s="53"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="49"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P44" s="48" t="s">
+      <c r="P44" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="Q44" s="48" t="n">
+      <c r="Q44" s="54" t="n">
         <f aca="false">R36/1000 -Q43</f>
-        <v>68.7761</v>
-      </c>
-      <c r="R44" s="47"/>
-      <c r="S44" s="47"/>
-      <c r="T44" s="47"/>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
+        <v>68.3341</v>
+      </c>
+      <c r="R44" s="53"/>
+      <c r="S44" s="53"/>
+      <c r="T44" s="53"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="49"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P45" s="48" t="s">
+      <c r="P45" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="Q45" s="48" t="n">
+      <c r="Q45" s="54" t="n">
         <f aca="false">Q44-Q46-Q47</f>
-        <v>30.7761</v>
-      </c>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="24"/>
-      <c r="V45" s="24"/>
+        <v>30.3341</v>
+      </c>
+      <c r="R45" s="53"/>
+      <c r="S45" s="53"/>
+      <c r="T45" s="53"/>
+      <c r="U45" s="49"/>
+      <c r="V45" s="49"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P46" s="48" t="s">
+      <c r="P46" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="Q46" s="49" t="n">
+      <c r="Q46" s="55" t="n">
         <v>14</v>
       </c>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="24"/>
-      <c r="V46" s="24"/>
+      <c r="R46" s="53"/>
+      <c r="S46" s="53"/>
+      <c r="T46" s="53"/>
+      <c r="U46" s="49"/>
+      <c r="V46" s="49"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P47" s="48" t="s">
+      <c r="P47" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="Q47" s="49" t="n">
+      <c r="Q47" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="R47" s="47"/>
-      <c r="S47" s="47"/>
-      <c r="T47" s="47"/>
-      <c r="U47" s="24"/>
-      <c r="V47" s="24"/>
+      <c r="R47" s="53"/>
+      <c r="S47" s="53"/>
+      <c r="T47" s="53"/>
+      <c r="U47" s="49"/>
+      <c r="V47" s="49"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="P48" s="48" t="s">
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="P48" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="Q48" s="48" t="n">
+      <c r="Q48" s="54" t="n">
         <f aca="false">Q40+Q46</f>
         <v>206.8</v>
       </c>
-      <c r="R48" s="47"/>
-      <c r="S48" s="47"/>
-      <c r="T48" s="47"/>
-      <c r="U48" s="24"/>
-      <c r="V48" s="24"/>
+      <c r="R48" s="53"/>
+      <c r="S48" s="53"/>
+      <c r="T48" s="53"/>
+      <c r="U48" s="49"/>
+      <c r="V48" s="49"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="P49" s="48" t="s">
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="49"/>
+      <c r="P49" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="Q49" s="48" t="n">
+      <c r="Q49" s="54" t="n">
         <f aca="false">Q41-Q45</f>
-        <v>104.1839</v>
-      </c>
-      <c r="R49" s="47"/>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="24"/>
-      <c r="V49" s="24"/>
+        <v>104.6259</v>
+      </c>
+      <c r="R49" s="53"/>
+      <c r="S49" s="53"/>
+      <c r="T49" s="53"/>
+      <c r="U49" s="49"/>
+      <c r="V49" s="49"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="P50" s="48" t="s">
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="49"/>
+      <c r="I50" s="49"/>
+      <c r="P50" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="Q50" s="48" t="n">
+      <c r="Q50" s="54" t="n">
         <f aca="false">Q49/Q48</f>
-        <v>0.503790618955513</v>
-      </c>
-      <c r="R50" s="47"/>
-      <c r="S50" s="47"/>
-      <c r="T50" s="47"/>
-      <c r="U50" s="24"/>
-      <c r="V50" s="24"/>
+        <v>0.505927949709865</v>
+      </c>
+      <c r="R50" s="53"/>
+      <c r="S50" s="53"/>
+      <c r="T50" s="53"/>
+      <c r="U50" s="49"/>
+      <c r="V50" s="49"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="50"/>
+      <c r="A53" s="56"/>
       <c r="U53" s="1" t="s">
         <v>147</v>
       </c>
@@ -7627,7 +8859,7 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="50"/>
+      <c r="A55" s="56"/>
       <c r="J55" s="1" t="s">
         <v>5</v>
       </c>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="212">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Millions EUR</t>
   </si>
   <si>
-    <t xml:space="preserve">/GNI</t>
+    <t xml:space="preserve">/GNI %</t>
   </si>
   <si>
     <t xml:space="preserve">(%)</t>
@@ -665,9 +665,9 @@
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="0.00E+00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00E+00"/>
+    <numFmt numFmtId="168" formatCode="General"/>
     <numFmt numFmtId="169" formatCode="#,##0"/>
   </numFmts>
   <fonts count="10">
@@ -737,7 +737,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -747,13 +747,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF650953"/>
-        <bgColor rgb="FF800080"/>
+        <bgColor rgb="FF88133D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCF4069"/>
-        <bgColor rgb="FF993366"/>
+        <bgColor rgb="FFBB5928"/>
       </patternFill>
     </fill>
     <fill>
@@ -764,14 +764,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF88133D"/>
+        <bgColor rgb="FF7E0021"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5983B0"/>
         <bgColor rgb="FF339966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7BB2DD"/>
+        <bgColor rgb="FF83CAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
         <bgColor rgb="FFFFD320"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB5928"/>
+        <bgColor rgb="FFCF4069"/>
       </patternFill>
     </fill>
     <fill>
@@ -857,7 +875,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -898,7 +916,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -906,31 +924,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -946,7 +972,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -958,59 +984,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1022,23 +1048,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1073,7 +1099,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FFD17486"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF7BB2DD"/>
       <rgbColor rgb="FFCF4069"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFD9E1F2"/>
@@ -1086,7 +1112,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF88133D"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
@@ -1109,7 +1135,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFBB5928"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1A237E"/>
       <rgbColor rgb="FF333333"/>
@@ -1130,10 +1156,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.120697610039679"/>
-          <c:y val="0.0304335343095033"/>
-          <c:w val="0.693111562240472"/>
-          <c:h val="0.776629342520815"/>
+          <c:x val="0.120700394490968"/>
+          <c:y val="0.0304347826086957"/>
+          <c:w val="0.693104482432464"/>
+          <c:h val="0.776579163248564"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -1289,85 +1315,85 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>0.000350512532661395</c:v>
+                  <c:v>0.0350512532661395</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.000396480984693072</c:v>
+                  <c:v>0.0396480984693072</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.000726008291778911</c:v>
+                  <c:v>0.0726008291778911</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.000786755148115208</c:v>
+                  <c:v>0.0786755148115208</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.000727603456116417</c:v>
+                  <c:v>0.0727603456116417</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.000782166601486117</c:v>
+                  <c:v>0.0782166601486116</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.000310018773359053</c:v>
+                  <c:v>0.0310018773359053</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.000744360658921001</c:v>
+                  <c:v>0.0744360658921001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.000379785988637743</c:v>
+                  <c:v>0.0379785988637743</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.000421022541018626</c:v>
+                  <c:v>0.0421022541018626</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.000262233683997149</c:v>
+                  <c:v>0.0262233683997149</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.000503093193867792</c:v>
+                  <c:v>0.0503093193867792</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.000940076817705675</c:v>
+                  <c:v>0.0940076817705675</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.000299863052234907</c:v>
+                  <c:v>0.0299863052234907</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.000257444955291679</c:v>
+                  <c:v>0.0257444955291679</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.000816326530612245</c:v>
+                  <c:v>0.0816326530612245</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.000759034360189574</c:v>
+                  <c:v>0.0759034360189574</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.000198137507430157</c:v>
+                  <c:v>0.0198137507430157</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.000510538983298082</c:v>
+                  <c:v>0.0510538983298082</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.000397775325029027</c:v>
+                  <c:v>0.0397775325029027</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.000907081624570414</c:v>
+                  <c:v>0.0907081624570414</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.000646607669616519</c:v>
+                  <c:v>0.0646607669616519</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.000626997101880063</c:v>
+                  <c:v>0.0626997101880062</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.000781105469793829</c:v>
+                  <c:v>0.0781105469793829</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.000641137728041033</c:v>
+                  <c:v>0.0641137728041033</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.00056628268798813</c:v>
+                  <c:v>0.056628268798813</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.000343768206145128</c:v>
+                  <c:v>0.0343768206145128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1519,88 +1545,88 @@
             <c:numRef>
               <c:f>Combined_2!$E$8:$E$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>0.00080887507537245</c:v>
+                  <c:v>0.080887507537245</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.000362947767082216</c:v>
+                  <c:v>0.0362947767082216</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.000343898664526853</c:v>
+                  <c:v>0.0343898664526853</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.000444687692412944</c:v>
+                  <c:v>0.0444687692412944</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.000773078672123693</c:v>
+                  <c:v>0.0773078672123693</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.00115567312466769</c:v>
+                  <c:v>0.115567312466769</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.000740600403024405</c:v>
+                  <c:v>0.0740600403024405</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.000679633645101783</c:v>
+                  <c:v>0.0679633645101783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.000520737489575462</c:v>
+                  <c:v>0.0520737489575462</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.000656779628101934</c:v>
+                  <c:v>0.0656779628101934</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.000723958023305013</c:v>
+                  <c:v>0.0723958023305013</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.000298538818339129</c:v>
+                  <c:v>0.0298538818339129</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.000758776288576724</c:v>
+                  <c:v>0.0758776288576724</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.000494619467603971</c:v>
+                  <c:v>0.0494619467603971</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.000491185128832733</c:v>
+                  <c:v>0.0491185128832733</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.000604686318972033</c:v>
+                  <c:v>0.0604686318972033</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.000444312796208531</c:v>
+                  <c:v>0.0444312796208531</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.000634040023776501</c:v>
+                  <c:v>0.0634040023776501</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.000729341404711545</c:v>
+                  <c:v>0.0729341404711545</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.000778827363119896</c:v>
+                  <c:v>0.0778827363119896</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.000779323649278806</c:v>
+                  <c:v>0.0779323649278806</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.00039646017699115</c:v>
+                  <c:v>0.039646017699115</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.000139332689306681</c:v>
+                  <c:v>0.0139332689306681</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.000380275031346996</c:v>
+                  <c:v>0.0380275031346996</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.000271997824017408</c:v>
+                  <c:v>0.0271997824017408</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.000684155212562079</c:v>
+                  <c:v>0.0684155212562079</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.00108739311522748</c:v>
+                  <c:v>0.108739311522748</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1755,55 +1781,55 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>6.4710006029796E-005</c:v>
+                  <c:v>0.0064710006029796</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.000120522329177844</c:v>
+                  <c:v>0.0120522329177844</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.82109627252059E-006</c:v>
+                  <c:v>0.000382109627252059</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.13101183553397E-006</c:v>
+                  <c:v>0.000513101183553397</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.63801728058208E-005</c:v>
+                  <c:v>0.00363801728058208</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.66979386834115E-005</c:v>
+                  <c:v>0.00166979386834115</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.000326667929706114</c:v>
+                  <c:v>0.0326667929706114</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.23635069096087E-006</c:v>
+                  <c:v>0.000323635069096087</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.000318315472951015</c:v>
+                  <c:v>0.0318315472951015</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.00120403125199054</c:v>
+                  <c:v>0.120403125199054</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.000427725125472651</c:v>
+                  <c:v>0.0427725125472651</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.000125496873635152</c:v>
+                  <c:v>0.0125496873635152</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.9617523031882E-005</c:v>
+                  <c:v>0.0039617523031882</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.000746257121747491</c:v>
+                  <c:v>0.0746257121747491</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.000300168689842225</c:v>
+                  <c:v>0.0300168689842225</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.85130331753555E-006</c:v>
+                  <c:v>0.000185130331753555</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -1812,28 +1838,28 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0023424546918376</c:v>
+                  <c:v>0.23424546918376</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.000114982177762447</c:v>
+                  <c:v>0.0114982177762447</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.000117522123893805</c:v>
+                  <c:v>0.0117522123893805</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.82440365608977E-006</c:v>
+                  <c:v>0.000882440365608977</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.77136640049737E-006</c:v>
+                  <c:v>0.000777136640049737</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.00019832258330414</c:v>
+                  <c:v>0.019832258330414</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.000443460985927215</c:v>
+                  <c:v>0.0443460985927215</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1988,85 +2014,85 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>0.00225504566467471</c:v>
+                  <c:v>0.225504566467471</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00142417547735522</c:v>
+                  <c:v>0.142417547735522</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.000764219254504117</c:v>
+                  <c:v>0.0764219254504117</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.000615721420264076</c:v>
+                  <c:v>0.0615721420264076</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0020918599363347</c:v>
+                  <c:v>0.20918599363347</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.00152917964784926</c:v>
+                  <c:v>0.152917964784926</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.00153000005741088</c:v>
+                  <c:v>0.153000005741088</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.000938541700378653</c:v>
+                  <c:v>0.0938541700378653</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.000595128559514814</c:v>
+                  <c:v>0.0595128559514814</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.00259060917766996</c:v>
+                  <c:v>0.259060917766996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.00223729842461372</c:v>
+                  <c:v>0.223729842461371</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.000652362603037356</c:v>
+                  <c:v>0.0652362603037356</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.00139668555773415</c:v>
+                  <c:v>0.139668555773415</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.00102324402360571</c:v>
+                  <c:v>0.102324402360571</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.00144323531681716</c:v>
+                  <c:v>0.144323531681716</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.000604686318972033</c:v>
+                  <c:v>0.0604686318972033</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.000573904028436019</c:v>
+                  <c:v>0.0573904028436019</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.00412126015454726</c:v>
+                  <c:v>0.412126015454726</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.000656407264240391</c:v>
+                  <c:v>0.0656407264240391</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.00109059721246697</c:v>
+                  <c:v>0.109059721246697</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.00102206380233286</c:v>
+                  <c:v>0.102206380233286</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.00155752212389381</c:v>
+                  <c:v>0.155752212389381</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.000561975180203612</c:v>
+                  <c:v>0.0561975180203611</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.000195276367448457</c:v>
+                  <c:v>0.0195276367448457</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.00145713120009326</c:v>
+                  <c:v>0.145713120009326</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.001773033568941</c:v>
+                  <c:v>0.1773033568941</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.00128822611987016</c:v>
+                  <c:v>0.128822611987016</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2221,85 +2247,85 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>0.000454195610504591</c:v>
+                  <c:v>0.0454195610504591</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.000368865393719426</c:v>
+                  <c:v>0.0368865393719426</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.000876941594543475</c:v>
+                  <c:v>0.0876941594543474</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00110487788191831</c:v>
+                  <c:v>0.110487788191831</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00224192814915871</c:v>
+                  <c:v>0.224192814915871</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.000328685740399784</c:v>
+                  <c:v>0.0328685740399784</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.000551431540391427</c:v>
+                  <c:v>0.0551431540391427</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.000495161655717014</c:v>
+                  <c:v>0.0495161655717014</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.000479235103188245</c:v>
+                  <c:v>0.0479235103188245</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.000355228059055014</c:v>
+                  <c:v>0.0355228059055014</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.000275318554936884</c:v>
+                  <c:v>0.0275318554936884</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.00238720484738585</c:v>
+                  <c:v>0.238720484738585</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.000422363084526336</c:v>
+                  <c:v>0.0422363084526336</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.000494001193269466</c:v>
+                  <c:v>0.0494001193269466</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.000666324876790262</c:v>
+                  <c:v>0.0666324876790262</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.000925170068027211</c:v>
+                  <c:v>0.0925170068027211</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.00044061018957346</c:v>
+                  <c:v>0.044061018957346</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.000707350901525659</c:v>
+                  <c:v>0.0707350901525659</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.00334767704762599</c:v>
+                  <c:v>0.334767704762599</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.000402075598813124</c:v>
+                  <c:v>0.0402075598813125</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.000369220548592746</c:v>
+                  <c:v>0.0369220548592746</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.0015646017699115</c:v>
+                  <c:v>0.15646017699115</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.000489522181764138</c:v>
+                  <c:v>0.0489522181764138</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8.73604801743099E-005</c:v>
+                  <c:v>0.00873604801743099</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>9.90849216063414E-005</c:v>
+                  <c:v>0.00990849216063414</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.00130739588270447</c:v>
+                  <c:v>0.130739588270447</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.00035679521185168</c:v>
+                  <c:v>0.035679521185168</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2451,88 +2477,88 @@
             <c:numRef>
               <c:f>Combined_2!$N$8:$N$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>0.0033002103075196</c:v>
+                  <c:v>0.33002103075196</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00262900426069118</c:v>
+                  <c:v>0.262900426069118</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0041573527445024</c:v>
+                  <c:v>0.41573527445024</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00534993500718342</c:v>
+                  <c:v>0.534993500718342</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00927694406548431</c:v>
+                  <c:v>0.927694406548431</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.00274900801061637</c:v>
+                  <c:v>0.274900801061637</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.00163965484576566</c:v>
+                  <c:v>0.163965484576566</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.00220071846985339</c:v>
+                  <c:v>0.220071846985339</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.00154420199916212</c:v>
+                  <c:v>0.154420199916212</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.00327496500541426</c:v>
+                  <c:v>0.327496500541426</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.00210409014832559</c:v>
+                  <c:v>0.210409014832559</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.00473681591764751</c:v>
+                  <c:v>0.473681591764751</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.00228304370014235</c:v>
+                  <c:v>0.228304370014235</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.00159762088036082</c:v>
+                  <c:v>0.159762088036082</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.00423598937143739</c:v>
+                  <c:v>0.423598937143739</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.00205593348450491</c:v>
+                  <c:v>0.205593348450491</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.00201421800947867</c:v>
+                  <c:v>0.201421800947867</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.00485040618189023</c:v>
+                  <c:v>0.485040618189023</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.00892713879366932</c:v>
+                  <c:v>0.892713879366932</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.00178700266139166</c:v>
+                  <c:v>0.178700266139166</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.00198572395881813</c:v>
+                  <c:v>0.198572395881813</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.00410808259587021</c:v>
+                  <c:v>0.410808259587021</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.00202125287954225</c:v>
+                  <c:v>0.202125287954225</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.00181709798762565</c:v>
+                  <c:v>0.181709798762565</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.00290649103378602</c:v>
+                  <c:v>0.290649103378602</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.00346396851237455</c:v>
+                  <c:v>0.346396851237455</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.0017470662097565</c:v>
+                  <c:v>0.17470662097565</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2540,11 +2566,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="37397844"/>
-        <c:axId val="42217168"/>
+        <c:axId val="4257055"/>
+        <c:axId val="82875935"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="37397844"/>
+        <c:axId val="4257055"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2576,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42217168"/>
+        <c:crossAx val="82875935"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2584,7 +2610,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42217168"/>
+        <c:axId val="82875935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2625,7 +2651,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37397844"/>
+        <c:crossAx val="4257055"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2681,16 +2707,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1138680</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>344880</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>107640</xdr:rowOff>
+      <xdr:rowOff>4320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>519480</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>14760</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>352080</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>86400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2698,8 +2724,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2899080" y="8332200"/>
-        <a:ext cx="15604920" cy="8776800"/>
+        <a:off x="344880" y="8228880"/>
+        <a:ext cx="15604560" cy="8776440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2827,15 +2853,19 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="41.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="11.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="25.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="13.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="14.37"/>
@@ -2874,9 +2904,7 @@
       <c r="K1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>5</v>
-      </c>
+      <c r="L1" s="7"/>
       <c r="M1" s="8"/>
       <c r="N1" s="9" t="s">
         <v>6</v>
@@ -2950,9 +2978,9 @@
       <c r="Q2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10" t="s">
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14" t="s">
         <v>13</v>
       </c>
       <c r="U2" s="13" t="s">
@@ -3016,13 +3044,13 @@
       <c r="Q3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="R3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
       <c r="W3" s="13" t="s">
         <v>22</v>
       </c>
@@ -3040,76 +3068,76 @@
       <c r="XFC3" s="1"/>
       <c r="XFD3" s="1"/>
     </row>
-    <row r="4" s="18" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+    <row r="4" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16" t="s">
+      <c r="I4" s="17"/>
+      <c r="J4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16" t="s">
+      <c r="K4" s="18"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="16"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="AC4" s="16"/>
-      <c r="XDN4" s="16"/>
-      <c r="XDO4" s="16"/>
-      <c r="XDP4" s="16"/>
-      <c r="XDQ4" s="16"/>
-      <c r="XDR4" s="16"/>
-      <c r="XDS4" s="16"/>
-      <c r="XDT4" s="16"/>
-      <c r="XDU4" s="16"/>
-      <c r="XDV4" s="16"/>
-      <c r="XDW4" s="16"/>
-      <c r="XDX4" s="16"/>
-      <c r="XDY4" s="16"/>
-      <c r="XDZ4" s="16"/>
-      <c r="XEA4" s="16"/>
-      <c r="XEB4" s="16"/>
-      <c r="XEC4" s="16"/>
-      <c r="XED4" s="16"/>
-      <c r="XEE4" s="16"/>
-      <c r="XEF4" s="16"/>
-      <c r="XEG4" s="16"/>
-      <c r="XEH4" s="16"/>
-      <c r="XEI4" s="16"/>
-      <c r="XEJ4" s="16"/>
-      <c r="XEK4" s="16"/>
-      <c r="XEL4" s="16"/>
-      <c r="XEM4" s="16"/>
-      <c r="XEN4" s="16"/>
-      <c r="XEO4" s="16"/>
-      <c r="XEP4" s="16"/>
-      <c r="XEQ4" s="16"/>
-      <c r="XER4" s="16"/>
-      <c r="XES4" s="16"/>
-      <c r="XET4" s="16"/>
-      <c r="XEU4" s="16"/>
-      <c r="XEV4" s="16"/>
-      <c r="XEW4" s="16"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="17"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="AC4" s="17"/>
+      <c r="XDN4" s="17"/>
+      <c r="XDO4" s="17"/>
+      <c r="XDP4" s="17"/>
+      <c r="XDQ4" s="17"/>
+      <c r="XDR4" s="17"/>
+      <c r="XDS4" s="17"/>
+      <c r="XDT4" s="17"/>
+      <c r="XDU4" s="17"/>
+      <c r="XDV4" s="17"/>
+      <c r="XDW4" s="17"/>
+      <c r="XDX4" s="17"/>
+      <c r="XDY4" s="17"/>
+      <c r="XDZ4" s="17"/>
+      <c r="XEA4" s="17"/>
+      <c r="XEB4" s="17"/>
+      <c r="XEC4" s="17"/>
+      <c r="XED4" s="17"/>
+      <c r="XEE4" s="17"/>
+      <c r="XEF4" s="17"/>
+      <c r="XEG4" s="17"/>
+      <c r="XEH4" s="17"/>
+      <c r="XEI4" s="17"/>
+      <c r="XEJ4" s="17"/>
+      <c r="XEK4" s="17"/>
+      <c r="XEL4" s="17"/>
+      <c r="XEM4" s="17"/>
+      <c r="XEN4" s="17"/>
+      <c r="XEO4" s="17"/>
+      <c r="XEP4" s="17"/>
+      <c r="XEQ4" s="17"/>
+      <c r="XER4" s="17"/>
+      <c r="XES4" s="17"/>
+      <c r="XET4" s="17"/>
+      <c r="XEU4" s="17"/>
+      <c r="XEV4" s="17"/>
+      <c r="XEW4" s="17"/>
       <c r="XEX4" s="1"/>
       <c r="XEY4" s="1"/>
       <c r="XEZ4" s="1"/>
@@ -3118,76 +3146,76 @@
       <c r="XFC4" s="1"/>
       <c r="XFD4" s="1"/>
     </row>
-    <row r="5" s="18" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
+    <row r="5" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16" t="s">
+      <c r="H5" s="17"/>
+      <c r="I5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16" t="s">
+      <c r="J5" s="17"/>
+      <c r="K5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16" t="s">
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="16"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="AC5" s="16"/>
-      <c r="XDN5" s="16"/>
-      <c r="XDO5" s="16"/>
-      <c r="XDP5" s="16"/>
-      <c r="XDQ5" s="16"/>
-      <c r="XDR5" s="16"/>
-      <c r="XDS5" s="16"/>
-      <c r="XDT5" s="16"/>
-      <c r="XDU5" s="16"/>
-      <c r="XDV5" s="16"/>
-      <c r="XDW5" s="16"/>
-      <c r="XDX5" s="16"/>
-      <c r="XDY5" s="16"/>
-      <c r="XDZ5" s="16"/>
-      <c r="XEA5" s="16"/>
-      <c r="XEB5" s="16"/>
-      <c r="XEC5" s="16"/>
-      <c r="XED5" s="16"/>
-      <c r="XEE5" s="16"/>
-      <c r="XEF5" s="16"/>
-      <c r="XEG5" s="16"/>
-      <c r="XEH5" s="16"/>
-      <c r="XEI5" s="16"/>
-      <c r="XEJ5" s="16"/>
-      <c r="XEK5" s="16"/>
-      <c r="XEL5" s="16"/>
-      <c r="XEM5" s="16"/>
-      <c r="XEN5" s="16"/>
-      <c r="XEO5" s="16"/>
-      <c r="XEP5" s="16"/>
-      <c r="XEQ5" s="16"/>
-      <c r="XER5" s="16"/>
-      <c r="XES5" s="16"/>
-      <c r="XET5" s="16"/>
-      <c r="XEU5" s="16"/>
-      <c r="XEV5" s="16"/>
-      <c r="XEW5" s="16"/>
+      <c r="O5" s="17"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="AC5" s="17"/>
+      <c r="XDN5" s="17"/>
+      <c r="XDO5" s="17"/>
+      <c r="XDP5" s="17"/>
+      <c r="XDQ5" s="17"/>
+      <c r="XDR5" s="17"/>
+      <c r="XDS5" s="17"/>
+      <c r="XDT5" s="17"/>
+      <c r="XDU5" s="17"/>
+      <c r="XDV5" s="17"/>
+      <c r="XDW5" s="17"/>
+      <c r="XDX5" s="17"/>
+      <c r="XDY5" s="17"/>
+      <c r="XDZ5" s="17"/>
+      <c r="XEA5" s="17"/>
+      <c r="XEB5" s="17"/>
+      <c r="XEC5" s="17"/>
+      <c r="XED5" s="17"/>
+      <c r="XEE5" s="17"/>
+      <c r="XEF5" s="17"/>
+      <c r="XEG5" s="17"/>
+      <c r="XEH5" s="17"/>
+      <c r="XEI5" s="17"/>
+      <c r="XEJ5" s="17"/>
+      <c r="XEK5" s="17"/>
+      <c r="XEL5" s="17"/>
+      <c r="XEM5" s="17"/>
+      <c r="XEN5" s="17"/>
+      <c r="XEO5" s="17"/>
+      <c r="XEP5" s="17"/>
+      <c r="XEQ5" s="17"/>
+      <c r="XER5" s="17"/>
+      <c r="XES5" s="17"/>
+      <c r="XET5" s="17"/>
+      <c r="XEU5" s="17"/>
+      <c r="XEV5" s="17"/>
+      <c r="XEW5" s="17"/>
       <c r="XEX5" s="1"/>
       <c r="XEY5" s="1"/>
       <c r="XEZ5" s="1"/>
@@ -3196,70 +3224,70 @@
       <c r="XFC5" s="1"/>
       <c r="XFD5" s="1"/>
     </row>
-    <row r="6" s="18" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+    <row r="6" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="16"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="18" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="17"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="Y6" s="18" t="s">
+      <c r="Y6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AC6" s="16"/>
-      <c r="XDN6" s="16"/>
-      <c r="XDO6" s="16"/>
-      <c r="XDP6" s="16"/>
-      <c r="XDQ6" s="16"/>
-      <c r="XDR6" s="16"/>
-      <c r="XDS6" s="16"/>
-      <c r="XDT6" s="16"/>
-      <c r="XDU6" s="16"/>
-      <c r="XDV6" s="16"/>
-      <c r="XDW6" s="16"/>
-      <c r="XDX6" s="16"/>
-      <c r="XDY6" s="16"/>
-      <c r="XDZ6" s="16"/>
-      <c r="XEA6" s="16"/>
-      <c r="XEB6" s="16"/>
-      <c r="XEC6" s="16"/>
-      <c r="XED6" s="16"/>
-      <c r="XEE6" s="16"/>
-      <c r="XEF6" s="16"/>
-      <c r="XEG6" s="16"/>
-      <c r="XEH6" s="16"/>
-      <c r="XEI6" s="16"/>
-      <c r="XEJ6" s="16"/>
-      <c r="XEK6" s="16"/>
-      <c r="XEL6" s="16"/>
-      <c r="XEM6" s="16"/>
-      <c r="XEN6" s="16"/>
-      <c r="XEO6" s="16"/>
-      <c r="XEP6" s="16"/>
-      <c r="XEQ6" s="16"/>
-      <c r="XER6" s="16"/>
-      <c r="XES6" s="16"/>
-      <c r="XET6" s="16"/>
-      <c r="XEU6" s="16"/>
-      <c r="XEV6" s="16"/>
-      <c r="XEW6" s="16"/>
+      <c r="AC6" s="17"/>
+      <c r="XDN6" s="17"/>
+      <c r="XDO6" s="17"/>
+      <c r="XDP6" s="17"/>
+      <c r="XDQ6" s="17"/>
+      <c r="XDR6" s="17"/>
+      <c r="XDS6" s="17"/>
+      <c r="XDT6" s="17"/>
+      <c r="XDU6" s="17"/>
+      <c r="XDV6" s="17"/>
+      <c r="XDW6" s="17"/>
+      <c r="XDX6" s="17"/>
+      <c r="XDY6" s="17"/>
+      <c r="XDZ6" s="17"/>
+      <c r="XEA6" s="17"/>
+      <c r="XEB6" s="17"/>
+      <c r="XEC6" s="17"/>
+      <c r="XED6" s="17"/>
+      <c r="XEE6" s="17"/>
+      <c r="XEF6" s="17"/>
+      <c r="XEG6" s="17"/>
+      <c r="XEH6" s="17"/>
+      <c r="XEI6" s="17"/>
+      <c r="XEJ6" s="17"/>
+      <c r="XEK6" s="17"/>
+      <c r="XEL6" s="17"/>
+      <c r="XEM6" s="17"/>
+      <c r="XEN6" s="17"/>
+      <c r="XEO6" s="17"/>
+      <c r="XEP6" s="17"/>
+      <c r="XEQ6" s="17"/>
+      <c r="XER6" s="17"/>
+      <c r="XES6" s="17"/>
+      <c r="XET6" s="17"/>
+      <c r="XEU6" s="17"/>
+      <c r="XEV6" s="17"/>
+      <c r="XEW6" s="17"/>
       <c r="XEX6" s="1"/>
       <c r="XEY6" s="1"/>
       <c r="XEZ6" s="1"/>
@@ -3268,81 +3296,81 @@
       <c r="XFC6" s="1"/>
       <c r="XFD6" s="1"/>
     </row>
-    <row r="7" s="18" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
+    <row r="7" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="16"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="17"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
       <c r="U7" s="1"/>
-      <c r="V7" s="18" t="s">
+      <c r="V7" s="19" t="s">
         <v>32</v>
       </c>
       <c r="Y7" s="1"/>
-      <c r="Z7" s="18" t="s">
+      <c r="Z7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AC7" s="16"/>
-      <c r="AV7" s="18" t="s">
+      <c r="AC7" s="17"/>
+      <c r="AV7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AW7" s="18" t="s">
+      <c r="AW7" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AZ7" s="18" t="s">
+      <c r="AZ7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="XDN7" s="16"/>
-      <c r="XDO7" s="16"/>
-      <c r="XDP7" s="16"/>
-      <c r="XDQ7" s="16"/>
-      <c r="XDR7" s="16"/>
-      <c r="XDS7" s="16"/>
-      <c r="XDT7" s="16"/>
-      <c r="XDU7" s="16"/>
-      <c r="XDV7" s="16"/>
-      <c r="XDW7" s="16"/>
-      <c r="XDX7" s="16"/>
-      <c r="XDY7" s="16"/>
-      <c r="XDZ7" s="16"/>
-      <c r="XEA7" s="16"/>
-      <c r="XEB7" s="16"/>
-      <c r="XEC7" s="16"/>
-      <c r="XED7" s="16"/>
-      <c r="XEE7" s="16"/>
-      <c r="XEF7" s="16"/>
-      <c r="XEG7" s="16"/>
-      <c r="XEH7" s="16"/>
-      <c r="XEI7" s="16"/>
-      <c r="XEJ7" s="16"/>
-      <c r="XEK7" s="16"/>
-      <c r="XEL7" s="16"/>
-      <c r="XEM7" s="16"/>
-      <c r="XEN7" s="16"/>
-      <c r="XEO7" s="16"/>
-      <c r="XEP7" s="16"/>
-      <c r="XEQ7" s="16"/>
-      <c r="XER7" s="16"/>
-      <c r="XES7" s="16"/>
-      <c r="XET7" s="16"/>
-      <c r="XEU7" s="16"/>
-      <c r="XEV7" s="16"/>
-      <c r="XEW7" s="16"/>
+      <c r="XDN7" s="17"/>
+      <c r="XDO7" s="17"/>
+      <c r="XDP7" s="17"/>
+      <c r="XDQ7" s="17"/>
+      <c r="XDR7" s="17"/>
+      <c r="XDS7" s="17"/>
+      <c r="XDT7" s="17"/>
+      <c r="XDU7" s="17"/>
+      <c r="XDV7" s="17"/>
+      <c r="XDW7" s="17"/>
+      <c r="XDX7" s="17"/>
+      <c r="XDY7" s="17"/>
+      <c r="XDZ7" s="17"/>
+      <c r="XEA7" s="17"/>
+      <c r="XEB7" s="17"/>
+      <c r="XEC7" s="17"/>
+      <c r="XED7" s="17"/>
+      <c r="XEE7" s="17"/>
+      <c r="XEF7" s="17"/>
+      <c r="XEG7" s="17"/>
+      <c r="XEH7" s="17"/>
+      <c r="XEI7" s="17"/>
+      <c r="XEJ7" s="17"/>
+      <c r="XEK7" s="17"/>
+      <c r="XEL7" s="17"/>
+      <c r="XEM7" s="17"/>
+      <c r="XEN7" s="17"/>
+      <c r="XEO7" s="17"/>
+      <c r="XEP7" s="17"/>
+      <c r="XEQ7" s="17"/>
+      <c r="XER7" s="17"/>
+      <c r="XES7" s="17"/>
+      <c r="XET7" s="17"/>
+      <c r="XEU7" s="17"/>
+      <c r="XEV7" s="17"/>
+      <c r="XEW7" s="17"/>
       <c r="XEX7" s="1"/>
       <c r="XEY7" s="1"/>
       <c r="XEZ7" s="1"/>
@@ -3351,4864 +3379,4864 @@
       <c r="XFC7" s="1"/>
       <c r="XFD7" s="1"/>
     </row>
-    <row r="8" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="22" t="n">
         <v>143</v>
       </c>
-      <c r="C8" s="21" t="n">
-        <f aca="false">B8/$P8/1000</f>
-        <v>0.000350512532661395</v>
-      </c>
-      <c r="D8" s="20" t="n">
+      <c r="C8" s="23" t="n">
+        <f aca="false">B8/$P8/10</f>
+        <v>0.0350512532661395</v>
+      </c>
+      <c r="D8" s="22" t="n">
         <v>330</v>
       </c>
-      <c r="E8" s="22" t="n">
-        <f aca="false">D8/$P8/1000</f>
-        <v>0.00080887507537245</v>
-      </c>
-      <c r="F8" s="22" t="n">
+      <c r="E8" s="23" t="n">
+        <f aca="false">D8/$P8/10</f>
+        <v>0.080887507537245</v>
+      </c>
+      <c r="F8" s="24" t="n">
         <v>26.4</v>
       </c>
-      <c r="G8" s="21" t="n">
-        <f aca="false">F8/$P8/1000</f>
-        <v>6.4710006029796E-005</v>
-      </c>
-      <c r="H8" s="22" t="n">
+      <c r="G8" s="23" t="n">
+        <f aca="false">F8/$P8/10</f>
+        <v>0.0064710006029796</v>
+      </c>
+      <c r="H8" s="24" t="n">
         <v>920</v>
       </c>
-      <c r="I8" s="21" t="n">
-        <f aca="false">H8/$P8/1000</f>
-        <v>0.00225504566467471</v>
-      </c>
-      <c r="J8" s="20" t="n">
+      <c r="I8" s="23" t="n">
+        <f aca="false">H8/$P8/10</f>
+        <v>0.225504566467471</v>
+      </c>
+      <c r="J8" s="22" t="n">
         <f aca="false">L8*$J$37/100</f>
         <v>185.3</v>
       </c>
-      <c r="K8" s="21" t="n">
-        <f aca="false">J8/$P8/1000</f>
-        <v>0.000454195610504591</v>
-      </c>
-      <c r="L8" s="20" t="n">
+      <c r="K8" s="23" t="n">
+        <f aca="false">J8/$P8/10</f>
+        <v>0.0454195610504591</v>
+      </c>
+      <c r="L8" s="22" t="n">
         <v>1090</v>
       </c>
-      <c r="M8" s="20" t="n">
+      <c r="M8" s="22" t="n">
         <f aca="false">O8*$M$37/100</f>
         <v>1346.4</v>
       </c>
-      <c r="N8" s="22" t="n">
-        <f aca="false">M8/$P8/1000</f>
-        <v>0.0033002103075196</v>
-      </c>
-      <c r="O8" s="20" t="n">
+      <c r="N8" s="23" t="n">
+        <f aca="false">M8/$P8/10</f>
+        <v>0.33002103075196</v>
+      </c>
+      <c r="O8" s="22" t="n">
         <v>9900</v>
       </c>
-      <c r="P8" s="23" t="n">
+      <c r="P8" s="25" t="n">
         <v>407.974</v>
       </c>
-      <c r="Q8" s="23" t="n">
+      <c r="Q8" s="25" t="n">
         <f aca="false">100*P8/$P$36</f>
         <v>2.80209736617656</v>
       </c>
-      <c r="R8" s="20" t="n">
+      <c r="R8" s="22" t="n">
         <f aca="false">H8+F8+B8+D8+J8+M8</f>
         <v>2951.1</v>
       </c>
-      <c r="S8" s="23" t="n">
+      <c r="S8" s="25" t="n">
         <f aca="false">R8/P8</f>
         <v>7.23354919676254</v>
       </c>
-      <c r="T8" s="20" t="n">
+      <c r="T8" s="22" t="n">
         <f aca="false">124*(1.08)^4*3/5</f>
         <v>101.220378624</v>
       </c>
-      <c r="U8" s="23" t="n">
+      <c r="U8" s="25" t="n">
         <f aca="false">-T8+($Q$45 + $Q$46)*1000*Q8/100</f>
         <v>1143.64219937096</v>
       </c>
-      <c r="V8" s="23" t="n">
+      <c r="V8" s="25" t="n">
         <f aca="false">U8/P8/10</f>
         <v>0.280322324307667</v>
       </c>
-      <c r="W8" s="23" t="n">
+      <c r="W8" s="25" t="n">
         <f aca="false">U8/P8</f>
         <v>2.80322324307667</v>
       </c>
-      <c r="Y8" s="23" t="n">
+      <c r="Y8" s="25" t="n">
         <f aca="false">-Q8*($Q$47)*10</f>
         <v>-672.503367882374</v>
       </c>
-      <c r="Z8" s="23" t="n">
+      <c r="Z8" s="25" t="n">
         <f aca="false">Y8/P8/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC8" s="20" t="n">
+      <c r="AC8" s="22" t="n">
         <v>514.3</v>
       </c>
-      <c r="AH8" s="20" t="s">
+      <c r="AH8" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="AI8" s="20" t="n">
+      <c r="AI8" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AJ8" s="20" t="n">
+      <c r="AJ8" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="AK8" s="20" t="n">
+      <c r="AK8" s="22" t="n">
         <f aca="false">AI8+AJ8/100</f>
         <v>1.9</v>
       </c>
-      <c r="AL8" s="20" t="n">
+      <c r="AL8" s="22" t="n">
         <f aca="false">AK8*1000</f>
         <v>1900</v>
       </c>
-      <c r="AO8" s="24" t="s">
+      <c r="AO8" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="AP8" s="20" t="n">
+      <c r="AP8" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="AQ8" s="20" t="n">
+      <c r="AQ8" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="AR8" s="24" t="n">
+      <c r="AR8" s="26" t="n">
         <f aca="false">AP8+AQ8/10</f>
         <v>9.9</v>
       </c>
-      <c r="AS8" s="24" t="n">
+      <c r="AS8" s="26" t="n">
         <f aca="false">1000*AR8</f>
         <v>9900</v>
       </c>
-      <c r="AU8" s="24" t="s">
+      <c r="AU8" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="AV8" s="20" t="n">
+      <c r="AV8" s="22" t="n">
         <v>1.09</v>
       </c>
-      <c r="AW8" s="20" t="n">
+      <c r="AW8" s="22" t="n">
         <v>2.43</v>
       </c>
-      <c r="AX8" s="20" t="n">
+      <c r="AX8" s="22" t="n">
         <v>2.81</v>
       </c>
-      <c r="AY8" s="20" t="n">
+      <c r="AY8" s="22" t="n">
         <v>0.86</v>
       </c>
-      <c r="AZ8" s="20" t="n">
+      <c r="AZ8" s="22" t="n">
         <v>1.17</v>
       </c>
-      <c r="BA8" s="24" t="s">
+      <c r="BA8" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="BC8" s="24" t="n">
+      <c r="BC8" s="26" t="n">
         <f aca="false">AV8*1000</f>
         <v>1090</v>
       </c>
-      <c r="BE8" s="20" t="s">
+      <c r="BE8" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="BF8" s="20" t="n">
+      <c r="BF8" s="22" t="n">
         <v>148</v>
       </c>
-      <c r="BG8" s="20" t="n">
+      <c r="BG8" s="22" t="n">
         <v>105</v>
       </c>
-      <c r="BH8" s="20" t="s">
+      <c r="BH8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="BI8" s="20" t="n">
+      <c r="BI8" s="22" t="n">
         <v>143</v>
       </c>
-      <c r="BK8" s="20" t="s">
+      <c r="BK8" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="BL8" s="20" t="n">
+      <c r="BL8" s="22" t="n">
         <v>330</v>
       </c>
-      <c r="BM8" s="20" t="s">
+      <c r="BM8" s="22" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+    <row r="9" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="22" t="n">
         <v>201</v>
       </c>
-      <c r="C9" s="21" t="n">
-        <f aca="false">B9/$P9/1000</f>
-        <v>0.000396480984693072</v>
-      </c>
-      <c r="D9" s="20" t="n">
+      <c r="C9" s="23" t="n">
+        <f aca="false">B9/$P9/10</f>
+        <v>0.0396480984693072</v>
+      </c>
+      <c r="D9" s="22" t="n">
         <v>184</v>
       </c>
-      <c r="E9" s="22" t="n">
-        <f aca="false">D9/$P9/1000</f>
-        <v>0.000362947767082216</v>
-      </c>
-      <c r="F9" s="26" t="n">
+      <c r="E9" s="23" t="n">
+        <f aca="false">D9/$P9/10</f>
+        <v>0.0362947767082216</v>
+      </c>
+      <c r="F9" s="28" t="n">
         <v>61.1</v>
       </c>
-      <c r="G9" s="21" t="n">
-        <f aca="false">F9/$P9/1000</f>
-        <v>0.000120522329177844</v>
-      </c>
-      <c r="H9" s="26" t="n">
+      <c r="G9" s="23" t="n">
+        <f aca="false">F9/$P9/10</f>
+        <v>0.0120522329177844</v>
+      </c>
+      <c r="H9" s="28" t="n">
         <v>722</v>
       </c>
-      <c r="I9" s="21" t="n">
-        <f aca="false">H9/$P9/1000</f>
-        <v>0.00142417547735522</v>
-      </c>
-      <c r="J9" s="20" t="n">
+      <c r="I9" s="23" t="n">
+        <f aca="false">H9/$P9/10</f>
+        <v>0.142417547735522</v>
+      </c>
+      <c r="J9" s="22" t="n">
         <f aca="false">L9*$J$37/100</f>
         <v>187</v>
       </c>
-      <c r="K9" s="21" t="n">
-        <f aca="false">J9/$P9/1000</f>
-        <v>0.000368865393719426</v>
-      </c>
-      <c r="L9" s="20" t="n">
+      <c r="K9" s="23" t="n">
+        <f aca="false">J9/$P9/10</f>
+        <v>0.0368865393719426</v>
+      </c>
+      <c r="L9" s="22" t="n">
         <v>1100</v>
       </c>
-      <c r="M9" s="20" t="n">
+      <c r="M9" s="22" t="n">
         <f aca="false">O9*$M$37/100</f>
         <v>1332.8</v>
       </c>
-      <c r="N9" s="22" t="n">
-        <f aca="false">M9/$P9/1000</f>
-        <v>0.00262900426069118</v>
-      </c>
-      <c r="O9" s="20" t="n">
+      <c r="N9" s="23" t="n">
+        <f aca="false">M9/$P9/10</f>
+        <v>0.262900426069118</v>
+      </c>
+      <c r="O9" s="22" t="n">
         <v>9800</v>
       </c>
-      <c r="P9" s="23" t="n">
+      <c r="P9" s="25" t="n">
         <v>506.96</v>
       </c>
-      <c r="Q9" s="23" t="n">
+      <c r="Q9" s="25" t="n">
         <f aca="false">100*P9/$P$36</f>
         <v>3.48196522512922</v>
       </c>
-      <c r="R9" s="20" t="n">
+      <c r="R9" s="22" t="n">
         <f aca="false">H9+F9+B9+D9+J9+M9</f>
         <v>2687.9</v>
       </c>
-      <c r="S9" s="23" t="n">
+      <c r="S9" s="25" t="n">
         <f aca="false">R9/P9</f>
         <v>5.30199621271895</v>
       </c>
-      <c r="T9" s="27" t="n">
+      <c r="T9" s="29" t="n">
         <f aca="false">F9</f>
         <v>61.1</v>
       </c>
-      <c r="U9" s="23" t="n">
+      <c r="U9" s="25" t="n">
         <f aca="false">-T9+($Q$45 + $Q$46)*1000*Q9/100</f>
         <v>1485.80135288113</v>
       </c>
-      <c r="V9" s="23" t="n">
+      <c r="V9" s="25" t="n">
         <f aca="false">U9/P9/10</f>
         <v>0.293080588780403</v>
       </c>
-      <c r="W9" s="23" t="n">
+      <c r="W9" s="25" t="n">
         <f aca="false">U9/P9</f>
         <v>2.93080588780403</v>
       </c>
-      <c r="Y9" s="23" t="n">
+      <c r="Y9" s="25" t="n">
         <f aca="false">-Q9*($Q$47)*10</f>
         <v>-835.671654031012</v>
       </c>
-      <c r="Z9" s="23" t="n">
+      <c r="Z9" s="25" t="n">
         <f aca="false">Y9/P9/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC9" s="20" t="n">
+      <c r="AC9" s="22" t="n">
         <v>642</v>
       </c>
-      <c r="AH9" s="20" t="s">
+      <c r="AH9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="AI9" s="20" t="n">
+      <c r="AI9" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AJ9" s="20" t="n">
+      <c r="AJ9" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="AK9" s="20" t="n">
+      <c r="AK9" s="22" t="n">
         <f aca="false">AI9+AJ9/100</f>
         <v>1.1</v>
       </c>
-      <c r="AL9" s="20" t="n">
+      <c r="AL9" s="22" t="n">
         <f aca="false">AK9*1000</f>
         <v>1100</v>
       </c>
-      <c r="AO9" s="24" t="s">
+      <c r="AO9" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="AP9" s="20" t="n">
+      <c r="AP9" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="AQ9" s="20" t="n">
+      <c r="AQ9" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="AR9" s="24" t="n">
+      <c r="AR9" s="26" t="n">
         <f aca="false">AP9+AQ9/10</f>
         <v>9.8</v>
       </c>
-      <c r="AS9" s="24" t="n">
+      <c r="AS9" s="26" t="n">
         <f aca="false">1000*AR9</f>
         <v>9800</v>
       </c>
-      <c r="AU9" s="24" t="s">
+      <c r="AU9" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="AV9" s="20" t="n">
+      <c r="AV9" s="22" t="n">
         <v>1.1</v>
       </c>
-      <c r="AW9" s="20" t="n">
+      <c r="AW9" s="22" t="n">
         <v>2.45</v>
       </c>
-      <c r="AX9" s="20" t="n">
+      <c r="AX9" s="22" t="n">
         <v>3.46</v>
       </c>
-      <c r="AY9" s="20" t="n">
+      <c r="AY9" s="22" t="n">
         <v>0.71</v>
       </c>
-      <c r="AZ9" s="20" t="n">
+      <c r="AZ9" s="22" t="n">
         <v>0.96</v>
       </c>
-      <c r="BA9" s="24" t="s">
+      <c r="BA9" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="BC9" s="24" t="n">
+      <c r="BC9" s="26" t="n">
         <f aca="false">AV9*1000</f>
         <v>1100</v>
       </c>
-      <c r="BE9" s="20" t="s">
+      <c r="BE9" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="BF9" s="20" t="n">
+      <c r="BF9" s="22" t="n">
         <v>82</v>
       </c>
-      <c r="BG9" s="20" t="n">
+      <c r="BG9" s="22" t="n">
         <v>148</v>
       </c>
-      <c r="BH9" s="20" t="s">
+      <c r="BH9" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI9" s="20" t="n">
+      <c r="BI9" s="22" t="n">
         <v>201</v>
       </c>
-      <c r="BK9" s="20" t="s">
+      <c r="BK9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="BL9" s="20" t="n">
+      <c r="BL9" s="22" t="n">
         <v>184</v>
       </c>
-      <c r="BM9" s="20" t="s">
+      <c r="BM9" s="22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="C10" s="21" t="n">
-        <f aca="false">B10/$P10/1000</f>
-        <v>0.000726008291778911</v>
-      </c>
-      <c r="D10" s="20" t="n">
+      <c r="C10" s="23" t="n">
+        <f aca="false">B10/$P10/10</f>
+        <v>0.0726008291778911</v>
+      </c>
+      <c r="D10" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="E10" s="22" t="n">
-        <f aca="false">D10/$P10/1000</f>
-        <v>0.000343898664526853</v>
-      </c>
-      <c r="F10" s="22" t="n">
+      <c r="E10" s="23" t="n">
+        <f aca="false">D10/$P10/10</f>
+        <v>0.0343898664526853</v>
+      </c>
+      <c r="F10" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="21" t="n">
-        <f aca="false">F10/$P10/1000</f>
-        <v>3.82109627252059E-006</v>
-      </c>
-      <c r="H10" s="22" t="n">
+      <c r="G10" s="23" t="n">
+        <f aca="false">F10/$P10/10</f>
+        <v>0.000382109627252059</v>
+      </c>
+      <c r="H10" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="I10" s="21" t="n">
-        <f aca="false">H10/$P10/1000</f>
-        <v>0.000764219254504117</v>
-      </c>
-      <c r="J10" s="20" t="n">
+      <c r="I10" s="23" t="n">
+        <f aca="false">H10/$P10/10</f>
+        <v>0.0764219254504117</v>
+      </c>
+      <c r="J10" s="22" t="n">
         <f aca="false">L10*$J$37/100</f>
         <v>45.9</v>
       </c>
-      <c r="K10" s="21" t="n">
-        <f aca="false">J10/$P10/1000</f>
-        <v>0.000876941594543475</v>
-      </c>
-      <c r="L10" s="20" t="n">
+      <c r="K10" s="23" t="n">
+        <f aca="false">J10/$P10/10</f>
+        <v>0.0876941594543474</v>
+      </c>
+      <c r="L10" s="22" t="n">
         <v>270</v>
       </c>
-      <c r="M10" s="20" t="n">
+      <c r="M10" s="22" t="n">
         <f aca="false">O10*$M$37/100</f>
         <v>217.6</v>
       </c>
-      <c r="N10" s="22" t="n">
-        <f aca="false">M10/$P10/1000</f>
-        <v>0.0041573527445024</v>
-      </c>
-      <c r="O10" s="20" t="n">
+      <c r="N10" s="23" t="n">
+        <f aca="false">M10/$P10/10</f>
+        <v>0.41573527445024</v>
+      </c>
+      <c r="O10" s="22" t="n">
         <v>1600</v>
       </c>
-      <c r="P10" s="23" t="n">
+      <c r="P10" s="25" t="n">
         <v>52.341</v>
       </c>
-      <c r="Q10" s="23" t="n">
+      <c r="Q10" s="25" t="n">
         <f aca="false">100*P10/$P$36</f>
         <v>0.359494914487313</v>
       </c>
-      <c r="R10" s="20" t="n">
+      <c r="R10" s="22" t="n">
         <f aca="false">H10+F10+B10+D10+J10+M10</f>
         <v>359.7</v>
       </c>
-      <c r="S10" s="23" t="n">
+      <c r="S10" s="25" t="n">
         <f aca="false">R10/P10</f>
         <v>6.87224164612827</v>
       </c>
-      <c r="U10" s="23" t="n">
+      <c r="U10" s="25" t="n">
         <f aca="false">-T10+($Q$45 + $Q$46)*1000*Q10/100</f>
         <v>159.709570205048</v>
       </c>
-      <c r="V10" s="23" t="n">
+      <c r="V10" s="25" t="n">
         <f aca="false">U10/P10/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W10" s="23" t="n">
+      <c r="W10" s="25" t="n">
         <f aca="false">U10/P10</f>
         <v>3.05132821698187</v>
       </c>
-      <c r="Y10" s="23" t="n">
+      <c r="Y10" s="25" t="n">
         <f aca="false">-Q10*($Q$47)*10</f>
         <v>-86.2787794769552</v>
       </c>
-      <c r="Z10" s="23" t="n">
+      <c r="Z10" s="25" t="n">
         <f aca="false">Y10/P10/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC10" s="20" t="n">
+      <c r="AC10" s="22" t="n">
         <v>116</v>
       </c>
-      <c r="AH10" s="20" t="s">
+      <c r="AH10" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="AI10" s="20" t="n">
+      <c r="AI10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" s="20" t="n">
+      <c r="AJ10" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="AK10" s="20" t="n">
+      <c r="AK10" s="22" t="n">
         <f aca="false">AI10+AJ10/100</f>
         <v>0.27</v>
       </c>
-      <c r="AL10" s="20" t="n">
+      <c r="AL10" s="22" t="n">
         <f aca="false">AK10*1000</f>
         <v>270</v>
       </c>
-      <c r="AO10" s="24" t="s">
+      <c r="AO10" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="AP10" s="20" t="n">
+      <c r="AP10" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ10" s="20" t="n">
+      <c r="AQ10" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="AR10" s="24" t="n">
+      <c r="AR10" s="26" t="n">
         <f aca="false">AP10+AQ10/10</f>
         <v>1.6</v>
       </c>
-      <c r="AS10" s="24" t="n">
+      <c r="AS10" s="26" t="n">
         <f aca="false">1000*AR10</f>
         <v>1600</v>
       </c>
-      <c r="AU10" s="24" t="s">
+      <c r="AU10" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="AV10" s="20" t="n">
+      <c r="AV10" s="22" t="n">
         <v>0.27</v>
       </c>
-      <c r="AW10" s="20" t="n">
+      <c r="AW10" s="22" t="n">
         <v>0.6</v>
       </c>
-      <c r="AX10" s="20" t="n">
+      <c r="AX10" s="22" t="n">
         <v>0.55</v>
       </c>
-      <c r="AY10" s="20" t="n">
+      <c r="AY10" s="22" t="n">
         <v>1.09</v>
       </c>
-      <c r="AZ10" s="20" t="n">
+      <c r="AZ10" s="22" t="n">
         <v>1.48</v>
       </c>
-      <c r="BA10" s="24" t="s">
+      <c r="BA10" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="BC10" s="24" t="n">
+      <c r="BC10" s="26" t="n">
         <f aca="false">AV10*1000</f>
         <v>270</v>
       </c>
-      <c r="BE10" s="20" t="s">
+      <c r="BE10" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="BF10" s="20" t="n">
+      <c r="BF10" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="BG10" s="20" t="n">
+      <c r="BG10" s="22" t="n">
         <v>28</v>
       </c>
-      <c r="BH10" s="20" t="s">
+      <c r="BH10" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI10" s="20" t="n">
+      <c r="BI10" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="BK10" s="20" t="s">
+      <c r="BK10" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="BL10" s="20" t="n">
+      <c r="BL10" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="BM10" s="20" t="s">
+      <c r="BM10" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+    <row r="11" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="22" t="n">
         <v>46</v>
       </c>
-      <c r="C11" s="21" t="n">
-        <f aca="false">B11/$P11/1000</f>
-        <v>0.000786755148115208</v>
-      </c>
-      <c r="D11" s="20" t="n">
+      <c r="C11" s="23" t="n">
+        <f aca="false">B11/$P11/10</f>
+        <v>0.0786755148115208</v>
+      </c>
+      <c r="D11" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="E11" s="22" t="n">
-        <f aca="false">D11/$P11/1000</f>
-        <v>0.000444687692412944</v>
-      </c>
-      <c r="F11" s="26" t="n">
+      <c r="E11" s="23" t="n">
+        <f aca="false">D11/$P11/10</f>
+        <v>0.0444687692412944</v>
+      </c>
+      <c r="F11" s="28" t="n">
         <v>0.3</v>
       </c>
-      <c r="G11" s="21" t="n">
-        <f aca="false">F11/$P11/1000</f>
-        <v>5.13101183553397E-006</v>
-      </c>
-      <c r="H11" s="26" t="n">
+      <c r="G11" s="23" t="n">
+        <f aca="false">F11/$P11/10</f>
+        <v>0.000513101183553397</v>
+      </c>
+      <c r="H11" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="21" t="n">
-        <f aca="false">H11/$P11/1000</f>
-        <v>0.000615721420264076</v>
-      </c>
-      <c r="J11" s="20" t="n">
+      <c r="I11" s="23" t="n">
+        <f aca="false">H11/$P11/10</f>
+        <v>0.0615721420264076</v>
+      </c>
+      <c r="J11" s="22" t="n">
         <f aca="false">L11*$J$37/100</f>
         <v>64.6</v>
       </c>
-      <c r="K11" s="21" t="n">
-        <f aca="false">J11/$P11/1000</f>
-        <v>0.00110487788191831</v>
-      </c>
-      <c r="L11" s="20" t="n">
+      <c r="K11" s="23" t="n">
+        <f aca="false">J11/$P11/10</f>
+        <v>0.110487788191831</v>
+      </c>
+      <c r="L11" s="22" t="n">
         <v>380</v>
       </c>
-      <c r="M11" s="20" t="n">
+      <c r="M11" s="22" t="n">
         <f aca="false">O11*$M$37/100</f>
         <v>312.8</v>
       </c>
-      <c r="N11" s="22" t="n">
-        <f aca="false">M11/$P11/1000</f>
-        <v>0.00534993500718342</v>
-      </c>
-      <c r="O11" s="20" t="n">
+      <c r="N11" s="23" t="n">
+        <f aca="false">M11/$P11/10</f>
+        <v>0.534993500718342</v>
+      </c>
+      <c r="O11" s="22" t="n">
         <v>2300</v>
       </c>
-      <c r="P11" s="23" t="n">
+      <c r="P11" s="25" t="n">
         <v>58.468</v>
       </c>
-      <c r="Q11" s="23" t="n">
+      <c r="Q11" s="25" t="n">
         <f aca="false">100*P11/$P$36</f>
         <v>0.401577131889804</v>
       </c>
-      <c r="R11" s="20" t="n">
+      <c r="R11" s="22" t="n">
         <f aca="false">H11+F11+B11+D11+J11+M11</f>
         <v>485.7</v>
       </c>
-      <c r="S11" s="23" t="n">
+      <c r="S11" s="25" t="n">
         <f aca="false">R11/P11</f>
         <v>8.30710816172949</v>
       </c>
-      <c r="U11" s="23" t="n">
+      <c r="U11" s="25" t="n">
         <f aca="false">-T11+($Q$45 + $Q$46)*1000*Q11/100</f>
         <v>178.405058190496</v>
       </c>
-      <c r="V11" s="23" t="n">
+      <c r="V11" s="25" t="n">
         <f aca="false">U11/P11/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W11" s="23" t="n">
+      <c r="W11" s="25" t="n">
         <f aca="false">ROUND(U11/P11 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y11" s="23" t="n">
+      <c r="Y11" s="25" t="n">
         <f aca="false">-Q11*($Q$47)*10</f>
         <v>-96.378511653553</v>
       </c>
-      <c r="Z11" s="23" t="n">
+      <c r="Z11" s="25" t="n">
         <f aca="false">Y11/P11/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC11" s="20" t="n">
+      <c r="AC11" s="22" t="n">
         <v>93</v>
       </c>
-      <c r="AH11" s="20" t="s">
+      <c r="AH11" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="AI11" s="20" t="n">
+      <c r="AI11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" s="20" t="n">
+      <c r="AJ11" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="AK11" s="20" t="n">
+      <c r="AK11" s="22" t="n">
         <f aca="false">AI11+AJ11/100</f>
         <v>0.38</v>
       </c>
-      <c r="AL11" s="20" t="n">
+      <c r="AL11" s="22" t="n">
         <f aca="false">AK11*1000</f>
         <v>380</v>
       </c>
-      <c r="AO11" s="24" t="s">
+      <c r="AO11" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="AP11" s="20" t="n">
+      <c r="AP11" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="AQ11" s="20" t="n">
+      <c r="AQ11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="AR11" s="24" t="n">
+      <c r="AR11" s="26" t="n">
         <f aca="false">AP11+AQ11/10</f>
         <v>2.3</v>
       </c>
-      <c r="AS11" s="24" t="n">
+      <c r="AS11" s="26" t="n">
         <f aca="false">1000*AR11</f>
         <v>2300</v>
       </c>
-      <c r="AU11" s="24" t="s">
+      <c r="AU11" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="AV11" s="20" t="n">
+      <c r="AV11" s="22" t="n">
         <v>0.38</v>
       </c>
-      <c r="AW11" s="20" t="n">
+      <c r="AW11" s="22" t="n">
         <v>0.84</v>
       </c>
-      <c r="AX11" s="20" t="n">
+      <c r="AX11" s="22" t="n">
         <v>0.48</v>
       </c>
-      <c r="AY11" s="20" t="n">
+      <c r="AY11" s="22" t="n">
         <v>1.76</v>
       </c>
-      <c r="AZ11" s="20" t="n">
+      <c r="AZ11" s="22" t="n">
         <v>2.39</v>
       </c>
-      <c r="BA11" s="24" t="s">
+      <c r="BA11" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="BC11" s="24" t="n">
+      <c r="BC11" s="26" t="n">
         <f aca="false">AV11*1000</f>
         <v>380</v>
       </c>
-      <c r="BE11" s="20" t="s">
+      <c r="BE11" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="BF11" s="20" t="n">
+      <c r="BF11" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="BG11" s="20" t="n">
+      <c r="BG11" s="22" t="n">
         <v>34</v>
       </c>
-      <c r="BH11" s="20" t="s">
+      <c r="BH11" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI11" s="20" t="n">
+      <c r="BI11" s="22" t="n">
         <v>46</v>
       </c>
-      <c r="BK11" s="20" t="s">
+      <c r="BK11" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="BL11" s="20" t="n">
+      <c r="BL11" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="BM11" s="20" t="s">
+      <c r="BM11" s="22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="C12" s="21" t="n">
-        <f aca="false">B12/$P12/1000</f>
-        <v>0.000727603456116417</v>
-      </c>
-      <c r="D12" s="20" t="n">
+      <c r="C12" s="23" t="n">
+        <f aca="false">B12/$P12/10</f>
+        <v>0.0727603456116417</v>
+      </c>
+      <c r="D12" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="E12" s="22" t="n">
-        <f aca="false">D12/$P12/1000</f>
-        <v>0.000773078672123693</v>
-      </c>
-      <c r="F12" s="22" t="n">
+      <c r="E12" s="23" t="n">
+        <f aca="false">D12/$P12/10</f>
+        <v>0.0773078672123693</v>
+      </c>
+      <c r="F12" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="G12" s="21" t="n">
-        <f aca="false">F12/$P12/1000</f>
-        <v>3.63801728058208E-005</v>
-      </c>
-      <c r="H12" s="22" t="n">
+      <c r="G12" s="23" t="n">
+        <f aca="false">F12/$P12/10</f>
+        <v>0.00363801728058208</v>
+      </c>
+      <c r="H12" s="24" t="n">
         <v>46</v>
       </c>
-      <c r="I12" s="21" t="n">
-        <f aca="false">H12/$P12/1000</f>
-        <v>0.0020918599363347</v>
-      </c>
-      <c r="J12" s="20" t="n">
+      <c r="I12" s="23" t="n">
+        <f aca="false">H12/$P12/10</f>
+        <v>0.20918599363347</v>
+      </c>
+      <c r="J12" s="22" t="n">
         <f aca="false">L12*$J$37/100</f>
         <v>49.3</v>
       </c>
-      <c r="K12" s="21" t="n">
-        <f aca="false">J12/$P12/1000</f>
-        <v>0.00224192814915871</v>
-      </c>
-      <c r="L12" s="20" t="n">
+      <c r="K12" s="23" t="n">
+        <f aca="false">J12/$P12/10</f>
+        <v>0.224192814915871</v>
+      </c>
+      <c r="L12" s="22" t="n">
         <v>290</v>
       </c>
-      <c r="M12" s="20" t="n">
+      <c r="M12" s="22" t="n">
         <f aca="false">O12*$M$37/100</f>
         <v>204</v>
       </c>
-      <c r="N12" s="22" t="n">
-        <f aca="false">M12/$P12/1000</f>
-        <v>0.00927694406548431</v>
-      </c>
-      <c r="O12" s="20" t="n">
+      <c r="N12" s="23" t="n">
+        <f aca="false">M12/$P12/10</f>
+        <v>0.927694406548431</v>
+      </c>
+      <c r="O12" s="22" t="n">
         <v>1500</v>
       </c>
-      <c r="P12" s="23" t="n">
+      <c r="P12" s="25" t="n">
         <v>21.99</v>
       </c>
-      <c r="Q12" s="23" t="n">
+      <c r="Q12" s="25" t="n">
         <f aca="false">100*P12/$P$36</f>
         <v>0.151034431317247</v>
       </c>
-      <c r="R12" s="20" t="n">
+      <c r="R12" s="22" t="n">
         <f aca="false">H12+F12+B12+D12+J12+M12</f>
         <v>333.1</v>
       </c>
-      <c r="S12" s="23" t="n">
+      <c r="S12" s="25" t="n">
         <f aca="false">R12/P12</f>
         <v>15.1477944520237</v>
       </c>
-      <c r="U12" s="23" t="n">
+      <c r="U12" s="25" t="n">
         <f aca="false">-T12+($Q$45 + $Q$46)*1000*Q12/100</f>
         <v>67.0987074914314</v>
       </c>
-      <c r="V12" s="23" t="n">
+      <c r="V12" s="25" t="n">
         <f aca="false">U12/P12/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W12" s="23" t="n">
+      <c r="W12" s="25" t="n">
         <f aca="false">ROUND(U12/P12 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y12" s="23" t="n">
+      <c r="Y12" s="25" t="n">
         <f aca="false">-Q12*($Q$47)*10</f>
         <v>-36.2482635161393</v>
       </c>
-      <c r="Z12" s="23" t="n">
+      <c r="Z12" s="25" t="n">
         <f aca="false">Y12/P12/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC12" s="20" t="n">
+      <c r="AC12" s="22" t="n">
         <v>36.5</v>
       </c>
-      <c r="AH12" s="20" t="s">
+      <c r="AH12" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="AI12" s="20" t="n">
+      <c r="AI12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ12" s="20" t="n">
+      <c r="AJ12" s="22" t="n">
         <v>29</v>
       </c>
-      <c r="AK12" s="20" t="n">
+      <c r="AK12" s="22" t="n">
         <f aca="false">AI12+AJ12/100</f>
         <v>0.29</v>
       </c>
-      <c r="AL12" s="20" t="n">
+      <c r="AL12" s="22" t="n">
         <f aca="false">AK12*1000</f>
         <v>290</v>
       </c>
-      <c r="AO12" s="24" t="s">
+      <c r="AO12" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="AP12" s="20" t="n">
+      <c r="AP12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ12" s="20" t="n">
+      <c r="AQ12" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="AR12" s="24" t="n">
+      <c r="AR12" s="26" t="n">
         <f aca="false">AP12+AQ12/10</f>
         <v>1.5</v>
       </c>
-      <c r="AS12" s="24" t="n">
+      <c r="AS12" s="26" t="n">
         <f aca="false">1000*AR12</f>
         <v>1500</v>
       </c>
-      <c r="AU12" s="24" t="s">
+      <c r="AU12" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="AV12" s="20" t="n">
+      <c r="AV12" s="22" t="n">
         <v>0.29</v>
       </c>
-      <c r="AW12" s="20" t="n">
+      <c r="AW12" s="22" t="n">
         <v>0.64</v>
       </c>
-      <c r="AX12" s="20" t="n">
+      <c r="AX12" s="22" t="n">
         <v>0.16</v>
       </c>
-      <c r="AY12" s="20" t="n">
+      <c r="AY12" s="22" t="n">
         <v>3.9</v>
       </c>
-      <c r="AZ12" s="20" t="n">
+      <c r="AZ12" s="22" t="n">
         <v>5.29</v>
       </c>
-      <c r="BA12" s="24" t="s">
+      <c r="BA12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="BC12" s="24" t="n">
+      <c r="BC12" s="26" t="n">
         <f aca="false">AV12*1000</f>
         <v>290</v>
       </c>
-      <c r="BE12" s="20" t="s">
+      <c r="BE12" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="BF12" s="20" t="s">
+      <c r="BF12" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="BG12" s="20" t="n">
+      <c r="BG12" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="BH12" s="20" t="s">
+      <c r="BH12" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI12" s="20" t="n">
+      <c r="BI12" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="BK12" s="20" t="s">
+      <c r="BK12" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="BL12" s="20" t="n">
+      <c r="BL12" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="BM12" s="20" t="s">
+      <c r="BM12" s="22" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="s">
+    <row r="13" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="22" t="n">
         <v>178</v>
       </c>
-      <c r="C13" s="21" t="n">
-        <f aca="false">B13/$P13/1000</f>
-        <v>0.000782166601486117</v>
-      </c>
-      <c r="D13" s="20" t="n">
+      <c r="C13" s="23" t="n">
+        <f aca="false">B13/$P13/10</f>
+        <v>0.0782166601486116</v>
+      </c>
+      <c r="D13" s="22" t="n">
         <v>263</v>
       </c>
-      <c r="E13" s="22" t="n">
-        <f aca="false">D13/$P13/1000</f>
-        <v>0.00115567312466769</v>
-      </c>
-      <c r="F13" s="26" t="n">
+      <c r="E13" s="23" t="n">
+        <f aca="false">D13/$P13/10</f>
+        <v>0.115567312466769</v>
+      </c>
+      <c r="F13" s="28" t="n">
         <v>3.8</v>
       </c>
-      <c r="G13" s="21" t="n">
-        <f aca="false">F13/$P13/1000</f>
-        <v>1.66979386834115E-005</v>
-      </c>
-      <c r="H13" s="26" t="n">
+      <c r="G13" s="23" t="n">
+        <f aca="false">F13/$P13/10</f>
+        <v>0.00166979386834115</v>
+      </c>
+      <c r="H13" s="28" t="n">
         <v>348</v>
       </c>
-      <c r="I13" s="21" t="n">
-        <f aca="false">H13/$P13/1000</f>
-        <v>0.00152917964784926</v>
-      </c>
-      <c r="J13" s="20" t="n">
+      <c r="I13" s="23" t="n">
+        <f aca="false">H13/$P13/10</f>
+        <v>0.152917964784926</v>
+      </c>
+      <c r="J13" s="22" t="n">
         <f aca="false">L13*$J$37/100</f>
         <v>74.8</v>
       </c>
-      <c r="K13" s="21" t="n">
-        <f aca="false">J13/$P13/1000</f>
-        <v>0.000328685740399784</v>
-      </c>
-      <c r="L13" s="20" t="n">
+      <c r="K13" s="23" t="n">
+        <f aca="false">J13/$P13/10</f>
+        <v>0.0328685740399784</v>
+      </c>
+      <c r="L13" s="22" t="n">
         <v>440</v>
       </c>
-      <c r="M13" s="20" t="n">
+      <c r="M13" s="22" t="n">
         <f aca="false">O13*$M$37/100</f>
         <v>625.6</v>
       </c>
-      <c r="N13" s="22" t="n">
-        <f aca="false">M13/$P13/1000</f>
-        <v>0.00274900801061637</v>
-      </c>
-      <c r="O13" s="20" t="n">
+      <c r="N13" s="23" t="n">
+        <f aca="false">M13/$P13/10</f>
+        <v>0.274900801061637</v>
+      </c>
+      <c r="O13" s="22" t="n">
         <v>4600</v>
       </c>
-      <c r="P13" s="23" t="n">
+      <c r="P13" s="25" t="n">
         <v>227.573</v>
       </c>
-      <c r="Q13" s="23" t="n">
+      <c r="Q13" s="25" t="n">
         <f aca="false">100*P13/$P$36</f>
         <v>1.56304495853387</v>
       </c>
-      <c r="R13" s="20" t="n">
+      <c r="R13" s="22" t="n">
         <f aca="false">H13+F13+B13+D13+J13+M13</f>
         <v>1493.2</v>
       </c>
-      <c r="S13" s="23" t="n">
+      <c r="S13" s="25" t="n">
         <f aca="false">R13/P13</f>
         <v>6.56141106370264</v>
       </c>
-      <c r="U13" s="23" t="n">
+      <c r="U13" s="25" t="n">
         <f aca="false">-T13+($Q$45 + $Q$46)*1000*Q13/100</f>
         <v>694.399916323216</v>
       </c>
-      <c r="V13" s="23" t="n">
+      <c r="V13" s="25" t="n">
         <f aca="false">U13/P13/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W13" s="23" t="n">
+      <c r="W13" s="25" t="n">
         <f aca="false">ROUND(U13/P13 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y13" s="23" t="n">
+      <c r="Y13" s="25" t="n">
         <f aca="false">-Q13*($Q$47)*10</f>
         <v>-375.130790048129</v>
       </c>
-      <c r="Z13" s="23" t="n">
+      <c r="Z13" s="25" t="n">
         <f aca="false">Y13/P13/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC13" s="20" t="n">
+      <c r="AC13" s="22" t="n">
         <v>347.3</v>
       </c>
-      <c r="AH13" s="20" t="s">
+      <c r="AH13" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="AI13" s="20" t="n">
+      <c r="AI13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ13" s="20" t="n">
+      <c r="AJ13" s="22" t="n">
         <v>44</v>
       </c>
-      <c r="AK13" s="20" t="n">
+      <c r="AK13" s="22" t="n">
         <f aca="false">AI13+AJ13/100</f>
         <v>0.44</v>
       </c>
-      <c r="AL13" s="20" t="n">
+      <c r="AL13" s="22" t="n">
         <f aca="false">AK13*1000</f>
         <v>440</v>
       </c>
-      <c r="AO13" s="24" t="s">
+      <c r="AO13" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="AP13" s="20" t="n">
+      <c r="AP13" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="AQ13" s="20" t="n">
+      <c r="AQ13" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="AR13" s="24" t="n">
+      <c r="AR13" s="26" t="n">
         <f aca="false">AP13+AQ13/10</f>
         <v>4.6</v>
       </c>
-      <c r="AS13" s="24" t="n">
+      <c r="AS13" s="26" t="n">
         <f aca="false">1000*AR13</f>
         <v>4600</v>
       </c>
-      <c r="AU13" s="24" t="s">
+      <c r="AU13" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="AV13" s="20" t="n">
+      <c r="AV13" s="22" t="n">
         <v>0.44</v>
       </c>
-      <c r="AW13" s="20" t="n">
+      <c r="AW13" s="22" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX13" s="20" t="n">
+      <c r="AX13" s="22" t="n">
         <v>1.68</v>
       </c>
-      <c r="AY13" s="20" t="n">
+      <c r="AY13" s="22" t="n">
         <v>0.58</v>
       </c>
-      <c r="AZ13" s="20" t="n">
+      <c r="AZ13" s="22" t="n">
         <v>0.79</v>
       </c>
-      <c r="BA13" s="24" t="s">
+      <c r="BA13" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="BC13" s="24" t="n">
+      <c r="BC13" s="26" t="n">
         <f aca="false">AV13*1000</f>
         <v>440</v>
       </c>
-      <c r="BE13" s="20" t="s">
+      <c r="BE13" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="BF13" s="20" t="n">
+      <c r="BF13" s="22" t="n">
         <v>118</v>
       </c>
-      <c r="BG13" s="20" t="n">
+      <c r="BG13" s="22" t="n">
         <v>131</v>
       </c>
-      <c r="BH13" s="20" t="s">
+      <c r="BH13" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI13" s="20" t="n">
+      <c r="BI13" s="22" t="n">
         <v>178</v>
       </c>
-      <c r="BK13" s="20" t="s">
+      <c r="BK13" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="BL13" s="20" t="n">
+      <c r="BL13" s="22" t="n">
         <v>263</v>
       </c>
-      <c r="BM13" s="20" t="s">
+      <c r="BM13" s="22" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="14" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="22" t="n">
         <v>108</v>
       </c>
-      <c r="C14" s="21" t="n">
-        <f aca="false">B14/$P14/1000</f>
-        <v>0.000310018773359053</v>
-      </c>
-      <c r="D14" s="20" t="n">
+      <c r="C14" s="23" t="n">
+        <f aca="false">B14/$P14/10</f>
+        <v>0.0310018773359053</v>
+      </c>
+      <c r="D14" s="22" t="n">
         <v>258</v>
       </c>
-      <c r="E14" s="22" t="n">
-        <f aca="false">D14/$P14/1000</f>
-        <v>0.000740600403024405</v>
-      </c>
-      <c r="F14" s="22" t="n">
+      <c r="E14" s="23" t="n">
+        <f aca="false">D14/$P14/10</f>
+        <v>0.0740600403024405</v>
+      </c>
+      <c r="F14" s="24" t="n">
         <v>113.8</v>
       </c>
-      <c r="G14" s="21" t="n">
-        <f aca="false">F14/$P14/1000</f>
-        <v>0.000326667929706114</v>
-      </c>
-      <c r="H14" s="22" t="n">
+      <c r="G14" s="23" t="n">
+        <f aca="false">F14/$P14/10</f>
+        <v>0.0326667929706114</v>
+      </c>
+      <c r="H14" s="24" t="n">
         <v>533</v>
       </c>
-      <c r="I14" s="21" t="n">
-        <f aca="false">H14/$P14/1000</f>
-        <v>0.00153000005741088</v>
-      </c>
-      <c r="J14" s="20" t="n">
+      <c r="I14" s="23" t="n">
+        <f aca="false">H14/$P14/10</f>
+        <v>0.153000005741088</v>
+      </c>
+      <c r="J14" s="22" t="n">
         <f aca="false">L14*$J$37/100</f>
         <v>192.1</v>
       </c>
-      <c r="K14" s="21" t="n">
-        <f aca="false">J14/$P14/1000</f>
-        <v>0.000551431540391427</v>
-      </c>
-      <c r="L14" s="20" t="n">
+      <c r="K14" s="23" t="n">
+        <f aca="false">J14/$P14/10</f>
+        <v>0.0551431540391427</v>
+      </c>
+      <c r="L14" s="22" t="n">
         <v>1130</v>
       </c>
-      <c r="M14" s="20" t="n">
+      <c r="M14" s="22" t="n">
         <f aca="false">O14*$M$37/100</f>
         <v>571.2</v>
       </c>
-      <c r="N14" s="22" t="n">
-        <f aca="false">M14/$P14/1000</f>
-        <v>0.00163965484576566</v>
-      </c>
-      <c r="O14" s="20" t="n">
+      <c r="N14" s="23" t="n">
+        <f aca="false">M14/$P14/10</f>
+        <v>0.163965484576566</v>
+      </c>
+      <c r="O14" s="22" t="n">
         <v>4200</v>
       </c>
-      <c r="P14" s="23" t="n">
+      <c r="P14" s="25" t="n">
         <v>348.366</v>
       </c>
-      <c r="Q14" s="23" t="n">
+      <c r="Q14" s="25" t="n">
         <f aca="false">100*P14/$P$36</f>
         <v>2.39269034562365</v>
       </c>
-      <c r="R14" s="20" t="n">
+      <c r="R14" s="22" t="n">
         <f aca="false">H14+F14+B14+D14+J14+M14</f>
         <v>1776.1</v>
       </c>
-      <c r="S14" s="23" t="n">
+      <c r="S14" s="25" t="n">
         <f aca="false">R14/P14</f>
         <v>5.09837354965754</v>
       </c>
-      <c r="U14" s="23" t="n">
+      <c r="U14" s="25" t="n">
         <f aca="false">-T14+($Q$45 + $Q$46)*1000*Q14/100</f>
         <v>1062.97900563711</v>
       </c>
-      <c r="V14" s="23" t="n">
+      <c r="V14" s="25" t="n">
         <f aca="false">U14/P14/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W14" s="23" t="n">
+      <c r="W14" s="25" t="n">
         <f aca="false">ROUND(U14/P14 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y14" s="23" t="n">
+      <c r="Y14" s="25" t="n">
         <f aca="false">-Q14*($Q$47)*10</f>
         <v>-574.245682949676</v>
       </c>
-      <c r="Z14" s="23" t="n">
+      <c r="Z14" s="25" t="n">
         <f aca="false">Y14/P14/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC14" s="20" t="n">
+      <c r="AC14" s="22" t="n">
         <v>417.8</v>
       </c>
-      <c r="AH14" s="20" t="s">
+      <c r="AH14" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="AI14" s="20" t="n">
+      <c r="AI14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AJ14" s="20" t="n">
+      <c r="AJ14" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="AK14" s="20" t="n">
+      <c r="AK14" s="22" t="n">
         <f aca="false">AI14+AJ14/100</f>
         <v>1.13</v>
       </c>
-      <c r="AL14" s="20" t="n">
+      <c r="AL14" s="22" t="n">
         <f aca="false">AK14*1000</f>
         <v>1130</v>
       </c>
-      <c r="AO14" s="24" t="s">
+      <c r="AO14" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="AP14" s="20" t="n">
+      <c r="AP14" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="AQ14" s="20" t="n">
+      <c r="AQ14" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="AR14" s="24" t="n">
+      <c r="AR14" s="26" t="n">
         <f aca="false">AP14+AQ14/10</f>
         <v>4.2</v>
       </c>
-      <c r="AS14" s="24" t="n">
+      <c r="AS14" s="26" t="n">
         <f aca="false">1000*AR14</f>
         <v>4200</v>
       </c>
-      <c r="AU14" s="24" t="s">
+      <c r="AU14" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="AV14" s="20" t="n">
+      <c r="AV14" s="22" t="n">
         <v>1.13</v>
       </c>
-      <c r="AW14" s="20" t="n">
+      <c r="AW14" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="AX14" s="20" t="n">
+      <c r="AX14" s="22" t="n">
         <v>2.27</v>
       </c>
-      <c r="AY14" s="20" t="n">
+      <c r="AY14" s="22" t="n">
         <v>1.1</v>
       </c>
-      <c r="AZ14" s="20" t="n">
+      <c r="AZ14" s="22" t="n">
         <v>1.49</v>
       </c>
-      <c r="BA14" s="24" t="s">
+      <c r="BA14" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="BC14" s="24" t="n">
+      <c r="BC14" s="26" t="n">
         <f aca="false">AV14*1000</f>
         <v>1130</v>
       </c>
-      <c r="BE14" s="20" t="s">
+      <c r="BE14" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="BF14" s="20" t="n">
+      <c r="BF14" s="22" t="n">
         <v>116</v>
       </c>
-      <c r="BG14" s="20" t="n">
+      <c r="BG14" s="22" t="n">
         <v>79</v>
       </c>
-      <c r="BH14" s="20" t="s">
+      <c r="BH14" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI14" s="20" t="n">
+      <c r="BI14" s="22" t="n">
         <v>108</v>
       </c>
-      <c r="BK14" s="20" t="s">
+      <c r="BK14" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="BL14" s="20" t="n">
+      <c r="BL14" s="22" t="n">
         <v>258</v>
       </c>
-      <c r="BM14" s="20" t="s">
+      <c r="BM14" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25" t="s">
+    <row r="15" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="21" t="n">
-        <f aca="false">B15/$P15/1000</f>
-        <v>0.000744360658921001</v>
-      </c>
-      <c r="D15" s="20" t="n">
+      <c r="C15" s="23" t="n">
+        <f aca="false">B15/$P15/10</f>
+        <v>0.0744360658921001</v>
+      </c>
+      <c r="D15" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="22" t="n">
-        <f aca="false">D15/$P15/1000</f>
-        <v>0.000679633645101783</v>
-      </c>
-      <c r="F15" s="26" t="n">
+      <c r="E15" s="23" t="n">
+        <f aca="false">D15/$P15/10</f>
+        <v>0.0679633645101783</v>
+      </c>
+      <c r="F15" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="G15" s="21" t="n">
-        <f aca="false">F15/$P15/1000</f>
-        <v>3.23635069096087E-006</v>
-      </c>
-      <c r="H15" s="26" t="n">
+      <c r="G15" s="23" t="n">
+        <f aca="false">F15/$P15/10</f>
+        <v>0.000323635069096087</v>
+      </c>
+      <c r="H15" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="I15" s="21" t="n">
-        <f aca="false">H15/$P15/1000</f>
-        <v>0.000938541700378653</v>
-      </c>
-      <c r="J15" s="20" t="n">
+      <c r="I15" s="23" t="n">
+        <f aca="false">H15/$P15/10</f>
+        <v>0.0938541700378653</v>
+      </c>
+      <c r="J15" s="22" t="n">
         <f aca="false">L15*$J$37/100</f>
         <v>15.3</v>
       </c>
-      <c r="K15" s="21" t="n">
-        <f aca="false">J15/$P15/1000</f>
-        <v>0.000495161655717014</v>
-      </c>
-      <c r="L15" s="20" t="n">
+      <c r="K15" s="23" t="n">
+        <f aca="false">J15/$P15/10</f>
+        <v>0.0495161655717014</v>
+      </c>
+      <c r="L15" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="M15" s="20" t="n">
+      <c r="M15" s="22" t="n">
         <f aca="false">O15*$M$37/100</f>
         <v>68</v>
       </c>
-      <c r="N15" s="22" t="n">
-        <f aca="false">M15/$P15/1000</f>
-        <v>0.00220071846985339</v>
-      </c>
-      <c r="O15" s="20" t="n">
+      <c r="N15" s="23" t="n">
+        <f aca="false">M15/$P15/10</f>
+        <v>0.220071846985339</v>
+      </c>
+      <c r="O15" s="22" t="n">
         <v>500</v>
       </c>
-      <c r="P15" s="23" t="n">
+      <c r="P15" s="25" t="n">
         <v>30.899</v>
       </c>
-      <c r="Q15" s="23" t="n">
+      <c r="Q15" s="25" t="n">
         <f aca="false">100*P15/$P$36</f>
         <v>0.212224324387067</v>
       </c>
-      <c r="R15" s="20" t="n">
+      <c r="R15" s="22" t="n">
         <f aca="false">H15+F15+B15+D15+J15+M15</f>
         <v>156.4</v>
       </c>
-      <c r="S15" s="23" t="n">
+      <c r="S15" s="25" t="n">
         <f aca="false">R15/P15</f>
         <v>5.0616524806628</v>
       </c>
-      <c r="U15" s="23" t="n">
+      <c r="U15" s="25" t="n">
         <f aca="false">-T15+($Q$45 + $Q$46)*1000*Q15/100</f>
         <v>94.2829905765229</v>
       </c>
-      <c r="V15" s="23" t="n">
+      <c r="V15" s="25" t="n">
         <f aca="false">U15/P15/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W15" s="23" t="n">
+      <c r="W15" s="25" t="n">
         <f aca="false">ROUND(U15/P15 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y15" s="23" t="n">
+      <c r="Y15" s="25" t="n">
         <f aca="false">-Q15*($Q$47)*10</f>
         <v>-50.9338378528962</v>
       </c>
-      <c r="Z15" s="23" t="n">
+      <c r="Z15" s="25" t="n">
         <f aca="false">Y15/P15/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC15" s="20" t="n">
+      <c r="AC15" s="22" t="n">
         <v>41.9</v>
       </c>
-      <c r="AH15" s="20" t="s">
+      <c r="AH15" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="AI15" s="20" t="n">
+      <c r="AI15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" s="20" t="n">
+      <c r="AJ15" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="AK15" s="20" t="n">
+      <c r="AK15" s="22" t="n">
         <f aca="false">AI15+AJ15/100</f>
         <v>0.9</v>
       </c>
-      <c r="AL15" s="20" t="n">
+      <c r="AL15" s="22" t="n">
         <f aca="false">AK15*1000</f>
         <v>900</v>
       </c>
-      <c r="AO15" s="24" t="s">
+      <c r="AO15" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AP15" s="20" t="n">
+      <c r="AP15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AQ15" s="20" t="n">
+      <c r="AQ15" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="AR15" s="24" t="n">
+      <c r="AR15" s="26" t="n">
         <f aca="false">AP15+AQ15/10</f>
         <v>0.5</v>
       </c>
-      <c r="AS15" s="24" t="n">
+      <c r="AS15" s="26" t="n">
         <f aca="false">1000*AR15</f>
         <v>500</v>
       </c>
-      <c r="AU15" s="24" t="s">
+      <c r="AU15" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="AV15" s="20" t="n">
+      <c r="AV15" s="22" t="n">
         <v>0.09</v>
       </c>
-      <c r="AW15" s="20" t="n">
+      <c r="AW15" s="22" t="n">
         <v>0.22</v>
       </c>
-      <c r="AX15" s="20" t="n">
+      <c r="AX15" s="22" t="n">
         <v>0.22</v>
       </c>
-      <c r="AY15" s="20" t="n">
+      <c r="AY15" s="22" t="n">
         <v>0.96</v>
       </c>
-      <c r="AZ15" s="20" t="n">
+      <c r="AZ15" s="22" t="n">
         <v>1.3</v>
       </c>
-      <c r="BA15" s="24" t="s">
+      <c r="BA15" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="BC15" s="24" t="n">
+      <c r="BC15" s="26" t="n">
         <f aca="false">AV15*1000</f>
         <v>90</v>
       </c>
-      <c r="BE15" s="20" t="s">
+      <c r="BE15" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="BF15" s="20" t="n">
+      <c r="BF15" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="BG15" s="20" t="n">
+      <c r="BG15" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="BH15" s="20" t="s">
+      <c r="BH15" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI15" s="20" t="n">
+      <c r="BI15" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="BK15" s="20" t="s">
+      <c r="BK15" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="BL15" s="20" t="n">
+      <c r="BL15" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="BM15" s="20" t="s">
+      <c r="BM15" s="22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row r="16" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="22" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="21" t="n">
-        <f aca="false">B16/$P16/1000</f>
-        <v>0.000379785988637743</v>
-      </c>
-      <c r="D16" s="20" t="n">
+      <c r="C16" s="23" t="n">
+        <f aca="false">B16/$P16/10</f>
+        <v>0.0379785988637743</v>
+      </c>
+      <c r="D16" s="22" t="n">
         <v>133</v>
       </c>
-      <c r="E16" s="22" t="n">
-        <f aca="false">D16/$P16/1000</f>
-        <v>0.000520737489575462</v>
-      </c>
-      <c r="F16" s="22" t="n">
+      <c r="E16" s="23" t="n">
+        <f aca="false">D16/$P16/10</f>
+        <v>0.0520737489575462</v>
+      </c>
+      <c r="F16" s="24" t="n">
         <v>81.3</v>
       </c>
-      <c r="G16" s="21" t="n">
-        <f aca="false">F16/$P16/1000</f>
-        <v>0.000318315472951015</v>
-      </c>
-      <c r="H16" s="22" t="n">
+      <c r="G16" s="23" t="n">
+        <f aca="false">F16/$P16/10</f>
+        <v>0.0318315472951015</v>
+      </c>
+      <c r="H16" s="24" t="n">
         <v>152</v>
       </c>
-      <c r="I16" s="21" t="n">
-        <f aca="false">H16/$P16/1000</f>
-        <v>0.000595128559514814</v>
-      </c>
-      <c r="J16" s="20" t="n">
+      <c r="I16" s="23" t="n">
+        <f aca="false">H16/$P16/10</f>
+        <v>0.0595128559514814</v>
+      </c>
+      <c r="J16" s="22" t="n">
         <f aca="false">L16*$J$37/100</f>
         <v>122.4</v>
       </c>
-      <c r="K16" s="21" t="n">
-        <f aca="false">J16/$P16/1000</f>
-        <v>0.000479235103188245</v>
-      </c>
-      <c r="L16" s="20" t="n">
+      <c r="K16" s="23" t="n">
+        <f aca="false">J16/$P16/10</f>
+        <v>0.0479235103188245</v>
+      </c>
+      <c r="L16" s="22" t="n">
         <v>720</v>
       </c>
-      <c r="M16" s="20" t="n">
+      <c r="M16" s="22" t="n">
         <f aca="false">O16*$M$37/100</f>
         <v>394.4</v>
       </c>
-      <c r="N16" s="22" t="n">
-        <f aca="false">M16/$P16/1000</f>
-        <v>0.00154420199916212</v>
-      </c>
-      <c r="O16" s="20" t="n">
+      <c r="N16" s="23" t="n">
+        <f aca="false">M16/$P16/10</f>
+        <v>0.154420199916212</v>
+      </c>
+      <c r="O16" s="22" t="n">
         <v>2900</v>
       </c>
-      <c r="P16" s="23" t="n">
+      <c r="P16" s="25" t="n">
         <v>255.407</v>
       </c>
-      <c r="Q16" s="23" t="n">
+      <c r="Q16" s="25" t="n">
         <f aca="false">100*P16/$P$36</f>
         <v>1.75421787173461</v>
       </c>
-      <c r="R16" s="20" t="n">
+      <c r="R16" s="22" t="n">
         <f aca="false">H16+F16+B16+D16+J16+M16</f>
         <v>980.1</v>
       </c>
-      <c r="S16" s="23" t="n">
+      <c r="S16" s="25" t="n">
         <f aca="false">R16/P16</f>
         <v>3.8374046130294</v>
       </c>
-      <c r="U16" s="23" t="n">
+      <c r="U16" s="25" t="n">
         <f aca="false">-T16+($Q$45 + $Q$46)*1000*Q16/100</f>
         <v>779.330585914689</v>
       </c>
-      <c r="V16" s="23" t="n">
+      <c r="V16" s="25" t="n">
         <f aca="false">U16/P16/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W16" s="23" t="n">
+      <c r="W16" s="25" t="n">
         <f aca="false">ROUND(U16/P16 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y16" s="23" t="n">
+      <c r="Y16" s="25" t="n">
         <f aca="false">-Q16*($Q$47)*10</f>
         <v>-421.012289216306</v>
       </c>
-      <c r="Z16" s="23" t="n">
+      <c r="Z16" s="25" t="n">
         <f aca="false">Y16/P16/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC16" s="20" t="n">
+      <c r="AC16" s="22" t="n">
         <v>281.7</v>
       </c>
-      <c r="AH16" s="20" t="s">
+      <c r="AH16" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="AI16" s="20" t="n">
+      <c r="AI16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ16" s="20" t="n">
+      <c r="AJ16" s="22" t="n">
         <v>72</v>
       </c>
-      <c r="AK16" s="20" t="n">
+      <c r="AK16" s="22" t="n">
         <f aca="false">AI16+AJ16/100</f>
         <v>0.72</v>
       </c>
-      <c r="AL16" s="20" t="n">
+      <c r="AL16" s="22" t="n">
         <f aca="false">AK16*1000</f>
         <v>720</v>
       </c>
-      <c r="AO16" s="24" t="s">
+      <c r="AO16" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="AP16" s="20" t="n">
+      <c r="AP16" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="AQ16" s="20" t="n">
+      <c r="AQ16" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="AR16" s="24" t="n">
+      <c r="AR16" s="26" t="n">
         <f aca="false">AP16+AQ16/10</f>
         <v>2.9</v>
       </c>
-      <c r="AS16" s="24" t="n">
+      <c r="AS16" s="26" t="n">
         <f aca="false">1000*AR16</f>
         <v>2900</v>
       </c>
-      <c r="AU16" s="24" t="s">
+      <c r="AU16" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="AV16" s="20" t="n">
+      <c r="AV16" s="22" t="n">
         <v>0.72</v>
       </c>
-      <c r="AW16" s="20" t="n">
+      <c r="AW16" s="22" t="n">
         <v>1.59</v>
       </c>
-      <c r="AX16" s="20" t="n">
+      <c r="AX16" s="22" t="n">
         <v>1.6</v>
       </c>
-      <c r="AY16" s="20" t="n">
+      <c r="AY16" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AZ16" s="20" t="n">
+      <c r="AZ16" s="22" t="n">
         <v>1.36</v>
       </c>
-      <c r="BA16" s="24" t="s">
+      <c r="BA16" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="BC16" s="24" t="n">
+      <c r="BC16" s="26" t="n">
         <f aca="false">AV16*1000</f>
         <v>720</v>
       </c>
-      <c r="BE16" s="20" t="s">
+      <c r="BE16" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="BF16" s="20" t="n">
+      <c r="BF16" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="BG16" s="20" t="n">
+      <c r="BG16" s="22" t="n">
         <v>71</v>
       </c>
-      <c r="BH16" s="20" t="s">
+      <c r="BH16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI16" s="20" t="n">
+      <c r="BI16" s="22" t="n">
         <v>97</v>
       </c>
-      <c r="BK16" s="20" t="s">
+      <c r="BK16" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="BL16" s="20" t="n">
+      <c r="BL16" s="22" t="n">
         <v>133</v>
       </c>
-      <c r="BM16" s="20" t="s">
+      <c r="BM16" s="22" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
+    <row r="17" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="22" t="n">
         <v>1084</v>
       </c>
-      <c r="C17" s="21" t="n">
-        <f aca="false">B17/$P17/1000</f>
-        <v>0.000421022541018626</v>
-      </c>
-      <c r="D17" s="20" t="n">
+      <c r="C17" s="23" t="n">
+        <f aca="false">B17/$P17/10</f>
+        <v>0.0421022541018626</v>
+      </c>
+      <c r="D17" s="22" t="n">
         <v>1691</v>
       </c>
-      <c r="E17" s="22" t="n">
-        <f aca="false">D17/$P17/1000</f>
-        <v>0.000656779628101934</v>
-      </c>
-      <c r="F17" s="26" t="n">
+      <c r="E17" s="23" t="n">
+        <f aca="false">D17/$P17/10</f>
+        <v>0.0656779628101934</v>
+      </c>
+      <c r="F17" s="28" t="n">
         <v>3100</v>
       </c>
-      <c r="G17" s="21" t="n">
-        <f aca="false">F17/$P17/1000</f>
-        <v>0.00120403125199054</v>
-      </c>
-      <c r="H17" s="26" t="n">
+      <c r="G17" s="23" t="n">
+        <f aca="false">F17/$P17/10</f>
+        <v>0.120403125199054</v>
+      </c>
+      <c r="H17" s="28" t="n">
         <v>6670</v>
       </c>
-      <c r="I17" s="21" t="n">
-        <f aca="false">H17/$P17/1000</f>
-        <v>0.00259060917766996</v>
-      </c>
-      <c r="J17" s="20" t="n">
+      <c r="I17" s="23" t="n">
+        <f aca="false">H17/$P17/10</f>
+        <v>0.259060917766996</v>
+      </c>
+      <c r="J17" s="22" t="n">
         <f aca="false">L17*$J$37/100</f>
         <v>914.6</v>
       </c>
-      <c r="K17" s="21" t="n">
-        <f aca="false">J17/$P17/1000</f>
-        <v>0.000355228059055014</v>
-      </c>
-      <c r="L17" s="20" t="n">
+      <c r="K17" s="23" t="n">
+        <f aca="false">J17/$P17/10</f>
+        <v>0.0355228059055014</v>
+      </c>
+      <c r="L17" s="22" t="n">
         <v>5380</v>
       </c>
-      <c r="M17" s="20" t="n">
+      <c r="M17" s="22" t="n">
         <f aca="false">O17*$M$37/100</f>
         <v>8432</v>
       </c>
-      <c r="N17" s="22" t="n">
-        <f aca="false">M17/$P17/1000</f>
-        <v>0.00327496500541426</v>
-      </c>
-      <c r="O17" s="20" t="n">
+      <c r="N17" s="23" t="n">
+        <f aca="false">M17/$P17/10</f>
+        <v>0.327496500541426</v>
+      </c>
+      <c r="O17" s="22" t="n">
         <v>62000</v>
       </c>
-      <c r="P17" s="23" t="n">
+      <c r="P17" s="25" t="n">
         <v>2574.684</v>
       </c>
-      <c r="Q17" s="23" t="n">
+      <c r="Q17" s="25" t="n">
         <f aca="false">100*P17/$P$36</f>
         <v>17.6837623356805</v>
       </c>
-      <c r="R17" s="20" t="n">
+      <c r="R17" s="22" t="n">
         <f aca="false">H17+F17+B17+D17+J17+M17</f>
         <v>21891.6</v>
       </c>
-      <c r="S17" s="23" t="n">
+      <c r="S17" s="25" t="n">
         <f aca="false">R17/P17</f>
         <v>8.50263566325032</v>
       </c>
-      <c r="T17" s="20" t="n">
+      <c r="T17" s="22" t="n">
         <f aca="false">B17+F17</f>
         <v>4184</v>
       </c>
-      <c r="U17" s="23" t="n">
+      <c r="U17" s="25" t="n">
         <f aca="false">-T17+($Q$45 + $Q$46)*1000*Q17/100</f>
         <v>3672.20593901176</v>
       </c>
-      <c r="V17" s="23" t="n">
+      <c r="V17" s="25" t="n">
         <f aca="false">U17/P17/10</f>
         <v>0.142627442397271</v>
       </c>
-      <c r="W17" s="23" t="n">
+      <c r="W17" s="25" t="n">
         <f aca="false">ROUND(U17/P17 *100/1000, 2)</f>
         <v>0.14</v>
       </c>
-      <c r="Y17" s="23" t="n">
+      <c r="Y17" s="25" t="n">
         <f aca="false">-Q17*($Q$47)*10</f>
         <v>-4244.10296056332</v>
       </c>
-      <c r="Z17" s="23" t="n">
+      <c r="Z17" s="25" t="n">
         <f aca="false">Y17/P17/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC17" s="20" t="n">
+      <c r="AC17" s="22" t="n">
         <v>2991.1</v>
       </c>
-      <c r="AH17" s="20" t="s">
+      <c r="AH17" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="AI17" s="20" t="n">
+      <c r="AI17" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="AJ17" s="20" t="n">
+      <c r="AJ17" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="AK17" s="20" t="n">
+      <c r="AK17" s="22" t="n">
         <f aca="false">AI17+AJ17/100</f>
         <v>5.38</v>
       </c>
-      <c r="AL17" s="20" t="n">
+      <c r="AL17" s="22" t="n">
         <f aca="false">AK17*1000</f>
         <v>5380</v>
       </c>
-      <c r="AO17" s="24" t="s">
+      <c r="AO17" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="AP17" s="20" t="n">
+      <c r="AP17" s="22" t="n">
         <v>62</v>
       </c>
-      <c r="AQ17" s="20" t="n">
+      <c r="AQ17" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AR17" s="24" t="n">
+      <c r="AR17" s="26" t="n">
         <f aca="false">AP17+AQ17/10</f>
         <v>62</v>
       </c>
-      <c r="AS17" s="24" t="n">
+      <c r="AS17" s="26" t="n">
         <f aca="false">1000*AR17</f>
         <v>62000</v>
       </c>
-      <c r="AU17" s="24" t="s">
+      <c r="AU17" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="AV17" s="20" t="n">
+      <c r="AV17" s="22" t="n">
         <v>5.38</v>
       </c>
-      <c r="AW17" s="20" t="n">
+      <c r="AW17" s="22" t="n">
         <v>11.96</v>
       </c>
-      <c r="AX17" s="20" t="n">
+      <c r="AX17" s="22" t="n">
         <v>16.61</v>
       </c>
-      <c r="AY17" s="20" t="n">
+      <c r="AY17" s="22" t="n">
         <v>0.72</v>
       </c>
-      <c r="AZ17" s="20" t="n">
+      <c r="AZ17" s="22" t="n">
         <v>0.98</v>
       </c>
-      <c r="BA17" s="24" t="s">
+      <c r="BA17" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="BC17" s="24" t="n">
+      <c r="BC17" s="26" t="n">
         <f aca="false">AV17*1000</f>
         <v>5380</v>
       </c>
-      <c r="BE17" s="20" t="s">
+      <c r="BE17" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="BF17" s="20" t="s">
+      <c r="BF17" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="BG17" s="20" t="n">
+      <c r="BG17" s="22" t="n">
         <v>797</v>
       </c>
-      <c r="BH17" s="20" t="n">
+      <c r="BH17" s="22" t="n">
         <v>756</v>
       </c>
-      <c r="BI17" s="20" t="n">
+      <c r="BI17" s="22" t="n">
         <v>1084</v>
       </c>
-      <c r="BK17" s="20" t="s">
+      <c r="BK17" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="BL17" s="20" t="n">
+      <c r="BL17" s="22" t="n">
         <v>1691</v>
       </c>
-      <c r="BM17" s="20" t="s">
+      <c r="BM17" s="22" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="18" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+    <row r="18" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="22" t="n">
         <v>978</v>
       </c>
-      <c r="C18" s="21" t="n">
-        <f aca="false">B18/$P18/1000</f>
-        <v>0.000262233683997149</v>
-      </c>
-      <c r="D18" s="20" t="n">
+      <c r="C18" s="23" t="n">
+        <f aca="false">B18/$P18/10</f>
+        <v>0.0262233683997149</v>
+      </c>
+      <c r="D18" s="22" t="n">
         <v>2700</v>
       </c>
-      <c r="E18" s="22" t="n">
-        <f aca="false">D18/$P18/1000</f>
-        <v>0.000723958023305013</v>
-      </c>
-      <c r="F18" s="22" t="n">
+      <c r="E18" s="23" t="n">
+        <f aca="false">D18/$P18/10</f>
+        <v>0.0723958023305013</v>
+      </c>
+      <c r="F18" s="24" t="n">
         <v>1595.2</v>
       </c>
-      <c r="G18" s="21" t="n">
-        <f aca="false">F18/$P18/1000</f>
-        <v>0.000427725125472651</v>
-      </c>
-      <c r="H18" s="22" t="n">
+      <c r="G18" s="23" t="n">
+        <f aca="false">F18/$P18/10</f>
+        <v>0.0427725125472651</v>
+      </c>
+      <c r="H18" s="24" t="n">
         <v>8344</v>
       </c>
-      <c r="I18" s="21" t="n">
-        <f aca="false">H18/$P18/1000</f>
-        <v>0.00223729842461372</v>
-      </c>
-      <c r="J18" s="20" t="n">
+      <c r="I18" s="23" t="n">
+        <f aca="false">H18/$P18/10</f>
+        <v>0.223729842461371</v>
+      </c>
+      <c r="J18" s="22" t="n">
         <f aca="false">L18*$J$37/100</f>
         <v>1026.8</v>
       </c>
-      <c r="K18" s="21" t="n">
-        <f aca="false">J18/$P18/1000</f>
-        <v>0.000275318554936884</v>
-      </c>
-      <c r="L18" s="20" t="n">
+      <c r="K18" s="23" t="n">
+        <f aca="false">J18/$P18/10</f>
+        <v>0.0275318554936884</v>
+      </c>
+      <c r="L18" s="22" t="n">
         <v>6040</v>
       </c>
-      <c r="M18" s="20" t="n">
+      <c r="M18" s="22" t="n">
         <f aca="false">O18*$M$37/100</f>
         <v>7847.2</v>
       </c>
-      <c r="N18" s="22" t="n">
-        <f aca="false">M18/$P18/1000</f>
-        <v>0.00210409014832559</v>
-      </c>
-      <c r="O18" s="20" t="n">
+      <c r="N18" s="23" t="n">
+        <f aca="false">M18/$P18/10</f>
+        <v>0.210409014832559</v>
+      </c>
+      <c r="O18" s="22" t="n">
         <v>57700</v>
       </c>
-      <c r="P18" s="23" t="n">
+      <c r="P18" s="25" t="n">
         <v>3729.498</v>
       </c>
-      <c r="Q18" s="23" t="n">
+      <c r="Q18" s="25" t="n">
         <f aca="false">100*P18/$P$36</f>
         <v>25.6153983414647</v>
       </c>
-      <c r="R18" s="20" t="n">
+      <c r="R18" s="22" t="n">
         <f aca="false">H18+F18+B18+D18+J18+M18</f>
         <v>22491.2</v>
       </c>
-      <c r="S18" s="23" t="n">
+      <c r="S18" s="25" t="n">
         <f aca="false">R18/P18</f>
         <v>6.030623960651</v>
       </c>
-      <c r="U18" s="23" t="n">
+      <c r="U18" s="25" t="n">
         <f aca="false">-T18+($Q$45 + $Q$46)*1000*Q18/100</f>
         <v>11379.9224825775</v>
       </c>
-      <c r="V18" s="23" t="n">
+      <c r="V18" s="25" t="n">
         <f aca="false">U18/P18/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W18" s="23" t="n">
+      <c r="W18" s="25" t="n">
         <f aca="false">ROUND(U18/P18 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y18" s="23" t="n">
+      <c r="Y18" s="25" t="n">
         <f aca="false">-Q18*($Q$47)*10</f>
         <v>-6147.69560195154</v>
       </c>
-      <c r="Z18" s="23" t="n">
+      <c r="Z18" s="25" t="n">
         <f aca="false">Y18/P18/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC18" s="20" t="n">
+      <c r="AC18" s="22" t="n">
         <v>4529.7</v>
       </c>
-      <c r="AH18" s="20" t="s">
+      <c r="AH18" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="AI18" s="20" t="n">
+      <c r="AI18" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="AJ18" s="20" t="n">
+      <c r="AJ18" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="AK18" s="20" t="n">
+      <c r="AK18" s="22" t="n">
         <f aca="false">AI18+AJ18/100</f>
         <v>6.4</v>
       </c>
-      <c r="AL18" s="20" t="n">
+      <c r="AL18" s="22" t="n">
         <f aca="false">AK18*1000</f>
         <v>6400</v>
       </c>
-      <c r="AO18" s="24" t="s">
+      <c r="AO18" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="AP18" s="20" t="n">
+      <c r="AP18" s="22" t="n">
         <v>57</v>
       </c>
-      <c r="AQ18" s="20" t="n">
+      <c r="AQ18" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="AR18" s="24" t="n">
+      <c r="AR18" s="26" t="n">
         <f aca="false">AP18+AQ18/10</f>
         <v>57.7</v>
       </c>
-      <c r="AS18" s="24" t="n">
+      <c r="AS18" s="26" t="n">
         <f aca="false">1000*AR18</f>
         <v>57700</v>
       </c>
-      <c r="AU18" s="24" t="s">
+      <c r="AU18" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="AV18" s="20" t="n">
+      <c r="AV18" s="22" t="n">
         <v>6.04</v>
       </c>
-      <c r="AW18" s="20" t="n">
+      <c r="AW18" s="22" t="n">
         <v>13.43</v>
       </c>
-      <c r="AX18" s="20" t="n">
+      <c r="AX18" s="22" t="n">
         <v>24.81</v>
       </c>
-      <c r="AY18" s="20" t="n">
+      <c r="AY18" s="22" t="n">
         <v>0.54</v>
       </c>
-      <c r="AZ18" s="20" t="n">
+      <c r="AZ18" s="22" t="n">
         <v>0.73</v>
       </c>
-      <c r="BA18" s="24" t="s">
+      <c r="BA18" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="BC18" s="24" t="n">
+      <c r="BC18" s="26" t="n">
         <f aca="false">AV18*1000</f>
         <v>6040</v>
       </c>
-      <c r="BE18" s="20" t="s">
+      <c r="BE18" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="BF18" s="20" t="s">
+      <c r="BF18" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="BG18" s="20" t="n">
+      <c r="BG18" s="22" t="n">
         <v>719</v>
       </c>
-      <c r="BH18" s="20" t="s">
+      <c r="BH18" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI18" s="20" t="n">
+      <c r="BI18" s="22" t="n">
         <v>978</v>
       </c>
-      <c r="BK18" s="20" t="s">
+      <c r="BK18" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="BL18" s="20" t="n">
+      <c r="BL18" s="22" t="n">
         <v>2700</v>
       </c>
-      <c r="BM18" s="20" t="s">
+      <c r="BM18" s="22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="s">
+    <row r="19" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="22" t="n">
         <v>91</v>
       </c>
-      <c r="C19" s="21" t="n">
-        <f aca="false">B19/$P19/1000</f>
-        <v>0.000503093193867792</v>
-      </c>
-      <c r="D19" s="20" t="n">
+      <c r="C19" s="23" t="n">
+        <f aca="false">B19/$P19/10</f>
+        <v>0.0503093193867792</v>
+      </c>
+      <c r="D19" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="E19" s="22" t="n">
-        <f aca="false">D19/$P19/1000</f>
-        <v>0.000298538818339129</v>
-      </c>
-      <c r="F19" s="26" t="n">
+      <c r="E19" s="23" t="n">
+        <f aca="false">D19/$P19/10</f>
+        <v>0.0298538818339129</v>
+      </c>
+      <c r="F19" s="28" t="n">
         <v>22.7</v>
       </c>
-      <c r="G19" s="21" t="n">
-        <f aca="false">F19/$P19/1000</f>
-        <v>0.000125496873635152</v>
-      </c>
-      <c r="H19" s="26" t="n">
+      <c r="G19" s="23" t="n">
+        <f aca="false">F19/$P19/10</f>
+        <v>0.0125496873635152</v>
+      </c>
+      <c r="H19" s="28" t="n">
         <v>118</v>
       </c>
-      <c r="I19" s="21" t="n">
-        <f aca="false">H19/$P19/1000</f>
-        <v>0.000652362603037356</v>
-      </c>
-      <c r="J19" s="20" t="n">
+      <c r="I19" s="23" t="n">
+        <f aca="false">H19/$P19/10</f>
+        <v>0.0652362603037356</v>
+      </c>
+      <c r="J19" s="22" t="n">
         <f aca="false">L19*$J$37/100</f>
         <v>431.8</v>
       </c>
-      <c r="K19" s="21" t="n">
-        <f aca="false">J19/$P19/1000</f>
-        <v>0.00238720484738585</v>
-      </c>
-      <c r="L19" s="20" t="n">
+      <c r="K19" s="23" t="n">
+        <f aca="false">J19/$P19/10</f>
+        <v>0.238720484738585</v>
+      </c>
+      <c r="L19" s="22" t="n">
         <v>2540</v>
       </c>
-      <c r="M19" s="20" t="n">
+      <c r="M19" s="22" t="n">
         <f aca="false">O19*$M$37/100</f>
         <v>856.8</v>
       </c>
-      <c r="N19" s="22" t="n">
-        <f aca="false">M19/$P19/1000</f>
-        <v>0.00473681591764751</v>
-      </c>
-      <c r="O19" s="20" t="n">
+      <c r="N19" s="23" t="n">
+        <f aca="false">M19/$P19/10</f>
+        <v>0.473681591764751</v>
+      </c>
+      <c r="O19" s="22" t="n">
         <v>6300</v>
       </c>
-      <c r="P19" s="23" t="n">
+      <c r="P19" s="25" t="n">
         <v>180.881</v>
       </c>
-      <c r="Q19" s="23" t="n">
+      <c r="Q19" s="25" t="n">
         <f aca="false">100*P19/$P$36</f>
         <v>1.24234920286926</v>
       </c>
-      <c r="R19" s="20" t="n">
+      <c r="R19" s="22" t="n">
         <f aca="false">H19+F19+B19+D19+J19+M19</f>
         <v>1574.3</v>
       </c>
-      <c r="S19" s="23" t="n">
+      <c r="S19" s="25" t="n">
         <f aca="false">R19/P19</f>
         <v>8.70351225391279</v>
       </c>
-      <c r="T19" s="27" t="n">
+      <c r="T19" s="29" t="n">
         <f aca="false">F19</f>
         <v>22.7</v>
       </c>
-      <c r="U19" s="23" t="n">
+      <c r="U19" s="25" t="n">
         <f aca="false">-T19+($Q$45 + $Q$46)*1000*Q19/100</f>
         <v>529.227299215898</v>
       </c>
-      <c r="V19" s="23" t="n">
+      <c r="V19" s="25" t="n">
         <f aca="false">U19/P19/10</f>
         <v>0.292583134334672</v>
       </c>
-      <c r="W19" s="23" t="n">
+      <c r="W19" s="25" t="n">
         <f aca="false">ROUND(U19/P19 *100/1000, 2)</f>
         <v>0.29</v>
       </c>
-      <c r="Y19" s="23" t="n">
+      <c r="Y19" s="25" t="n">
         <f aca="false">-Q19*($Q$47)*10</f>
         <v>-298.163808688621</v>
       </c>
-      <c r="Z19" s="23" t="n">
+      <c r="Z19" s="25" t="n">
         <f aca="false">Y19/P19/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC19" s="20" t="n">
+      <c r="AC19" s="22" t="n">
         <v>248.4</v>
       </c>
-      <c r="AH19" s="20" t="s">
+      <c r="AH19" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="AI19" s="20" t="n">
+      <c r="AI19" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="AJ19" s="20" t="n">
+      <c r="AJ19" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="AK19" s="20" t="n">
+      <c r="AK19" s="22" t="n">
         <f aca="false">AI19+AJ19/100</f>
         <v>2.54</v>
       </c>
-      <c r="AL19" s="20" t="n">
+      <c r="AL19" s="22" t="n">
         <f aca="false">AK19*1000</f>
         <v>2540</v>
       </c>
-      <c r="AO19" s="24" t="s">
+      <c r="AO19" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="AP19" s="20" t="n">
+      <c r="AP19" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="AQ19" s="20" t="n">
+      <c r="AQ19" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="AR19" s="24" t="n">
+      <c r="AR19" s="26" t="n">
         <f aca="false">AP19+AQ19/10</f>
         <v>6.3</v>
       </c>
-      <c r="AS19" s="24" t="n">
+      <c r="AS19" s="26" t="n">
         <f aca="false">1000*AR19</f>
         <v>6300</v>
       </c>
-      <c r="AU19" s="24" t="s">
+      <c r="AU19" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="AV19" s="20" t="n">
+      <c r="AV19" s="22" t="n">
         <v>2.54</v>
       </c>
-      <c r="AW19" s="20" t="n">
+      <c r="AW19" s="22" t="n">
         <v>5.64</v>
       </c>
-      <c r="AX19" s="20" t="n">
+      <c r="AX19" s="22" t="n">
         <v>1.3</v>
       </c>
-      <c r="AY19" s="20" t="n">
+      <c r="AY19" s="22" t="n">
         <v>4.34</v>
       </c>
-      <c r="AZ19" s="20" t="n">
+      <c r="AZ19" s="22" t="n">
         <v>5.88</v>
       </c>
-      <c r="BA19" s="24" t="s">
+      <c r="BA19" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="BC19" s="24" t="n">
+      <c r="BC19" s="26" t="n">
         <f aca="false">AV19*1000</f>
         <v>2540</v>
       </c>
-      <c r="BE19" s="20" t="s">
+      <c r="BE19" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="BF19" s="20" t="n">
+      <c r="BF19" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="BG19" s="20" t="n">
+      <c r="BG19" s="22" t="n">
         <v>67</v>
       </c>
-      <c r="BH19" s="20" t="s">
+      <c r="BH19" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI19" s="20" t="n">
+      <c r="BI19" s="22" t="n">
         <v>91</v>
       </c>
-      <c r="BK19" s="20" t="s">
+      <c r="BK19" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="BL19" s="20" t="n">
+      <c r="BL19" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="BM19" s="20" t="s">
+      <c r="BM19" s="22" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row r="20" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="22" t="n">
         <v>140</v>
       </c>
-      <c r="C20" s="21" t="n">
-        <f aca="false">B20/$P20/1000</f>
-        <v>0.000940076817705675</v>
-      </c>
-      <c r="D20" s="20" t="n">
+      <c r="C20" s="23" t="n">
+        <f aca="false">B20/$P20/10</f>
+        <v>0.0940076817705675</v>
+      </c>
+      <c r="D20" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="E20" s="22" t="n">
-        <f aca="false">D20/$P20/1000</f>
-        <v>0.000758776288576724</v>
-      </c>
-      <c r="F20" s="22" t="n">
+      <c r="E20" s="23" t="n">
+        <f aca="false">D20/$P20/10</f>
+        <v>0.0758776288576724</v>
+      </c>
+      <c r="F20" s="24" t="n">
         <v>5.9</v>
       </c>
-      <c r="G20" s="21" t="n">
-        <f aca="false">F20/$P20/1000</f>
-        <v>3.9617523031882E-005</v>
-      </c>
-      <c r="H20" s="22" t="n">
+      <c r="G20" s="23" t="n">
+        <f aca="false">F20/$P20/10</f>
+        <v>0.0039617523031882</v>
+      </c>
+      <c r="H20" s="24" t="n">
         <v>208</v>
       </c>
-      <c r="I20" s="21" t="n">
-        <f aca="false">H20/$P20/1000</f>
-        <v>0.00139668555773415</v>
-      </c>
-      <c r="J20" s="20" t="n">
+      <c r="I20" s="23" t="n">
+        <f aca="false">H20/$P20/10</f>
+        <v>0.139668555773415</v>
+      </c>
+      <c r="J20" s="22" t="n">
         <f aca="false">L20*$J$37/100</f>
         <v>62.9</v>
       </c>
-      <c r="K20" s="21" t="n">
-        <f aca="false">J20/$P20/1000</f>
-        <v>0.000422363084526336</v>
-      </c>
-      <c r="L20" s="20" t="n">
+      <c r="K20" s="23" t="n">
+        <f aca="false">J20/$P20/10</f>
+        <v>0.0422363084526336</v>
+      </c>
+      <c r="L20" s="22" t="n">
         <v>370</v>
       </c>
-      <c r="M20" s="20" t="n">
+      <c r="M20" s="22" t="n">
         <f aca="false">O20*$M$37/100</f>
         <v>340</v>
       </c>
-      <c r="N20" s="22" t="n">
-        <f aca="false">M20/$P20/1000</f>
-        <v>0.00228304370014235</v>
-      </c>
-      <c r="O20" s="20" t="n">
+      <c r="N20" s="23" t="n">
+        <f aca="false">M20/$P20/10</f>
+        <v>0.228304370014235</v>
+      </c>
+      <c r="O20" s="22" t="n">
         <v>2500</v>
       </c>
-      <c r="P20" s="23" t="n">
+      <c r="P20" s="25" t="n">
         <v>148.924</v>
       </c>
-      <c r="Q20" s="23" t="n">
+      <c r="Q20" s="25" t="n">
         <f aca="false">100*P20/$P$36</f>
         <v>1.02285819233696</v>
       </c>
-      <c r="R20" s="20" t="n">
+      <c r="R20" s="22" t="n">
         <f aca="false">H20+F20+B20+D20+J20+M20</f>
         <v>869.8</v>
       </c>
-      <c r="S20" s="23" t="n">
+      <c r="S20" s="25" t="n">
         <f aca="false">R20/P20</f>
         <v>5.84056297171712</v>
       </c>
-      <c r="U20" s="23" t="n">
+      <c r="U20" s="25" t="n">
         <f aca="false">-T20+($Q$45 + $Q$46)*1000*Q20/100</f>
         <v>454.416003385809</v>
       </c>
-      <c r="V20" s="23" t="n">
+      <c r="V20" s="25" t="n">
         <f aca="false">U20/P20/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W20" s="23" t="n">
+      <c r="W20" s="25" t="n">
         <f aca="false">ROUND(U20/P20 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y20" s="23" t="n">
+      <c r="Y20" s="25" t="n">
         <f aca="false">-Q20*($Q$47)*10</f>
         <v>-245.48596616087</v>
       </c>
-      <c r="Z20" s="23" t="n">
+      <c r="Z20" s="25" t="n">
         <f aca="false">Y20/P20/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC20" s="20" t="n">
+      <c r="AC20" s="22" t="n">
         <v>218.8</v>
       </c>
-      <c r="AH20" s="20" t="s">
+      <c r="AH20" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="AI20" s="20" t="n">
+      <c r="AI20" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" s="20" t="n">
+      <c r="AJ20" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="AK20" s="20" t="n">
+      <c r="AK20" s="22" t="n">
         <f aca="false">AI20+AJ20/100</f>
         <v>0.37</v>
       </c>
-      <c r="AL20" s="20" t="n">
+      <c r="AL20" s="22" t="n">
         <f aca="false">AK20*1000</f>
         <v>370</v>
       </c>
-      <c r="AO20" s="24" t="s">
+      <c r="AO20" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="AP20" s="20" t="n">
+      <c r="AP20" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="AQ20" s="20" t="n">
+      <c r="AQ20" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="AR20" s="24" t="n">
+      <c r="AR20" s="26" t="n">
         <f aca="false">AP20+AQ20/10</f>
         <v>2.5</v>
       </c>
-      <c r="AS20" s="24" t="n">
+      <c r="AS20" s="26" t="n">
         <f aca="false">1000*AR20</f>
         <v>2500</v>
       </c>
-      <c r="AU20" s="24" t="s">
+      <c r="AU20" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="AV20" s="20" t="n">
+      <c r="AV20" s="22" t="n">
         <v>0.37</v>
       </c>
-      <c r="AW20" s="20" t="n">
+      <c r="AW20" s="22" t="n">
         <v>0.82</v>
       </c>
-      <c r="AX20" s="20" t="n">
+      <c r="AX20" s="22" t="n">
         <v>1.18</v>
       </c>
-      <c r="AY20" s="20" t="n">
+      <c r="AY20" s="22" t="n">
         <v>0.7</v>
       </c>
-      <c r="AZ20" s="20" t="n">
+      <c r="AZ20" s="22" t="n">
         <v>0.95</v>
       </c>
-      <c r="BA20" s="24" t="s">
+      <c r="BA20" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="BC20" s="24" t="n">
+      <c r="BC20" s="26" t="n">
         <f aca="false">AV20*1000</f>
         <v>370</v>
       </c>
-      <c r="BE20" s="20" t="s">
+      <c r="BE20" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="BF20" s="20" t="n">
+      <c r="BF20" s="22" t="n">
         <v>51</v>
       </c>
-      <c r="BG20" s="20" t="n">
+      <c r="BG20" s="22" t="n">
         <v>103</v>
       </c>
-      <c r="BH20" s="20" t="s">
+      <c r="BH20" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI20" s="20" t="n">
+      <c r="BI20" s="22" t="n">
         <v>140</v>
       </c>
-      <c r="BK20" s="20" t="s">
+      <c r="BK20" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="BL20" s="20" t="n">
+      <c r="BL20" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="BM20" s="20" t="s">
+      <c r="BM20" s="22" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="21" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
+    <row r="21" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="22" t="n">
         <v>97</v>
       </c>
-      <c r="C21" s="21" t="n">
-        <f aca="false">B21/$P21/1000</f>
-        <v>0.000299863052234907</v>
-      </c>
-      <c r="D21" s="20" t="n">
+      <c r="C21" s="23" t="n">
+        <f aca="false">B21/$P21/10</f>
+        <v>0.0299863052234907</v>
+      </c>
+      <c r="D21" s="22" t="n">
         <v>160</v>
       </c>
-      <c r="E21" s="22" t="n">
-        <f aca="false">D21/$P21/1000</f>
-        <v>0.000494619467603971</v>
-      </c>
-      <c r="F21" s="26" t="n">
+      <c r="E21" s="23" t="n">
+        <f aca="false">D21/$P21/10</f>
+        <v>0.0494619467603971</v>
+      </c>
+      <c r="F21" s="28" t="n">
         <v>241.4</v>
       </c>
-      <c r="G21" s="21" t="n">
-        <f aca="false">F21/$P21/1000</f>
-        <v>0.000746257121747491</v>
-      </c>
-      <c r="H21" s="26" t="n">
+      <c r="G21" s="23" t="n">
+        <f aca="false">F21/$P21/10</f>
+        <v>0.0746257121747491</v>
+      </c>
+      <c r="H21" s="28" t="n">
         <v>331</v>
       </c>
-      <c r="I21" s="21" t="n">
-        <f aca="false">H21/$P21/1000</f>
-        <v>0.00102324402360571</v>
-      </c>
-      <c r="J21" s="20" t="n">
+      <c r="I21" s="23" t="n">
+        <f aca="false">H21/$P21/10</f>
+        <v>0.102324402360571</v>
+      </c>
+      <c r="J21" s="22" t="n">
         <f aca="false">L21*$J$37/100</f>
         <v>159.8</v>
       </c>
-      <c r="K21" s="21" t="n">
-        <f aca="false">J21/$P21/1000</f>
-        <v>0.000494001193269466</v>
-      </c>
-      <c r="L21" s="20" t="n">
+      <c r="K21" s="23" t="n">
+        <f aca="false">J21/$P21/10</f>
+        <v>0.0494001193269466</v>
+      </c>
+      <c r="L21" s="22" t="n">
         <v>940</v>
       </c>
-      <c r="M21" s="20" t="n">
+      <c r="M21" s="22" t="n">
         <f aca="false">O21*$M$37/100</f>
         <v>516.8</v>
       </c>
-      <c r="N21" s="22" t="n">
-        <f aca="false">M21/$P21/1000</f>
-        <v>0.00159762088036082</v>
-      </c>
-      <c r="O21" s="20" t="n">
+      <c r="N21" s="23" t="n">
+        <f aca="false">M21/$P21/10</f>
+        <v>0.159762088036082</v>
+      </c>
+      <c r="O21" s="22" t="n">
         <v>3800</v>
       </c>
-      <c r="P21" s="23" t="n">
+      <c r="P21" s="25" t="n">
         <v>323.481</v>
       </c>
-      <c r="Q21" s="23" t="n">
+      <c r="Q21" s="25" t="n">
         <f aca="false">100*P21/$P$36</f>
         <v>2.22177211809615</v>
       </c>
-      <c r="R21" s="20" t="n">
+      <c r="R21" s="22" t="n">
         <f aca="false">H21+F21+B21+D21+J21+M21</f>
         <v>1506</v>
       </c>
-      <c r="S21" s="23" t="n">
+      <c r="S21" s="25" t="n">
         <f aca="false">R21/P21</f>
         <v>4.65560573882237</v>
       </c>
-      <c r="T21" s="27" t="n">
+      <c r="T21" s="29" t="n">
         <f aca="false">F21</f>
         <v>241.4</v>
       </c>
-      <c r="U21" s="23" t="n">
+      <c r="U21" s="25" t="n">
         <f aca="false">-T21+($Q$45 + $Q$46)*1000*Q21/100</f>
         <v>745.646702957514</v>
       </c>
-      <c r="V21" s="23" t="n">
+      <c r="V21" s="25" t="n">
         <f aca="false">U21/P21/10</f>
         <v>0.230507109523438</v>
       </c>
-      <c r="W21" s="23" t="n">
+      <c r="W21" s="25" t="n">
         <f aca="false">ROUND(U21/P21 *100/1000, 2)</f>
         <v>0.23</v>
       </c>
-      <c r="Y21" s="23" t="n">
+      <c r="Y21" s="25" t="n">
         <f aca="false">-Q21*($Q$47)*10</f>
         <v>-533.225308343076</v>
       </c>
-      <c r="Z21" s="23" t="n">
+      <c r="Z21" s="25" t="n">
         <f aca="false">Y21/P21/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC21" s="20" t="n">
+      <c r="AC21" s="22" t="n">
         <v>602.4</v>
       </c>
-      <c r="AH21" s="20" t="s">
+      <c r="AH21" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="AI21" s="20" t="n">
+      <c r="AI21" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" s="20" t="n">
+      <c r="AJ21" s="22" t="n">
         <v>94</v>
       </c>
-      <c r="AK21" s="20" t="n">
+      <c r="AK21" s="22" t="n">
         <f aca="false">AI21+AJ21/100</f>
         <v>0.94</v>
       </c>
-      <c r="AL21" s="20" t="n">
+      <c r="AL21" s="22" t="n">
         <f aca="false">AK21*1000</f>
         <v>940</v>
       </c>
-      <c r="AO21" s="24" t="s">
+      <c r="AO21" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="AP21" s="20" t="n">
+      <c r="AP21" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="AQ21" s="20" t="n">
+      <c r="AQ21" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="AR21" s="24" t="n">
+      <c r="AR21" s="26" t="n">
         <f aca="false">AP21+AQ21/10</f>
         <v>3.8</v>
       </c>
-      <c r="AS21" s="24" t="n">
+      <c r="AS21" s="26" t="n">
         <f aca="false">1000*AR21</f>
         <v>3800</v>
       </c>
-      <c r="AT21" s="24" t="s">
+      <c r="AT21" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="AU21" s="24" t="s">
+      <c r="AU21" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="AV21" s="20" t="n">
+      <c r="AV21" s="22" t="n">
         <v>0.94</v>
       </c>
-      <c r="AW21" s="20" t="n">
+      <c r="AW21" s="22" t="n">
         <v>2.1</v>
       </c>
-      <c r="AX21" s="20" t="n">
+      <c r="AX21" s="22" t="n">
         <v>2.33</v>
       </c>
-      <c r="AY21" s="20" t="n">
+      <c r="AY21" s="22" t="n">
         <v>0.9</v>
       </c>
-      <c r="AZ21" s="20" t="n">
+      <c r="AZ21" s="22" t="n">
         <v>1.22</v>
       </c>
-      <c r="BA21" s="24" t="s">
+      <c r="BA21" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="BC21" s="24" t="n">
+      <c r="BC21" s="26" t="n">
         <f aca="false">AV21*1000</f>
         <v>940</v>
       </c>
-      <c r="BE21" s="20" t="s">
+      <c r="BE21" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="BF21" s="20" t="n">
+      <c r="BF21" s="22" t="n">
         <v>72</v>
       </c>
-      <c r="BG21" s="20" t="n">
+      <c r="BG21" s="22" t="n">
         <v>71</v>
       </c>
-      <c r="BH21" s="20" t="s">
+      <c r="BH21" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI21" s="20" t="n">
+      <c r="BI21" s="22" t="n">
         <v>97</v>
       </c>
-      <c r="BK21" s="20" t="s">
+      <c r="BK21" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="BL21" s="20" t="n">
+      <c r="BL21" s="22" t="n">
         <v>160</v>
       </c>
-      <c r="BM21" s="20" t="s">
+      <c r="BM21" s="22" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="22" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="22" t="n">
         <v>467</v>
       </c>
-      <c r="C22" s="21" t="n">
-        <f aca="false">B22/$P22/1000</f>
-        <v>0.000257444955291679</v>
-      </c>
-      <c r="D22" s="20" t="n">
+      <c r="C22" s="23" t="n">
+        <f aca="false">B22/$P22/10</f>
+        <v>0.0257444955291679</v>
+      </c>
+      <c r="D22" s="22" t="n">
         <v>891</v>
       </c>
-      <c r="E22" s="22" t="n">
-        <f aca="false">D22/$P22/1000</f>
-        <v>0.000491185128832733</v>
-      </c>
-      <c r="F22" s="22" t="n">
+      <c r="E22" s="23" t="n">
+        <f aca="false">D22/$P22/10</f>
+        <v>0.0491185128832733</v>
+      </c>
+      <c r="F22" s="24" t="n">
         <v>544.5</v>
       </c>
-      <c r="G22" s="21" t="n">
-        <f aca="false">F22/$P22/1000</f>
-        <v>0.000300168689842225</v>
-      </c>
-      <c r="H22" s="22" t="n">
+      <c r="G22" s="23" t="n">
+        <f aca="false">F22/$P22/10</f>
+        <v>0.0300168689842225</v>
+      </c>
+      <c r="H22" s="24" t="n">
         <v>2618</v>
       </c>
-      <c r="I22" s="21" t="n">
-        <f aca="false">H22/$P22/1000</f>
-        <v>0.00144323531681716</v>
-      </c>
-      <c r="J22" s="20" t="n">
+      <c r="I22" s="23" t="n">
+        <f aca="false">H22/$P22/10</f>
+        <v>0.144323531681716</v>
+      </c>
+      <c r="J22" s="22" t="n">
         <f aca="false">L22*$J$37/100</f>
         <v>1208.7</v>
       </c>
-      <c r="K22" s="21" t="n">
-        <f aca="false">J22/$P22/1000</f>
-        <v>0.000666324876790262</v>
-      </c>
-      <c r="L22" s="20" t="n">
+      <c r="K22" s="23" t="n">
+        <f aca="false">J22/$P22/10</f>
+        <v>0.0666324876790262</v>
+      </c>
+      <c r="L22" s="22" t="n">
         <v>7110</v>
       </c>
-      <c r="M22" s="20" t="n">
+      <c r="M22" s="22" t="n">
         <f aca="false">O22*$M$37/100</f>
         <v>7684</v>
       </c>
-      <c r="N22" s="22" t="n">
-        <f aca="false">M22/$P22/1000</f>
-        <v>0.00423598937143739</v>
-      </c>
-      <c r="O22" s="20" t="n">
+      <c r="N22" s="23" t="n">
+        <f aca="false">M22/$P22/10</f>
+        <v>0.423598937143739</v>
+      </c>
+      <c r="O22" s="22" t="n">
         <v>56500</v>
       </c>
-      <c r="P22" s="23" t="n">
+      <c r="P22" s="25" t="n">
         <v>1813.98</v>
       </c>
-      <c r="Q22" s="23" t="n">
+      <c r="Q22" s="25" t="n">
         <f aca="false">100*P22/$P$36</f>
         <v>12.4590012606121</v>
       </c>
-      <c r="R22" s="20" t="n">
+      <c r="R22" s="22" t="n">
         <f aca="false">H22+F22+B22+D22+J22+M22</f>
         <v>13413.2</v>
       </c>
-      <c r="S22" s="23" t="n">
+      <c r="S22" s="25" t="n">
         <f aca="false">R22/P22</f>
         <v>7.39434833901146</v>
       </c>
-      <c r="T22" s="20" t="n">
+      <c r="T22" s="22" t="n">
         <f aca="false">B22+F22</f>
         <v>1011.5</v>
       </c>
-      <c r="U22" s="23" t="n">
+      <c r="U22" s="25" t="n">
         <f aca="false">-T22+($Q$45 + $Q$46)*1000*Q22/100</f>
         <v>4523.54835904078</v>
       </c>
-      <c r="V22" s="23" t="n">
+      <c r="V22" s="25" t="n">
         <f aca="false">U22/P22/10</f>
         <v>0.249371457184797</v>
       </c>
-      <c r="W22" s="23" t="n">
+      <c r="W22" s="25" t="n">
         <f aca="false">ROUND(U22/P22 *100/1000, 2)</f>
         <v>0.25</v>
       </c>
-      <c r="Y22" s="23" t="n">
+      <c r="Y22" s="25" t="n">
         <f aca="false">-Q22*($Q$47)*10</f>
         <v>-2990.1603025469</v>
       </c>
-      <c r="Z22" s="23" t="n">
+      <c r="Z22" s="25" t="n">
         <f aca="false">Y22/P22/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC22" s="20" t="n">
+      <c r="AC22" s="22" t="n">
         <v>2258</v>
       </c>
-      <c r="AH22" s="20" t="s">
+      <c r="AH22" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="AI22" s="20" t="n">
+      <c r="AI22" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="AJ22" s="20" t="n">
+      <c r="AJ22" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="AK22" s="20" t="n">
+      <c r="AK22" s="22" t="n">
         <f aca="false">AI22+AJ22/100</f>
         <v>7.11</v>
       </c>
-      <c r="AL22" s="20" t="n">
+      <c r="AL22" s="22" t="n">
         <f aca="false">AK22*1000</f>
         <v>7110</v>
       </c>
-      <c r="AO22" s="24" t="s">
+      <c r="AO22" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="AP22" s="20" t="n">
+      <c r="AP22" s="22" t="n">
         <v>56</v>
       </c>
-      <c r="AQ22" s="20" t="n">
+      <c r="AQ22" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="AR22" s="24" t="n">
+      <c r="AR22" s="26" t="n">
         <f aca="false">AP22+AQ22/10</f>
         <v>56.5</v>
       </c>
-      <c r="AS22" s="24" t="n">
+      <c r="AS22" s="26" t="n">
         <f aca="false">1000*AR22</f>
         <v>56500</v>
       </c>
-      <c r="AU22" s="24" t="s">
+      <c r="AU22" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="AV22" s="20" t="n">
+      <c r="AV22" s="22" t="n">
         <v>7.11</v>
       </c>
-      <c r="AW22" s="20" t="n">
+      <c r="AW22" s="22" t="n">
         <v>15.81</v>
       </c>
-      <c r="AX22" s="20" t="n">
+      <c r="AX22" s="22" t="n">
         <v>12.06</v>
       </c>
-      <c r="AY22" s="20" t="n">
+      <c r="AY22" s="22" t="n">
         <v>1.31</v>
       </c>
-      <c r="AZ22" s="20" t="n">
+      <c r="AZ22" s="22" t="n">
         <v>1.78</v>
       </c>
-      <c r="BA22" s="24" t="s">
+      <c r="BA22" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="BC22" s="24" t="n">
+      <c r="BC22" s="26" t="n">
         <f aca="false">AV22*1000</f>
         <v>7110</v>
       </c>
-      <c r="BE22" s="20" t="s">
+      <c r="BE22" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="BF22" s="20" t="n">
+      <c r="BF22" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="BG22" s="20" t="n">
+      <c r="BG22" s="22" t="n">
         <v>343</v>
       </c>
-      <c r="BH22" s="20" t="s">
+      <c r="BH22" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="BI22" s="20" t="n">
+      <c r="BI22" s="22" t="n">
         <v>467</v>
       </c>
-      <c r="BK22" s="20" t="s">
+      <c r="BK22" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="BL22" s="20" t="n">
+      <c r="BL22" s="22" t="n">
         <v>891</v>
       </c>
-      <c r="BM22" s="20" t="s">
+      <c r="BM22" s="22" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="23" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="s">
+    <row r="23" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="C23" s="21" t="n">
-        <f aca="false">B23/$P23/1000</f>
-        <v>0.000816326530612245</v>
-      </c>
-      <c r="D23" s="20" t="n">
+      <c r="C23" s="23" t="n">
+        <f aca="false">B23/$P23/10</f>
+        <v>0.0816326530612245</v>
+      </c>
+      <c r="D23" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="22" t="n">
-        <f aca="false">D23/$P23/1000</f>
-        <v>0.000604686318972033</v>
-      </c>
-      <c r="F23" s="26" t="n">
+      <c r="E23" s="23" t="n">
+        <f aca="false">D23/$P23/10</f>
+        <v>0.0604686318972033</v>
+      </c>
+      <c r="F23" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="21" t="n">
-        <f aca="false">F23/$P23/1000</f>
+      <c r="G23" s="23" t="n">
+        <f aca="false">F23/$P23/10</f>
         <v>0</v>
       </c>
-      <c r="H23" s="26" t="n">
+      <c r="H23" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="21" t="n">
-        <f aca="false">H23/$P23/1000</f>
-        <v>0.000604686318972033</v>
-      </c>
-      <c r="J23" s="20" t="n">
+      <c r="I23" s="23" t="n">
+        <f aca="false">H23/$P23/10</f>
+        <v>0.0604686318972033</v>
+      </c>
+      <c r="J23" s="22" t="n">
         <f aca="false">L23*$J$37/100</f>
         <v>30.6</v>
       </c>
-      <c r="K23" s="21" t="n">
-        <f aca="false">J23/$P23/1000</f>
-        <v>0.000925170068027211</v>
-      </c>
-      <c r="L23" s="20" t="n">
+      <c r="K23" s="23" t="n">
+        <f aca="false">J23/$P23/10</f>
+        <v>0.0925170068027211</v>
+      </c>
+      <c r="L23" s="22" t="n">
         <v>180</v>
       </c>
-      <c r="M23" s="20" t="n">
+      <c r="M23" s="22" t="n">
         <f aca="false">O23*$M$37/100</f>
         <v>68</v>
       </c>
-      <c r="N23" s="22" t="n">
-        <f aca="false">M23/$P23/1000</f>
-        <v>0.00205593348450491</v>
-      </c>
-      <c r="O23" s="20" t="n">
+      <c r="N23" s="23" t="n">
+        <f aca="false">M23/$P23/10</f>
+        <v>0.205593348450491</v>
+      </c>
+      <c r="O23" s="22" t="n">
         <v>500</v>
       </c>
-      <c r="P23" s="23" t="n">
+      <c r="P23" s="25" t="n">
         <v>33.075</v>
       </c>
-      <c r="Q23" s="23" t="n">
+      <c r="Q23" s="25" t="n">
         <f aca="false">100*P23/$P$36</f>
         <v>0.227169796080852</v>
       </c>
-      <c r="R23" s="20" t="n">
+      <c r="R23" s="22" t="n">
         <f aca="false">H23+F23+B23+D23+J23+M23</f>
         <v>165.6</v>
       </c>
-      <c r="S23" s="23" t="n">
+      <c r="S23" s="25" t="n">
         <f aca="false">R23/P23</f>
         <v>5.00680272108844</v>
       </c>
-      <c r="U23" s="23" t="n">
+      <c r="U23" s="25" t="n">
         <f aca="false">-T23+($Q$45 + $Q$46)*1000*Q23/100</f>
         <v>100.922680776675</v>
       </c>
-      <c r="V23" s="23" t="n">
+      <c r="V23" s="25" t="n">
         <f aca="false">U23/P23/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W23" s="23" t="n">
+      <c r="W23" s="25" t="n">
         <f aca="false">ROUND(U23/P23 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y23" s="23" t="n">
+      <c r="Y23" s="25" t="n">
         <f aca="false">-Q23*($Q$47)*10</f>
         <v>-54.5207510594045</v>
       </c>
-      <c r="Z23" s="23" t="n">
+      <c r="Z23" s="25" t="n">
         <f aca="false">Y23/P23/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC23" s="20" t="n">
+      <c r="AC23" s="22" t="n">
         <v>43</v>
       </c>
-      <c r="AH23" s="20" t="s">
+      <c r="AH23" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="AI23" s="20" t="n">
+      <c r="AI23" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" s="20" t="n">
+      <c r="AJ23" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="AK23" s="20" t="n">
+      <c r="AK23" s="22" t="n">
         <f aca="false">AI23+AJ23/100</f>
         <v>0.18</v>
       </c>
-      <c r="AL23" s="20" t="n">
+      <c r="AL23" s="22" t="n">
         <f aca="false">AK23*1000</f>
         <v>180</v>
       </c>
-      <c r="AO23" s="24" t="s">
+      <c r="AO23" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="AP23" s="20" t="n">
+      <c r="AP23" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AQ23" s="20" t="n">
+      <c r="AQ23" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="AR23" s="24" t="n">
+      <c r="AR23" s="26" t="n">
         <f aca="false">AP23+AQ23/10</f>
         <v>0.5</v>
       </c>
-      <c r="AS23" s="24" t="n">
+      <c r="AS23" s="26" t="n">
         <f aca="false">1000*AR23</f>
         <v>500</v>
       </c>
-      <c r="AU23" s="24" t="s">
+      <c r="AU23" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="AV23" s="20" t="n">
+      <c r="AV23" s="22" t="n">
         <v>0.18</v>
       </c>
-      <c r="AW23" s="20" t="n">
+      <c r="AW23" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="AX23" s="20" t="n">
+      <c r="AX23" s="22" t="n">
         <v>0.24</v>
       </c>
-      <c r="AY23" s="20" t="n">
+      <c r="AY23" s="22" t="n">
         <v>1.67</v>
       </c>
-      <c r="AZ23" s="20" t="n">
+      <c r="AZ23" s="22" t="n">
         <v>2.26</v>
       </c>
-      <c r="BA23" s="24" t="s">
+      <c r="BA23" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="BC23" s="24" t="n">
+      <c r="BC23" s="26" t="n">
         <f aca="false">AV23*1000</f>
         <v>180</v>
       </c>
-      <c r="BE23" s="20" t="s">
+      <c r="BE23" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="BF23" s="20" t="n">
+      <c r="BF23" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="BG23" s="20" t="n">
+      <c r="BG23" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="BH23" s="20" t="s">
+      <c r="BH23" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI23" s="20" t="n">
+      <c r="BI23" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="BK23" s="20" t="s">
+      <c r="BK23" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="BL23" s="20" t="n">
+      <c r="BL23" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="BM23" s="20" t="s">
+      <c r="BM23" s="22" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="24" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="24" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="22" t="n">
         <v>41</v>
       </c>
-      <c r="C24" s="21" t="n">
-        <f aca="false">B24/$P24/1000</f>
-        <v>0.000759034360189574</v>
-      </c>
-      <c r="D24" s="20" t="n">
+      <c r="C24" s="23" t="n">
+        <f aca="false">B24/$P24/10</f>
+        <v>0.0759034360189574</v>
+      </c>
+      <c r="D24" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="E24" s="22" t="n">
-        <f aca="false">D24/$P24/1000</f>
-        <v>0.000444312796208531</v>
-      </c>
-      <c r="F24" s="22" t="n">
+      <c r="E24" s="23" t="n">
+        <f aca="false">D24/$P24/10</f>
+        <v>0.0444312796208531</v>
+      </c>
+      <c r="F24" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="G24" s="21" t="n">
-        <f aca="false">F24/$P24/1000</f>
-        <v>1.85130331753555E-006</v>
-      </c>
-      <c r="H24" s="22" t="n">
+      <c r="G24" s="23" t="n">
+        <f aca="false">F24/$P24/10</f>
+        <v>0.000185130331753555</v>
+      </c>
+      <c r="H24" s="24" t="n">
         <v>31</v>
       </c>
-      <c r="I24" s="21" t="n">
-        <f aca="false">H24/$P24/1000</f>
-        <v>0.000573904028436019</v>
-      </c>
-      <c r="J24" s="20" t="n">
+      <c r="I24" s="23" t="n">
+        <f aca="false">H24/$P24/10</f>
+        <v>0.0573904028436019</v>
+      </c>
+      <c r="J24" s="22" t="n">
         <f aca="false">L24*$J$37/100</f>
         <v>23.8</v>
       </c>
-      <c r="K24" s="21" t="n">
-        <f aca="false">J24/$P24/1000</f>
-        <v>0.00044061018957346</v>
-      </c>
-      <c r="L24" s="20" t="n">
+      <c r="K24" s="23" t="n">
+        <f aca="false">J24/$P24/10</f>
+        <v>0.044061018957346</v>
+      </c>
+      <c r="L24" s="22" t="n">
         <v>140</v>
       </c>
-      <c r="M24" s="20" t="n">
+      <c r="M24" s="22" t="n">
         <f aca="false">O24*$M$37/100</f>
         <v>108.8</v>
       </c>
-      <c r="N24" s="22" t="n">
-        <f aca="false">M24/$P24/1000</f>
-        <v>0.00201421800947867</v>
-      </c>
-      <c r="O24" s="20" t="n">
+      <c r="N24" s="23" t="n">
+        <f aca="false">M24/$P24/10</f>
+        <v>0.201421800947867</v>
+      </c>
+      <c r="O24" s="22" t="n">
         <v>800</v>
       </c>
-      <c r="P24" s="23" t="n">
+      <c r="P24" s="25" t="n">
         <v>54.016</v>
       </c>
-      <c r="Q24" s="23" t="n">
+      <c r="Q24" s="25" t="n">
         <f aca="false">100*P24/$P$36</f>
         <v>0.370999356163366</v>
       </c>
-      <c r="R24" s="20" t="n">
+      <c r="R24" s="22" t="n">
         <f aca="false">H24+F24+B24+D24+J24+M24</f>
         <v>228.7</v>
       </c>
-      <c r="S24" s="23" t="n">
+      <c r="S24" s="25" t="n">
         <f aca="false">R24/P24</f>
         <v>4.23393068720379</v>
       </c>
-      <c r="U24" s="23" t="n">
+      <c r="U24" s="25" t="n">
         <f aca="false">-T24+($Q$45 + $Q$46)*1000*Q24/100</f>
         <v>164.820544968493</v>
       </c>
-      <c r="V24" s="23" t="n">
+      <c r="V24" s="25" t="n">
         <f aca="false">U24/P24/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W24" s="23" t="n">
+      <c r="W24" s="25" t="n">
         <f aca="false">ROUND(U24/P24 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y24" s="23" t="n">
+      <c r="Y24" s="25" t="n">
         <f aca="false">-Q24*($Q$47)*10</f>
         <v>-89.0398454792077</v>
       </c>
-      <c r="Z24" s="23" t="n">
+      <c r="Z24" s="25" t="n">
         <f aca="false">Y24/P24/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC24" s="20" t="n">
+      <c r="AC24" s="22" t="n">
         <v>84.3</v>
       </c>
-      <c r="AH24" s="20" t="s">
+      <c r="AH24" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="AI24" s="20" t="n">
+      <c r="AI24" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" s="20" t="n">
+      <c r="AJ24" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="AK24" s="20" t="n">
+      <c r="AK24" s="22" t="n">
         <f aca="false">AI24+AJ24/100</f>
         <v>0.14</v>
       </c>
-      <c r="AL24" s="20" t="n">
+      <c r="AL24" s="22" t="n">
         <f aca="false">AK24*1000</f>
         <v>140</v>
       </c>
-      <c r="AO24" s="24" t="s">
+      <c r="AO24" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="AP24" s="20" t="n">
+      <c r="AP24" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AQ24" s="20" t="n">
+      <c r="AQ24" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="AR24" s="24" t="n">
+      <c r="AR24" s="26" t="n">
         <f aca="false">AP24+AQ24/10</f>
         <v>0.8</v>
       </c>
-      <c r="AS24" s="24" t="n">
+      <c r="AS24" s="26" t="n">
         <f aca="false">1000*AR24</f>
         <v>800</v>
       </c>
-      <c r="AU24" s="24" t="s">
+      <c r="AU24" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="AV24" s="20" t="n">
+      <c r="AV24" s="22" t="n">
         <v>0.14</v>
       </c>
-      <c r="AW24" s="20" t="n">
+      <c r="AW24" s="22" t="n">
         <v>0.31</v>
       </c>
-      <c r="AX24" s="20" t="n">
+      <c r="AX24" s="22" t="n">
         <v>0.42</v>
       </c>
-      <c r="AY24" s="20" t="n">
+      <c r="AY24" s="22" t="n">
         <v>0.74</v>
       </c>
-      <c r="AZ24" s="20" t="n">
+      <c r="AZ24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="BA24" s="24" t="s">
+      <c r="BA24" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="BC24" s="24" t="n">
+      <c r="BC24" s="26" t="n">
         <f aca="false">AV24*1000</f>
         <v>140</v>
       </c>
-      <c r="BE24" s="20" t="s">
+      <c r="BE24" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="BF24" s="20" t="n">
+      <c r="BF24" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="BG24" s="20" t="n">
+      <c r="BG24" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="BH24" s="20" t="s">
+      <c r="BH24" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI24" s="20" t="n">
+      <c r="BI24" s="22" t="n">
         <v>41</v>
       </c>
-      <c r="BK24" s="20" t="s">
+      <c r="BK24" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="BL24" s="20" t="n">
+      <c r="BL24" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="BM24" s="20" t="s">
+      <c r="BM24" s="22" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="25" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="25" t="s">
+    <row r="25" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="C25" s="21" t="n">
-        <f aca="false">B25/$P25/1000</f>
-        <v>0.000198137507430157</v>
-      </c>
-      <c r="D25" s="20" t="n">
+      <c r="C25" s="23" t="n">
+        <f aca="false">B25/$P25/10</f>
+        <v>0.0198137507430157</v>
+      </c>
+      <c r="D25" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="E25" s="22" t="n">
-        <f aca="false">D25/$P25/1000</f>
-        <v>0.000634040023776501</v>
-      </c>
-      <c r="F25" s="26" t="n">
+      <c r="E25" s="23" t="n">
+        <f aca="false">D25/$P25/10</f>
+        <v>0.0634040023776501</v>
+      </c>
+      <c r="F25" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="21" t="n">
-        <f aca="false">F25/$P25/1000</f>
+      <c r="G25" s="23" t="n">
+        <f aca="false">F25/$P25/10</f>
         <v>0</v>
       </c>
-      <c r="H25" s="26" t="n">
+      <c r="H25" s="28" t="n">
         <v>208</v>
       </c>
-      <c r="I25" s="21" t="n">
-        <f aca="false">H25/$P25/1000</f>
-        <v>0.00412126015454726</v>
-      </c>
-      <c r="J25" s="20" t="n">
+      <c r="I25" s="23" t="n">
+        <f aca="false">H25/$P25/10</f>
+        <v>0.412126015454726</v>
+      </c>
+      <c r="J25" s="22" t="n">
         <f aca="false">L25*$J$37/100</f>
         <v>35.7</v>
       </c>
-      <c r="K25" s="21" t="n">
-        <f aca="false">J25/$P25/1000</f>
-        <v>0.000707350901525659</v>
-      </c>
-      <c r="L25" s="20" t="n">
+      <c r="K25" s="23" t="n">
+        <f aca="false">J25/$P25/10</f>
+        <v>0.0707350901525659</v>
+      </c>
+      <c r="L25" s="22" t="n">
         <v>210</v>
       </c>
-      <c r="M25" s="20" t="n">
+      <c r="M25" s="22" t="n">
         <f aca="false">O25*$M$37/100</f>
         <v>244.8</v>
       </c>
-      <c r="N25" s="22" t="n">
-        <f aca="false">M25/$P25/1000</f>
-        <v>0.00485040618189023</v>
-      </c>
-      <c r="O25" s="20" t="n">
+      <c r="N25" s="23" t="n">
+        <f aca="false">M25/$P25/10</f>
+        <v>0.485040618189023</v>
+      </c>
+      <c r="O25" s="22" t="n">
         <v>1800</v>
       </c>
-      <c r="P25" s="23" t="n">
+      <c r="P25" s="25" t="n">
         <v>50.47</v>
       </c>
-      <c r="Q25" s="23" t="n">
+      <c r="Q25" s="25" t="n">
         <f aca="false">100*P25/$P$36</f>
         <v>0.346644281427078</v>
       </c>
-      <c r="R25" s="20" t="n">
+      <c r="R25" s="22" t="n">
         <f aca="false">H25+F25+B25+D25+J25+M25</f>
         <v>530.5</v>
       </c>
-      <c r="S25" s="23" t="n">
+      <c r="S25" s="25" t="n">
         <f aca="false">R25/P25</f>
         <v>10.5111947691698</v>
       </c>
-      <c r="U25" s="23" t="n">
+      <c r="U25" s="25" t="n">
         <f aca="false">-T25+($Q$45 + $Q$46)*1000*Q25/100</f>
         <v>154.000535111075</v>
       </c>
-      <c r="V25" s="23" t="n">
+      <c r="V25" s="25" t="n">
         <f aca="false">U25/P25/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W25" s="23" t="n">
+      <c r="W25" s="25" t="n">
         <f aca="false">ROUND(U25/P25 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y25" s="23" t="n">
+      <c r="Y25" s="25" t="n">
         <f aca="false">-Q25*($Q$47)*10</f>
         <v>-83.1946275424988</v>
       </c>
-      <c r="Z25" s="23" t="n">
+      <c r="Z25" s="25" t="n">
         <f aca="false">Y25/P25/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC25" s="20" t="n">
+      <c r="AC25" s="22" t="n">
         <v>89.5</v>
       </c>
-      <c r="AH25" s="20" t="s">
+      <c r="AH25" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="AI25" s="20" t="n">
+      <c r="AI25" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" s="20" t="n">
+      <c r="AJ25" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="AK25" s="20" t="n">
+      <c r="AK25" s="22" t="n">
         <f aca="false">AI25+AJ25/100</f>
         <v>0.21</v>
       </c>
-      <c r="AL25" s="20" t="n">
+      <c r="AL25" s="22" t="n">
         <f aca="false">AK25*1000</f>
         <v>210</v>
       </c>
-      <c r="AO25" s="24" t="s">
+      <c r="AO25" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="AP25" s="20" t="n">
+      <c r="AP25" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ25" s="20" t="n">
+      <c r="AQ25" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="AR25" s="24" t="n">
+      <c r="AR25" s="26" t="n">
         <f aca="false">AP25+AQ25/10</f>
         <v>1.8</v>
       </c>
-      <c r="AS25" s="24" t="n">
+      <c r="AS25" s="26" t="n">
         <f aca="false">1000*AR25</f>
         <v>1800</v>
       </c>
-      <c r="AU25" s="24" t="s">
+      <c r="AU25" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="AV25" s="20" t="n">
+      <c r="AV25" s="22" t="n">
         <v>0.21</v>
       </c>
-      <c r="AW25" s="20" t="n">
+      <c r="AW25" s="22" t="n">
         <v>0.46</v>
       </c>
-      <c r="AX25" s="20" t="n">
+      <c r="AX25" s="22" t="n">
         <v>0.31</v>
       </c>
-      <c r="AY25" s="20" t="n">
+      <c r="AY25" s="22" t="n">
         <v>1.48</v>
       </c>
-      <c r="AZ25" s="20" t="n">
+      <c r="AZ25" s="22" t="n">
         <v>2.01</v>
       </c>
-      <c r="BA25" s="24" t="s">
+      <c r="BA25" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="BC25" s="24" t="n">
+      <c r="BC25" s="26" t="n">
         <f aca="false">AV25*1000</f>
         <v>210</v>
       </c>
-      <c r="BE25" s="20" t="s">
+      <c r="BE25" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="BF25" s="20" t="s">
+      <c r="BF25" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="BG25" s="20" t="n">
+      <c r="BG25" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="BH25" s="20" t="s">
+      <c r="BH25" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI25" s="20" t="n">
+      <c r="BI25" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="BK25" s="20" t="s">
+      <c r="BK25" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="BL25" s="20" t="n">
+      <c r="BL25" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="BM25" s="20" t="s">
+      <c r="BM25" s="22" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="26" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+    <row r="26" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="21" t="n">
-        <f aca="false">B26/$P26/1000</f>
-        <v>0.000510538983298082</v>
-      </c>
-      <c r="D26" s="20" t="n">
+      <c r="C26" s="23" t="n">
+        <f aca="false">B26/$P26/10</f>
+        <v>0.0510538983298082</v>
+      </c>
+      <c r="D26" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="E26" s="22" t="n">
-        <f aca="false">D26/$P26/1000</f>
-        <v>0.000729341404711545</v>
-      </c>
-      <c r="F26" s="22" t="n">
+      <c r="E26" s="23" t="n">
+        <f aca="false">D26/$P26/10</f>
+        <v>0.0729341404711545</v>
+      </c>
+      <c r="F26" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="21" t="n">
-        <f aca="false">F26/$P26/1000</f>
+      <c r="G26" s="23" t="n">
+        <f aca="false">F26/$P26/10</f>
         <v>0</v>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="H26" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="I26" s="21" t="n">
-        <f aca="false">H26/$P26/1000</f>
-        <v>0.000656407264240391</v>
-      </c>
-      <c r="J26" s="20" t="n">
+      <c r="I26" s="23" t="n">
+        <f aca="false">H26/$P26/10</f>
+        <v>0.0656407264240391</v>
+      </c>
+      <c r="J26" s="22" t="n">
         <f aca="false">L26*$J$37/100</f>
         <v>45.9</v>
       </c>
-      <c r="K26" s="21" t="n">
-        <f aca="false">J26/$P26/1000</f>
-        <v>0.00334767704762599</v>
-      </c>
-      <c r="L26" s="20" t="n">
+      <c r="K26" s="23" t="n">
+        <f aca="false">J26/$P26/10</f>
+        <v>0.334767704762599</v>
+      </c>
+      <c r="L26" s="22" t="n">
         <v>270</v>
       </c>
-      <c r="M26" s="20" t="n">
+      <c r="M26" s="22" t="n">
         <f aca="false">O26*$M$37/100</f>
         <v>122.4</v>
       </c>
-      <c r="N26" s="22" t="n">
-        <f aca="false">M26/$P26/1000</f>
-        <v>0.00892713879366932</v>
-      </c>
-      <c r="O26" s="20" t="n">
+      <c r="N26" s="23" t="n">
+        <f aca="false">M26/$P26/10</f>
+        <v>0.892713879366932</v>
+      </c>
+      <c r="O26" s="22" t="n">
         <v>900</v>
       </c>
-      <c r="P26" s="23" t="n">
+      <c r="P26" s="25" t="n">
         <v>13.711</v>
       </c>
-      <c r="Q26" s="23" t="n">
+      <c r="Q26" s="25" t="n">
         <f aca="false">100*P26/$P$36</f>
         <v>0.0941715819822998</v>
       </c>
-      <c r="R26" s="20" t="n">
+      <c r="R26" s="22" t="n">
         <f aca="false">H26+F26+B26+D26+J26+M26</f>
         <v>194.3</v>
       </c>
-      <c r="S26" s="23" t="n">
+      <c r="S26" s="25" t="n">
         <f aca="false">R26/P26</f>
         <v>14.1711034935453</v>
       </c>
-      <c r="U26" s="23" t="n">
+      <c r="U26" s="25" t="n">
         <f aca="false">-T26+($Q$45 + $Q$46)*1000*Q26/100</f>
         <v>41.8367611830385</v>
       </c>
-      <c r="V26" s="23" t="n">
+      <c r="V26" s="25" t="n">
         <f aca="false">U26/P26/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W26" s="23" t="n">
+      <c r="W26" s="25" t="n">
         <f aca="false">ROUND(U26/P26 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y26" s="23" t="n">
+      <c r="Y26" s="25" t="n">
         <f aca="false">-Q26*($Q$47)*10</f>
         <v>-22.6011796757519</v>
       </c>
-      <c r="Z26" s="23" t="n">
+      <c r="Z26" s="25" t="n">
         <f aca="false">Y26/P26/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC26" s="20" t="n">
+      <c r="AC26" s="22" t="n">
         <v>24.6</v>
       </c>
-      <c r="AH26" s="20" t="s">
+      <c r="AH26" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="AI26" s="20" t="n">
+      <c r="AI26" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ26" s="20" t="n">
+      <c r="AJ26" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="AK26" s="20" t="n">
+      <c r="AK26" s="22" t="n">
         <f aca="false">AI26+AJ26/100</f>
         <v>0.27</v>
       </c>
-      <c r="AL26" s="20" t="n">
+      <c r="AL26" s="22" t="n">
         <f aca="false">AK26*1000</f>
         <v>270</v>
       </c>
-      <c r="AO26" s="24" t="s">
+      <c r="AO26" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="AP26" s="20" t="n">
+      <c r="AP26" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AQ26" s="20" t="n">
+      <c r="AQ26" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="AR26" s="24" t="n">
+      <c r="AR26" s="26" t="n">
         <f aca="false">AP26+AQ26/10</f>
         <v>0.9</v>
       </c>
-      <c r="AS26" s="24" t="n">
+      <c r="AS26" s="26" t="n">
         <f aca="false">1000*AR26</f>
         <v>900</v>
       </c>
-      <c r="AU26" s="24" t="s">
+      <c r="AU26" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="AV26" s="20" t="n">
+      <c r="AV26" s="22" t="n">
         <v>0.27</v>
       </c>
-      <c r="AW26" s="20" t="n">
+      <c r="AW26" s="22" t="n">
         <v>0.61</v>
       </c>
-      <c r="AX26" s="20" t="n">
+      <c r="AX26" s="22" t="n">
         <v>0.11</v>
       </c>
-      <c r="AY26" s="20" t="n">
+      <c r="AY26" s="22" t="n">
         <v>5.6</v>
       </c>
-      <c r="AZ26" s="20" t="n">
+      <c r="AZ26" s="22" t="n">
         <v>7.59</v>
       </c>
-      <c r="BA26" s="24" t="s">
+      <c r="BA26" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="BC26" s="24" t="n">
+      <c r="BC26" s="26" t="n">
         <f aca="false">AV26*1000</f>
         <v>270</v>
       </c>
-      <c r="BE26" s="20" t="s">
+      <c r="BE26" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="BF26" s="20" t="s">
+      <c r="BF26" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="BG26" s="20" t="n">
+      <c r="BG26" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="BH26" s="20" t="s">
+      <c r="BH26" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI26" s="20" t="n">
+      <c r="BI26" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="BK26" s="20" t="s">
+      <c r="BK26" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="BL26" s="20" t="n">
+      <c r="BL26" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="BM26" s="20" t="s">
+      <c r="BM26" s="22" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="27" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="s">
+    <row r="27" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="22" t="n">
         <v>333</v>
       </c>
-      <c r="C27" s="21" t="n">
-        <f aca="false">B27/$P27/1000</f>
-        <v>0.000397775325029027</v>
-      </c>
-      <c r="D27" s="20" t="n">
+      <c r="C27" s="23" t="n">
+        <f aca="false">B27/$P27/10</f>
+        <v>0.0397775325029027</v>
+      </c>
+      <c r="D27" s="22" t="n">
         <v>652</v>
       </c>
-      <c r="E27" s="22" t="n">
-        <f aca="false">D27/$P27/1000</f>
-        <v>0.000778827363119896</v>
-      </c>
-      <c r="F27" s="26" t="n">
+      <c r="E27" s="23" t="n">
+        <f aca="false">D27/$P27/10</f>
+        <v>0.0778827363119896</v>
+      </c>
+      <c r="F27" s="28" t="n">
         <v>1961</v>
       </c>
-      <c r="G27" s="21" t="n">
-        <f aca="false">F27/$P27/1000</f>
-        <v>0.0023424546918376</v>
-      </c>
-      <c r="H27" s="26" t="n">
+      <c r="G27" s="23" t="n">
+        <f aca="false">F27/$P27/10</f>
+        <v>0.23424546918376</v>
+      </c>
+      <c r="H27" s="28" t="n">
         <v>913</v>
       </c>
-      <c r="I27" s="21" t="n">
-        <f aca="false">H27/$P27/1000</f>
-        <v>0.00109059721246697</v>
-      </c>
-      <c r="J27" s="20" t="n">
+      <c r="I27" s="23" t="n">
+        <f aca="false">H27/$P27/10</f>
+        <v>0.109059721246697</v>
+      </c>
+      <c r="J27" s="22" t="n">
         <f aca="false">L27*$J$37/100</f>
         <v>336.6</v>
       </c>
-      <c r="K27" s="21" t="n">
-        <f aca="false">J27/$P27/1000</f>
-        <v>0.000402075598813124</v>
-      </c>
-      <c r="L27" s="20" t="n">
+      <c r="K27" s="23" t="n">
+        <f aca="false">J27/$P27/10</f>
+        <v>0.0402075598813125</v>
+      </c>
+      <c r="L27" s="22" t="n">
         <v>1980</v>
       </c>
-      <c r="M27" s="20" t="n">
+      <c r="M27" s="22" t="n">
         <f aca="false">O27*$M$37/100</f>
         <v>1496</v>
       </c>
-      <c r="N27" s="22" t="n">
-        <f aca="false">M27/$P27/1000</f>
-        <v>0.00178700266139166</v>
-      </c>
-      <c r="O27" s="20" t="n">
+      <c r="N27" s="23" t="n">
+        <f aca="false">M27/$P27/10</f>
+        <v>0.178700266139166</v>
+      </c>
+      <c r="O27" s="22" t="n">
         <v>11000</v>
       </c>
-      <c r="P27" s="23" t="n">
+      <c r="P27" s="25" t="n">
         <v>837.156</v>
       </c>
-      <c r="Q27" s="23" t="n">
+      <c r="Q27" s="25" t="n">
         <f aca="false">100*P27/$P$36</f>
         <v>5.74985813478041</v>
       </c>
-      <c r="R27" s="20" t="n">
+      <c r="R27" s="22" t="n">
         <f aca="false">H27+F27+B27+D27+J27+M27</f>
         <v>5691.6</v>
       </c>
-      <c r="S27" s="23" t="n">
+      <c r="S27" s="25" t="n">
         <f aca="false">R27/P27</f>
         <v>6.79873285265829</v>
       </c>
-      <c r="U27" s="23" t="n">
+      <c r="U27" s="25" t="n">
         <f aca="false">-T27+($Q$45 + $Q$46)*1000*Q27/100</f>
         <v>2554.43772481568</v>
       </c>
-      <c r="V27" s="23" t="n">
+      <c r="V27" s="25" t="n">
         <f aca="false">U27/P27/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W27" s="23" t="n">
+      <c r="W27" s="25" t="n">
         <f aca="false">ROUND(U27/P27 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y27" s="23" t="n">
+      <c r="Y27" s="25" t="n">
         <f aca="false">-Q27*($Q$47)*10</f>
         <v>-1379.9659523473</v>
       </c>
-      <c r="Z27" s="23" t="n">
+      <c r="Z27" s="25" t="n">
         <f aca="false">Y27/P27/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC27" s="20" t="n">
+      <c r="AC27" s="22" t="n">
         <v>1170.6</v>
       </c>
-      <c r="AH27" s="20" t="s">
+      <c r="AH27" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="AI27" s="20" t="n">
+      <c r="AI27" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AJ27" s="20" t="n">
+      <c r="AJ27" s="22" t="n">
         <v>98</v>
       </c>
-      <c r="AK27" s="20" t="n">
+      <c r="AK27" s="22" t="n">
         <f aca="false">AI27+AJ27/100</f>
         <v>1.98</v>
       </c>
-      <c r="AL27" s="20" t="n">
+      <c r="AL27" s="22" t="n">
         <f aca="false">AK27*1000</f>
         <v>1980</v>
       </c>
-      <c r="AO27" s="24" t="s">
+      <c r="AO27" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="AP27" s="20" t="n">
+      <c r="AP27" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="AQ27" s="20" t="n">
+      <c r="AQ27" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AR27" s="24" t="n">
+      <c r="AR27" s="26" t="n">
         <f aca="false">AP27+AQ27/10</f>
         <v>11</v>
       </c>
-      <c r="AS27" s="24" t="n">
+      <c r="AS27" s="26" t="n">
         <f aca="false">1000*AR27</f>
         <v>11000</v>
       </c>
-      <c r="AU27" s="24" t="s">
+      <c r="AU27" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="AV27" s="20" t="n">
+      <c r="AV27" s="22" t="n">
         <v>1.98</v>
       </c>
-      <c r="AW27" s="20" t="n">
+      <c r="AW27" s="22" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX27" s="20" t="n">
+      <c r="AX27" s="22" t="n">
         <v>6.06</v>
       </c>
-      <c r="AY27" s="20" t="n">
+      <c r="AY27" s="22" t="n">
         <v>0.73</v>
       </c>
-      <c r="AZ27" s="20" t="n">
+      <c r="AZ27" s="22" t="n">
         <v>0.99</v>
       </c>
-      <c r="BA27" s="24" t="s">
+      <c r="BA27" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="BC27" s="24" t="n">
+      <c r="BC27" s="26" t="n">
         <f aca="false">AV27*1000</f>
         <v>1980</v>
       </c>
-      <c r="BE27" s="20" t="s">
+      <c r="BE27" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="BF27" s="20" t="n">
+      <c r="BF27" s="22" t="n">
         <v>293</v>
       </c>
-      <c r="BG27" s="20" t="n">
+      <c r="BG27" s="22" t="n">
         <v>245</v>
       </c>
-      <c r="BH27" s="20" t="s">
+      <c r="BH27" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI27" s="20" t="n">
+      <c r="BI27" s="22" t="n">
         <v>333</v>
       </c>
-      <c r="BK27" s="20" t="s">
+      <c r="BK27" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="BL27" s="20" t="n">
+      <c r="BL27" s="22" t="n">
         <v>652</v>
       </c>
-      <c r="BM27" s="20" t="s">
+      <c r="BM27" s="22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="28" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="28" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="22" t="n">
         <v>497</v>
       </c>
-      <c r="C28" s="21" t="n">
-        <f aca="false">B28/$P28/1000</f>
-        <v>0.000907081624570414</v>
-      </c>
-      <c r="D28" s="20" t="n">
+      <c r="C28" s="23" t="n">
+        <f aca="false">B28/$P28/10</f>
+        <v>0.0907081624570414</v>
+      </c>
+      <c r="D28" s="22" t="n">
         <v>427</v>
       </c>
-      <c r="E28" s="22" t="n">
-        <f aca="false">D28/$P28/1000</f>
-        <v>0.000779323649278806</v>
-      </c>
-      <c r="F28" s="22" t="n">
+      <c r="E28" s="23" t="n">
+        <f aca="false">D28/$P28/10</f>
+        <v>0.0779323649278806</v>
+      </c>
+      <c r="F28" s="24" t="n">
         <v>63</v>
       </c>
-      <c r="G28" s="21" t="n">
-        <f aca="false">F28/$P28/1000</f>
-        <v>0.000114982177762447</v>
-      </c>
-      <c r="H28" s="22" t="n">
+      <c r="G28" s="23" t="n">
+        <f aca="false">F28/$P28/10</f>
+        <v>0.0114982177762447</v>
+      </c>
+      <c r="H28" s="24" t="n">
         <v>560</v>
       </c>
-      <c r="I28" s="21" t="n">
-        <f aca="false">H28/$P28/1000</f>
-        <v>0.00102206380233286</v>
-      </c>
-      <c r="J28" s="20" t="n">
+      <c r="I28" s="23" t="n">
+        <f aca="false">H28/$P28/10</f>
+        <v>0.102206380233286</v>
+      </c>
+      <c r="J28" s="22" t="n">
         <f aca="false">L28*$J$37/100</f>
         <v>202.3</v>
       </c>
-      <c r="K28" s="21" t="n">
-        <f aca="false">J28/$P28/1000</f>
-        <v>0.000369220548592746</v>
-      </c>
-      <c r="L28" s="20" t="n">
+      <c r="K28" s="23" t="n">
+        <f aca="false">J28/$P28/10</f>
+        <v>0.0369220548592746</v>
+      </c>
+      <c r="L28" s="22" t="n">
         <v>1190</v>
       </c>
-      <c r="M28" s="20" t="n">
+      <c r="M28" s="22" t="n">
         <f aca="false">O28*$M$37/100</f>
         <v>1088</v>
       </c>
-      <c r="N28" s="22" t="n">
-        <f aca="false">M28/$P28/1000</f>
-        <v>0.00198572395881813</v>
-      </c>
-      <c r="O28" s="20" t="n">
+      <c r="N28" s="23" t="n">
+        <f aca="false">M28/$P28/10</f>
+        <v>0.198572395881813</v>
+      </c>
+      <c r="O28" s="22" t="n">
         <v>8000</v>
       </c>
-      <c r="P28" s="23" t="n">
+      <c r="P28" s="25" t="n">
         <v>547.911</v>
       </c>
-      <c r="Q28" s="23" t="n">
+      <c r="Q28" s="25" t="n">
         <f aca="false">100*P28/$P$36</f>
         <v>3.76322993621937</v>
       </c>
-      <c r="R28" s="20" t="n">
+      <c r="R28" s="22" t="n">
         <f aca="false">H28+F28+B28+D28+J28+M28</f>
         <v>2837.3</v>
       </c>
-      <c r="S28" s="23" t="n">
+      <c r="S28" s="25" t="n">
         <f aca="false">R28/P28</f>
         <v>5.1783957613554</v>
       </c>
-      <c r="U28" s="23" t="n">
+      <c r="U28" s="25" t="n">
         <f aca="false">-T28+($Q$45 + $Q$46)*1000*Q28/100</f>
         <v>1671.85629469476</v>
       </c>
-      <c r="V28" s="23" t="n">
+      <c r="V28" s="25" t="n">
         <f aca="false">U28/P28/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W28" s="23" t="n">
+      <c r="W28" s="25" t="n">
         <f aca="false">ROUND(U28/P28 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y28" s="23" t="n">
+      <c r="Y28" s="25" t="n">
         <f aca="false">-Q28*($Q$47)*10</f>
         <v>-903.17518469265</v>
       </c>
-      <c r="Z28" s="23" t="n">
+      <c r="Z28" s="25" t="n">
         <f aca="false">Y28/P28/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC28" s="20" t="n">
+      <c r="AC28" s="22" t="n">
         <v>922.9</v>
       </c>
-      <c r="AH28" s="20" t="s">
+      <c r="AH28" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="AI28" s="20" t="n">
+      <c r="AI28" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AJ28" s="20" t="n">
+      <c r="AJ28" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="AK28" s="20" t="n">
+      <c r="AK28" s="22" t="n">
         <f aca="false">AI28+AJ28/100</f>
         <v>1.19</v>
       </c>
-      <c r="AL28" s="20" t="n">
+      <c r="AL28" s="22" t="n">
         <f aca="false">AK28*1000</f>
         <v>1190</v>
       </c>
-      <c r="AO28" s="24" t="s">
+      <c r="AO28" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="AP28" s="20" t="n">
+      <c r="AP28" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="AQ28" s="20" t="n">
+      <c r="AQ28" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AR28" s="24" t="n">
+      <c r="AR28" s="26" t="n">
         <f aca="false">AP28+AQ28/10</f>
         <v>8</v>
       </c>
-      <c r="AS28" s="24" t="n">
+      <c r="AS28" s="26" t="n">
         <f aca="false">1000*AR28</f>
         <v>8000</v>
       </c>
-      <c r="AU28" s="24" t="s">
+      <c r="AU28" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="AV28" s="20" t="n">
+      <c r="AV28" s="22" t="n">
         <v>1.19</v>
       </c>
-      <c r="AW28" s="20" t="n">
+      <c r="AW28" s="22" t="n">
         <v>2.65</v>
       </c>
-      <c r="AX28" s="20" t="n">
+      <c r="AX28" s="22" t="n">
         <v>4.77</v>
       </c>
-      <c r="AY28" s="20" t="n">
+      <c r="AY28" s="22" t="n">
         <v>0.56</v>
       </c>
-      <c r="AZ28" s="20" t="n">
+      <c r="AZ28" s="22" t="n">
         <v>0.76</v>
       </c>
-      <c r="BA28" s="24" t="s">
+      <c r="BA28" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="BC28" s="24" t="n">
+      <c r="BC28" s="26" t="n">
         <f aca="false">AV28*1000</f>
         <v>1190</v>
       </c>
-      <c r="BE28" s="20" t="s">
+      <c r="BE28" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="BF28" s="20" t="n">
+      <c r="BF28" s="22" t="n">
         <v>192</v>
       </c>
-      <c r="BG28" s="20" t="n">
+      <c r="BG28" s="22" t="n">
         <v>365</v>
       </c>
-      <c r="BH28" s="20" t="s">
+      <c r="BH28" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI28" s="20" t="n">
+      <c r="BI28" s="22" t="n">
         <v>497</v>
       </c>
-      <c r="BK28" s="20" t="s">
+      <c r="BK28" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="BL28" s="20" t="n">
+      <c r="BL28" s="22" t="n">
         <v>427</v>
       </c>
-      <c r="BM28" s="20" t="s">
+      <c r="BM28" s="22" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="29" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25" t="s">
+    <row r="29" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="22" t="n">
         <v>137</v>
       </c>
-      <c r="C29" s="21" t="n">
-        <f aca="false">B29/$P29/1000</f>
-        <v>0.000646607669616519</v>
-      </c>
-      <c r="D29" s="20" t="n">
+      <c r="C29" s="23" t="n">
+        <f aca="false">B29/$P29/10</f>
+        <v>0.0646607669616519</v>
+      </c>
+      <c r="D29" s="22" t="n">
         <v>84</v>
       </c>
-      <c r="E29" s="22" t="n">
-        <f aca="false">D29/$P29/1000</f>
-        <v>0.00039646017699115</v>
-      </c>
-      <c r="F29" s="26" t="n">
+      <c r="E29" s="23" t="n">
+        <f aca="false">D29/$P29/10</f>
+        <v>0.039646017699115</v>
+      </c>
+      <c r="F29" s="28" t="n">
         <v>24.9</v>
       </c>
-      <c r="G29" s="21" t="n">
-        <f aca="false">F29/$P29/1000</f>
-        <v>0.000117522123893805</v>
-      </c>
-      <c r="H29" s="26" t="n">
+      <c r="G29" s="23" t="n">
+        <f aca="false">F29/$P29/10</f>
+        <v>0.0117522123893805</v>
+      </c>
+      <c r="H29" s="28" t="n">
         <v>330</v>
       </c>
-      <c r="I29" s="21" t="n">
-        <f aca="false">H29/$P29/1000</f>
-        <v>0.00155752212389381</v>
-      </c>
-      <c r="J29" s="20" t="n">
+      <c r="I29" s="23" t="n">
+        <f aca="false">H29/$P29/10</f>
+        <v>0.155752212389381</v>
+      </c>
+      <c r="J29" s="22" t="n">
         <f aca="false">L29*$J$37/100</f>
         <v>331.5</v>
       </c>
-      <c r="K29" s="21" t="n">
-        <f aca="false">J29/$P29/1000</f>
-        <v>0.0015646017699115</v>
-      </c>
-      <c r="L29" s="20" t="n">
+      <c r="K29" s="23" t="n">
+        <f aca="false">J29/$P29/10</f>
+        <v>0.15646017699115</v>
+      </c>
+      <c r="L29" s="22" t="n">
         <v>1950</v>
       </c>
-      <c r="M29" s="20" t="n">
+      <c r="M29" s="22" t="n">
         <f aca="false">O29*$M$37/100</f>
         <v>870.4</v>
       </c>
-      <c r="N29" s="22" t="n">
-        <f aca="false">M29/$P29/1000</f>
-        <v>0.00410808259587021</v>
-      </c>
-      <c r="O29" s="20" t="n">
+      <c r="N29" s="23" t="n">
+        <f aca="false">M29/$P29/10</f>
+        <v>0.410808259587021</v>
+      </c>
+      <c r="O29" s="22" t="n">
         <v>6400</v>
       </c>
-      <c r="P29" s="23" t="n">
+      <c r="P29" s="25" t="n">
         <v>211.875</v>
       </c>
-      <c r="Q29" s="23" t="n">
+      <c r="Q29" s="25" t="n">
         <f aca="false">100*P29/$P$36</f>
         <v>1.45522601797825</v>
       </c>
-      <c r="R29" s="20" t="n">
+      <c r="R29" s="22" t="n">
         <f aca="false">H29+F29+B29+D29+J29+M29</f>
         <v>1777.8</v>
       </c>
-      <c r="S29" s="23" t="n">
+      <c r="S29" s="25" t="n">
         <f aca="false">R29/P29</f>
         <v>8.39079646017699</v>
       </c>
-      <c r="U29" s="23" t="n">
+      <c r="U29" s="25" t="n">
         <f aca="false">-T29+($Q$45 + $Q$46)*1000*Q29/100</f>
         <v>646.500165973035</v>
       </c>
-      <c r="V29" s="23" t="n">
+      <c r="V29" s="25" t="n">
         <f aca="false">U29/P29/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W29" s="23" t="n">
+      <c r="W29" s="25" t="n">
         <f aca="false">ROUND(U29/P29 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y29" s="23" t="n">
+      <c r="Y29" s="25" t="n">
         <f aca="false">-Q29*($Q$47)*10</f>
         <v>-349.25424431478</v>
       </c>
-      <c r="Z29" s="23" t="n">
+      <c r="Z29" s="25" t="n">
         <f aca="false">Y29/P29/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC29" s="20" t="n">
+      <c r="AC29" s="22" t="n">
         <v>306.8</v>
       </c>
-      <c r="AH29" s="20" t="s">
+      <c r="AH29" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="AI29" s="20" t="n">
+      <c r="AI29" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AJ29" s="20" t="n">
+      <c r="AJ29" s="22" t="n">
         <v>95</v>
       </c>
-      <c r="AK29" s="20" t="n">
+      <c r="AK29" s="22" t="n">
         <f aca="false">AI29+AJ29/100</f>
         <v>1.95</v>
       </c>
-      <c r="AL29" s="20" t="n">
+      <c r="AL29" s="22" t="n">
         <f aca="false">AK29*1000</f>
         <v>1950</v>
       </c>
-      <c r="AO29" s="24" t="s">
+      <c r="AO29" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="AP29" s="20" t="n">
+      <c r="AP29" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="AQ29" s="20" t="n">
+      <c r="AQ29" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="AR29" s="24" t="n">
+      <c r="AR29" s="26" t="n">
         <f aca="false">AP29+AQ29/10</f>
         <v>6.4</v>
       </c>
-      <c r="AS29" s="24" t="n">
+      <c r="AS29" s="26" t="n">
         <f aca="false">1000*AR29</f>
         <v>6400</v>
       </c>
-      <c r="AU29" s="24" t="s">
+      <c r="AU29" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="AV29" s="20" t="n">
+      <c r="AV29" s="22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AW29" s="20" t="n">
+      <c r="AW29" s="22" t="n">
         <v>4.33</v>
       </c>
-      <c r="AX29" s="20" t="n">
+      <c r="AX29" s="22" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY29" s="20" t="n">
+      <c r="AY29" s="22" t="n">
         <v>2.8</v>
       </c>
-      <c r="AZ29" s="20" t="n">
+      <c r="AZ29" s="22" t="n">
         <v>3.8</v>
       </c>
-      <c r="BA29" s="24" t="s">
+      <c r="BA29" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="BC29" s="24" t="n">
+      <c r="BC29" s="26" t="n">
         <f aca="false">AV29*1000</f>
         <v>1950</v>
       </c>
-      <c r="BE29" s="20" t="s">
+      <c r="BE29" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="BF29" s="20" t="n">
+      <c r="BF29" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="BG29" s="20" t="n">
+      <c r="BG29" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="BH29" s="20" t="s">
+      <c r="BH29" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI29" s="20" t="n">
+      <c r="BI29" s="22" t="n">
         <v>137</v>
       </c>
-      <c r="BK29" s="20" t="s">
+      <c r="BK29" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="BL29" s="20" t="n">
+      <c r="BL29" s="22" t="n">
         <v>84</v>
       </c>
-      <c r="BM29" s="20" t="s">
+      <c r="BM29" s="22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="22" t="n">
         <v>135</v>
       </c>
-      <c r="C30" s="21" t="n">
-        <f aca="false">B30/$P30/1000</f>
-        <v>0.000626997101880063</v>
-      </c>
-      <c r="D30" s="20" t="n">
+      <c r="C30" s="23" t="n">
+        <f aca="false">B30/$P30/10</f>
+        <v>0.0626997101880062</v>
+      </c>
+      <c r="D30" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="E30" s="22" t="n">
-        <f aca="false">D30/$P30/1000</f>
-        <v>0.000139332689306681</v>
-      </c>
-      <c r="F30" s="22" t="n">
+      <c r="E30" s="23" t="n">
+        <f aca="false">D30/$P30/10</f>
+        <v>0.0139332689306681</v>
+      </c>
+      <c r="F30" s="24" t="n">
         <v>1.9</v>
       </c>
-      <c r="G30" s="21" t="n">
-        <f aca="false">F30/$P30/1000</f>
-        <v>8.82440365608977E-006</v>
-      </c>
-      <c r="H30" s="22" t="n">
+      <c r="G30" s="23" t="n">
+        <f aca="false">F30/$P30/10</f>
+        <v>0.000882440365608977</v>
+      </c>
+      <c r="H30" s="24" t="n">
         <v>121</v>
       </c>
-      <c r="I30" s="21" t="n">
-        <f aca="false">H30/$P30/1000</f>
-        <v>0.000561975180203612</v>
-      </c>
-      <c r="J30" s="20" t="n">
+      <c r="I30" s="23" t="n">
+        <f aca="false">H30/$P30/10</f>
+        <v>0.0561975180203611</v>
+      </c>
+      <c r="J30" s="22" t="n">
         <f aca="false">L30*$J$37/100</f>
         <v>105.4</v>
       </c>
-      <c r="K30" s="21" t="n">
-        <f aca="false">J30/$P30/1000</f>
-        <v>0.000489522181764138</v>
-      </c>
-      <c r="L30" s="20" t="n">
+      <c r="K30" s="23" t="n">
+        <f aca="false">J30/$P30/10</f>
+        <v>0.0489522181764138</v>
+      </c>
+      <c r="L30" s="22" t="n">
         <v>620</v>
       </c>
-      <c r="M30" s="20" t="n">
+      <c r="M30" s="22" t="n">
         <f aca="false">O30*$M$37/100</f>
         <v>435.2</v>
       </c>
-      <c r="N30" s="22" t="n">
-        <f aca="false">M30/$P30/1000</f>
-        <v>0.00202125287954225</v>
-      </c>
-      <c r="O30" s="20" t="n">
+      <c r="N30" s="23" t="n">
+        <f aca="false">M30/$P30/10</f>
+        <v>0.202125287954225</v>
+      </c>
+      <c r="O30" s="22" t="n">
         <v>3200</v>
       </c>
-      <c r="P30" s="23" t="n">
+      <c r="P30" s="25" t="n">
         <v>215.312</v>
       </c>
-      <c r="Q30" s="23" t="n">
+      <c r="Q30" s="25" t="n">
         <f aca="false">100*P30/$P$36</f>
         <v>1.47883244546517</v>
       </c>
-      <c r="R30" s="20" t="n">
+      <c r="R30" s="22" t="n">
         <f aca="false">H30+F30+B30+D30+J30+M30</f>
         <v>828.5</v>
       </c>
-      <c r="S30" s="23" t="n">
+      <c r="S30" s="25" t="n">
         <f aca="false">R30/P30</f>
         <v>3.84790443635283</v>
       </c>
-      <c r="U30" s="23" t="n">
+      <c r="U30" s="25" t="n">
         <f aca="false">-T30+($Q$45 + $Q$46)*1000*Q30/100</f>
         <v>656.987581054801</v>
       </c>
-      <c r="V30" s="23" t="n">
+      <c r="V30" s="25" t="n">
         <f aca="false">U30/P30/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W30" s="23" t="n">
+      <c r="W30" s="25" t="n">
         <f aca="false">ROUND(U30/P30 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y30" s="23" t="n">
+      <c r="Y30" s="25" t="n">
         <f aca="false">-Q30*($Q$47)*10</f>
         <v>-354.919786911641</v>
       </c>
-      <c r="Z30" s="23" t="n">
+      <c r="Z30" s="25" t="n">
         <f aca="false">Y30/P30/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC30" s="20" t="n">
+      <c r="AC30" s="22" t="n">
         <v>380.1</v>
       </c>
-      <c r="AH30" s="20" t="s">
+      <c r="AH30" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="AI30" s="20" t="n">
+      <c r="AI30" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" s="20" t="n">
+      <c r="AJ30" s="22" t="n">
         <v>62</v>
       </c>
-      <c r="AK30" s="20" t="n">
+      <c r="AK30" s="22" t="n">
         <f aca="false">AI30+AJ30/100</f>
         <v>0.62</v>
       </c>
-      <c r="AL30" s="20" t="n">
+      <c r="AL30" s="22" t="n">
         <f aca="false">AK30*1000</f>
         <v>620</v>
       </c>
-      <c r="AO30" s="24" t="s">
+      <c r="AO30" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="AP30" s="20" t="n">
+      <c r="AP30" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="AQ30" s="20" t="n">
+      <c r="AQ30" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="AR30" s="24" t="n">
+      <c r="AR30" s="26" t="n">
         <f aca="false">AP30+AQ30/10</f>
         <v>3.2</v>
       </c>
-      <c r="AS30" s="24" t="n">
+      <c r="AS30" s="26" t="n">
         <f aca="false">1000*AR30</f>
         <v>3200</v>
       </c>
-      <c r="AU30" s="24" t="s">
+      <c r="AU30" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="AV30" s="20" t="n">
+      <c r="AV30" s="22" t="n">
         <v>0.62</v>
       </c>
-      <c r="AW30" s="20" t="n">
+      <c r="AW30" s="22" t="n">
         <v>1.37</v>
       </c>
-      <c r="AX30" s="20" t="n">
+      <c r="AX30" s="22" t="n">
         <v>2.03</v>
       </c>
-      <c r="AY30" s="20" t="n">
+      <c r="AY30" s="22" t="n">
         <v>0.68</v>
       </c>
-      <c r="AZ30" s="20" t="n">
+      <c r="AZ30" s="22" t="n">
         <v>0.92</v>
       </c>
-      <c r="BA30" s="24" t="s">
+      <c r="BA30" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="BC30" s="24" t="n">
+      <c r="BC30" s="26" t="n">
         <f aca="false">AV30*1000</f>
         <v>620</v>
       </c>
-      <c r="BE30" s="20" t="s">
+      <c r="BE30" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="BF30" s="20" t="n">
+      <c r="BF30" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="BG30" s="20" t="n">
+      <c r="BG30" s="22" t="n">
         <v>99</v>
       </c>
-      <c r="BH30" s="20" t="s">
+      <c r="BH30" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI30" s="20" t="n">
+      <c r="BI30" s="22" t="n">
         <v>135</v>
       </c>
-      <c r="BK30" s="20" t="s">
+      <c r="BK30" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="BL30" s="20" t="n">
+      <c r="BL30" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="BM30" s="20" t="s">
+      <c r="BM30" s="22" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="31" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25" t="s">
+    <row r="31" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="22" t="n">
         <v>76</v>
       </c>
-      <c r="C31" s="21" t="n">
-        <f aca="false">B31/$P31/1000</f>
-        <v>0.000781105469793829</v>
-      </c>
-      <c r="D31" s="20" t="n">
+      <c r="C31" s="23" t="n">
+        <f aca="false">B31/$P31/10</f>
+        <v>0.0781105469793829</v>
+      </c>
+      <c r="D31" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="E31" s="22" t="n">
-        <f aca="false">D31/$P31/1000</f>
-        <v>0.000380275031346996</v>
-      </c>
-      <c r="F31" s="26" t="n">
+      <c r="E31" s="23" t="n">
+        <f aca="false">D31/$P31/10</f>
+        <v>0.0380275031346996</v>
+      </c>
+      <c r="F31" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="21" t="n">
-        <f aca="false">F31/$P31/1000</f>
+      <c r="G31" s="23" t="n">
+        <f aca="false">F31/$P31/10</f>
         <v>0</v>
       </c>
-      <c r="H31" s="26" t="n">
+      <c r="H31" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="I31" s="21" t="n">
-        <f aca="false">H31/$P31/1000</f>
-        <v>0.000195276367448457</v>
-      </c>
-      <c r="J31" s="20" t="n">
+      <c r="I31" s="23" t="n">
+        <f aca="false">H31/$P31/10</f>
+        <v>0.0195276367448457</v>
+      </c>
+      <c r="J31" s="22" t="n">
         <f aca="false">L31*$J$37/100</f>
         <v>8.5</v>
       </c>
-      <c r="K31" s="21" t="n">
-        <f aca="false">J31/$P31/1000</f>
-        <v>8.73604801743099E-005</v>
-      </c>
-      <c r="L31" s="20" t="n">
+      <c r="K31" s="23" t="n">
+        <f aca="false">J31/$P31/10</f>
+        <v>0.00873604801743099</v>
+      </c>
+      <c r="L31" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="M31" s="20" t="n">
+      <c r="M31" s="22" t="n">
         <f aca="false">O31*$M$37/100</f>
         <v>176.8</v>
       </c>
-      <c r="N31" s="22" t="n">
-        <f aca="false">M31/$P31/1000</f>
-        <v>0.00181709798762565</v>
-      </c>
-      <c r="O31" s="20" t="n">
+      <c r="N31" s="23" t="n">
+        <f aca="false">M31/$P31/10</f>
+        <v>0.181709798762565</v>
+      </c>
+      <c r="O31" s="22" t="n">
         <v>1300</v>
       </c>
-      <c r="P31" s="23" t="n">
+      <c r="P31" s="25" t="n">
         <v>97.298</v>
       </c>
-      <c r="Q31" s="23" t="n">
+      <c r="Q31" s="25" t="n">
         <f aca="false">100*P31/$P$36</f>
         <v>0.668274129072555</v>
       </c>
-      <c r="R31" s="20" t="n">
+      <c r="R31" s="22" t="n">
         <f aca="false">H31+F31+B31+D31+J31+M31</f>
         <v>317.3</v>
       </c>
-      <c r="S31" s="23" t="n">
+      <c r="S31" s="25" t="n">
         <f aca="false">R31/P31</f>
         <v>3.26111533638924</v>
       </c>
-      <c r="U31" s="23" t="n">
+      <c r="U31" s="25" t="n">
         <f aca="false">-T31+($Q$45 + $Q$46)*1000*Q31/100</f>
         <v>296.888132855902</v>
       </c>
-      <c r="V31" s="23" t="n">
+      <c r="V31" s="25" t="n">
         <f aca="false">U31/P31/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W31" s="23" t="n">
+      <c r="W31" s="25" t="n">
         <f aca="false">ROUND(U31/P31 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y31" s="23" t="n">
+      <c r="Y31" s="25" t="n">
         <f aca="false">-Q31*($Q$47)*10</f>
         <v>-160.385790977413</v>
       </c>
-      <c r="Z31" s="23" t="n">
+      <c r="Z31" s="25" t="n">
         <f aca="false">Y31/P31/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AA31" s="28"/>
-      <c r="AC31" s="20" t="n">
+      <c r="AA31" s="30"/>
+      <c r="AC31" s="22" t="n">
         <v>136.8</v>
       </c>
-      <c r="AH31" s="20" t="s">
+      <c r="AH31" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="AI31" s="20" t="n">
+      <c r="AI31" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" s="20" t="n">
+      <c r="AJ31" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="AK31" s="20" t="n">
+      <c r="AK31" s="22" t="n">
         <f aca="false">AI31+AJ31/100</f>
         <v>0.4</v>
       </c>
-      <c r="AL31" s="20" t="n">
+      <c r="AL31" s="22" t="n">
         <f aca="false">AK31*1000</f>
         <v>400</v>
       </c>
-      <c r="AO31" s="24" t="s">
+      <c r="AO31" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="AP31" s="20" t="n">
+      <c r="AP31" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ31" s="20" t="n">
+      <c r="AQ31" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="AR31" s="24" t="n">
+      <c r="AR31" s="26" t="n">
         <f aca="false">AP31+AQ31/10</f>
         <v>1.3</v>
       </c>
-      <c r="AS31" s="24" t="n">
+      <c r="AS31" s="26" t="n">
         <f aca="false">1000*AR31</f>
         <v>1300</v>
       </c>
-      <c r="AU31" s="24" t="s">
+      <c r="AU31" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="AV31" s="20" t="n">
+      <c r="AV31" s="22" t="n">
         <v>0.05</v>
       </c>
-      <c r="AW31" s="20" t="n">
+      <c r="AW31" s="22" t="n">
         <v>0.1</v>
       </c>
-      <c r="AX31" s="20" t="n">
+      <c r="AX31" s="22" t="n">
         <v>0.73</v>
       </c>
-      <c r="AY31" s="20" t="n">
+      <c r="AY31" s="22" t="n">
         <v>0.14</v>
       </c>
-      <c r="AZ31" s="20" t="n">
+      <c r="AZ31" s="22" t="n">
         <v>0.19</v>
       </c>
-      <c r="BA31" s="24" t="s">
+      <c r="BA31" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="BC31" s="24" t="n">
+      <c r="BC31" s="26" t="n">
         <f aca="false">AV31*1000</f>
         <v>50</v>
       </c>
-      <c r="BE31" s="20" t="s">
+      <c r="BE31" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="BF31" s="20" t="n">
+      <c r="BF31" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="BG31" s="20" t="n">
+      <c r="BG31" s="22" t="n">
         <v>56</v>
       </c>
-      <c r="BH31" s="20" t="s">
+      <c r="BH31" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI31" s="20" t="n">
+      <c r="BI31" s="22" t="n">
         <v>76</v>
       </c>
-      <c r="BK31" s="20" t="s">
+      <c r="BK31" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="BL31" s="20" t="n">
+      <c r="BL31" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="BM31" s="20" t="s">
+      <c r="BM31" s="22" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="32" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+    <row r="32" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="B32" s="20" t="n">
+      <c r="B32" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="C32" s="21" t="n">
-        <f aca="false">B32/$P32/1000</f>
-        <v>0.000641137728041033</v>
-      </c>
-      <c r="D32" s="20" t="n">
+      <c r="C32" s="23" t="n">
+        <f aca="false">B32/$P32/10</f>
+        <v>0.0641137728041033</v>
+      </c>
+      <c r="D32" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="22" t="n">
-        <f aca="false">D32/$P32/1000</f>
-        <v>0.000271997824017408</v>
-      </c>
-      <c r="F32" s="22" t="n">
+      <c r="E32" s="23" t="n">
+        <f aca="false">D32/$P32/10</f>
+        <v>0.0271997824017408</v>
+      </c>
+      <c r="F32" s="24" t="n">
         <v>0.4</v>
       </c>
-      <c r="G32" s="21" t="n">
-        <f aca="false">F32/$P32/1000</f>
-        <v>7.77136640049737E-006</v>
-      </c>
-      <c r="H32" s="22" t="n">
+      <c r="G32" s="23" t="n">
+        <f aca="false">F32/$P32/10</f>
+        <v>0.000777136640049737</v>
+      </c>
+      <c r="H32" s="24" t="n">
         <v>75</v>
       </c>
-      <c r="I32" s="21" t="n">
-        <f aca="false">H32/$P32/1000</f>
-        <v>0.00145713120009326</v>
-      </c>
-      <c r="J32" s="20" t="n">
+      <c r="I32" s="23" t="n">
+        <f aca="false">H32/$P32/10</f>
+        <v>0.145713120009326</v>
+      </c>
+      <c r="J32" s="22" t="n">
         <f aca="false">L32*$J$37/100</f>
         <v>5.1</v>
       </c>
-      <c r="K32" s="21" t="n">
-        <f aca="false">J32/$P32/1000</f>
-        <v>9.90849216063414E-005</v>
-      </c>
-      <c r="L32" s="20" t="n">
+      <c r="K32" s="23" t="n">
+        <f aca="false">J32/$P32/10</f>
+        <v>0.00990849216063414</v>
+      </c>
+      <c r="L32" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="M32" s="20" t="n">
+      <c r="M32" s="22" t="n">
         <f aca="false">O32*$M$37/100</f>
         <v>149.6</v>
       </c>
-      <c r="N32" s="22" t="n">
-        <f aca="false">M32/$P32/1000</f>
-        <v>0.00290649103378602</v>
-      </c>
-      <c r="O32" s="20" t="n">
+      <c r="N32" s="23" t="n">
+        <f aca="false">M32/$P32/10</f>
+        <v>0.290649103378602</v>
+      </c>
+      <c r="O32" s="22" t="n">
         <v>1100</v>
       </c>
-      <c r="P32" s="23" t="n">
+      <c r="P32" s="25" t="n">
         <v>51.471</v>
       </c>
-      <c r="Q32" s="23" t="n">
+      <c r="Q32" s="25" t="n">
         <f aca="false">100*P32/$P$36</f>
         <v>0.353519473139155</v>
       </c>
-      <c r="R32" s="20" t="n">
+      <c r="R32" s="22" t="n">
         <f aca="false">H32+F32+B32+D32+J32+M32</f>
         <v>277.1</v>
       </c>
-      <c r="S32" s="23" t="n">
+      <c r="S32" s="25" t="n">
         <f aca="false">R32/P32</f>
         <v>5.38361407394455</v>
       </c>
-      <c r="U32" s="23" t="n">
+      <c r="U32" s="25" t="n">
         <f aca="false">-T32+($Q$45 + $Q$46)*1000*Q32/100</f>
         <v>157.054914656274</v>
       </c>
-      <c r="V32" s="23" t="n">
+      <c r="V32" s="25" t="n">
         <f aca="false">U32/P32/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W32" s="23" t="n">
+      <c r="W32" s="25" t="n">
         <f aca="false">ROUND(U32/P32 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y32" s="23" t="n">
+      <c r="Y32" s="25" t="n">
         <f aca="false">-Q32*($Q$47)*10</f>
         <v>-84.8446735533971</v>
       </c>
-      <c r="Z32" s="23" t="n">
+      <c r="Z32" s="25" t="n">
         <f aca="false">Y32/P32/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC32" s="20" t="n">
+      <c r="AC32" s="22" t="n">
         <v>70.5</v>
       </c>
-      <c r="AH32" s="20" t="s">
+      <c r="AH32" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="AI32" s="20" t="n">
+      <c r="AI32" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ32" s="20" t="n">
+      <c r="AJ32" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="AK32" s="20" t="n">
+      <c r="AK32" s="22" t="n">
         <f aca="false">AI32+AJ32/100</f>
         <v>0.3</v>
       </c>
-      <c r="AL32" s="20" t="n">
+      <c r="AL32" s="22" t="n">
         <f aca="false">AK32*1000</f>
         <v>300</v>
       </c>
-      <c r="AO32" s="24" t="s">
+      <c r="AO32" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="AP32" s="20" t="n">
+      <c r="AP32" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AQ32" s="20" t="n">
+      <c r="AQ32" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AR32" s="24" t="n">
+      <c r="AR32" s="26" t="n">
         <f aca="false">AP32+AQ32/10</f>
         <v>1.1</v>
       </c>
-      <c r="AS32" s="24" t="n">
+      <c r="AS32" s="26" t="n">
         <f aca="false">1000*AR32</f>
         <v>1100</v>
       </c>
-      <c r="AU32" s="24" t="s">
+      <c r="AU32" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="AV32" s="20" t="n">
+      <c r="AV32" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="AW32" s="20" t="n">
+      <c r="AW32" s="22" t="n">
         <v>0.06</v>
       </c>
-      <c r="AX32" s="20" t="n">
+      <c r="AX32" s="22" t="n">
         <v>0.38</v>
       </c>
-      <c r="AY32" s="20" t="n">
+      <c r="AY32" s="22" t="n">
         <v>0.16</v>
       </c>
-      <c r="AZ32" s="20" t="n">
+      <c r="AZ32" s="22" t="n">
         <v>0.22</v>
       </c>
-      <c r="BA32" s="24" t="s">
+      <c r="BA32" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="BC32" s="24" t="n">
+      <c r="BC32" s="26" t="n">
         <f aca="false">AV32*1000</f>
         <v>30</v>
       </c>
-      <c r="BE32" s="20" t="s">
+      <c r="BE32" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="BF32" s="20" t="n">
+      <c r="BF32" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="BG32" s="20" t="n">
+      <c r="BG32" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="BH32" s="20" t="s">
+      <c r="BH32" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI32" s="20" t="n">
+      <c r="BI32" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="BK32" s="20" t="s">
+      <c r="BK32" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="BL32" s="20" t="n">
+      <c r="BL32" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="BM32" s="20" t="s">
+      <c r="BM32" s="22" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="33" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
+    <row r="33" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="20" t="n">
+      <c r="B33" s="22" t="n">
         <v>687</v>
       </c>
-      <c r="C33" s="21" t="n">
-        <f aca="false">B33/$P33/1000</f>
-        <v>0.00056628268798813</v>
-      </c>
-      <c r="D33" s="20" t="n">
+      <c r="C33" s="23" t="n">
+        <f aca="false">B33/$P33/10</f>
+        <v>0.056628268798813</v>
+      </c>
+      <c r="D33" s="22" t="n">
         <v>830</v>
       </c>
-      <c r="E33" s="22" t="n">
-        <f aca="false">D33/$P33/1000</f>
-        <v>0.000684155212562079</v>
-      </c>
-      <c r="F33" s="26" t="n">
+      <c r="E33" s="23" t="n">
+        <f aca="false">D33/$P33/10</f>
+        <v>0.0684155212562079</v>
+      </c>
+      <c r="F33" s="28" t="n">
         <v>240.6</v>
       </c>
-      <c r="G33" s="21" t="n">
-        <f aca="false">F33/$P33/1000</f>
-        <v>0.00019832258330414</v>
-      </c>
-      <c r="H33" s="26" t="n">
+      <c r="G33" s="23" t="n">
+        <f aca="false">F33/$P33/10</f>
+        <v>0.019832258330414</v>
+      </c>
+      <c r="H33" s="28" t="n">
         <v>2151</v>
       </c>
-      <c r="I33" s="21" t="n">
-        <f aca="false">H33/$P33/1000</f>
-        <v>0.001773033568941</v>
-      </c>
-      <c r="J33" s="20" t="n">
+      <c r="I33" s="23" t="n">
+        <f aca="false">H33/$P33/10</f>
+        <v>0.1773033568941</v>
+      </c>
+      <c r="J33" s="22" t="n">
         <f aca="false">L33*$J$37/100</f>
         <v>1586.1</v>
       </c>
-      <c r="K33" s="21" t="n">
-        <f aca="false">J33/$P33/1000</f>
-        <v>0.00130739588270447</v>
-      </c>
-      <c r="L33" s="20" t="n">
+      <c r="K33" s="23" t="n">
+        <f aca="false">J33/$P33/10</f>
+        <v>0.130739588270447</v>
+      </c>
+      <c r="L33" s="22" t="n">
         <v>9330</v>
       </c>
-      <c r="M33" s="20" t="n">
+      <c r="M33" s="22" t="n">
         <f aca="false">O33*$M$37/100</f>
         <v>4202.4</v>
       </c>
-      <c r="N33" s="22" t="n">
-        <f aca="false">M33/$P33/1000</f>
-        <v>0.00346396851237455</v>
-      </c>
-      <c r="O33" s="20" t="n">
+      <c r="N33" s="23" t="n">
+        <f aca="false">M33/$P33/10</f>
+        <v>0.346396851237455</v>
+      </c>
+      <c r="O33" s="22" t="n">
         <v>30900</v>
       </c>
-      <c r="P33" s="23" t="n">
+      <c r="P33" s="25" t="n">
         <v>1213.175</v>
       </c>
-      <c r="Q33" s="23" t="n">
+      <c r="Q33" s="25" t="n">
         <f aca="false">100*P33/$P$36</f>
         <v>8.33247822707144</v>
       </c>
-      <c r="R33" s="20" t="n">
+      <c r="R33" s="22" t="n">
         <f aca="false">H33+F33+B33+D33+J33+M33</f>
         <v>9697.1</v>
       </c>
-      <c r="S33" s="23" t="n">
+      <c r="S33" s="25" t="n">
         <f aca="false">R33/P33</f>
         <v>7.99315844787438</v>
       </c>
-      <c r="T33" s="20" t="n">
+      <c r="T33" s="22" t="n">
         <f aca="false">B33+F33</f>
         <v>927.6</v>
       </c>
-      <c r="U33" s="23" t="n">
+      <c r="U33" s="25" t="n">
         <f aca="false">-T33+($Q$45 + $Q$46)*1000*Q33/100</f>
         <v>2774.19510963698</v>
       </c>
-      <c r="V33" s="23" t="n">
+      <c r="V33" s="25" t="n">
         <f aca="false">U33/P33/10</f>
         <v>0.22867229456896</v>
       </c>
-      <c r="W33" s="23" t="n">
+      <c r="W33" s="25" t="n">
         <f aca="false">ROUND(U33/P33 *100/1000, 2)</f>
         <v>0.23</v>
       </c>
-      <c r="Y33" s="23" t="n">
+      <c r="Y33" s="25" t="n">
         <f aca="false">-Q33*($Q$47)*10</f>
         <v>-1999.79477449715</v>
       </c>
-      <c r="Z33" s="23" t="n">
+      <c r="Z33" s="25" t="n">
         <f aca="false">Y33/P33/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC33" s="20" t="n">
+      <c r="AC33" s="22" t="n">
         <v>1687.2</v>
       </c>
-      <c r="AH33" s="20" t="s">
+      <c r="AH33" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="AI33" s="20" t="n">
+      <c r="AI33" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="AJ33" s="20" t="n">
+      <c r="AJ33" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="AK33" s="20" t="n">
+      <c r="AK33" s="22" t="n">
         <f aca="false">AI33+AJ33/100</f>
         <v>9.33</v>
       </c>
-      <c r="AL33" s="20" t="n">
+      <c r="AL33" s="22" t="n">
         <f aca="false">AK33*1000</f>
         <v>9330</v>
       </c>
-      <c r="AO33" s="24" t="s">
+      <c r="AO33" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="AP33" s="20" t="n">
+      <c r="AP33" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="AQ33" s="20" t="n">
+      <c r="AQ33" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="AR33" s="24" t="n">
+      <c r="AR33" s="26" t="n">
         <f aca="false">AP33+AQ33/10</f>
         <v>30.9</v>
       </c>
-      <c r="AS33" s="24" t="n">
+      <c r="AS33" s="26" t="n">
         <f aca="false">1000*AR33</f>
         <v>30900</v>
       </c>
-      <c r="AU33" s="24" t="s">
+      <c r="AU33" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="AV33" s="20" t="n">
+      <c r="AV33" s="22" t="n">
         <v>9.33</v>
       </c>
-      <c r="AW33" s="20" t="n">
+      <c r="AW33" s="22" t="n">
         <v>20.74</v>
       </c>
-      <c r="AX33" s="20" t="n">
+      <c r="AX33" s="22" t="n">
         <v>8.68</v>
       </c>
-      <c r="AY33" s="20" t="n">
+      <c r="AY33" s="22" t="n">
         <v>2.39</v>
       </c>
-      <c r="AZ33" s="20" t="n">
+      <c r="AZ33" s="22" t="n">
         <v>3.24</v>
       </c>
-      <c r="BA33" s="24" t="s">
+      <c r="BA33" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="BC33" s="24" t="n">
+      <c r="BC33" s="26" t="n">
         <f aca="false">AV33*1000</f>
         <v>9330</v>
       </c>
-      <c r="BE33" s="20" t="s">
+      <c r="BE33" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="BF33" s="20" t="s">
+      <c r="BF33" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="BG33" s="20" t="n">
+      <c r="BG33" s="22" t="n">
         <v>505</v>
       </c>
-      <c r="BH33" s="20" t="n">
+      <c r="BH33" s="22" t="n">
         <v>375</v>
       </c>
-      <c r="BI33" s="20" t="n">
+      <c r="BI33" s="22" t="n">
         <v>687</v>
       </c>
-      <c r="BK33" s="20" t="s">
+      <c r="BK33" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="BL33" s="20" t="n">
+      <c r="BL33" s="22" t="n">
         <v>830</v>
       </c>
-      <c r="BM33" s="20" t="s">
+      <c r="BM33" s="22" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" s="20" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
+    <row r="34" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B34" s="20" t="n">
+      <c r="B34" s="22" t="n">
         <v>190</v>
       </c>
-      <c r="C34" s="21" t="n">
-        <f aca="false">B34/$P34/1000</f>
-        <v>0.000343768206145128</v>
-      </c>
-      <c r="D34" s="20" t="n">
+      <c r="C34" s="23" t="n">
+        <f aca="false">B34/$P34/10</f>
+        <v>0.0343768206145128</v>
+      </c>
+      <c r="D34" s="22" t="n">
         <v>601</v>
       </c>
-      <c r="E34" s="22" t="n">
-        <f aca="false">D34/$P34/1000</f>
-        <v>0.00108739311522748</v>
-      </c>
-      <c r="F34" s="22" t="n">
+      <c r="E34" s="23" t="n">
+        <f aca="false">D34/$P34/10</f>
+        <v>0.108739311522748</v>
+      </c>
+      <c r="F34" s="24" t="n">
         <v>245.1</v>
       </c>
-      <c r="G34" s="21" t="n">
-        <f aca="false">F34/$P34/1000</f>
-        <v>0.000443460985927215</v>
-      </c>
-      <c r="H34" s="22" t="n">
+      <c r="G34" s="23" t="n">
+        <f aca="false">F34/$P34/10</f>
+        <v>0.0443460985927215</v>
+      </c>
+      <c r="H34" s="24" t="n">
         <v>712</v>
       </c>
-      <c r="I34" s="21" t="n">
-        <f aca="false">H34/$P34/1000</f>
-        <v>0.00128822611987016</v>
-      </c>
-      <c r="J34" s="20" t="n">
+      <c r="I34" s="23" t="n">
+        <f aca="false">H34/$P34/10</f>
+        <v>0.128822611987016</v>
+      </c>
+      <c r="J34" s="22" t="n">
         <f aca="false">L34*$J$37/100</f>
         <v>197.2</v>
       </c>
-      <c r="K34" s="21" t="n">
-        <f aca="false">J34/$P34/1000</f>
-        <v>0.00035679521185168</v>
-      </c>
-      <c r="L34" s="20" t="n">
+      <c r="K34" s="23" t="n">
+        <f aca="false">J34/$P34/10</f>
+        <v>0.035679521185168</v>
+      </c>
+      <c r="L34" s="22" t="n">
         <v>1160</v>
       </c>
-      <c r="M34" s="20" t="n">
+      <c r="M34" s="22" t="n">
         <f aca="false">O34*$M$37/100</f>
         <v>965.6</v>
       </c>
-      <c r="N34" s="22" t="n">
-        <f aca="false">M34/$P34/1000</f>
-        <v>0.0017470662097565</v>
-      </c>
-      <c r="O34" s="20" t="n">
+      <c r="N34" s="23" t="n">
+        <f aca="false">M34/$P34/10</f>
+        <v>0.17470662097565</v>
+      </c>
+      <c r="O34" s="22" t="n">
         <v>7100</v>
       </c>
-      <c r="P34" s="23" t="n">
+      <c r="P34" s="25" t="n">
         <v>552.698</v>
       </c>
-      <c r="Q34" s="23" t="n">
+      <c r="Q34" s="25" t="n">
         <f aca="false">100*P34/$P$36</f>
         <v>3.79610860028102</v>
       </c>
-      <c r="R34" s="20" t="n">
+      <c r="R34" s="22" t="n">
         <f aca="false">H34+F34+B34+D34+J34+M34</f>
         <v>2910.9</v>
       </c>
-      <c r="S34" s="23" t="n">
+      <c r="S34" s="25" t="n">
         <f aca="false">R34/P34</f>
         <v>5.26670984877818</v>
       </c>
-      <c r="U34" s="23" t="n">
+      <c r="U34" s="25" t="n">
         <f aca="false">-T34+($Q$45 + $Q$46)*1000*Q34/100</f>
         <v>1686.46300286945</v>
       </c>
-      <c r="V34" s="23" t="n">
+      <c r="V34" s="25" t="n">
         <f aca="false">U34/P34/10</f>
         <v>0.305132821698187</v>
       </c>
-      <c r="W34" s="23" t="n">
+      <c r="W34" s="25" t="n">
         <f aca="false">ROUND(U34/P34 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y34" s="23" t="n">
+      <c r="Y34" s="25" t="n">
         <f aca="false">-Q34*($Q$47)*10</f>
         <v>-911.066064067446</v>
       </c>
-      <c r="Z34" s="23" t="n">
+      <c r="Z34" s="25" t="n">
         <f aca="false">Y34/P34/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC34" s="20" t="n">
+      <c r="AC34" s="22" t="n">
         <v>601.2</v>
       </c>
-      <c r="AH34" s="20" t="s">
+      <c r="AH34" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="AI34" s="20" t="n">
+      <c r="AI34" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AJ34" s="20" t="n">
+      <c r="AJ34" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="AK34" s="20" t="n">
+      <c r="AK34" s="22" t="n">
         <f aca="false">AI34+AJ34/100</f>
         <v>1.16</v>
       </c>
-      <c r="AL34" s="20" t="n">
+      <c r="AL34" s="22" t="n">
         <f aca="false">AK34*1000</f>
         <v>1160</v>
       </c>
-      <c r="AO34" s="24" t="s">
+      <c r="AO34" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="AP34" s="20" t="n">
+      <c r="AP34" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="AQ34" s="20" t="n">
+      <c r="AQ34" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="AR34" s="24" t="n">
+      <c r="AR34" s="26" t="n">
         <f aca="false">AP34+AQ34/10</f>
         <v>7.1</v>
       </c>
-      <c r="AS34" s="24" t="n">
+      <c r="AS34" s="26" t="n">
         <f aca="false">1000*AR34</f>
         <v>7100</v>
       </c>
-      <c r="AU34" s="24" t="s">
+      <c r="AU34" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="AV34" s="20" t="n">
+      <c r="AV34" s="22" t="n">
         <v>1.16</v>
       </c>
-      <c r="AW34" s="20" t="n">
+      <c r="AW34" s="22" t="n">
         <v>2.58</v>
       </c>
-      <c r="AX34" s="20" t="n">
+      <c r="AX34" s="22" t="n">
         <v>3.23</v>
       </c>
-      <c r="AY34" s="20" t="n">
+      <c r="AY34" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="AZ34" s="20" t="n">
+      <c r="AZ34" s="22" t="n">
         <v>1.08</v>
       </c>
-      <c r="BA34" s="24" t="s">
+      <c r="BA34" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="BC34" s="24" t="n">
+      <c r="BC34" s="26" t="n">
         <f aca="false">AV34*1000</f>
         <v>1160</v>
       </c>
-      <c r="BE34" s="20" t="s">
+      <c r="BE34" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="BF34" s="20" t="n">
+      <c r="BF34" s="22" t="n">
         <v>270</v>
       </c>
-      <c r="BG34" s="20" t="n">
+      <c r="BG34" s="22" t="n">
         <v>140</v>
       </c>
-      <c r="BH34" s="20" t="s">
+      <c r="BH34" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BI34" s="20" t="n">
+      <c r="BI34" s="22" t="n">
         <v>190</v>
       </c>
-      <c r="BK34" s="20" t="s">
+      <c r="BK34" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="BL34" s="20" t="n">
+      <c r="BL34" s="22" t="n">
         <v>601</v>
       </c>
-      <c r="BM34" s="20" t="s">
+      <c r="BM34" s="22" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="35" s="34" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="s">
+    <row r="35" s="36" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="32" t="n">
         <v>5880</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="32" t="n">
+      <c r="C35" s="33"/>
+      <c r="D35" s="34" t="n">
         <v>9616</v>
       </c>
-      <c r="E35" s="31"/>
-      <c r="F35" s="30" t="n">
+      <c r="E35" s="33"/>
+      <c r="F35" s="32" t="n">
         <v>8334.6</v>
       </c>
-      <c r="G35" s="31"/>
-      <c r="H35" s="30" t="n">
+      <c r="G35" s="33"/>
+      <c r="H35" s="32" t="n">
         <v>26264</v>
       </c>
-      <c r="I35" s="31"/>
-      <c r="J35" s="20" t="n">
+      <c r="I35" s="33"/>
+      <c r="J35" s="22" t="n">
         <f aca="false">SUM(J8:J34)</f>
         <v>7650</v>
       </c>
-      <c r="K35" s="23"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20" t="n">
+      <c r="K35" s="25"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22" t="n">
         <f aca="false">SUM(M8:M34)</f>
         <v>40677.6</v>
       </c>
-      <c r="N35" s="23"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="33" t="n">
+      <c r="N35" s="25"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="R35" s="20" t="n">
+      <c r="R35" s="22" t="n">
         <f aca="false">H35+F35+B35+D35+L35+M35</f>
         <v>90772.2</v>
       </c>
-      <c r="S35" s="23"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20" t="n">
+      <c r="S35" s="25"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="22" t="n">
         <f aca="false">SUM(U8:U34)</f>
         <v>37876.579621376</v>
       </c>
-      <c r="V35" s="20"/>
-      <c r="W35" s="34" t="e">
+      <c r="V35" s="22"/>
+      <c r="W35" s="36" t="e">
         <f aca="false">ROUND(U35/P35 *100/1000, 2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y35" s="23" t="n">
+      <c r="Y35" s="25" t="n">
         <f aca="false">-Q35*($Q$47)*10</f>
         <v>-24000</v>
       </c>
-      <c r="Z35" s="23"/>
-      <c r="AC35" s="34" t="n">
+      <c r="Z35" s="25"/>
+      <c r="AC35" s="36" t="n">
         <v>18796</v>
       </c>
-      <c r="AL35" s="34" t="n">
+      <c r="AL35" s="36" t="n">
         <f aca="false">SUM(AL8:AL34)</f>
         <v>47600</v>
       </c>
-      <c r="AR35" s="34" t="n">
+      <c r="AR35" s="36" t="n">
         <f aca="false">SUM(AR8:AR34)</f>
         <v>299.1</v>
       </c>
-      <c r="XEX35" s="20"/>
-      <c r="XEY35" s="20"/>
-      <c r="XEZ35" s="20"/>
-      <c r="XFA35" s="20"/>
-      <c r="XFB35" s="20"/>
-      <c r="XFC35" s="20"/>
-      <c r="XFD35" s="20"/>
+      <c r="XEX35" s="22"/>
+      <c r="XEY35" s="22"/>
+      <c r="XEZ35" s="22"/>
+      <c r="XFA35" s="22"/>
+      <c r="XFB35" s="22"/>
+      <c r="XFC35" s="22"/>
+      <c r="XFD35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="n">
@@ -8256,222 +8284,222 @@
       <c r="S36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="35" t="n">
+      <c r="J37" s="37" t="n">
         <v>17</v>
       </c>
-      <c r="K37" s="36"/>
-      <c r="M37" s="35" t="n">
+      <c r="K37" s="38"/>
+      <c r="M37" s="37" t="n">
         <v>13.6</v>
       </c>
-      <c r="N37" s="36"/>
+      <c r="N37" s="38"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="C38" s="38" t="n">
+      <c r="C38" s="40" t="n">
         <f aca="false">SUM(B35:M35)</f>
         <v>98422.2</v>
       </c>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
       <c r="J38" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M38" s="39" t="s">
+      <c r="M38" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="N38" s="40"/>
+      <c r="N38" s="42"/>
       <c r="T38" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="37"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
       <c r="T39" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="37"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="P40" s="41" t="s">
+      <c r="B40" s="39"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="P40" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="Q40" s="42" t="n">
+      <c r="Q40" s="44" t="n">
         <v>192.8</v>
       </c>
-      <c r="R40" s="39"/>
-      <c r="S40" s="39"/>
-      <c r="T40" s="39" t="s">
+      <c r="R40" s="41"/>
+      <c r="S40" s="41"/>
+      <c r="T40" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="U40" s="39"/>
-      <c r="V40" s="39"/>
+      <c r="U40" s="41"/>
+      <c r="V40" s="41"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P41" s="41" t="s">
+      <c r="P41" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="Q41" s="41" t="n">
+      <c r="Q41" s="43" t="n">
         <f aca="false">Q40*0.7</f>
         <v>134.96</v>
       </c>
-      <c r="R41" s="39"/>
-      <c r="S41" s="39"/>
-      <c r="T41" s="39"/>
-      <c r="U41" s="39"/>
-      <c r="V41" s="39"/>
+      <c r="R41" s="41"/>
+      <c r="S41" s="41"/>
+      <c r="T41" s="41"/>
+      <c r="U41" s="41"/>
+      <c r="V41" s="41"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="39"/>
-      <c r="S42" s="39"/>
-      <c r="T42" s="39"/>
-      <c r="U42" s="39"/>
-      <c r="V42" s="39"/>
+      <c r="P42" s="43"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="41"/>
+      <c r="T42" s="41"/>
+      <c r="U42" s="41"/>
+      <c r="V42" s="41"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P43" s="43" t="s">
+      <c r="P43" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="Q43" s="44" t="n">
+      <c r="Q43" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="R43" s="39"/>
-      <c r="S43" s="39"/>
-      <c r="T43" s="39"/>
-      <c r="U43" s="39"/>
-      <c r="V43" s="39"/>
+      <c r="R43" s="41"/>
+      <c r="S43" s="41"/>
+      <c r="T43" s="41"/>
+      <c r="U43" s="41"/>
+      <c r="V43" s="41"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P44" s="43" t="s">
+      <c r="P44" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="Q44" s="43" t="n">
+      <c r="Q44" s="45" t="n">
         <f aca="false">R36/1000 -Q43</f>
         <v>68.4261</v>
       </c>
-      <c r="R44" s="39"/>
-      <c r="S44" s="39"/>
-      <c r="T44" s="39"/>
-      <c r="U44" s="39"/>
-      <c r="V44" s="39"/>
+      <c r="R44" s="41"/>
+      <c r="S44" s="41"/>
+      <c r="T44" s="41"/>
+      <c r="U44" s="41"/>
+      <c r="V44" s="41"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P45" s="43" t="s">
+      <c r="P45" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="Q45" s="43" t="n">
+      <c r="Q45" s="45" t="n">
         <f aca="false">Q44-Q46-Q47</f>
         <v>30.4261</v>
       </c>
-      <c r="R45" s="39"/>
-      <c r="S45" s="39"/>
-      <c r="T45" s="39"/>
-      <c r="U45" s="39"/>
-      <c r="V45" s="39"/>
+      <c r="R45" s="41"/>
+      <c r="S45" s="41"/>
+      <c r="T45" s="41"/>
+      <c r="U45" s="41"/>
+      <c r="V45" s="41"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P46" s="43" t="s">
+      <c r="P46" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="Q46" s="44" t="n">
+      <c r="Q46" s="46" t="n">
         <v>14</v>
       </c>
-      <c r="R46" s="39"/>
-      <c r="S46" s="39"/>
-      <c r="T46" s="39"/>
-      <c r="U46" s="39"/>
-      <c r="V46" s="39"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="41"/>
+      <c r="U46" s="41"/>
+      <c r="V46" s="41"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P47" s="43" t="s">
+      <c r="P47" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="Q47" s="44" t="n">
+      <c r="Q47" s="46" t="n">
         <v>24</v>
       </c>
-      <c r="R47" s="39"/>
-      <c r="S47" s="39"/>
-      <c r="T47" s="39"/>
-      <c r="U47" s="39"/>
-      <c r="V47" s="39"/>
+      <c r="R47" s="41"/>
+      <c r="S47" s="41"/>
+      <c r="T47" s="41"/>
+      <c r="U47" s="41"/>
+      <c r="V47" s="41"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="39"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="39"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="39"/>
-      <c r="P48" s="43" t="s">
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
+      <c r="P48" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="Q48" s="43" t="n">
+      <c r="Q48" s="45" t="n">
         <f aca="false">Q40+Q46</f>
         <v>206.8</v>
       </c>
-      <c r="R48" s="39"/>
-      <c r="S48" s="39"/>
-      <c r="T48" s="39"/>
-      <c r="U48" s="39"/>
-      <c r="V48" s="39"/>
+      <c r="R48" s="41"/>
+      <c r="S48" s="41"/>
+      <c r="T48" s="41"/>
+      <c r="U48" s="41"/>
+      <c r="V48" s="41"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="39"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
-      <c r="G49" s="39"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="39"/>
-      <c r="P49" s="43" t="s">
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="P49" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="Q49" s="43" t="n">
+      <c r="Q49" s="45" t="n">
         <f aca="false">Q41-Q45</f>
         <v>104.5339</v>
       </c>
-      <c r="R49" s="39"/>
-      <c r="S49" s="39"/>
-      <c r="T49" s="39"/>
-      <c r="U49" s="39"/>
-      <c r="V49" s="39"/>
+      <c r="R49" s="41"/>
+      <c r="S49" s="41"/>
+      <c r="T49" s="41"/>
+      <c r="U49" s="41"/>
+      <c r="V49" s="41"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="39"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="39"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="39"/>
-      <c r="P50" s="43" t="s">
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="P50" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="Q50" s="45" t="n">
+      <c r="Q50" s="47" t="n">
         <f aca="false">Q49/Q48</f>
         <v>0.505483075435203</v>
       </c>
-      <c r="R50" s="39"/>
-      <c r="S50" s="39"/>
-      <c r="T50" s="39"/>
-      <c r="U50" s="39"/>
-      <c r="V50" s="39"/>
+      <c r="R50" s="41"/>
+      <c r="S50" s="41"/>
+      <c r="T50" s="41"/>
+      <c r="U50" s="41"/>
+      <c r="V50" s="41"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="46"/>
+      <c r="A53" s="48"/>
       <c r="U53" s="1" t="s">
         <v>210</v>
       </c>
@@ -8481,7 +8509,7 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="46"/>
+      <c r="A55" s="48"/>
       <c r="J55" s="1" t="s">
         <v>5</v>
       </c>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="219">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -85,7 +85,13 @@
     <t xml:space="preserve">(%)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOR total (Ad 80%)</t>
+    <t xml:space="preserve">NOR total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">œ</t>
   </si>
   <si>
     <t xml:space="preserve">rapporté au PIB ( %)</t>
@@ -118,15 +124,33 @@
     <t xml:space="preserve">table_scenario</t>
   </si>
   <si>
+    <t xml:space="preserve">New revenue </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foregone revenues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Funds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic budget gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relative gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_sscenario</t>
+  </si>
+  <si>
     <t xml:space="preserve">6 NOR scenario</t>
   </si>
   <si>
     <t xml:space="preserve">Status-quo scenario</t>
   </si>
   <si>
-    <t xml:space="preserve">table_sscenario</t>
-  </si>
-  <si>
     <t xml:space="preserve">tax base </t>
   </si>
   <si>
@@ -632,9 +656,6 @@
   </si>
   <si>
     <t xml:space="preserve">Reward fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR</t>
   </si>
   <si>
     <t xml:space="preserve">GNI contrib reduction</t>
@@ -753,7 +774,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCF4069"/>
-        <bgColor rgb="FFBB5928"/>
+        <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
     <fill>
@@ -782,14 +803,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFBF00"/>
-        <bgColor rgb="FFFFD320"/>
+        <fgColor rgb="FF00A2B3"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBB5928"/>
-        <bgColor rgb="FFCF4069"/>
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFFD320"/>
       </patternFill>
     </fill>
     <fill>
@@ -875,7 +896,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -936,23 +957,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -977,6 +1002,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1060,7 +1089,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1096,7 +1125,7 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF00A2B3"/>
       <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FFD17486"/>
       <rgbColor rgb="FF7BB2DD"/>
@@ -1135,7 +1164,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFBB5928"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1A237E"/>
       <rgbColor rgb="FF333333"/>
@@ -1156,10 +1185,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.120700394490968"/>
-          <c:y val="0.0304347826086957"/>
-          <c:w val="0.693104482432464"/>
-          <c:h val="0.776579163248564"/>
+          <c:x val="0.120686473519099"/>
+          <c:y val="0.0304360310102957"/>
+          <c:w val="0.693093744233253"/>
+          <c:h val="0.776528979859715"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -2566,11 +2595,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="4257055"/>
-        <c:axId val="82875935"/>
+        <c:axId val="51947549"/>
+        <c:axId val="798835"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4257055"/>
+        <c:axId val="51947549"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2602,7 +2631,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82875935"/>
+        <c:crossAx val="798835"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2610,7 +2639,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82875935"/>
+        <c:axId val="798835"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2651,7 +2680,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4257055"/>
+        <c:crossAx val="51947549"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2714,9 +2743,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>352080</xdr:colOff>
+      <xdr:colOff>351720</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>86040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2725,7 +2754,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="344880" y="8228880"/>
-        <a:ext cx="15604560" cy="8776440"/>
+        <a:ext cx="15606360" cy="8776080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2858,24 +2887,24 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="11.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="13.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="14.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="1" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="14.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="11.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="12.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16342" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="20" style="1" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="14.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="11.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="12.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16348" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" s="11" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2917,18 +2946,18 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
       <c r="T1" s="10"/>
-      <c r="AB1" s="11" t="s">
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AH1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AI1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="XEX1" s="1"/>
-      <c r="XEY1" s="1"/>
-      <c r="XEZ1" s="1"/>
-      <c r="XFA1" s="1"/>
-      <c r="XFB1" s="1"/>
-      <c r="XFC1" s="1"/>
       <c r="XFD1" s="1"/>
     </row>
     <row r="2" s="13" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2980,27 +3009,23 @@
       </c>
       <c r="R2" s="14"/>
       <c r="S2" s="14"/>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="15"/>
+      <c r="U2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="V2" s="15"/>
+      <c r="AA2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="AE2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="13" t="s">
+      <c r="AH2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="AC2" s="13" t="s">
+      <c r="AI2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="XEX2" s="1"/>
-      <c r="XEY2" s="1"/>
-      <c r="XEZ2" s="1"/>
-      <c r="XFA2" s="1"/>
-      <c r="XFB2" s="1"/>
-      <c r="XFC2" s="1"/>
       <c r="XFD2" s="1"/>
     </row>
     <row r="3" s="13" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3048,5195 +3073,5794 @@
         <v>21</v>
       </c>
       <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="13" t="s">
+      <c r="T3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="V3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="X3" s="13" t="s">
         <v>23</v>
       </c>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
       <c r="AC3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="XEX3" s="1"/>
-      <c r="XEY3" s="1"/>
-      <c r="XEZ3" s="1"/>
-      <c r="XFA3" s="1"/>
-      <c r="XFB3" s="1"/>
-      <c r="XFC3" s="1"/>
+      <c r="AE3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI3" s="13" t="s">
+        <v>26</v>
+      </c>
       <c r="XFD3" s="1"/>
     </row>
-    <row r="4" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17" t="s">
+    <row r="4" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17" t="s">
+      <c r="B4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17" t="s">
+      <c r="C4" s="19"/>
+      <c r="D4" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17" t="s">
+      <c r="E4" s="19"/>
+      <c r="F4" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17" t="s">
+      <c r="K4" s="20"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="17"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="AC4" s="17"/>
-      <c r="XDN4" s="17"/>
-      <c r="XDO4" s="17"/>
-      <c r="XDP4" s="17"/>
-      <c r="XDQ4" s="17"/>
-      <c r="XDR4" s="17"/>
-      <c r="XDS4" s="17"/>
-      <c r="XDT4" s="17"/>
-      <c r="XDU4" s="17"/>
-      <c r="XDV4" s="17"/>
-      <c r="XDW4" s="17"/>
-      <c r="XDX4" s="17"/>
-      <c r="XDY4" s="17"/>
-      <c r="XDZ4" s="17"/>
-      <c r="XEA4" s="17"/>
-      <c r="XEB4" s="17"/>
-      <c r="XEC4" s="17"/>
-      <c r="XED4" s="17"/>
-      <c r="XEE4" s="17"/>
-      <c r="XEF4" s="17"/>
-      <c r="XEG4" s="17"/>
-      <c r="XEH4" s="17"/>
-      <c r="XEI4" s="17"/>
-      <c r="XEJ4" s="17"/>
-      <c r="XEK4" s="17"/>
-      <c r="XEL4" s="17"/>
-      <c r="XEM4" s="17"/>
-      <c r="XEN4" s="17"/>
-      <c r="XEO4" s="17"/>
-      <c r="XEP4" s="17"/>
-      <c r="XEQ4" s="17"/>
-      <c r="XER4" s="17"/>
-      <c r="XES4" s="17"/>
-      <c r="XET4" s="17"/>
-      <c r="XEU4" s="17"/>
-      <c r="XEV4" s="17"/>
-      <c r="XEW4" s="17"/>
-      <c r="XEX4" s="1"/>
-      <c r="XEY4" s="1"/>
-      <c r="XEZ4" s="1"/>
-      <c r="XFA4" s="1"/>
-      <c r="XFB4" s="1"/>
-      <c r="XFC4" s="1"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="AI4" s="19"/>
+      <c r="XDT4" s="19"/>
+      <c r="XDU4" s="19"/>
+      <c r="XDV4" s="19"/>
+      <c r="XDW4" s="19"/>
+      <c r="XDX4" s="19"/>
+      <c r="XDY4" s="19"/>
+      <c r="XDZ4" s="19"/>
+      <c r="XEA4" s="19"/>
+      <c r="XEB4" s="19"/>
+      <c r="XEC4" s="19"/>
+      <c r="XED4" s="19"/>
+      <c r="XEE4" s="19"/>
+      <c r="XEF4" s="19"/>
+      <c r="XEG4" s="19"/>
+      <c r="XEH4" s="19"/>
+      <c r="XEI4" s="19"/>
+      <c r="XEJ4" s="19"/>
+      <c r="XEK4" s="19"/>
+      <c r="XEL4" s="19"/>
+      <c r="XEM4" s="19"/>
+      <c r="XEN4" s="19"/>
+      <c r="XEO4" s="19"/>
+      <c r="XEP4" s="19"/>
+      <c r="XEQ4" s="19"/>
+      <c r="XER4" s="19"/>
+      <c r="XES4" s="19"/>
+      <c r="XET4" s="19"/>
+      <c r="XEU4" s="19"/>
+      <c r="XEV4" s="19"/>
+      <c r="XEW4" s="19"/>
+      <c r="XEX4" s="19"/>
+      <c r="XEY4" s="19"/>
+      <c r="XEZ4" s="19"/>
+      <c r="XFA4" s="19"/>
+      <c r="XFB4" s="19"/>
+      <c r="XFC4" s="19"/>
       <c r="XFD4" s="1"/>
     </row>
-    <row r="5" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17" t="s">
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="17"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
-      <c r="AC5" s="17"/>
-      <c r="XDN5" s="17"/>
-      <c r="XDO5" s="17"/>
-      <c r="XDP5" s="17"/>
-      <c r="XDQ5" s="17"/>
-      <c r="XDR5" s="17"/>
-      <c r="XDS5" s="17"/>
-      <c r="XDT5" s="17"/>
-      <c r="XDU5" s="17"/>
-      <c r="XDV5" s="17"/>
-      <c r="XDW5" s="17"/>
-      <c r="XDX5" s="17"/>
-      <c r="XDY5" s="17"/>
-      <c r="XDZ5" s="17"/>
-      <c r="XEA5" s="17"/>
-      <c r="XEB5" s="17"/>
-      <c r="XEC5" s="17"/>
-      <c r="XED5" s="17"/>
-      <c r="XEE5" s="17"/>
-      <c r="XEF5" s="17"/>
-      <c r="XEG5" s="17"/>
-      <c r="XEH5" s="17"/>
-      <c r="XEI5" s="17"/>
-      <c r="XEJ5" s="17"/>
-      <c r="XEK5" s="17"/>
-      <c r="XEL5" s="17"/>
-      <c r="XEM5" s="17"/>
-      <c r="XEN5" s="17"/>
-      <c r="XEO5" s="17"/>
-      <c r="XEP5" s="17"/>
-      <c r="XEQ5" s="17"/>
-      <c r="XER5" s="17"/>
-      <c r="XES5" s="17"/>
-      <c r="XET5" s="17"/>
-      <c r="XEU5" s="17"/>
-      <c r="XEV5" s="17"/>
-      <c r="XEW5" s="17"/>
-      <c r="XEX5" s="1"/>
-      <c r="XEY5" s="1"/>
-      <c r="XEZ5" s="1"/>
-      <c r="XFA5" s="1"/>
-      <c r="XFB5" s="1"/>
-      <c r="XFC5" s="1"/>
+      <c r="O5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="AI5" s="19"/>
+      <c r="XDT5" s="19"/>
+      <c r="XDU5" s="19"/>
+      <c r="XDV5" s="19"/>
+      <c r="XDW5" s="19"/>
+      <c r="XDX5" s="19"/>
+      <c r="XDY5" s="19"/>
+      <c r="XDZ5" s="19"/>
+      <c r="XEA5" s="19"/>
+      <c r="XEB5" s="19"/>
+      <c r="XEC5" s="19"/>
+      <c r="XED5" s="19"/>
+      <c r="XEE5" s="19"/>
+      <c r="XEF5" s="19"/>
+      <c r="XEG5" s="19"/>
+      <c r="XEH5" s="19"/>
+      <c r="XEI5" s="19"/>
+      <c r="XEJ5" s="19"/>
+      <c r="XEK5" s="19"/>
+      <c r="XEL5" s="19"/>
+      <c r="XEM5" s="19"/>
+      <c r="XEN5" s="19"/>
+      <c r="XEO5" s="19"/>
+      <c r="XEP5" s="19"/>
+      <c r="XEQ5" s="19"/>
+      <c r="XER5" s="19"/>
+      <c r="XES5" s="19"/>
+      <c r="XET5" s="19"/>
+      <c r="XEU5" s="19"/>
+      <c r="XEV5" s="19"/>
+      <c r="XEW5" s="19"/>
+      <c r="XEX5" s="19"/>
+      <c r="XEY5" s="19"/>
+      <c r="XEZ5" s="19"/>
+      <c r="XFA5" s="19"/>
+      <c r="XFB5" s="19"/>
+      <c r="XFC5" s="19"/>
       <c r="XFD5" s="1"/>
     </row>
-    <row r="6" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="17"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y6" s="19" t="s">
+    <row r="6" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="AC6" s="17"/>
-      <c r="XDN6" s="17"/>
-      <c r="XDO6" s="17"/>
-      <c r="XDP6" s="17"/>
-      <c r="XDQ6" s="17"/>
-      <c r="XDR6" s="17"/>
-      <c r="XDS6" s="17"/>
-      <c r="XDT6" s="17"/>
-      <c r="XDU6" s="17"/>
-      <c r="XDV6" s="17"/>
-      <c r="XDW6" s="17"/>
-      <c r="XDX6" s="17"/>
-      <c r="XDY6" s="17"/>
-      <c r="XDZ6" s="17"/>
-      <c r="XEA6" s="17"/>
-      <c r="XEB6" s="17"/>
-      <c r="XEC6" s="17"/>
-      <c r="XED6" s="17"/>
-      <c r="XEE6" s="17"/>
-      <c r="XEF6" s="17"/>
-      <c r="XEG6" s="17"/>
-      <c r="XEH6" s="17"/>
-      <c r="XEI6" s="17"/>
-      <c r="XEJ6" s="17"/>
-      <c r="XEK6" s="17"/>
-      <c r="XEL6" s="17"/>
-      <c r="XEM6" s="17"/>
-      <c r="XEN6" s="17"/>
-      <c r="XEO6" s="17"/>
-      <c r="XEP6" s="17"/>
-      <c r="XEQ6" s="17"/>
-      <c r="XER6" s="17"/>
-      <c r="XES6" s="17"/>
-      <c r="XET6" s="17"/>
-      <c r="XEU6" s="17"/>
-      <c r="XEV6" s="17"/>
-      <c r="XEW6" s="17"/>
-      <c r="XEX6" s="1"/>
-      <c r="XEY6" s="1"/>
-      <c r="XEZ6" s="1"/>
-      <c r="XFA6" s="1"/>
-      <c r="XFB6" s="1"/>
-      <c r="XFC6" s="1"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="19"/>
+      <c r="R6" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="V6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="W6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y6" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI6" s="19"/>
+      <c r="XDT6" s="19"/>
+      <c r="XDU6" s="19"/>
+      <c r="XDV6" s="19"/>
+      <c r="XDW6" s="19"/>
+      <c r="XDX6" s="19"/>
+      <c r="XDY6" s="19"/>
+      <c r="XDZ6" s="19"/>
+      <c r="XEA6" s="19"/>
+      <c r="XEB6" s="19"/>
+      <c r="XEC6" s="19"/>
+      <c r="XED6" s="19"/>
+      <c r="XEE6" s="19"/>
+      <c r="XEF6" s="19"/>
+      <c r="XEG6" s="19"/>
+      <c r="XEH6" s="19"/>
+      <c r="XEI6" s="19"/>
+      <c r="XEJ6" s="19"/>
+      <c r="XEK6" s="19"/>
+      <c r="XEL6" s="19"/>
+      <c r="XEM6" s="19"/>
+      <c r="XEN6" s="19"/>
+      <c r="XEO6" s="19"/>
+      <c r="XEP6" s="19"/>
+      <c r="XEQ6" s="19"/>
+      <c r="XER6" s="19"/>
+      <c r="XES6" s="19"/>
+      <c r="XET6" s="19"/>
+      <c r="XEU6" s="19"/>
+      <c r="XEV6" s="19"/>
+      <c r="XEW6" s="19"/>
+      <c r="XEX6" s="19"/>
+      <c r="XEY6" s="19"/>
+      <c r="XEZ6" s="19"/>
+      <c r="XFA6" s="19"/>
+      <c r="XFB6" s="19"/>
+      <c r="XFC6" s="19"/>
       <c r="XFD6" s="1"/>
     </row>
-    <row r="7" s="19" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="17"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC7" s="17"/>
-      <c r="AV7" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="AW7" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AZ7" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="XDN7" s="17"/>
-      <c r="XDO7" s="17"/>
-      <c r="XDP7" s="17"/>
-      <c r="XDQ7" s="17"/>
-      <c r="XDR7" s="17"/>
-      <c r="XDS7" s="17"/>
-      <c r="XDT7" s="17"/>
-      <c r="XDU7" s="17"/>
-      <c r="XDV7" s="17"/>
-      <c r="XDW7" s="17"/>
-      <c r="XDX7" s="17"/>
-      <c r="XDY7" s="17"/>
-      <c r="XDZ7" s="17"/>
-      <c r="XEA7" s="17"/>
-      <c r="XEB7" s="17"/>
-      <c r="XEC7" s="17"/>
-      <c r="XED7" s="17"/>
-      <c r="XEE7" s="17"/>
-      <c r="XEF7" s="17"/>
-      <c r="XEG7" s="17"/>
-      <c r="XEH7" s="17"/>
-      <c r="XEI7" s="17"/>
-      <c r="XEJ7" s="17"/>
-      <c r="XEK7" s="17"/>
-      <c r="XEL7" s="17"/>
-      <c r="XEM7" s="17"/>
-      <c r="XEN7" s="17"/>
-      <c r="XEO7" s="17"/>
-      <c r="XEP7" s="17"/>
-      <c r="XEQ7" s="17"/>
-      <c r="XER7" s="17"/>
-      <c r="XES7" s="17"/>
-      <c r="XET7" s="17"/>
-      <c r="XEU7" s="17"/>
-      <c r="XEV7" s="17"/>
-      <c r="XEW7" s="17"/>
-      <c r="XEX7" s="1"/>
-      <c r="XEY7" s="1"/>
-      <c r="XEZ7" s="1"/>
-      <c r="XFA7" s="1"/>
-      <c r="XFB7" s="1"/>
-      <c r="XFC7" s="1"/>
+    <row r="7" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="AB7" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF7" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI7" s="19"/>
+      <c r="BB7" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC7" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF7" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="XDT7" s="19"/>
+      <c r="XDU7" s="19"/>
+      <c r="XDV7" s="19"/>
+      <c r="XDW7" s="19"/>
+      <c r="XDX7" s="19"/>
+      <c r="XDY7" s="19"/>
+      <c r="XDZ7" s="19"/>
+      <c r="XEA7" s="19"/>
+      <c r="XEB7" s="19"/>
+      <c r="XEC7" s="19"/>
+      <c r="XED7" s="19"/>
+      <c r="XEE7" s="19"/>
+      <c r="XEF7" s="19"/>
+      <c r="XEG7" s="19"/>
+      <c r="XEH7" s="19"/>
+      <c r="XEI7" s="19"/>
+      <c r="XEJ7" s="19"/>
+      <c r="XEK7" s="19"/>
+      <c r="XEL7" s="19"/>
+      <c r="XEM7" s="19"/>
+      <c r="XEN7" s="19"/>
+      <c r="XEO7" s="19"/>
+      <c r="XEP7" s="19"/>
+      <c r="XEQ7" s="19"/>
+      <c r="XER7" s="19"/>
+      <c r="XES7" s="19"/>
+      <c r="XET7" s="19"/>
+      <c r="XEU7" s="19"/>
+      <c r="XEV7" s="19"/>
+      <c r="XEW7" s="19"/>
+      <c r="XEX7" s="19"/>
+      <c r="XEY7" s="19"/>
+      <c r="XEZ7" s="19"/>
+      <c r="XFA7" s="19"/>
+      <c r="XFB7" s="19"/>
+      <c r="XFC7" s="19"/>
       <c r="XFD7" s="1"/>
     </row>
-    <row r="8" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="22" t="n">
+    <row r="8" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <v>143</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <f aca="false">B8/$P8/10</f>
         <v>0.0350512532661395</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>330</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">D8/$P8/10</f>
         <v>0.080887507537245</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="25" t="n">
         <v>26.4</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="24" t="n">
         <f aca="false">F8/$P8/10</f>
         <v>0.0064710006029796</v>
       </c>
-      <c r="H8" s="24" t="n">
+      <c r="H8" s="25" t="n">
         <v>920</v>
       </c>
-      <c r="I8" s="23" t="n">
+      <c r="I8" s="24" t="n">
         <f aca="false">H8/$P8/10</f>
         <v>0.225504566467471</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="23" t="n">
         <f aca="false">L8*$J$37/100</f>
         <v>185.3</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="24" t="n">
         <f aca="false">J8/$P8/10</f>
         <v>0.0454195610504591</v>
       </c>
-      <c r="L8" s="22" t="n">
+      <c r="L8" s="23" t="n">
         <v>1090</v>
       </c>
-      <c r="M8" s="22" t="n">
+      <c r="M8" s="23" t="n">
         <f aca="false">O8*$M$37/100</f>
         <v>1346.4</v>
       </c>
-      <c r="N8" s="23" t="n">
+      <c r="N8" s="24" t="n">
         <f aca="false">M8/$P8/10</f>
         <v>0.33002103075196</v>
       </c>
-      <c r="O8" s="22" t="n">
+      <c r="O8" s="23" t="n">
         <v>9900</v>
       </c>
-      <c r="P8" s="25" t="n">
+      <c r="P8" s="26" t="n">
         <v>407.974</v>
       </c>
-      <c r="Q8" s="25" t="n">
+      <c r="Q8" s="26" t="n">
         <f aca="false">100*P8/$P$36</f>
         <v>2.80209736617656</v>
       </c>
-      <c r="R8" s="22" t="n">
+      <c r="R8" s="23" t="n">
         <f aca="false">H8+F8+B8+D8+J8+M8</f>
         <v>2951.1</v>
       </c>
-      <c r="S8" s="25" t="n">
+      <c r="S8" s="26" t="n">
         <f aca="false">R8/P8</f>
         <v>7.23354919676254</v>
       </c>
-      <c r="T8" s="22" t="n">
+      <c r="T8" s="23" t="n">
         <f aca="false">124*(1.08)^4*3/5</f>
         <v>101.220378624</v>
       </c>
-      <c r="U8" s="25" t="n">
+      <c r="U8" s="26"/>
+      <c r="V8" s="0" t="n">
+        <f aca="false">T8+U8</f>
+        <v>101.220378624</v>
+      </c>
+      <c r="W8" s="27" t="n">
+        <f aca="false">3/5*H8+M8/3</f>
+        <v>1000.8</v>
+      </c>
+      <c r="X8" s="27" t="n">
+        <f aca="false">R8-V8</f>
+        <v>2849.879621376</v>
+      </c>
+      <c r="Y8" s="27" t="n">
+        <f aca="false">1000/100*Q8*($Q$41+$Q$47-$Q$49)-V8</f>
+        <v>1442.97344841541</v>
+      </c>
+      <c r="Z8" s="27" t="n">
+        <f aca="false">Y8-V8+Q8/100*1000 *($Q$46+$Q$43)</f>
+        <v>2555.55439848231</v>
+      </c>
+      <c r="AA8" s="26" t="n">
         <f aca="false">-T8+($Q$45 + $Q$46)*1000*Q8/100</f>
-        <v>1143.64219937096</v>
-      </c>
-      <c r="V8" s="25" t="n">
-        <f aca="false">U8/P8/10</f>
-        <v>0.280322324307667</v>
-      </c>
-      <c r="W8" s="25" t="n">
-        <f aca="false">U8/P8</f>
-        <v>2.80322324307667</v>
-      </c>
-      <c r="Y8" s="25" t="n">
+        <v>1162.76371179775</v>
+      </c>
+      <c r="AB8" s="26" t="n">
+        <f aca="false">AA8/P8/10</f>
+        <v>0.285009268188109</v>
+      </c>
+      <c r="AC8" s="26" t="n">
+        <f aca="false">AA8/P8</f>
+        <v>2.85009268188109</v>
+      </c>
+      <c r="AE8" s="26" t="n">
         <f aca="false">-Q8*($Q$47)*10</f>
         <v>-672.503367882374</v>
       </c>
-      <c r="Z8" s="25" t="n">
-        <f aca="false">Y8/P8/10</f>
+      <c r="AF8" s="26" t="n">
+        <f aca="false">AE8/P8/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC8" s="22" t="n">
+      <c r="AI8" s="23" t="n">
         <v>514.3</v>
       </c>
-      <c r="AH8" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI8" s="22" t="n">
+      <c r="AN8" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="AO8" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ8" s="22" t="n">
+      <c r="AP8" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="AK8" s="22" t="n">
-        <f aca="false">AI8+AJ8/100</f>
+      <c r="AQ8" s="23" t="n">
+        <f aca="false">AO8+AP8/100</f>
         <v>1.9</v>
       </c>
-      <c r="AL8" s="22" t="n">
-        <f aca="false">AK8*1000</f>
+      <c r="AR8" s="23" t="n">
+        <f aca="false">AQ8*1000</f>
         <v>1900</v>
       </c>
-      <c r="AO8" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP8" s="22" t="n">
+      <c r="AU8" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV8" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AQ8" s="22" t="n">
+      <c r="AW8" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AR8" s="26" t="n">
-        <f aca="false">AP8+AQ8/10</f>
+      <c r="AX8" s="28" t="n">
+        <f aca="false">AV8+AW8/10</f>
         <v>9.9</v>
       </c>
-      <c r="AS8" s="26" t="n">
-        <f aca="false">1000*AR8</f>
+      <c r="AY8" s="28" t="n">
+        <f aca="false">1000*AX8</f>
         <v>9900</v>
       </c>
-      <c r="AU8" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="AV8" s="22" t="n">
+      <c r="BA8" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="BB8" s="23" t="n">
         <v>1.09</v>
       </c>
-      <c r="AW8" s="22" t="n">
+      <c r="BC8" s="23" t="n">
         <v>2.43</v>
       </c>
-      <c r="AX8" s="22" t="n">
+      <c r="BD8" s="23" t="n">
         <v>2.81</v>
       </c>
-      <c r="AY8" s="22" t="n">
+      <c r="BE8" s="23" t="n">
         <v>0.86</v>
       </c>
-      <c r="AZ8" s="22" t="n">
+      <c r="BF8" s="23" t="n">
         <v>1.17</v>
       </c>
-      <c r="BA8" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="BC8" s="26" t="n">
-        <f aca="false">AV8*1000</f>
+      <c r="BG8" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="BI8" s="28" t="n">
+        <f aca="false">BB8*1000</f>
         <v>1090</v>
       </c>
-      <c r="BE8" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="BF8" s="22" t="n">
+      <c r="BK8" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="BL8" s="23" t="n">
         <v>148</v>
       </c>
-      <c r="BG8" s="22" t="n">
+      <c r="BM8" s="23" t="n">
         <v>105</v>
       </c>
-      <c r="BH8" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="BI8" s="22" t="n">
+      <c r="BN8" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="BO8" s="23" t="n">
         <v>143</v>
       </c>
-      <c r="BK8" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="BL8" s="22" t="n">
+      <c r="BQ8" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="BR8" s="23" t="n">
         <v>330</v>
       </c>
-      <c r="BM8" s="22" t="s">
-        <v>44</v>
+      <c r="BS8" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="9" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="22" t="n">
+    <row r="9" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="23" t="n">
         <v>201</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <f aca="false">B9/$P9/10</f>
         <v>0.0396480984693072</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>184</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="24" t="n">
         <f aca="false">D9/$P9/10</f>
         <v>0.0362947767082216</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="30" t="n">
         <v>61.1</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="24" t="n">
         <f aca="false">F9/$P9/10</f>
         <v>0.0120522329177844</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="30" t="n">
         <v>722</v>
       </c>
-      <c r="I9" s="23" t="n">
+      <c r="I9" s="24" t="n">
         <f aca="false">H9/$P9/10</f>
         <v>0.142417547735522</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="23" t="n">
         <f aca="false">L9*$J$37/100</f>
         <v>187</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="24" t="n">
         <f aca="false">J9/$P9/10</f>
         <v>0.0368865393719426</v>
       </c>
-      <c r="L9" s="22" t="n">
+      <c r="L9" s="23" t="n">
         <v>1100</v>
       </c>
-      <c r="M9" s="22" t="n">
+      <c r="M9" s="23" t="n">
         <f aca="false">O9*$M$37/100</f>
         <v>1332.8</v>
       </c>
-      <c r="N9" s="23" t="n">
+      <c r="N9" s="24" t="n">
         <f aca="false">M9/$P9/10</f>
         <v>0.262900426069118</v>
       </c>
-      <c r="O9" s="22" t="n">
+      <c r="O9" s="23" t="n">
         <v>9800</v>
       </c>
-      <c r="P9" s="25" t="n">
+      <c r="P9" s="26" t="n">
         <v>506.96</v>
       </c>
-      <c r="Q9" s="25" t="n">
+      <c r="Q9" s="26" t="n">
         <f aca="false">100*P9/$P$36</f>
         <v>3.48196522512922</v>
       </c>
-      <c r="R9" s="22" t="n">
+      <c r="R9" s="23" t="n">
         <f aca="false">H9+F9+B9+D9+J9+M9</f>
         <v>2687.9</v>
       </c>
-      <c r="S9" s="25" t="n">
+      <c r="S9" s="26" t="n">
         <f aca="false">R9/P9</f>
         <v>5.30199621271895</v>
       </c>
-      <c r="T9" s="29" t="n">
+      <c r="T9" s="26"/>
+      <c r="U9" s="31" t="n">
         <f aca="false">F9</f>
         <v>61.1</v>
       </c>
-      <c r="U9" s="25" t="n">
-        <f aca="false">-T9+($Q$45 + $Q$46)*1000*Q9/100</f>
-        <v>1485.80135288113</v>
-      </c>
-      <c r="V9" s="25" t="n">
-        <f aca="false">U9/P9/10</f>
-        <v>0.293080588780403</v>
-      </c>
-      <c r="W9" s="25" t="n">
-        <f aca="false">U9/P9</f>
-        <v>2.93080588780403</v>
-      </c>
-      <c r="Y9" s="25" t="n">
+      <c r="V9" s="0" t="n">
+        <f aca="false">T9+U9</f>
+        <v>61.1</v>
+      </c>
+      <c r="W9" s="27" t="n">
+        <f aca="false">3/5*H9+M9/3</f>
+        <v>877.466666666667</v>
+      </c>
+      <c r="X9" s="27" t="n">
+        <f aca="false">R9-V9</f>
+        <v>2626.8</v>
+      </c>
+      <c r="Y9" s="27" t="n">
+        <f aca="false">1000/100*Q9*($Q$41+$Q$47-$Q$49)-V9</f>
+        <v>1857.75880609034</v>
+      </c>
+      <c r="Z9" s="27" t="n">
+        <f aca="false">Y9-V9+Q9/100*1000 *($Q$46+$Q$43)</f>
+        <v>3304.96257445091</v>
+      </c>
+      <c r="AA9" s="26" t="n">
+        <f aca="false">-U9+($Q$45 + $Q$46)*1000*Q9/100</f>
+        <v>1509.56228357741</v>
+      </c>
+      <c r="AB9" s="26" t="n">
+        <f aca="false">AA9/P9/10</f>
+        <v>0.297767532660844</v>
+      </c>
+      <c r="AC9" s="26" t="n">
+        <f aca="false">AA9/P9</f>
+        <v>2.97767532660844</v>
+      </c>
+      <c r="AE9" s="26" t="n">
         <f aca="false">-Q9*($Q$47)*10</f>
         <v>-835.671654031012</v>
       </c>
-      <c r="Z9" s="25" t="n">
-        <f aca="false">Y9/P9/10</f>
+      <c r="AF9" s="26" t="n">
+        <f aca="false">AE9/P9/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC9" s="22" t="n">
+      <c r="AI9" s="23" t="n">
         <v>642</v>
       </c>
-      <c r="AH9" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI9" s="22" t="n">
+      <c r="AN9" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ9" s="22" t="n">
+      <c r="AP9" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="AK9" s="22" t="n">
-        <f aca="false">AI9+AJ9/100</f>
+      <c r="AQ9" s="23" t="n">
+        <f aca="false">AO9+AP9/100</f>
         <v>1.1</v>
       </c>
-      <c r="AL9" s="22" t="n">
-        <f aca="false">AK9*1000</f>
+      <c r="AR9" s="23" t="n">
+        <f aca="false">AQ9*1000</f>
         <v>1100</v>
       </c>
-      <c r="AO9" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="AP9" s="22" t="n">
+      <c r="AU9" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV9" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AQ9" s="22" t="n">
+      <c r="AW9" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="AR9" s="26" t="n">
-        <f aca="false">AP9+AQ9/10</f>
+      <c r="AX9" s="28" t="n">
+        <f aca="false">AV9+AW9/10</f>
         <v>9.8</v>
       </c>
-      <c r="AS9" s="26" t="n">
-        <f aca="false">1000*AR9</f>
+      <c r="AY9" s="28" t="n">
+        <f aca="false">1000*AX9</f>
         <v>9800</v>
       </c>
-      <c r="AU9" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV9" s="22" t="n">
+      <c r="BA9" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB9" s="23" t="n">
         <v>1.1</v>
       </c>
-      <c r="AW9" s="22" t="n">
+      <c r="BC9" s="23" t="n">
         <v>2.45</v>
       </c>
-      <c r="AX9" s="22" t="n">
+      <c r="BD9" s="23" t="n">
         <v>3.46</v>
       </c>
-      <c r="AY9" s="22" t="n">
+      <c r="BE9" s="23" t="n">
         <v>0.71</v>
       </c>
-      <c r="AZ9" s="22" t="n">
+      <c r="BF9" s="23" t="n">
         <v>0.96</v>
       </c>
-      <c r="BA9" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="BC9" s="26" t="n">
-        <f aca="false">AV9*1000</f>
+      <c r="BG9" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="BI9" s="28" t="n">
+        <f aca="false">BB9*1000</f>
         <v>1100</v>
       </c>
-      <c r="BE9" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="BF9" s="22" t="n">
+      <c r="BK9" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="BL9" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="BG9" s="22" t="n">
+      <c r="BM9" s="23" t="n">
         <v>148</v>
       </c>
-      <c r="BH9" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI9" s="22" t="n">
+      <c r="BN9" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO9" s="23" t="n">
         <v>201</v>
       </c>
-      <c r="BK9" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="BL9" s="22" t="n">
+      <c r="BQ9" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="BR9" s="23" t="n">
         <v>184</v>
       </c>
-      <c r="BM9" s="22" t="s">
-        <v>51</v>
+      <c r="BS9" s="23" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="10" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="22" t="n">
+    <row r="10" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="24" t="n">
         <f aca="false">B10/$P10/10</f>
         <v>0.0726008291778911</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="24" t="n">
         <f aca="false">D10/$P10/10</f>
         <v>0.0343898664526853</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="24" t="n">
         <f aca="false">F10/$P10/10</f>
         <v>0.000382109627252059</v>
       </c>
-      <c r="H10" s="24" t="n">
+      <c r="H10" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="I10" s="23" t="n">
+      <c r="I10" s="24" t="n">
         <f aca="false">H10/$P10/10</f>
         <v>0.0764219254504117</v>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="23" t="n">
         <f aca="false">L10*$J$37/100</f>
         <v>45.9</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="24" t="n">
         <f aca="false">J10/$P10/10</f>
         <v>0.0876941594543474</v>
       </c>
-      <c r="L10" s="22" t="n">
+      <c r="L10" s="23" t="n">
         <v>270</v>
       </c>
-      <c r="M10" s="22" t="n">
+      <c r="M10" s="23" t="n">
         <f aca="false">O10*$M$37/100</f>
         <v>217.6</v>
       </c>
-      <c r="N10" s="23" t="n">
+      <c r="N10" s="24" t="n">
         <f aca="false">M10/$P10/10</f>
         <v>0.41573527445024</v>
       </c>
-      <c r="O10" s="22" t="n">
+      <c r="O10" s="23" t="n">
         <v>1600</v>
       </c>
-      <c r="P10" s="25" t="n">
+      <c r="P10" s="26" t="n">
         <v>52.341</v>
       </c>
-      <c r="Q10" s="25" t="n">
+      <c r="Q10" s="26" t="n">
         <f aca="false">100*P10/$P$36</f>
         <v>0.359494914487313</v>
       </c>
-      <c r="R10" s="22" t="n">
+      <c r="R10" s="23" t="n">
         <f aca="false">H10+F10+B10+D10+J10+M10</f>
         <v>359.7</v>
       </c>
-      <c r="S10" s="25" t="n">
+      <c r="S10" s="26" t="n">
         <f aca="false">R10/P10</f>
         <v>6.87224164612827</v>
       </c>
-      <c r="U10" s="25" t="n">
-        <f aca="false">-T10+($Q$45 + $Q$46)*1000*Q10/100</f>
-        <v>159.709570205048</v>
-      </c>
-      <c r="V10" s="25" t="n">
-        <f aca="false">U10/P10/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W10" s="25" t="n">
-        <f aca="false">U10/P10</f>
-        <v>3.05132821698187</v>
-      </c>
-      <c r="Y10" s="25" t="n">
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="0" t="n">
+        <f aca="false">T10+U10</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="27" t="n">
+        <f aca="false">3/5*H10+M10/3</f>
+        <v>96.5333333333333</v>
+      </c>
+      <c r="X10" s="27" t="n">
+        <f aca="false">R10-V10</f>
+        <v>359.7</v>
+      </c>
+      <c r="Y10" s="27" t="n">
+        <f aca="false">1000/100*Q10*($Q$41+$Q$47-$Q$49)-V10</f>
+        <v>198.112254950241</v>
+      </c>
+      <c r="Z10" s="27" t="n">
+        <f aca="false">Y10-V10+Q10/100*1000 *($Q$46+$Q$43)</f>
+        <v>353.836824028197</v>
+      </c>
+      <c r="AA10" s="26" t="n">
+        <f aca="false">-V10+($Q$45 + $Q$46)*1000*Q10/100</f>
+        <v>162.16276350151</v>
+      </c>
+      <c r="AB10" s="26" t="n">
+        <f aca="false">AA10/P10/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC10" s="26" t="n">
+        <f aca="false">AA10/P10</f>
+        <v>3.09819765578628</v>
+      </c>
+      <c r="AE10" s="26" t="n">
         <f aca="false">-Q10*($Q$47)*10</f>
         <v>-86.2787794769552</v>
       </c>
-      <c r="Z10" s="25" t="n">
-        <f aca="false">Y10/P10/10</f>
+      <c r="AF10" s="26" t="n">
+        <f aca="false">AE10/P10/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC10" s="22" t="n">
+      <c r="AI10" s="23" t="n">
         <v>116</v>
       </c>
-      <c r="AH10" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI10" s="22" t="n">
+      <c r="AN10" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" s="22" t="n">
+      <c r="AP10" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="AK10" s="22" t="n">
-        <f aca="false">AI10+AJ10/100</f>
+      <c r="AQ10" s="23" t="n">
+        <f aca="false">AO10+AP10/100</f>
         <v>0.27</v>
       </c>
-      <c r="AL10" s="22" t="n">
-        <f aca="false">AK10*1000</f>
+      <c r="AR10" s="23" t="n">
+        <f aca="false">AQ10*1000</f>
         <v>270</v>
       </c>
-      <c r="AO10" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP10" s="22" t="n">
+      <c r="AU10" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="AV10" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AQ10" s="22" t="n">
+      <c r="AW10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AR10" s="26" t="n">
-        <f aca="false">AP10+AQ10/10</f>
+      <c r="AX10" s="28" t="n">
+        <f aca="false">AV10+AW10/10</f>
         <v>1.6</v>
       </c>
-      <c r="AS10" s="26" t="n">
-        <f aca="false">1000*AR10</f>
+      <c r="AY10" s="28" t="n">
+        <f aca="false">1000*AX10</f>
         <v>1600</v>
       </c>
-      <c r="AU10" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV10" s="22" t="n">
+      <c r="BA10" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="BB10" s="23" t="n">
         <v>0.27</v>
       </c>
-      <c r="AW10" s="22" t="n">
+      <c r="BC10" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="AX10" s="22" t="n">
+      <c r="BD10" s="23" t="n">
         <v>0.55</v>
       </c>
-      <c r="AY10" s="22" t="n">
+      <c r="BE10" s="23" t="n">
         <v>1.09</v>
       </c>
-      <c r="AZ10" s="22" t="n">
+      <c r="BF10" s="23" t="n">
         <v>1.48</v>
       </c>
-      <c r="BA10" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="BC10" s="26" t="n">
-        <f aca="false">AV10*1000</f>
+      <c r="BG10" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="BI10" s="28" t="n">
+        <f aca="false">BB10*1000</f>
         <v>270</v>
       </c>
-      <c r="BE10" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="BF10" s="22" t="n">
+      <c r="BK10" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="BL10" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="BG10" s="22" t="n">
+      <c r="BM10" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="BH10" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI10" s="22" t="n">
+      <c r="BN10" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO10" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="BK10" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="BL10" s="22" t="n">
+      <c r="BQ10" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="BR10" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="BM10" s="22" t="s">
-        <v>56</v>
+      <c r="BS10" s="23" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="11" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="22" t="n">
+    <row r="11" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <v>46</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="24" t="n">
         <f aca="false">B11/$P11/10</f>
         <v>0.0786755148115208</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="24" t="n">
         <f aca="false">D11/$P11/10</f>
         <v>0.0444687692412944</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="24" t="n">
         <f aca="false">F11/$P11/10</f>
         <v>0.000513101183553397</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="24" t="n">
         <f aca="false">H11/$P11/10</f>
         <v>0.0615721420264076</v>
       </c>
-      <c r="J11" s="22" t="n">
+      <c r="J11" s="23" t="n">
         <f aca="false">L11*$J$37/100</f>
         <v>64.6</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="24" t="n">
         <f aca="false">J11/$P11/10</f>
         <v>0.110487788191831</v>
       </c>
-      <c r="L11" s="22" t="n">
+      <c r="L11" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="M11" s="22" t="n">
+      <c r="M11" s="23" t="n">
         <f aca="false">O11*$M$37/100</f>
         <v>312.8</v>
       </c>
-      <c r="N11" s="23" t="n">
+      <c r="N11" s="24" t="n">
         <f aca="false">M11/$P11/10</f>
         <v>0.534993500718342</v>
       </c>
-      <c r="O11" s="22" t="n">
+      <c r="O11" s="23" t="n">
         <v>2300</v>
       </c>
-      <c r="P11" s="25" t="n">
+      <c r="P11" s="26" t="n">
         <v>58.468</v>
       </c>
-      <c r="Q11" s="25" t="n">
+      <c r="Q11" s="26" t="n">
         <f aca="false">100*P11/$P$36</f>
         <v>0.401577131889804</v>
       </c>
-      <c r="R11" s="22" t="n">
+      <c r="R11" s="23" t="n">
         <f aca="false">H11+F11+B11+D11+J11+M11</f>
         <v>485.7</v>
       </c>
-      <c r="S11" s="25" t="n">
+      <c r="S11" s="26" t="n">
         <f aca="false">R11/P11</f>
         <v>8.30710816172949</v>
       </c>
-      <c r="U11" s="25" t="n">
-        <f aca="false">-T11+($Q$45 + $Q$46)*1000*Q11/100</f>
-        <v>178.405058190496</v>
-      </c>
-      <c r="V11" s="25" t="n">
-        <f aca="false">U11/P11/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W11" s="25" t="n">
-        <f aca="false">ROUND(U11/P11 *100/1000, 2)</f>
+      <c r="T11" s="26"/>
+      <c r="U11" s="26"/>
+      <c r="V11" s="0" t="n">
+        <f aca="false">T11+U11</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="27" t="n">
+        <f aca="false">3/5*H11+M11/3</f>
+        <v>125.866666666667</v>
+      </c>
+      <c r="X11" s="27" t="n">
+        <f aca="false">R11-V11</f>
+        <v>485.7</v>
+      </c>
+      <c r="Y11" s="27" t="n">
+        <f aca="false">1000/100*Q11*($Q$41+$Q$47-$Q$49)-V11</f>
+        <v>221.303133727493</v>
+      </c>
+      <c r="Z11" s="27" t="n">
+        <f aca="false">Y11-V11+Q11/100*1000 *($Q$46+$Q$43)</f>
+        <v>395.25670941099</v>
+      </c>
+      <c r="AA11" s="26" t="n">
+        <f aca="false">-V11+($Q$45 + $Q$46)*1000*Q11/100</f>
+        <v>181.145420538512</v>
+      </c>
+      <c r="AB11" s="26" t="n">
+        <f aca="false">AA11/P11/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC11" s="26" t="n">
+        <f aca="false">ROUND(AA11/P11 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y11" s="25" t="n">
+      <c r="AE11" s="26" t="n">
         <f aca="false">-Q11*($Q$47)*10</f>
         <v>-96.378511653553</v>
       </c>
-      <c r="Z11" s="25" t="n">
-        <f aca="false">Y11/P11/10</f>
+      <c r="AF11" s="26" t="n">
+        <f aca="false">AE11/P11/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC11" s="22" t="n">
+      <c r="AI11" s="23" t="n">
         <v>93</v>
       </c>
-      <c r="AH11" s="22" t="s">
+      <c r="AN11" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ11" s="23" t="n">
+        <f aca="false">AO11+AP11/100</f>
+        <v>0.38</v>
+      </c>
+      <c r="AR11" s="23" t="n">
+        <f aca="false">AQ11*1000</f>
+        <v>380</v>
+      </c>
+      <c r="AU11" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV11" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW11" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX11" s="28" t="n">
+        <f aca="false">AV11+AW11/10</f>
+        <v>2.3</v>
+      </c>
+      <c r="AY11" s="28" t="n">
+        <f aca="false">1000*AX11</f>
+        <v>2300</v>
+      </c>
+      <c r="BA11" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB11" s="23" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BC11" s="23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BD11" s="23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BE11" s="23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF11" s="23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BG11" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="BI11" s="28" t="n">
+        <f aca="false">BB11*1000</f>
+        <v>380</v>
+      </c>
+      <c r="BK11" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL11" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BM11" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BN11" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="AI11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK11" s="22" t="n">
-        <f aca="false">AI11+AJ11/100</f>
-        <v>0.38</v>
-      </c>
-      <c r="AL11" s="22" t="n">
-        <f aca="false">AK11*1000</f>
-        <v>380</v>
-      </c>
-      <c r="AO11" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="AP11" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ11" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR11" s="26" t="n">
-        <f aca="false">AP11+AQ11/10</f>
-        <v>2.3</v>
-      </c>
-      <c r="AS11" s="26" t="n">
-        <f aca="false">1000*AR11</f>
-        <v>2300</v>
-      </c>
-      <c r="AU11" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="AV11" s="22" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AW11" s="22" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AX11" s="22" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AY11" s="22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AZ11" s="22" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BA11" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="BC11" s="26" t="n">
-        <f aca="false">AV11*1000</f>
-        <v>380</v>
-      </c>
-      <c r="BE11" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="BF11" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG11" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH11" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI11" s="22" t="n">
+      <c r="BO11" s="23" t="n">
         <v>46</v>
       </c>
-      <c r="BK11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BL11" s="22" t="n">
+      <c r="BQ11" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="BR11" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="BM11" s="22" t="s">
-        <v>61</v>
+      <c r="BS11" s="23" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="12" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="22" t="n">
+    <row r="12" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="24" t="n">
         <f aca="false">B12/$P12/10</f>
         <v>0.0727603456116417</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="24" t="n">
         <f aca="false">D12/$P12/10</f>
         <v>0.0773078672123693</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="24" t="n">
         <f aca="false">F12/$P12/10</f>
         <v>0.00363801728058208</v>
       </c>
-      <c r="H12" s="24" t="n">
+      <c r="H12" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="I12" s="23" t="n">
+      <c r="I12" s="24" t="n">
         <f aca="false">H12/$P12/10</f>
         <v>0.20918599363347</v>
       </c>
-      <c r="J12" s="22" t="n">
+      <c r="J12" s="23" t="n">
         <f aca="false">L12*$J$37/100</f>
         <v>49.3</v>
       </c>
-      <c r="K12" s="23" t="n">
+      <c r="K12" s="24" t="n">
         <f aca="false">J12/$P12/10</f>
         <v>0.224192814915871</v>
       </c>
-      <c r="L12" s="22" t="n">
+      <c r="L12" s="23" t="n">
         <v>290</v>
       </c>
-      <c r="M12" s="22" t="n">
+      <c r="M12" s="23" t="n">
         <f aca="false">O12*$M$37/100</f>
         <v>204</v>
       </c>
-      <c r="N12" s="23" t="n">
+      <c r="N12" s="24" t="n">
         <f aca="false">M12/$P12/10</f>
         <v>0.927694406548431</v>
       </c>
-      <c r="O12" s="22" t="n">
+      <c r="O12" s="23" t="n">
         <v>1500</v>
       </c>
-      <c r="P12" s="25" t="n">
+      <c r="P12" s="26" t="n">
         <v>21.99</v>
       </c>
-      <c r="Q12" s="25" t="n">
+      <c r="Q12" s="26" t="n">
         <f aca="false">100*P12/$P$36</f>
         <v>0.151034431317247</v>
       </c>
-      <c r="R12" s="22" t="n">
+      <c r="R12" s="23" t="n">
         <f aca="false">H12+F12+B12+D12+J12+M12</f>
         <v>333.1</v>
       </c>
-      <c r="S12" s="25" t="n">
+      <c r="S12" s="26" t="n">
         <f aca="false">R12/P12</f>
         <v>15.1477944520237</v>
       </c>
-      <c r="U12" s="25" t="n">
-        <f aca="false">-T12+($Q$45 + $Q$46)*1000*Q12/100</f>
-        <v>67.0987074914314</v>
-      </c>
-      <c r="V12" s="25" t="n">
-        <f aca="false">U12/P12/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W12" s="25" t="n">
-        <f aca="false">ROUND(U12/P12 *100/1000, 2)</f>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="0" t="n">
+        <f aca="false">T12+U12</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="27" t="n">
+        <f aca="false">3/5*H12+M12/3</f>
+        <v>95.6</v>
+      </c>
+      <c r="X12" s="27" t="n">
+        <f aca="false">R12-V12</f>
+        <v>333.1</v>
+      </c>
+      <c r="Y12" s="27" t="n">
+        <f aca="false">1000/100*Q12*($Q$41+$Q$47-$Q$49)-V12</f>
+        <v>83.2328095824651</v>
+      </c>
+      <c r="Z12" s="27" t="n">
+        <f aca="false">Y12-V12+Q12/100*1000 *($Q$46+$Q$43)</f>
+        <v>148.657300402745</v>
+      </c>
+      <c r="AA12" s="26" t="n">
+        <f aca="false">-V12+($Q$45 + $Q$46)*1000*Q12/100</f>
+        <v>68.1293664507404</v>
+      </c>
+      <c r="AB12" s="26" t="n">
+        <f aca="false">AA12/P12/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC12" s="26" t="n">
+        <f aca="false">ROUND(AA12/P12 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y12" s="25" t="n">
+      <c r="AE12" s="26" t="n">
         <f aca="false">-Q12*($Q$47)*10</f>
         <v>-36.2482635161393</v>
       </c>
-      <c r="Z12" s="25" t="n">
-        <f aca="false">Y12/P12/10</f>
+      <c r="AF12" s="26" t="n">
+        <f aca="false">AE12/P12/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC12" s="22" t="n">
+      <c r="AI12" s="23" t="n">
         <v>36.5</v>
       </c>
-      <c r="AH12" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI12" s="22" t="n">
+      <c r="AN12" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO12" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ12" s="22" t="n">
+      <c r="AP12" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="AK12" s="22" t="n">
-        <f aca="false">AI12+AJ12/100</f>
+      <c r="AQ12" s="23" t="n">
+        <f aca="false">AO12+AP12/100</f>
         <v>0.29</v>
       </c>
-      <c r="AL12" s="22" t="n">
-        <f aca="false">AK12*1000</f>
+      <c r="AR12" s="23" t="n">
+        <f aca="false">AQ12*1000</f>
         <v>290</v>
       </c>
-      <c r="AO12" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="AP12" s="22" t="n">
+      <c r="AU12" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="AV12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AQ12" s="22" t="n">
+      <c r="AW12" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="AR12" s="26" t="n">
-        <f aca="false">AP12+AQ12/10</f>
+      <c r="AX12" s="28" t="n">
+        <f aca="false">AV12+AW12/10</f>
         <v>1.5</v>
       </c>
-      <c r="AS12" s="26" t="n">
-        <f aca="false">1000*AR12</f>
+      <c r="AY12" s="28" t="n">
+        <f aca="false">1000*AX12</f>
         <v>1500</v>
       </c>
-      <c r="AU12" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="AV12" s="22" t="n">
+      <c r="BA12" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="BB12" s="23" t="n">
         <v>0.29</v>
       </c>
-      <c r="AW12" s="22" t="n">
+      <c r="BC12" s="23" t="n">
         <v>0.64</v>
       </c>
-      <c r="AX12" s="22" t="n">
+      <c r="BD12" s="23" t="n">
         <v>0.16</v>
       </c>
-      <c r="AY12" s="22" t="n">
+      <c r="BE12" s="23" t="n">
         <v>3.9</v>
       </c>
-      <c r="AZ12" s="22" t="n">
+      <c r="BF12" s="23" t="n">
         <v>5.29</v>
       </c>
-      <c r="BA12" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC12" s="26" t="n">
-        <f aca="false">AV12*1000</f>
+      <c r="BG12" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI12" s="28" t="n">
+        <f aca="false">BB12*1000</f>
         <v>290</v>
       </c>
-      <c r="BE12" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="BF12" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="BG12" s="22" t="n">
+      <c r="BK12" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL12" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM12" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="BH12" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI12" s="22" t="n">
+      <c r="BN12" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO12" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="BK12" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="BL12" s="22" t="n">
+      <c r="BQ12" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="BR12" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="BM12" s="22" t="s">
-        <v>68</v>
+      <c r="BS12" s="23" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="13" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="22" t="n">
+    <row r="13" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="23" t="n">
         <v>178</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="24" t="n">
         <f aca="false">B13/$P13/10</f>
         <v>0.0782166601486116</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>263</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <f aca="false">D13/$P13/10</f>
         <v>0.115567312466769</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="30" t="n">
         <v>3.8</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="24" t="n">
         <f aca="false">F13/$P13/10</f>
         <v>0.00166979386834115</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="30" t="n">
         <v>348</v>
       </c>
-      <c r="I13" s="23" t="n">
+      <c r="I13" s="24" t="n">
         <f aca="false">H13/$P13/10</f>
         <v>0.152917964784926</v>
       </c>
-      <c r="J13" s="22" t="n">
+      <c r="J13" s="23" t="n">
         <f aca="false">L13*$J$37/100</f>
         <v>74.8</v>
       </c>
-      <c r="K13" s="23" t="n">
+      <c r="K13" s="24" t="n">
         <f aca="false">J13/$P13/10</f>
         <v>0.0328685740399784</v>
       </c>
-      <c r="L13" s="22" t="n">
+      <c r="L13" s="23" t="n">
         <v>440</v>
       </c>
-      <c r="M13" s="22" t="n">
+      <c r="M13" s="23" t="n">
         <f aca="false">O13*$M$37/100</f>
         <v>625.6</v>
       </c>
-      <c r="N13" s="23" t="n">
+      <c r="N13" s="24" t="n">
         <f aca="false">M13/$P13/10</f>
         <v>0.274900801061637</v>
       </c>
-      <c r="O13" s="22" t="n">
+      <c r="O13" s="23" t="n">
         <v>4600</v>
       </c>
-      <c r="P13" s="25" t="n">
+      <c r="P13" s="26" t="n">
         <v>227.573</v>
       </c>
-      <c r="Q13" s="25" t="n">
+      <c r="Q13" s="26" t="n">
         <f aca="false">100*P13/$P$36</f>
         <v>1.56304495853387</v>
       </c>
-      <c r="R13" s="22" t="n">
+      <c r="R13" s="23" t="n">
         <f aca="false">H13+F13+B13+D13+J13+M13</f>
         <v>1493.2</v>
       </c>
-      <c r="S13" s="25" t="n">
+      <c r="S13" s="26" t="n">
         <f aca="false">R13/P13</f>
         <v>6.56141106370264</v>
       </c>
-      <c r="U13" s="25" t="n">
-        <f aca="false">-T13+($Q$45 + $Q$46)*1000*Q13/100</f>
-        <v>694.399916323216</v>
-      </c>
-      <c r="V13" s="25" t="n">
-        <f aca="false">U13/P13/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W13" s="25" t="n">
-        <f aca="false">ROUND(U13/P13 *100/1000, 2)</f>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="0" t="n">
+        <f aca="false">T13+U13</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="27" t="n">
+        <f aca="false">3/5*H13+M13/3</f>
+        <v>417.333333333333</v>
+      </c>
+      <c r="X13" s="27" t="n">
+        <f aca="false">R13-V13</f>
+        <v>1493.2</v>
+      </c>
+      <c r="Y13" s="27" t="n">
+        <f aca="false">1000/100*Q13*($Q$41+$Q$47-$Q$49)-V13</f>
+        <v>861.370630973638</v>
+      </c>
+      <c r="Z13" s="27" t="n">
+        <f aca="false">Y13-V13+Q13/100*1000 *($Q$46+$Q$43)</f>
+        <v>1538.44419393151</v>
+      </c>
+      <c r="AA13" s="26" t="n">
+        <f aca="false">-V13+($Q$45 + $Q$46)*1000*Q13/100</f>
+        <v>705.066135120251</v>
+      </c>
+      <c r="AB13" s="26" t="n">
+        <f aca="false">AA13/P13/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC13" s="26" t="n">
+        <f aca="false">ROUND(AA13/P13 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y13" s="25" t="n">
+      <c r="AE13" s="26" t="n">
         <f aca="false">-Q13*($Q$47)*10</f>
         <v>-375.130790048129</v>
       </c>
-      <c r="Z13" s="25" t="n">
-        <f aca="false">Y13/P13/10</f>
+      <c r="AF13" s="26" t="n">
+        <f aca="false">AE13/P13/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC13" s="22" t="n">
+      <c r="AI13" s="23" t="n">
         <v>347.3</v>
       </c>
-      <c r="AH13" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI13" s="22" t="n">
+      <c r="AN13" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ13" s="22" t="n">
+      <c r="AP13" s="23" t="n">
         <v>44</v>
       </c>
-      <c r="AK13" s="22" t="n">
-        <f aca="false">AI13+AJ13/100</f>
+      <c r="AQ13" s="23" t="n">
+        <f aca="false">AO13+AP13/100</f>
         <v>0.44</v>
       </c>
-      <c r="AL13" s="22" t="n">
-        <f aca="false">AK13*1000</f>
+      <c r="AR13" s="23" t="n">
+        <f aca="false">AQ13*1000</f>
         <v>440</v>
       </c>
-      <c r="AO13" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP13" s="22" t="n">
+      <c r="AU13" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV13" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="AQ13" s="22" t="n">
+      <c r="AW13" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AR13" s="26" t="n">
-        <f aca="false">AP13+AQ13/10</f>
+      <c r="AX13" s="28" t="n">
+        <f aca="false">AV13+AW13/10</f>
         <v>4.6</v>
       </c>
-      <c r="AS13" s="26" t="n">
-        <f aca="false">1000*AR13</f>
+      <c r="AY13" s="28" t="n">
+        <f aca="false">1000*AX13</f>
         <v>4600</v>
       </c>
-      <c r="AU13" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="AV13" s="22" t="n">
+      <c r="BA13" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB13" s="23" t="n">
         <v>0.44</v>
       </c>
-      <c r="AW13" s="22" t="n">
+      <c r="BC13" s="23" t="n">
         <v>0.98</v>
       </c>
-      <c r="AX13" s="22" t="n">
+      <c r="BD13" s="23" t="n">
         <v>1.68</v>
       </c>
-      <c r="AY13" s="22" t="n">
+      <c r="BE13" s="23" t="n">
         <v>0.58</v>
       </c>
-      <c r="AZ13" s="22" t="n">
+      <c r="BF13" s="23" t="n">
         <v>0.79</v>
       </c>
-      <c r="BA13" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="BC13" s="26" t="n">
-        <f aca="false">AV13*1000</f>
+      <c r="BG13" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="BI13" s="28" t="n">
+        <f aca="false">BB13*1000</f>
         <v>440</v>
       </c>
-      <c r="BE13" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="BF13" s="22" t="n">
+      <c r="BK13" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="BL13" s="23" t="n">
         <v>118</v>
       </c>
-      <c r="BG13" s="22" t="n">
+      <c r="BM13" s="23" t="n">
         <v>131</v>
       </c>
-      <c r="BH13" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI13" s="22" t="n">
+      <c r="BN13" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO13" s="23" t="n">
         <v>178</v>
       </c>
-      <c r="BK13" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL13" s="22" t="n">
+      <c r="BQ13" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="BR13" s="23" t="n">
         <v>263</v>
       </c>
-      <c r="BM13" s="22" t="s">
-        <v>75</v>
+      <c r="BS13" s="23" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="14" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="22" t="n">
+    <row r="14" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <v>108</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="24" t="n">
         <f aca="false">B14/$P14/10</f>
         <v>0.0310018773359053</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>258</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="24" t="n">
         <f aca="false">D14/$P14/10</f>
         <v>0.0740600403024405</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="25" t="n">
         <v>113.8</v>
       </c>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="24" t="n">
         <f aca="false">F14/$P14/10</f>
         <v>0.0326667929706114</v>
       </c>
-      <c r="H14" s="24" t="n">
+      <c r="H14" s="25" t="n">
         <v>533</v>
       </c>
-      <c r="I14" s="23" t="n">
+      <c r="I14" s="24" t="n">
         <f aca="false">H14/$P14/10</f>
         <v>0.153000005741088</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="23" t="n">
         <f aca="false">L14*$J$37/100</f>
         <v>192.1</v>
       </c>
-      <c r="K14" s="23" t="n">
+      <c r="K14" s="24" t="n">
         <f aca="false">J14/$P14/10</f>
         <v>0.0551431540391427</v>
       </c>
-      <c r="L14" s="22" t="n">
+      <c r="L14" s="23" t="n">
         <v>1130</v>
       </c>
-      <c r="M14" s="22" t="n">
+      <c r="M14" s="23" t="n">
         <f aca="false">O14*$M$37/100</f>
         <v>571.2</v>
       </c>
-      <c r="N14" s="23" t="n">
+      <c r="N14" s="24" t="n">
         <f aca="false">M14/$P14/10</f>
         <v>0.163965484576566</v>
       </c>
-      <c r="O14" s="22" t="n">
+      <c r="O14" s="23" t="n">
         <v>4200</v>
       </c>
-      <c r="P14" s="25" t="n">
+      <c r="P14" s="26" t="n">
         <v>348.366</v>
       </c>
-      <c r="Q14" s="25" t="n">
+      <c r="Q14" s="26" t="n">
         <f aca="false">100*P14/$P$36</f>
         <v>2.39269034562365</v>
       </c>
-      <c r="R14" s="22" t="n">
+      <c r="R14" s="23" t="n">
         <f aca="false">H14+F14+B14+D14+J14+M14</f>
         <v>1776.1</v>
       </c>
-      <c r="S14" s="25" t="n">
+      <c r="S14" s="26" t="n">
         <f aca="false">R14/P14</f>
         <v>5.09837354965754</v>
       </c>
-      <c r="U14" s="25" t="n">
-        <f aca="false">-T14+($Q$45 + $Q$46)*1000*Q14/100</f>
-        <v>1062.97900563711</v>
-      </c>
-      <c r="V14" s="25" t="n">
-        <f aca="false">U14/P14/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W14" s="25" t="n">
-        <f aca="false">ROUND(U14/P14 *100/1000, 2)</f>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="0" t="n">
+        <f aca="false">T14+U14</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="27" t="n">
+        <f aca="false">3/5*H14+M14/3</f>
+        <v>510.2</v>
+      </c>
+      <c r="X14" s="27" t="n">
+        <f aca="false">R14-V14</f>
+        <v>1776.1</v>
+      </c>
+      <c r="Y14" s="27" t="n">
+        <f aca="false">1000/100*Q14*($Q$41+$Q$47-$Q$49)-V14</f>
+        <v>1318.57575911801</v>
+      </c>
+      <c r="Z14" s="27" t="n">
+        <f aca="false">Y14-V14+Q14/100*1000 *($Q$46+$Q$43)</f>
+        <v>2355.03179227388</v>
+      </c>
+      <c r="AA14" s="26" t="n">
+        <f aca="false">-V14+($Q$45 + $Q$46)*1000*Q14/100</f>
+        <v>1079.30672455564</v>
+      </c>
+      <c r="AB14" s="26" t="n">
+        <f aca="false">AA14/P14/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC14" s="26" t="n">
+        <f aca="false">ROUND(AA14/P14 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y14" s="25" t="n">
+      <c r="AE14" s="26" t="n">
         <f aca="false">-Q14*($Q$47)*10</f>
         <v>-574.245682949676</v>
       </c>
-      <c r="Z14" s="25" t="n">
-        <f aca="false">Y14/P14/10</f>
+      <c r="AF14" s="26" t="n">
+        <f aca="false">AE14/P14/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC14" s="22" t="n">
+      <c r="AI14" s="23" t="n">
         <v>417.8</v>
       </c>
-      <c r="AH14" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI14" s="22" t="n">
+      <c r="AN14" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ14" s="22" t="n">
+      <c r="AP14" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="AK14" s="22" t="n">
-        <f aca="false">AI14+AJ14/100</f>
+      <c r="AQ14" s="23" t="n">
+        <f aca="false">AO14+AP14/100</f>
         <v>1.13</v>
       </c>
-      <c r="AL14" s="22" t="n">
-        <f aca="false">AK14*1000</f>
+      <c r="AR14" s="23" t="n">
+        <f aca="false">AQ14*1000</f>
         <v>1130</v>
       </c>
-      <c r="AO14" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP14" s="22" t="n">
+      <c r="AU14" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="AV14" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="AQ14" s="22" t="n">
+      <c r="AW14" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AR14" s="26" t="n">
-        <f aca="false">AP14+AQ14/10</f>
+      <c r="AX14" s="28" t="n">
+        <f aca="false">AV14+AW14/10</f>
         <v>4.2</v>
       </c>
-      <c r="AS14" s="26" t="n">
-        <f aca="false">1000*AR14</f>
+      <c r="AY14" s="28" t="n">
+        <f aca="false">1000*AX14</f>
         <v>4200</v>
       </c>
-      <c r="AU14" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="AV14" s="22" t="n">
+      <c r="BA14" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB14" s="23" t="n">
         <v>1.13</v>
       </c>
-      <c r="AW14" s="22" t="n">
+      <c r="BC14" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="AX14" s="22" t="n">
+      <c r="BD14" s="23" t="n">
         <v>2.27</v>
       </c>
-      <c r="AY14" s="22" t="n">
+      <c r="BE14" s="23" t="n">
         <v>1.1</v>
       </c>
-      <c r="AZ14" s="22" t="n">
+      <c r="BF14" s="23" t="n">
         <v>1.49</v>
       </c>
-      <c r="BA14" s="26" t="s">
+      <c r="BG14" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI14" s="28" t="n">
+        <f aca="false">BB14*1000</f>
+        <v>1130</v>
+      </c>
+      <c r="BK14" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL14" s="23" t="n">
+        <v>116</v>
+      </c>
+      <c r="BM14" s="23" t="n">
         <v>79</v>
       </c>
-      <c r="BC14" s="26" t="n">
-        <f aca="false">AV14*1000</f>
-        <v>1130</v>
-      </c>
-      <c r="BE14" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="BF14" s="22" t="n">
-        <v>116</v>
-      </c>
-      <c r="BG14" s="22" t="n">
-        <v>79</v>
-      </c>
-      <c r="BH14" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI14" s="22" t="n">
+      <c r="BN14" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO14" s="23" t="n">
         <v>108</v>
       </c>
-      <c r="BK14" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="BL14" s="22" t="n">
+      <c r="BQ14" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="BR14" s="23" t="n">
         <v>258</v>
       </c>
-      <c r="BM14" s="22" t="s">
-        <v>81</v>
+      <c r="BS14" s="23" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="15" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="22" t="n">
+    <row r="15" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="24" t="n">
         <f aca="false">B15/$P15/10</f>
         <v>0.0744360658921001</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="24" t="n">
         <f aca="false">D15/$P15/10</f>
         <v>0.0679633645101783</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="24" t="n">
         <f aca="false">F15/$P15/10</f>
         <v>0.000323635069096087</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="I15" s="23" t="n">
+      <c r="I15" s="24" t="n">
         <f aca="false">H15/$P15/10</f>
         <v>0.0938541700378653</v>
       </c>
-      <c r="J15" s="22" t="n">
+      <c r="J15" s="23" t="n">
         <f aca="false">L15*$J$37/100</f>
         <v>15.3</v>
       </c>
-      <c r="K15" s="23" t="n">
+      <c r="K15" s="24" t="n">
         <f aca="false">J15/$P15/10</f>
         <v>0.0495161655717014</v>
       </c>
-      <c r="L15" s="22" t="n">
+      <c r="L15" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="M15" s="22" t="n">
+      <c r="M15" s="23" t="n">
         <f aca="false">O15*$M$37/100</f>
         <v>68</v>
       </c>
-      <c r="N15" s="23" t="n">
+      <c r="N15" s="24" t="n">
         <f aca="false">M15/$P15/10</f>
         <v>0.220071846985339</v>
       </c>
-      <c r="O15" s="22" t="n">
+      <c r="O15" s="23" t="n">
         <v>500</v>
       </c>
-      <c r="P15" s="25" t="n">
+      <c r="P15" s="26" t="n">
         <v>30.899</v>
       </c>
-      <c r="Q15" s="25" t="n">
+      <c r="Q15" s="26" t="n">
         <f aca="false">100*P15/$P$36</f>
         <v>0.212224324387067</v>
       </c>
-      <c r="R15" s="22" t="n">
+      <c r="R15" s="23" t="n">
         <f aca="false">H15+F15+B15+D15+J15+M15</f>
         <v>156.4</v>
       </c>
-      <c r="S15" s="25" t="n">
+      <c r="S15" s="26" t="n">
         <f aca="false">R15/P15</f>
         <v>5.0616524806628</v>
       </c>
-      <c r="U15" s="25" t="n">
-        <f aca="false">-T15+($Q$45 + $Q$46)*1000*Q15/100</f>
-        <v>94.2829905765229</v>
-      </c>
-      <c r="V15" s="25" t="n">
-        <f aca="false">U15/P15/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W15" s="25" t="n">
-        <f aca="false">ROUND(U15/P15 *100/1000, 2)</f>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="0" t="n">
+        <f aca="false">T15+U15</f>
+        <v>0</v>
+      </c>
+      <c r="W15" s="27" t="n">
+        <f aca="false">3/5*H15+M15/3</f>
+        <v>40.0666666666667</v>
+      </c>
+      <c r="X15" s="27" t="n">
+        <f aca="false">R15-V15</f>
+        <v>156.4</v>
+      </c>
+      <c r="Y15" s="27" t="n">
+        <f aca="false">1000/100*Q15*($Q$41+$Q$47-$Q$49)-V15</f>
+        <v>116.953641804847</v>
+      </c>
+      <c r="Z15" s="27" t="n">
+        <f aca="false">Y15-V15+Q15/100*1000 *($Q$46+$Q$43)</f>
+        <v>208.884125745539</v>
+      </c>
+      <c r="AA15" s="26" t="n">
+        <f aca="false">-V15+($Q$45 + $Q$46)*1000*Q15/100</f>
+        <v>95.7312093661401</v>
+      </c>
+      <c r="AB15" s="26" t="n">
+        <f aca="false">AA15/P15/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC15" s="26" t="n">
+        <f aca="false">ROUND(AA15/P15 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y15" s="25" t="n">
+      <c r="AE15" s="26" t="n">
         <f aca="false">-Q15*($Q$47)*10</f>
         <v>-50.9338378528962</v>
       </c>
-      <c r="Z15" s="25" t="n">
-        <f aca="false">Y15/P15/10</f>
+      <c r="AF15" s="26" t="n">
+        <f aca="false">AE15/P15/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC15" s="22" t="n">
+      <c r="AI15" s="23" t="n">
         <v>41.9</v>
       </c>
-      <c r="AH15" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="AI15" s="22" t="n">
+      <c r="AN15" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" s="22" t="n">
+      <c r="AP15" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="AK15" s="22" t="n">
-        <f aca="false">AI15+AJ15/100</f>
+      <c r="AQ15" s="23" t="n">
+        <f aca="false">AO15+AP15/100</f>
         <v>0.9</v>
       </c>
-      <c r="AL15" s="22" t="n">
-        <f aca="false">AK15*1000</f>
+      <c r="AR15" s="23" t="n">
+        <f aca="false">AQ15*1000</f>
         <v>900</v>
       </c>
-      <c r="AO15" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP15" s="22" t="n">
+      <c r="AU15" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AQ15" s="22" t="n">
+      <c r="AW15" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="AR15" s="26" t="n">
-        <f aca="false">AP15+AQ15/10</f>
+      <c r="AX15" s="28" t="n">
+        <f aca="false">AV15+AW15/10</f>
         <v>0.5</v>
       </c>
-      <c r="AS15" s="26" t="n">
-        <f aca="false">1000*AR15</f>
+      <c r="AY15" s="28" t="n">
+        <f aca="false">1000*AX15</f>
         <v>500</v>
       </c>
-      <c r="AU15" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV15" s="22" t="n">
+      <c r="BA15" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="BB15" s="23" t="n">
         <v>0.09</v>
       </c>
-      <c r="AW15" s="22" t="n">
+      <c r="BC15" s="23" t="n">
         <v>0.22</v>
       </c>
-      <c r="AX15" s="22" t="n">
+      <c r="BD15" s="23" t="n">
         <v>0.22</v>
       </c>
-      <c r="AY15" s="22" t="n">
+      <c r="BE15" s="23" t="n">
         <v>0.96</v>
       </c>
-      <c r="AZ15" s="22" t="n">
+      <c r="BF15" s="23" t="n">
         <v>1.3</v>
       </c>
-      <c r="BA15" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="BC15" s="26" t="n">
-        <f aca="false">AV15*1000</f>
+      <c r="BG15" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI15" s="28" t="n">
+        <f aca="false">BB15*1000</f>
         <v>90</v>
       </c>
-      <c r="BE15" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="BF15" s="22" t="n">
+      <c r="BK15" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="BL15" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="BG15" s="22" t="n">
+      <c r="BM15" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="BH15" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI15" s="22" t="n">
+      <c r="BN15" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO15" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="BK15" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL15" s="22" t="n">
+      <c r="BQ15" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="BR15" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="BM15" s="22" t="s">
-        <v>86</v>
+      <c r="BS15" s="23" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="16" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="22" t="n">
+    <row r="16" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="23" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <f aca="false">B16/$P16/10</f>
         <v>0.0379785988637743</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>133</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <f aca="false">D16/$P16/10</f>
         <v>0.0520737489575462</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="25" t="n">
         <v>81.3</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G16" s="24" t="n">
         <f aca="false">F16/$P16/10</f>
         <v>0.0318315472951015</v>
       </c>
-      <c r="H16" s="24" t="n">
+      <c r="H16" s="25" t="n">
         <v>152</v>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I16" s="24" t="n">
         <f aca="false">H16/$P16/10</f>
         <v>0.0595128559514814</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="23" t="n">
         <f aca="false">L16*$J$37/100</f>
         <v>122.4</v>
       </c>
-      <c r="K16" s="23" t="n">
+      <c r="K16" s="24" t="n">
         <f aca="false">J16/$P16/10</f>
         <v>0.0479235103188245</v>
       </c>
-      <c r="L16" s="22" t="n">
+      <c r="L16" s="23" t="n">
         <v>720</v>
       </c>
-      <c r="M16" s="22" t="n">
+      <c r="M16" s="23" t="n">
         <f aca="false">O16*$M$37/100</f>
         <v>394.4</v>
       </c>
-      <c r="N16" s="23" t="n">
+      <c r="N16" s="24" t="n">
         <f aca="false">M16/$P16/10</f>
         <v>0.154420199916212</v>
       </c>
-      <c r="O16" s="22" t="n">
+      <c r="O16" s="23" t="n">
         <v>2900</v>
       </c>
-      <c r="P16" s="25" t="n">
+      <c r="P16" s="26" t="n">
         <v>255.407</v>
       </c>
-      <c r="Q16" s="25" t="n">
+      <c r="Q16" s="26" t="n">
         <f aca="false">100*P16/$P$36</f>
         <v>1.75421787173461</v>
       </c>
-      <c r="R16" s="22" t="n">
+      <c r="R16" s="23" t="n">
         <f aca="false">H16+F16+B16+D16+J16+M16</f>
         <v>980.1</v>
       </c>
-      <c r="S16" s="25" t="n">
+      <c r="S16" s="26" t="n">
         <f aca="false">R16/P16</f>
         <v>3.8374046130294</v>
       </c>
-      <c r="U16" s="25" t="n">
-        <f aca="false">-T16+($Q$45 + $Q$46)*1000*Q16/100</f>
-        <v>779.330585914689</v>
-      </c>
-      <c r="V16" s="25" t="n">
-        <f aca="false">U16/P16/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W16" s="25" t="n">
-        <f aca="false">ROUND(U16/P16 *100/1000, 2)</f>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="0" t="n">
+        <f aca="false">T16+U16</f>
+        <v>0</v>
+      </c>
+      <c r="W16" s="27" t="n">
+        <f aca="false">3/5*H16+M16/3</f>
+        <v>222.666666666667</v>
+      </c>
+      <c r="X16" s="27" t="n">
+        <f aca="false">R16-V16</f>
+        <v>980.1</v>
+      </c>
+      <c r="Y16" s="27" t="n">
+        <f aca="false">1000/100*Q16*($Q$41+$Q$47-$Q$49)-V16</f>
+        <v>966.723155844868</v>
+      </c>
+      <c r="Z16" s="27" t="n">
+        <f aca="false">Y16-V16+Q16/100*1000 *($Q$46+$Q$43)</f>
+        <v>1726.60823665138</v>
+      </c>
+      <c r="AA16" s="26" t="n">
+        <f aca="false">-V16+($Q$45 + $Q$46)*1000*Q16/100</f>
+        <v>791.301368671407</v>
+      </c>
+      <c r="AB16" s="26" t="n">
+        <f aca="false">AA16/P16/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC16" s="26" t="n">
+        <f aca="false">ROUND(AA16/P16 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y16" s="25" t="n">
+      <c r="AE16" s="26" t="n">
         <f aca="false">-Q16*($Q$47)*10</f>
         <v>-421.012289216306</v>
       </c>
-      <c r="Z16" s="25" t="n">
-        <f aca="false">Y16/P16/10</f>
+      <c r="AF16" s="26" t="n">
+        <f aca="false">AE16/P16/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC16" s="22" t="n">
+      <c r="AI16" s="23" t="n">
         <v>281.7</v>
       </c>
-      <c r="AH16" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI16" s="22" t="n">
+      <c r="AN16" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ16" s="22" t="n">
+      <c r="AP16" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="AK16" s="22" t="n">
-        <f aca="false">AI16+AJ16/100</f>
+      <c r="AQ16" s="23" t="n">
+        <f aca="false">AO16+AP16/100</f>
         <v>0.72</v>
       </c>
-      <c r="AL16" s="22" t="n">
-        <f aca="false">AK16*1000</f>
+      <c r="AR16" s="23" t="n">
+        <f aca="false">AQ16*1000</f>
         <v>720</v>
       </c>
-      <c r="AO16" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP16" s="22" t="n">
+      <c r="AU16" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV16" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AQ16" s="22" t="n">
+      <c r="AW16" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AR16" s="26" t="n">
-        <f aca="false">AP16+AQ16/10</f>
+      <c r="AX16" s="28" t="n">
+        <f aca="false">AV16+AW16/10</f>
         <v>2.9</v>
       </c>
-      <c r="AS16" s="26" t="n">
-        <f aca="false">1000*AR16</f>
+      <c r="AY16" s="28" t="n">
+        <f aca="false">1000*AX16</f>
         <v>2900</v>
       </c>
-      <c r="AU16" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV16" s="22" t="n">
+      <c r="BA16" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB16" s="23" t="n">
         <v>0.72</v>
       </c>
-      <c r="AW16" s="22" t="n">
+      <c r="BC16" s="23" t="n">
         <v>1.59</v>
       </c>
-      <c r="AX16" s="22" t="n">
+      <c r="BD16" s="23" t="n">
         <v>1.6</v>
       </c>
-      <c r="AY16" s="22" t="n">
+      <c r="BE16" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AZ16" s="22" t="n">
+      <c r="BF16" s="23" t="n">
         <v>1.36</v>
       </c>
-      <c r="BA16" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="BC16" s="26" t="n">
-        <f aca="false">AV16*1000</f>
+      <c r="BG16" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="BI16" s="28" t="n">
+        <f aca="false">BB16*1000</f>
         <v>720</v>
       </c>
-      <c r="BE16" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="BF16" s="22" t="n">
+      <c r="BK16" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="BL16" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="BG16" s="22" t="n">
+      <c r="BM16" s="23" t="n">
         <v>71</v>
       </c>
-      <c r="BH16" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI16" s="22" t="n">
+      <c r="BN16" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO16" s="23" t="n">
         <v>97</v>
       </c>
-      <c r="BK16" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="BL16" s="22" t="n">
+      <c r="BQ16" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="BR16" s="23" t="n">
         <v>133</v>
       </c>
-      <c r="BM16" s="22" t="s">
-        <v>91</v>
+      <c r="BS16" s="23" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="17" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="22" t="n">
+    <row r="17" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <v>1084</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="24" t="n">
         <f aca="false">B17/$P17/10</f>
         <v>0.0421022541018626</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="23" t="n">
         <v>1691</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="24" t="n">
         <f aca="false">D17/$P17/10</f>
         <v>0.0656779628101934</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="30" t="n">
         <v>3100</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="24" t="n">
         <f aca="false">F17/$P17/10</f>
         <v>0.120403125199054</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="30" t="n">
         <v>6670</v>
       </c>
-      <c r="I17" s="23" t="n">
+      <c r="I17" s="24" t="n">
         <f aca="false">H17/$P17/10</f>
         <v>0.259060917766996</v>
       </c>
-      <c r="J17" s="22" t="n">
+      <c r="J17" s="23" t="n">
         <f aca="false">L17*$J$37/100</f>
         <v>914.6</v>
       </c>
-      <c r="K17" s="23" t="n">
+      <c r="K17" s="24" t="n">
         <f aca="false">J17/$P17/10</f>
         <v>0.0355228059055014</v>
       </c>
-      <c r="L17" s="22" t="n">
+      <c r="L17" s="23" t="n">
         <v>5380</v>
       </c>
-      <c r="M17" s="22" t="n">
+      <c r="M17" s="23" t="n">
         <f aca="false">O17*$M$37/100</f>
         <v>8432</v>
       </c>
-      <c r="N17" s="23" t="n">
+      <c r="N17" s="24" t="n">
         <f aca="false">M17/$P17/10</f>
         <v>0.327496500541426</v>
       </c>
-      <c r="O17" s="22" t="n">
+      <c r="O17" s="23" t="n">
         <v>62000</v>
       </c>
-      <c r="P17" s="25" t="n">
+      <c r="P17" s="26" t="n">
         <v>2574.684</v>
       </c>
-      <c r="Q17" s="25" t="n">
+      <c r="Q17" s="26" t="n">
         <f aca="false">100*P17/$P$36</f>
         <v>17.6837623356805</v>
       </c>
-      <c r="R17" s="22" t="n">
+      <c r="R17" s="23" t="n">
         <f aca="false">H17+F17+B17+D17+J17+M17</f>
         <v>21891.6</v>
       </c>
-      <c r="S17" s="25" t="n">
+      <c r="S17" s="26" t="n">
         <f aca="false">R17/P17</f>
         <v>8.50263566325032</v>
       </c>
-      <c r="T17" s="22" t="n">
-        <f aca="false">B17+F17</f>
+      <c r="T17" s="26" t="n">
+        <f aca="false">B17</f>
+        <v>1084</v>
+      </c>
+      <c r="U17" s="26" t="n">
+        <f aca="false">F17</f>
+        <v>3100</v>
+      </c>
+      <c r="V17" s="0" t="n">
+        <f aca="false">T17+U17</f>
         <v>4184</v>
       </c>
-      <c r="U17" s="25" t="n">
-        <f aca="false">-T17+($Q$45 + $Q$46)*1000*Q17/100</f>
-        <v>3672.20593901176</v>
-      </c>
-      <c r="V17" s="25" t="n">
-        <f aca="false">U17/P17/10</f>
-        <v>0.142627442397271</v>
-      </c>
-      <c r="W17" s="25" t="n">
-        <f aca="false">ROUND(U17/P17 *100/1000, 2)</f>
-        <v>0.14</v>
-      </c>
-      <c r="Y17" s="25" t="n">
+      <c r="W17" s="27" t="n">
+        <f aca="false">3/5*H17+M17/3</f>
+        <v>6812.66666666667</v>
+      </c>
+      <c r="X17" s="27" t="n">
+        <f aca="false">R17-V17</f>
+        <v>17707.6</v>
+      </c>
+      <c r="Y17" s="27" t="n">
+        <f aca="false">1000/100*Q17*($Q$41+$Q$47-$Q$49)-V17</f>
+        <v>5561.25616675849</v>
+      </c>
+      <c r="Z17" s="27" t="n">
+        <f aca="false">Y17-V17+Q17/100*1000 *($Q$46+$Q$43)</f>
+        <v>9037.43760027922</v>
+      </c>
+      <c r="AA17" s="26" t="n">
+        <f aca="false">-V17+($Q$45 + $Q$46)*1000*Q17/100</f>
+        <v>3792.87993319044</v>
+      </c>
+      <c r="AB17" s="26" t="n">
+        <f aca="false">AA17/P17/10</f>
+        <v>0.147314386277712</v>
+      </c>
+      <c r="AC17" s="26" t="n">
+        <f aca="false">ROUND(AA17/P17 *100/1000, 2)</f>
+        <v>0.15</v>
+      </c>
+      <c r="AE17" s="26" t="n">
         <f aca="false">-Q17*($Q$47)*10</f>
         <v>-4244.10296056332</v>
       </c>
-      <c r="Z17" s="25" t="n">
-        <f aca="false">Y17/P17/10</f>
+      <c r="AF17" s="26" t="n">
+        <f aca="false">AE17/P17/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC17" s="22" t="n">
+      <c r="AI17" s="23" t="n">
         <v>2991.1</v>
       </c>
-      <c r="AH17" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI17" s="22" t="n">
+      <c r="AN17" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO17" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="AJ17" s="22" t="n">
+      <c r="AP17" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="AK17" s="22" t="n">
-        <f aca="false">AI17+AJ17/100</f>
+      <c r="AQ17" s="23" t="n">
+        <f aca="false">AO17+AP17/100</f>
         <v>5.38</v>
       </c>
-      <c r="AL17" s="22" t="n">
-        <f aca="false">AK17*1000</f>
+      <c r="AR17" s="23" t="n">
+        <f aca="false">AQ17*1000</f>
         <v>5380</v>
       </c>
-      <c r="AO17" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP17" s="22" t="n">
+      <c r="AU17" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="AV17" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="AQ17" s="22" t="n">
+      <c r="AW17" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AR17" s="26" t="n">
-        <f aca="false">AP17+AQ17/10</f>
+      <c r="AX17" s="28" t="n">
+        <f aca="false">AV17+AW17/10</f>
         <v>62</v>
       </c>
-      <c r="AS17" s="26" t="n">
-        <f aca="false">1000*AR17</f>
+      <c r="AY17" s="28" t="n">
+        <f aca="false">1000*AX17</f>
         <v>62000</v>
       </c>
-      <c r="AU17" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="AV17" s="22" t="n">
+      <c r="BA17" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB17" s="23" t="n">
         <v>5.38</v>
       </c>
-      <c r="AW17" s="22" t="n">
+      <c r="BC17" s="23" t="n">
         <v>11.96</v>
       </c>
-      <c r="AX17" s="22" t="n">
+      <c r="BD17" s="23" t="n">
         <v>16.61</v>
       </c>
-      <c r="AY17" s="22" t="n">
+      <c r="BE17" s="23" t="n">
         <v>0.72</v>
       </c>
-      <c r="AZ17" s="22" t="n">
+      <c r="BF17" s="23" t="n">
         <v>0.98</v>
       </c>
-      <c r="BA17" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="BC17" s="26" t="n">
-        <f aca="false">AV17*1000</f>
+      <c r="BG17" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI17" s="28" t="n">
+        <f aca="false">BB17*1000</f>
         <v>5380</v>
       </c>
-      <c r="BE17" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF17" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="BG17" s="22" t="n">
+      <c r="BK17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL17" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="BM17" s="23" t="n">
         <v>797</v>
       </c>
-      <c r="BH17" s="22" t="n">
+      <c r="BN17" s="23" t="n">
         <v>756</v>
       </c>
-      <c r="BI17" s="22" t="n">
+      <c r="BO17" s="23" t="n">
         <v>1084</v>
       </c>
-      <c r="BK17" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="BL17" s="22" t="n">
+      <c r="BQ17" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR17" s="23" t="n">
         <v>1691</v>
       </c>
-      <c r="BM17" s="22" t="s">
-        <v>98</v>
+      <c r="BS17" s="23" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="18" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="22" t="n">
+    <row r="18" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="23" t="n">
         <v>978</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="24" t="n">
         <f aca="false">B18/$P18/10</f>
         <v>0.0262233683997149</v>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="23" t="n">
         <v>2700</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="24" t="n">
         <f aca="false">D18/$P18/10</f>
         <v>0.0723958023305013</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="25" t="n">
         <v>1595.2</v>
       </c>
-      <c r="G18" s="23" t="n">
+      <c r="G18" s="24" t="n">
         <f aca="false">F18/$P18/10</f>
         <v>0.0427725125472651</v>
       </c>
-      <c r="H18" s="24" t="n">
+      <c r="H18" s="25" t="n">
         <v>8344</v>
       </c>
-      <c r="I18" s="23" t="n">
+      <c r="I18" s="24" t="n">
         <f aca="false">H18/$P18/10</f>
         <v>0.223729842461371</v>
       </c>
-      <c r="J18" s="22" t="n">
+      <c r="J18" s="23" t="n">
         <f aca="false">L18*$J$37/100</f>
         <v>1026.8</v>
       </c>
-      <c r="K18" s="23" t="n">
+      <c r="K18" s="24" t="n">
         <f aca="false">J18/$P18/10</f>
         <v>0.0275318554936884</v>
       </c>
-      <c r="L18" s="22" t="n">
+      <c r="L18" s="23" t="n">
         <v>6040</v>
       </c>
-      <c r="M18" s="22" t="n">
+      <c r="M18" s="23" t="n">
         <f aca="false">O18*$M$37/100</f>
         <v>7847.2</v>
       </c>
-      <c r="N18" s="23" t="n">
+      <c r="N18" s="24" t="n">
         <f aca="false">M18/$P18/10</f>
         <v>0.210409014832559</v>
       </c>
-      <c r="O18" s="22" t="n">
+      <c r="O18" s="23" t="n">
         <v>57700</v>
       </c>
-      <c r="P18" s="25" t="n">
+      <c r="P18" s="26" t="n">
         <v>3729.498</v>
       </c>
-      <c r="Q18" s="25" t="n">
+      <c r="Q18" s="26" t="n">
         <f aca="false">100*P18/$P$36</f>
         <v>25.6153983414647</v>
       </c>
-      <c r="R18" s="22" t="n">
+      <c r="R18" s="23" t="n">
         <f aca="false">H18+F18+B18+D18+J18+M18</f>
         <v>22491.2</v>
       </c>
-      <c r="S18" s="25" t="n">
+      <c r="S18" s="26" t="n">
         <f aca="false">R18/P18</f>
         <v>6.030623960651</v>
       </c>
-      <c r="U18" s="25" t="n">
-        <f aca="false">-T18+($Q$45 + $Q$46)*1000*Q18/100</f>
-        <v>11379.9224825775</v>
-      </c>
-      <c r="V18" s="25" t="n">
-        <f aca="false">U18/P18/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W18" s="25" t="n">
-        <f aca="false">ROUND(U18/P18 *100/1000, 2)</f>
+      <c r="T18" s="26"/>
+      <c r="U18" s="26"/>
+      <c r="V18" s="0" t="n">
+        <f aca="false">T18+U18</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="27" t="n">
+        <f aca="false">3/5*H18+M18/3</f>
+        <v>7622.13333333333</v>
+      </c>
+      <c r="X18" s="27" t="n">
+        <f aca="false">R18-V18</f>
+        <v>22491.2</v>
+      </c>
+      <c r="Y18" s="27" t="n">
+        <f aca="false">1000/100*Q18*($Q$41+$Q$47-$Q$49)-V18</f>
+        <v>14116.2617950061</v>
+      </c>
+      <c r="Z18" s="27" t="n">
+        <f aca="false">Y18-V18+Q18/100*1000 *($Q$46+$Q$43)</f>
+        <v>25212.2375869684</v>
+      </c>
+      <c r="AA18" s="26" t="n">
+        <f aca="false">-V18+($Q$45 + $Q$46)*1000*Q18/100</f>
+        <v>11554.7219608596</v>
+      </c>
+      <c r="AB18" s="26" t="n">
+        <f aca="false">AA18/P18/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC18" s="26" t="n">
+        <f aca="false">ROUND(AA18/P18 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y18" s="25" t="n">
+      <c r="AE18" s="26" t="n">
         <f aca="false">-Q18*($Q$47)*10</f>
         <v>-6147.69560195154</v>
       </c>
-      <c r="Z18" s="25" t="n">
-        <f aca="false">Y18/P18/10</f>
+      <c r="AF18" s="26" t="n">
+        <f aca="false">AE18/P18/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC18" s="22" t="n">
+      <c r="AI18" s="23" t="n">
         <v>4529.7</v>
       </c>
-      <c r="AH18" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI18" s="22" t="n">
+      <c r="AN18" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO18" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AJ18" s="22" t="n">
+      <c r="AP18" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="AK18" s="22" t="n">
-        <f aca="false">AI18+AJ18/100</f>
+      <c r="AQ18" s="23" t="n">
+        <f aca="false">AO18+AP18/100</f>
         <v>6.4</v>
       </c>
-      <c r="AL18" s="22" t="n">
-        <f aca="false">AK18*1000</f>
+      <c r="AR18" s="23" t="n">
+        <f aca="false">AQ18*1000</f>
         <v>6400</v>
       </c>
-      <c r="AO18" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="AP18" s="22" t="n">
+      <c r="AU18" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="AV18" s="23" t="n">
         <v>57</v>
       </c>
-      <c r="AQ18" s="22" t="n">
+      <c r="AW18" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="AR18" s="26" t="n">
-        <f aca="false">AP18+AQ18/10</f>
+      <c r="AX18" s="28" t="n">
+        <f aca="false">AV18+AW18/10</f>
         <v>57.7</v>
       </c>
-      <c r="AS18" s="26" t="n">
-        <f aca="false">1000*AR18</f>
+      <c r="AY18" s="28" t="n">
+        <f aca="false">1000*AX18</f>
         <v>57700</v>
       </c>
-      <c r="AU18" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="AV18" s="22" t="n">
+      <c r="BA18" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB18" s="23" t="n">
         <v>6.04</v>
       </c>
-      <c r="AW18" s="22" t="n">
+      <c r="BC18" s="23" t="n">
         <v>13.43</v>
       </c>
-      <c r="AX18" s="22" t="n">
+      <c r="BD18" s="23" t="n">
         <v>24.81</v>
       </c>
-      <c r="AY18" s="22" t="n">
+      <c r="BE18" s="23" t="n">
         <v>0.54</v>
       </c>
-      <c r="AZ18" s="22" t="n">
+      <c r="BF18" s="23" t="n">
         <v>0.73</v>
       </c>
-      <c r="BA18" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="BC18" s="26" t="n">
-        <f aca="false">AV18*1000</f>
+      <c r="BG18" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="BI18" s="28" t="n">
+        <f aca="false">BB18*1000</f>
         <v>6040</v>
       </c>
-      <c r="BE18" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="BF18" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="BG18" s="22" t="n">
+      <c r="BK18" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL18" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BM18" s="23" t="n">
         <v>719</v>
       </c>
-      <c r="BH18" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI18" s="22" t="n">
+      <c r="BN18" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO18" s="23" t="n">
         <v>978</v>
       </c>
-      <c r="BK18" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="BL18" s="22" t="n">
+      <c r="BQ18" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="BR18" s="23" t="n">
         <v>2700</v>
       </c>
-      <c r="BM18" s="22" t="s">
-        <v>105</v>
+      <c r="BS18" s="23" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="19" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="22" t="n">
+    <row r="19" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C19" s="24" t="n">
         <f aca="false">B19/$P19/10</f>
         <v>0.0503093193867792</v>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="24" t="n">
         <f aca="false">D19/$P19/10</f>
         <v>0.0298538818339129</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="30" t="n">
         <v>22.7</v>
       </c>
-      <c r="G19" s="23" t="n">
+      <c r="G19" s="24" t="n">
         <f aca="false">F19/$P19/10</f>
         <v>0.0125496873635152</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="30" t="n">
         <v>118</v>
       </c>
-      <c r="I19" s="23" t="n">
+      <c r="I19" s="24" t="n">
         <f aca="false">H19/$P19/10</f>
         <v>0.0652362603037356</v>
       </c>
-      <c r="J19" s="22" t="n">
+      <c r="J19" s="23" t="n">
         <f aca="false">L19*$J$37/100</f>
         <v>431.8</v>
       </c>
-      <c r="K19" s="23" t="n">
+      <c r="K19" s="24" t="n">
         <f aca="false">J19/$P19/10</f>
         <v>0.238720484738585</v>
       </c>
-      <c r="L19" s="22" t="n">
+      <c r="L19" s="23" t="n">
         <v>2540</v>
       </c>
-      <c r="M19" s="22" t="n">
+      <c r="M19" s="23" t="n">
         <f aca="false">O19*$M$37/100</f>
         <v>856.8</v>
       </c>
-      <c r="N19" s="23" t="n">
+      <c r="N19" s="24" t="n">
         <f aca="false">M19/$P19/10</f>
         <v>0.473681591764751</v>
       </c>
-      <c r="O19" s="22" t="n">
+      <c r="O19" s="23" t="n">
         <v>6300</v>
       </c>
-      <c r="P19" s="25" t="n">
+      <c r="P19" s="26" t="n">
         <v>180.881</v>
       </c>
-      <c r="Q19" s="25" t="n">
+      <c r="Q19" s="26" t="n">
         <f aca="false">100*P19/$P$36</f>
         <v>1.24234920286926</v>
       </c>
-      <c r="R19" s="22" t="n">
+      <c r="R19" s="23" t="n">
         <f aca="false">H19+F19+B19+D19+J19+M19</f>
         <v>1574.3</v>
       </c>
-      <c r="S19" s="25" t="n">
+      <c r="S19" s="26" t="n">
         <f aca="false">R19/P19</f>
         <v>8.70351225391279</v>
       </c>
-      <c r="T19" s="29" t="n">
+      <c r="T19" s="26"/>
+      <c r="U19" s="31" t="n">
         <f aca="false">F19</f>
         <v>22.7</v>
       </c>
-      <c r="U19" s="25" t="n">
-        <f aca="false">-T19+($Q$45 + $Q$46)*1000*Q19/100</f>
-        <v>529.227299215898</v>
-      </c>
-      <c r="V19" s="25" t="n">
-        <f aca="false">U19/P19/10</f>
-        <v>0.292583134334672</v>
-      </c>
-      <c r="W19" s="25" t="n">
-        <f aca="false">ROUND(U19/P19 *100/1000, 2)</f>
-        <v>0.29</v>
-      </c>
-      <c r="Y19" s="25" t="n">
+      <c r="V19" s="0" t="n">
+        <f aca="false">T19+U19</f>
+        <v>22.7</v>
+      </c>
+      <c r="W19" s="27" t="n">
+        <f aca="false">3/5*H19+M19/3</f>
+        <v>356.4</v>
+      </c>
+      <c r="X19" s="27" t="n">
+        <f aca="false">R19-V19</f>
+        <v>1551.6</v>
+      </c>
+      <c r="Y19" s="27" t="n">
+        <f aca="false">1000/100*Q19*($Q$41+$Q$47-$Q$49)-V19</f>
+        <v>661.940010463206</v>
+      </c>
+      <c r="Z19" s="27" t="n">
+        <f aca="false">Y19-V19+Q19/100*1000 *($Q$46+$Q$43)</f>
+        <v>1177.3958687653</v>
+      </c>
+      <c r="AA19" s="26" t="n">
+        <f aca="false">-U19+($Q$45 + $Q$46)*1000*Q19/100</f>
+        <v>537.70509017628</v>
+      </c>
+      <c r="AB19" s="26" t="n">
+        <f aca="false">AA19/P19/10</f>
+        <v>0.297270078215114</v>
+      </c>
+      <c r="AC19" s="26" t="n">
+        <f aca="false">ROUND(AA19/P19 *100/1000, 2)</f>
+        <v>0.3</v>
+      </c>
+      <c r="AE19" s="26" t="n">
         <f aca="false">-Q19*($Q$47)*10</f>
         <v>-298.163808688621</v>
       </c>
-      <c r="Z19" s="25" t="n">
-        <f aca="false">Y19/P19/10</f>
+      <c r="AF19" s="26" t="n">
+        <f aca="false">AE19/P19/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC19" s="22" t="n">
+      <c r="AI19" s="23" t="n">
         <v>248.4</v>
       </c>
-      <c r="AH19" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI19" s="22" t="n">
+      <c r="AN19" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO19" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AJ19" s="22" t="n">
+      <c r="AP19" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="AK19" s="22" t="n">
-        <f aca="false">AI19+AJ19/100</f>
+      <c r="AQ19" s="23" t="n">
+        <f aca="false">AO19+AP19/100</f>
         <v>2.54</v>
       </c>
-      <c r="AL19" s="22" t="n">
-        <f aca="false">AK19*1000</f>
+      <c r="AR19" s="23" t="n">
+        <f aca="false">AQ19*1000</f>
         <v>2540</v>
       </c>
-      <c r="AO19" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP19" s="22" t="n">
+      <c r="AU19" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV19" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AQ19" s="22" t="n">
+      <c r="AW19" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AR19" s="26" t="n">
-        <f aca="false">AP19+AQ19/10</f>
+      <c r="AX19" s="28" t="n">
+        <f aca="false">AV19+AW19/10</f>
         <v>6.3</v>
       </c>
-      <c r="AS19" s="26" t="n">
-        <f aca="false">1000*AR19</f>
+      <c r="AY19" s="28" t="n">
+        <f aca="false">1000*AX19</f>
         <v>6300</v>
       </c>
-      <c r="AU19" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="AV19" s="22" t="n">
+      <c r="BA19" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="BB19" s="23" t="n">
         <v>2.54</v>
       </c>
-      <c r="AW19" s="22" t="n">
+      <c r="BC19" s="23" t="n">
         <v>5.64</v>
       </c>
-      <c r="AX19" s="22" t="n">
+      <c r="BD19" s="23" t="n">
         <v>1.3</v>
       </c>
-      <c r="AY19" s="22" t="n">
+      <c r="BE19" s="23" t="n">
         <v>4.34</v>
       </c>
-      <c r="AZ19" s="22" t="n">
+      <c r="BF19" s="23" t="n">
         <v>5.88</v>
       </c>
-      <c r="BA19" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="BC19" s="26" t="n">
-        <f aca="false">AV19*1000</f>
+      <c r="BG19" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI19" s="28" t="n">
+        <f aca="false">BB19*1000</f>
         <v>2540</v>
       </c>
-      <c r="BE19" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="BF19" s="22" t="n">
+      <c r="BK19" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="BL19" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="BG19" s="22" t="n">
+      <c r="BM19" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="BH19" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI19" s="22" t="n">
+      <c r="BN19" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO19" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="BK19" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="BL19" s="22" t="n">
+      <c r="BQ19" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR19" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="BM19" s="22" t="s">
-        <v>111</v>
+      <c r="BS19" s="23" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="20" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="22" t="n">
+    <row r="20" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="24" t="n">
         <f aca="false">B20/$P20/10</f>
         <v>0.0940076817705675</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>113</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="24" t="n">
         <f aca="false">D20/$P20/10</f>
         <v>0.0758776288576724</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="25" t="n">
         <v>5.9</v>
       </c>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="24" t="n">
         <f aca="false">F20/$P20/10</f>
         <v>0.0039617523031882</v>
       </c>
-      <c r="H20" s="24" t="n">
+      <c r="H20" s="25" t="n">
         <v>208</v>
       </c>
-      <c r="I20" s="23" t="n">
+      <c r="I20" s="24" t="n">
         <f aca="false">H20/$P20/10</f>
         <v>0.139668555773415</v>
       </c>
-      <c r="J20" s="22" t="n">
+      <c r="J20" s="23" t="n">
         <f aca="false">L20*$J$37/100</f>
         <v>62.9</v>
       </c>
-      <c r="K20" s="23" t="n">
+      <c r="K20" s="24" t="n">
         <f aca="false">J20/$P20/10</f>
         <v>0.0422363084526336</v>
       </c>
-      <c r="L20" s="22" t="n">
+      <c r="L20" s="23" t="n">
         <v>370</v>
       </c>
-      <c r="M20" s="22" t="n">
+      <c r="M20" s="23" t="n">
         <f aca="false">O20*$M$37/100</f>
         <v>340</v>
       </c>
-      <c r="N20" s="23" t="n">
+      <c r="N20" s="24" t="n">
         <f aca="false">M20/$P20/10</f>
         <v>0.228304370014235</v>
       </c>
-      <c r="O20" s="22" t="n">
+      <c r="O20" s="23" t="n">
         <v>2500</v>
       </c>
-      <c r="P20" s="25" t="n">
+      <c r="P20" s="26" t="n">
         <v>148.924</v>
       </c>
-      <c r="Q20" s="25" t="n">
+      <c r="Q20" s="26" t="n">
         <f aca="false">100*P20/$P$36</f>
         <v>1.02285819233696</v>
       </c>
-      <c r="R20" s="22" t="n">
+      <c r="R20" s="23" t="n">
         <f aca="false">H20+F20+B20+D20+J20+M20</f>
         <v>869.8</v>
       </c>
-      <c r="S20" s="25" t="n">
+      <c r="S20" s="26" t="n">
         <f aca="false">R20/P20</f>
         <v>5.84056297171712</v>
       </c>
-      <c r="U20" s="25" t="n">
-        <f aca="false">-T20+($Q$45 + $Q$46)*1000*Q20/100</f>
-        <v>454.416003385809</v>
-      </c>
-      <c r="V20" s="25" t="n">
-        <f aca="false">U20/P20/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W20" s="25" t="n">
-        <f aca="false">ROUND(U20/P20 *100/1000, 2)</f>
+      <c r="T20" s="26"/>
+      <c r="U20" s="26"/>
+      <c r="V20" s="0" t="n">
+        <f aca="false">T20+U20</f>
+        <v>0</v>
+      </c>
+      <c r="W20" s="27" t="n">
+        <f aca="false">3/5*H20+M20/3</f>
+        <v>238.133333333333</v>
+      </c>
+      <c r="X20" s="27" t="n">
+        <f aca="false">R20-V20</f>
+        <v>869.8</v>
+      </c>
+      <c r="Y20" s="27" t="n">
+        <f aca="false">1000/100*Q20*($Q$41+$Q$47-$Q$49)-V20</f>
+        <v>563.681806924014</v>
+      </c>
+      <c r="Z20" s="27" t="n">
+        <f aca="false">Y20-V20+Q20/100*1000 *($Q$46+$Q$43)</f>
+        <v>1006.75942724777</v>
+      </c>
+      <c r="AA20" s="26" t="n">
+        <f aca="false">-V20+($Q$45 + $Q$46)*1000*Q20/100</f>
+        <v>461.395987690318</v>
+      </c>
+      <c r="AB20" s="26" t="n">
+        <f aca="false">AA20/P20/10</f>
+        <v>0.309819765578629</v>
+      </c>
+      <c r="AC20" s="26" t="n">
+        <f aca="false">ROUND(AA20/P20 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y20" s="25" t="n">
+      <c r="AE20" s="26" t="n">
         <f aca="false">-Q20*($Q$47)*10</f>
         <v>-245.48596616087</v>
       </c>
-      <c r="Z20" s="25" t="n">
-        <f aca="false">Y20/P20/10</f>
+      <c r="AF20" s="26" t="n">
+        <f aca="false">AE20/P20/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC20" s="22" t="n">
+      <c r="AI20" s="23" t="n">
         <v>218.8</v>
       </c>
-      <c r="AH20" s="22" t="s">
+      <c r="AN20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AO20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="23" t="n">
+        <v>37</v>
+      </c>
+      <c r="AQ20" s="23" t="n">
+        <f aca="false">AO20+AP20/100</f>
+        <v>0.37</v>
+      </c>
+      <c r="AR20" s="23" t="n">
+        <f aca="false">AQ20*1000</f>
+        <v>370</v>
+      </c>
+      <c r="AU20" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV20" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX20" s="28" t="n">
+        <f aca="false">AV20+AW20/10</f>
+        <v>2.5</v>
+      </c>
+      <c r="AY20" s="28" t="n">
+        <f aca="false">1000*AX20</f>
+        <v>2500</v>
+      </c>
+      <c r="BA20" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB20" s="23" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BC20" s="23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BD20" s="23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BE20" s="23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BF20" s="23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BG20" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI20" s="28" t="n">
+        <f aca="false">BB20*1000</f>
+        <v>370</v>
+      </c>
+      <c r="BK20" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="BL20" s="23" t="n">
+        <v>51</v>
+      </c>
+      <c r="BM20" s="23" t="n">
+        <v>103</v>
+      </c>
+      <c r="BN20" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO20" s="23" t="n">
+        <v>140</v>
+      </c>
+      <c r="BQ20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="BR20" s="23" t="n">
         <v>113</v>
       </c>
-      <c r="AI20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="AK20" s="22" t="n">
-        <f aca="false">AI20+AJ20/100</f>
-        <v>0.37</v>
-      </c>
-      <c r="AL20" s="22" t="n">
-        <f aca="false">AK20*1000</f>
-        <v>370</v>
-      </c>
-      <c r="AO20" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="AP20" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ20" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR20" s="26" t="n">
-        <f aca="false">AP20+AQ20/10</f>
-        <v>2.5</v>
-      </c>
-      <c r="AS20" s="26" t="n">
-        <f aca="false">1000*AR20</f>
-        <v>2500</v>
-      </c>
-      <c r="AU20" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="AV20" s="22" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AW20" s="22" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AX20" s="22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY20" s="22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AZ20" s="22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BA20" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="BC20" s="26" t="n">
-        <f aca="false">AV20*1000</f>
-        <v>370</v>
-      </c>
-      <c r="BE20" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="BF20" s="22" t="n">
-        <v>51</v>
-      </c>
-      <c r="BG20" s="22" t="n">
-        <v>103</v>
-      </c>
-      <c r="BH20" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI20" s="22" t="n">
-        <v>140</v>
-      </c>
-      <c r="BK20" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="BL20" s="22" t="n">
-        <v>113</v>
-      </c>
-      <c r="BM20" s="22" t="s">
-        <v>116</v>
+      <c r="BS20" s="23" t="s">
+        <v>124</v>
       </c>
     </row>
-    <row r="21" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="22" t="n">
+    <row r="21" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="23" t="n">
         <v>97</v>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="24" t="n">
         <f aca="false">B21/$P21/10</f>
         <v>0.0299863052234907</v>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="23" t="n">
         <v>160</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="24" t="n">
         <f aca="false">D21/$P21/10</f>
         <v>0.0494619467603971</v>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="30" t="n">
         <v>241.4</v>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="G21" s="24" t="n">
         <f aca="false">F21/$P21/10</f>
         <v>0.0746257121747491</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="30" t="n">
         <v>331</v>
       </c>
-      <c r="I21" s="23" t="n">
+      <c r="I21" s="24" t="n">
         <f aca="false">H21/$P21/10</f>
         <v>0.102324402360571</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="23" t="n">
         <f aca="false">L21*$J$37/100</f>
         <v>159.8</v>
       </c>
-      <c r="K21" s="23" t="n">
+      <c r="K21" s="24" t="n">
         <f aca="false">J21/$P21/10</f>
         <v>0.0494001193269466</v>
       </c>
-      <c r="L21" s="22" t="n">
+      <c r="L21" s="23" t="n">
         <v>940</v>
       </c>
-      <c r="M21" s="22" t="n">
+      <c r="M21" s="23" t="n">
         <f aca="false">O21*$M$37/100</f>
         <v>516.8</v>
       </c>
-      <c r="N21" s="23" t="n">
+      <c r="N21" s="24" t="n">
         <f aca="false">M21/$P21/10</f>
         <v>0.159762088036082</v>
       </c>
-      <c r="O21" s="22" t="n">
+      <c r="O21" s="23" t="n">
         <v>3800</v>
       </c>
-      <c r="P21" s="25" t="n">
+      <c r="P21" s="26" t="n">
         <v>323.481</v>
       </c>
-      <c r="Q21" s="25" t="n">
+      <c r="Q21" s="26" t="n">
         <f aca="false">100*P21/$P$36</f>
         <v>2.22177211809615</v>
       </c>
-      <c r="R21" s="22" t="n">
+      <c r="R21" s="23" t="n">
         <f aca="false">H21+F21+B21+D21+J21+M21</f>
         <v>1506</v>
       </c>
-      <c r="S21" s="25" t="n">
+      <c r="S21" s="26" t="n">
         <f aca="false">R21/P21</f>
         <v>4.65560573882237</v>
       </c>
-      <c r="T21" s="29" t="n">
+      <c r="T21" s="26"/>
+      <c r="U21" s="31" t="n">
         <f aca="false">F21</f>
         <v>241.4</v>
       </c>
-      <c r="U21" s="25" t="n">
-        <f aca="false">-T21+($Q$45 + $Q$46)*1000*Q21/100</f>
-        <v>745.646702957514</v>
-      </c>
-      <c r="V21" s="25" t="n">
-        <f aca="false">U21/P21/10</f>
-        <v>0.230507109523438</v>
-      </c>
-      <c r="W21" s="25" t="n">
-        <f aca="false">ROUND(U21/P21 *100/1000, 2)</f>
-        <v>0.23</v>
-      </c>
-      <c r="Y21" s="25" t="n">
+      <c r="V21" s="0" t="n">
+        <f aca="false">T21+U21</f>
+        <v>241.4</v>
+      </c>
+      <c r="W21" s="27" t="n">
+        <f aca="false">3/5*H21+M21/3</f>
+        <v>370.866666666667</v>
+      </c>
+      <c r="X21" s="27" t="n">
+        <f aca="false">R21-V21</f>
+        <v>1264.6</v>
+      </c>
+      <c r="Y21" s="27" t="n">
+        <f aca="false">1000/100*Q21*($Q$41+$Q$47-$Q$49)-V21</f>
+        <v>982.985287701017</v>
+      </c>
+      <c r="Z21" s="27" t="n">
+        <f aca="false">Y21-V21+Q21/100*1000 *($Q$46+$Q$43)</f>
+        <v>1704.00364672943</v>
+      </c>
+      <c r="AA21" s="26" t="n">
+        <f aca="false">-U21+($Q$45 + $Q$46)*1000*Q21/100</f>
+        <v>760.808075891402</v>
+      </c>
+      <c r="AB21" s="26" t="n">
+        <f aca="false">AA21/P21/10</f>
+        <v>0.235194053403879</v>
+      </c>
+      <c r="AC21" s="26" t="n">
+        <f aca="false">ROUND(AA21/P21 *100/1000, 2)</f>
+        <v>0.24</v>
+      </c>
+      <c r="AE21" s="26" t="n">
         <f aca="false">-Q21*($Q$47)*10</f>
         <v>-533.225308343076</v>
       </c>
-      <c r="Z21" s="25" t="n">
-        <f aca="false">Y21/P21/10</f>
+      <c r="AF21" s="26" t="n">
+        <f aca="false">AE21/P21/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC21" s="22" t="n">
+      <c r="AI21" s="23" t="n">
         <v>602.4</v>
       </c>
-      <c r="AH21" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI21" s="22" t="n">
+      <c r="AN21" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AO21" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" s="22" t="n">
+      <c r="AP21" s="23" t="n">
         <v>94</v>
       </c>
-      <c r="AK21" s="22" t="n">
-        <f aca="false">AI21+AJ21/100</f>
+      <c r="AQ21" s="23" t="n">
+        <f aca="false">AO21+AP21/100</f>
         <v>0.94</v>
       </c>
-      <c r="AL21" s="22" t="n">
-        <f aca="false">AK21*1000</f>
+      <c r="AR21" s="23" t="n">
+        <f aca="false">AQ21*1000</f>
         <v>940</v>
       </c>
-      <c r="AO21" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP21" s="22" t="n">
+      <c r="AU21" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="AV21" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AQ21" s="22" t="n">
+      <c r="AW21" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="AR21" s="26" t="n">
-        <f aca="false">AP21+AQ21/10</f>
+      <c r="AX21" s="28" t="n">
+        <f aca="false">AV21+AW21/10</f>
         <v>3.8</v>
       </c>
-      <c r="AS21" s="26" t="n">
-        <f aca="false">1000*AR21</f>
+      <c r="AY21" s="28" t="n">
+        <f aca="false">1000*AX21</f>
         <v>3800</v>
       </c>
-      <c r="AT21" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="AU21" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV21" s="22" t="n">
+      <c r="AZ21" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BA21" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB21" s="23" t="n">
         <v>0.94</v>
       </c>
-      <c r="AW21" s="22" t="n">
+      <c r="BC21" s="23" t="n">
         <v>2.1</v>
       </c>
-      <c r="AX21" s="22" t="n">
+      <c r="BD21" s="23" t="n">
         <v>2.33</v>
       </c>
-      <c r="AY21" s="22" t="n">
+      <c r="BE21" s="23" t="n">
         <v>0.9</v>
       </c>
-      <c r="AZ21" s="22" t="n">
+      <c r="BF21" s="23" t="n">
         <v>1.22</v>
       </c>
-      <c r="BA21" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC21" s="26" t="n">
-        <f aca="false">AV21*1000</f>
+      <c r="BG21" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="BI21" s="28" t="n">
+        <f aca="false">BB21*1000</f>
         <v>940</v>
       </c>
-      <c r="BE21" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="BF21" s="22" t="n">
+      <c r="BK21" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="BL21" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="BG21" s="22" t="n">
+      <c r="BM21" s="23" t="n">
         <v>71</v>
       </c>
-      <c r="BH21" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI21" s="22" t="n">
+      <c r="BN21" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO21" s="23" t="n">
         <v>97</v>
       </c>
-      <c r="BK21" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="BL21" s="22" t="n">
+      <c r="BQ21" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="BR21" s="23" t="n">
         <v>160</v>
       </c>
-      <c r="BM21" s="22" t="s">
-        <v>123</v>
+      <c r="BS21" s="23" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="22" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="22" t="n">
+    <row r="22" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="23" t="n">
         <v>467</v>
       </c>
-      <c r="C22" s="23" t="n">
+      <c r="C22" s="24" t="n">
         <f aca="false">B22/$P22/10</f>
         <v>0.0257444955291679</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <v>891</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="24" t="n">
         <f aca="false">D22/$P22/10</f>
         <v>0.0491185128832733</v>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="F22" s="25" t="n">
         <v>544.5</v>
       </c>
-      <c r="G22" s="23" t="n">
+      <c r="G22" s="24" t="n">
         <f aca="false">F22/$P22/10</f>
         <v>0.0300168689842225</v>
       </c>
-      <c r="H22" s="24" t="n">
+      <c r="H22" s="25" t="n">
         <v>2618</v>
       </c>
-      <c r="I22" s="23" t="n">
+      <c r="I22" s="24" t="n">
         <f aca="false">H22/$P22/10</f>
         <v>0.144323531681716</v>
       </c>
-      <c r="J22" s="22" t="n">
+      <c r="J22" s="23" t="n">
         <f aca="false">L22*$J$37/100</f>
         <v>1208.7</v>
       </c>
-      <c r="K22" s="23" t="n">
+      <c r="K22" s="24" t="n">
         <f aca="false">J22/$P22/10</f>
         <v>0.0666324876790262</v>
       </c>
-      <c r="L22" s="22" t="n">
+      <c r="L22" s="23" t="n">
         <v>7110</v>
       </c>
-      <c r="M22" s="22" t="n">
+      <c r="M22" s="23" t="n">
         <f aca="false">O22*$M$37/100</f>
         <v>7684</v>
       </c>
-      <c r="N22" s="23" t="n">
+      <c r="N22" s="24" t="n">
         <f aca="false">M22/$P22/10</f>
         <v>0.423598937143739</v>
       </c>
-      <c r="O22" s="22" t="n">
+      <c r="O22" s="23" t="n">
         <v>56500</v>
       </c>
-      <c r="P22" s="25" t="n">
+      <c r="P22" s="26" t="n">
         <v>1813.98</v>
       </c>
-      <c r="Q22" s="25" t="n">
+      <c r="Q22" s="26" t="n">
         <f aca="false">100*P22/$P$36</f>
         <v>12.4590012606121</v>
       </c>
-      <c r="R22" s="22" t="n">
+      <c r="R22" s="23" t="n">
         <f aca="false">H22+F22+B22+D22+J22+M22</f>
         <v>13413.2</v>
       </c>
-      <c r="S22" s="25" t="n">
+      <c r="S22" s="26" t="n">
         <f aca="false">R22/P22</f>
         <v>7.39434833901146</v>
       </c>
-      <c r="T22" s="22" t="n">
-        <f aca="false">B22+F22</f>
+      <c r="T22" s="26" t="n">
+        <f aca="false">B22</f>
+        <v>467</v>
+      </c>
+      <c r="U22" s="26" t="n">
+        <f aca="false">F22</f>
+        <v>544.5</v>
+      </c>
+      <c r="V22" s="0" t="n">
+        <f aca="false">T22+U22</f>
         <v>1011.5</v>
       </c>
-      <c r="U22" s="25" t="n">
-        <f aca="false">-T22+($Q$45 + $Q$46)*1000*Q22/100</f>
-        <v>4523.54835904078</v>
-      </c>
-      <c r="V22" s="25" t="n">
-        <f aca="false">U22/P22/10</f>
-        <v>0.249371457184797</v>
-      </c>
-      <c r="W22" s="25" t="n">
-        <f aca="false">ROUND(U22/P22 *100/1000, 2)</f>
+      <c r="W22" s="27" t="n">
+        <f aca="false">3/5*H22+M22/3</f>
+        <v>4132.13333333333</v>
+      </c>
+      <c r="X22" s="27" t="n">
+        <f aca="false">R22-V22</f>
+        <v>12401.7</v>
+      </c>
+      <c r="Y22" s="27" t="n">
+        <f aca="false">1000/100*Q22*($Q$41+$Q$47-$Q$49)-V22</f>
+        <v>5854.46870970442</v>
+      </c>
+      <c r="Z22" s="27" t="n">
+        <f aca="false">Y22-V22+Q22/100*1000 *($Q$46+$Q$43)</f>
+        <v>10239.9090397713</v>
+      </c>
+      <c r="AA22" s="26" t="n">
+        <f aca="false">-V22+($Q$45 + $Q$46)*1000*Q22/100</f>
+        <v>4608.56858364321</v>
+      </c>
+      <c r="AB22" s="26" t="n">
+        <f aca="false">AA22/P22/10</f>
+        <v>0.254058401065238</v>
+      </c>
+      <c r="AC22" s="26" t="n">
+        <f aca="false">ROUND(AA22/P22 *100/1000, 2)</f>
         <v>0.25</v>
       </c>
-      <c r="Y22" s="25" t="n">
+      <c r="AE22" s="26" t="n">
         <f aca="false">-Q22*($Q$47)*10</f>
         <v>-2990.1603025469</v>
       </c>
-      <c r="Z22" s="25" t="n">
-        <f aca="false">Y22/P22/10</f>
+      <c r="AF22" s="26" t="n">
+        <f aca="false">AE22/P22/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC22" s="22" t="n">
+      <c r="AI22" s="23" t="n">
         <v>2258</v>
       </c>
-      <c r="AH22" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI22" s="22" t="n">
+      <c r="AN22" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO22" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="AJ22" s="22" t="n">
+      <c r="AP22" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="AK22" s="22" t="n">
-        <f aca="false">AI22+AJ22/100</f>
+      <c r="AQ22" s="23" t="n">
+        <f aca="false">AO22+AP22/100</f>
         <v>7.11</v>
       </c>
-      <c r="AL22" s="22" t="n">
-        <f aca="false">AK22*1000</f>
+      <c r="AR22" s="23" t="n">
+        <f aca="false">AQ22*1000</f>
         <v>7110</v>
       </c>
-      <c r="AO22" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="AP22" s="22" t="n">
+      <c r="AU22" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV22" s="23" t="n">
         <v>56</v>
       </c>
-      <c r="AQ22" s="22" t="n">
+      <c r="AW22" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="AR22" s="26" t="n">
-        <f aca="false">AP22+AQ22/10</f>
+      <c r="AX22" s="28" t="n">
+        <f aca="false">AV22+AW22/10</f>
         <v>56.5</v>
       </c>
-      <c r="AS22" s="26" t="n">
-        <f aca="false">1000*AR22</f>
+      <c r="AY22" s="28" t="n">
+        <f aca="false">1000*AX22</f>
         <v>56500</v>
       </c>
-      <c r="AU22" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="AV22" s="22" t="n">
+      <c r="BA22" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB22" s="23" t="n">
         <v>7.11</v>
       </c>
-      <c r="AW22" s="22" t="n">
+      <c r="BC22" s="23" t="n">
         <v>15.81</v>
       </c>
-      <c r="AX22" s="22" t="n">
+      <c r="BD22" s="23" t="n">
         <v>12.06</v>
       </c>
-      <c r="AY22" s="22" t="n">
+      <c r="BE22" s="23" t="n">
         <v>1.31</v>
       </c>
-      <c r="AZ22" s="22" t="n">
+      <c r="BF22" s="23" t="n">
         <v>1.78</v>
       </c>
-      <c r="BA22" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="BC22" s="26" t="n">
-        <f aca="false">AV22*1000</f>
+      <c r="BG22" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="BI22" s="28" t="n">
+        <f aca="false">BB22*1000</f>
         <v>7110</v>
       </c>
-      <c r="BE22" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="BF22" s="22" t="n">
+      <c r="BK22" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="BL22" s="23" t="n">
         <v>400</v>
       </c>
-      <c r="BG22" s="22" t="n">
+      <c r="BM22" s="23" t="n">
         <v>343</v>
       </c>
-      <c r="BH22" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="BI22" s="22" t="n">
+      <c r="BN22" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO22" s="23" t="n">
         <v>467</v>
       </c>
-      <c r="BK22" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="BL22" s="22" t="n">
+      <c r="BQ22" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="BR22" s="23" t="n">
         <v>891</v>
       </c>
-      <c r="BM22" s="22" t="s">
-        <v>130</v>
+      <c r="BS22" s="23" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="23" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="22" t="n">
+    <row r="23" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="24" t="n">
         <f aca="false">B23/$P23/10</f>
         <v>0.0816326530612245</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="24" t="n">
         <f aca="false">D23/$P23/10</f>
         <v>0.0604686318972033</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="24" t="n">
         <f aca="false">F23/$P23/10</f>
         <v>0</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I23" s="24" t="n">
         <f aca="false">H23/$P23/10</f>
         <v>0.0604686318972033</v>
       </c>
-      <c r="J23" s="22" t="n">
+      <c r="J23" s="23" t="n">
         <f aca="false">L23*$J$37/100</f>
         <v>30.6</v>
       </c>
-      <c r="K23" s="23" t="n">
+      <c r="K23" s="24" t="n">
         <f aca="false">J23/$P23/10</f>
         <v>0.0925170068027211</v>
       </c>
-      <c r="L23" s="22" t="n">
+      <c r="L23" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="M23" s="22" t="n">
+      <c r="M23" s="23" t="n">
         <f aca="false">O23*$M$37/100</f>
         <v>68</v>
       </c>
-      <c r="N23" s="23" t="n">
+      <c r="N23" s="24" t="n">
         <f aca="false">M23/$P23/10</f>
         <v>0.205593348450491</v>
       </c>
-      <c r="O23" s="22" t="n">
+      <c r="O23" s="23" t="n">
         <v>500</v>
       </c>
-      <c r="P23" s="25" t="n">
+      <c r="P23" s="26" t="n">
         <v>33.075</v>
       </c>
-      <c r="Q23" s="25" t="n">
+      <c r="Q23" s="26" t="n">
         <f aca="false">100*P23/$P$36</f>
         <v>0.227169796080852</v>
       </c>
-      <c r="R23" s="22" t="n">
+      <c r="R23" s="23" t="n">
         <f aca="false">H23+F23+B23+D23+J23+M23</f>
         <v>165.6</v>
       </c>
-      <c r="S23" s="25" t="n">
+      <c r="S23" s="26" t="n">
         <f aca="false">R23/P23</f>
         <v>5.00680272108844</v>
       </c>
-      <c r="U23" s="25" t="n">
-        <f aca="false">-T23+($Q$45 + $Q$46)*1000*Q23/100</f>
-        <v>100.922680776675</v>
-      </c>
-      <c r="V23" s="25" t="n">
-        <f aca="false">U23/P23/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W23" s="25" t="n">
-        <f aca="false">ROUND(U23/P23 *100/1000, 2)</f>
+      <c r="T23" s="26"/>
+      <c r="U23" s="26"/>
+      <c r="V23" s="0" t="n">
+        <f aca="false">T23+U23</f>
+        <v>0</v>
+      </c>
+      <c r="W23" s="27" t="n">
+        <f aca="false">3/5*H23+M23/3</f>
+        <v>34.6666666666667</v>
+      </c>
+      <c r="X23" s="27" t="n">
+        <f aca="false">R23-V23</f>
+        <v>165.6</v>
+      </c>
+      <c r="Y23" s="27" t="n">
+        <f aca="false">1000/100*Q23*($Q$41+$Q$47-$Q$49)-V23</f>
+        <v>125.189867073216</v>
+      </c>
+      <c r="Z23" s="27" t="n">
+        <f aca="false">Y23-V23+Q23/100*1000 *($Q$46+$Q$43)</f>
+        <v>223.594370660335</v>
+      </c>
+      <c r="AA23" s="26" t="n">
+        <f aca="false">-V23+($Q$45 + $Q$46)*1000*Q23/100</f>
+        <v>102.472887465131</v>
+      </c>
+      <c r="AB23" s="26" t="n">
+        <f aca="false">AA23/P23/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC23" s="26" t="n">
+        <f aca="false">ROUND(AA23/P23 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y23" s="25" t="n">
+      <c r="AE23" s="26" t="n">
         <f aca="false">-Q23*($Q$47)*10</f>
         <v>-54.5207510594045</v>
       </c>
-      <c r="Z23" s="25" t="n">
-        <f aca="false">Y23/P23/10</f>
+      <c r="AF23" s="26" t="n">
+        <f aca="false">AE23/P23/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC23" s="22" t="n">
+      <c r="AI23" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="AH23" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="AI23" s="22" t="n">
+      <c r="AN23" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" s="22" t="n">
+      <c r="AP23" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="AK23" s="22" t="n">
-        <f aca="false">AI23+AJ23/100</f>
+      <c r="AQ23" s="23" t="n">
+        <f aca="false">AO23+AP23/100</f>
         <v>0.18</v>
       </c>
-      <c r="AL23" s="22" t="n">
-        <f aca="false">AK23*1000</f>
+      <c r="AR23" s="23" t="n">
+        <f aca="false">AQ23*1000</f>
         <v>180</v>
       </c>
-      <c r="AO23" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="AP23" s="22" t="n">
+      <c r="AU23" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="AV23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AQ23" s="22" t="n">
+      <c r="AW23" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="AR23" s="26" t="n">
-        <f aca="false">AP23+AQ23/10</f>
+      <c r="AX23" s="28" t="n">
+        <f aca="false">AV23+AW23/10</f>
         <v>0.5</v>
       </c>
-      <c r="AS23" s="26" t="n">
-        <f aca="false">1000*AR23</f>
+      <c r="AY23" s="28" t="n">
+        <f aca="false">1000*AX23</f>
         <v>500</v>
       </c>
-      <c r="AU23" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="AV23" s="22" t="n">
+      <c r="BA23" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB23" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="AW23" s="22" t="n">
+      <c r="BC23" s="23" t="n">
         <v>0.4</v>
       </c>
-      <c r="AX23" s="22" t="n">
+      <c r="BD23" s="23" t="n">
         <v>0.24</v>
       </c>
-      <c r="AY23" s="22" t="n">
+      <c r="BE23" s="23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AZ23" s="22" t="n">
+      <c r="BF23" s="23" t="n">
         <v>2.26</v>
       </c>
-      <c r="BA23" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC23" s="26" t="n">
-        <f aca="false">AV23*1000</f>
+      <c r="BG23" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="BI23" s="28" t="n">
+        <f aca="false">BB23*1000</f>
         <v>180</v>
       </c>
-      <c r="BE23" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF23" s="22" t="n">
+      <c r="BK23" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="BL23" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="BG23" s="22" t="n">
+      <c r="BM23" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="BH23" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI23" s="22" t="n">
+      <c r="BN23" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO23" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="BK23" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="BL23" s="22" t="n">
+      <c r="BQ23" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="BR23" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="BM23" s="22" t="s">
-        <v>130</v>
+      <c r="BS23" s="23" t="s">
+        <v>138</v>
       </c>
     </row>
-    <row r="24" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B24" s="22" t="n">
+    <row r="24" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="23" t="n">
         <v>41</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="24" t="n">
         <f aca="false">B24/$P24/10</f>
         <v>0.0759034360189574</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="24" t="n">
         <f aca="false">D24/$P24/10</f>
         <v>0.0444312796208531</v>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="25" t="n">
         <v>0.1</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G24" s="24" t="n">
         <f aca="false">F24/$P24/10</f>
         <v>0.000185130331753555</v>
       </c>
-      <c r="H24" s="24" t="n">
+      <c r="H24" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="I24" s="23" t="n">
+      <c r="I24" s="24" t="n">
         <f aca="false">H24/$P24/10</f>
         <v>0.0573904028436019</v>
       </c>
-      <c r="J24" s="22" t="n">
+      <c r="J24" s="23" t="n">
         <f aca="false">L24*$J$37/100</f>
         <v>23.8</v>
       </c>
-      <c r="K24" s="23" t="n">
+      <c r="K24" s="24" t="n">
         <f aca="false">J24/$P24/10</f>
         <v>0.044061018957346</v>
       </c>
-      <c r="L24" s="22" t="n">
+      <c r="L24" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="M24" s="22" t="n">
+      <c r="M24" s="23" t="n">
         <f aca="false">O24*$M$37/100</f>
         <v>108.8</v>
       </c>
-      <c r="N24" s="23" t="n">
+      <c r="N24" s="24" t="n">
         <f aca="false">M24/$P24/10</f>
         <v>0.201421800947867</v>
       </c>
-      <c r="O24" s="22" t="n">
+      <c r="O24" s="23" t="n">
         <v>800</v>
       </c>
-      <c r="P24" s="25" t="n">
+      <c r="P24" s="26" t="n">
         <v>54.016</v>
       </c>
-      <c r="Q24" s="25" t="n">
+      <c r="Q24" s="26" t="n">
         <f aca="false">100*P24/$P$36</f>
         <v>0.370999356163366</v>
       </c>
-      <c r="R24" s="22" t="n">
+      <c r="R24" s="23" t="n">
         <f aca="false">H24+F24+B24+D24+J24+M24</f>
         <v>228.7</v>
       </c>
-      <c r="S24" s="25" t="n">
+      <c r="S24" s="26" t="n">
         <f aca="false">R24/P24</f>
         <v>4.23393068720379</v>
       </c>
-      <c r="U24" s="25" t="n">
-        <f aca="false">-T24+($Q$45 + $Q$46)*1000*Q24/100</f>
-        <v>164.820544968493</v>
-      </c>
-      <c r="V24" s="25" t="n">
-        <f aca="false">U24/P24/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W24" s="25" t="n">
-        <f aca="false">ROUND(U24/P24 *100/1000, 2)</f>
+      <c r="T24" s="26"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="0" t="n">
+        <f aca="false">T24+U24</f>
+        <v>0</v>
+      </c>
+      <c r="W24" s="27" t="n">
+        <f aca="false">3/5*H24+M24/3</f>
+        <v>54.8666666666667</v>
+      </c>
+      <c r="X24" s="27" t="n">
+        <f aca="false">R24-V24</f>
+        <v>228.7</v>
+      </c>
+      <c r="Y24" s="27" t="n">
+        <f aca="false">1000/100*Q24*($Q$41+$Q$47-$Q$49)-V24</f>
+        <v>204.452180191289</v>
+      </c>
+      <c r="Z24" s="27" t="n">
+        <f aca="false">Y24-V24+Q24/100*1000 *($Q$46+$Q$43)</f>
+        <v>365.160197296711</v>
+      </c>
+      <c r="AA24" s="26" t="n">
+        <f aca="false">-V24+($Q$45 + $Q$46)*1000*Q24/100</f>
+        <v>167.352244574952</v>
+      </c>
+      <c r="AB24" s="26" t="n">
+        <f aca="false">AA24/P24/10</f>
+        <v>0.309819765578629</v>
+      </c>
+      <c r="AC24" s="26" t="n">
+        <f aca="false">ROUND(AA24/P24 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y24" s="25" t="n">
+      <c r="AE24" s="26" t="n">
         <f aca="false">-Q24*($Q$47)*10</f>
         <v>-89.0398454792077</v>
       </c>
-      <c r="Z24" s="25" t="n">
-        <f aca="false">Y24/P24/10</f>
+      <c r="AF24" s="26" t="n">
+        <f aca="false">AE24/P24/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC24" s="22" t="n">
+      <c r="AI24" s="23" t="n">
         <v>84.3</v>
       </c>
-      <c r="AH24" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="AI24" s="22" t="n">
+      <c r="AN24" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="AO24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" s="22" t="n">
+      <c r="AP24" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="AK24" s="22" t="n">
-        <f aca="false">AI24+AJ24/100</f>
+      <c r="AQ24" s="23" t="n">
+        <f aca="false">AO24+AP24/100</f>
         <v>0.14</v>
       </c>
-      <c r="AL24" s="22" t="n">
-        <f aca="false">AK24*1000</f>
+      <c r="AR24" s="23" t="n">
+        <f aca="false">AQ24*1000</f>
         <v>140</v>
       </c>
-      <c r="AO24" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="AP24" s="22" t="n">
+      <c r="AU24" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AQ24" s="22" t="n">
+      <c r="AW24" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="AR24" s="26" t="n">
-        <f aca="false">AP24+AQ24/10</f>
+      <c r="AX24" s="28" t="n">
+        <f aca="false">AV24+AW24/10</f>
         <v>0.8</v>
       </c>
-      <c r="AS24" s="26" t="n">
-        <f aca="false">1000*AR24</f>
+      <c r="AY24" s="28" t="n">
+        <f aca="false">1000*AX24</f>
         <v>800</v>
       </c>
-      <c r="AU24" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="AV24" s="22" t="n">
+      <c r="BA24" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="BB24" s="23" t="n">
         <v>0.14</v>
       </c>
-      <c r="AW24" s="22" t="n">
+      <c r="BC24" s="23" t="n">
         <v>0.31</v>
       </c>
-      <c r="AX24" s="22" t="n">
+      <c r="BD24" s="23" t="n">
         <v>0.42</v>
       </c>
-      <c r="AY24" s="22" t="n">
+      <c r="BE24" s="23" t="n">
         <v>0.74</v>
       </c>
-      <c r="AZ24" s="22" t="n">
+      <c r="BF24" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="BA24" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="BC24" s="26" t="n">
-        <f aca="false">AV24*1000</f>
+      <c r="BG24" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="BI24" s="28" t="n">
+        <f aca="false">BB24*1000</f>
         <v>140</v>
       </c>
-      <c r="BE24" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="BF24" s="22" t="n">
+      <c r="BK24" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="BL24" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="BG24" s="22" t="n">
+      <c r="BM24" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="BH24" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI24" s="22" t="n">
+      <c r="BN24" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO24" s="23" t="n">
         <v>41</v>
       </c>
-      <c r="BK24" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="BL24" s="22" t="n">
+      <c r="BQ24" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="BR24" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="BM24" s="22" t="s">
-        <v>139</v>
+      <c r="BS24" s="23" t="s">
+        <v>147</v>
       </c>
     </row>
-    <row r="25" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="22" t="n">
+    <row r="25" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C25" s="24" t="n">
         <f aca="false">B25/$P25/10</f>
         <v>0.0198137507430157</v>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="24" t="n">
         <f aca="false">D25/$P25/10</f>
         <v>0.0634040023776501</v>
       </c>
-      <c r="F25" s="28" t="n">
+      <c r="F25" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="23" t="n">
+      <c r="G25" s="24" t="n">
         <f aca="false">F25/$P25/10</f>
         <v>0</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="30" t="n">
         <v>208</v>
       </c>
-      <c r="I25" s="23" t="n">
+      <c r="I25" s="24" t="n">
         <f aca="false">H25/$P25/10</f>
         <v>0.412126015454726</v>
       </c>
-      <c r="J25" s="22" t="n">
+      <c r="J25" s="23" t="n">
         <f aca="false">L25*$J$37/100</f>
         <v>35.7</v>
       </c>
-      <c r="K25" s="23" t="n">
+      <c r="K25" s="24" t="n">
         <f aca="false">J25/$P25/10</f>
         <v>0.0707350901525659</v>
       </c>
-      <c r="L25" s="22" t="n">
+      <c r="L25" s="23" t="n">
         <v>210</v>
       </c>
-      <c r="M25" s="22" t="n">
+      <c r="M25" s="23" t="n">
         <f aca="false">O25*$M$37/100</f>
         <v>244.8</v>
       </c>
-      <c r="N25" s="23" t="n">
+      <c r="N25" s="24" t="n">
         <f aca="false">M25/$P25/10</f>
         <v>0.485040618189023</v>
       </c>
-      <c r="O25" s="22" t="n">
+      <c r="O25" s="23" t="n">
         <v>1800</v>
       </c>
-      <c r="P25" s="25" t="n">
+      <c r="P25" s="26" t="n">
         <v>50.47</v>
       </c>
-      <c r="Q25" s="25" t="n">
+      <c r="Q25" s="26" t="n">
         <f aca="false">100*P25/$P$36</f>
         <v>0.346644281427078</v>
       </c>
-      <c r="R25" s="22" t="n">
+      <c r="R25" s="23" t="n">
         <f aca="false">H25+F25+B25+D25+J25+M25</f>
         <v>530.5</v>
       </c>
-      <c r="S25" s="25" t="n">
+      <c r="S25" s="26" t="n">
         <f aca="false">R25/P25</f>
         <v>10.5111947691698</v>
       </c>
-      <c r="U25" s="25" t="n">
-        <f aca="false">-T25+($Q$45 + $Q$46)*1000*Q25/100</f>
-        <v>154.000535111075</v>
-      </c>
-      <c r="V25" s="25" t="n">
-        <f aca="false">U25/P25/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W25" s="25" t="n">
-        <f aca="false">ROUND(U25/P25 *100/1000, 2)</f>
+      <c r="T25" s="26"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="0" t="n">
+        <f aca="false">T25+U25</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="27" t="n">
+        <f aca="false">3/5*H25+M25/3</f>
+        <v>206.4</v>
+      </c>
+      <c r="X25" s="27" t="n">
+        <f aca="false">R25-V25</f>
+        <v>530.5</v>
+      </c>
+      <c r="Y25" s="27" t="n">
+        <f aca="false">1000/100*Q25*($Q$41+$Q$47-$Q$49)-V25</f>
+        <v>191.030463830241</v>
+      </c>
+      <c r="Z25" s="27" t="n">
+        <f aca="false">Y25-V25+Q25/100*1000 *($Q$46+$Q$43)</f>
+        <v>341.188447081697</v>
+      </c>
+      <c r="AA25" s="26" t="n">
+        <f aca="false">-V25+($Q$45 + $Q$46)*1000*Q25/100</f>
+        <v>156.366035687534</v>
+      </c>
+      <c r="AB25" s="26" t="n">
+        <f aca="false">AA25/P25/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC25" s="26" t="n">
+        <f aca="false">ROUND(AA25/P25 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y25" s="25" t="n">
+      <c r="AE25" s="26" t="n">
         <f aca="false">-Q25*($Q$47)*10</f>
         <v>-83.1946275424988</v>
       </c>
-      <c r="Z25" s="25" t="n">
-        <f aca="false">Y25/P25/10</f>
+      <c r="AF25" s="26" t="n">
+        <f aca="false">AE25/P25/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC25" s="22" t="n">
+      <c r="AI25" s="23" t="n">
         <v>89.5</v>
       </c>
-      <c r="AH25" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI25" s="22" t="n">
+      <c r="AN25" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" s="22" t="n">
+      <c r="AP25" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="AK25" s="22" t="n">
-        <f aca="false">AI25+AJ25/100</f>
+      <c r="AQ25" s="23" t="n">
+        <f aca="false">AO25+AP25/100</f>
         <v>0.21</v>
       </c>
-      <c r="AL25" s="22" t="n">
-        <f aca="false">AK25*1000</f>
+      <c r="AR25" s="23" t="n">
+        <f aca="false">AQ25*1000</f>
         <v>210</v>
       </c>
-      <c r="AO25" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="AP25" s="22" t="n">
+      <c r="AU25" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="AV25" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AQ25" s="22" t="n">
+      <c r="AW25" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="AR25" s="26" t="n">
-        <f aca="false">AP25+AQ25/10</f>
+      <c r="AX25" s="28" t="n">
+        <f aca="false">AV25+AW25/10</f>
         <v>1.8</v>
       </c>
-      <c r="AS25" s="26" t="n">
-        <f aca="false">1000*AR25</f>
+      <c r="AY25" s="28" t="n">
+        <f aca="false">1000*AX25</f>
         <v>1800</v>
       </c>
-      <c r="AU25" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="AV25" s="22" t="n">
+      <c r="BA25" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="BB25" s="23" t="n">
         <v>0.21</v>
       </c>
-      <c r="AW25" s="22" t="n">
+      <c r="BC25" s="23" t="n">
         <v>0.46</v>
       </c>
-      <c r="AX25" s="22" t="n">
+      <c r="BD25" s="23" t="n">
         <v>0.31</v>
       </c>
-      <c r="AY25" s="22" t="n">
+      <c r="BE25" s="23" t="n">
         <v>1.48</v>
       </c>
-      <c r="AZ25" s="22" t="n">
+      <c r="BF25" s="23" t="n">
         <v>2.01</v>
       </c>
-      <c r="BA25" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="BC25" s="26" t="n">
-        <f aca="false">AV25*1000</f>
+      <c r="BG25" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="BI25" s="28" t="n">
+        <f aca="false">BB25*1000</f>
         <v>210</v>
       </c>
-      <c r="BE25" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="BF25" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="BG25" s="22" t="n">
+      <c r="BK25" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="BL25" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM25" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="BH25" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI25" s="22" t="n">
+      <c r="BN25" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO25" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="BK25" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="BL25" s="22" t="n">
+      <c r="BQ25" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="BR25" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="BM25" s="22" t="s">
-        <v>145</v>
+      <c r="BS25" s="23" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="26" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B26" s="22" t="n">
+    <row r="26" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="23" t="n">
+      <c r="C26" s="24" t="n">
         <f aca="false">B26/$P26/10</f>
         <v>0.0510538983298082</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="E26" s="23" t="n">
+      <c r="E26" s="24" t="n">
         <f aca="false">D26/$P26/10</f>
         <v>0.0729341404711545</v>
       </c>
-      <c r="F26" s="24" t="n">
+      <c r="F26" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="23" t="n">
+      <c r="G26" s="24" t="n">
         <f aca="false">F26/$P26/10</f>
         <v>0</v>
       </c>
-      <c r="H26" s="24" t="n">
+      <c r="H26" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="I26" s="23" t="n">
+      <c r="I26" s="24" t="n">
         <f aca="false">H26/$P26/10</f>
         <v>0.0656407264240391</v>
       </c>
-      <c r="J26" s="22" t="n">
+      <c r="J26" s="23" t="n">
         <f aca="false">L26*$J$37/100</f>
         <v>45.9</v>
       </c>
-      <c r="K26" s="23" t="n">
+      <c r="K26" s="24" t="n">
         <f aca="false">J26/$P26/10</f>
         <v>0.334767704762599</v>
       </c>
-      <c r="L26" s="22" t="n">
+      <c r="L26" s="23" t="n">
         <v>270</v>
       </c>
-      <c r="M26" s="22" t="n">
+      <c r="M26" s="23" t="n">
         <f aca="false">O26*$M$37/100</f>
         <v>122.4</v>
       </c>
-      <c r="N26" s="23" t="n">
+      <c r="N26" s="24" t="n">
         <f aca="false">M26/$P26/10</f>
         <v>0.892713879366932</v>
       </c>
-      <c r="O26" s="22" t="n">
+      <c r="O26" s="23" t="n">
         <v>900</v>
       </c>
-      <c r="P26" s="25" t="n">
+      <c r="P26" s="26" t="n">
         <v>13.711</v>
       </c>
-      <c r="Q26" s="25" t="n">
+      <c r="Q26" s="26" t="n">
         <f aca="false">100*P26/$P$36</f>
         <v>0.0941715819822998</v>
       </c>
-      <c r="R26" s="22" t="n">
+      <c r="R26" s="23" t="n">
         <f aca="false">H26+F26+B26+D26+J26+M26</f>
         <v>194.3</v>
       </c>
-      <c r="S26" s="25" t="n">
+      <c r="S26" s="26" t="n">
         <f aca="false">R26/P26</f>
         <v>14.1711034935453</v>
       </c>
-      <c r="U26" s="25" t="n">
-        <f aca="false">-T26+($Q$45 + $Q$46)*1000*Q26/100</f>
-        <v>41.8367611830385</v>
-      </c>
-      <c r="V26" s="25" t="n">
-        <f aca="false">U26/P26/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W26" s="25" t="n">
-        <f aca="false">ROUND(U26/P26 *100/1000, 2)</f>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="0" t="n">
+        <f aca="false">T26+U26</f>
+        <v>0</v>
+      </c>
+      <c r="W26" s="27" t="n">
+        <f aca="false">3/5*H26+M26/3</f>
+        <v>46.2</v>
+      </c>
+      <c r="X26" s="27" t="n">
+        <f aca="false">R26-V26</f>
+        <v>194.3</v>
+      </c>
+      <c r="Y26" s="27" t="n">
+        <f aca="false">1000/100*Q26*($Q$41+$Q$47-$Q$49)-V26</f>
+        <v>51.8965462567157</v>
+      </c>
+      <c r="Z26" s="27" t="n">
+        <f aca="false">Y26-V26+Q26/100*1000 *($Q$46+$Q$43)</f>
+        <v>92.6894154534804</v>
+      </c>
+      <c r="AA26" s="26" t="n">
+        <f aca="false">-V26+($Q$45 + $Q$46)*1000*Q26/100</f>
+        <v>42.4793880584857</v>
+      </c>
+      <c r="AB26" s="26" t="n">
+        <f aca="false">AA26/P26/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC26" s="26" t="n">
+        <f aca="false">ROUND(AA26/P26 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y26" s="25" t="n">
+      <c r="AE26" s="26" t="n">
         <f aca="false">-Q26*($Q$47)*10</f>
         <v>-22.6011796757519</v>
       </c>
-      <c r="Z26" s="25" t="n">
-        <f aca="false">Y26/P26/10</f>
+      <c r="AF26" s="26" t="n">
+        <f aca="false">AE26/P26/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC26" s="22" t="n">
+      <c r="AI26" s="23" t="n">
         <v>24.6</v>
       </c>
-      <c r="AH26" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="AI26" s="22" t="n">
+      <c r="AN26" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="AO26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ26" s="22" t="n">
+      <c r="AP26" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="AK26" s="22" t="n">
-        <f aca="false">AI26+AJ26/100</f>
+      <c r="AQ26" s="23" t="n">
+        <f aca="false">AO26+AP26/100</f>
         <v>0.27</v>
       </c>
-      <c r="AL26" s="22" t="n">
-        <f aca="false">AK26*1000</f>
+      <c r="AR26" s="23" t="n">
+        <f aca="false">AQ26*1000</f>
         <v>270</v>
       </c>
-      <c r="AO26" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="AP26" s="22" t="n">
+      <c r="AU26" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="AV26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AQ26" s="22" t="n">
+      <c r="AW26" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AR26" s="26" t="n">
-        <f aca="false">AP26+AQ26/10</f>
+      <c r="AX26" s="28" t="n">
+        <f aca="false">AV26+AW26/10</f>
         <v>0.9</v>
       </c>
-      <c r="AS26" s="26" t="n">
-        <f aca="false">1000*AR26</f>
+      <c r="AY26" s="28" t="n">
+        <f aca="false">1000*AX26</f>
         <v>900</v>
       </c>
-      <c r="AU26" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="AV26" s="22" t="n">
+      <c r="BA26" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="BB26" s="23" t="n">
         <v>0.27</v>
       </c>
-      <c r="AW26" s="22" t="n">
+      <c r="BC26" s="23" t="n">
         <v>0.61</v>
       </c>
-      <c r="AX26" s="22" t="n">
+      <c r="BD26" s="23" t="n">
         <v>0.11</v>
       </c>
-      <c r="AY26" s="22" t="n">
+      <c r="BE26" s="23" t="n">
         <v>5.6</v>
       </c>
-      <c r="AZ26" s="22" t="n">
+      <c r="BF26" s="23" t="n">
         <v>7.59</v>
       </c>
-      <c r="BA26" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="BC26" s="26" t="n">
-        <f aca="false">AV26*1000</f>
+      <c r="BG26" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="BI26" s="28" t="n">
+        <f aca="false">BB26*1000</f>
         <v>270</v>
       </c>
-      <c r="BE26" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="BF26" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="BG26" s="22" t="n">
+      <c r="BK26" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="BL26" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="BM26" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="BH26" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI26" s="22" t="n">
+      <c r="BN26" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO26" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="BK26" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="BL26" s="22" t="n">
+      <c r="BQ26" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="BR26" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="BM26" s="22" t="s">
-        <v>151</v>
+      <c r="BS26" s="23" t="s">
+        <v>159</v>
       </c>
     </row>
-    <row r="27" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="B27" s="22" t="n">
+    <row r="27" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="23" t="n">
         <v>333</v>
       </c>
-      <c r="C27" s="23" t="n">
+      <c r="C27" s="24" t="n">
         <f aca="false">B27/$P27/10</f>
         <v>0.0397775325029027</v>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="23" t="n">
         <v>652</v>
       </c>
-      <c r="E27" s="23" t="n">
+      <c r="E27" s="24" t="n">
         <f aca="false">D27/$P27/10</f>
         <v>0.0778827363119896</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="F27" s="30" t="n">
         <v>1961</v>
       </c>
-      <c r="G27" s="23" t="n">
+      <c r="G27" s="24" t="n">
         <f aca="false">F27/$P27/10</f>
         <v>0.23424546918376</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="30" t="n">
         <v>913</v>
       </c>
-      <c r="I27" s="23" t="n">
+      <c r="I27" s="24" t="n">
         <f aca="false">H27/$P27/10</f>
         <v>0.109059721246697</v>
       </c>
-      <c r="J27" s="22" t="n">
+      <c r="J27" s="23" t="n">
         <f aca="false">L27*$J$37/100</f>
         <v>336.6</v>
       </c>
-      <c r="K27" s="23" t="n">
+      <c r="K27" s="24" t="n">
         <f aca="false">J27/$P27/10</f>
         <v>0.0402075598813125</v>
       </c>
-      <c r="L27" s="22" t="n">
+      <c r="L27" s="23" t="n">
         <v>1980</v>
       </c>
-      <c r="M27" s="22" t="n">
+      <c r="M27" s="23" t="n">
         <f aca="false">O27*$M$37/100</f>
         <v>1496</v>
       </c>
-      <c r="N27" s="23" t="n">
+      <c r="N27" s="24" t="n">
         <f aca="false">M27/$P27/10</f>
         <v>0.178700266139166</v>
       </c>
-      <c r="O27" s="22" t="n">
+      <c r="O27" s="23" t="n">
         <v>11000</v>
       </c>
-      <c r="P27" s="25" t="n">
+      <c r="P27" s="26" t="n">
         <v>837.156</v>
       </c>
-      <c r="Q27" s="25" t="n">
+      <c r="Q27" s="26" t="n">
         <f aca="false">100*P27/$P$36</f>
         <v>5.74985813478041</v>
       </c>
-      <c r="R27" s="22" t="n">
+      <c r="R27" s="23" t="n">
         <f aca="false">H27+F27+B27+D27+J27+M27</f>
         <v>5691.6</v>
       </c>
-      <c r="S27" s="25" t="n">
+      <c r="S27" s="26" t="n">
         <f aca="false">R27/P27</f>
         <v>6.79873285265829</v>
       </c>
-      <c r="U27" s="25" t="n">
-        <f aca="false">-T27+($Q$45 + $Q$46)*1000*Q27/100</f>
-        <v>2554.43772481568</v>
-      </c>
-      <c r="V27" s="25" t="n">
-        <f aca="false">U27/P27/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W27" s="25" t="n">
-        <f aca="false">ROUND(U27/P27 *100/1000, 2)</f>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="0" t="n">
+        <f aca="false">T27+U27</f>
+        <v>0</v>
+      </c>
+      <c r="W27" s="27" t="n">
+        <f aca="false">3/5*H27+M27/3</f>
+        <v>1046.46666666667</v>
+      </c>
+      <c r="X27" s="27" t="n">
+        <f aca="false">R27-V27</f>
+        <v>5691.6</v>
+      </c>
+      <c r="Y27" s="27" t="n">
+        <f aca="false">1000/100*Q27*($Q$41+$Q$47-$Q$49)-V27</f>
+        <v>3168.66057020546</v>
+      </c>
+      <c r="Z27" s="27" t="n">
+        <f aca="false">Y27-V27+Q27/100*1000 *($Q$46+$Q$43)</f>
+        <v>5659.3611175971</v>
+      </c>
+      <c r="AA27" s="26" t="n">
+        <f aca="false">-V27+($Q$45 + $Q$46)*1000*Q27/100</f>
+        <v>2593.67475672742</v>
+      </c>
+      <c r="AB27" s="26" t="n">
+        <f aca="false">AA27/P27/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC27" s="26" t="n">
+        <f aca="false">ROUND(AA27/P27 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y27" s="25" t="n">
+      <c r="AE27" s="26" t="n">
         <f aca="false">-Q27*($Q$47)*10</f>
         <v>-1379.9659523473</v>
       </c>
-      <c r="Z27" s="25" t="n">
-        <f aca="false">Y27/P27/10</f>
+      <c r="AF27" s="26" t="n">
+        <f aca="false">AE27/P27/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC27" s="22" t="n">
+      <c r="AI27" s="23" t="n">
         <v>1170.6</v>
       </c>
-      <c r="AH27" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="AI27" s="22" t="n">
+      <c r="AN27" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="AO27" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ27" s="22" t="n">
+      <c r="AP27" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="AK27" s="22" t="n">
-        <f aca="false">AI27+AJ27/100</f>
+      <c r="AQ27" s="23" t="n">
+        <f aca="false">AO27+AP27/100</f>
         <v>1.98</v>
       </c>
-      <c r="AL27" s="22" t="n">
-        <f aca="false">AK27*1000</f>
+      <c r="AR27" s="23" t="n">
+        <f aca="false">AQ27*1000</f>
         <v>1980</v>
       </c>
-      <c r="AO27" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="AP27" s="22" t="n">
+      <c r="AU27" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="AV27" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="AQ27" s="22" t="n">
+      <c r="AW27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AR27" s="26" t="n">
-        <f aca="false">AP27+AQ27/10</f>
+      <c r="AX27" s="28" t="n">
+        <f aca="false">AV27+AW27/10</f>
         <v>11</v>
       </c>
-      <c r="AS27" s="26" t="n">
-        <f aca="false">1000*AR27</f>
+      <c r="AY27" s="28" t="n">
+        <f aca="false">1000*AX27</f>
         <v>11000</v>
       </c>
-      <c r="AU27" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="AV27" s="22" t="n">
+      <c r="BA27" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="BB27" s="23" t="n">
         <v>1.98</v>
       </c>
-      <c r="AW27" s="22" t="n">
+      <c r="BC27" s="23" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX27" s="22" t="n">
+      <c r="BD27" s="23" t="n">
         <v>6.06</v>
       </c>
-      <c r="AY27" s="22" t="n">
+      <c r="BE27" s="23" t="n">
         <v>0.73</v>
       </c>
-      <c r="AZ27" s="22" t="n">
+      <c r="BF27" s="23" t="n">
         <v>0.99</v>
       </c>
-      <c r="BA27" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="BC27" s="26" t="n">
-        <f aca="false">AV27*1000</f>
+      <c r="BG27" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="BI27" s="28" t="n">
+        <f aca="false">BB27*1000</f>
         <v>1980</v>
       </c>
-      <c r="BE27" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="BF27" s="22" t="n">
+      <c r="BK27" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="BL27" s="23" t="n">
         <v>293</v>
       </c>
-      <c r="BG27" s="22" t="n">
+      <c r="BM27" s="23" t="n">
         <v>245</v>
       </c>
-      <c r="BH27" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI27" s="22" t="n">
+      <c r="BN27" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO27" s="23" t="n">
         <v>333</v>
       </c>
-      <c r="BK27" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="BL27" s="22" t="n">
+      <c r="BQ27" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="BR27" s="23" t="n">
         <v>652</v>
       </c>
-      <c r="BM27" s="22" t="s">
-        <v>105</v>
+      <c r="BS27" s="23" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="28" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="B28" s="22" t="n">
+    <row r="28" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="23" t="n">
         <v>497</v>
       </c>
-      <c r="C28" s="23" t="n">
+      <c r="C28" s="24" t="n">
         <f aca="false">B28/$P28/10</f>
         <v>0.0907081624570414</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="23" t="n">
         <v>427</v>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="24" t="n">
         <f aca="false">D28/$P28/10</f>
         <v>0.0779323649278806</v>
       </c>
-      <c r="F28" s="24" t="n">
+      <c r="F28" s="25" t="n">
         <v>63</v>
       </c>
-      <c r="G28" s="23" t="n">
+      <c r="G28" s="24" t="n">
         <f aca="false">F28/$P28/10</f>
         <v>0.0114982177762447</v>
       </c>
-      <c r="H28" s="24" t="n">
+      <c r="H28" s="25" t="n">
         <v>560</v>
       </c>
-      <c r="I28" s="23" t="n">
+      <c r="I28" s="24" t="n">
         <f aca="false">H28/$P28/10</f>
         <v>0.102206380233286</v>
       </c>
-      <c r="J28" s="22" t="n">
+      <c r="J28" s="23" t="n">
         <f aca="false">L28*$J$37/100</f>
         <v>202.3</v>
       </c>
-      <c r="K28" s="23" t="n">
+      <c r="K28" s="24" t="n">
         <f aca="false">J28/$P28/10</f>
         <v>0.0369220548592746</v>
       </c>
-      <c r="L28" s="22" t="n">
+      <c r="L28" s="23" t="n">
         <v>1190</v>
       </c>
-      <c r="M28" s="22" t="n">
+      <c r="M28" s="23" t="n">
         <f aca="false">O28*$M$37/100</f>
         <v>1088</v>
       </c>
-      <c r="N28" s="23" t="n">
+      <c r="N28" s="24" t="n">
         <f aca="false">M28/$P28/10</f>
         <v>0.198572395881813</v>
       </c>
-      <c r="O28" s="22" t="n">
+      <c r="O28" s="23" t="n">
         <v>8000</v>
       </c>
-      <c r="P28" s="25" t="n">
+      <c r="P28" s="26" t="n">
         <v>547.911</v>
       </c>
-      <c r="Q28" s="25" t="n">
+      <c r="Q28" s="26" t="n">
         <f aca="false">100*P28/$P$36</f>
         <v>3.76322993621937</v>
       </c>
-      <c r="R28" s="22" t="n">
+      <c r="R28" s="23" t="n">
         <f aca="false">H28+F28+B28+D28+J28+M28</f>
         <v>2837.3</v>
       </c>
-      <c r="S28" s="25" t="n">
+      <c r="S28" s="26" t="n">
         <f aca="false">R28/P28</f>
         <v>5.1783957613554</v>
       </c>
-      <c r="U28" s="25" t="n">
-        <f aca="false">-T28+($Q$45 + $Q$46)*1000*Q28/100</f>
-        <v>1671.85629469476</v>
-      </c>
-      <c r="V28" s="25" t="n">
-        <f aca="false">U28/P28/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W28" s="25" t="n">
-        <f aca="false">ROUND(U28/P28 *100/1000, 2)</f>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="0" t="n">
+        <f aca="false">T28+U28</f>
+        <v>0</v>
+      </c>
+      <c r="W28" s="27" t="n">
+        <f aca="false">3/5*H28+M28/3</f>
+        <v>698.666666666667</v>
+      </c>
+      <c r="X28" s="27" t="n">
+        <f aca="false">R28-V28</f>
+        <v>2837.3</v>
+      </c>
+      <c r="Y28" s="27" t="n">
+        <f aca="false">1000/100*Q28*($Q$41+$Q$47-$Q$49)-V28</f>
+        <v>2073.85956940145</v>
+      </c>
+      <c r="Z28" s="27" t="n">
+        <f aca="false">Y28-V28+Q28/100*1000 *($Q$46+$Q$43)</f>
+        <v>3704.00046025321</v>
+      </c>
+      <c r="AA28" s="26" t="n">
+        <f aca="false">-V28+($Q$45 + $Q$46)*1000*Q28/100</f>
+        <v>1697.53657577951</v>
+      </c>
+      <c r="AB28" s="26" t="n">
+        <f aca="false">AA28/P28/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC28" s="26" t="n">
+        <f aca="false">ROUND(AA28/P28 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y28" s="25" t="n">
+      <c r="AE28" s="26" t="n">
         <f aca="false">-Q28*($Q$47)*10</f>
         <v>-903.17518469265</v>
       </c>
-      <c r="Z28" s="25" t="n">
-        <f aca="false">Y28/P28/10</f>
+      <c r="AF28" s="26" t="n">
+        <f aca="false">AE28/P28/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC28" s="22" t="n">
+      <c r="AI28" s="23" t="n">
         <v>922.9</v>
       </c>
-      <c r="AH28" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI28" s="22" t="n">
+      <c r="AN28" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO28" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ28" s="22" t="n">
+      <c r="AP28" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="AK28" s="22" t="n">
-        <f aca="false">AI28+AJ28/100</f>
+      <c r="AQ28" s="23" t="n">
+        <f aca="false">AO28+AP28/100</f>
         <v>1.19</v>
       </c>
-      <c r="AL28" s="22" t="n">
-        <f aca="false">AK28*1000</f>
+      <c r="AR28" s="23" t="n">
+        <f aca="false">AQ28*1000</f>
         <v>1190</v>
       </c>
-      <c r="AO28" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="AP28" s="22" t="n">
+      <c r="AU28" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="AV28" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="AQ28" s="22" t="n">
+      <c r="AW28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AR28" s="26" t="n">
-        <f aca="false">AP28+AQ28/10</f>
+      <c r="AX28" s="28" t="n">
+        <f aca="false">AV28+AW28/10</f>
         <v>8</v>
       </c>
-      <c r="AS28" s="26" t="n">
-        <f aca="false">1000*AR28</f>
+      <c r="AY28" s="28" t="n">
+        <f aca="false">1000*AX28</f>
         <v>8000</v>
       </c>
-      <c r="AU28" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="AV28" s="22" t="n">
+      <c r="BA28" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="BB28" s="23" t="n">
         <v>1.19</v>
       </c>
-      <c r="AW28" s="22" t="n">
+      <c r="BC28" s="23" t="n">
         <v>2.65</v>
       </c>
-      <c r="AX28" s="22" t="n">
+      <c r="BD28" s="23" t="n">
         <v>4.77</v>
       </c>
-      <c r="AY28" s="22" t="n">
+      <c r="BE28" s="23" t="n">
         <v>0.56</v>
       </c>
-      <c r="AZ28" s="22" t="n">
+      <c r="BF28" s="23" t="n">
         <v>0.76</v>
       </c>
-      <c r="BA28" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="BC28" s="26" t="n">
-        <f aca="false">AV28*1000</f>
+      <c r="BG28" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="BI28" s="28" t="n">
+        <f aca="false">BB28*1000</f>
         <v>1190</v>
       </c>
-      <c r="BE28" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="BF28" s="22" t="n">
+      <c r="BK28" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="BL28" s="23" t="n">
         <v>192</v>
       </c>
-      <c r="BG28" s="22" t="n">
+      <c r="BM28" s="23" t="n">
         <v>365</v>
       </c>
-      <c r="BH28" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI28" s="22" t="n">
+      <c r="BN28" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO28" s="23" t="n">
         <v>497</v>
       </c>
-      <c r="BK28" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="BL28" s="22" t="n">
+      <c r="BQ28" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="BR28" s="23" t="n">
         <v>427</v>
       </c>
-      <c r="BM28" s="22" t="s">
-        <v>162</v>
+      <c r="BS28" s="23" t="s">
+        <v>170</v>
       </c>
     </row>
-    <row r="29" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B29" s="22" t="n">
+    <row r="29" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" s="23" t="n">
         <v>137</v>
       </c>
-      <c r="C29" s="23" t="n">
+      <c r="C29" s="24" t="n">
         <f aca="false">B29/$P29/10</f>
         <v>0.0646607669616519</v>
       </c>
-      <c r="D29" s="22" t="n">
+      <c r="D29" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="E29" s="23" t="n">
+      <c r="E29" s="24" t="n">
         <f aca="false">D29/$P29/10</f>
         <v>0.039646017699115</v>
       </c>
-      <c r="F29" s="28" t="n">
+      <c r="F29" s="30" t="n">
         <v>24.9</v>
       </c>
-      <c r="G29" s="23" t="n">
+      <c r="G29" s="24" t="n">
         <f aca="false">F29/$P29/10</f>
         <v>0.0117522123893805</v>
       </c>
-      <c r="H29" s="28" t="n">
+      <c r="H29" s="30" t="n">
         <v>330</v>
       </c>
-      <c r="I29" s="23" t="n">
+      <c r="I29" s="24" t="n">
         <f aca="false">H29/$P29/10</f>
         <v>0.155752212389381</v>
       </c>
-      <c r="J29" s="22" t="n">
+      <c r="J29" s="23" t="n">
         <f aca="false">L29*$J$37/100</f>
         <v>331.5</v>
       </c>
-      <c r="K29" s="23" t="n">
+      <c r="K29" s="24" t="n">
         <f aca="false">J29/$P29/10</f>
         <v>0.15646017699115</v>
       </c>
-      <c r="L29" s="22" t="n">
+      <c r="L29" s="23" t="n">
         <v>1950</v>
       </c>
-      <c r="M29" s="22" t="n">
+      <c r="M29" s="23" t="n">
         <f aca="false">O29*$M$37/100</f>
         <v>870.4</v>
       </c>
-      <c r="N29" s="23" t="n">
+      <c r="N29" s="24" t="n">
         <f aca="false">M29/$P29/10</f>
         <v>0.410808259587021</v>
       </c>
-      <c r="O29" s="22" t="n">
+      <c r="O29" s="23" t="n">
         <v>6400</v>
       </c>
-      <c r="P29" s="25" t="n">
+      <c r="P29" s="26" t="n">
         <v>211.875</v>
       </c>
-      <c r="Q29" s="25" t="n">
+      <c r="Q29" s="26" t="n">
         <f aca="false">100*P29/$P$36</f>
         <v>1.45522601797825</v>
       </c>
-      <c r="R29" s="22" t="n">
+      <c r="R29" s="23" t="n">
         <f aca="false">H29+F29+B29+D29+J29+M29</f>
         <v>1777.8</v>
       </c>
-      <c r="S29" s="25" t="n">
+      <c r="S29" s="26" t="n">
         <f aca="false">R29/P29</f>
         <v>8.39079646017699</v>
       </c>
-      <c r="U29" s="25" t="n">
-        <f aca="false">-T29+($Q$45 + $Q$46)*1000*Q29/100</f>
-        <v>646.500165973035</v>
-      </c>
-      <c r="V29" s="25" t="n">
-        <f aca="false">U29/P29/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W29" s="25" t="n">
-        <f aca="false">ROUND(U29/P29 *100/1000, 2)</f>
+      <c r="T29" s="26"/>
+      <c r="U29" s="26"/>
+      <c r="V29" s="0" t="n">
+        <f aca="false">T29+U29</f>
+        <v>0</v>
+      </c>
+      <c r="W29" s="27" t="n">
+        <f aca="false">3/5*H29+M29/3</f>
+        <v>488.133333333333</v>
+      </c>
+      <c r="X29" s="27" t="n">
+        <f aca="false">R29-V29</f>
+        <v>1777.8</v>
+      </c>
+      <c r="Y29" s="27" t="n">
+        <f aca="false">1000/100*Q29*($Q$41+$Q$47-$Q$49)-V29</f>
+        <v>801.953230117544</v>
+      </c>
+      <c r="Z29" s="27" t="n">
+        <f aca="false">Y29-V29+Q29/100*1000 *($Q$46+$Q$43)</f>
+        <v>1432.32221568129</v>
+      </c>
+      <c r="AA29" s="26" t="n">
+        <f aca="false">-V29+($Q$45 + $Q$46)*1000*Q29/100</f>
+        <v>656.430628319719</v>
+      </c>
+      <c r="AB29" s="26" t="n">
+        <f aca="false">AA29/P29/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC29" s="26" t="n">
+        <f aca="false">ROUND(AA29/P29 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y29" s="25" t="n">
+      <c r="AE29" s="26" t="n">
         <f aca="false">-Q29*($Q$47)*10</f>
         <v>-349.25424431478</v>
       </c>
-      <c r="Z29" s="25" t="n">
-        <f aca="false">Y29/P29/10</f>
+      <c r="AF29" s="26" t="n">
+        <f aca="false">AE29/P29/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC29" s="22" t="n">
+      <c r="AI29" s="23" t="n">
         <v>306.8</v>
       </c>
-      <c r="AH29" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI29" s="22" t="n">
+      <c r="AN29" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO29" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ29" s="22" t="n">
+      <c r="AP29" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="AK29" s="22" t="n">
-        <f aca="false">AI29+AJ29/100</f>
+      <c r="AQ29" s="23" t="n">
+        <f aca="false">AO29+AP29/100</f>
         <v>1.95</v>
       </c>
-      <c r="AL29" s="22" t="n">
-        <f aca="false">AK29*1000</f>
+      <c r="AR29" s="23" t="n">
+        <f aca="false">AQ29*1000</f>
         <v>1950</v>
       </c>
-      <c r="AO29" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="AP29" s="22" t="n">
+      <c r="AU29" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="AV29" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AQ29" s="22" t="n">
+      <c r="AW29" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="AR29" s="26" t="n">
-        <f aca="false">AP29+AQ29/10</f>
+      <c r="AX29" s="28" t="n">
+        <f aca="false">AV29+AW29/10</f>
         <v>6.4</v>
       </c>
-      <c r="AS29" s="26" t="n">
-        <f aca="false">1000*AR29</f>
+      <c r="AY29" s="28" t="n">
+        <f aca="false">1000*AX29</f>
         <v>6400</v>
       </c>
-      <c r="AU29" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="AV29" s="22" t="n">
+      <c r="BA29" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="BB29" s="23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AW29" s="22" t="n">
+      <c r="BC29" s="23" t="n">
         <v>4.33</v>
       </c>
-      <c r="AX29" s="22" t="n">
+      <c r="BD29" s="23" t="n">
         <v>1.55</v>
       </c>
-      <c r="AY29" s="22" t="n">
+      <c r="BE29" s="23" t="n">
         <v>2.8</v>
       </c>
-      <c r="AZ29" s="22" t="n">
+      <c r="BF29" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="BA29" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="BC29" s="26" t="n">
-        <f aca="false">AV29*1000</f>
+      <c r="BG29" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="BI29" s="28" t="n">
+        <f aca="false">BB29*1000</f>
         <v>1950</v>
       </c>
-      <c r="BE29" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="BF29" s="22" t="n">
+      <c r="BK29" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="BL29" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="BG29" s="22" t="n">
+      <c r="BM29" s="23" t="n">
         <v>101</v>
       </c>
-      <c r="BH29" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI29" s="22" t="n">
+      <c r="BN29" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO29" s="23" t="n">
         <v>137</v>
       </c>
-      <c r="BK29" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="BL29" s="22" t="n">
+      <c r="BQ29" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="BR29" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="BM29" s="22" t="s">
-        <v>61</v>
+      <c r="BS29" s="23" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="30" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="B30" s="22" t="n">
+    <row r="30" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" s="23" t="n">
         <v>135</v>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C30" s="24" t="n">
         <f aca="false">B30/$P30/10</f>
         <v>0.0626997101880062</v>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="24" t="n">
         <f aca="false">D30/$P30/10</f>
         <v>0.0139332689306681</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="25" t="n">
         <v>1.9</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G30" s="24" t="n">
         <f aca="false">F30/$P30/10</f>
         <v>0.000882440365608977</v>
       </c>
-      <c r="H30" s="24" t="n">
+      <c r="H30" s="25" t="n">
         <v>121</v>
       </c>
-      <c r="I30" s="23" t="n">
+      <c r="I30" s="24" t="n">
         <f aca="false">H30/$P30/10</f>
         <v>0.0561975180203611</v>
       </c>
-      <c r="J30" s="22" t="n">
+      <c r="J30" s="23" t="n">
         <f aca="false">L30*$J$37/100</f>
         <v>105.4</v>
       </c>
-      <c r="K30" s="23" t="n">
+      <c r="K30" s="24" t="n">
         <f aca="false">J30/$P30/10</f>
         <v>0.0489522181764138</v>
       </c>
-      <c r="L30" s="22" t="n">
+      <c r="L30" s="23" t="n">
         <v>620</v>
       </c>
-      <c r="M30" s="22" t="n">
+      <c r="M30" s="23" t="n">
         <f aca="false">O30*$M$37/100</f>
         <v>435.2</v>
       </c>
-      <c r="N30" s="23" t="n">
+      <c r="N30" s="24" t="n">
         <f aca="false">M30/$P30/10</f>
         <v>0.202125287954225</v>
       </c>
-      <c r="O30" s="22" t="n">
+      <c r="O30" s="23" t="n">
         <v>3200</v>
       </c>
-      <c r="P30" s="25" t="n">
+      <c r="P30" s="26" t="n">
         <v>215.312</v>
       </c>
-      <c r="Q30" s="25" t="n">
+      <c r="Q30" s="26" t="n">
         <f aca="false">100*P30/$P$36</f>
         <v>1.47883244546517</v>
       </c>
-      <c r="R30" s="22" t="n">
+      <c r="R30" s="23" t="n">
         <f aca="false">H30+F30+B30+D30+J30+M30</f>
         <v>828.5</v>
       </c>
-      <c r="S30" s="25" t="n">
+      <c r="S30" s="26" t="n">
         <f aca="false">R30/P30</f>
         <v>3.84790443635283</v>
       </c>
-      <c r="U30" s="25" t="n">
-        <f aca="false">-T30+($Q$45 + $Q$46)*1000*Q30/100</f>
-        <v>656.987581054801</v>
-      </c>
-      <c r="V30" s="25" t="n">
-        <f aca="false">U30/P30/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W30" s="25" t="n">
-        <f aca="false">ROUND(U30/P30 *100/1000, 2)</f>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="0" t="n">
+        <f aca="false">T30+U30</f>
+        <v>0</v>
+      </c>
+      <c r="W30" s="27" t="n">
+        <f aca="false">3/5*H30+M30/3</f>
+        <v>217.666666666667</v>
+      </c>
+      <c r="X30" s="27" t="n">
+        <f aca="false">R30-V30</f>
+        <v>828.5</v>
+      </c>
+      <c r="Y30" s="27" t="n">
+        <f aca="false">1000/100*Q30*($Q$41+$Q$47-$Q$49)-V30</f>
+        <v>814.962378209173</v>
+      </c>
+      <c r="Z30" s="27" t="n">
+        <f aca="false">Y30-V30+Q30/100*1000 *($Q$46+$Q$43)</f>
+        <v>1455.55710160599</v>
+      </c>
+      <c r="AA30" s="26" t="n">
+        <f aca="false">-V30+($Q$45 + $Q$46)*1000*Q30/100</f>
+        <v>667.079133662656</v>
+      </c>
+      <c r="AB30" s="26" t="n">
+        <f aca="false">AA30/P30/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC30" s="26" t="n">
+        <f aca="false">ROUND(AA30/P30 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y30" s="25" t="n">
+      <c r="AE30" s="26" t="n">
         <f aca="false">-Q30*($Q$47)*10</f>
         <v>-354.919786911641</v>
       </c>
-      <c r="Z30" s="25" t="n">
-        <f aca="false">Y30/P30/10</f>
+      <c r="AF30" s="26" t="n">
+        <f aca="false">AE30/P30/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC30" s="22" t="n">
+      <c r="AI30" s="23" t="n">
         <v>380.1</v>
       </c>
-      <c r="AH30" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="AI30" s="22" t="n">
+      <c r="AN30" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" s="22" t="n">
+      <c r="AP30" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="AK30" s="22" t="n">
-        <f aca="false">AI30+AJ30/100</f>
+      <c r="AQ30" s="23" t="n">
+        <f aca="false">AO30+AP30/100</f>
         <v>0.62</v>
       </c>
-      <c r="AL30" s="22" t="n">
-        <f aca="false">AK30*1000</f>
+      <c r="AR30" s="23" t="n">
+        <f aca="false">AQ30*1000</f>
         <v>620</v>
       </c>
-      <c r="AO30" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="AP30" s="22" t="n">
+      <c r="AU30" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="AV30" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AQ30" s="22" t="n">
+      <c r="AW30" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AR30" s="26" t="n">
-        <f aca="false">AP30+AQ30/10</f>
+      <c r="AX30" s="28" t="n">
+        <f aca="false">AV30+AW30/10</f>
         <v>3.2</v>
       </c>
-      <c r="AS30" s="26" t="n">
-        <f aca="false">1000*AR30</f>
+      <c r="AY30" s="28" t="n">
+        <f aca="false">1000*AX30</f>
         <v>3200</v>
       </c>
-      <c r="AU30" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="AV30" s="22" t="n">
+      <c r="BA30" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="BB30" s="23" t="n">
         <v>0.62</v>
       </c>
-      <c r="AW30" s="22" t="n">
+      <c r="BC30" s="23" t="n">
         <v>1.37</v>
       </c>
-      <c r="AX30" s="22" t="n">
+      <c r="BD30" s="23" t="n">
         <v>2.03</v>
       </c>
-      <c r="AY30" s="22" t="n">
+      <c r="BE30" s="23" t="n">
         <v>0.68</v>
       </c>
-      <c r="AZ30" s="22" t="n">
+      <c r="BF30" s="23" t="n">
         <v>0.92</v>
       </c>
-      <c r="BA30" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="BC30" s="26" t="n">
-        <f aca="false">AV30*1000</f>
+      <c r="BG30" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="BI30" s="28" t="n">
+        <f aca="false">BB30*1000</f>
         <v>620</v>
       </c>
-      <c r="BE30" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="BF30" s="22" t="n">
+      <c r="BK30" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="BL30" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="BG30" s="22" t="n">
+      <c r="BM30" s="23" t="n">
         <v>99</v>
       </c>
-      <c r="BH30" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI30" s="22" t="n">
+      <c r="BN30" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO30" s="23" t="n">
         <v>135</v>
       </c>
-      <c r="BK30" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="BL30" s="22" t="n">
+      <c r="BQ30" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="BR30" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="BM30" s="22" t="s">
-        <v>172</v>
+      <c r="BS30" s="23" t="s">
+        <v>180</v>
       </c>
     </row>
-    <row r="31" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="B31" s="22" t="n">
+    <row r="31" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C31" s="24" t="n">
         <f aca="false">B31/$P31/10</f>
         <v>0.0781105469793829</v>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E31" s="24" t="n">
         <f aca="false">D31/$P31/10</f>
         <v>0.0380275031346996</v>
       </c>
-      <c r="F31" s="28" t="n">
+      <c r="F31" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G31" s="24" t="n">
         <f aca="false">F31/$P31/10</f>
         <v>0</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="I31" s="23" t="n">
+      <c r="I31" s="24" t="n">
         <f aca="false">H31/$P31/10</f>
         <v>0.0195276367448457</v>
       </c>
-      <c r="J31" s="22" t="n">
+      <c r="J31" s="23" t="n">
         <f aca="false">L31*$J$37/100</f>
         <v>8.5</v>
       </c>
-      <c r="K31" s="23" t="n">
+      <c r="K31" s="24" t="n">
         <f aca="false">J31/$P31/10</f>
         <v>0.00873604801743099</v>
       </c>
-      <c r="L31" s="22" t="n">
+      <c r="L31" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="M31" s="22" t="n">
+      <c r="M31" s="23" t="n">
         <f aca="false">O31*$M$37/100</f>
         <v>176.8</v>
       </c>
-      <c r="N31" s="23" t="n">
+      <c r="N31" s="24" t="n">
         <f aca="false">M31/$P31/10</f>
         <v>0.181709798762565</v>
       </c>
-      <c r="O31" s="22" t="n">
+      <c r="O31" s="23" t="n">
         <v>1300</v>
       </c>
-      <c r="P31" s="25" t="n">
+      <c r="P31" s="26" t="n">
         <v>97.298</v>
       </c>
-      <c r="Q31" s="25" t="n">
+      <c r="Q31" s="26" t="n">
         <f aca="false">100*P31/$P$36</f>
         <v>0.668274129072555</v>
       </c>
-      <c r="R31" s="22" t="n">
+      <c r="R31" s="23" t="n">
         <f aca="false">H31+F31+B31+D31+J31+M31</f>
         <v>317.3</v>
       </c>
-      <c r="S31" s="25" t="n">
+      <c r="S31" s="26" t="n">
         <f aca="false">R31/P31</f>
         <v>3.26111533638924</v>
       </c>
-      <c r="U31" s="25" t="n">
-        <f aca="false">-T31+($Q$45 + $Q$46)*1000*Q31/100</f>
-        <v>296.888132855902</v>
-      </c>
-      <c r="V31" s="25" t="n">
-        <f aca="false">U31/P31/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W31" s="25" t="n">
-        <f aca="false">ROUND(U31/P31 *100/1000, 2)</f>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="0" t="n">
+        <f aca="false">T31+U31</f>
+        <v>0</v>
+      </c>
+      <c r="W31" s="27" t="n">
+        <f aca="false">3/5*H31+M31/3</f>
+        <v>70.3333333333333</v>
+      </c>
+      <c r="X31" s="27" t="n">
+        <f aca="false">R31-V31</f>
+        <v>317.3</v>
+      </c>
+      <c r="Y31" s="27" t="n">
+        <f aca="false">1000/100*Q31*($Q$41+$Q$47-$Q$49)-V31</f>
+        <v>368.275848419949</v>
+      </c>
+      <c r="Z31" s="27" t="n">
+        <f aca="false">Y31-V31+Q31/100*1000 *($Q$46+$Q$43)</f>
+        <v>657.756162555082</v>
+      </c>
+      <c r="AA31" s="26" t="n">
+        <f aca="false">-V31+($Q$45 + $Q$46)*1000*Q31/100</f>
+        <v>301.448435512694</v>
+      </c>
+      <c r="AB31" s="26" t="n">
+        <f aca="false">AA31/P31/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC31" s="26" t="n">
+        <f aca="false">ROUND(AA31/P31 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y31" s="25" t="n">
+      <c r="AE31" s="26" t="n">
         <f aca="false">-Q31*($Q$47)*10</f>
         <v>-160.385790977413</v>
       </c>
-      <c r="Z31" s="25" t="n">
-        <f aca="false">Y31/P31/10</f>
+      <c r="AF31" s="26" t="n">
+        <f aca="false">AE31/P31/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AA31" s="30"/>
-      <c r="AC31" s="22" t="n">
+      <c r="AG31" s="32"/>
+      <c r="AI31" s="23" t="n">
         <v>136.8</v>
       </c>
-      <c r="AH31" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="AI31" s="22" t="n">
+      <c r="AN31" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="AO31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" s="22" t="n">
+      <c r="AP31" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="AK31" s="22" t="n">
-        <f aca="false">AI31+AJ31/100</f>
+      <c r="AQ31" s="23" t="n">
+        <f aca="false">AO31+AP31/100</f>
         <v>0.4</v>
       </c>
-      <c r="AL31" s="22" t="n">
-        <f aca="false">AK31*1000</f>
+      <c r="AR31" s="23" t="n">
+        <f aca="false">AQ31*1000</f>
         <v>400</v>
       </c>
-      <c r="AO31" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="AP31" s="22" t="n">
+      <c r="AU31" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV31" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AQ31" s="22" t="n">
+      <c r="AW31" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AR31" s="26" t="n">
-        <f aca="false">AP31+AQ31/10</f>
+      <c r="AX31" s="28" t="n">
+        <f aca="false">AV31+AW31/10</f>
         <v>1.3</v>
       </c>
-      <c r="AS31" s="26" t="n">
-        <f aca="false">1000*AR31</f>
+      <c r="AY31" s="28" t="n">
+        <f aca="false">1000*AX31</f>
         <v>1300</v>
       </c>
-      <c r="AU31" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="AV31" s="22" t="n">
+      <c r="BA31" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="BB31" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="AW31" s="22" t="n">
+      <c r="BC31" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="AX31" s="22" t="n">
+      <c r="BD31" s="23" t="n">
         <v>0.73</v>
       </c>
-      <c r="AY31" s="22" t="n">
+      <c r="BE31" s="23" t="n">
         <v>0.14</v>
       </c>
-      <c r="AZ31" s="22" t="n">
+      <c r="BF31" s="23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BA31" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="BC31" s="26" t="n">
-        <f aca="false">AV31*1000</f>
+      <c r="BG31" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI31" s="28" t="n">
+        <f aca="false">BB31*1000</f>
         <v>50</v>
       </c>
-      <c r="BE31" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="BF31" s="22" t="n">
+      <c r="BK31" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="BL31" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="BG31" s="22" t="n">
+      <c r="BM31" s="23" t="n">
         <v>56</v>
       </c>
-      <c r="BH31" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI31" s="22" t="n">
+      <c r="BN31" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO31" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="BK31" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="BL31" s="22" t="n">
+      <c r="BQ31" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="BR31" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="BM31" s="22" t="s">
-        <v>139</v>
+      <c r="BS31" s="23" t="s">
+        <v>147</v>
       </c>
     </row>
-    <row r="32" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="B32" s="22" t="n">
+    <row r="32" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="C32" s="23" t="n">
+      <c r="C32" s="24" t="n">
         <f aca="false">B32/$P32/10</f>
         <v>0.0641137728041033</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="23" t="n">
+      <c r="E32" s="24" t="n">
         <f aca="false">D32/$P32/10</f>
         <v>0.0271997824017408</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="G32" s="23" t="n">
+      <c r="G32" s="24" t="n">
         <f aca="false">F32/$P32/10</f>
         <v>0.000777136640049737</v>
       </c>
-      <c r="H32" s="24" t="n">
+      <c r="H32" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="I32" s="23" t="n">
+      <c r="I32" s="24" t="n">
         <f aca="false">H32/$P32/10</f>
         <v>0.145713120009326</v>
       </c>
-      <c r="J32" s="22" t="n">
+      <c r="J32" s="23" t="n">
         <f aca="false">L32*$J$37/100</f>
         <v>5.1</v>
       </c>
-      <c r="K32" s="23" t="n">
+      <c r="K32" s="24" t="n">
         <f aca="false">J32/$P32/10</f>
         <v>0.00990849216063414</v>
       </c>
-      <c r="L32" s="22" t="n">
+      <c r="L32" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="M32" s="22" t="n">
+      <c r="M32" s="23" t="n">
         <f aca="false">O32*$M$37/100</f>
         <v>149.6</v>
       </c>
-      <c r="N32" s="23" t="n">
+      <c r="N32" s="24" t="n">
         <f aca="false">M32/$P32/10</f>
         <v>0.290649103378602</v>
       </c>
-      <c r="O32" s="22" t="n">
+      <c r="O32" s="23" t="n">
         <v>1100</v>
       </c>
-      <c r="P32" s="25" t="n">
+      <c r="P32" s="26" t="n">
         <v>51.471</v>
       </c>
-      <c r="Q32" s="25" t="n">
+      <c r="Q32" s="26" t="n">
         <f aca="false">100*P32/$P$36</f>
         <v>0.353519473139155</v>
       </c>
-      <c r="R32" s="22" t="n">
+      <c r="R32" s="23" t="n">
         <f aca="false">H32+F32+B32+D32+J32+M32</f>
         <v>277.1</v>
       </c>
-      <c r="S32" s="25" t="n">
+      <c r="S32" s="26" t="n">
         <f aca="false">R32/P32</f>
         <v>5.38361407394455</v>
       </c>
-      <c r="U32" s="25" t="n">
-        <f aca="false">-T32+($Q$45 + $Q$46)*1000*Q32/100</f>
-        <v>157.054914656274</v>
-      </c>
-      <c r="V32" s="25" t="n">
-        <f aca="false">U32/P32/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W32" s="25" t="n">
-        <f aca="false">ROUND(U32/P32 *100/1000, 2)</f>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="0" t="n">
+        <f aca="false">T32+U32</f>
+        <v>0</v>
+      </c>
+      <c r="W32" s="27" t="n">
+        <f aca="false">3/5*H32+M32/3</f>
+        <v>94.8666666666667</v>
+      </c>
+      <c r="X32" s="27" t="n">
+        <f aca="false">R32-V32</f>
+        <v>277.1</v>
+      </c>
+      <c r="Y32" s="27" t="n">
+        <f aca="false">1000/100*Q32*($Q$41+$Q$47-$Q$49)-V32</f>
+        <v>194.819278854891</v>
+      </c>
+      <c r="Z32" s="27" t="n">
+        <f aca="false">Y32-V32+Q32/100*1000 *($Q$46+$Q$43)</f>
+        <v>347.955430151418</v>
+      </c>
+      <c r="AA32" s="26" t="n">
+        <f aca="false">-V32+($Q$45 + $Q$46)*1000*Q32/100</f>
+        <v>159.467331540976</v>
+      </c>
+      <c r="AB32" s="26" t="n">
+        <f aca="false">AA32/P32/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC32" s="26" t="n">
+        <f aca="false">ROUND(AA32/P32 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y32" s="25" t="n">
+      <c r="AE32" s="26" t="n">
         <f aca="false">-Q32*($Q$47)*10</f>
         <v>-84.8446735533971</v>
       </c>
-      <c r="Z32" s="25" t="n">
-        <f aca="false">Y32/P32/10</f>
+      <c r="AF32" s="26" t="n">
+        <f aca="false">AE32/P32/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC32" s="22" t="n">
+      <c r="AI32" s="23" t="n">
         <v>70.5</v>
       </c>
-      <c r="AH32" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="AI32" s="22" t="n">
+      <c r="AN32" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ32" s="22" t="n">
+      <c r="AP32" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="AK32" s="22" t="n">
-        <f aca="false">AI32+AJ32/100</f>
+      <c r="AQ32" s="23" t="n">
+        <f aca="false">AO32+AP32/100</f>
         <v>0.3</v>
       </c>
-      <c r="AL32" s="22" t="n">
-        <f aca="false">AK32*1000</f>
+      <c r="AR32" s="23" t="n">
+        <f aca="false">AQ32*1000</f>
         <v>300</v>
       </c>
-      <c r="AO32" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="AP32" s="22" t="n">
+      <c r="AU32" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="AV32" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AQ32" s="22" t="n">
+      <c r="AW32" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AR32" s="26" t="n">
-        <f aca="false">AP32+AQ32/10</f>
+      <c r="AX32" s="28" t="n">
+        <f aca="false">AV32+AW32/10</f>
         <v>1.1</v>
       </c>
-      <c r="AS32" s="26" t="n">
-        <f aca="false">1000*AR32</f>
+      <c r="AY32" s="28" t="n">
+        <f aca="false">1000*AX32</f>
         <v>1100</v>
       </c>
-      <c r="AU32" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="AV32" s="22" t="n">
+      <c r="BA32" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="BB32" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="AW32" s="22" t="n">
+      <c r="BC32" s="23" t="n">
         <v>0.06</v>
       </c>
-      <c r="AX32" s="22" t="n">
+      <c r="BD32" s="23" t="n">
         <v>0.38</v>
       </c>
-      <c r="AY32" s="22" t="n">
+      <c r="BE32" s="23" t="n">
         <v>0.16</v>
       </c>
-      <c r="AZ32" s="22" t="n">
+      <c r="BF32" s="23" t="n">
         <v>0.22</v>
       </c>
-      <c r="BA32" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="BC32" s="26" t="n">
-        <f aca="false">AV32*1000</f>
+      <c r="BG32" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="BI32" s="28" t="n">
+        <f aca="false">BB32*1000</f>
         <v>30</v>
       </c>
-      <c r="BE32" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="BF32" s="22" t="n">
+      <c r="BK32" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="BL32" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="BG32" s="22" t="n">
+      <c r="BM32" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="BH32" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI32" s="22" t="n">
+      <c r="BN32" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO32" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="BK32" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="BL32" s="22" t="n">
+      <c r="BQ32" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="BR32" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="BM32" s="22" t="s">
-        <v>181</v>
+      <c r="BS32" s="23" t="s">
+        <v>189</v>
       </c>
     </row>
-    <row r="33" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="B33" s="22" t="n">
+    <row r="33" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" s="23" t="n">
         <v>687</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="24" t="n">
         <f aca="false">B33/$P33/10</f>
         <v>0.056628268798813</v>
       </c>
-      <c r="D33" s="22" t="n">
+      <c r="D33" s="23" t="n">
         <v>830</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="24" t="n">
         <f aca="false">D33/$P33/10</f>
         <v>0.0684155212562079</v>
       </c>
-      <c r="F33" s="28" t="n">
+      <c r="F33" s="30" t="n">
         <v>240.6</v>
       </c>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="24" t="n">
         <f aca="false">F33/$P33/10</f>
         <v>0.019832258330414</v>
       </c>
-      <c r="H33" s="28" t="n">
+      <c r="H33" s="30" t="n">
         <v>2151</v>
       </c>
-      <c r="I33" s="23" t="n">
+      <c r="I33" s="24" t="n">
         <f aca="false">H33/$P33/10</f>
         <v>0.1773033568941</v>
       </c>
-      <c r="J33" s="22" t="n">
+      <c r="J33" s="23" t="n">
         <f aca="false">L33*$J$37/100</f>
         <v>1586.1</v>
       </c>
-      <c r="K33" s="23" t="n">
+      <c r="K33" s="24" t="n">
         <f aca="false">J33/$P33/10</f>
         <v>0.130739588270447</v>
       </c>
-      <c r="L33" s="22" t="n">
+      <c r="L33" s="23" t="n">
         <v>9330</v>
       </c>
-      <c r="M33" s="22" t="n">
+      <c r="M33" s="23" t="n">
         <f aca="false">O33*$M$37/100</f>
         <v>4202.4</v>
       </c>
-      <c r="N33" s="23" t="n">
+      <c r="N33" s="24" t="n">
         <f aca="false">M33/$P33/10</f>
         <v>0.346396851237455</v>
       </c>
-      <c r="O33" s="22" t="n">
+      <c r="O33" s="23" t="n">
         <v>30900</v>
       </c>
-      <c r="P33" s="25" t="n">
+      <c r="P33" s="26" t="n">
         <v>1213.175</v>
       </c>
-      <c r="Q33" s="25" t="n">
+      <c r="Q33" s="26" t="n">
         <f aca="false">100*P33/$P$36</f>
         <v>8.33247822707144</v>
       </c>
-      <c r="R33" s="22" t="n">
+      <c r="R33" s="23" t="n">
         <f aca="false">H33+F33+B33+D33+J33+M33</f>
         <v>9697.1</v>
       </c>
-      <c r="S33" s="25" t="n">
+      <c r="S33" s="26" t="n">
         <f aca="false">R33/P33</f>
         <v>7.99315844787438</v>
       </c>
-      <c r="T33" s="22" t="n">
-        <f aca="false">B33+F33</f>
+      <c r="T33" s="26" t="n">
+        <f aca="false">B33</f>
+        <v>687</v>
+      </c>
+      <c r="U33" s="26" t="n">
+        <f aca="false">F33</f>
+        <v>240.6</v>
+      </c>
+      <c r="V33" s="0" t="n">
+        <f aca="false">T33+U33</f>
         <v>927.6</v>
       </c>
-      <c r="U33" s="25" t="n">
-        <f aca="false">-T33+($Q$45 + $Q$46)*1000*Q33/100</f>
-        <v>2774.19510963698</v>
-      </c>
-      <c r="V33" s="25" t="n">
-        <f aca="false">U33/P33/10</f>
-        <v>0.22867229456896</v>
-      </c>
-      <c r="W33" s="25" t="n">
-        <f aca="false">ROUND(U33/P33 *100/1000, 2)</f>
+      <c r="W33" s="27" t="n">
+        <f aca="false">3/5*H33+M33/3</f>
+        <v>2691.4</v>
+      </c>
+      <c r="X33" s="27" t="n">
+        <f aca="false">R33-V33</f>
+        <v>8769.5</v>
+      </c>
+      <c r="Y33" s="27" t="n">
+        <f aca="false">1000/100*Q33*($Q$41+$Q$47-$Q$49)-V33</f>
+        <v>3664.30376376567</v>
+      </c>
+      <c r="Z33" s="27" t="n">
+        <f aca="false">Y33-V33+Q33/100*1000 *($Q$46+$Q$43)</f>
+        <v>6346.13335225556</v>
+      </c>
+      <c r="AA33" s="26" t="n">
+        <f aca="false">-V33+($Q$45 + $Q$46)*1000*Q33/100</f>
+        <v>2831.05594105852</v>
+      </c>
+      <c r="AB33" s="26" t="n">
+        <f aca="false">AA33/P33/10</f>
+        <v>0.233359238449401</v>
+      </c>
+      <c r="AC33" s="26" t="n">
+        <f aca="false">ROUND(AA33/P33 *100/1000, 2)</f>
         <v>0.23</v>
       </c>
-      <c r="Y33" s="25" t="n">
+      <c r="AE33" s="26" t="n">
         <f aca="false">-Q33*($Q$47)*10</f>
         <v>-1999.79477449715</v>
       </c>
-      <c r="Z33" s="25" t="n">
-        <f aca="false">Y33/P33/10</f>
+      <c r="AF33" s="26" t="n">
+        <f aca="false">AE33/P33/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC33" s="22" t="n">
+      <c r="AI33" s="23" t="n">
         <v>1687.2</v>
       </c>
-      <c r="AH33" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI33" s="22" t="n">
+      <c r="AN33" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="AO33" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AJ33" s="22" t="n">
+      <c r="AP33" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="AK33" s="22" t="n">
-        <f aca="false">AI33+AJ33/100</f>
+      <c r="AQ33" s="23" t="n">
+        <f aca="false">AO33+AP33/100</f>
         <v>9.33</v>
       </c>
-      <c r="AL33" s="22" t="n">
-        <f aca="false">AK33*1000</f>
+      <c r="AR33" s="23" t="n">
+        <f aca="false">AQ33*1000</f>
         <v>9330</v>
       </c>
-      <c r="AO33" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="AP33" s="22" t="n">
+      <c r="AU33" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="AV33" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="AQ33" s="22" t="n">
+      <c r="AW33" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AR33" s="26" t="n">
-        <f aca="false">AP33+AQ33/10</f>
+      <c r="AX33" s="28" t="n">
+        <f aca="false">AV33+AW33/10</f>
         <v>30.9</v>
       </c>
-      <c r="AS33" s="26" t="n">
-        <f aca="false">1000*AR33</f>
+      <c r="AY33" s="28" t="n">
+        <f aca="false">1000*AX33</f>
         <v>30900</v>
       </c>
-      <c r="AU33" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="AV33" s="22" t="n">
+      <c r="BA33" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="BB33" s="23" t="n">
         <v>9.33</v>
       </c>
-      <c r="AW33" s="22" t="n">
+      <c r="BC33" s="23" t="n">
         <v>20.74</v>
       </c>
-      <c r="AX33" s="22" t="n">
+      <c r="BD33" s="23" t="n">
         <v>8.68</v>
       </c>
-      <c r="AY33" s="22" t="n">
+      <c r="BE33" s="23" t="n">
         <v>2.39</v>
       </c>
-      <c r="AZ33" s="22" t="n">
+      <c r="BF33" s="23" t="n">
         <v>3.24</v>
       </c>
-      <c r="BA33" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="BC33" s="26" t="n">
-        <f aca="false">AV33*1000</f>
+      <c r="BG33" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="BI33" s="28" t="n">
+        <f aca="false">BB33*1000</f>
         <v>9330</v>
       </c>
-      <c r="BE33" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="BF33" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="BG33" s="22" t="n">
+      <c r="BK33" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="BL33" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="BM33" s="23" t="n">
         <v>505</v>
       </c>
-      <c r="BH33" s="22" t="n">
+      <c r="BN33" s="23" t="n">
         <v>375</v>
       </c>
-      <c r="BI33" s="22" t="n">
+      <c r="BO33" s="23" t="n">
         <v>687</v>
       </c>
-      <c r="BK33" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL33" s="22" t="n">
+      <c r="BQ33" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="BR33" s="23" t="n">
         <v>830</v>
       </c>
-      <c r="BM33" s="22" t="s">
-        <v>98</v>
+      <c r="BS33" s="23" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="34" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B34" s="22" t="n">
+    <row r="34" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="B34" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="24" t="n">
         <f aca="false">B34/$P34/10</f>
         <v>0.0343768206145128</v>
       </c>
-      <c r="D34" s="22" t="n">
+      <c r="D34" s="23" t="n">
         <v>601</v>
       </c>
-      <c r="E34" s="23" t="n">
+      <c r="E34" s="24" t="n">
         <f aca="false">D34/$P34/10</f>
         <v>0.108739311522748</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="25" t="n">
         <v>245.1</v>
       </c>
-      <c r="G34" s="23" t="n">
+      <c r="G34" s="24" t="n">
         <f aca="false">F34/$P34/10</f>
         <v>0.0443460985927215</v>
       </c>
-      <c r="H34" s="24" t="n">
+      <c r="H34" s="25" t="n">
         <v>712</v>
       </c>
-      <c r="I34" s="23" t="n">
+      <c r="I34" s="24" t="n">
         <f aca="false">H34/$P34/10</f>
         <v>0.128822611987016</v>
       </c>
-      <c r="J34" s="22" t="n">
+      <c r="J34" s="23" t="n">
         <f aca="false">L34*$J$37/100</f>
         <v>197.2</v>
       </c>
-      <c r="K34" s="23" t="n">
+      <c r="K34" s="24" t="n">
         <f aca="false">J34/$P34/10</f>
         <v>0.035679521185168</v>
       </c>
-      <c r="L34" s="22" t="n">
+      <c r="L34" s="23" t="n">
         <v>1160</v>
       </c>
-      <c r="M34" s="22" t="n">
+      <c r="M34" s="23" t="n">
         <f aca="false">O34*$M$37/100</f>
         <v>965.6</v>
       </c>
-      <c r="N34" s="23" t="n">
+      <c r="N34" s="24" t="n">
         <f aca="false">M34/$P34/10</f>
         <v>0.17470662097565</v>
       </c>
-      <c r="O34" s="22" t="n">
+      <c r="O34" s="23" t="n">
         <v>7100</v>
       </c>
-      <c r="P34" s="25" t="n">
+      <c r="P34" s="26" t="n">
         <v>552.698</v>
       </c>
-      <c r="Q34" s="25" t="n">
+      <c r="Q34" s="26" t="n">
         <f aca="false">100*P34/$P$36</f>
         <v>3.79610860028102</v>
       </c>
-      <c r="R34" s="22" t="n">
+      <c r="R34" s="23" t="n">
         <f aca="false">H34+F34+B34+D34+J34+M34</f>
         <v>2910.9</v>
       </c>
-      <c r="S34" s="25" t="n">
+      <c r="S34" s="26" t="n">
         <f aca="false">R34/P34</f>
         <v>5.26670984877818</v>
       </c>
-      <c r="U34" s="25" t="n">
-        <f aca="false">-T34+($Q$45 + $Q$46)*1000*Q34/100</f>
-        <v>1686.46300286945</v>
-      </c>
-      <c r="V34" s="25" t="n">
-        <f aca="false">U34/P34/10</f>
-        <v>0.305132821698187</v>
-      </c>
-      <c r="W34" s="25" t="n">
-        <f aca="false">ROUND(U34/P34 *100/1000, 2)</f>
+      <c r="T34" s="26"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="0" t="n">
+        <f aca="false">T34+U34</f>
+        <v>0</v>
+      </c>
+      <c r="W34" s="27" t="n">
+        <f aca="false">3/5*H34+M34/3</f>
+        <v>749.066666666667</v>
+      </c>
+      <c r="X34" s="27" t="n">
+        <f aca="false">R34-V34</f>
+        <v>2910.9</v>
+      </c>
+      <c r="Y34" s="27" t="n">
+        <f aca="false">1000/100*Q34*($Q$41+$Q$47-$Q$49)-V34</f>
+        <v>2091.97850798587</v>
+      </c>
+      <c r="Z34" s="27" t="n">
+        <f aca="false">Y34-V34+Q34/100*1000 *($Q$46+$Q$43)</f>
+        <v>3736.3616470212</v>
+      </c>
+      <c r="AA34" s="26" t="n">
+        <f aca="false">-V34+($Q$45 + $Q$46)*1000*Q34/100</f>
+        <v>1712.36764795776</v>
+      </c>
+      <c r="AB34" s="26" t="n">
+        <f aca="false">AA34/P34/10</f>
+        <v>0.309819765578628</v>
+      </c>
+      <c r="AC34" s="26" t="n">
+        <f aca="false">ROUND(AA34/P34 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="Y34" s="25" t="n">
+      <c r="AE34" s="26" t="n">
         <f aca="false">-Q34*($Q$47)*10</f>
         <v>-911.066064067446</v>
       </c>
-      <c r="Z34" s="25" t="n">
-        <f aca="false">Y34/P34/10</f>
+      <c r="AF34" s="26" t="n">
+        <f aca="false">AE34/P34/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AC34" s="22" t="n">
+      <c r="AI34" s="23" t="n">
         <v>601.2</v>
       </c>
-      <c r="AH34" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="AI34" s="22" t="n">
+      <c r="AN34" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="AO34" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ34" s="22" t="n">
+      <c r="AP34" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="AK34" s="22" t="n">
-        <f aca="false">AI34+AJ34/100</f>
+      <c r="AQ34" s="23" t="n">
+        <f aca="false">AO34+AP34/100</f>
         <v>1.16</v>
       </c>
-      <c r="AL34" s="22" t="n">
-        <f aca="false">AK34*1000</f>
+      <c r="AR34" s="23" t="n">
+        <f aca="false">AQ34*1000</f>
         <v>1160</v>
       </c>
-      <c r="AO34" s="26" t="s">
+      <c r="AU34" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="AV34" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" s="28" t="n">
+        <f aca="false">AV34+AW34/10</f>
+        <v>7.1</v>
+      </c>
+      <c r="AY34" s="28" t="n">
+        <f aca="false">1000*AX34</f>
+        <v>7100</v>
+      </c>
+      <c r="BA34" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="BB34" s="23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC34" s="23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BD34" s="23" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BE34" s="23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BF34" s="23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BG34" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="BI34" s="28" t="n">
+        <f aca="false">BB34*1000</f>
+        <v>1160</v>
+      </c>
+      <c r="BK34" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="BL34" s="23" t="n">
+        <v>270</v>
+      </c>
+      <c r="BM34" s="23" t="n">
+        <v>140</v>
+      </c>
+      <c r="BN34" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BO34" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="AP34" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ34" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR34" s="26" t="n">
-        <f aca="false">AP34+AQ34/10</f>
-        <v>7.1</v>
-      </c>
-      <c r="AS34" s="26" t="n">
-        <f aca="false">1000*AR34</f>
-        <v>7100</v>
-      </c>
-      <c r="AU34" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="AV34" s="22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AW34" s="22" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX34" s="22" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AY34" s="22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AZ34" s="22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BA34" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="BC34" s="26" t="n">
-        <f aca="false">AV34*1000</f>
-        <v>1160</v>
-      </c>
-      <c r="BE34" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="BF34" s="22" t="n">
-        <v>270</v>
-      </c>
-      <c r="BG34" s="22" t="n">
-        <v>140</v>
-      </c>
-      <c r="BH34" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI34" s="22" t="n">
-        <v>190</v>
-      </c>
-      <c r="BK34" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="BL34" s="22" t="n">
+      <c r="BQ34" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="BR34" s="23" t="n">
         <v>601</v>
       </c>
-      <c r="BM34" s="22" t="s">
-        <v>193</v>
+      <c r="BS34" s="23" t="s">
+        <v>201</v>
       </c>
     </row>
-    <row r="35" s="36" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="B35" s="32" t="n">
+    <row r="35" s="38" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="B35" s="34" t="n">
         <v>5880</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="34" t="n">
+      <c r="C35" s="35"/>
+      <c r="D35" s="36" t="n">
         <v>9616</v>
       </c>
-      <c r="E35" s="33"/>
-      <c r="F35" s="32" t="n">
+      <c r="E35" s="35"/>
+      <c r="F35" s="34" t="n">
         <v>8334.6</v>
       </c>
-      <c r="G35" s="33"/>
-      <c r="H35" s="32" t="n">
+      <c r="G35" s="35"/>
+      <c r="H35" s="34" t="n">
         <v>26264</v>
       </c>
-      <c r="I35" s="33"/>
-      <c r="J35" s="22" t="n">
+      <c r="I35" s="35"/>
+      <c r="J35" s="23" t="n">
         <f aca="false">SUM(J8:J34)</f>
         <v>7650</v>
       </c>
-      <c r="K35" s="25"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22" t="n">
+      <c r="K35" s="26"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23" t="n">
         <f aca="false">SUM(M8:M34)</f>
         <v>40677.6</v>
       </c>
-      <c r="N35" s="25"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="35" t="n">
+      <c r="N35" s="26"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="37" t="n">
         <v>100</v>
       </c>
-      <c r="R35" s="22" t="n">
-        <f aca="false">H35+F35+B35+D35+L35+M35</f>
-        <v>90772.2</v>
-      </c>
-      <c r="S35" s="25"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="22" t="n">
+      <c r="R35" s="23" t="n">
+        <f aca="false">H35+F35+B35+D35+J35+M35</f>
+        <v>98422.2</v>
+      </c>
+      <c r="S35" s="26"/>
+      <c r="T35" s="23" t="n">
+        <f aca="false">SUM(T8:T34)</f>
+        <v>2339.220378624</v>
+      </c>
+      <c r="U35" s="23" t="n">
         <f aca="false">SUM(U8:U34)</f>
-        <v>37876.579621376</v>
-      </c>
-      <c r="V35" s="22"/>
-      <c r="W35" s="36" t="e">
-        <f aca="false">ROUND(U35/P35 *100/1000, 2)</f>
+        <v>4210.3</v>
+      </c>
+      <c r="V35" s="26" t="n">
+        <f aca="false">SUM(V8:V34)</f>
+        <v>6549.520378624</v>
+      </c>
+      <c r="W35" s="27" t="n">
+        <f aca="false">3/5*H35+M35/3</f>
+        <v>29317.6</v>
+      </c>
+      <c r="X35" s="27" t="n">
+        <f aca="false">R35-V35</f>
+        <v>91872.679621376</v>
+      </c>
+      <c r="Y35" s="27" t="n">
+        <f aca="false">1000/100*Q35*($Q$41+$Q$47-$Q$49)-V35</f>
+        <v>48558.979621376</v>
+      </c>
+      <c r="Z35" s="27" t="n">
+        <f aca="false">Y35-V35+Q35/100*1000 *($Q$46+$Q$43)</f>
+        <v>85327.059242752</v>
+      </c>
+      <c r="AA35" s="26" t="n">
+        <f aca="false">SUM(AA8:AA34)</f>
+        <v>38558.979621376</v>
+      </c>
+      <c r="AB35" s="23"/>
+      <c r="AC35" s="38" t="e">
+        <f aca="false">ROUND(AA35/P35 *100/1000, 2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y35" s="25" t="n">
+      <c r="AE35" s="26" t="n">
         <f aca="false">-Q35*($Q$47)*10</f>
         <v>-24000</v>
       </c>
-      <c r="Z35" s="25"/>
-      <c r="AC35" s="36" t="n">
+      <c r="AF35" s="26"/>
+      <c r="AI35" s="38" t="n">
         <v>18796</v>
       </c>
-      <c r="AL35" s="36" t="n">
-        <f aca="false">SUM(AL8:AL34)</f>
+      <c r="AR35" s="38" t="n">
+        <f aca="false">SUM(AR8:AR34)</f>
         <v>47600</v>
       </c>
-      <c r="AR35" s="36" t="n">
-        <f aca="false">SUM(AR8:AR34)</f>
+      <c r="AX35" s="38" t="n">
+        <f aca="false">SUM(AX8:AX34)</f>
         <v>299.1</v>
       </c>
-      <c r="XEX35" s="22"/>
-      <c r="XEY35" s="22"/>
-      <c r="XEZ35" s="22"/>
-      <c r="XFA35" s="22"/>
-      <c r="XFB35" s="22"/>
-      <c r="XFC35" s="22"/>
-      <c r="XFD35" s="22"/>
+      <c r="XFD35" s="23"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="n">
@@ -8282,234 +8906,303 @@
         <v>98426.1</v>
       </c>
       <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="37" t="n">
+      <c r="J37" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="K37" s="38"/>
-      <c r="M37" s="37" t="n">
+      <c r="K37" s="40"/>
+      <c r="M37" s="39" t="n">
         <v>13.6</v>
       </c>
-      <c r="N37" s="38"/>
+      <c r="N37" s="40"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="39" t="s">
-        <v>195</v>
-      </c>
-      <c r="C38" s="40" t="n">
+      <c r="B38" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="42" t="n">
         <f aca="false">SUM(B35:M35)</f>
         <v>98422.2</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
       <c r="J38" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="M38" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="N38" s="42"/>
-      <c r="T38" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
+      </c>
+      <c r="M38" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="N38" s="44"/>
+      <c r="V38" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="39"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="T39" s="1" t="s">
-        <v>199</v>
+      <c r="B39" s="41"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="V39" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="39"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="P40" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q40" s="44" t="n">
+      <c r="B40" s="41"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="P40" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q40" s="46" t="n">
         <v>192.8</v>
       </c>
-      <c r="R40" s="41"/>
-      <c r="S40" s="41"/>
-      <c r="T40" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="U40" s="41"/>
-      <c r="V40" s="41"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="W40" s="43"/>
+      <c r="X40" s="43"/>
+      <c r="Y40" s="43"/>
+      <c r="Z40" s="43"/>
+      <c r="AA40" s="43"/>
+      <c r="AB40" s="43"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P41" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q41" s="43" t="n">
+      <c r="P41" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q41" s="45" t="n">
         <f aca="false">Q40*0.7</f>
         <v>134.96</v>
       </c>
-      <c r="R41" s="41"/>
-      <c r="S41" s="41"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-      <c r="V41" s="41"/>
+      <c r="R41" s="43"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="43"/>
+      <c r="U41" s="43"/>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
+      <c r="X41" s="43"/>
+      <c r="Y41" s="43"/>
+      <c r="Z41" s="43"/>
+      <c r="AA41" s="43"/>
+      <c r="AB41" s="43"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P42" s="43"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="41"/>
-      <c r="S42" s="41"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="41"/>
+      <c r="P42" s="45"/>
+      <c r="Q42" s="45"/>
+      <c r="R42" s="43"/>
+      <c r="S42" s="43"/>
+      <c r="T42" s="43"/>
+      <c r="U42" s="43"/>
+      <c r="V42" s="43"/>
+      <c r="W42" s="43"/>
+      <c r="X42" s="43"/>
+      <c r="Y42" s="43"/>
+      <c r="Z42" s="43"/>
+      <c r="AA42" s="43"/>
+      <c r="AB42" s="43"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P43" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q43" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="R43" s="41"/>
-      <c r="S43" s="41"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="41"/>
+      <c r="P43" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q43" s="48" t="n">
+        <f aca="false">W35/1000</f>
+        <v>29.3176</v>
+      </c>
+      <c r="R43" s="43"/>
+      <c r="S43" s="43"/>
+      <c r="T43" s="43"/>
+      <c r="U43" s="43"/>
+      <c r="V43" s="43"/>
+      <c r="W43" s="43"/>
+      <c r="X43" s="43"/>
+      <c r="Y43" s="43"/>
+      <c r="Z43" s="43"/>
+      <c r="AA43" s="43"/>
+      <c r="AB43" s="43"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P44" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q44" s="45" t="n">
+      <c r="P44" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q44" s="47" t="n">
         <f aca="false">R36/1000 -Q43</f>
-        <v>68.4261</v>
-      </c>
-      <c r="R44" s="41"/>
-      <c r="S44" s="41"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="41"/>
+        <v>69.1085</v>
+      </c>
+      <c r="R44" s="43"/>
+      <c r="S44" s="43"/>
+      <c r="T44" s="43"/>
+      <c r="U44" s="43"/>
+      <c r="V44" s="43"/>
+      <c r="W44" s="43"/>
+      <c r="X44" s="43"/>
+      <c r="Y44" s="43"/>
+      <c r="Z44" s="43"/>
+      <c r="AA44" s="43"/>
+      <c r="AB44" s="43"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P45" s="45" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q45" s="45" t="n">
+      <c r="P45" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q45" s="47" t="n">
         <f aca="false">Q44-Q46-Q47</f>
-        <v>30.4261</v>
-      </c>
-      <c r="R45" s="41"/>
-      <c r="S45" s="41"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="41"/>
+        <v>31.1085</v>
+      </c>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="43"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
+      <c r="W45" s="43"/>
+      <c r="X45" s="43"/>
+      <c r="Y45" s="43"/>
+      <c r="Z45" s="43"/>
+      <c r="AA45" s="43"/>
+      <c r="AB45" s="43"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P46" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q46" s="46" t="n">
+      <c r="P46" s="47" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q46" s="48" t="n">
         <v>14</v>
       </c>
-      <c r="R46" s="41"/>
-      <c r="S46" s="41"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="41"/>
+      <c r="R46" s="43"/>
+      <c r="S46" s="43"/>
+      <c r="T46" s="43"/>
+      <c r="U46" s="43"/>
+      <c r="V46" s="43"/>
+      <c r="W46" s="43"/>
+      <c r="X46" s="43"/>
+      <c r="Y46" s="43"/>
+      <c r="Z46" s="43"/>
+      <c r="AA46" s="43"/>
+      <c r="AB46" s="43"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P47" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q47" s="46" t="n">
+      <c r="P47" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q47" s="48" t="n">
         <v>24</v>
       </c>
-      <c r="R47" s="41"/>
-      <c r="S47" s="41"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="41"/>
-      <c r="V47" s="41"/>
+      <c r="R47" s="43"/>
+      <c r="S47" s="43"/>
+      <c r="T47" s="43"/>
+      <c r="U47" s="43"/>
+      <c r="V47" s="43"/>
+      <c r="W47" s="43"/>
+      <c r="X47" s="43"/>
+      <c r="Y47" s="43"/>
+      <c r="Z47" s="43"/>
+      <c r="AA47" s="43"/>
+      <c r="AB47" s="43"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="41"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="P48" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q48" s="45" t="n">
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="P48" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q48" s="47" t="n">
         <f aca="false">Q40+Q46</f>
         <v>206.8</v>
       </c>
-      <c r="R48" s="41"/>
-      <c r="S48" s="41"/>
-      <c r="T48" s="41"/>
-      <c r="U48" s="41"/>
-      <c r="V48" s="41"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="43"/>
+      <c r="T48" s="43"/>
+      <c r="U48" s="43"/>
+      <c r="V48" s="43"/>
+      <c r="W48" s="43"/>
+      <c r="X48" s="43"/>
+      <c r="Y48" s="43"/>
+      <c r="Z48" s="43"/>
+      <c r="AA48" s="43"/>
+      <c r="AB48" s="43"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="P49" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q49" s="45" t="n">
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="P49" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q49" s="47" t="n">
         <f aca="false">Q41-Q45</f>
-        <v>104.5339</v>
-      </c>
-      <c r="R49" s="41"/>
-      <c r="S49" s="41"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
+        <v>103.8515</v>
+      </c>
+      <c r="R49" s="43"/>
+      <c r="S49" s="43"/>
+      <c r="T49" s="43"/>
+      <c r="U49" s="43"/>
+      <c r="V49" s="43"/>
+      <c r="W49" s="43"/>
+      <c r="X49" s="43"/>
+      <c r="Y49" s="43"/>
+      <c r="Z49" s="43"/>
+      <c r="AA49" s="43"/>
+      <c r="AB49" s="43"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="P50" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q50" s="47" t="n">
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="P50" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q50" s="49" t="n">
         <f aca="false">Q49/Q48</f>
-        <v>0.505483075435203</v>
-      </c>
-      <c r="R50" s="41"/>
-      <c r="S50" s="41"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="41"/>
-      <c r="V50" s="41"/>
+        <v>0.502183268858801</v>
+      </c>
+      <c r="R50" s="43"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="43"/>
+      <c r="U50" s="43"/>
+      <c r="V50" s="43"/>
+      <c r="W50" s="43"/>
+      <c r="X50" s="43"/>
+      <c r="Y50" s="43"/>
+      <c r="Z50" s="43"/>
+      <c r="AA50" s="43"/>
+      <c r="AB50" s="43"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="48"/>
-      <c r="U53" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y53" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z53" s="1"/>
+      <c r="A53" s="50"/>
+      <c r="AA53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE53" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AF53" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="48"/>
+      <c r="A55" s="50"/>
       <c r="J55" s="1" t="s">
         <v>5</v>
       </c>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="220">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">table_scenario</t>
   </si>
   <si>
-    <t xml:space="preserve">New revenue </t>
+    <t xml:space="preserve">New revenues </t>
   </si>
   <si>
     <t xml:space="preserve">Foregone revenues</t>
@@ -133,529 +133,532 @@
     <t xml:space="preserve">New Funds</t>
   </si>
   <si>
+    <t xml:space="preserve">Net new ressources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic budget gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relative gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_sscenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 NOR scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status-quo scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tax base </t>
+  </si>
+  <si>
+    <t xml:space="preserve">share of </t>
+  </si>
+  <si>
+    <t xml:space="preserve">passenger flow preserving reform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3,73 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 124$^{a}$       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.57 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3,08 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ---       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.25 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4,73 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.15 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  7,63 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.28 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyprus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyprus         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 16,92 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyprus               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ---$^{b}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyprus$^{a}$   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.45 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2,52 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech Republic       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech Republic </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.72 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4,77 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.53 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4,16 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.44 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4,34 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.40 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">France      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3,12 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 760$^{c}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.48 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2,34 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1{,}213   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.54 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 18,82 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.20 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3,04 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.50 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3,90 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.33 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5,68 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 637$^{d}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.36 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  7,24 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuania      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3,21 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuania            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.26 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxembourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxembourg     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  6,42 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxembourg           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxembourg$^{a}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.43 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 24,29 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta$^{a}$    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.46 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3,17 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2,43 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.49 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12,14 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romania        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2,95 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romania              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.08 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  0,61 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  0,69 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.17 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10,37 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 373$^{c}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3,47 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.83 \\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European Union</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux effectif (inclus elasticité)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux effectif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autriche </t>
+  </si>
+  <si>
+    <t xml:space="preserve">124 M en 2024 a 5 % pub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget 2026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 % de croissance du secteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share GNI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reward fund</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domestic budget gain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relative gain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">table_sscenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 NOR scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status-quo scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tax base </t>
-  </si>
-  <si>
-    <t xml:space="preserve">share of </t>
-  </si>
-  <si>
-    <t xml:space="preserve">passenger flow preserving reform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3,73 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 124$^{a}$       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.57 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belgium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belgium        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belgium     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3,08 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belgium              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ---       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.25 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4,73 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.15 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatia        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  7,63 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatia              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.28 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyprus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyprus         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 16,92 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyprus               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ---$^{b}$ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyprus$^{a}$   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.45 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2,52 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech Republic       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech Republic </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.72 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4,77 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.53 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4,16 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.44 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4,34 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.40 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">France      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3,12 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 760$^{c}$ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.48 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2,34 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1{,}213   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.54 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greece</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greece         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greece      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 18,82 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greece               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.20 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3,04 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.50 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland     </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3,90 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.33 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  5,68 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy                </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 637$^{d}$ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.36 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  7,24 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lithuania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lithuania      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3,21 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lithuania            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.26 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxembourg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxembourg     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  6,42 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxembourg           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luxembourg$^{a}$ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.43 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malta          </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 24,29 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malta                </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malta$^{a}$    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.46 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3,17 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2,43 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.49 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 12,14 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romania        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2,95 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romania              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.08 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovakia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovakia       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  0,61 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovakia             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  0,69 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.17 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 10,37 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain                </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 373$^{c}$ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3,47 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.83 \\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">European Union</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taux effectif (inclus elasticité)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taux effectif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autriche </t>
-  </si>
-  <si>
-    <t xml:space="preserve">124 M en 2024 a 5 % pub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget 2026 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 % de croissance du secteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">share GNI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reward fund</t>
   </si>
   <si>
     <t xml:space="preserve">GNI contrib reduction</t>
@@ -2595,11 +2598,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="51947549"/>
-        <c:axId val="798835"/>
+        <c:axId val="31036089"/>
+        <c:axId val="65090437"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="51947549"/>
+        <c:axId val="31036089"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2631,7 +2634,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="798835"/>
+        <c:crossAx val="65090437"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2639,7 +2642,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="798835"/>
+        <c:axId val="65090437"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2680,7 +2683,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51947549"/>
+        <c:crossAx val="31036089"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9031,7 +9034,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P44" s="47" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="Q44" s="47" t="n">
         <f aca="false">R36/1000 -Q43</f>
@@ -9051,7 +9054,7 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P45" s="47" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q45" s="47" t="n">
         <f aca="false">Q44-Q46-Q47</f>
@@ -9071,7 +9074,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P46" s="47" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q46" s="48" t="n">
         <v>14</v>
@@ -9090,7 +9093,7 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P47" s="47" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q47" s="48" t="n">
         <v>24</v>
@@ -9117,7 +9120,7 @@
       <c r="H48" s="43"/>
       <c r="I48" s="43"/>
       <c r="P48" s="47" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q48" s="47" t="n">
         <f aca="false">Q40+Q46</f>
@@ -9173,7 +9176,7 @@
       <c r="H50" s="43"/>
       <c r="I50" s="43"/>
       <c r="P50" s="47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q50" s="49" t="n">
         <f aca="false">Q49/Q48</f>
@@ -9194,10 +9197,10 @@
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="50"/>
       <c r="AA53" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AE53" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AF53" s="1"/>
     </row>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="215">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -88,12 +88,12 @@
     <t xml:space="preserve">NOR total</t>
   </si>
   <si>
+    <t xml:space="preserve">œ</t>
+  </si>
+  <si>
     <t xml:space="preserve">total</t>
   </si>
   <si>
-    <t xml:space="preserve">œ</t>
-  </si>
-  <si>
     <t xml:space="preserve">rapporté au PIB ( %)</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t xml:space="preserve">Wealth tax</t>
   </si>
   <si>
-    <t xml:space="preserve">table_s</t>
+    <t xml:space="preserve">table_gni</t>
   </si>
   <si>
     <t xml:space="preserve">table_scenario</t>
@@ -127,37 +127,22 @@
     <t xml:space="preserve">New revenues </t>
   </si>
   <si>
-    <t xml:space="preserve">Foregone revenues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Funds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net new ressources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domestic budget gain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relative gain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">table_sscenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 NOR scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status-quo scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tax base </t>
-  </si>
-  <si>
-    <t xml:space="preserve">share of </t>
-  </si>
-  <si>
-    <t xml:space="preserve">passenger flow preserving reform</t>
+    <t xml:space="preserve">New funds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EU budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foregone domestic revenues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State budget gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">table_scenario_gni</t>
   </si>
   <si>
     <t xml:space="preserve">Austria</t>
@@ -2598,11 +2583,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="31036089"/>
-        <c:axId val="65090437"/>
+        <c:axId val="9513269"/>
+        <c:axId val="92381258"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="31036089"/>
+        <c:axId val="9513269"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2634,7 +2619,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65090437"/>
+        <c:crossAx val="92381258"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2642,7 +2627,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65090437"/>
+        <c:axId val="92381258"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2683,7 +2668,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31036089"/>
+        <c:crossAx val="9513269"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2901,13 +2886,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="14.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="20" style="1" width="14.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="14.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="11.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="11.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="12.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16348" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="21" style="1" width="14.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="14.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="11.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="76" style="1" width="12.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16380" min="16354" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" s="11" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2955,13 +2941,22 @@
       <c r="X1" s="10"/>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AH1" s="11" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AN1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AO1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="XFD1" s="1"/>
+      <c r="XFA1" s="0"/>
+      <c r="XFB1" s="0"/>
+      <c r="XFC1" s="0"/>
+      <c r="XFD1" s="0"/>
     </row>
     <row r="2" s="13" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
@@ -3012,24 +3007,29 @@
       </c>
       <c r="R2" s="14"/>
       <c r="S2" s="14"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="16" t="s">
+      <c r="T2" s="14"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="V2" s="15"/>
-      <c r="AA2" s="13" t="s">
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AG2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="AE2" s="13" t="s">
+      <c r="AK2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AH2" s="13" t="s">
+      <c r="AN2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="AI2" s="13" t="s">
+      <c r="AO2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="XFD2" s="1"/>
+      <c r="XFA2" s="0"/>
+      <c r="XFB2" s="0"/>
+      <c r="XFC2" s="0"/>
+      <c r="XFD2" s="0"/>
     </row>
     <row r="3" s="13" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
@@ -3076,30 +3076,35 @@
         <v>21</v>
       </c>
       <c r="S3" s="14"/>
-      <c r="T3" s="15" t="s">
+      <c r="T3" s="14"/>
+      <c r="W3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="Z3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="V3" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="X3" s="13" t="s">
+      <c r="AA3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AA3" s="17"/>
-      <c r="AB3" s="17"/>
-      <c r="AC3" s="13" t="s">
+      <c r="AB3" s="15"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AK3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="AI3" s="13" t="s">
+      <c r="AO3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="XFD3" s="1"/>
+      <c r="XFA3" s="0"/>
+      <c r="XFB3" s="0"/>
+      <c r="XFC3" s="0"/>
+      <c r="XFD3" s="0"/>
     </row>
     <row r="4" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
@@ -3132,13 +3137,8 @@
       <c r="N4" s="20"/>
       <c r="O4" s="19"/>
       <c r="R4" s="19"/>
-      <c r="AI4" s="19"/>
-      <c r="XDT4" s="19"/>
-      <c r="XDU4" s="19"/>
-      <c r="XDV4" s="19"/>
-      <c r="XDW4" s="19"/>
-      <c r="XDX4" s="19"/>
-      <c r="XDY4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="AO4" s="19"/>
       <c r="XDZ4" s="19"/>
       <c r="XEA4" s="19"/>
       <c r="XEB4" s="19"/>
@@ -3166,10 +3166,10 @@
       <c r="XEX4" s="19"/>
       <c r="XEY4" s="19"/>
       <c r="XEZ4" s="19"/>
-      <c r="XFA4" s="19"/>
-      <c r="XFB4" s="19"/>
-      <c r="XFC4" s="19"/>
-      <c r="XFD4" s="1"/>
+      <c r="XFA4" s="0"/>
+      <c r="XFB4" s="0"/>
+      <c r="XFC4" s="0"/>
+      <c r="XFD4" s="0"/>
     </row>
     <row r="5" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
@@ -3202,13 +3202,8 @@
       </c>
       <c r="O5" s="19"/>
       <c r="R5" s="19"/>
-      <c r="AI5" s="19"/>
-      <c r="XDT5" s="19"/>
-      <c r="XDU5" s="19"/>
-      <c r="XDV5" s="19"/>
-      <c r="XDW5" s="19"/>
-      <c r="XDX5" s="19"/>
-      <c r="XDY5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="AO5" s="19"/>
       <c r="XDZ5" s="19"/>
       <c r="XEA5" s="19"/>
       <c r="XEB5" s="19"/>
@@ -3236,10 +3231,10 @@
       <c r="XEX5" s="19"/>
       <c r="XEY5" s="19"/>
       <c r="XEZ5" s="19"/>
-      <c r="XFA5" s="19"/>
-      <c r="XFB5" s="19"/>
-      <c r="XFC5" s="19"/>
-      <c r="XFD5" s="1"/>
+      <c r="XFA5" s="0"/>
+      <c r="XFB5" s="0"/>
+      <c r="XFC5" s="0"/>
+      <c r="XFD5" s="0"/>
     </row>
     <row r="6" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
@@ -3262,28 +3257,23 @@
       <c r="R6" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="V6" s="21" t="s">
+      <c r="S6" s="19"/>
+      <c r="U6" s="21" t="s">
         <v>35</v>
       </c>
       <c r="W6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="X6" s="21" t="s">
+      <c r="AA6" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="Y6" s="21" t="s">
+      <c r="AC6" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="Z6" s="21" t="s">
+      <c r="AE6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AI6" s="19"/>
-      <c r="XDT6" s="19"/>
-      <c r="XDU6" s="19"/>
-      <c r="XDV6" s="19"/>
-      <c r="XDW6" s="19"/>
-      <c r="XDX6" s="19"/>
-      <c r="XDY6" s="19"/>
+      <c r="AO6" s="19"/>
       <c r="XDZ6" s="19"/>
       <c r="XEA6" s="19"/>
       <c r="XEB6" s="19"/>
@@ -3311,10 +3301,10 @@
       <c r="XEX6" s="19"/>
       <c r="XEY6" s="19"/>
       <c r="XEZ6" s="19"/>
-      <c r="XFA6" s="19"/>
-      <c r="XFB6" s="19"/>
-      <c r="XFC6" s="19"/>
-      <c r="XFD6" s="1"/>
+      <c r="XFA6" s="0"/>
+      <c r="XFB6" s="0"/>
+      <c r="XFC6" s="0"/>
+      <c r="XFD6" s="0"/>
     </row>
     <row r="7" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
@@ -3335,28 +3325,25 @@
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
       <c r="R7" s="19"/>
+      <c r="S7" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="V7" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="AB7" s="21" t="s">
-        <v>41</v>
+        <v>37</v>
+      </c>
+      <c r="AD7" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="AF7" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI7" s="19"/>
-      <c r="BB7" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="BC7" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="BF7" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="XDT7" s="19"/>
-      <c r="XDU7" s="19"/>
-      <c r="XDV7" s="19"/>
-      <c r="XDW7" s="19"/>
-      <c r="XDX7" s="19"/>
-      <c r="XDY7" s="19"/>
+        <v>39</v>
+      </c>
+      <c r="AO7" s="19"/>
       <c r="XDZ7" s="19"/>
       <c r="XEA7" s="19"/>
       <c r="XEB7" s="19"/>
@@ -3384,14 +3371,14 @@
       <c r="XEX7" s="19"/>
       <c r="XEY7" s="19"/>
       <c r="XEZ7" s="19"/>
-      <c r="XFA7" s="19"/>
-      <c r="XFB7" s="19"/>
-      <c r="XFC7" s="19"/>
-      <c r="XFD7" s="1"/>
+      <c r="XFA7" s="0"/>
+      <c r="XFB7" s="0"/>
+      <c r="XFC7" s="0"/>
+      <c r="XFD7" s="0"/>
     </row>
     <row r="8" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>143</v>
@@ -3455,144 +3442,172 @@
         <v>2951.1</v>
       </c>
       <c r="S8" s="26" t="n">
+        <f aca="false">R8/$P8</f>
+        <v>7.23354919676254</v>
+      </c>
+      <c r="T8" s="26" t="n">
         <f aca="false">R8/P8</f>
         <v>7.23354919676254</v>
       </c>
-      <c r="T8" s="23" t="n">
+      <c r="U8" s="27" t="n">
+        <f aca="false">3/5*H8+M8/3</f>
+        <v>1000.8</v>
+      </c>
+      <c r="V8" s="26" t="n">
+        <f aca="false">U8/$P8</f>
+        <v>2.45309750131136</v>
+      </c>
+      <c r="W8" s="27" t="n">
+        <f aca="false">R8-U8</f>
+        <v>1950.3</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <f aca="false">W8/$P8</f>
+        <v>4.78045169545118</v>
+      </c>
+      <c r="Y8" s="23" t="n">
         <f aca="false">124*(1.08)^4*3/5</f>
         <v>101.220378624</v>
       </c>
-      <c r="U8" s="26"/>
-      <c r="V8" s="0" t="n">
-        <f aca="false">T8+U8</f>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="0" t="n">
+        <f aca="false">Y8+Z8</f>
         <v>101.220378624</v>
       </c>
-      <c r="W8" s="27" t="n">
-        <f aca="false">3/5*H8+M8/3</f>
-        <v>1000.8</v>
-      </c>
-      <c r="X8" s="27" t="n">
-        <f aca="false">R8-V8</f>
-        <v>2849.879621376</v>
-      </c>
-      <c r="Y8" s="27" t="n">
-        <f aca="false">1000/100*Q8*($Q$41+$Q$47-$Q$49)-V8</f>
+      <c r="AB8" s="26" t="n">
+        <f aca="false">AA8/$P8</f>
+        <v>0.2481049739052</v>
+      </c>
+      <c r="AC8" s="27" t="n">
+        <f aca="false">1000/100*Q8*($Q$41+$Q$47-$Q$49)-AA8</f>
         <v>1442.97344841541</v>
       </c>
-      <c r="Z8" s="27" t="n">
-        <f aca="false">Y8-V8+Q8/100*1000 *($Q$46+$Q$43)</f>
-        <v>2555.55439848231</v>
-      </c>
-      <c r="AA8" s="26" t="n">
-        <f aca="false">-T8+($Q$45 + $Q$46)*1000*Q8/100</f>
+      <c r="AD8" s="26" t="n">
+        <f aca="false">AC8/$P8</f>
+        <v>3.53692502074988</v>
+      </c>
+      <c r="AE8" s="27" t="n">
+        <f aca="false">AC8+Q8/100*1000 *($Q$46+$Q$43)</f>
+        <v>2656.77477710631</v>
+      </c>
+      <c r="AF8" s="26" t="n">
+        <f aca="false">AE8/$P8</f>
+        <v>6.51211787296815</v>
+      </c>
+      <c r="AG8" s="26" t="n">
+        <f aca="false">-Y8+($Q$45 + $Q$46)*1000*Q8/100</f>
         <v>1162.76371179775</v>
       </c>
-      <c r="AB8" s="26" t="n">
-        <f aca="false">AA8/P8/10</f>
+      <c r="AH8" s="26" t="n">
+        <f aca="false">AG8/P8/10</f>
         <v>0.285009268188109</v>
       </c>
-      <c r="AC8" s="26" t="n">
-        <f aca="false">AA8/P8</f>
+      <c r="AI8" s="26" t="n">
+        <f aca="false">AG8/P8</f>
         <v>2.85009268188109</v>
       </c>
-      <c r="AE8" s="26" t="n">
+      <c r="AK8" s="26" t="n">
         <f aca="false">-Q8*($Q$47)*10</f>
         <v>-672.503367882374</v>
       </c>
-      <c r="AF8" s="26" t="n">
-        <f aca="false">AE8/P8/10</f>
+      <c r="AL8" s="26" t="n">
+        <f aca="false">AK8/P8/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI8" s="23" t="n">
+      <c r="AO8" s="23" t="n">
         <v>514.3</v>
       </c>
-      <c r="AN8" s="23" t="s">
+      <c r="AT8" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AU8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AW8" s="23" t="n">
+        <f aca="false">AU8+AV8/100</f>
+        <v>1.9</v>
+      </c>
+      <c r="AX8" s="23" t="n">
+        <f aca="false">AW8*1000</f>
+        <v>1900</v>
+      </c>
+      <c r="BA8" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="BB8" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC8" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD8" s="28" t="n">
+        <f aca="false">BB8+BC8/10</f>
+        <v>9.9</v>
+      </c>
+      <c r="BE8" s="28" t="n">
+        <f aca="false">1000*BD8</f>
+        <v>9900</v>
+      </c>
+      <c r="BG8" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="BH8" s="23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BI8" s="23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BJ8" s="23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BK8" s="23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BL8" s="23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BM8" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO8" s="28" t="n">
+        <f aca="false">BH8*1000</f>
+        <v>1090</v>
+      </c>
+      <c r="BQ8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR8" s="23" t="n">
+        <v>148</v>
+      </c>
+      <c r="BS8" s="23" t="n">
+        <v>105</v>
+      </c>
+      <c r="BT8" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="BU8" s="23" t="n">
+        <v>143</v>
+      </c>
+      <c r="BW8" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="BX8" s="23" t="n">
+        <v>330</v>
+      </c>
+      <c r="BY8" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="AO8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP8" s="23" t="n">
-        <v>90</v>
-      </c>
-      <c r="AQ8" s="23" t="n">
-        <f aca="false">AO8+AP8/100</f>
-        <v>1.9</v>
-      </c>
-      <c r="AR8" s="23" t="n">
-        <f aca="false">AQ8*1000</f>
-        <v>1900</v>
-      </c>
-      <c r="AU8" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV8" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW8" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX8" s="28" t="n">
-        <f aca="false">AV8+AW8/10</f>
-        <v>9.9</v>
-      </c>
-      <c r="AY8" s="28" t="n">
-        <f aca="false">1000*AX8</f>
-        <v>9900</v>
-      </c>
-      <c r="BA8" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="BB8" s="23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BC8" s="23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD8" s="23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BE8" s="23" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BF8" s="23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BG8" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="BI8" s="28" t="n">
-        <f aca="false">BB8*1000</f>
-        <v>1090</v>
-      </c>
-      <c r="BK8" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="BL8" s="23" t="n">
-        <v>148</v>
-      </c>
-      <c r="BM8" s="23" t="n">
-        <v>105</v>
-      </c>
-      <c r="BN8" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="BO8" s="23" t="n">
-        <v>143</v>
-      </c>
-      <c r="BQ8" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="BR8" s="23" t="n">
-        <v>330</v>
-      </c>
-      <c r="BS8" s="23" t="s">
-        <v>52</v>
-      </c>
+      <c r="XFA8" s="0"/>
+      <c r="XFB8" s="0"/>
+      <c r="XFC8" s="0"/>
+      <c r="XFD8" s="0"/>
     </row>
     <row r="9" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>201</v>
@@ -3656,144 +3671,172 @@
         <v>2687.9</v>
       </c>
       <c r="S9" s="26" t="n">
+        <f aca="false">R9/$P9</f>
+        <v>5.30199621271895</v>
+      </c>
+      <c r="T9" s="26" t="n">
         <f aca="false">R9/P9</f>
         <v>5.30199621271895</v>
       </c>
-      <c r="T9" s="26"/>
-      <c r="U9" s="31" t="n">
+      <c r="U9" s="27" t="n">
+        <f aca="false">3/5*H9+M9/3</f>
+        <v>877.466666666667</v>
+      </c>
+      <c r="V9" s="26" t="n">
+        <f aca="false">U9/$P9</f>
+        <v>1.73084003997686</v>
+      </c>
+      <c r="W9" s="27" t="n">
+        <f aca="false">R9-U9</f>
+        <v>1810.43333333333</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <f aca="false">W9/$P9</f>
+        <v>3.5711561727421</v>
+      </c>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="31" t="n">
         <f aca="false">F9</f>
         <v>61.1</v>
       </c>
-      <c r="V9" s="0" t="n">
-        <f aca="false">T9+U9</f>
+      <c r="AA9" s="0" t="n">
+        <f aca="false">Y9+Z9</f>
         <v>61.1</v>
       </c>
-      <c r="W9" s="27" t="n">
-        <f aca="false">3/5*H9+M9/3</f>
-        <v>877.466666666667</v>
-      </c>
-      <c r="X9" s="27" t="n">
-        <f aca="false">R9-V9</f>
-        <v>2626.8</v>
-      </c>
-      <c r="Y9" s="27" t="n">
-        <f aca="false">1000/100*Q9*($Q$41+$Q$47-$Q$49)-V9</f>
+      <c r="AB9" s="26" t="n">
+        <f aca="false">AA9/$P9</f>
+        <v>0.120522329177844</v>
+      </c>
+      <c r="AC9" s="27" t="n">
+        <f aca="false">1000/100*Q9*($Q$41+$Q$47-$Q$49)-AA9</f>
         <v>1857.75880609034</v>
       </c>
-      <c r="Z9" s="27" t="n">
-        <f aca="false">Y9-V9+Q9/100*1000 *($Q$46+$Q$43)</f>
-        <v>3304.96257445091</v>
-      </c>
-      <c r="AA9" s="26" t="n">
-        <f aca="false">-U9+($Q$45 + $Q$46)*1000*Q9/100</f>
+      <c r="AD9" s="26" t="n">
+        <f aca="false">AC9/$P9</f>
+        <v>3.66450766547723</v>
+      </c>
+      <c r="AE9" s="27" t="n">
+        <f aca="false">AC9+Q9/100*1000 *($Q$46+$Q$43)</f>
+        <v>3366.06257445091</v>
+      </c>
+      <c r="AF9" s="26" t="n">
+        <f aca="false">AE9/$P9</f>
+        <v>6.6397005176955</v>
+      </c>
+      <c r="AG9" s="26" t="n">
+        <f aca="false">-Z9+($Q$45 + $Q$46)*1000*Q9/100</f>
         <v>1509.56228357741</v>
       </c>
-      <c r="AB9" s="26" t="n">
-        <f aca="false">AA9/P9/10</f>
+      <c r="AH9" s="26" t="n">
+        <f aca="false">AG9/P9/10</f>
         <v>0.297767532660844</v>
       </c>
-      <c r="AC9" s="26" t="n">
-        <f aca="false">AA9/P9</f>
+      <c r="AI9" s="26" t="n">
+        <f aca="false">AG9/P9</f>
         <v>2.97767532660844</v>
       </c>
-      <c r="AE9" s="26" t="n">
+      <c r="AK9" s="26" t="n">
         <f aca="false">-Q9*($Q$47)*10</f>
         <v>-835.671654031012</v>
       </c>
-      <c r="AF9" s="26" t="n">
-        <f aca="false">AE9/P9/10</f>
+      <c r="AL9" s="26" t="n">
+        <f aca="false">AK9/P9/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI9" s="23" t="n">
+      <c r="AO9" s="23" t="n">
         <v>642</v>
       </c>
-      <c r="AN9" s="23" t="s">
+      <c r="AT9" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" s="23" t="n">
+        <f aca="false">AU9+AV9/100</f>
+        <v>1.1</v>
+      </c>
+      <c r="AX9" s="23" t="n">
+        <f aca="false">AW9*1000</f>
+        <v>1100</v>
+      </c>
+      <c r="BA9" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="BB9" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC9" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD9" s="28" t="n">
+        <f aca="false">BB9+BC9/10</f>
+        <v>9.8</v>
+      </c>
+      <c r="BE9" s="28" t="n">
+        <f aca="false">1000*BD9</f>
+        <v>9800</v>
+      </c>
+      <c r="BG9" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="BH9" s="23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BI9" s="23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BJ9" s="23" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BK9" s="23" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL9" s="23" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BM9" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="BO9" s="28" t="n">
+        <f aca="false">BH9*1000</f>
+        <v>1100</v>
+      </c>
+      <c r="BQ9" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="BR9" s="23" t="n">
+        <v>82</v>
+      </c>
+      <c r="BS9" s="23" t="n">
+        <v>148</v>
+      </c>
+      <c r="BT9" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU9" s="23" t="n">
+        <v>201</v>
+      </c>
+      <c r="BW9" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="BX9" s="23" t="n">
+        <v>184</v>
+      </c>
+      <c r="BY9" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="AO9" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP9" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ9" s="23" t="n">
-        <f aca="false">AO9+AP9/100</f>
-        <v>1.1</v>
-      </c>
-      <c r="AR9" s="23" t="n">
-        <f aca="false">AQ9*1000</f>
-        <v>1100</v>
-      </c>
-      <c r="AU9" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="AV9" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW9" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX9" s="28" t="n">
-        <f aca="false">AV9+AW9/10</f>
-        <v>9.8</v>
-      </c>
-      <c r="AY9" s="28" t="n">
-        <f aca="false">1000*AX9</f>
-        <v>9800</v>
-      </c>
-      <c r="BA9" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="BB9" s="23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC9" s="23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BD9" s="23" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="BE9" s="23" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BF9" s="23" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BG9" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="BI9" s="28" t="n">
-        <f aca="false">BB9*1000</f>
-        <v>1100</v>
-      </c>
-      <c r="BK9" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="BL9" s="23" t="n">
-        <v>82</v>
-      </c>
-      <c r="BM9" s="23" t="n">
-        <v>148</v>
-      </c>
-      <c r="BN9" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO9" s="23" t="n">
-        <v>201</v>
-      </c>
-      <c r="BQ9" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="BR9" s="23" t="n">
-        <v>184</v>
-      </c>
-      <c r="BS9" s="23" t="s">
-        <v>59</v>
-      </c>
+      <c r="XFA9" s="0"/>
+      <c r="XFB9" s="0"/>
+      <c r="XFC9" s="0"/>
+      <c r="XFD9" s="0"/>
     </row>
     <row r="10" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B10" s="23" t="n">
         <v>38</v>
@@ -3857,141 +3900,169 @@
         <v>359.7</v>
       </c>
       <c r="S10" s="26" t="n">
+        <f aca="false">R10/$P10</f>
+        <v>6.87224164612827</v>
+      </c>
+      <c r="T10" s="26" t="n">
         <f aca="false">R10/P10</f>
         <v>6.87224164612827</v>
       </c>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="0" t="n">
-        <f aca="false">T10+U10</f>
-        <v>0</v>
-      </c>
-      <c r="W10" s="27" t="n">
+      <c r="U10" s="27" t="n">
         <f aca="false">3/5*H10+M10/3</f>
         <v>96.5333333333333</v>
       </c>
-      <c r="X10" s="27" t="n">
-        <f aca="false">R10-V10</f>
-        <v>359.7</v>
-      </c>
-      <c r="Y10" s="27" t="n">
-        <f aca="false">1000/100*Q10*($Q$41+$Q$47-$Q$49)-V10</f>
+      <c r="V10" s="26" t="n">
+        <f aca="false">U10/$P10</f>
+        <v>1.84431580086994</v>
+      </c>
+      <c r="W10" s="27" t="n">
+        <f aca="false">R10-U10</f>
+        <v>263.166666666667</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <f aca="false">W10/$P10</f>
+        <v>5.02792584525834</v>
+      </c>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="26"/>
+      <c r="AA10" s="0" t="n">
+        <f aca="false">Y10+Z10</f>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="26" t="n">
+        <f aca="false">AA10/$P10</f>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="27" t="n">
+        <f aca="false">1000/100*Q10*($Q$41+$Q$47-$Q$49)-AA10</f>
         <v>198.112254950241</v>
       </c>
-      <c r="Z10" s="27" t="n">
-        <f aca="false">Y10-V10+Q10/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD10" s="26" t="n">
+        <f aca="false">AC10/$P10</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE10" s="27" t="n">
+        <f aca="false">AC10+Q10/100*1000 *($Q$46+$Q$43)</f>
         <v>353.836824028197</v>
       </c>
-      <c r="AA10" s="26" t="n">
-        <f aca="false">-V10+($Q$45 + $Q$46)*1000*Q10/100</f>
+      <c r="AF10" s="26" t="n">
+        <f aca="false">AE10/$P10</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG10" s="26" t="n">
+        <f aca="false">-AA10+($Q$45 + $Q$46)*1000*Q10/100</f>
         <v>162.16276350151</v>
       </c>
-      <c r="AB10" s="26" t="n">
-        <f aca="false">AA10/P10/10</f>
+      <c r="AH10" s="26" t="n">
+        <f aca="false">AG10/P10/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC10" s="26" t="n">
-        <f aca="false">AA10/P10</f>
+      <c r="AI10" s="26" t="n">
+        <f aca="false">AG10/P10</f>
         <v>3.09819765578628</v>
       </c>
-      <c r="AE10" s="26" t="n">
+      <c r="AK10" s="26" t="n">
         <f aca="false">-Q10*($Q$47)*10</f>
         <v>-86.2787794769552</v>
       </c>
-      <c r="AF10" s="26" t="n">
-        <f aca="false">AE10/P10/10</f>
+      <c r="AL10" s="26" t="n">
+        <f aca="false">AK10/P10/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI10" s="23" t="n">
+      <c r="AO10" s="23" t="n">
         <v>116</v>
       </c>
-      <c r="AN10" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AO10" s="23" t="n">
+      <c r="AT10" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP10" s="23" t="n">
+      <c r="AV10" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="AQ10" s="23" t="n">
-        <f aca="false">AO10+AP10/100</f>
+      <c r="AW10" s="23" t="n">
+        <f aca="false">AU10+AV10/100</f>
         <v>0.27</v>
       </c>
-      <c r="AR10" s="23" t="n">
-        <f aca="false">AQ10*1000</f>
+      <c r="AX10" s="23" t="n">
+        <f aca="false">AW10*1000</f>
         <v>270</v>
       </c>
-      <c r="AU10" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AV10" s="23" t="n">
+      <c r="BA10" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="BB10" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AW10" s="23" t="n">
+      <c r="BC10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AX10" s="28" t="n">
-        <f aca="false">AV10+AW10/10</f>
+      <c r="BD10" s="28" t="n">
+        <f aca="false">BB10+BC10/10</f>
         <v>1.6</v>
       </c>
-      <c r="AY10" s="28" t="n">
-        <f aca="false">1000*AX10</f>
+      <c r="BE10" s="28" t="n">
+        <f aca="false">1000*BD10</f>
         <v>1600</v>
       </c>
-      <c r="BA10" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="BB10" s="23" t="n">
+      <c r="BG10" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="BH10" s="23" t="n">
         <v>0.27</v>
       </c>
-      <c r="BC10" s="23" t="n">
+      <c r="BI10" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="BD10" s="23" t="n">
+      <c r="BJ10" s="23" t="n">
         <v>0.55</v>
       </c>
-      <c r="BE10" s="23" t="n">
+      <c r="BK10" s="23" t="n">
         <v>1.09</v>
       </c>
-      <c r="BF10" s="23" t="n">
+      <c r="BL10" s="23" t="n">
         <v>1.48</v>
       </c>
-      <c r="BG10" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="BI10" s="28" t="n">
-        <f aca="false">BB10*1000</f>
+      <c r="BM10" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="BO10" s="28" t="n">
+        <f aca="false">BH10*1000</f>
         <v>270</v>
       </c>
-      <c r="BK10" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="BL10" s="23" t="n">
+      <c r="BQ10" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="BR10" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="BM10" s="23" t="n">
+      <c r="BS10" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="BN10" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO10" s="23" t="n">
+      <c r="BT10" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU10" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="BQ10" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="BR10" s="23" t="n">
+      <c r="BW10" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="BX10" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="BS10" s="23" t="s">
-        <v>64</v>
-      </c>
+      <c r="BY10" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="XFA10" s="0"/>
+      <c r="XFB10" s="0"/>
+      <c r="XFC10" s="0"/>
+      <c r="XFD10" s="0"/>
     </row>
     <row r="11" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B11" s="23" t="n">
         <v>46</v>
@@ -4055,141 +4126,169 @@
         <v>485.7</v>
       </c>
       <c r="S11" s="26" t="n">
+        <f aca="false">R11/$P11</f>
+        <v>8.30710816172949</v>
+      </c>
+      <c r="T11" s="26" t="n">
         <f aca="false">R11/P11</f>
         <v>8.30710816172949</v>
       </c>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="0" t="n">
-        <f aca="false">T11+U11</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="27" t="n">
+      <c r="U11" s="27" t="n">
         <f aca="false">3/5*H11+M11/3</f>
         <v>125.866666666667</v>
       </c>
-      <c r="X11" s="27" t="n">
-        <f aca="false">R11-V11</f>
-        <v>485.7</v>
-      </c>
-      <c r="Y11" s="27" t="n">
-        <f aca="false">1000/100*Q11*($Q$41+$Q$47-$Q$49)-V11</f>
+      <c r="V11" s="26" t="n">
+        <f aca="false">U11/$P11</f>
+        <v>2.15274452121958</v>
+      </c>
+      <c r="W11" s="27" t="n">
+        <f aca="false">R11-U11</f>
+        <v>359.833333333333</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <f aca="false">W11/$P11</f>
+        <v>6.15436364050991</v>
+      </c>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="26"/>
+      <c r="AA11" s="0" t="n">
+        <f aca="false">Y11+Z11</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="26" t="n">
+        <f aca="false">AA11/$P11</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="27" t="n">
+        <f aca="false">1000/100*Q11*($Q$41+$Q$47-$Q$49)-AA11</f>
         <v>221.303133727493</v>
       </c>
-      <c r="Z11" s="27" t="n">
-        <f aca="false">Y11-V11+Q11/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD11" s="26" t="n">
+        <f aca="false">AC11/$P11</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE11" s="27" t="n">
+        <f aca="false">AC11+Q11/100*1000 *($Q$46+$Q$43)</f>
         <v>395.25670941099</v>
       </c>
-      <c r="AA11" s="26" t="n">
-        <f aca="false">-V11+($Q$45 + $Q$46)*1000*Q11/100</f>
+      <c r="AF11" s="26" t="n">
+        <f aca="false">AE11/$P11</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG11" s="26" t="n">
+        <f aca="false">-AA11+($Q$45 + $Q$46)*1000*Q11/100</f>
         <v>181.145420538512</v>
       </c>
-      <c r="AB11" s="26" t="n">
-        <f aca="false">AA11/P11/10</f>
+      <c r="AH11" s="26" t="n">
+        <f aca="false">AG11/P11/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC11" s="26" t="n">
-        <f aca="false">ROUND(AA11/P11 *100/1000, 2)</f>
+      <c r="AI11" s="26" t="n">
+        <f aca="false">ROUND(AG11/P11 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE11" s="26" t="n">
+      <c r="AK11" s="26" t="n">
         <f aca="false">-Q11*($Q$47)*10</f>
         <v>-96.378511653553</v>
       </c>
-      <c r="AF11" s="26" t="n">
-        <f aca="false">AE11/P11/10</f>
+      <c r="AL11" s="26" t="n">
+        <f aca="false">AK11/P11/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI11" s="23" t="n">
+      <c r="AO11" s="23" t="n">
         <v>93</v>
       </c>
-      <c r="AN11" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO11" s="23" t="n">
+      <c r="AT11" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AU11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP11" s="23" t="n">
+      <c r="AV11" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="AQ11" s="23" t="n">
-        <f aca="false">AO11+AP11/100</f>
+      <c r="AW11" s="23" t="n">
+        <f aca="false">AU11+AV11/100</f>
         <v>0.38</v>
       </c>
-      <c r="AR11" s="23" t="n">
-        <f aca="false">AQ11*1000</f>
+      <c r="AX11" s="23" t="n">
+        <f aca="false">AW11*1000</f>
         <v>380</v>
       </c>
-      <c r="AU11" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV11" s="23" t="n">
+      <c r="BA11" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB11" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AW11" s="23" t="n">
+      <c r="BC11" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AX11" s="28" t="n">
-        <f aca="false">AV11+AW11/10</f>
+      <c r="BD11" s="28" t="n">
+        <f aca="false">BB11+BC11/10</f>
         <v>2.3</v>
       </c>
-      <c r="AY11" s="28" t="n">
-        <f aca="false">1000*AX11</f>
+      <c r="BE11" s="28" t="n">
+        <f aca="false">1000*BD11</f>
         <v>2300</v>
       </c>
-      <c r="BA11" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB11" s="23" t="n">
+      <c r="BG11" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="BH11" s="23" t="n">
         <v>0.38</v>
       </c>
-      <c r="BC11" s="23" t="n">
+      <c r="BI11" s="23" t="n">
         <v>0.84</v>
       </c>
-      <c r="BD11" s="23" t="n">
+      <c r="BJ11" s="23" t="n">
         <v>0.48</v>
       </c>
-      <c r="BE11" s="23" t="n">
+      <c r="BK11" s="23" t="n">
         <v>1.76</v>
       </c>
-      <c r="BF11" s="23" t="n">
+      <c r="BL11" s="23" t="n">
         <v>2.39</v>
       </c>
-      <c r="BG11" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="BI11" s="28" t="n">
-        <f aca="false">BB11*1000</f>
+      <c r="BM11" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="BO11" s="28" t="n">
+        <f aca="false">BH11*1000</f>
         <v>380</v>
       </c>
-      <c r="BK11" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="BL11" s="23" t="n">
+      <c r="BQ11" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="BR11" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="BM11" s="23" t="n">
+      <c r="BS11" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="BN11" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO11" s="23" t="n">
+      <c r="BT11" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU11" s="23" t="n">
         <v>46</v>
       </c>
-      <c r="BQ11" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="BR11" s="23" t="n">
+      <c r="BW11" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="BX11" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="BS11" s="23" t="s">
-        <v>69</v>
-      </c>
+      <c r="BY11" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="XFA11" s="0"/>
+      <c r="XFB11" s="0"/>
+      <c r="XFC11" s="0"/>
+      <c r="XFD11" s="0"/>
     </row>
     <row r="12" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B12" s="23" t="n">
         <v>16</v>
@@ -4253,141 +4352,169 @@
         <v>333.1</v>
       </c>
       <c r="S12" s="26" t="n">
+        <f aca="false">R12/$P12</f>
+        <v>15.1477944520237</v>
+      </c>
+      <c r="T12" s="26" t="n">
         <f aca="false">R12/P12</f>
         <v>15.1477944520237</v>
       </c>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="0" t="n">
-        <f aca="false">T12+U12</f>
-        <v>0</v>
-      </c>
-      <c r="W12" s="27" t="n">
+      <c r="U12" s="27" t="n">
         <f aca="false">3/5*H12+M12/3</f>
         <v>95.6</v>
       </c>
-      <c r="X12" s="27" t="n">
-        <f aca="false">R12-V12</f>
-        <v>333.1</v>
-      </c>
-      <c r="Y12" s="27" t="n">
-        <f aca="false">1000/100*Q12*($Q$41+$Q$47-$Q$49)-V12</f>
+      <c r="V12" s="26" t="n">
+        <f aca="false">U12/$P12</f>
+        <v>4.34743065029559</v>
+      </c>
+      <c r="W12" s="27" t="n">
+        <f aca="false">R12-U12</f>
+        <v>237.5</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <f aca="false">W12/$P12</f>
+        <v>10.8003638017281</v>
+      </c>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="0" t="n">
+        <f aca="false">Y12+Z12</f>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="26" t="n">
+        <f aca="false">AA12/$P12</f>
+        <v>0</v>
+      </c>
+      <c r="AC12" s="27" t="n">
+        <f aca="false">1000/100*Q12*($Q$41+$Q$47-$Q$49)-AA12</f>
         <v>83.2328095824651</v>
       </c>
-      <c r="Z12" s="27" t="n">
-        <f aca="false">Y12-V12+Q12/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD12" s="26" t="n">
+        <f aca="false">AC12/$P12</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE12" s="27" t="n">
+        <f aca="false">AC12+Q12/100*1000 *($Q$46+$Q$43)</f>
         <v>148.657300402745</v>
       </c>
-      <c r="AA12" s="26" t="n">
-        <f aca="false">-V12+($Q$45 + $Q$46)*1000*Q12/100</f>
+      <c r="AF12" s="26" t="n">
+        <f aca="false">AE12/$P12</f>
+        <v>6.76022284687335</v>
+      </c>
+      <c r="AG12" s="26" t="n">
+        <f aca="false">-AA12+($Q$45 + $Q$46)*1000*Q12/100</f>
         <v>68.1293664507404</v>
       </c>
-      <c r="AB12" s="26" t="n">
-        <f aca="false">AA12/P12/10</f>
+      <c r="AH12" s="26" t="n">
+        <f aca="false">AG12/P12/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC12" s="26" t="n">
-        <f aca="false">ROUND(AA12/P12 *100/1000, 2)</f>
+      <c r="AI12" s="26" t="n">
+        <f aca="false">ROUND(AG12/P12 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE12" s="26" t="n">
+      <c r="AK12" s="26" t="n">
         <f aca="false">-Q12*($Q$47)*10</f>
         <v>-36.2482635161393</v>
       </c>
-      <c r="AF12" s="26" t="n">
-        <f aca="false">AE12/P12/10</f>
+      <c r="AL12" s="26" t="n">
+        <f aca="false">AK12/P12/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI12" s="23" t="n">
+      <c r="AO12" s="23" t="n">
         <v>36.5</v>
       </c>
-      <c r="AN12" s="23" t="s">
+      <c r="AT12" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW12" s="23" t="n">
+        <f aca="false">AU12+AV12/100</f>
+        <v>0.29</v>
+      </c>
+      <c r="AX12" s="23" t="n">
+        <f aca="false">AW12*1000</f>
+        <v>290</v>
+      </c>
+      <c r="BA12" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC12" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD12" s="28" t="n">
+        <f aca="false">BB12+BC12/10</f>
+        <v>1.5</v>
+      </c>
+      <c r="BE12" s="28" t="n">
+        <f aca="false">1000*BD12</f>
+        <v>1500</v>
+      </c>
+      <c r="BG12" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH12" s="23" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BI12" s="23" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BJ12" s="23" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BK12" s="23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BL12" s="23" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="BM12" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="BO12" s="28" t="n">
+        <f aca="false">BH12*1000</f>
+        <v>290</v>
+      </c>
+      <c r="BQ12" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR12" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS12" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT12" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU12" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW12" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BX12" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BY12" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="AO12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AQ12" s="23" t="n">
-        <f aca="false">AO12+AP12/100</f>
-        <v>0.29</v>
-      </c>
-      <c r="AR12" s="23" t="n">
-        <f aca="false">AQ12*1000</f>
-        <v>290</v>
-      </c>
-      <c r="AU12" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="AV12" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW12" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX12" s="28" t="n">
-        <f aca="false">AV12+AW12/10</f>
-        <v>1.5</v>
-      </c>
-      <c r="AY12" s="28" t="n">
-        <f aca="false">1000*AX12</f>
-        <v>1500</v>
-      </c>
-      <c r="BA12" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="BB12" s="23" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BC12" s="23" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BD12" s="23" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="BE12" s="23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF12" s="23" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="BG12" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI12" s="28" t="n">
-        <f aca="false">BB12*1000</f>
-        <v>290</v>
-      </c>
-      <c r="BK12" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="BL12" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM12" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN12" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO12" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ12" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="BR12" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BS12" s="23" t="s">
-        <v>76</v>
-      </c>
+      <c r="XFA12" s="0"/>
+      <c r="XFB12" s="0"/>
+      <c r="XFC12" s="0"/>
+      <c r="XFD12" s="0"/>
     </row>
     <row r="13" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B13" s="23" t="n">
         <v>178</v>
@@ -4451,141 +4578,169 @@
         <v>1493.2</v>
       </c>
       <c r="S13" s="26" t="n">
+        <f aca="false">R13/$P13</f>
+        <v>6.56141106370264</v>
+      </c>
+      <c r="T13" s="26" t="n">
         <f aca="false">R13/P13</f>
         <v>6.56141106370264</v>
       </c>
-      <c r="T13" s="26"/>
-      <c r="U13" s="26"/>
-      <c r="V13" s="0" t="n">
-        <f aca="false">T13+U13</f>
-        <v>0</v>
-      </c>
-      <c r="W13" s="27" t="n">
+      <c r="U13" s="27" t="n">
         <f aca="false">3/5*H13+M13/3</f>
         <v>417.333333333333</v>
       </c>
-      <c r="X13" s="27" t="n">
-        <f aca="false">R13-V13</f>
-        <v>1493.2</v>
-      </c>
-      <c r="Y13" s="27" t="n">
-        <f aca="false">1000/100*Q13*($Q$41+$Q$47-$Q$49)-V13</f>
+      <c r="V13" s="26" t="n">
+        <f aca="false">U13/$P13</f>
+        <v>1.83384379224835</v>
+      </c>
+      <c r="W13" s="27" t="n">
+        <f aca="false">R13-U13</f>
+        <v>1075.86666666667</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <f aca="false">W13/$P13</f>
+        <v>4.72756727145429</v>
+      </c>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="0" t="n">
+        <f aca="false">Y13+Z13</f>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="26" t="n">
+        <f aca="false">AA13/$P13</f>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="27" t="n">
+        <f aca="false">1000/100*Q13*($Q$41+$Q$47-$Q$49)-AA13</f>
         <v>861.370630973638</v>
       </c>
-      <c r="Z13" s="27" t="n">
-        <f aca="false">Y13-V13+Q13/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD13" s="26" t="n">
+        <f aca="false">AC13/$P13</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE13" s="27" t="n">
+        <f aca="false">AC13+Q13/100*1000 *($Q$46+$Q$43)</f>
         <v>1538.44419393151</v>
       </c>
-      <c r="AA13" s="26" t="n">
-        <f aca="false">-V13+($Q$45 + $Q$46)*1000*Q13/100</f>
+      <c r="AF13" s="26" t="n">
+        <f aca="false">AE13/$P13</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG13" s="26" t="n">
+        <f aca="false">-AA13+($Q$45 + $Q$46)*1000*Q13/100</f>
         <v>705.066135120251</v>
       </c>
-      <c r="AB13" s="26" t="n">
-        <f aca="false">AA13/P13/10</f>
+      <c r="AH13" s="26" t="n">
+        <f aca="false">AG13/P13/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC13" s="26" t="n">
-        <f aca="false">ROUND(AA13/P13 *100/1000, 2)</f>
+      <c r="AI13" s="26" t="n">
+        <f aca="false">ROUND(AG13/P13 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE13" s="26" t="n">
+      <c r="AK13" s="26" t="n">
         <f aca="false">-Q13*($Q$47)*10</f>
         <v>-375.130790048129</v>
       </c>
-      <c r="AF13" s="26" t="n">
-        <f aca="false">AE13/P13/10</f>
+      <c r="AL13" s="26" t="n">
+        <f aca="false">AK13/P13/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI13" s="23" t="n">
+      <c r="AO13" s="23" t="n">
         <v>347.3</v>
       </c>
-      <c r="AN13" s="23" t="s">
+      <c r="AT13" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW13" s="23" t="n">
+        <f aca="false">AU13+AV13/100</f>
+        <v>0.44</v>
+      </c>
+      <c r="AX13" s="23" t="n">
+        <f aca="false">AW13*1000</f>
+        <v>440</v>
+      </c>
+      <c r="BA13" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB13" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC13" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD13" s="28" t="n">
+        <f aca="false">BB13+BC13/10</f>
+        <v>4.6</v>
+      </c>
+      <c r="BE13" s="28" t="n">
+        <f aca="false">1000*BD13</f>
+        <v>4600</v>
+      </c>
+      <c r="BG13" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="BH13" s="23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BI13" s="23" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BJ13" s="23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BK13" s="23" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL13" s="23" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BM13" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="BO13" s="28" t="n">
+        <f aca="false">BH13*1000</f>
+        <v>440</v>
+      </c>
+      <c r="BQ13" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="BR13" s="23" t="n">
+        <v>118</v>
+      </c>
+      <c r="BS13" s="23" t="n">
+        <v>131</v>
+      </c>
+      <c r="BT13" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU13" s="23" t="n">
+        <v>178</v>
+      </c>
+      <c r="BW13" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="BX13" s="23" t="n">
+        <v>263</v>
+      </c>
+      <c r="BY13" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="AO13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AQ13" s="23" t="n">
-        <f aca="false">AO13+AP13/100</f>
-        <v>0.44</v>
-      </c>
-      <c r="AR13" s="23" t="n">
-        <f aca="false">AQ13*1000</f>
-        <v>440</v>
-      </c>
-      <c r="AU13" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV13" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW13" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX13" s="28" t="n">
-        <f aca="false">AV13+AW13/10</f>
-        <v>4.6</v>
-      </c>
-      <c r="AY13" s="28" t="n">
-        <f aca="false">1000*AX13</f>
-        <v>4600</v>
-      </c>
-      <c r="BA13" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="BB13" s="23" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BC13" s="23" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="BD13" s="23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BE13" s="23" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BF13" s="23" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BG13" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="BI13" s="28" t="n">
-        <f aca="false">BB13*1000</f>
-        <v>440</v>
-      </c>
-      <c r="BK13" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="BL13" s="23" t="n">
-        <v>118</v>
-      </c>
-      <c r="BM13" s="23" t="n">
-        <v>131</v>
-      </c>
-      <c r="BN13" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO13" s="23" t="n">
-        <v>178</v>
-      </c>
-      <c r="BQ13" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="BR13" s="23" t="n">
-        <v>263</v>
-      </c>
-      <c r="BS13" s="23" t="s">
-        <v>83</v>
-      </c>
+      <c r="XFA13" s="0"/>
+      <c r="XFB13" s="0"/>
+      <c r="XFC13" s="0"/>
+      <c r="XFD13" s="0"/>
     </row>
     <row r="14" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B14" s="23" t="n">
         <v>108</v>
@@ -4649,141 +4804,169 @@
         <v>1776.1</v>
       </c>
       <c r="S14" s="26" t="n">
+        <f aca="false">R14/$P14</f>
+        <v>5.09837354965754</v>
+      </c>
+      <c r="T14" s="26" t="n">
         <f aca="false">R14/P14</f>
         <v>5.09837354965754</v>
       </c>
-      <c r="T14" s="26"/>
-      <c r="U14" s="26"/>
-      <c r="V14" s="0" t="n">
-        <f aca="false">T14+U14</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="27" t="n">
+      <c r="U14" s="27" t="n">
         <f aca="false">3/5*H14+M14/3</f>
         <v>510.2</v>
       </c>
-      <c r="X14" s="27" t="n">
-        <f aca="false">R14-V14</f>
-        <v>1776.1</v>
-      </c>
-      <c r="Y14" s="27" t="n">
-        <f aca="false">1000/100*Q14*($Q$41+$Q$47-$Q$49)-V14</f>
+      <c r="V14" s="26" t="n">
+        <f aca="false">U14/$P14</f>
+        <v>1.46455164970175</v>
+      </c>
+      <c r="W14" s="27" t="n">
+        <f aca="false">R14-U14</f>
+        <v>1265.9</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <f aca="false">W14/$P14</f>
+        <v>3.63382189995579</v>
+      </c>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="0" t="n">
+        <f aca="false">Y14+Z14</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="26" t="n">
+        <f aca="false">AA14/$P14</f>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="27" t="n">
+        <f aca="false">1000/100*Q14*($Q$41+$Q$47-$Q$49)-AA14</f>
         <v>1318.57575911801</v>
       </c>
-      <c r="Z14" s="27" t="n">
-        <f aca="false">Y14-V14+Q14/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD14" s="26" t="n">
+        <f aca="false">AC14/$P14</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE14" s="27" t="n">
+        <f aca="false">AC14+Q14/100*1000 *($Q$46+$Q$43)</f>
         <v>2355.03179227388</v>
       </c>
-      <c r="AA14" s="26" t="n">
-        <f aca="false">-V14+($Q$45 + $Q$46)*1000*Q14/100</f>
+      <c r="AF14" s="26" t="n">
+        <f aca="false">AE14/$P14</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG14" s="26" t="n">
+        <f aca="false">-AA14+($Q$45 + $Q$46)*1000*Q14/100</f>
         <v>1079.30672455564</v>
       </c>
-      <c r="AB14" s="26" t="n">
-        <f aca="false">AA14/P14/10</f>
+      <c r="AH14" s="26" t="n">
+        <f aca="false">AG14/P14/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC14" s="26" t="n">
-        <f aca="false">ROUND(AA14/P14 *100/1000, 2)</f>
+      <c r="AI14" s="26" t="n">
+        <f aca="false">ROUND(AG14/P14 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE14" s="26" t="n">
+      <c r="AK14" s="26" t="n">
         <f aca="false">-Q14*($Q$47)*10</f>
         <v>-574.245682949676</v>
       </c>
-      <c r="AF14" s="26" t="n">
-        <f aca="false">AE14/P14/10</f>
+      <c r="AL14" s="26" t="n">
+        <f aca="false">AK14/P14/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI14" s="23" t="n">
+      <c r="AO14" s="23" t="n">
         <v>417.8</v>
       </c>
-      <c r="AN14" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO14" s="23" t="n">
+      <c r="AT14" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AU14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AP14" s="23" t="n">
+      <c r="AV14" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="AQ14" s="23" t="n">
-        <f aca="false">AO14+AP14/100</f>
+      <c r="AW14" s="23" t="n">
+        <f aca="false">AU14+AV14/100</f>
         <v>1.13</v>
       </c>
-      <c r="AR14" s="23" t="n">
-        <f aca="false">AQ14*1000</f>
+      <c r="AX14" s="23" t="n">
+        <f aca="false">AW14*1000</f>
         <v>1130</v>
       </c>
-      <c r="AU14" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="AV14" s="23" t="n">
+      <c r="BA14" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="BB14" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="AW14" s="23" t="n">
+      <c r="BC14" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AX14" s="28" t="n">
-        <f aca="false">AV14+AW14/10</f>
+      <c r="BD14" s="28" t="n">
+        <f aca="false">BB14+BC14/10</f>
         <v>4.2</v>
       </c>
-      <c r="AY14" s="28" t="n">
-        <f aca="false">1000*AX14</f>
+      <c r="BE14" s="28" t="n">
+        <f aca="false">1000*BD14</f>
         <v>4200</v>
       </c>
-      <c r="BA14" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="BB14" s="23" t="n">
+      <c r="BG14" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="BH14" s="23" t="n">
         <v>1.13</v>
       </c>
-      <c r="BC14" s="23" t="n">
+      <c r="BI14" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="BD14" s="23" t="n">
+      <c r="BJ14" s="23" t="n">
         <v>2.27</v>
       </c>
-      <c r="BE14" s="23" t="n">
+      <c r="BK14" s="23" t="n">
         <v>1.1</v>
       </c>
-      <c r="BF14" s="23" t="n">
+      <c r="BL14" s="23" t="n">
         <v>1.49</v>
       </c>
-      <c r="BG14" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI14" s="28" t="n">
-        <f aca="false">BB14*1000</f>
+      <c r="BM14" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO14" s="28" t="n">
+        <f aca="false">BH14*1000</f>
         <v>1130</v>
       </c>
-      <c r="BK14" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="BL14" s="23" t="n">
+      <c r="BQ14" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="BR14" s="23" t="n">
         <v>116</v>
       </c>
-      <c r="BM14" s="23" t="n">
+      <c r="BS14" s="23" t="n">
         <v>79</v>
       </c>
-      <c r="BN14" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO14" s="23" t="n">
+      <c r="BT14" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU14" s="23" t="n">
         <v>108</v>
       </c>
-      <c r="BQ14" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="BR14" s="23" t="n">
+      <c r="BW14" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="BX14" s="23" t="n">
         <v>258</v>
       </c>
-      <c r="BS14" s="23" t="s">
-        <v>89</v>
-      </c>
+      <c r="BY14" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="XFA14" s="0"/>
+      <c r="XFB14" s="0"/>
+      <c r="XFC14" s="0"/>
+      <c r="XFD14" s="0"/>
     </row>
     <row r="15" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B15" s="23" t="n">
         <v>23</v>
@@ -4847,141 +5030,169 @@
         <v>156.4</v>
       </c>
       <c r="S15" s="26" t="n">
+        <f aca="false">R15/$P15</f>
+        <v>5.0616524806628</v>
+      </c>
+      <c r="T15" s="26" t="n">
         <f aca="false">R15/P15</f>
         <v>5.0616524806628</v>
       </c>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="0" t="n">
-        <f aca="false">T15+U15</f>
-        <v>0</v>
-      </c>
-      <c r="W15" s="27" t="n">
+      <c r="U15" s="27" t="n">
         <f aca="false">3/5*H15+M15/3</f>
         <v>40.0666666666667</v>
       </c>
-      <c r="X15" s="27" t="n">
-        <f aca="false">R15-V15</f>
-        <v>156.4</v>
-      </c>
-      <c r="Y15" s="27" t="n">
-        <f aca="false">1000/100*Q15*($Q$41+$Q$47-$Q$49)-V15</f>
+      <c r="V15" s="26" t="n">
+        <f aca="false">U15/$P15</f>
+        <v>1.29669784351166</v>
+      </c>
+      <c r="W15" s="27" t="n">
+        <f aca="false">R15-U15</f>
+        <v>116.333333333333</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <f aca="false">W15/$P15</f>
+        <v>3.76495463715115</v>
+      </c>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="26"/>
+      <c r="AA15" s="0" t="n">
+        <f aca="false">Y15+Z15</f>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="26" t="n">
+        <f aca="false">AA15/$P15</f>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="27" t="n">
+        <f aca="false">1000/100*Q15*($Q$41+$Q$47-$Q$49)-AA15</f>
         <v>116.953641804847</v>
       </c>
-      <c r="Z15" s="27" t="n">
-        <f aca="false">Y15-V15+Q15/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD15" s="26" t="n">
+        <f aca="false">AC15/$P15</f>
+        <v>3.78502999465506</v>
+      </c>
+      <c r="AE15" s="27" t="n">
+        <f aca="false">AC15+Q15/100*1000 *($Q$46+$Q$43)</f>
         <v>208.884125745539</v>
       </c>
-      <c r="AA15" s="26" t="n">
-        <f aca="false">-V15+($Q$45 + $Q$46)*1000*Q15/100</f>
+      <c r="AF15" s="26" t="n">
+        <f aca="false">AE15/$P15</f>
+        <v>6.76022284687333</v>
+      </c>
+      <c r="AG15" s="26" t="n">
+        <f aca="false">-AA15+($Q$45 + $Q$46)*1000*Q15/100</f>
         <v>95.7312093661401</v>
       </c>
-      <c r="AB15" s="26" t="n">
-        <f aca="false">AA15/P15/10</f>
+      <c r="AH15" s="26" t="n">
+        <f aca="false">AG15/P15/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC15" s="26" t="n">
-        <f aca="false">ROUND(AA15/P15 *100/1000, 2)</f>
+      <c r="AI15" s="26" t="n">
+        <f aca="false">ROUND(AG15/P15 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE15" s="26" t="n">
+      <c r="AK15" s="26" t="n">
         <f aca="false">-Q15*($Q$47)*10</f>
         <v>-50.9338378528962</v>
       </c>
-      <c r="AF15" s="26" t="n">
-        <f aca="false">AE15/P15/10</f>
+      <c r="AL15" s="26" t="n">
+        <f aca="false">AK15/P15/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI15" s="23" t="n">
+      <c r="AO15" s="23" t="n">
         <v>41.9</v>
       </c>
-      <c r="AN15" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO15" s="23" t="n">
+      <c r="AT15" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP15" s="23" t="n">
+      <c r="AV15" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="AQ15" s="23" t="n">
-        <f aca="false">AO15+AP15/100</f>
+      <c r="AW15" s="23" t="n">
+        <f aca="false">AU15+AV15/100</f>
         <v>0.9</v>
       </c>
-      <c r="AR15" s="23" t="n">
-        <f aca="false">AQ15*1000</f>
+      <c r="AX15" s="23" t="n">
+        <f aca="false">AW15*1000</f>
         <v>900</v>
       </c>
-      <c r="AU15" s="28" t="s">
+      <c r="BA15" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD15" s="28" t="n">
+        <f aca="false">BB15+BC15/10</f>
+        <v>0.5</v>
+      </c>
+      <c r="BE15" s="28" t="n">
+        <f aca="false">1000*BD15</f>
+        <v>500</v>
+      </c>
+      <c r="BG15" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="BH15" s="23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BI15" s="23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BJ15" s="23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BK15" s="23" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BL15" s="23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BM15" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO15" s="28" t="n">
+        <f aca="false">BH15*1000</f>
         <v>90</v>
       </c>
-      <c r="AV15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX15" s="28" t="n">
-        <f aca="false">AV15+AW15/10</f>
-        <v>0.5</v>
-      </c>
-      <c r="AY15" s="28" t="n">
-        <f aca="false">1000*AX15</f>
-        <v>500</v>
-      </c>
-      <c r="BA15" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="BB15" s="23" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BC15" s="23" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BD15" s="23" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BE15" s="23" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BF15" s="23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BG15" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="BI15" s="28" t="n">
-        <f aca="false">BB15*1000</f>
-        <v>90</v>
-      </c>
-      <c r="BK15" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="BL15" s="23" t="n">
+      <c r="BQ15" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="BR15" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="BM15" s="23" t="n">
+      <c r="BS15" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="BN15" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO15" s="23" t="n">
+      <c r="BT15" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU15" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="BQ15" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="BR15" s="23" t="n">
+      <c r="BW15" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="BX15" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="BS15" s="23" t="s">
-        <v>94</v>
-      </c>
+      <c r="BY15" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="XFA15" s="0"/>
+      <c r="XFB15" s="0"/>
+      <c r="XFC15" s="0"/>
+      <c r="XFD15" s="0"/>
     </row>
     <row r="16" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B16" s="23" t="n">
         <v>97</v>
@@ -5045,141 +5256,169 @@
         <v>980.1</v>
       </c>
       <c r="S16" s="26" t="n">
+        <f aca="false">R16/$P16</f>
+        <v>3.8374046130294</v>
+      </c>
+      <c r="T16" s="26" t="n">
         <f aca="false">R16/P16</f>
         <v>3.8374046130294</v>
       </c>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="0" t="n">
-        <f aca="false">T16+U16</f>
-        <v>0</v>
-      </c>
-      <c r="W16" s="27" t="n">
+      <c r="U16" s="27" t="n">
         <f aca="false">3/5*H16+M16/3</f>
         <v>222.666666666667</v>
       </c>
-      <c r="X16" s="27" t="n">
-        <f aca="false">R16-V16</f>
-        <v>980.1</v>
-      </c>
-      <c r="Y16" s="27" t="n">
-        <f aca="false">1000/100*Q16*($Q$41+$Q$47-$Q$49)-V16</f>
+      <c r="V16" s="26" t="n">
+        <f aca="false">U16/$P16</f>
+        <v>0.871811135429595</v>
+      </c>
+      <c r="W16" s="27" t="n">
+        <f aca="false">R16-U16</f>
+        <v>757.433333333333</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <f aca="false">W16/$P16</f>
+        <v>2.9655934775998</v>
+      </c>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="0" t="n">
+        <f aca="false">Y16+Z16</f>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="26" t="n">
+        <f aca="false">AA16/$P16</f>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="27" t="n">
+        <f aca="false">1000/100*Q16*($Q$41+$Q$47-$Q$49)-AA16</f>
         <v>966.723155844868</v>
       </c>
-      <c r="Z16" s="27" t="n">
-        <f aca="false">Y16-V16+Q16/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD16" s="26" t="n">
+        <f aca="false">AC16/$P16</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE16" s="27" t="n">
+        <f aca="false">AC16+Q16/100*1000 *($Q$46+$Q$43)</f>
         <v>1726.60823665138</v>
       </c>
-      <c r="AA16" s="26" t="n">
-        <f aca="false">-V16+($Q$45 + $Q$46)*1000*Q16/100</f>
+      <c r="AF16" s="26" t="n">
+        <f aca="false">AE16/$P16</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG16" s="26" t="n">
+        <f aca="false">-AA16+($Q$45 + $Q$46)*1000*Q16/100</f>
         <v>791.301368671407</v>
       </c>
-      <c r="AB16" s="26" t="n">
-        <f aca="false">AA16/P16/10</f>
+      <c r="AH16" s="26" t="n">
+        <f aca="false">AG16/P16/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC16" s="26" t="n">
-        <f aca="false">ROUND(AA16/P16 *100/1000, 2)</f>
+      <c r="AI16" s="26" t="n">
+        <f aca="false">ROUND(AG16/P16 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE16" s="26" t="n">
+      <c r="AK16" s="26" t="n">
         <f aca="false">-Q16*($Q$47)*10</f>
         <v>-421.012289216306</v>
       </c>
-      <c r="AF16" s="26" t="n">
-        <f aca="false">AE16/P16/10</f>
+      <c r="AL16" s="26" t="n">
+        <f aca="false">AK16/P16/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI16" s="23" t="n">
+      <c r="AO16" s="23" t="n">
         <v>281.7</v>
       </c>
-      <c r="AN16" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO16" s="23" t="n">
+      <c r="AT16" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP16" s="23" t="n">
+      <c r="AV16" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="AQ16" s="23" t="n">
-        <f aca="false">AO16+AP16/100</f>
+      <c r="AW16" s="23" t="n">
+        <f aca="false">AU16+AV16/100</f>
         <v>0.72</v>
       </c>
-      <c r="AR16" s="23" t="n">
-        <f aca="false">AQ16*1000</f>
+      <c r="AX16" s="23" t="n">
+        <f aca="false">AW16*1000</f>
         <v>720</v>
       </c>
-      <c r="AU16" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="AV16" s="23" t="n">
+      <c r="BA16" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="BB16" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AW16" s="23" t="n">
+      <c r="BC16" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AX16" s="28" t="n">
-        <f aca="false">AV16+AW16/10</f>
+      <c r="BD16" s="28" t="n">
+        <f aca="false">BB16+BC16/10</f>
         <v>2.9</v>
       </c>
-      <c r="AY16" s="28" t="n">
-        <f aca="false">1000*AX16</f>
+      <c r="BE16" s="28" t="n">
+        <f aca="false">1000*BD16</f>
         <v>2900</v>
       </c>
-      <c r="BA16" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB16" s="23" t="n">
+      <c r="BG16" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="BH16" s="23" t="n">
         <v>0.72</v>
       </c>
-      <c r="BC16" s="23" t="n">
+      <c r="BI16" s="23" t="n">
         <v>1.59</v>
       </c>
-      <c r="BD16" s="23" t="n">
+      <c r="BJ16" s="23" t="n">
         <v>1.6</v>
       </c>
-      <c r="BE16" s="23" t="n">
+      <c r="BK16" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="BF16" s="23" t="n">
+      <c r="BL16" s="23" t="n">
         <v>1.36</v>
       </c>
-      <c r="BG16" s="28" t="s">
+      <c r="BM16" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="BO16" s="28" t="n">
+        <f aca="false">BH16*1000</f>
+        <v>720</v>
+      </c>
+      <c r="BQ16" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR16" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS16" s="23" t="n">
+        <v>71</v>
+      </c>
+      <c r="BT16" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU16" s="23" t="n">
         <v>97</v>
       </c>
-      <c r="BI16" s="28" t="n">
-        <f aca="false">BB16*1000</f>
-        <v>720</v>
-      </c>
-      <c r="BK16" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="BL16" s="23" t="n">
-        <v>60</v>
-      </c>
-      <c r="BM16" s="23" t="n">
-        <v>71</v>
-      </c>
-      <c r="BN16" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO16" s="23" t="n">
-        <v>97</v>
-      </c>
-      <c r="BQ16" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="BR16" s="23" t="n">
+      <c r="BW16" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="BX16" s="23" t="n">
         <v>133</v>
       </c>
-      <c r="BS16" s="23" t="s">
-        <v>99</v>
-      </c>
+      <c r="BY16" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="XFA16" s="0"/>
+      <c r="XFB16" s="0"/>
+      <c r="XFC16" s="0"/>
+      <c r="XFD16" s="0"/>
     </row>
     <row r="17" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B17" s="23" t="n">
         <v>1084</v>
@@ -5243,147 +5482,175 @@
         <v>21891.6</v>
       </c>
       <c r="S17" s="26" t="n">
+        <f aca="false">R17/$P17</f>
+        <v>8.50263566325032</v>
+      </c>
+      <c r="T17" s="26" t="n">
         <f aca="false">R17/P17</f>
         <v>8.50263566325032</v>
       </c>
-      <c r="T17" s="26" t="n">
+      <c r="U17" s="27" t="n">
+        <f aca="false">3/5*H17+M17/3</f>
+        <v>6812.66666666667</v>
+      </c>
+      <c r="V17" s="26" t="n">
+        <f aca="false">U17/$P17</f>
+        <v>2.64602050840673</v>
+      </c>
+      <c r="W17" s="27" t="n">
+        <f aca="false">R17-U17</f>
+        <v>15078.9333333333</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <f aca="false">W17/$P17</f>
+        <v>5.8566151548436</v>
+      </c>
+      <c r="Y17" s="26" t="n">
         <f aca="false">B17</f>
         <v>1084</v>
       </c>
-      <c r="U17" s="26" t="n">
+      <c r="Z17" s="26" t="n">
         <f aca="false">F17</f>
         <v>3100</v>
       </c>
-      <c r="V17" s="0" t="n">
-        <f aca="false">T17+U17</f>
+      <c r="AA17" s="0" t="n">
+        <f aca="false">Y17+Z17</f>
         <v>4184</v>
       </c>
-      <c r="W17" s="27" t="n">
-        <f aca="false">3/5*H17+M17/3</f>
-        <v>6812.66666666667</v>
-      </c>
-      <c r="X17" s="27" t="n">
-        <f aca="false">R17-V17</f>
-        <v>17707.6</v>
-      </c>
-      <c r="Y17" s="27" t="n">
-        <f aca="false">1000/100*Q17*($Q$41+$Q$47-$Q$49)-V17</f>
+      <c r="AB17" s="26" t="n">
+        <f aca="false">AA17/$P17</f>
+        <v>1.62505379300916</v>
+      </c>
+      <c r="AC17" s="27" t="n">
+        <f aca="false">1000/100*Q17*($Q$41+$Q$47-$Q$49)-AA17</f>
         <v>5561.25616675849</v>
       </c>
-      <c r="Z17" s="27" t="n">
-        <f aca="false">Y17-V17+Q17/100*1000 *($Q$46+$Q$43)</f>
-        <v>9037.43760027922</v>
-      </c>
-      <c r="AA17" s="26" t="n">
-        <f aca="false">-V17+($Q$45 + $Q$46)*1000*Q17/100</f>
+      <c r="AD17" s="26" t="n">
+        <f aca="false">AC17/$P17</f>
+        <v>2.15997620164591</v>
+      </c>
+      <c r="AE17" s="27" t="n">
+        <f aca="false">AC17+Q17/100*1000 *($Q$46+$Q$43)</f>
+        <v>13221.4376002792</v>
+      </c>
+      <c r="AF17" s="26" t="n">
+        <f aca="false">AE17/$P17</f>
+        <v>5.13516905386417</v>
+      </c>
+      <c r="AG17" s="26" t="n">
+        <f aca="false">-AA17+($Q$45 + $Q$46)*1000*Q17/100</f>
         <v>3792.87993319044</v>
       </c>
-      <c r="AB17" s="26" t="n">
-        <f aca="false">AA17/P17/10</f>
+      <c r="AH17" s="26" t="n">
+        <f aca="false">AG17/P17/10</f>
         <v>0.147314386277712</v>
       </c>
-      <c r="AC17" s="26" t="n">
-        <f aca="false">ROUND(AA17/P17 *100/1000, 2)</f>
+      <c r="AI17" s="26" t="n">
+        <f aca="false">ROUND(AG17/P17 *100/1000, 2)</f>
         <v>0.15</v>
       </c>
-      <c r="AE17" s="26" t="n">
+      <c r="AK17" s="26" t="n">
         <f aca="false">-Q17*($Q$47)*10</f>
         <v>-4244.10296056332</v>
       </c>
-      <c r="AF17" s="26" t="n">
-        <f aca="false">AE17/P17/10</f>
+      <c r="AL17" s="26" t="n">
+        <f aca="false">AK17/P17/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI17" s="23" t="n">
+      <c r="AO17" s="23" t="n">
         <v>2991.1</v>
       </c>
-      <c r="AN17" s="23" t="s">
+      <c r="AT17" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU17" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV17" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AW17" s="23" t="n">
+        <f aca="false">AU17+AV17/100</f>
+        <v>5.38</v>
+      </c>
+      <c r="AX17" s="23" t="n">
+        <f aca="false">AW17*1000</f>
+        <v>5380</v>
+      </c>
+      <c r="BA17" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="BB17" s="23" t="n">
+        <v>62</v>
+      </c>
+      <c r="BC17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" s="28" t="n">
+        <f aca="false">BB17+BC17/10</f>
+        <v>62</v>
+      </c>
+      <c r="BE17" s="28" t="n">
+        <f aca="false">1000*BD17</f>
+        <v>62000</v>
+      </c>
+      <c r="BG17" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH17" s="23" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="BI17" s="23" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="BJ17" s="23" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="BK17" s="23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BL17" s="23" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BM17" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="BO17" s="28" t="n">
+        <f aca="false">BH17*1000</f>
+        <v>5380</v>
+      </c>
+      <c r="BQ17" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="BR17" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="BS17" s="23" t="n">
+        <v>797</v>
+      </c>
+      <c r="BT17" s="23" t="n">
+        <v>756</v>
+      </c>
+      <c r="BU17" s="23" t="n">
+        <v>1084</v>
+      </c>
+      <c r="BW17" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="BX17" s="23" t="n">
+        <v>1691</v>
+      </c>
+      <c r="BY17" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="AO17" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP17" s="23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ17" s="23" t="n">
-        <f aca="false">AO17+AP17/100</f>
-        <v>5.38</v>
-      </c>
-      <c r="AR17" s="23" t="n">
-        <f aca="false">AQ17*1000</f>
-        <v>5380</v>
-      </c>
-      <c r="AU17" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="AV17" s="23" t="n">
-        <v>62</v>
-      </c>
-      <c r="AW17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" s="28" t="n">
-        <f aca="false">AV17+AW17/10</f>
-        <v>62</v>
-      </c>
-      <c r="AY17" s="28" t="n">
-        <f aca="false">1000*AX17</f>
-        <v>62000</v>
-      </c>
-      <c r="BA17" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="BB17" s="23" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="BC17" s="23" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="BD17" s="23" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="BE17" s="23" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BF17" s="23" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="BG17" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI17" s="28" t="n">
-        <f aca="false">BB17*1000</f>
-        <v>5380</v>
-      </c>
-      <c r="BK17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="BL17" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="BM17" s="23" t="n">
-        <v>797</v>
-      </c>
-      <c r="BN17" s="23" t="n">
-        <v>756</v>
-      </c>
-      <c r="BO17" s="23" t="n">
-        <v>1084</v>
-      </c>
-      <c r="BQ17" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="BR17" s="23" t="n">
-        <v>1691</v>
-      </c>
-      <c r="BS17" s="23" t="s">
-        <v>106</v>
-      </c>
+      <c r="XFA17" s="0"/>
+      <c r="XFB17" s="0"/>
+      <c r="XFC17" s="0"/>
+      <c r="XFD17" s="0"/>
     </row>
     <row r="18" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B18" s="23" t="n">
         <v>978</v>
@@ -5447,141 +5714,169 @@
         <v>22491.2</v>
       </c>
       <c r="S18" s="26" t="n">
+        <f aca="false">R18/$P18</f>
+        <v>6.030623960651</v>
+      </c>
+      <c r="T18" s="26" t="n">
         <f aca="false">R18/P18</f>
         <v>6.030623960651</v>
       </c>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="0" t="n">
-        <f aca="false">T18+U18</f>
-        <v>0</v>
-      </c>
-      <c r="W18" s="27" t="n">
+      <c r="U18" s="27" t="n">
         <f aca="false">3/5*H18+M18/3</f>
         <v>7622.13333333333</v>
       </c>
-      <c r="X18" s="27" t="n">
-        <f aca="false">R18-V18</f>
-        <v>22491.2</v>
-      </c>
-      <c r="Y18" s="27" t="n">
-        <f aca="false">1000/100*Q18*($Q$41+$Q$47-$Q$49)-V18</f>
+      <c r="V18" s="26" t="n">
+        <f aca="false">U18/$P18</f>
+        <v>2.04374243754343</v>
+      </c>
+      <c r="W18" s="27" t="n">
+        <f aca="false">R18-U18</f>
+        <v>14869.0666666667</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <f aca="false">W18/$P18</f>
+        <v>3.98688152310758</v>
+      </c>
+      <c r="Y18" s="26"/>
+      <c r="Z18" s="26"/>
+      <c r="AA18" s="0" t="n">
+        <f aca="false">Y18+Z18</f>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="26" t="n">
+        <f aca="false">AA18/$P18</f>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="27" t="n">
+        <f aca="false">1000/100*Q18*($Q$41+$Q$47-$Q$49)-AA18</f>
         <v>14116.2617950061</v>
       </c>
-      <c r="Z18" s="27" t="n">
-        <f aca="false">Y18-V18+Q18/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD18" s="26" t="n">
+        <f aca="false">AC18/$P18</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE18" s="27" t="n">
+        <f aca="false">AC18+Q18/100*1000 *($Q$46+$Q$43)</f>
         <v>25212.2375869684</v>
       </c>
-      <c r="AA18" s="26" t="n">
-        <f aca="false">-V18+($Q$45 + $Q$46)*1000*Q18/100</f>
+      <c r="AF18" s="26" t="n">
+        <f aca="false">AE18/$P18</f>
+        <v>6.76022284687333</v>
+      </c>
+      <c r="AG18" s="26" t="n">
+        <f aca="false">-AA18+($Q$45 + $Q$46)*1000*Q18/100</f>
         <v>11554.7219608596</v>
       </c>
-      <c r="AB18" s="26" t="n">
-        <f aca="false">AA18/P18/10</f>
+      <c r="AH18" s="26" t="n">
+        <f aca="false">AG18/P18/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC18" s="26" t="n">
-        <f aca="false">ROUND(AA18/P18 *100/1000, 2)</f>
+      <c r="AI18" s="26" t="n">
+        <f aca="false">ROUND(AG18/P18 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE18" s="26" t="n">
+      <c r="AK18" s="26" t="n">
         <f aca="false">-Q18*($Q$47)*10</f>
         <v>-6147.69560195154</v>
       </c>
-      <c r="AF18" s="26" t="n">
-        <f aca="false">AE18/P18/10</f>
+      <c r="AL18" s="26" t="n">
+        <f aca="false">AK18/P18/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI18" s="23" t="n">
+      <c r="AO18" s="23" t="n">
         <v>4529.7</v>
       </c>
-      <c r="AN18" s="23" t="s">
+      <c r="AT18" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU18" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV18" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AW18" s="23" t="n">
+        <f aca="false">AU18+AV18/100</f>
+        <v>6.4</v>
+      </c>
+      <c r="AX18" s="23" t="n">
+        <f aca="false">AW18*1000</f>
+        <v>6400</v>
+      </c>
+      <c r="BA18" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB18" s="23" t="n">
+        <v>57</v>
+      </c>
+      <c r="BC18" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD18" s="28" t="n">
+        <f aca="false">BB18+BC18/10</f>
+        <v>57.7</v>
+      </c>
+      <c r="BE18" s="28" t="n">
+        <f aca="false">1000*BD18</f>
+        <v>57700</v>
+      </c>
+      <c r="BG18" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="BH18" s="23" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="BI18" s="23" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="BJ18" s="23" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="BK18" s="23" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BL18" s="23" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BM18" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="BO18" s="28" t="n">
+        <f aca="false">BH18*1000</f>
+        <v>6040</v>
+      </c>
+      <c r="BQ18" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="BR18" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="BS18" s="23" t="n">
+        <v>719</v>
+      </c>
+      <c r="BT18" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU18" s="23" t="n">
+        <v>978</v>
+      </c>
+      <c r="BW18" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="BX18" s="23" t="n">
+        <v>2700</v>
+      </c>
+      <c r="BY18" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="AO18" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP18" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AQ18" s="23" t="n">
-        <f aca="false">AO18+AP18/100</f>
-        <v>6.4</v>
-      </c>
-      <c r="AR18" s="23" t="n">
-        <f aca="false">AQ18*1000</f>
-        <v>6400</v>
-      </c>
-      <c r="AU18" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="AV18" s="23" t="n">
-        <v>57</v>
-      </c>
-      <c r="AW18" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX18" s="28" t="n">
-        <f aca="false">AV18+AW18/10</f>
-        <v>57.7</v>
-      </c>
-      <c r="AY18" s="28" t="n">
-        <f aca="false">1000*AX18</f>
-        <v>57700</v>
-      </c>
-      <c r="BA18" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="BB18" s="23" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="BC18" s="23" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="BD18" s="23" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="BE18" s="23" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BF18" s="23" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BG18" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI18" s="28" t="n">
-        <f aca="false">BB18*1000</f>
-        <v>6040</v>
-      </c>
-      <c r="BK18" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="BL18" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="BM18" s="23" t="n">
-        <v>719</v>
-      </c>
-      <c r="BN18" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO18" s="23" t="n">
-        <v>978</v>
-      </c>
-      <c r="BQ18" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="BR18" s="23" t="n">
-        <v>2700</v>
-      </c>
-      <c r="BS18" s="23" t="s">
-        <v>113</v>
-      </c>
+      <c r="XFA18" s="0"/>
+      <c r="XFB18" s="0"/>
+      <c r="XFC18" s="0"/>
+      <c r="XFD18" s="0"/>
     </row>
     <row r="19" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B19" s="23" t="n">
         <v>91</v>
@@ -5645,144 +5940,172 @@
         <v>1574.3</v>
       </c>
       <c r="S19" s="26" t="n">
+        <f aca="false">R19/$P19</f>
+        <v>8.70351225391279</v>
+      </c>
+      <c r="T19" s="26" t="n">
         <f aca="false">R19/P19</f>
         <v>8.70351225391279</v>
       </c>
-      <c r="T19" s="26"/>
-      <c r="U19" s="31" t="n">
+      <c r="U19" s="27" t="n">
+        <f aca="false">3/5*H19+M19/3</f>
+        <v>356.4</v>
+      </c>
+      <c r="V19" s="26" t="n">
+        <f aca="false">U19/$P19</f>
+        <v>1.97035620103825</v>
+      </c>
+      <c r="W19" s="27" t="n">
+        <f aca="false">R19-U19</f>
+        <v>1217.9</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <f aca="false">W19/$P19</f>
+        <v>6.73315605287454</v>
+      </c>
+      <c r="Y19" s="26"/>
+      <c r="Z19" s="31" t="n">
         <f aca="false">F19</f>
         <v>22.7</v>
       </c>
-      <c r="V19" s="0" t="n">
-        <f aca="false">T19+U19</f>
+      <c r="AA19" s="0" t="n">
+        <f aca="false">Y19+Z19</f>
         <v>22.7</v>
       </c>
-      <c r="W19" s="27" t="n">
-        <f aca="false">3/5*H19+M19/3</f>
-        <v>356.4</v>
-      </c>
-      <c r="X19" s="27" t="n">
-        <f aca="false">R19-V19</f>
-        <v>1551.6</v>
-      </c>
-      <c r="Y19" s="27" t="n">
-        <f aca="false">1000/100*Q19*($Q$41+$Q$47-$Q$49)-V19</f>
+      <c r="AB19" s="26" t="n">
+        <f aca="false">AA19/$P19</f>
+        <v>0.125496873635152</v>
+      </c>
+      <c r="AC19" s="27" t="n">
+        <f aca="false">1000/100*Q19*($Q$41+$Q$47-$Q$49)-AA19</f>
         <v>661.940010463206</v>
       </c>
-      <c r="Z19" s="27" t="n">
-        <f aca="false">Y19-V19+Q19/100*1000 *($Q$46+$Q$43)</f>
-        <v>1177.3958687653</v>
-      </c>
-      <c r="AA19" s="26" t="n">
-        <f aca="false">-U19+($Q$45 + $Q$46)*1000*Q19/100</f>
+      <c r="AD19" s="26" t="n">
+        <f aca="false">AC19/$P19</f>
+        <v>3.65953312101993</v>
+      </c>
+      <c r="AE19" s="27" t="n">
+        <f aca="false">AC19+Q19/100*1000 *($Q$46+$Q$43)</f>
+        <v>1200.0958687653</v>
+      </c>
+      <c r="AF19" s="26" t="n">
+        <f aca="false">AE19/$P19</f>
+        <v>6.63472597323821</v>
+      </c>
+      <c r="AG19" s="26" t="n">
+        <f aca="false">-Z19+($Q$45 + $Q$46)*1000*Q19/100</f>
         <v>537.70509017628</v>
       </c>
-      <c r="AB19" s="26" t="n">
-        <f aca="false">AA19/P19/10</f>
+      <c r="AH19" s="26" t="n">
+        <f aca="false">AG19/P19/10</f>
         <v>0.297270078215114</v>
       </c>
-      <c r="AC19" s="26" t="n">
-        <f aca="false">ROUND(AA19/P19 *100/1000, 2)</f>
+      <c r="AI19" s="26" t="n">
+        <f aca="false">ROUND(AG19/P19 *100/1000, 2)</f>
         <v>0.3</v>
       </c>
-      <c r="AE19" s="26" t="n">
+      <c r="AK19" s="26" t="n">
         <f aca="false">-Q19*($Q$47)*10</f>
         <v>-298.163808688621</v>
       </c>
-      <c r="AF19" s="26" t="n">
-        <f aca="false">AE19/P19/10</f>
+      <c r="AL19" s="26" t="n">
+        <f aca="false">AK19/P19/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI19" s="23" t="n">
+      <c r="AO19" s="23" t="n">
         <v>248.4</v>
       </c>
-      <c r="AN19" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO19" s="23" t="n">
+      <c r="AT19" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="AU19" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AP19" s="23" t="n">
+      <c r="AV19" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="AQ19" s="23" t="n">
-        <f aca="false">AO19+AP19/100</f>
+      <c r="AW19" s="23" t="n">
+        <f aca="false">AU19+AV19/100</f>
         <v>2.54</v>
       </c>
-      <c r="AR19" s="23" t="n">
-        <f aca="false">AQ19*1000</f>
+      <c r="AX19" s="23" t="n">
+        <f aca="false">AW19*1000</f>
         <v>2540</v>
       </c>
-      <c r="AU19" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV19" s="23" t="n">
+      <c r="BA19" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="BB19" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AW19" s="23" t="n">
+      <c r="BC19" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AX19" s="28" t="n">
-        <f aca="false">AV19+AW19/10</f>
+      <c r="BD19" s="28" t="n">
+        <f aca="false">BB19+BC19/10</f>
         <v>6.3</v>
       </c>
-      <c r="AY19" s="28" t="n">
-        <f aca="false">1000*AX19</f>
+      <c r="BE19" s="28" t="n">
+        <f aca="false">1000*BD19</f>
         <v>6300</v>
       </c>
-      <c r="BA19" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="BB19" s="23" t="n">
+      <c r="BG19" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="BH19" s="23" t="n">
         <v>2.54</v>
       </c>
-      <c r="BC19" s="23" t="n">
+      <c r="BI19" s="23" t="n">
         <v>5.64</v>
       </c>
-      <c r="BD19" s="23" t="n">
+      <c r="BJ19" s="23" t="n">
         <v>1.3</v>
       </c>
-      <c r="BE19" s="23" t="n">
+      <c r="BK19" s="23" t="n">
         <v>4.34</v>
       </c>
-      <c r="BF19" s="23" t="n">
+      <c r="BL19" s="23" t="n">
         <v>5.88</v>
       </c>
-      <c r="BG19" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI19" s="28" t="n">
-        <f aca="false">BB19*1000</f>
+      <c r="BM19" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="BO19" s="28" t="n">
+        <f aca="false">BH19*1000</f>
         <v>2540</v>
       </c>
-      <c r="BK19" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="BL19" s="23" t="n">
+      <c r="BQ19" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="BR19" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="BM19" s="23" t="n">
+      <c r="BS19" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="BN19" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO19" s="23" t="n">
+      <c r="BT19" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU19" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="BQ19" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="BR19" s="23" t="n">
+      <c r="BW19" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="BX19" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="BS19" s="23" t="s">
-        <v>119</v>
-      </c>
+      <c r="BY19" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="XFA19" s="0"/>
+      <c r="XFB19" s="0"/>
+      <c r="XFC19" s="0"/>
+      <c r="XFD19" s="0"/>
     </row>
     <row r="20" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B20" s="23" t="n">
         <v>140</v>
@@ -5846,141 +6169,169 @@
         <v>869.8</v>
       </c>
       <c r="S20" s="26" t="n">
+        <f aca="false">R20/$P20</f>
+        <v>5.84056297171712</v>
+      </c>
+      <c r="T20" s="26" t="n">
         <f aca="false">R20/P20</f>
         <v>5.84056297171712</v>
       </c>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="0" t="n">
-        <f aca="false">T20+U20</f>
-        <v>0</v>
-      </c>
-      <c r="W20" s="27" t="n">
+      <c r="U20" s="27" t="n">
         <f aca="false">3/5*H20+M20/3</f>
         <v>238.133333333333</v>
       </c>
-      <c r="X20" s="27" t="n">
-        <f aca="false">R20-V20</f>
-        <v>869.8</v>
-      </c>
-      <c r="Y20" s="27" t="n">
-        <f aca="false">1000/100*Q20*($Q$41+$Q$47-$Q$49)-V20</f>
+      <c r="V20" s="26" t="n">
+        <f aca="false">U20/$P20</f>
+        <v>1.59902590135461</v>
+      </c>
+      <c r="W20" s="27" t="n">
+        <f aca="false">R20-U20</f>
+        <v>631.666666666667</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <f aca="false">W20/$P20</f>
+        <v>4.24153707036251</v>
+      </c>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="26"/>
+      <c r="AA20" s="0" t="n">
+        <f aca="false">Y20+Z20</f>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="26" t="n">
+        <f aca="false">AA20/$P20</f>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="27" t="n">
+        <f aca="false">1000/100*Q20*($Q$41+$Q$47-$Q$49)-AA20</f>
         <v>563.681806924014</v>
       </c>
-      <c r="Z20" s="27" t="n">
-        <f aca="false">Y20-V20+Q20/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD20" s="26" t="n">
+        <f aca="false">AC20/$P20</f>
+        <v>3.78502999465508</v>
+      </c>
+      <c r="AE20" s="27" t="n">
+        <f aca="false">AC20+Q20/100*1000 *($Q$46+$Q$43)</f>
         <v>1006.75942724777</v>
       </c>
-      <c r="AA20" s="26" t="n">
-        <f aca="false">-V20+($Q$45 + $Q$46)*1000*Q20/100</f>
+      <c r="AF20" s="26" t="n">
+        <f aca="false">AE20/$P20</f>
+        <v>6.76022284687336</v>
+      </c>
+      <c r="AG20" s="26" t="n">
+        <f aca="false">-AA20+($Q$45 + $Q$46)*1000*Q20/100</f>
         <v>461.395987690318</v>
       </c>
-      <c r="AB20" s="26" t="n">
-        <f aca="false">AA20/P20/10</f>
+      <c r="AH20" s="26" t="n">
+        <f aca="false">AG20/P20/10</f>
         <v>0.309819765578629</v>
       </c>
-      <c r="AC20" s="26" t="n">
-        <f aca="false">ROUND(AA20/P20 *100/1000, 2)</f>
+      <c r="AI20" s="26" t="n">
+        <f aca="false">ROUND(AG20/P20 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE20" s="26" t="n">
+      <c r="AK20" s="26" t="n">
         <f aca="false">-Q20*($Q$47)*10</f>
         <v>-245.48596616087</v>
       </c>
-      <c r="AF20" s="26" t="n">
-        <f aca="false">AE20/P20/10</f>
+      <c r="AL20" s="26" t="n">
+        <f aca="false">AK20/P20/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI20" s="23" t="n">
+      <c r="AO20" s="23" t="n">
         <v>218.8</v>
       </c>
-      <c r="AN20" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="AO20" s="23" t="n">
+      <c r="AT20" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="AU20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP20" s="23" t="n">
+      <c r="AV20" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="AQ20" s="23" t="n">
-        <f aca="false">AO20+AP20/100</f>
+      <c r="AW20" s="23" t="n">
+        <f aca="false">AU20+AV20/100</f>
         <v>0.37</v>
       </c>
-      <c r="AR20" s="23" t="n">
-        <f aca="false">AQ20*1000</f>
+      <c r="AX20" s="23" t="n">
+        <f aca="false">AW20*1000</f>
         <v>370</v>
       </c>
-      <c r="AU20" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="AV20" s="23" t="n">
+      <c r="BA20" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="BB20" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AW20" s="23" t="n">
+      <c r="BC20" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="AX20" s="28" t="n">
-        <f aca="false">AV20+AW20/10</f>
+      <c r="BD20" s="28" t="n">
+        <f aca="false">BB20+BC20/10</f>
         <v>2.5</v>
       </c>
-      <c r="AY20" s="28" t="n">
-        <f aca="false">1000*AX20</f>
+      <c r="BE20" s="28" t="n">
+        <f aca="false">1000*BD20</f>
         <v>2500</v>
       </c>
-      <c r="BA20" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="BB20" s="23" t="n">
+      <c r="BG20" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="BH20" s="23" t="n">
         <v>0.37</v>
       </c>
-      <c r="BC20" s="23" t="n">
+      <c r="BI20" s="23" t="n">
         <v>0.82</v>
       </c>
-      <c r="BD20" s="23" t="n">
+      <c r="BJ20" s="23" t="n">
         <v>1.18</v>
       </c>
-      <c r="BE20" s="23" t="n">
+      <c r="BK20" s="23" t="n">
         <v>0.7</v>
       </c>
-      <c r="BF20" s="23" t="n">
+      <c r="BL20" s="23" t="n">
         <v>0.95</v>
       </c>
-      <c r="BG20" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="BI20" s="28" t="n">
-        <f aca="false">BB20*1000</f>
+      <c r="BM20" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO20" s="28" t="n">
+        <f aca="false">BH20*1000</f>
         <v>370</v>
       </c>
-      <c r="BK20" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="BL20" s="23" t="n">
+      <c r="BQ20" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="BR20" s="23" t="n">
         <v>51</v>
       </c>
-      <c r="BM20" s="23" t="n">
+      <c r="BS20" s="23" t="n">
         <v>103</v>
       </c>
-      <c r="BN20" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO20" s="23" t="n">
+      <c r="BT20" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU20" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="BQ20" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="BR20" s="23" t="n">
+      <c r="BW20" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="BX20" s="23" t="n">
         <v>113</v>
       </c>
-      <c r="BS20" s="23" t="s">
-        <v>124</v>
-      </c>
+      <c r="BY20" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="XFA20" s="0"/>
+      <c r="XFB20" s="0"/>
+      <c r="XFC20" s="0"/>
+      <c r="XFD20" s="0"/>
     </row>
     <row r="21" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B21" s="23" t="n">
         <v>97</v>
@@ -6044,147 +6395,175 @@
         <v>1506</v>
       </c>
       <c r="S21" s="26" t="n">
+        <f aca="false">R21/$P21</f>
+        <v>4.65560573882237</v>
+      </c>
+      <c r="T21" s="26" t="n">
         <f aca="false">R21/P21</f>
         <v>4.65560573882237</v>
       </c>
-      <c r="T21" s="26"/>
-      <c r="U21" s="31" t="n">
+      <c r="U21" s="27" t="n">
+        <f aca="false">3/5*H21+M21/3</f>
+        <v>370.866666666667</v>
+      </c>
+      <c r="V21" s="26" t="n">
+        <f aca="false">U21/$P21</f>
+        <v>1.14648670761704</v>
+      </c>
+      <c r="W21" s="27" t="n">
+        <f aca="false">R21-U21</f>
+        <v>1135.13333333333</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <f aca="false">W21/$P21</f>
+        <v>3.50911903120534</v>
+      </c>
+      <c r="Y21" s="26"/>
+      <c r="Z21" s="31" t="n">
         <f aca="false">F21</f>
         <v>241.4</v>
       </c>
-      <c r="V21" s="0" t="n">
-        <f aca="false">T21+U21</f>
+      <c r="AA21" s="0" t="n">
+        <f aca="false">Y21+Z21</f>
         <v>241.4</v>
       </c>
-      <c r="W21" s="27" t="n">
-        <f aca="false">3/5*H21+M21/3</f>
-        <v>370.866666666667</v>
-      </c>
-      <c r="X21" s="27" t="n">
-        <f aca="false">R21-V21</f>
-        <v>1264.6</v>
-      </c>
-      <c r="Y21" s="27" t="n">
-        <f aca="false">1000/100*Q21*($Q$41+$Q$47-$Q$49)-V21</f>
+      <c r="AB21" s="26" t="n">
+        <f aca="false">AA21/$P21</f>
+        <v>0.746257121747491</v>
+      </c>
+      <c r="AC21" s="27" t="n">
+        <f aca="false">1000/100*Q21*($Q$41+$Q$47-$Q$49)-AA21</f>
         <v>982.985287701017</v>
       </c>
-      <c r="Z21" s="27" t="n">
-        <f aca="false">Y21-V21+Q21/100*1000 *($Q$46+$Q$43)</f>
-        <v>1704.00364672943</v>
-      </c>
-      <c r="AA21" s="26" t="n">
-        <f aca="false">-U21+($Q$45 + $Q$46)*1000*Q21/100</f>
+      <c r="AD21" s="26" t="n">
+        <f aca="false">AC21/$P21</f>
+        <v>3.03877287290758</v>
+      </c>
+      <c r="AE21" s="27" t="n">
+        <f aca="false">AC21+Q21/100*1000 *($Q$46+$Q$43)</f>
+        <v>1945.40364672943</v>
+      </c>
+      <c r="AF21" s="26" t="n">
+        <f aca="false">AE21/$P21</f>
+        <v>6.01396572512585</v>
+      </c>
+      <c r="AG21" s="26" t="n">
+        <f aca="false">-Z21+($Q$45 + $Q$46)*1000*Q21/100</f>
         <v>760.808075891402</v>
       </c>
-      <c r="AB21" s="26" t="n">
-        <f aca="false">AA21/P21/10</f>
+      <c r="AH21" s="26" t="n">
+        <f aca="false">AG21/P21/10</f>
         <v>0.235194053403879</v>
       </c>
-      <c r="AC21" s="26" t="n">
-        <f aca="false">ROUND(AA21/P21 *100/1000, 2)</f>
+      <c r="AI21" s="26" t="n">
+        <f aca="false">ROUND(AG21/P21 *100/1000, 2)</f>
         <v>0.24</v>
       </c>
-      <c r="AE21" s="26" t="n">
+      <c r="AK21" s="26" t="n">
         <f aca="false">-Q21*($Q$47)*10</f>
         <v>-533.225308343076</v>
       </c>
-      <c r="AF21" s="26" t="n">
-        <f aca="false">AE21/P21/10</f>
+      <c r="AL21" s="26" t="n">
+        <f aca="false">AK21/P21/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI21" s="23" t="n">
+      <c r="AO21" s="23" t="n">
         <v>602.4</v>
       </c>
-      <c r="AN21" s="23" t="s">
+      <c r="AT21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AU21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="23" t="n">
+        <v>94</v>
+      </c>
+      <c r="AW21" s="23" t="n">
+        <f aca="false">AU21+AV21/100</f>
+        <v>0.94</v>
+      </c>
+      <c r="AX21" s="23" t="n">
+        <f aca="false">AW21*1000</f>
+        <v>940</v>
+      </c>
+      <c r="BA21" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="BB21" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC21" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD21" s="28" t="n">
+        <f aca="false">BB21+BC21/10</f>
+        <v>3.8</v>
+      </c>
+      <c r="BE21" s="28" t="n">
+        <f aca="false">1000*BD21</f>
+        <v>3800</v>
+      </c>
+      <c r="BF21" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG21" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="BH21" s="23" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="BI21" s="23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ21" s="23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK21" s="23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BL21" s="23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BM21" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="BO21" s="28" t="n">
+        <f aca="false">BH21*1000</f>
+        <v>940</v>
+      </c>
+      <c r="BQ21" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="BR21" s="23" t="n">
+        <v>72</v>
+      </c>
+      <c r="BS21" s="23" t="n">
+        <v>71</v>
+      </c>
+      <c r="BT21" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU21" s="23" t="n">
+        <v>97</v>
+      </c>
+      <c r="BW21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="BX21" s="23" t="n">
+        <v>160</v>
+      </c>
+      <c r="BY21" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="AO21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" s="23" t="n">
-        <v>94</v>
-      </c>
-      <c r="AQ21" s="23" t="n">
-        <f aca="false">AO21+AP21/100</f>
-        <v>0.94</v>
-      </c>
-      <c r="AR21" s="23" t="n">
-        <f aca="false">AQ21*1000</f>
-        <v>940</v>
-      </c>
-      <c r="AU21" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="AV21" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW21" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX21" s="28" t="n">
-        <f aca="false">AV21+AW21/10</f>
-        <v>3.8</v>
-      </c>
-      <c r="AY21" s="28" t="n">
-        <f aca="false">1000*AX21</f>
-        <v>3800</v>
-      </c>
-      <c r="AZ21" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="BA21" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="BB21" s="23" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="BC21" s="23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD21" s="23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BE21" s="23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BF21" s="23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BG21" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="BI21" s="28" t="n">
-        <f aca="false">BB21*1000</f>
-        <v>940</v>
-      </c>
-      <c r="BK21" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="BL21" s="23" t="n">
-        <v>72</v>
-      </c>
-      <c r="BM21" s="23" t="n">
-        <v>71</v>
-      </c>
-      <c r="BN21" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO21" s="23" t="n">
-        <v>97</v>
-      </c>
-      <c r="BQ21" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="BR21" s="23" t="n">
-        <v>160</v>
-      </c>
-      <c r="BS21" s="23" t="s">
-        <v>131</v>
-      </c>
+      <c r="XFA21" s="0"/>
+      <c r="XFB21" s="0"/>
+      <c r="XFC21" s="0"/>
+      <c r="XFD21" s="0"/>
     </row>
     <row r="22" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B22" s="23" t="n">
         <v>467</v>
@@ -6248,147 +6627,175 @@
         <v>13413.2</v>
       </c>
       <c r="S22" s="26" t="n">
+        <f aca="false">R22/$P22</f>
+        <v>7.39434833901146</v>
+      </c>
+      <c r="T22" s="26" t="n">
         <f aca="false">R22/P22</f>
         <v>7.39434833901146</v>
       </c>
-      <c r="T22" s="26" t="n">
+      <c r="U22" s="27" t="n">
+        <f aca="false">3/5*H22+M22/3</f>
+        <v>4132.13333333333</v>
+      </c>
+      <c r="V22" s="26" t="n">
+        <f aca="false">U22/$P22</f>
+        <v>2.2779376472361</v>
+      </c>
+      <c r="W22" s="27" t="n">
+        <f aca="false">R22-U22</f>
+        <v>9281.06666666667</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <f aca="false">W22/$P22</f>
+        <v>5.11641069177536</v>
+      </c>
+      <c r="Y22" s="26" t="n">
         <f aca="false">B22</f>
         <v>467</v>
       </c>
-      <c r="U22" s="26" t="n">
+      <c r="Z22" s="26" t="n">
         <f aca="false">F22</f>
         <v>544.5</v>
       </c>
-      <c r="V22" s="0" t="n">
-        <f aca="false">T22+U22</f>
+      <c r="AA22" s="0" t="n">
+        <f aca="false">Y22+Z22</f>
         <v>1011.5</v>
       </c>
-      <c r="W22" s="27" t="n">
-        <f aca="false">3/5*H22+M22/3</f>
-        <v>4132.13333333333</v>
-      </c>
-      <c r="X22" s="27" t="n">
-        <f aca="false">R22-V22</f>
-        <v>12401.7</v>
-      </c>
-      <c r="Y22" s="27" t="n">
-        <f aca="false">1000/100*Q22*($Q$41+$Q$47-$Q$49)-V22</f>
+      <c r="AB22" s="26" t="n">
+        <f aca="false">AA22/$P22</f>
+        <v>0.557613645133904</v>
+      </c>
+      <c r="AC22" s="27" t="n">
+        <f aca="false">1000/100*Q22*($Q$41+$Q$47-$Q$49)-AA22</f>
         <v>5854.46870970442</v>
       </c>
-      <c r="Z22" s="27" t="n">
-        <f aca="false">Y22-V22+Q22/100*1000 *($Q$46+$Q$43)</f>
-        <v>10239.9090397713</v>
-      </c>
-      <c r="AA22" s="26" t="n">
-        <f aca="false">-V22+($Q$45 + $Q$46)*1000*Q22/100</f>
+      <c r="AD22" s="26" t="n">
+        <f aca="false">AC22/$P22</f>
+        <v>3.22741634952117</v>
+      </c>
+      <c r="AE22" s="27" t="n">
+        <f aca="false">AC22+Q22/100*1000 *($Q$46+$Q$43)</f>
+        <v>11251.4090397713</v>
+      </c>
+      <c r="AF22" s="26" t="n">
+        <f aca="false">AE22/$P22</f>
+        <v>6.20260920173945</v>
+      </c>
+      <c r="AG22" s="26" t="n">
+        <f aca="false">-AA22+($Q$45 + $Q$46)*1000*Q22/100</f>
         <v>4608.56858364321</v>
       </c>
-      <c r="AB22" s="26" t="n">
-        <f aca="false">AA22/P22/10</f>
+      <c r="AH22" s="26" t="n">
+        <f aca="false">AG22/P22/10</f>
         <v>0.254058401065238</v>
       </c>
-      <c r="AC22" s="26" t="n">
-        <f aca="false">ROUND(AA22/P22 *100/1000, 2)</f>
+      <c r="AI22" s="26" t="n">
+        <f aca="false">ROUND(AG22/P22 *100/1000, 2)</f>
         <v>0.25</v>
       </c>
-      <c r="AE22" s="26" t="n">
+      <c r="AK22" s="26" t="n">
         <f aca="false">-Q22*($Q$47)*10</f>
         <v>-2990.1603025469</v>
       </c>
-      <c r="AF22" s="26" t="n">
-        <f aca="false">AE22/P22/10</f>
+      <c r="AL22" s="26" t="n">
+        <f aca="false">AK22/P22/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI22" s="23" t="n">
+      <c r="AO22" s="23" t="n">
         <v>2258</v>
       </c>
-      <c r="AN22" s="23" t="s">
+      <c r="AT22" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="AU22" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW22" s="23" t="n">
+        <f aca="false">AU22+AV22/100</f>
+        <v>7.11</v>
+      </c>
+      <c r="AX22" s="23" t="n">
+        <f aca="false">AW22*1000</f>
+        <v>7110</v>
+      </c>
+      <c r="BA22" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="BB22" s="23" t="n">
+        <v>56</v>
+      </c>
+      <c r="BC22" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD22" s="28" t="n">
+        <f aca="false">BB22+BC22/10</f>
+        <v>56.5</v>
+      </c>
+      <c r="BE22" s="28" t="n">
+        <f aca="false">1000*BD22</f>
+        <v>56500</v>
+      </c>
+      <c r="BG22" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH22" s="23" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="BI22" s="23" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="BJ22" s="23" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="BK22" s="23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BL22" s="23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM22" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="BO22" s="28" t="n">
+        <f aca="false">BH22*1000</f>
+        <v>7110</v>
+      </c>
+      <c r="BQ22" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="BR22" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="BS22" s="23" t="n">
+        <v>343</v>
+      </c>
+      <c r="BT22" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="BU22" s="23" t="n">
+        <v>467</v>
+      </c>
+      <c r="BW22" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX22" s="23" t="n">
+        <v>891</v>
+      </c>
+      <c r="BY22" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="AO22" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP22" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ22" s="23" t="n">
-        <f aca="false">AO22+AP22/100</f>
-        <v>7.11</v>
-      </c>
-      <c r="AR22" s="23" t="n">
-        <f aca="false">AQ22*1000</f>
-        <v>7110</v>
-      </c>
-      <c r="AU22" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="AV22" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="AW22" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX22" s="28" t="n">
-        <f aca="false">AV22+AW22/10</f>
-        <v>56.5</v>
-      </c>
-      <c r="AY22" s="28" t="n">
-        <f aca="false">1000*AX22</f>
-        <v>56500</v>
-      </c>
-      <c r="BA22" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="BB22" s="23" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="BC22" s="23" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="BD22" s="23" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="BE22" s="23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BF22" s="23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BG22" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="BI22" s="28" t="n">
-        <f aca="false">BB22*1000</f>
-        <v>7110</v>
-      </c>
-      <c r="BK22" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="BL22" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="BM22" s="23" t="n">
-        <v>343</v>
-      </c>
-      <c r="BN22" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="BO22" s="23" t="n">
-        <v>467</v>
-      </c>
-      <c r="BQ22" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="BR22" s="23" t="n">
-        <v>891</v>
-      </c>
-      <c r="BS22" s="23" t="s">
-        <v>138</v>
-      </c>
+      <c r="XFA22" s="0"/>
+      <c r="XFB22" s="0"/>
+      <c r="XFC22" s="0"/>
+      <c r="XFD22" s="0"/>
     </row>
     <row r="23" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B23" s="23" t="n">
         <v>27</v>
@@ -6452,141 +6859,169 @@
         <v>165.6</v>
       </c>
       <c r="S23" s="26" t="n">
+        <f aca="false">R23/$P23</f>
+        <v>5.00680272108844</v>
+      </c>
+      <c r="T23" s="26" t="n">
         <f aca="false">R23/P23</f>
         <v>5.00680272108844</v>
       </c>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="0" t="n">
-        <f aca="false">T23+U23</f>
-        <v>0</v>
-      </c>
-      <c r="W23" s="27" t="n">
+      <c r="U23" s="27" t="n">
         <f aca="false">3/5*H23+M23/3</f>
         <v>34.6666666666667</v>
       </c>
-      <c r="X23" s="27" t="n">
-        <f aca="false">R23-V23</f>
-        <v>165.6</v>
-      </c>
-      <c r="Y23" s="27" t="n">
-        <f aca="false">1000/100*Q23*($Q$41+$Q$47-$Q$49)-V23</f>
+      <c r="V23" s="26" t="n">
+        <f aca="false">U23/$P23</f>
+        <v>1.04812295288486</v>
+      </c>
+      <c r="W23" s="27" t="n">
+        <f aca="false">R23-U23</f>
+        <v>130.933333333333</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <f aca="false">W23/$P23</f>
+        <v>3.95867976820358</v>
+      </c>
+      <c r="Y23" s="26"/>
+      <c r="Z23" s="26"/>
+      <c r="AA23" s="0" t="n">
+        <f aca="false">Y23+Z23</f>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="26" t="n">
+        <f aca="false">AA23/$P23</f>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="27" t="n">
+        <f aca="false">1000/100*Q23*($Q$41+$Q$47-$Q$49)-AA23</f>
         <v>125.189867073216</v>
       </c>
-      <c r="Z23" s="27" t="n">
-        <f aca="false">Y23-V23+Q23/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD23" s="26" t="n">
+        <f aca="false">AC23/$P23</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE23" s="27" t="n">
+        <f aca="false">AC23+Q23/100*1000 *($Q$46+$Q$43)</f>
         <v>223.594370660335</v>
       </c>
-      <c r="AA23" s="26" t="n">
-        <f aca="false">-V23+($Q$45 + $Q$46)*1000*Q23/100</f>
+      <c r="AF23" s="26" t="n">
+        <f aca="false">AE23/$P23</f>
+        <v>6.76022284687333</v>
+      </c>
+      <c r="AG23" s="26" t="n">
+        <f aca="false">-AA23+($Q$45 + $Q$46)*1000*Q23/100</f>
         <v>102.472887465131</v>
       </c>
-      <c r="AB23" s="26" t="n">
-        <f aca="false">AA23/P23/10</f>
+      <c r="AH23" s="26" t="n">
+        <f aca="false">AG23/P23/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC23" s="26" t="n">
-        <f aca="false">ROUND(AA23/P23 *100/1000, 2)</f>
+      <c r="AI23" s="26" t="n">
+        <f aca="false">ROUND(AG23/P23 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE23" s="26" t="n">
+      <c r="AK23" s="26" t="n">
         <f aca="false">-Q23*($Q$47)*10</f>
         <v>-54.5207510594045</v>
       </c>
-      <c r="AF23" s="26" t="n">
-        <f aca="false">AE23/P23/10</f>
+      <c r="AL23" s="26" t="n">
+        <f aca="false">AK23/P23/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI23" s="23" t="n">
+      <c r="AO23" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="AN23" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="AO23" s="23" t="n">
+      <c r="AT23" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP23" s="23" t="n">
+      <c r="AV23" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="AQ23" s="23" t="n">
-        <f aca="false">AO23+AP23/100</f>
+      <c r="AW23" s="23" t="n">
+        <f aca="false">AU23+AV23/100</f>
         <v>0.18</v>
       </c>
-      <c r="AR23" s="23" t="n">
-        <f aca="false">AQ23*1000</f>
+      <c r="AX23" s="23" t="n">
+        <f aca="false">AW23*1000</f>
         <v>180</v>
       </c>
-      <c r="AU23" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="AV23" s="23" t="n">
+      <c r="BA23" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="BB23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AW23" s="23" t="n">
+      <c r="BC23" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="AX23" s="28" t="n">
-        <f aca="false">AV23+AW23/10</f>
+      <c r="BD23" s="28" t="n">
+        <f aca="false">BB23+BC23/10</f>
         <v>0.5</v>
       </c>
-      <c r="AY23" s="28" t="n">
-        <f aca="false">1000*AX23</f>
+      <c r="BE23" s="28" t="n">
+        <f aca="false">1000*BD23</f>
         <v>500</v>
       </c>
-      <c r="BA23" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="BB23" s="23" t="n">
+      <c r="BG23" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="BH23" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="BC23" s="23" t="n">
+      <c r="BI23" s="23" t="n">
         <v>0.4</v>
       </c>
-      <c r="BD23" s="23" t="n">
+      <c r="BJ23" s="23" t="n">
         <v>0.24</v>
       </c>
-      <c r="BE23" s="23" t="n">
+      <c r="BK23" s="23" t="n">
         <v>1.67</v>
       </c>
-      <c r="BF23" s="23" t="n">
+      <c r="BL23" s="23" t="n">
         <v>2.26</v>
       </c>
-      <c r="BG23" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="BI23" s="28" t="n">
-        <f aca="false">BB23*1000</f>
+      <c r="BM23" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="BO23" s="28" t="n">
+        <f aca="false">BH23*1000</f>
         <v>180</v>
       </c>
-      <c r="BK23" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="BL23" s="23" t="n">
+      <c r="BQ23" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR23" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="BM23" s="23" t="n">
+      <c r="BS23" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="BN23" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO23" s="23" t="n">
+      <c r="BT23" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU23" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="BQ23" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="BR23" s="23" t="n">
+      <c r="BW23" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="BX23" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="BS23" s="23" t="s">
-        <v>138</v>
-      </c>
+      <c r="BY23" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="XFA23" s="0"/>
+      <c r="XFB23" s="0"/>
+      <c r="XFC23" s="0"/>
+      <c r="XFD23" s="0"/>
     </row>
     <row r="24" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B24" s="23" t="n">
         <v>41</v>
@@ -6650,141 +7085,169 @@
         <v>228.7</v>
       </c>
       <c r="S24" s="26" t="n">
+        <f aca="false">R24/$P24</f>
+        <v>4.23393068720379</v>
+      </c>
+      <c r="T24" s="26" t="n">
         <f aca="false">R24/P24</f>
         <v>4.23393068720379</v>
       </c>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="0" t="n">
-        <f aca="false">T24+U24</f>
-        <v>0</v>
-      </c>
-      <c r="W24" s="27" t="n">
+      <c r="U24" s="27" t="n">
         <f aca="false">3/5*H24+M24/3</f>
         <v>54.8666666666667</v>
       </c>
-      <c r="X24" s="27" t="n">
-        <f aca="false">R24-V24</f>
-        <v>228.7</v>
-      </c>
-      <c r="Y24" s="27" t="n">
-        <f aca="false">1000/100*Q24*($Q$41+$Q$47-$Q$49)-V24</f>
+      <c r="V24" s="26" t="n">
+        <f aca="false">U24/$P24</f>
+        <v>1.01574842022117</v>
+      </c>
+      <c r="W24" s="27" t="n">
+        <f aca="false">R24-U24</f>
+        <v>173.833333333333</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <f aca="false">W24/$P24</f>
+        <v>3.21818226698262</v>
+      </c>
+      <c r="Y24" s="26"/>
+      <c r="Z24" s="26"/>
+      <c r="AA24" s="0" t="n">
+        <f aca="false">Y24+Z24</f>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="26" t="n">
+        <f aca="false">AA24/$P24</f>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="27" t="n">
+        <f aca="false">1000/100*Q24*($Q$41+$Q$47-$Q$49)-AA24</f>
         <v>204.452180191289</v>
       </c>
-      <c r="Z24" s="27" t="n">
-        <f aca="false">Y24-V24+Q24/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD24" s="26" t="n">
+        <f aca="false">AC24/$P24</f>
+        <v>3.78502999465508</v>
+      </c>
+      <c r="AE24" s="27" t="n">
+        <f aca="false">AC24+Q24/100*1000 *($Q$46+$Q$43)</f>
         <v>365.160197296711</v>
       </c>
-      <c r="AA24" s="26" t="n">
-        <f aca="false">-V24+($Q$45 + $Q$46)*1000*Q24/100</f>
+      <c r="AF24" s="26" t="n">
+        <f aca="false">AE24/$P24</f>
+        <v>6.76022284687335</v>
+      </c>
+      <c r="AG24" s="26" t="n">
+        <f aca="false">-AA24+($Q$45 + $Q$46)*1000*Q24/100</f>
         <v>167.352244574952</v>
       </c>
-      <c r="AB24" s="26" t="n">
-        <f aca="false">AA24/P24/10</f>
+      <c r="AH24" s="26" t="n">
+        <f aca="false">AG24/P24/10</f>
         <v>0.309819765578629</v>
       </c>
-      <c r="AC24" s="26" t="n">
-        <f aca="false">ROUND(AA24/P24 *100/1000, 2)</f>
+      <c r="AI24" s="26" t="n">
+        <f aca="false">ROUND(AG24/P24 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE24" s="26" t="n">
+      <c r="AK24" s="26" t="n">
         <f aca="false">-Q24*($Q$47)*10</f>
         <v>-89.0398454792077</v>
       </c>
-      <c r="AF24" s="26" t="n">
-        <f aca="false">AE24/P24/10</f>
+      <c r="AL24" s="26" t="n">
+        <f aca="false">AK24/P24/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI24" s="23" t="n">
+      <c r="AO24" s="23" t="n">
         <v>84.3</v>
       </c>
-      <c r="AN24" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="AO24" s="23" t="n">
+      <c r="AT24" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="AU24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP24" s="23" t="n">
+      <c r="AV24" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="AQ24" s="23" t="n">
-        <f aca="false">AO24+AP24/100</f>
+      <c r="AW24" s="23" t="n">
+        <f aca="false">AU24+AV24/100</f>
         <v>0.14</v>
       </c>
-      <c r="AR24" s="23" t="n">
-        <f aca="false">AQ24*1000</f>
+      <c r="AX24" s="23" t="n">
+        <f aca="false">AW24*1000</f>
         <v>140</v>
       </c>
-      <c r="AU24" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="AV24" s="23" t="n">
+      <c r="BA24" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="BB24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AW24" s="23" t="n">
+      <c r="BC24" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="AX24" s="28" t="n">
-        <f aca="false">AV24+AW24/10</f>
+      <c r="BD24" s="28" t="n">
+        <f aca="false">BB24+BC24/10</f>
         <v>0.8</v>
       </c>
-      <c r="AY24" s="28" t="n">
-        <f aca="false">1000*AX24</f>
+      <c r="BE24" s="28" t="n">
+        <f aca="false">1000*BD24</f>
         <v>800</v>
       </c>
-      <c r="BA24" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="BB24" s="23" t="n">
+      <c r="BG24" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="BH24" s="23" t="n">
         <v>0.14</v>
       </c>
-      <c r="BC24" s="23" t="n">
+      <c r="BI24" s="23" t="n">
         <v>0.31</v>
       </c>
-      <c r="BD24" s="23" t="n">
+      <c r="BJ24" s="23" t="n">
         <v>0.42</v>
       </c>
-      <c r="BE24" s="23" t="n">
+      <c r="BK24" s="23" t="n">
         <v>0.74</v>
       </c>
-      <c r="BF24" s="23" t="n">
+      <c r="BL24" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="BG24" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="BI24" s="28" t="n">
-        <f aca="false">BB24*1000</f>
+      <c r="BM24" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="BK24" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="BL24" s="23" t="n">
+      <c r="BO24" s="28" t="n">
+        <f aca="false">BH24*1000</f>
+        <v>140</v>
+      </c>
+      <c r="BQ24" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="BR24" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="BM24" s="23" t="n">
+      <c r="BS24" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="BN24" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO24" s="23" t="n">
+      <c r="BT24" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU24" s="23" t="n">
         <v>41</v>
       </c>
-      <c r="BQ24" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="BR24" s="23" t="n">
+      <c r="BW24" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="BX24" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="BS24" s="23" t="s">
-        <v>147</v>
-      </c>
+      <c r="BY24" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="XFA24" s="0"/>
+      <c r="XFB24" s="0"/>
+      <c r="XFC24" s="0"/>
+      <c r="XFD24" s="0"/>
     </row>
     <row r="25" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B25" s="23" t="n">
         <v>10</v>
@@ -6848,141 +7311,169 @@
         <v>530.5</v>
       </c>
       <c r="S25" s="26" t="n">
+        <f aca="false">R25/$P25</f>
+        <v>10.5111947691698</v>
+      </c>
+      <c r="T25" s="26" t="n">
         <f aca="false">R25/P25</f>
         <v>10.5111947691698</v>
       </c>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-      <c r="V25" s="0" t="n">
-        <f aca="false">T25+U25</f>
-        <v>0</v>
-      </c>
-      <c r="W25" s="27" t="n">
+      <c r="U25" s="27" t="n">
         <f aca="false">3/5*H25+M25/3</f>
         <v>206.4</v>
       </c>
-      <c r="X25" s="27" t="n">
-        <f aca="false">R25-V25</f>
-        <v>530.5</v>
-      </c>
-      <c r="Y25" s="27" t="n">
-        <f aca="false">1000/100*Q25*($Q$41+$Q$47-$Q$49)-V25</f>
+      <c r="V25" s="26" t="n">
+        <f aca="false">U25/$P25</f>
+        <v>4.08955815335843</v>
+      </c>
+      <c r="W25" s="27" t="n">
+        <f aca="false">R25-U25</f>
+        <v>324.1</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <f aca="false">W25/$P25</f>
+        <v>6.42163661581137</v>
+      </c>
+      <c r="Y25" s="26"/>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="0" t="n">
+        <f aca="false">Y25+Z25</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="26" t="n">
+        <f aca="false">AA25/$P25</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="27" t="n">
+        <f aca="false">1000/100*Q25*($Q$41+$Q$47-$Q$49)-AA25</f>
         <v>191.030463830241</v>
       </c>
-      <c r="Z25" s="27" t="n">
-        <f aca="false">Y25-V25+Q25/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD25" s="26" t="n">
+        <f aca="false">AC25/$P25</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE25" s="27" t="n">
+        <f aca="false">AC25+Q25/100*1000 *($Q$46+$Q$43)</f>
         <v>341.188447081697</v>
       </c>
-      <c r="AA25" s="26" t="n">
-        <f aca="false">-V25+($Q$45 + $Q$46)*1000*Q25/100</f>
+      <c r="AF25" s="26" t="n">
+        <f aca="false">AE25/$P25</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG25" s="26" t="n">
+        <f aca="false">-AA25+($Q$45 + $Q$46)*1000*Q25/100</f>
         <v>156.366035687534</v>
       </c>
-      <c r="AB25" s="26" t="n">
-        <f aca="false">AA25/P25/10</f>
+      <c r="AH25" s="26" t="n">
+        <f aca="false">AG25/P25/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC25" s="26" t="n">
-        <f aca="false">ROUND(AA25/P25 *100/1000, 2)</f>
+      <c r="AI25" s="26" t="n">
+        <f aca="false">ROUND(AG25/P25 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE25" s="26" t="n">
+      <c r="AK25" s="26" t="n">
         <f aca="false">-Q25*($Q$47)*10</f>
         <v>-83.1946275424988</v>
       </c>
-      <c r="AF25" s="26" t="n">
-        <f aca="false">AE25/P25/10</f>
+      <c r="AL25" s="26" t="n">
+        <f aca="false">AK25/P25/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI25" s="23" t="n">
+      <c r="AO25" s="23" t="n">
         <v>89.5</v>
       </c>
-      <c r="AN25" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="AO25" s="23" t="n">
+      <c r="AT25" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="AU25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP25" s="23" t="n">
+      <c r="AV25" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="AQ25" s="23" t="n">
-        <f aca="false">AO25+AP25/100</f>
+      <c r="AW25" s="23" t="n">
+        <f aca="false">AU25+AV25/100</f>
         <v>0.21</v>
       </c>
-      <c r="AR25" s="23" t="n">
-        <f aca="false">AQ25*1000</f>
+      <c r="AX25" s="23" t="n">
+        <f aca="false">AW25*1000</f>
         <v>210</v>
       </c>
-      <c r="AU25" s="28" t="s">
+      <c r="BA25" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="BB25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD25" s="28" t="n">
+        <f aca="false">BB25+BC25/10</f>
+        <v>1.8</v>
+      </c>
+      <c r="BE25" s="28" t="n">
+        <f aca="false">1000*BD25</f>
+        <v>1800</v>
+      </c>
+      <c r="BG25" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="BH25" s="23" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BI25" s="23" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BJ25" s="23" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BK25" s="23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL25" s="23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM25" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="BO25" s="28" t="n">
+        <f aca="false">BH25*1000</f>
+        <v>210</v>
+      </c>
+      <c r="BQ25" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="BR25" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS25" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT25" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU25" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW25" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="BX25" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY25" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="AV25" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW25" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX25" s="28" t="n">
-        <f aca="false">AV25+AW25/10</f>
-        <v>1.8</v>
-      </c>
-      <c r="AY25" s="28" t="n">
-        <f aca="false">1000*AX25</f>
-        <v>1800</v>
-      </c>
-      <c r="BA25" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="BB25" s="23" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BC25" s="23" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BD25" s="23" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BE25" s="23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF25" s="23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BG25" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="BI25" s="28" t="n">
-        <f aca="false">BB25*1000</f>
-        <v>210</v>
-      </c>
-      <c r="BK25" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="BL25" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM25" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN25" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO25" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ25" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="BR25" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS25" s="23" t="s">
-        <v>153</v>
-      </c>
+      <c r="XFA25" s="0"/>
+      <c r="XFB25" s="0"/>
+      <c r="XFC25" s="0"/>
+      <c r="XFD25" s="0"/>
     </row>
     <row r="26" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B26" s="23" t="n">
         <v>7</v>
@@ -7046,141 +7537,169 @@
         <v>194.3</v>
       </c>
       <c r="S26" s="26" t="n">
+        <f aca="false">R26/$P26</f>
+        <v>14.1711034935453</v>
+      </c>
+      <c r="T26" s="26" t="n">
         <f aca="false">R26/P26</f>
         <v>14.1711034935453</v>
       </c>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="0" t="n">
-        <f aca="false">T26+U26</f>
-        <v>0</v>
-      </c>
-      <c r="W26" s="27" t="n">
+      <c r="U26" s="27" t="n">
         <f aca="false">3/5*H26+M26/3</f>
         <v>46.2</v>
       </c>
-      <c r="X26" s="27" t="n">
-        <f aca="false">R26-V26</f>
-        <v>194.3</v>
-      </c>
-      <c r="Y26" s="27" t="n">
-        <f aca="false">1000/100*Q26*($Q$41+$Q$47-$Q$49)-V26</f>
+      <c r="V26" s="26" t="n">
+        <f aca="false">U26/$P26</f>
+        <v>3.36955728976734</v>
+      </c>
+      <c r="W26" s="27" t="n">
+        <f aca="false">R26-U26</f>
+        <v>148.1</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <f aca="false">W26/$P26</f>
+        <v>10.801546203778</v>
+      </c>
+      <c r="Y26" s="26"/>
+      <c r="Z26" s="26"/>
+      <c r="AA26" s="0" t="n">
+        <f aca="false">Y26+Z26</f>
+        <v>0</v>
+      </c>
+      <c r="AB26" s="26" t="n">
+        <f aca="false">AA26/$P26</f>
+        <v>0</v>
+      </c>
+      <c r="AC26" s="27" t="n">
+        <f aca="false">1000/100*Q26*($Q$41+$Q$47-$Q$49)-AA26</f>
         <v>51.8965462567157</v>
       </c>
-      <c r="Z26" s="27" t="n">
-        <f aca="false">Y26-V26+Q26/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD26" s="26" t="n">
+        <f aca="false">AC26/$P26</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE26" s="27" t="n">
+        <f aca="false">AC26+Q26/100*1000 *($Q$46+$Q$43)</f>
         <v>92.6894154534804</v>
       </c>
-      <c r="AA26" s="26" t="n">
-        <f aca="false">-V26+($Q$45 + $Q$46)*1000*Q26/100</f>
+      <c r="AF26" s="26" t="n">
+        <f aca="false">AE26/$P26</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG26" s="26" t="n">
+        <f aca="false">-AA26+($Q$45 + $Q$46)*1000*Q26/100</f>
         <v>42.4793880584857</v>
       </c>
-      <c r="AB26" s="26" t="n">
-        <f aca="false">AA26/P26/10</f>
+      <c r="AH26" s="26" t="n">
+        <f aca="false">AG26/P26/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC26" s="26" t="n">
-        <f aca="false">ROUND(AA26/P26 *100/1000, 2)</f>
+      <c r="AI26" s="26" t="n">
+        <f aca="false">ROUND(AG26/P26 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE26" s="26" t="n">
+      <c r="AK26" s="26" t="n">
         <f aca="false">-Q26*($Q$47)*10</f>
         <v>-22.6011796757519</v>
       </c>
-      <c r="AF26" s="26" t="n">
-        <f aca="false">AE26/P26/10</f>
+      <c r="AL26" s="26" t="n">
+        <f aca="false">AK26/P26/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI26" s="23" t="n">
+      <c r="AO26" s="23" t="n">
         <v>24.6</v>
       </c>
-      <c r="AN26" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="AO26" s="23" t="n">
+      <c r="AT26" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="AU26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP26" s="23" t="n">
+      <c r="AV26" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="AQ26" s="23" t="n">
-        <f aca="false">AO26+AP26/100</f>
+      <c r="AW26" s="23" t="n">
+        <f aca="false">AU26+AV26/100</f>
         <v>0.27</v>
       </c>
-      <c r="AR26" s="23" t="n">
-        <f aca="false">AQ26*1000</f>
+      <c r="AX26" s="23" t="n">
+        <f aca="false">AW26*1000</f>
         <v>270</v>
       </c>
-      <c r="AU26" s="28" t="s">
+      <c r="BA26" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="BB26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD26" s="28" t="n">
+        <f aca="false">BB26+BC26/10</f>
+        <v>0.9</v>
+      </c>
+      <c r="BE26" s="28" t="n">
+        <f aca="false">1000*BD26</f>
+        <v>900</v>
+      </c>
+      <c r="BG26" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="BH26" s="23" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BI26" s="23" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BJ26" s="23" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BK26" s="23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL26" s="23" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="BM26" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="BO26" s="28" t="n">
+        <f aca="false">BH26*1000</f>
+        <v>270</v>
+      </c>
+      <c r="BQ26" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="BR26" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS26" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT26" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU26" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BW26" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="BX26" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BY26" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="AV26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX26" s="28" t="n">
-        <f aca="false">AV26+AW26/10</f>
-        <v>0.9</v>
-      </c>
-      <c r="AY26" s="28" t="n">
-        <f aca="false">1000*AX26</f>
-        <v>900</v>
-      </c>
-      <c r="BA26" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="BB26" s="23" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BC26" s="23" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BD26" s="23" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BE26" s="23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF26" s="23" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="BG26" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="BI26" s="28" t="n">
-        <f aca="false">BB26*1000</f>
-        <v>270</v>
-      </c>
-      <c r="BK26" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="BL26" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="BM26" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN26" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO26" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ26" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="BR26" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BS26" s="23" t="s">
-        <v>159</v>
-      </c>
+      <c r="XFA26" s="0"/>
+      <c r="XFB26" s="0"/>
+      <c r="XFC26" s="0"/>
+      <c r="XFD26" s="0"/>
     </row>
     <row r="27" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B27" s="23" t="n">
         <v>333</v>
@@ -7244,141 +7763,169 @@
         <v>5691.6</v>
       </c>
       <c r="S27" s="26" t="n">
+        <f aca="false">R27/$P27</f>
+        <v>6.79873285265829</v>
+      </c>
+      <c r="T27" s="26" t="n">
         <f aca="false">R27/P27</f>
         <v>6.79873285265829</v>
       </c>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="0" t="n">
-        <f aca="false">T27+U27</f>
-        <v>0</v>
-      </c>
-      <c r="W27" s="27" t="n">
+      <c r="U27" s="27" t="n">
         <f aca="false">3/5*H27+M27/3</f>
         <v>1046.46666666667</v>
       </c>
-      <c r="X27" s="27" t="n">
-        <f aca="false">R27-V27</f>
-        <v>5691.6</v>
-      </c>
-      <c r="Y27" s="27" t="n">
-        <f aca="false">1000/100*Q27*($Q$41+$Q$47-$Q$49)-V27</f>
+      <c r="V27" s="26" t="n">
+        <f aca="false">U27/$P27</f>
+        <v>1.2500258812774</v>
+      </c>
+      <c r="W27" s="27" t="n">
+        <f aca="false">R27-U27</f>
+        <v>4645.13333333333</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <f aca="false">W27/$P27</f>
+        <v>5.54870697138088</v>
+      </c>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="26"/>
+      <c r="AA27" s="0" t="n">
+        <f aca="false">Y27+Z27</f>
+        <v>0</v>
+      </c>
+      <c r="AB27" s="26" t="n">
+        <f aca="false">AA27/$P27</f>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="27" t="n">
+        <f aca="false">1000/100*Q27*($Q$41+$Q$47-$Q$49)-AA27</f>
         <v>3168.66057020546</v>
       </c>
-      <c r="Z27" s="27" t="n">
-        <f aca="false">Y27-V27+Q27/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD27" s="26" t="n">
+        <f aca="false">AC27/$P27</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE27" s="27" t="n">
+        <f aca="false">AC27+Q27/100*1000 *($Q$46+$Q$43)</f>
         <v>5659.3611175971</v>
       </c>
-      <c r="AA27" s="26" t="n">
-        <f aca="false">-V27+($Q$45 + $Q$46)*1000*Q27/100</f>
+      <c r="AF27" s="26" t="n">
+        <f aca="false">AE27/$P27</f>
+        <v>6.76022284687335</v>
+      </c>
+      <c r="AG27" s="26" t="n">
+        <f aca="false">-AA27+($Q$45 + $Q$46)*1000*Q27/100</f>
         <v>2593.67475672742</v>
       </c>
-      <c r="AB27" s="26" t="n">
-        <f aca="false">AA27/P27/10</f>
+      <c r="AH27" s="26" t="n">
+        <f aca="false">AG27/P27/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC27" s="26" t="n">
-        <f aca="false">ROUND(AA27/P27 *100/1000, 2)</f>
+      <c r="AI27" s="26" t="n">
+        <f aca="false">ROUND(AG27/P27 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE27" s="26" t="n">
+      <c r="AK27" s="26" t="n">
         <f aca="false">-Q27*($Q$47)*10</f>
         <v>-1379.9659523473</v>
       </c>
-      <c r="AF27" s="26" t="n">
-        <f aca="false">AE27/P27/10</f>
+      <c r="AL27" s="26" t="n">
+        <f aca="false">AK27/P27/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI27" s="23" t="n">
+      <c r="AO27" s="23" t="n">
         <v>1170.6</v>
       </c>
-      <c r="AN27" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="AO27" s="23" t="n">
+      <c r="AT27" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="AU27" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AP27" s="23" t="n">
+      <c r="AV27" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="AQ27" s="23" t="n">
-        <f aca="false">AO27+AP27/100</f>
+      <c r="AW27" s="23" t="n">
+        <f aca="false">AU27+AV27/100</f>
         <v>1.98</v>
       </c>
-      <c r="AR27" s="23" t="n">
-        <f aca="false">AQ27*1000</f>
+      <c r="AX27" s="23" t="n">
+        <f aca="false">AW27*1000</f>
         <v>1980</v>
       </c>
-      <c r="AU27" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="AV27" s="23" t="n">
+      <c r="BA27" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="BB27" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="AW27" s="23" t="n">
+      <c r="BC27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AX27" s="28" t="n">
-        <f aca="false">AV27+AW27/10</f>
+      <c r="BD27" s="28" t="n">
+        <f aca="false">BB27+BC27/10</f>
         <v>11</v>
       </c>
-      <c r="AY27" s="28" t="n">
-        <f aca="false">1000*AX27</f>
+      <c r="BE27" s="28" t="n">
+        <f aca="false">1000*BD27</f>
         <v>11000</v>
       </c>
-      <c r="BA27" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="BB27" s="23" t="n">
+      <c r="BG27" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="BH27" s="23" t="n">
         <v>1.98</v>
       </c>
-      <c r="BC27" s="23" t="n">
+      <c r="BI27" s="23" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD27" s="23" t="n">
+      <c r="BJ27" s="23" t="n">
         <v>6.06</v>
       </c>
-      <c r="BE27" s="23" t="n">
+      <c r="BK27" s="23" t="n">
         <v>0.73</v>
       </c>
-      <c r="BF27" s="23" t="n">
+      <c r="BL27" s="23" t="n">
         <v>0.99</v>
       </c>
-      <c r="BG27" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="BI27" s="28" t="n">
-        <f aca="false">BB27*1000</f>
+      <c r="BM27" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="BO27" s="28" t="n">
+        <f aca="false">BH27*1000</f>
         <v>1980</v>
       </c>
-      <c r="BK27" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="BL27" s="23" t="n">
+      <c r="BQ27" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="BR27" s="23" t="n">
         <v>293</v>
       </c>
-      <c r="BM27" s="23" t="n">
+      <c r="BS27" s="23" t="n">
         <v>245</v>
       </c>
-      <c r="BN27" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO27" s="23" t="n">
+      <c r="BT27" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU27" s="23" t="n">
         <v>333</v>
       </c>
-      <c r="BQ27" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR27" s="23" t="n">
+      <c r="BW27" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="BX27" s="23" t="n">
         <v>652</v>
       </c>
-      <c r="BS27" s="23" t="s">
-        <v>113</v>
-      </c>
+      <c r="BY27" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="XFA27" s="0"/>
+      <c r="XFB27" s="0"/>
+      <c r="XFC27" s="0"/>
+      <c r="XFD27" s="0"/>
     </row>
     <row r="28" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B28" s="23" t="n">
         <v>497</v>
@@ -7442,141 +7989,169 @@
         <v>2837.3</v>
       </c>
       <c r="S28" s="26" t="n">
+        <f aca="false">R28/$P28</f>
+        <v>5.1783957613554</v>
+      </c>
+      <c r="T28" s="26" t="n">
         <f aca="false">R28/P28</f>
         <v>5.1783957613554</v>
       </c>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="0" t="n">
-        <f aca="false">T28+U28</f>
-        <v>0</v>
-      </c>
-      <c r="W28" s="27" t="n">
+      <c r="U28" s="27" t="n">
         <f aca="false">3/5*H28+M28/3</f>
         <v>698.666666666667</v>
       </c>
-      <c r="X28" s="27" t="n">
-        <f aca="false">R28-V28</f>
-        <v>2837.3</v>
-      </c>
-      <c r="Y28" s="27" t="n">
-        <f aca="false">1000/100*Q28*($Q$41+$Q$47-$Q$49)-V28</f>
+      <c r="V28" s="26" t="n">
+        <f aca="false">U28/$P28</f>
+        <v>1.27514626767243</v>
+      </c>
+      <c r="W28" s="27" t="n">
+        <f aca="false">R28-U28</f>
+        <v>2138.63333333333</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <f aca="false">W28/$P28</f>
+        <v>3.90324949368298</v>
+      </c>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="26"/>
+      <c r="AA28" s="0" t="n">
+        <f aca="false">Y28+Z28</f>
+        <v>0</v>
+      </c>
+      <c r="AB28" s="26" t="n">
+        <f aca="false">AA28/$P28</f>
+        <v>0</v>
+      </c>
+      <c r="AC28" s="27" t="n">
+        <f aca="false">1000/100*Q28*($Q$41+$Q$47-$Q$49)-AA28</f>
         <v>2073.85956940145</v>
       </c>
-      <c r="Z28" s="27" t="n">
-        <f aca="false">Y28-V28+Q28/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD28" s="26" t="n">
+        <f aca="false">AC28/$P28</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE28" s="27" t="n">
+        <f aca="false">AC28+Q28/100*1000 *($Q$46+$Q$43)</f>
         <v>3704.00046025321</v>
       </c>
-      <c r="AA28" s="26" t="n">
-        <f aca="false">-V28+($Q$45 + $Q$46)*1000*Q28/100</f>
+      <c r="AF28" s="26" t="n">
+        <f aca="false">AE28/$P28</f>
+        <v>6.76022284687333</v>
+      </c>
+      <c r="AG28" s="26" t="n">
+        <f aca="false">-AA28+($Q$45 + $Q$46)*1000*Q28/100</f>
         <v>1697.53657577951</v>
       </c>
-      <c r="AB28" s="26" t="n">
-        <f aca="false">AA28/P28/10</f>
+      <c r="AH28" s="26" t="n">
+        <f aca="false">AG28/P28/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC28" s="26" t="n">
-        <f aca="false">ROUND(AA28/P28 *100/1000, 2)</f>
+      <c r="AI28" s="26" t="n">
+        <f aca="false">ROUND(AG28/P28 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE28" s="26" t="n">
+      <c r="AK28" s="26" t="n">
         <f aca="false">-Q28*($Q$47)*10</f>
         <v>-903.17518469265</v>
       </c>
-      <c r="AF28" s="26" t="n">
-        <f aca="false">AE28/P28/10</f>
+      <c r="AL28" s="26" t="n">
+        <f aca="false">AK28/P28/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI28" s="23" t="n">
+      <c r="AO28" s="23" t="n">
         <v>922.9</v>
       </c>
-      <c r="AN28" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="AO28" s="23" t="n">
+      <c r="AT28" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="AU28" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AP28" s="23" t="n">
+      <c r="AV28" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="AQ28" s="23" t="n">
-        <f aca="false">AO28+AP28/100</f>
+      <c r="AW28" s="23" t="n">
+        <f aca="false">AU28+AV28/100</f>
         <v>1.19</v>
       </c>
-      <c r="AR28" s="23" t="n">
-        <f aca="false">AQ28*1000</f>
+      <c r="AX28" s="23" t="n">
+        <f aca="false">AW28*1000</f>
         <v>1190</v>
       </c>
-      <c r="AU28" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="AV28" s="23" t="n">
+      <c r="BA28" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="BB28" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="AW28" s="23" t="n">
+      <c r="BC28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AX28" s="28" t="n">
-        <f aca="false">AV28+AW28/10</f>
+      <c r="BD28" s="28" t="n">
+        <f aca="false">BB28+BC28/10</f>
         <v>8</v>
       </c>
-      <c r="AY28" s="28" t="n">
-        <f aca="false">1000*AX28</f>
+      <c r="BE28" s="28" t="n">
+        <f aca="false">1000*BD28</f>
         <v>8000</v>
       </c>
-      <c r="BA28" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="BB28" s="23" t="n">
+      <c r="BG28" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="BH28" s="23" t="n">
         <v>1.19</v>
       </c>
-      <c r="BC28" s="23" t="n">
+      <c r="BI28" s="23" t="n">
         <v>2.65</v>
       </c>
-      <c r="BD28" s="23" t="n">
+      <c r="BJ28" s="23" t="n">
         <v>4.77</v>
       </c>
-      <c r="BE28" s="23" t="n">
+      <c r="BK28" s="23" t="n">
         <v>0.56</v>
       </c>
-      <c r="BF28" s="23" t="n">
+      <c r="BL28" s="23" t="n">
         <v>0.76</v>
       </c>
-      <c r="BG28" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="BI28" s="28" t="n">
-        <f aca="false">BB28*1000</f>
+      <c r="BM28" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="BO28" s="28" t="n">
+        <f aca="false">BH28*1000</f>
         <v>1190</v>
       </c>
-      <c r="BK28" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="BL28" s="23" t="n">
+      <c r="BQ28" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="BR28" s="23" t="n">
         <v>192</v>
       </c>
-      <c r="BM28" s="23" t="n">
+      <c r="BS28" s="23" t="n">
         <v>365</v>
       </c>
-      <c r="BN28" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO28" s="23" t="n">
+      <c r="BT28" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU28" s="23" t="n">
         <v>497</v>
       </c>
-      <c r="BQ28" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="BR28" s="23" t="n">
+      <c r="BW28" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="BX28" s="23" t="n">
         <v>427</v>
       </c>
-      <c r="BS28" s="23" t="s">
-        <v>170</v>
-      </c>
+      <c r="BY28" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="XFA28" s="0"/>
+      <c r="XFB28" s="0"/>
+      <c r="XFC28" s="0"/>
+      <c r="XFD28" s="0"/>
     </row>
     <row r="29" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B29" s="23" t="n">
         <v>137</v>
@@ -7640,141 +8215,169 @@
         <v>1777.8</v>
       </c>
       <c r="S29" s="26" t="n">
+        <f aca="false">R29/$P29</f>
+        <v>8.39079646017699</v>
+      </c>
+      <c r="T29" s="26" t="n">
         <f aca="false">R29/P29</f>
         <v>8.39079646017699</v>
       </c>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="0" t="n">
-        <f aca="false">T29+U29</f>
-        <v>0</v>
-      </c>
-      <c r="W29" s="27" t="n">
+      <c r="U29" s="27" t="n">
         <f aca="false">3/5*H29+M29/3</f>
         <v>488.133333333333</v>
       </c>
-      <c r="X29" s="27" t="n">
-        <f aca="false">R29-V29</f>
-        <v>1777.8</v>
-      </c>
-      <c r="Y29" s="27" t="n">
-        <f aca="false">1000/100*Q29*($Q$41+$Q$47-$Q$49)-V29</f>
+      <c r="V29" s="26" t="n">
+        <f aca="false">U29/$P29</f>
+        <v>2.30387413962635</v>
+      </c>
+      <c r="W29" s="27" t="n">
+        <f aca="false">R29-U29</f>
+        <v>1289.66666666667</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <f aca="false">W29/$P29</f>
+        <v>6.08692232055064</v>
+      </c>
+      <c r="Y29" s="26"/>
+      <c r="Z29" s="26"/>
+      <c r="AA29" s="0" t="n">
+        <f aca="false">Y29+Z29</f>
+        <v>0</v>
+      </c>
+      <c r="AB29" s="26" t="n">
+        <f aca="false">AA29/$P29</f>
+        <v>0</v>
+      </c>
+      <c r="AC29" s="27" t="n">
+        <f aca="false">1000/100*Q29*($Q$41+$Q$47-$Q$49)-AA29</f>
         <v>801.953230117544</v>
       </c>
-      <c r="Z29" s="27" t="n">
-        <f aca="false">Y29-V29+Q29/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD29" s="26" t="n">
+        <f aca="false">AC29/$P29</f>
+        <v>3.78502999465508</v>
+      </c>
+      <c r="AE29" s="27" t="n">
+        <f aca="false">AC29+Q29/100*1000 *($Q$46+$Q$43)</f>
         <v>1432.32221568129</v>
       </c>
-      <c r="AA29" s="26" t="n">
-        <f aca="false">-V29+($Q$45 + $Q$46)*1000*Q29/100</f>
+      <c r="AF29" s="26" t="n">
+        <f aca="false">AE29/$P29</f>
+        <v>6.76022284687335</v>
+      </c>
+      <c r="AG29" s="26" t="n">
+        <f aca="false">-AA29+($Q$45 + $Q$46)*1000*Q29/100</f>
         <v>656.430628319719</v>
       </c>
-      <c r="AB29" s="26" t="n">
-        <f aca="false">AA29/P29/10</f>
+      <c r="AH29" s="26" t="n">
+        <f aca="false">AG29/P29/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC29" s="26" t="n">
-        <f aca="false">ROUND(AA29/P29 *100/1000, 2)</f>
+      <c r="AI29" s="26" t="n">
+        <f aca="false">ROUND(AG29/P29 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE29" s="26" t="n">
+      <c r="AK29" s="26" t="n">
         <f aca="false">-Q29*($Q$47)*10</f>
         <v>-349.25424431478</v>
       </c>
-      <c r="AF29" s="26" t="n">
-        <f aca="false">AE29/P29/10</f>
+      <c r="AL29" s="26" t="n">
+        <f aca="false">AK29/P29/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI29" s="23" t="n">
+      <c r="AO29" s="23" t="n">
         <v>306.8</v>
       </c>
-      <c r="AN29" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="AO29" s="23" t="n">
+      <c r="AT29" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="AU29" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AP29" s="23" t="n">
+      <c r="AV29" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="AQ29" s="23" t="n">
-        <f aca="false">AO29+AP29/100</f>
+      <c r="AW29" s="23" t="n">
+        <f aca="false">AU29+AV29/100</f>
         <v>1.95</v>
       </c>
-      <c r="AR29" s="23" t="n">
-        <f aca="false">AQ29*1000</f>
+      <c r="AX29" s="23" t="n">
+        <f aca="false">AW29*1000</f>
         <v>1950</v>
       </c>
-      <c r="AU29" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="AV29" s="23" t="n">
+      <c r="BA29" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="BB29" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="AW29" s="23" t="n">
+      <c r="BC29" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="AX29" s="28" t="n">
-        <f aca="false">AV29+AW29/10</f>
+      <c r="BD29" s="28" t="n">
+        <f aca="false">BB29+BC29/10</f>
         <v>6.4</v>
       </c>
-      <c r="AY29" s="28" t="n">
-        <f aca="false">1000*AX29</f>
+      <c r="BE29" s="28" t="n">
+        <f aca="false">1000*BD29</f>
         <v>6400</v>
       </c>
-      <c r="BA29" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="BB29" s="23" t="n">
+      <c r="BG29" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="BH29" s="23" t="n">
         <v>1.95</v>
       </c>
-      <c r="BC29" s="23" t="n">
+      <c r="BI29" s="23" t="n">
         <v>4.33</v>
       </c>
-      <c r="BD29" s="23" t="n">
+      <c r="BJ29" s="23" t="n">
         <v>1.55</v>
       </c>
-      <c r="BE29" s="23" t="n">
+      <c r="BK29" s="23" t="n">
         <v>2.8</v>
       </c>
-      <c r="BF29" s="23" t="n">
+      <c r="BL29" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="BG29" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="BI29" s="28" t="n">
-        <f aca="false">BB29*1000</f>
+      <c r="BM29" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="BO29" s="28" t="n">
+        <f aca="false">BH29*1000</f>
         <v>1950</v>
       </c>
-      <c r="BK29" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="BL29" s="23" t="n">
+      <c r="BQ29" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="BR29" s="23" t="n">
         <v>38</v>
       </c>
-      <c r="BM29" s="23" t="n">
+      <c r="BS29" s="23" t="n">
         <v>101</v>
       </c>
-      <c r="BN29" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO29" s="23" t="n">
+      <c r="BT29" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU29" s="23" t="n">
         <v>137</v>
       </c>
-      <c r="BQ29" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="BR29" s="23" t="n">
+      <c r="BW29" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="BX29" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="BS29" s="23" t="s">
-        <v>69</v>
-      </c>
+      <c r="BY29" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="XFA29" s="0"/>
+      <c r="XFB29" s="0"/>
+      <c r="XFC29" s="0"/>
+      <c r="XFD29" s="0"/>
     </row>
     <row r="30" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B30" s="23" t="n">
         <v>135</v>
@@ -7838,141 +8441,169 @@
         <v>828.5</v>
       </c>
       <c r="S30" s="26" t="n">
+        <f aca="false">R30/$P30</f>
+        <v>3.84790443635283</v>
+      </c>
+      <c r="T30" s="26" t="n">
         <f aca="false">R30/P30</f>
         <v>3.84790443635283</v>
       </c>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="0" t="n">
-        <f aca="false">T30+U30</f>
-        <v>0</v>
-      </c>
-      <c r="W30" s="27" t="n">
+      <c r="U30" s="27" t="n">
         <f aca="false">3/5*H30+M30/3</f>
         <v>217.666666666667</v>
       </c>
-      <c r="X30" s="27" t="n">
-        <f aca="false">R30-V30</f>
-        <v>828.5</v>
-      </c>
-      <c r="Y30" s="27" t="n">
-        <f aca="false">1000/100*Q30*($Q$41+$Q$47-$Q$49)-V30</f>
+      <c r="V30" s="26" t="n">
+        <f aca="false">U30/$P30</f>
+        <v>1.01093606796958</v>
+      </c>
+      <c r="W30" s="27" t="n">
+        <f aca="false">R30-U30</f>
+        <v>610.833333333333</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <f aca="false">W30/$P30</f>
+        <v>2.83696836838325</v>
+      </c>
+      <c r="Y30" s="26"/>
+      <c r="Z30" s="26"/>
+      <c r="AA30" s="0" t="n">
+        <f aca="false">Y30+Z30</f>
+        <v>0</v>
+      </c>
+      <c r="AB30" s="26" t="n">
+        <f aca="false">AA30/$P30</f>
+        <v>0</v>
+      </c>
+      <c r="AC30" s="27" t="n">
+        <f aca="false">1000/100*Q30*($Q$41+$Q$47-$Q$49)-AA30</f>
         <v>814.962378209173</v>
       </c>
-      <c r="Z30" s="27" t="n">
-        <f aca="false">Y30-V30+Q30/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD30" s="26" t="n">
+        <f aca="false">AC30/$P30</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE30" s="27" t="n">
+        <f aca="false">AC30+Q30/100*1000 *($Q$46+$Q$43)</f>
         <v>1455.55710160599</v>
       </c>
-      <c r="AA30" s="26" t="n">
-        <f aca="false">-V30+($Q$45 + $Q$46)*1000*Q30/100</f>
+      <c r="AF30" s="26" t="n">
+        <f aca="false">AE30/$P30</f>
+        <v>6.76022284687335</v>
+      </c>
+      <c r="AG30" s="26" t="n">
+        <f aca="false">-AA30+($Q$45 + $Q$46)*1000*Q30/100</f>
         <v>667.079133662656</v>
       </c>
-      <c r="AB30" s="26" t="n">
-        <f aca="false">AA30/P30/10</f>
+      <c r="AH30" s="26" t="n">
+        <f aca="false">AG30/P30/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC30" s="26" t="n">
-        <f aca="false">ROUND(AA30/P30 *100/1000, 2)</f>
+      <c r="AI30" s="26" t="n">
+        <f aca="false">ROUND(AG30/P30 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE30" s="26" t="n">
+      <c r="AK30" s="26" t="n">
         <f aca="false">-Q30*($Q$47)*10</f>
         <v>-354.919786911641</v>
       </c>
-      <c r="AF30" s="26" t="n">
-        <f aca="false">AE30/P30/10</f>
+      <c r="AL30" s="26" t="n">
+        <f aca="false">AK30/P30/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI30" s="23" t="n">
+      <c r="AO30" s="23" t="n">
         <v>380.1</v>
       </c>
-      <c r="AN30" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="AO30" s="23" t="n">
+      <c r="AT30" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="AU30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP30" s="23" t="n">
+      <c r="AV30" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="AQ30" s="23" t="n">
-        <f aca="false">AO30+AP30/100</f>
+      <c r="AW30" s="23" t="n">
+        <f aca="false">AU30+AV30/100</f>
         <v>0.62</v>
       </c>
-      <c r="AR30" s="23" t="n">
-        <f aca="false">AQ30*1000</f>
+      <c r="AX30" s="23" t="n">
+        <f aca="false">AW30*1000</f>
         <v>620</v>
       </c>
-      <c r="AU30" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="AV30" s="23" t="n">
+      <c r="BA30" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="BB30" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AW30" s="23" t="n">
+      <c r="BC30" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="AX30" s="28" t="n">
-        <f aca="false">AV30+AW30/10</f>
+      <c r="BD30" s="28" t="n">
+        <f aca="false">BB30+BC30/10</f>
         <v>3.2</v>
       </c>
-      <c r="AY30" s="28" t="n">
-        <f aca="false">1000*AX30</f>
+      <c r="BE30" s="28" t="n">
+        <f aca="false">1000*BD30</f>
         <v>3200</v>
       </c>
-      <c r="BA30" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="BB30" s="23" t="n">
+      <c r="BG30" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="BH30" s="23" t="n">
         <v>0.62</v>
       </c>
-      <c r="BC30" s="23" t="n">
+      <c r="BI30" s="23" t="n">
         <v>1.37</v>
       </c>
-      <c r="BD30" s="23" t="n">
+      <c r="BJ30" s="23" t="n">
         <v>2.03</v>
       </c>
-      <c r="BE30" s="23" t="n">
+      <c r="BK30" s="23" t="n">
         <v>0.68</v>
       </c>
-      <c r="BF30" s="23" t="n">
+      <c r="BL30" s="23" t="n">
         <v>0.92</v>
       </c>
-      <c r="BG30" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="BI30" s="28" t="n">
-        <f aca="false">BB30*1000</f>
+      <c r="BM30" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="BO30" s="28" t="n">
+        <f aca="false">BH30*1000</f>
         <v>620</v>
       </c>
-      <c r="BK30" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="BL30" s="23" t="n">
+      <c r="BQ30" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="BR30" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="BM30" s="23" t="n">
+      <c r="BS30" s="23" t="n">
         <v>99</v>
       </c>
-      <c r="BN30" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO30" s="23" t="n">
+      <c r="BT30" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU30" s="23" t="n">
         <v>135</v>
       </c>
-      <c r="BQ30" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="BR30" s="23" t="n">
+      <c r="BW30" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="BX30" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="BS30" s="23" t="s">
-        <v>180</v>
-      </c>
+      <c r="BY30" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="XFA30" s="0"/>
+      <c r="XFB30" s="0"/>
+      <c r="XFC30" s="0"/>
+      <c r="XFD30" s="0"/>
     </row>
     <row r="31" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B31" s="23" t="n">
         <v>76</v>
@@ -8036,142 +8667,170 @@
         <v>317.3</v>
       </c>
       <c r="S31" s="26" t="n">
+        <f aca="false">R31/$P31</f>
+        <v>3.26111533638924</v>
+      </c>
+      <c r="T31" s="26" t="n">
         <f aca="false">R31/P31</f>
         <v>3.26111533638924</v>
       </c>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="0" t="n">
-        <f aca="false">T31+U31</f>
-        <v>0</v>
-      </c>
-      <c r="W31" s="27" t="n">
+      <c r="U31" s="27" t="n">
         <f aca="false">3/5*H31+M31/3</f>
         <v>70.3333333333333</v>
       </c>
-      <c r="X31" s="27" t="n">
-        <f aca="false">R31-V31</f>
-        <v>317.3</v>
-      </c>
-      <c r="Y31" s="27" t="n">
-        <f aca="false">1000/100*Q31*($Q$41+$Q$47-$Q$49)-V31</f>
+      <c r="V31" s="26" t="n">
+        <f aca="false">U31/$P31</f>
+        <v>0.722865149677623</v>
+      </c>
+      <c r="W31" s="27" t="n">
+        <f aca="false">R31-U31</f>
+        <v>246.966666666667</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <f aca="false">W31/$P31</f>
+        <v>2.53825018671161</v>
+      </c>
+      <c r="Y31" s="26"/>
+      <c r="Z31" s="26"/>
+      <c r="AA31" s="0" t="n">
+        <f aca="false">Y31+Z31</f>
+        <v>0</v>
+      </c>
+      <c r="AB31" s="26" t="n">
+        <f aca="false">AA31/$P31</f>
+        <v>0</v>
+      </c>
+      <c r="AC31" s="27" t="n">
+        <f aca="false">1000/100*Q31*($Q$41+$Q$47-$Q$49)-AA31</f>
         <v>368.275848419949</v>
       </c>
-      <c r="Z31" s="27" t="n">
-        <f aca="false">Y31-V31+Q31/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD31" s="26" t="n">
+        <f aca="false">AC31/$P31</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE31" s="27" t="n">
+        <f aca="false">AC31+Q31/100*1000 *($Q$46+$Q$43)</f>
         <v>657.756162555082</v>
       </c>
-      <c r="AA31" s="26" t="n">
-        <f aca="false">-V31+($Q$45 + $Q$46)*1000*Q31/100</f>
+      <c r="AF31" s="26" t="n">
+        <f aca="false">AE31/$P31</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG31" s="26" t="n">
+        <f aca="false">-AA31+($Q$45 + $Q$46)*1000*Q31/100</f>
         <v>301.448435512694</v>
       </c>
-      <c r="AB31" s="26" t="n">
-        <f aca="false">AA31/P31/10</f>
+      <c r="AH31" s="26" t="n">
+        <f aca="false">AG31/P31/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC31" s="26" t="n">
-        <f aca="false">ROUND(AA31/P31 *100/1000, 2)</f>
+      <c r="AI31" s="26" t="n">
+        <f aca="false">ROUND(AG31/P31 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE31" s="26" t="n">
+      <c r="AK31" s="26" t="n">
         <f aca="false">-Q31*($Q$47)*10</f>
         <v>-160.385790977413</v>
       </c>
-      <c r="AF31" s="26" t="n">
-        <f aca="false">AE31/P31/10</f>
+      <c r="AL31" s="26" t="n">
+        <f aca="false">AK31/P31/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AG31" s="32"/>
-      <c r="AI31" s="23" t="n">
+      <c r="AM31" s="32"/>
+      <c r="AO31" s="23" t="n">
         <v>136.8</v>
       </c>
-      <c r="AN31" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="AO31" s="23" t="n">
+      <c r="AT31" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP31" s="23" t="n">
+      <c r="AV31" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="AQ31" s="23" t="n">
-        <f aca="false">AO31+AP31/100</f>
+      <c r="AW31" s="23" t="n">
+        <f aca="false">AU31+AV31/100</f>
         <v>0.4</v>
       </c>
-      <c r="AR31" s="23" t="n">
-        <f aca="false">AQ31*1000</f>
+      <c r="AX31" s="23" t="n">
+        <f aca="false">AW31*1000</f>
         <v>400</v>
       </c>
-      <c r="AU31" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV31" s="23" t="n">
+      <c r="BA31" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="BB31" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AW31" s="23" t="n">
+      <c r="BC31" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AX31" s="28" t="n">
-        <f aca="false">AV31+AW31/10</f>
+      <c r="BD31" s="28" t="n">
+        <f aca="false">BB31+BC31/10</f>
         <v>1.3</v>
       </c>
-      <c r="AY31" s="28" t="n">
-        <f aca="false">1000*AX31</f>
+      <c r="BE31" s="28" t="n">
+        <f aca="false">1000*BD31</f>
         <v>1300</v>
       </c>
-      <c r="BA31" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="BB31" s="23" t="n">
+      <c r="BG31" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="BH31" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="BC31" s="23" t="n">
+      <c r="BI31" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="BD31" s="23" t="n">
+      <c r="BJ31" s="23" t="n">
         <v>0.73</v>
       </c>
-      <c r="BE31" s="23" t="n">
+      <c r="BK31" s="23" t="n">
         <v>0.14</v>
       </c>
-      <c r="BF31" s="23" t="n">
+      <c r="BL31" s="23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BG31" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI31" s="28" t="n">
-        <f aca="false">BB31*1000</f>
+      <c r="BM31" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="BO31" s="28" t="n">
+        <f aca="false">BH31*1000</f>
         <v>50</v>
       </c>
-      <c r="BK31" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="BL31" s="23" t="n">
+      <c r="BQ31" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="BR31" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="BM31" s="23" t="n">
+      <c r="BS31" s="23" t="n">
         <v>56</v>
       </c>
-      <c r="BN31" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO31" s="23" t="n">
+      <c r="BT31" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU31" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="BQ31" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="BR31" s="23" t="n">
+      <c r="BW31" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="BX31" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="BS31" s="23" t="s">
-        <v>147</v>
-      </c>
+      <c r="BY31" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="XFA31" s="0"/>
+      <c r="XFB31" s="0"/>
+      <c r="XFC31" s="0"/>
+      <c r="XFD31" s="0"/>
     </row>
     <row r="32" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B32" s="23" t="n">
         <v>33</v>
@@ -8235,141 +8894,169 @@
         <v>277.1</v>
       </c>
       <c r="S32" s="26" t="n">
+        <f aca="false">R32/$P32</f>
+        <v>5.38361407394455</v>
+      </c>
+      <c r="T32" s="26" t="n">
         <f aca="false">R32/P32</f>
         <v>5.38361407394455</v>
       </c>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="0" t="n">
-        <f aca="false">T32+U32</f>
-        <v>0</v>
-      </c>
-      <c r="W32" s="27" t="n">
+      <c r="U32" s="27" t="n">
         <f aca="false">3/5*H32+M32/3</f>
         <v>94.8666666666667</v>
       </c>
-      <c r="X32" s="27" t="n">
-        <f aca="false">R32-V32</f>
-        <v>277.1</v>
-      </c>
-      <c r="Y32" s="27" t="n">
-        <f aca="false">1000/100*Q32*($Q$41+$Q$47-$Q$49)-V32</f>
+      <c r="V32" s="26" t="n">
+        <f aca="false">U32/$P32</f>
+        <v>1.84310906465129</v>
+      </c>
+      <c r="W32" s="27" t="n">
+        <f aca="false">R32-U32</f>
+        <v>182.233333333333</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <f aca="false">W32/$P32</f>
+        <v>3.54050500929326</v>
+      </c>
+      <c r="Y32" s="26"/>
+      <c r="Z32" s="26"/>
+      <c r="AA32" s="0" t="n">
+        <f aca="false">Y32+Z32</f>
+        <v>0</v>
+      </c>
+      <c r="AB32" s="26" t="n">
+        <f aca="false">AA32/$P32</f>
+        <v>0</v>
+      </c>
+      <c r="AC32" s="27" t="n">
+        <f aca="false">1000/100*Q32*($Q$41+$Q$47-$Q$49)-AA32</f>
         <v>194.819278854891</v>
       </c>
-      <c r="Z32" s="27" t="n">
-        <f aca="false">Y32-V32+Q32/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD32" s="26" t="n">
+        <f aca="false">AC32/$P32</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE32" s="27" t="n">
+        <f aca="false">AC32+Q32/100*1000 *($Q$46+$Q$43)</f>
         <v>347.955430151418</v>
       </c>
-      <c r="AA32" s="26" t="n">
-        <f aca="false">-V32+($Q$45 + $Q$46)*1000*Q32/100</f>
+      <c r="AF32" s="26" t="n">
+        <f aca="false">AE32/$P32</f>
+        <v>6.76022284687334</v>
+      </c>
+      <c r="AG32" s="26" t="n">
+        <f aca="false">-AA32+($Q$45 + $Q$46)*1000*Q32/100</f>
         <v>159.467331540976</v>
       </c>
-      <c r="AB32" s="26" t="n">
-        <f aca="false">AA32/P32/10</f>
+      <c r="AH32" s="26" t="n">
+        <f aca="false">AG32/P32/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC32" s="26" t="n">
-        <f aca="false">ROUND(AA32/P32 *100/1000, 2)</f>
+      <c r="AI32" s="26" t="n">
+        <f aca="false">ROUND(AG32/P32 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE32" s="26" t="n">
+      <c r="AK32" s="26" t="n">
         <f aca="false">-Q32*($Q$47)*10</f>
         <v>-84.8446735533971</v>
       </c>
-      <c r="AF32" s="26" t="n">
-        <f aca="false">AE32/P32/10</f>
+      <c r="AL32" s="26" t="n">
+        <f aca="false">AK32/P32/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI32" s="23" t="n">
+      <c r="AO32" s="23" t="n">
         <v>70.5</v>
       </c>
-      <c r="AN32" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="AO32" s="23" t="n">
+      <c r="AT32" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="AU32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AP32" s="23" t="n">
+      <c r="AV32" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="AQ32" s="23" t="n">
-        <f aca="false">AO32+AP32/100</f>
+      <c r="AW32" s="23" t="n">
+        <f aca="false">AU32+AV32/100</f>
         <v>0.3</v>
       </c>
-      <c r="AR32" s="23" t="n">
-        <f aca="false">AQ32*1000</f>
+      <c r="AX32" s="23" t="n">
+        <f aca="false">AW32*1000</f>
         <v>300</v>
       </c>
-      <c r="AU32" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="AV32" s="23" t="n">
+      <c r="BA32" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="BB32" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AW32" s="23" t="n">
+      <c r="BC32" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AX32" s="28" t="n">
-        <f aca="false">AV32+AW32/10</f>
+      <c r="BD32" s="28" t="n">
+        <f aca="false">BB32+BC32/10</f>
         <v>1.1</v>
       </c>
-      <c r="AY32" s="28" t="n">
-        <f aca="false">1000*AX32</f>
+      <c r="BE32" s="28" t="n">
+        <f aca="false">1000*BD32</f>
         <v>1100</v>
       </c>
-      <c r="BA32" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="BB32" s="23" t="n">
+      <c r="BG32" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="BH32" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="BC32" s="23" t="n">
+      <c r="BI32" s="23" t="n">
         <v>0.06</v>
       </c>
-      <c r="BD32" s="23" t="n">
+      <c r="BJ32" s="23" t="n">
         <v>0.38</v>
       </c>
-      <c r="BE32" s="23" t="n">
+      <c r="BK32" s="23" t="n">
         <v>0.16</v>
       </c>
-      <c r="BF32" s="23" t="n">
+      <c r="BL32" s="23" t="n">
         <v>0.22</v>
       </c>
-      <c r="BG32" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="BI32" s="28" t="n">
-        <f aca="false">BB32*1000</f>
+      <c r="BM32" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="BO32" s="28" t="n">
+        <f aca="false">BH32*1000</f>
         <v>30</v>
       </c>
-      <c r="BK32" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="BL32" s="23" t="n">
+      <c r="BQ32" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR32" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="BM32" s="23" t="n">
+      <c r="BS32" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="BN32" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO32" s="23" t="n">
+      <c r="BT32" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU32" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="BQ32" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="BR32" s="23" t="n">
+      <c r="BW32" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="BX32" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="BS32" s="23" t="s">
-        <v>189</v>
-      </c>
+      <c r="BY32" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="XFA32" s="0"/>
+      <c r="XFB32" s="0"/>
+      <c r="XFC32" s="0"/>
+      <c r="XFD32" s="0"/>
     </row>
     <row r="33" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B33" s="23" t="n">
         <v>687</v>
@@ -8433,147 +9120,175 @@
         <v>9697.1</v>
       </c>
       <c r="S33" s="26" t="n">
+        <f aca="false">R33/$P33</f>
+        <v>7.99315844787438</v>
+      </c>
+      <c r="T33" s="26" t="n">
         <f aca="false">R33/P33</f>
         <v>7.99315844787438</v>
       </c>
-      <c r="T33" s="26" t="n">
+      <c r="U33" s="27" t="n">
+        <f aca="false">3/5*H33+M33/3</f>
+        <v>2691.4</v>
+      </c>
+      <c r="V33" s="26" t="n">
+        <f aca="false">U33/$P33</f>
+        <v>2.21847631215612</v>
+      </c>
+      <c r="W33" s="27" t="n">
+        <f aca="false">R33-U33</f>
+        <v>7005.7</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <f aca="false">W33/$P33</f>
+        <v>5.77468213571826</v>
+      </c>
+      <c r="Y33" s="26" t="n">
         <f aca="false">B33</f>
         <v>687</v>
       </c>
-      <c r="U33" s="26" t="n">
+      <c r="Z33" s="26" t="n">
         <f aca="false">F33</f>
         <v>240.6</v>
       </c>
-      <c r="V33" s="0" t="n">
-        <f aca="false">T33+U33</f>
+      <c r="AA33" s="0" t="n">
+        <f aca="false">Y33+Z33</f>
         <v>927.6</v>
       </c>
-      <c r="W33" s="27" t="n">
-        <f aca="false">3/5*H33+M33/3</f>
-        <v>2691.4</v>
-      </c>
-      <c r="X33" s="27" t="n">
-        <f aca="false">R33-V33</f>
-        <v>8769.5</v>
-      </c>
-      <c r="Y33" s="27" t="n">
-        <f aca="false">1000/100*Q33*($Q$41+$Q$47-$Q$49)-V33</f>
+      <c r="AB33" s="26" t="n">
+        <f aca="false">AA33/$P33</f>
+        <v>0.76460527129227</v>
+      </c>
+      <c r="AC33" s="27" t="n">
+        <f aca="false">1000/100*Q33*($Q$41+$Q$47-$Q$49)-AA33</f>
         <v>3664.30376376567</v>
       </c>
-      <c r="Z33" s="27" t="n">
-        <f aca="false">Y33-V33+Q33/100*1000 *($Q$46+$Q$43)</f>
-        <v>6346.13335225556</v>
-      </c>
-      <c r="AA33" s="26" t="n">
-        <f aca="false">-V33+($Q$45 + $Q$46)*1000*Q33/100</f>
+      <c r="AD33" s="26" t="n">
+        <f aca="false">AC33/$P33</f>
+        <v>3.0204247233628</v>
+      </c>
+      <c r="AE33" s="27" t="n">
+        <f aca="false">AC33+Q33/100*1000 *($Q$46+$Q$43)</f>
+        <v>7273.73335225556</v>
+      </c>
+      <c r="AF33" s="26" t="n">
+        <f aca="false">AE33/$P33</f>
+        <v>5.99561757558107</v>
+      </c>
+      <c r="AG33" s="26" t="n">
+        <f aca="false">-AA33+($Q$45 + $Q$46)*1000*Q33/100</f>
         <v>2831.05594105852</v>
       </c>
-      <c r="AB33" s="26" t="n">
-        <f aca="false">AA33/P33/10</f>
+      <c r="AH33" s="26" t="n">
+        <f aca="false">AG33/P33/10</f>
         <v>0.233359238449401</v>
       </c>
-      <c r="AC33" s="26" t="n">
-        <f aca="false">ROUND(AA33/P33 *100/1000, 2)</f>
+      <c r="AI33" s="26" t="n">
+        <f aca="false">ROUND(AG33/P33 *100/1000, 2)</f>
         <v>0.23</v>
       </c>
-      <c r="AE33" s="26" t="n">
+      <c r="AK33" s="26" t="n">
         <f aca="false">-Q33*($Q$47)*10</f>
         <v>-1999.79477449715</v>
       </c>
-      <c r="AF33" s="26" t="n">
-        <f aca="false">AE33/P33/10</f>
+      <c r="AL33" s="26" t="n">
+        <f aca="false">AK33/P33/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI33" s="23" t="n">
+      <c r="AO33" s="23" t="n">
         <v>1687.2</v>
       </c>
-      <c r="AN33" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="AO33" s="23" t="n">
+      <c r="AT33" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="AU33" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AP33" s="23" t="n">
+      <c r="AV33" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="AQ33" s="23" t="n">
-        <f aca="false">AO33+AP33/100</f>
+      <c r="AW33" s="23" t="n">
+        <f aca="false">AU33+AV33/100</f>
         <v>9.33</v>
       </c>
-      <c r="AR33" s="23" t="n">
-        <f aca="false">AQ33*1000</f>
+      <c r="AX33" s="23" t="n">
+        <f aca="false">AW33*1000</f>
         <v>9330</v>
       </c>
-      <c r="AU33" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="AV33" s="23" t="n">
+      <c r="BA33" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="BB33" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="AW33" s="23" t="n">
+      <c r="BC33" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="AX33" s="28" t="n">
-        <f aca="false">AV33+AW33/10</f>
+      <c r="BD33" s="28" t="n">
+        <f aca="false">BB33+BC33/10</f>
         <v>30.9</v>
       </c>
-      <c r="AY33" s="28" t="n">
-        <f aca="false">1000*AX33</f>
+      <c r="BE33" s="28" t="n">
+        <f aca="false">1000*BD33</f>
         <v>30900</v>
       </c>
-      <c r="BA33" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="BB33" s="23" t="n">
+      <c r="BG33" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="BH33" s="23" t="n">
         <v>9.33</v>
       </c>
-      <c r="BC33" s="23" t="n">
+      <c r="BI33" s="23" t="n">
         <v>20.74</v>
       </c>
-      <c r="BD33" s="23" t="n">
+      <c r="BJ33" s="23" t="n">
         <v>8.68</v>
       </c>
-      <c r="BE33" s="23" t="n">
+      <c r="BK33" s="23" t="n">
         <v>2.39</v>
       </c>
-      <c r="BF33" s="23" t="n">
+      <c r="BL33" s="23" t="n">
         <v>3.24</v>
       </c>
-      <c r="BG33" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="BI33" s="28" t="n">
-        <f aca="false">BB33*1000</f>
+      <c r="BM33" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="BO33" s="28" t="n">
+        <f aca="false">BH33*1000</f>
         <v>9330</v>
       </c>
-      <c r="BK33" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="BL33" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="BM33" s="23" t="n">
+      <c r="BQ33" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="BR33" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="BS33" s="23" t="n">
         <v>505</v>
       </c>
-      <c r="BN33" s="23" t="n">
+      <c r="BT33" s="23" t="n">
         <v>375</v>
       </c>
-      <c r="BO33" s="23" t="n">
+      <c r="BU33" s="23" t="n">
         <v>687</v>
       </c>
-      <c r="BQ33" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="BR33" s="23" t="n">
+      <c r="BW33" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="BX33" s="23" t="n">
         <v>830</v>
       </c>
-      <c r="BS33" s="23" t="s">
-        <v>106</v>
-      </c>
+      <c r="BY33" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="XFA33" s="0"/>
+      <c r="XFB33" s="0"/>
+      <c r="XFC33" s="0"/>
+      <c r="XFD33" s="0"/>
     </row>
     <row r="34" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B34" s="23" t="n">
         <v>190</v>
@@ -8637,141 +9352,169 @@
         <v>2910.9</v>
       </c>
       <c r="S34" s="26" t="n">
+        <f aca="false">R34/$P34</f>
+        <v>5.26670984877818</v>
+      </c>
+      <c r="T34" s="26" t="n">
         <f aca="false">R34/P34</f>
         <v>5.26670984877818</v>
       </c>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="0" t="n">
-        <f aca="false">T34+U34</f>
-        <v>0</v>
-      </c>
-      <c r="W34" s="27" t="n">
+      <c r="U34" s="27" t="n">
         <f aca="false">3/5*H34+M34/3</f>
         <v>749.066666666667</v>
       </c>
-      <c r="X34" s="27" t="n">
-        <f aca="false">R34-V34</f>
-        <v>2910.9</v>
-      </c>
-      <c r="Y34" s="27" t="n">
-        <f aca="false">1000/100*Q34*($Q$41+$Q$47-$Q$49)-V34</f>
+      <c r="V34" s="26" t="n">
+        <f aca="false">U34/$P34</f>
+        <v>1.35529107517427</v>
+      </c>
+      <c r="W34" s="27" t="n">
+        <f aca="false">R34-U34</f>
+        <v>2161.83333333333</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <f aca="false">W34/$P34</f>
+        <v>3.91141877360391</v>
+      </c>
+      <c r="Y34" s="26"/>
+      <c r="Z34" s="26"/>
+      <c r="AA34" s="0" t="n">
+        <f aca="false">Y34+Z34</f>
+        <v>0</v>
+      </c>
+      <c r="AB34" s="26" t="n">
+        <f aca="false">AA34/$P34</f>
+        <v>0</v>
+      </c>
+      <c r="AC34" s="27" t="n">
+        <f aca="false">1000/100*Q34*($Q$41+$Q$47-$Q$49)-AA34</f>
         <v>2091.97850798587</v>
       </c>
-      <c r="Z34" s="27" t="n">
-        <f aca="false">Y34-V34+Q34/100*1000 *($Q$46+$Q$43)</f>
+      <c r="AD34" s="26" t="n">
+        <f aca="false">AC34/$P34</f>
+        <v>3.78502999465507</v>
+      </c>
+      <c r="AE34" s="27" t="n">
+        <f aca="false">AC34+Q34/100*1000 *($Q$46+$Q$43)</f>
         <v>3736.3616470212</v>
       </c>
-      <c r="AA34" s="26" t="n">
-        <f aca="false">-V34+($Q$45 + $Q$46)*1000*Q34/100</f>
+      <c r="AF34" s="26" t="n">
+        <f aca="false">AE34/$P34</f>
+        <v>6.76022284687333</v>
+      </c>
+      <c r="AG34" s="26" t="n">
+        <f aca="false">-AA34+($Q$45 + $Q$46)*1000*Q34/100</f>
         <v>1712.36764795776</v>
       </c>
-      <c r="AB34" s="26" t="n">
-        <f aca="false">AA34/P34/10</f>
+      <c r="AH34" s="26" t="n">
+        <f aca="false">AG34/P34/10</f>
         <v>0.309819765578628</v>
       </c>
-      <c r="AC34" s="26" t="n">
-        <f aca="false">ROUND(AA34/P34 *100/1000, 2)</f>
+      <c r="AI34" s="26" t="n">
+        <f aca="false">ROUND(AG34/P34 *100/1000, 2)</f>
         <v>0.31</v>
       </c>
-      <c r="AE34" s="26" t="n">
+      <c r="AK34" s="26" t="n">
         <f aca="false">-Q34*($Q$47)*10</f>
         <v>-911.066064067446</v>
       </c>
-      <c r="AF34" s="26" t="n">
-        <f aca="false">AE34/P34/10</f>
+      <c r="AL34" s="26" t="n">
+        <f aca="false">AK34/P34/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AI34" s="23" t="n">
+      <c r="AO34" s="23" t="n">
         <v>601.2</v>
       </c>
-      <c r="AN34" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="AO34" s="23" t="n">
+      <c r="AT34" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="AU34" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AP34" s="23" t="n">
+      <c r="AV34" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="AQ34" s="23" t="n">
-        <f aca="false">AO34+AP34/100</f>
+      <c r="AW34" s="23" t="n">
+        <f aca="false">AU34+AV34/100</f>
         <v>1.16</v>
       </c>
-      <c r="AR34" s="23" t="n">
-        <f aca="false">AQ34*1000</f>
+      <c r="AX34" s="23" t="n">
+        <f aca="false">AW34*1000</f>
         <v>1160</v>
       </c>
-      <c r="AU34" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="AV34" s="23" t="n">
+      <c r="BA34" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="BB34" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="AW34" s="23" t="n">
+      <c r="BC34" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="AX34" s="28" t="n">
-        <f aca="false">AV34+AW34/10</f>
+      <c r="BD34" s="28" t="n">
+        <f aca="false">BB34+BC34/10</f>
         <v>7.1</v>
       </c>
-      <c r="AY34" s="28" t="n">
-        <f aca="false">1000*AX34</f>
+      <c r="BE34" s="28" t="n">
+        <f aca="false">1000*BD34</f>
         <v>7100</v>
       </c>
-      <c r="BA34" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="BB34" s="23" t="n">
+      <c r="BG34" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="BH34" s="23" t="n">
         <v>1.16</v>
       </c>
-      <c r="BC34" s="23" t="n">
+      <c r="BI34" s="23" t="n">
         <v>2.58</v>
       </c>
-      <c r="BD34" s="23" t="n">
+      <c r="BJ34" s="23" t="n">
         <v>3.23</v>
       </c>
-      <c r="BE34" s="23" t="n">
+      <c r="BK34" s="23" t="n">
         <v>0.8</v>
       </c>
-      <c r="BF34" s="23" t="n">
+      <c r="BL34" s="23" t="n">
         <v>1.08</v>
       </c>
-      <c r="BG34" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="BI34" s="28" t="n">
-        <f aca="false">BB34*1000</f>
+      <c r="BM34" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="BO34" s="28" t="n">
+        <f aca="false">BH34*1000</f>
         <v>1160</v>
       </c>
-      <c r="BK34" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="BL34" s="23" t="n">
+      <c r="BQ34" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="BR34" s="23" t="n">
         <v>270</v>
       </c>
-      <c r="BM34" s="23" t="n">
+      <c r="BS34" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="BN34" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO34" s="23" t="n">
+      <c r="BT34" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU34" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="BQ34" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="BR34" s="23" t="n">
+      <c r="BW34" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="BX34" s="23" t="n">
         <v>601</v>
       </c>
-      <c r="BS34" s="23" t="s">
-        <v>201</v>
-      </c>
+      <c r="BY34" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="XFA34" s="0"/>
+      <c r="XFB34" s="0"/>
+      <c r="XFC34" s="0"/>
+      <c r="XFD34" s="0"/>
     </row>
     <row r="35" s="38" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="33" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B35" s="34" t="n">
         <v>5880</v>
@@ -8801,7 +9544,10 @@
       </c>
       <c r="N35" s="26"/>
       <c r="O35" s="23"/>
-      <c r="P35" s="26"/>
+      <c r="P35" s="2" t="n">
+        <f aca="false">SUM(P8:P34)</f>
+        <v>14559.594</v>
+      </c>
       <c r="Q35" s="37" t="n">
         <v>100</v>
       </c>
@@ -8809,61 +9555,88 @@
         <f aca="false">H35+F35+B35+D35+J35+M35</f>
         <v>98422.2</v>
       </c>
-      <c r="S35" s="26"/>
-      <c r="T35" s="23" t="n">
-        <f aca="false">SUM(T8:T34)</f>
-        <v>2339.220378624</v>
-      </c>
-      <c r="U35" s="23" t="n">
-        <f aca="false">SUM(U8:U34)</f>
-        <v>4210.3</v>
-      </c>
-      <c r="V35" s="26" t="n">
-        <f aca="false">SUM(V8:V34)</f>
-        <v>6549.520378624</v>
-      </c>
-      <c r="W35" s="27" t="n">
+      <c r="S35" s="26" t="n">
+        <f aca="false">R35/$P35</f>
+        <v>6.75995498226118</v>
+      </c>
+      <c r="T35" s="26"/>
+      <c r="U35" s="27" t="n">
         <f aca="false">3/5*H35+M35/3</f>
         <v>29317.6</v>
       </c>
-      <c r="X35" s="27" t="n">
-        <f aca="false">R35-V35</f>
-        <v>91872.679621376</v>
-      </c>
-      <c r="Y35" s="27" t="n">
-        <f aca="false">1000/100*Q35*($Q$41+$Q$47-$Q$49)-V35</f>
+      <c r="V35" s="26" t="n">
+        <f aca="false">U35/$P35</f>
+        <v>2.01362757780196</v>
+      </c>
+      <c r="W35" s="27" t="n">
+        <f aca="false">R35-U35</f>
+        <v>69104.6</v>
+      </c>
+      <c r="X35" s="26" t="n">
+        <f aca="false">W35/$P35</f>
+        <v>4.74632740445922</v>
+      </c>
+      <c r="Y35" s="23" t="n">
+        <f aca="false">SUM(Y8:Y34)</f>
+        <v>2339.220378624</v>
+      </c>
+      <c r="Z35" s="23" t="n">
+        <f aca="false">SUM(Z8:Z34)</f>
+        <v>4210.3</v>
+      </c>
+      <c r="AA35" s="0" t="n">
+        <f aca="false">Y35+Z35</f>
+        <v>6549.520378624</v>
+      </c>
+      <c r="AB35" s="26" t="n">
+        <f aca="false">AA35/$P35</f>
+        <v>0.449842240011912</v>
+      </c>
+      <c r="AC35" s="27" t="n">
+        <f aca="false">1000/100*Q35*($Q$41+$Q$47-$Q$49)-AA35</f>
         <v>48558.979621376</v>
       </c>
-      <c r="Z35" s="27" t="n">
-        <f aca="false">Y35-V35+Q35/100*1000 *($Q$46+$Q$43)</f>
-        <v>85327.059242752</v>
-      </c>
-      <c r="AA35" s="26" t="n">
-        <f aca="false">SUM(AA8:AA34)</f>
+      <c r="AD35" s="26" t="n">
+        <f aca="false">AC35/$P35</f>
+        <v>3.33518775464316</v>
+      </c>
+      <c r="AE35" s="27" t="n">
+        <f aca="false">AC35+Q35/100*1000 *($Q$46+$Q$43)</f>
+        <v>91876.579621376</v>
+      </c>
+      <c r="AF35" s="26" t="n">
+        <f aca="false">AE35/$P35</f>
+        <v>6.31038060686143</v>
+      </c>
+      <c r="AG35" s="26" t="n">
+        <f aca="false">SUM(AG8:AG34)</f>
         <v>38558.979621376</v>
       </c>
-      <c r="AB35" s="23"/>
-      <c r="AC35" s="38" t="e">
-        <f aca="false">ROUND(AA35/P35 *100/1000, 2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE35" s="26" t="n">
+      <c r="AH35" s="23"/>
+      <c r="AI35" s="38" t="n">
+        <f aca="false">ROUND(AG35/P35 *100/1000, 2)</f>
+        <v>0.26</v>
+      </c>
+      <c r="AK35" s="26" t="n">
         <f aca="false">-Q35*($Q$47)*10</f>
         <v>-24000</v>
       </c>
-      <c r="AF35" s="26"/>
-      <c r="AI35" s="38" t="n">
+      <c r="AL35" s="26"/>
+      <c r="AO35" s="38" t="n">
         <v>18796</v>
-      </c>
-      <c r="AR35" s="38" t="n">
-        <f aca="false">SUM(AR8:AR34)</f>
-        <v>47600</v>
       </c>
       <c r="AX35" s="38" t="n">
         <f aca="false">SUM(AX8:AX34)</f>
+        <v>47600</v>
+      </c>
+      <c r="BD35" s="38" t="n">
+        <f aca="false">SUM(BD8:BD34)</f>
         <v>299.1</v>
       </c>
-      <c r="XFD35" s="23"/>
+      <c r="XFA35" s="0"/>
+      <c r="XFB35" s="0"/>
+      <c r="XFC35" s="0"/>
+      <c r="XFD35" s="0"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="n">
@@ -8908,9 +9681,9 @@
         <f aca="false">SUM(R8:R34)</f>
         <v>98426.1</v>
       </c>
-      <c r="S36" s="2"/>
       <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J37" s="39" t="n">
@@ -8924,7 +9697,7 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="41" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C38" s="42" t="n">
         <f aca="false">SUM(B35:M35)</f>
@@ -8933,14 +9706,14 @@
       <c r="D38" s="42"/>
       <c r="E38" s="42"/>
       <c r="J38" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="M38" s="43" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="N38" s="44"/>
-      <c r="V38" s="1" t="s">
-        <v>206</v>
+      <c r="AA38" s="1" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8948,8 +9721,8 @@
       <c r="C39" s="42"/>
       <c r="D39" s="42"/>
       <c r="E39" s="42"/>
-      <c r="V39" s="1" t="s">
-        <v>207</v>
+      <c r="AA39" s="1" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8958,7 +9731,7 @@
       <c r="D40" s="42"/>
       <c r="E40" s="42"/>
       <c r="P40" s="45" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Q40" s="46" t="n">
         <v>192.8</v>
@@ -8967,19 +9740,25 @@
       <c r="S40" s="43"/>
       <c r="T40" s="43"/>
       <c r="U40" s="43"/>
-      <c r="V40" s="43" t="s">
-        <v>209</v>
-      </c>
+      <c r="V40" s="43"/>
       <c r="W40" s="43"/>
       <c r="X40" s="43"/>
       <c r="Y40" s="43"/>
       <c r="Z40" s="43"/>
-      <c r="AA40" s="43"/>
+      <c r="AA40" s="43" t="s">
+        <v>204</v>
+      </c>
       <c r="AB40" s="43"/>
+      <c r="AC40" s="43"/>
+      <c r="AD40" s="43"/>
+      <c r="AE40" s="43"/>
+      <c r="AF40" s="43"/>
+      <c r="AG40" s="43"/>
+      <c r="AH40" s="43"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P41" s="45" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="Q41" s="45" t="n">
         <f aca="false">Q40*0.7</f>
@@ -8996,6 +9775,12 @@
       <c r="Z41" s="43"/>
       <c r="AA41" s="43"/>
       <c r="AB41" s="43"/>
+      <c r="AC41" s="43"/>
+      <c r="AD41" s="43"/>
+      <c r="AE41" s="43"/>
+      <c r="AF41" s="43"/>
+      <c r="AG41" s="43"/>
+      <c r="AH41" s="43"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P42" s="45"/>
@@ -9011,13 +9796,19 @@
       <c r="Z42" s="43"/>
       <c r="AA42" s="43"/>
       <c r="AB42" s="43"/>
+      <c r="AC42" s="43"/>
+      <c r="AD42" s="43"/>
+      <c r="AE42" s="43"/>
+      <c r="AF42" s="43"/>
+      <c r="AG42" s="43"/>
+      <c r="AH42" s="43"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P43" s="47" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Q43" s="48" t="n">
-        <f aca="false">W35/1000</f>
+        <f aca="false">U35/1000</f>
         <v>29.3176</v>
       </c>
       <c r="R43" s="43"/>
@@ -9031,10 +9822,16 @@
       <c r="Z43" s="43"/>
       <c r="AA43" s="43"/>
       <c r="AB43" s="43"/>
+      <c r="AC43" s="43"/>
+      <c r="AD43" s="43"/>
+      <c r="AE43" s="43"/>
+      <c r="AF43" s="43"/>
+      <c r="AG43" s="43"/>
+      <c r="AH43" s="43"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P44" s="47" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="Q44" s="47" t="n">
         <f aca="false">R36/1000 -Q43</f>
@@ -9051,10 +9848,16 @@
       <c r="Z44" s="43"/>
       <c r="AA44" s="43"/>
       <c r="AB44" s="43"/>
+      <c r="AC44" s="43"/>
+      <c r="AD44" s="43"/>
+      <c r="AE44" s="43"/>
+      <c r="AF44" s="43"/>
+      <c r="AG44" s="43"/>
+      <c r="AH44" s="43"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P45" s="47" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="Q45" s="47" t="n">
         <f aca="false">Q44-Q46-Q47</f>
@@ -9071,10 +9874,16 @@
       <c r="Z45" s="43"/>
       <c r="AA45" s="43"/>
       <c r="AB45" s="43"/>
+      <c r="AC45" s="43"/>
+      <c r="AD45" s="43"/>
+      <c r="AE45" s="43"/>
+      <c r="AF45" s="43"/>
+      <c r="AG45" s="43"/>
+      <c r="AH45" s="43"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P46" s="47" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="Q46" s="48" t="n">
         <v>14</v>
@@ -9090,10 +9899,16 @@
       <c r="Z46" s="43"/>
       <c r="AA46" s="43"/>
       <c r="AB46" s="43"/>
+      <c r="AC46" s="43"/>
+      <c r="AD46" s="43"/>
+      <c r="AE46" s="43"/>
+      <c r="AF46" s="43"/>
+      <c r="AG46" s="43"/>
+      <c r="AH46" s="43"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P47" s="47" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="Q47" s="48" t="n">
         <v>24</v>
@@ -9109,6 +9924,12 @@
       <c r="Z47" s="43"/>
       <c r="AA47" s="43"/>
       <c r="AB47" s="43"/>
+      <c r="AC47" s="43"/>
+      <c r="AD47" s="43"/>
+      <c r="AE47" s="43"/>
+      <c r="AF47" s="43"/>
+      <c r="AG47" s="43"/>
+      <c r="AH47" s="43"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="43"/>
@@ -9120,7 +9941,7 @@
       <c r="H48" s="43"/>
       <c r="I48" s="43"/>
       <c r="P48" s="47" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Q48" s="47" t="n">
         <f aca="false">Q40+Q46</f>
@@ -9137,6 +9958,12 @@
       <c r="Z48" s="43"/>
       <c r="AA48" s="43"/>
       <c r="AB48" s="43"/>
+      <c r="AC48" s="43"/>
+      <c r="AD48" s="43"/>
+      <c r="AE48" s="43"/>
+      <c r="AF48" s="43"/>
+      <c r="AG48" s="43"/>
+      <c r="AH48" s="43"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="43"/>
@@ -9148,7 +9975,7 @@
       <c r="H49" s="43"/>
       <c r="I49" s="43"/>
       <c r="P49" s="47" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="Q49" s="47" t="n">
         <f aca="false">Q41-Q45</f>
@@ -9165,6 +9992,12 @@
       <c r="Z49" s="43"/>
       <c r="AA49" s="43"/>
       <c r="AB49" s="43"/>
+      <c r="AC49" s="43"/>
+      <c r="AD49" s="43"/>
+      <c r="AE49" s="43"/>
+      <c r="AF49" s="43"/>
+      <c r="AG49" s="43"/>
+      <c r="AH49" s="43"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="43"/>
@@ -9176,7 +10009,7 @@
       <c r="H50" s="43"/>
       <c r="I50" s="43"/>
       <c r="P50" s="47" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="Q50" s="49" t="n">
         <f aca="false">Q49/Q48</f>
@@ -9193,16 +10026,22 @@
       <c r="Z50" s="43"/>
       <c r="AA50" s="43"/>
       <c r="AB50" s="43"/>
+      <c r="AC50" s="43"/>
+      <c r="AD50" s="43"/>
+      <c r="AE50" s="43"/>
+      <c r="AF50" s="43"/>
+      <c r="AG50" s="43"/>
+      <c r="AH50" s="43"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="50"/>
-      <c r="AA53" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="AE53" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AF53" s="1"/>
+      <c r="AG53" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK53" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AL53" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="50"/>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -2583,11 +2583,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="9513269"/>
-        <c:axId val="92381258"/>
+        <c:axId val="38914575"/>
+        <c:axId val="51911800"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9513269"/>
+        <c:axId val="38914575"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,7 +2619,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92381258"/>
+        <c:crossAx val="51911800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2627,7 +2627,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92381258"/>
+        <c:axId val="51911800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2668,7 +2668,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9513269"/>
+        <c:crossAx val="38914575"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3442,8 +3442,8 @@
         <v>2951.1</v>
       </c>
       <c r="S8" s="26" t="n">
-        <f aca="false">R8/$P8</f>
-        <v>7.23354919676254</v>
+        <f aca="false">R8/$P8/1000*100</f>
+        <v>0.723354919676254</v>
       </c>
       <c r="T8" s="26" t="n">
         <f aca="false">R8/P8</f>
@@ -3454,16 +3454,16 @@
         <v>1000.8</v>
       </c>
       <c r="V8" s="26" t="n">
-        <f aca="false">U8/$P8</f>
-        <v>2.45309750131136</v>
+        <f aca="false">U8/$P8/1000*100</f>
+        <v>0.245309750131136</v>
       </c>
       <c r="W8" s="27" t="n">
         <f aca="false">R8-U8</f>
         <v>1950.3</v>
       </c>
       <c r="X8" s="26" t="n">
-        <f aca="false">W8/$P8</f>
-        <v>4.78045169545118</v>
+        <f aca="false">W8/$P8/1000*100</f>
+        <v>0.478045169545118</v>
       </c>
       <c r="Y8" s="23" t="n">
         <f aca="false">124*(1.08)^4*3/5</f>
@@ -3475,24 +3475,24 @@
         <v>101.220378624</v>
       </c>
       <c r="AB8" s="26" t="n">
-        <f aca="false">AA8/$P8</f>
-        <v>0.2481049739052</v>
+        <f aca="false">AA8/$P8/1000*100</f>
+        <v>0.02481049739052</v>
       </c>
       <c r="AC8" s="27" t="n">
         <f aca="false">1000/100*Q8*($Q$41+$Q$47-$Q$49)-AA8</f>
         <v>1442.97344841541</v>
       </c>
       <c r="AD8" s="26" t="n">
-        <f aca="false">AC8/$P8</f>
-        <v>3.53692502074988</v>
+        <f aca="false">AC8/$P8/1000*100</f>
+        <v>0.353692502074988</v>
       </c>
       <c r="AE8" s="27" t="n">
         <f aca="false">AC8+Q8/100*1000 *($Q$46+$Q$43)</f>
         <v>2656.77477710631</v>
       </c>
       <c r="AF8" s="26" t="n">
-        <f aca="false">AE8/$P8</f>
-        <v>6.51211787296815</v>
+        <f aca="false">AE8/$P8/1000*100</f>
+        <v>0.651211787296815</v>
       </c>
       <c r="AG8" s="26" t="n">
         <f aca="false">-Y8+($Q$45 + $Q$46)*1000*Q8/100</f>
@@ -3671,8 +3671,8 @@
         <v>2687.9</v>
       </c>
       <c r="S9" s="26" t="n">
-        <f aca="false">R9/$P9</f>
-        <v>5.30199621271895</v>
+        <f aca="false">R9/$P9/1000*100</f>
+        <v>0.530199621271895</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">R9/P9</f>
@@ -3683,16 +3683,16 @@
         <v>877.466666666667</v>
       </c>
       <c r="V9" s="26" t="n">
-        <f aca="false">U9/$P9</f>
-        <v>1.73084003997686</v>
+        <f aca="false">U9/$P9/1000*100</f>
+        <v>0.173084003997686</v>
       </c>
       <c r="W9" s="27" t="n">
         <f aca="false">R9-U9</f>
         <v>1810.43333333333</v>
       </c>
       <c r="X9" s="26" t="n">
-        <f aca="false">W9/$P9</f>
-        <v>3.5711561727421</v>
+        <f aca="false">W9/$P9/1000*100</f>
+        <v>0.35711561727421</v>
       </c>
       <c r="Y9" s="26"/>
       <c r="Z9" s="31" t="n">
@@ -3704,24 +3704,24 @@
         <v>61.1</v>
       </c>
       <c r="AB9" s="26" t="n">
-        <f aca="false">AA9/$P9</f>
-        <v>0.120522329177844</v>
+        <f aca="false">AA9/$P9/1000*100</f>
+        <v>0.0120522329177844</v>
       </c>
       <c r="AC9" s="27" t="n">
         <f aca="false">1000/100*Q9*($Q$41+$Q$47-$Q$49)-AA9</f>
         <v>1857.75880609034</v>
       </c>
       <c r="AD9" s="26" t="n">
-        <f aca="false">AC9/$P9</f>
-        <v>3.66450766547723</v>
+        <f aca="false">AC9/$P9/1000*100</f>
+        <v>0.366450766547723</v>
       </c>
       <c r="AE9" s="27" t="n">
         <f aca="false">AC9+Q9/100*1000 *($Q$46+$Q$43)</f>
         <v>3366.06257445091</v>
       </c>
       <c r="AF9" s="26" t="n">
-        <f aca="false">AE9/$P9</f>
-        <v>6.6397005176955</v>
+        <f aca="false">AE9/$P9/1000*100</f>
+        <v>0.66397005176955</v>
       </c>
       <c r="AG9" s="26" t="n">
         <f aca="false">-Z9+($Q$45 + $Q$46)*1000*Q9/100</f>
@@ -3900,8 +3900,8 @@
         <v>359.7</v>
       </c>
       <c r="S10" s="26" t="n">
-        <f aca="false">R10/$P10</f>
-        <v>6.87224164612827</v>
+        <f aca="false">R10/$P10/1000*100</f>
+        <v>0.687224164612827</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">R10/P10</f>
@@ -3912,16 +3912,16 @@
         <v>96.5333333333333</v>
       </c>
       <c r="V10" s="26" t="n">
-        <f aca="false">U10/$P10</f>
-        <v>1.84431580086994</v>
+        <f aca="false">U10/$P10/1000*100</f>
+        <v>0.184431580086994</v>
       </c>
       <c r="W10" s="27" t="n">
         <f aca="false">R10-U10</f>
         <v>263.166666666667</v>
       </c>
       <c r="X10" s="26" t="n">
-        <f aca="false">W10/$P10</f>
-        <v>5.02792584525834</v>
+        <f aca="false">W10/$P10/1000*100</f>
+        <v>0.502792584525834</v>
       </c>
       <c r="Y10" s="26"/>
       <c r="Z10" s="26"/>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <f aca="false">AA10/$P10</f>
+        <f aca="false">AA10/$P10/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC10" s="27" t="n">
@@ -3938,16 +3938,16 @@
         <v>198.112254950241</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <f aca="false">AC10/$P10</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC10/$P10/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE10" s="27" t="n">
         <f aca="false">AC10+Q10/100*1000 *($Q$46+$Q$43)</f>
         <v>353.836824028197</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <f aca="false">AE10/$P10</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE10/$P10/1000*100</f>
+        <v>0.676022284687334</v>
       </c>
       <c r="AG10" s="26" t="n">
         <f aca="false">-AA10+($Q$45 + $Q$46)*1000*Q10/100</f>
@@ -4126,8 +4126,8 @@
         <v>485.7</v>
       </c>
       <c r="S11" s="26" t="n">
-        <f aca="false">R11/$P11</f>
-        <v>8.30710816172949</v>
+        <f aca="false">R11/$P11/1000*100</f>
+        <v>0.830710816172949</v>
       </c>
       <c r="T11" s="26" t="n">
         <f aca="false">R11/P11</f>
@@ -4138,16 +4138,16 @@
         <v>125.866666666667</v>
       </c>
       <c r="V11" s="26" t="n">
-        <f aca="false">U11/$P11</f>
-        <v>2.15274452121958</v>
+        <f aca="false">U11/$P11/1000*100</f>
+        <v>0.215274452121958</v>
       </c>
       <c r="W11" s="27" t="n">
         <f aca="false">R11-U11</f>
         <v>359.833333333333</v>
       </c>
       <c r="X11" s="26" t="n">
-        <f aca="false">W11/$P11</f>
-        <v>6.15436364050991</v>
+        <f aca="false">W11/$P11/1000*100</f>
+        <v>0.615436364050991</v>
       </c>
       <c r="Y11" s="26"/>
       <c r="Z11" s="26"/>
@@ -4156,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="26" t="n">
-        <f aca="false">AA11/$P11</f>
+        <f aca="false">AA11/$P11/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC11" s="27" t="n">
@@ -4164,16 +4164,16 @@
         <v>221.303133727493</v>
       </c>
       <c r="AD11" s="26" t="n">
-        <f aca="false">AC11/$P11</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC11/$P11/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE11" s="27" t="n">
         <f aca="false">AC11+Q11/100*1000 *($Q$46+$Q$43)</f>
         <v>395.25670941099</v>
       </c>
       <c r="AF11" s="26" t="n">
-        <f aca="false">AE11/$P11</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE11/$P11/1000*100</f>
+        <v>0.676022284687334</v>
       </c>
       <c r="AG11" s="26" t="n">
         <f aca="false">-AA11+($Q$45 + $Q$46)*1000*Q11/100</f>
@@ -4352,8 +4352,8 @@
         <v>333.1</v>
       </c>
       <c r="S12" s="26" t="n">
-        <f aca="false">R12/$P12</f>
-        <v>15.1477944520237</v>
+        <f aca="false">R12/$P12/1000*100</f>
+        <v>1.51477944520237</v>
       </c>
       <c r="T12" s="26" t="n">
         <f aca="false">R12/P12</f>
@@ -4364,16 +4364,16 @@
         <v>95.6</v>
       </c>
       <c r="V12" s="26" t="n">
-        <f aca="false">U12/$P12</f>
-        <v>4.34743065029559</v>
+        <f aca="false">U12/$P12/1000*100</f>
+        <v>0.434743065029559</v>
       </c>
       <c r="W12" s="27" t="n">
         <f aca="false">R12-U12</f>
         <v>237.5</v>
       </c>
       <c r="X12" s="26" t="n">
-        <f aca="false">W12/$P12</f>
-        <v>10.8003638017281</v>
+        <f aca="false">W12/$P12/1000*100</f>
+        <v>1.08003638017281</v>
       </c>
       <c r="Y12" s="26"/>
       <c r="Z12" s="26"/>
@@ -4382,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="AB12" s="26" t="n">
-        <f aca="false">AA12/$P12</f>
+        <f aca="false">AA12/$P12/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC12" s="27" t="n">
@@ -4390,16 +4390,16 @@
         <v>83.2328095824651</v>
       </c>
       <c r="AD12" s="26" t="n">
-        <f aca="false">AC12/$P12</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC12/$P12/1000*100</f>
+        <v>0.378502999465508</v>
       </c>
       <c r="AE12" s="27" t="n">
         <f aca="false">AC12+Q12/100*1000 *($Q$46+$Q$43)</f>
         <v>148.657300402745</v>
       </c>
       <c r="AF12" s="26" t="n">
-        <f aca="false">AE12/$P12</f>
-        <v>6.76022284687335</v>
+        <f aca="false">AE12/$P12/1000*100</f>
+        <v>0.676022284687335</v>
       </c>
       <c r="AG12" s="26" t="n">
         <f aca="false">-AA12+($Q$45 + $Q$46)*1000*Q12/100</f>
@@ -4578,8 +4578,8 @@
         <v>1493.2</v>
       </c>
       <c r="S13" s="26" t="n">
-        <f aca="false">R13/$P13</f>
-        <v>6.56141106370264</v>
+        <f aca="false">R13/$P13/1000*100</f>
+        <v>0.656141106370264</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">R13/P13</f>
@@ -4590,16 +4590,16 @@
         <v>417.333333333333</v>
       </c>
       <c r="V13" s="26" t="n">
-        <f aca="false">U13/$P13</f>
-        <v>1.83384379224835</v>
+        <f aca="false">U13/$P13/1000*100</f>
+        <v>0.183384379224835</v>
       </c>
       <c r="W13" s="27" t="n">
         <f aca="false">R13-U13</f>
         <v>1075.86666666667</v>
       </c>
       <c r="X13" s="26" t="n">
-        <f aca="false">W13/$P13</f>
-        <v>4.72756727145429</v>
+        <f aca="false">W13/$P13/1000*100</f>
+        <v>0.472756727145429</v>
       </c>
       <c r="Y13" s="26"/>
       <c r="Z13" s="26"/>
@@ -4608,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <f aca="false">AA13/$P13</f>
+        <f aca="false">AA13/$P13/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC13" s="27" t="n">
@@ -4616,16 +4616,16 @@
         <v>861.370630973638</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <f aca="false">AC13/$P13</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC13/$P13/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE13" s="27" t="n">
         <f aca="false">AC13+Q13/100*1000 *($Q$46+$Q$43)</f>
         <v>1538.44419393151</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <f aca="false">AE13/$P13</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE13/$P13/1000*100</f>
+        <v>0.676022284687334</v>
       </c>
       <c r="AG13" s="26" t="n">
         <f aca="false">-AA13+($Q$45 + $Q$46)*1000*Q13/100</f>
@@ -4804,8 +4804,8 @@
         <v>1776.1</v>
       </c>
       <c r="S14" s="26" t="n">
-        <f aca="false">R14/$P14</f>
-        <v>5.09837354965754</v>
+        <f aca="false">R14/$P14/1000*100</f>
+        <v>0.509837354965754</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">R14/P14</f>
@@ -4816,16 +4816,16 @@
         <v>510.2</v>
       </c>
       <c r="V14" s="26" t="n">
-        <f aca="false">U14/$P14</f>
-        <v>1.46455164970175</v>
+        <f aca="false">U14/$P14/1000*100</f>
+        <v>0.146455164970175</v>
       </c>
       <c r="W14" s="27" t="n">
         <f aca="false">R14-U14</f>
         <v>1265.9</v>
       </c>
       <c r="X14" s="26" t="n">
-        <f aca="false">W14/$P14</f>
-        <v>3.63382189995579</v>
+        <f aca="false">W14/$P14/1000*100</f>
+        <v>0.363382189995579</v>
       </c>
       <c r="Y14" s="26"/>
       <c r="Z14" s="26"/>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="AB14" s="26" t="n">
-        <f aca="false">AA14/$P14</f>
+        <f aca="false">AA14/$P14/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC14" s="27" t="n">
@@ -4842,16 +4842,16 @@
         <v>1318.57575911801</v>
       </c>
       <c r="AD14" s="26" t="n">
-        <f aca="false">AC14/$P14</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC14/$P14/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE14" s="27" t="n">
         <f aca="false">AC14+Q14/100*1000 *($Q$46+$Q$43)</f>
         <v>2355.03179227388</v>
       </c>
       <c r="AF14" s="26" t="n">
-        <f aca="false">AE14/$P14</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE14/$P14/1000*100</f>
+        <v>0.676022284687335</v>
       </c>
       <c r="AG14" s="26" t="n">
         <f aca="false">-AA14+($Q$45 + $Q$46)*1000*Q14/100</f>
@@ -5030,8 +5030,8 @@
         <v>156.4</v>
       </c>
       <c r="S15" s="26" t="n">
-        <f aca="false">R15/$P15</f>
-        <v>5.0616524806628</v>
+        <f aca="false">R15/$P15/1000*100</f>
+        <v>0.506165248066281</v>
       </c>
       <c r="T15" s="26" t="n">
         <f aca="false">R15/P15</f>
@@ -5042,16 +5042,16 @@
         <v>40.0666666666667</v>
       </c>
       <c r="V15" s="26" t="n">
-        <f aca="false">U15/$P15</f>
-        <v>1.29669784351166</v>
+        <f aca="false">U15/$P15/1000*100</f>
+        <v>0.129669784351166</v>
       </c>
       <c r="W15" s="27" t="n">
         <f aca="false">R15-U15</f>
         <v>116.333333333333</v>
       </c>
       <c r="X15" s="26" t="n">
-        <f aca="false">W15/$P15</f>
-        <v>3.76495463715115</v>
+        <f aca="false">W15/$P15/1000*100</f>
+        <v>0.376495463715115</v>
       </c>
       <c r="Y15" s="26"/>
       <c r="Z15" s="26"/>
@@ -5060,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="26" t="n">
-        <f aca="false">AA15/$P15</f>
+        <f aca="false">AA15/$P15/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC15" s="27" t="n">
@@ -5068,16 +5068,16 @@
         <v>116.953641804847</v>
       </c>
       <c r="AD15" s="26" t="n">
-        <f aca="false">AC15/$P15</f>
-        <v>3.78502999465506</v>
+        <f aca="false">AC15/$P15/1000*100</f>
+        <v>0.378502999465506</v>
       </c>
       <c r="AE15" s="27" t="n">
         <f aca="false">AC15+Q15/100*1000 *($Q$46+$Q$43)</f>
         <v>208.884125745539</v>
       </c>
       <c r="AF15" s="26" t="n">
-        <f aca="false">AE15/$P15</f>
-        <v>6.76022284687333</v>
+        <f aca="false">AE15/$P15/1000*100</f>
+        <v>0.676022284687333</v>
       </c>
       <c r="AG15" s="26" t="n">
         <f aca="false">-AA15+($Q$45 + $Q$46)*1000*Q15/100</f>
@@ -5256,8 +5256,8 @@
         <v>980.1</v>
       </c>
       <c r="S16" s="26" t="n">
-        <f aca="false">R16/$P16</f>
-        <v>3.8374046130294</v>
+        <f aca="false">R16/$P16/1000*100</f>
+        <v>0.38374046130294</v>
       </c>
       <c r="T16" s="26" t="n">
         <f aca="false">R16/P16</f>
@@ -5268,16 +5268,16 @@
         <v>222.666666666667</v>
       </c>
       <c r="V16" s="26" t="n">
-        <f aca="false">U16/$P16</f>
-        <v>0.871811135429595</v>
+        <f aca="false">U16/$P16/1000*100</f>
+        <v>0.0871811135429595</v>
       </c>
       <c r="W16" s="27" t="n">
         <f aca="false">R16-U16</f>
         <v>757.433333333333</v>
       </c>
       <c r="X16" s="26" t="n">
-        <f aca="false">W16/$P16</f>
-        <v>2.9655934775998</v>
+        <f aca="false">W16/$P16/1000*100</f>
+        <v>0.29655934775998</v>
       </c>
       <c r="Y16" s="26"/>
       <c r="Z16" s="26"/>
@@ -5286,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="AB16" s="26" t="n">
-        <f aca="false">AA16/$P16</f>
+        <f aca="false">AA16/$P16/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC16" s="27" t="n">
@@ -5294,16 +5294,16 @@
         <v>966.723155844868</v>
       </c>
       <c r="AD16" s="26" t="n">
-        <f aca="false">AC16/$P16</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC16/$P16/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE16" s="27" t="n">
         <f aca="false">AC16+Q16/100*1000 *($Q$46+$Q$43)</f>
         <v>1726.60823665138</v>
       </c>
       <c r="AF16" s="26" t="n">
-        <f aca="false">AE16/$P16</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE16/$P16/1000*100</f>
+        <v>0.676022284687334</v>
       </c>
       <c r="AG16" s="26" t="n">
         <f aca="false">-AA16+($Q$45 + $Q$46)*1000*Q16/100</f>
@@ -5482,8 +5482,8 @@
         <v>21891.6</v>
       </c>
       <c r="S17" s="26" t="n">
-        <f aca="false">R17/$P17</f>
-        <v>8.50263566325032</v>
+        <f aca="false">R17/$P17/1000*100</f>
+        <v>0.850263566325032</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">R17/P17</f>
@@ -5494,16 +5494,16 @@
         <v>6812.66666666667</v>
       </c>
       <c r="V17" s="26" t="n">
-        <f aca="false">U17/$P17</f>
-        <v>2.64602050840673</v>
+        <f aca="false">U17/$P17/1000*100</f>
+        <v>0.264602050840673</v>
       </c>
       <c r="W17" s="27" t="n">
         <f aca="false">R17-U17</f>
         <v>15078.9333333333</v>
       </c>
       <c r="X17" s="26" t="n">
-        <f aca="false">W17/$P17</f>
-        <v>5.8566151548436</v>
+        <f aca="false">W17/$P17/1000*100</f>
+        <v>0.58566151548436</v>
       </c>
       <c r="Y17" s="26" t="n">
         <f aca="false">B17</f>
@@ -5518,24 +5518,24 @@
         <v>4184</v>
       </c>
       <c r="AB17" s="26" t="n">
-        <f aca="false">AA17/$P17</f>
-        <v>1.62505379300916</v>
+        <f aca="false">AA17/$P17/1000*100</f>
+        <v>0.162505379300916</v>
       </c>
       <c r="AC17" s="27" t="n">
         <f aca="false">1000/100*Q17*($Q$41+$Q$47-$Q$49)-AA17</f>
         <v>5561.25616675849</v>
       </c>
       <c r="AD17" s="26" t="n">
-        <f aca="false">AC17/$P17</f>
-        <v>2.15997620164591</v>
+        <f aca="false">AC17/$P17/1000*100</f>
+        <v>0.215997620164591</v>
       </c>
       <c r="AE17" s="27" t="n">
         <f aca="false">AC17+Q17/100*1000 *($Q$46+$Q$43)</f>
         <v>13221.4376002792</v>
       </c>
       <c r="AF17" s="26" t="n">
-        <f aca="false">AE17/$P17</f>
-        <v>5.13516905386417</v>
+        <f aca="false">AE17/$P17/1000*100</f>
+        <v>0.513516905386417</v>
       </c>
       <c r="AG17" s="26" t="n">
         <f aca="false">-AA17+($Q$45 + $Q$46)*1000*Q17/100</f>
@@ -5714,8 +5714,8 @@
         <v>22491.2</v>
       </c>
       <c r="S18" s="26" t="n">
-        <f aca="false">R18/$P18</f>
-        <v>6.030623960651</v>
+        <f aca="false">R18/$P18/1000*100</f>
+        <v>0.603062396065101</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">R18/P18</f>
@@ -5726,16 +5726,16 @@
         <v>7622.13333333333</v>
       </c>
       <c r="V18" s="26" t="n">
-        <f aca="false">U18/$P18</f>
-        <v>2.04374243754343</v>
+        <f aca="false">U18/$P18/1000*100</f>
+        <v>0.204374243754343</v>
       </c>
       <c r="W18" s="27" t="n">
         <f aca="false">R18-U18</f>
         <v>14869.0666666667</v>
       </c>
       <c r="X18" s="26" t="n">
-        <f aca="false">W18/$P18</f>
-        <v>3.98688152310758</v>
+        <f aca="false">W18/$P18/1000*100</f>
+        <v>0.398688152310758</v>
       </c>
       <c r="Y18" s="26"/>
       <c r="Z18" s="26"/>
@@ -5744,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="26" t="n">
-        <f aca="false">AA18/$P18</f>
+        <f aca="false">AA18/$P18/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC18" s="27" t="n">
@@ -5752,16 +5752,16 @@
         <v>14116.2617950061</v>
       </c>
       <c r="AD18" s="26" t="n">
-        <f aca="false">AC18/$P18</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC18/$P18/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE18" s="27" t="n">
         <f aca="false">AC18+Q18/100*1000 *($Q$46+$Q$43)</f>
         <v>25212.2375869684</v>
       </c>
       <c r="AF18" s="26" t="n">
-        <f aca="false">AE18/$P18</f>
-        <v>6.76022284687333</v>
+        <f aca="false">AE18/$P18/1000*100</f>
+        <v>0.676022284687333</v>
       </c>
       <c r="AG18" s="26" t="n">
         <f aca="false">-AA18+($Q$45 + $Q$46)*1000*Q18/100</f>
@@ -5940,8 +5940,8 @@
         <v>1574.3</v>
       </c>
       <c r="S19" s="26" t="n">
-        <f aca="false">R19/$P19</f>
-        <v>8.70351225391279</v>
+        <f aca="false">R19/$P19/1000*100</f>
+        <v>0.870351225391279</v>
       </c>
       <c r="T19" s="26" t="n">
         <f aca="false">R19/P19</f>
@@ -5952,16 +5952,16 @@
         <v>356.4</v>
       </c>
       <c r="V19" s="26" t="n">
-        <f aca="false">U19/$P19</f>
-        <v>1.97035620103825</v>
+        <f aca="false">U19/$P19/1000*100</f>
+        <v>0.197035620103825</v>
       </c>
       <c r="W19" s="27" t="n">
         <f aca="false">R19-U19</f>
         <v>1217.9</v>
       </c>
       <c r="X19" s="26" t="n">
-        <f aca="false">W19/$P19</f>
-        <v>6.73315605287454</v>
+        <f aca="false">W19/$P19/1000*100</f>
+        <v>0.673315605287454</v>
       </c>
       <c r="Y19" s="26"/>
       <c r="Z19" s="31" t="n">
@@ -5973,24 +5973,24 @@
         <v>22.7</v>
       </c>
       <c r="AB19" s="26" t="n">
-        <f aca="false">AA19/$P19</f>
-        <v>0.125496873635152</v>
+        <f aca="false">AA19/$P19/1000*100</f>
+        <v>0.0125496873635152</v>
       </c>
       <c r="AC19" s="27" t="n">
         <f aca="false">1000/100*Q19*($Q$41+$Q$47-$Q$49)-AA19</f>
         <v>661.940010463206</v>
       </c>
       <c r="AD19" s="26" t="n">
-        <f aca="false">AC19/$P19</f>
-        <v>3.65953312101993</v>
+        <f aca="false">AC19/$P19/1000*100</f>
+        <v>0.365953312101993</v>
       </c>
       <c r="AE19" s="27" t="n">
         <f aca="false">AC19+Q19/100*1000 *($Q$46+$Q$43)</f>
         <v>1200.0958687653</v>
       </c>
       <c r="AF19" s="26" t="n">
-        <f aca="false">AE19/$P19</f>
-        <v>6.63472597323821</v>
+        <f aca="false">AE19/$P19/1000*100</f>
+        <v>0.663472597323821</v>
       </c>
       <c r="AG19" s="26" t="n">
         <f aca="false">-Z19+($Q$45 + $Q$46)*1000*Q19/100</f>
@@ -6169,8 +6169,8 @@
         <v>869.8</v>
       </c>
       <c r="S20" s="26" t="n">
-        <f aca="false">R20/$P20</f>
-        <v>5.84056297171712</v>
+        <f aca="false">R20/$P20/1000*100</f>
+        <v>0.584056297171712</v>
       </c>
       <c r="T20" s="26" t="n">
         <f aca="false">R20/P20</f>
@@ -6181,16 +6181,16 @@
         <v>238.133333333333</v>
       </c>
       <c r="V20" s="26" t="n">
-        <f aca="false">U20/$P20</f>
-        <v>1.59902590135461</v>
+        <f aca="false">U20/$P20/1000*100</f>
+        <v>0.159902590135461</v>
       </c>
       <c r="W20" s="27" t="n">
         <f aca="false">R20-U20</f>
         <v>631.666666666667</v>
       </c>
       <c r="X20" s="26" t="n">
-        <f aca="false">W20/$P20</f>
-        <v>4.24153707036251</v>
+        <f aca="false">W20/$P20/1000*100</f>
+        <v>0.424153707036251</v>
       </c>
       <c r="Y20" s="26"/>
       <c r="Z20" s="26"/>
@@ -6199,7 +6199,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="26" t="n">
-        <f aca="false">AA20/$P20</f>
+        <f aca="false">AA20/$P20/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC20" s="27" t="n">
@@ -6207,16 +6207,16 @@
         <v>563.681806924014</v>
       </c>
       <c r="AD20" s="26" t="n">
-        <f aca="false">AC20/$P20</f>
-        <v>3.78502999465508</v>
+        <f aca="false">AC20/$P20/1000*100</f>
+        <v>0.378502999465508</v>
       </c>
       <c r="AE20" s="27" t="n">
         <f aca="false">AC20+Q20/100*1000 *($Q$46+$Q$43)</f>
         <v>1006.75942724777</v>
       </c>
       <c r="AF20" s="26" t="n">
-        <f aca="false">AE20/$P20</f>
-        <v>6.76022284687336</v>
+        <f aca="false">AE20/$P20/1000*100</f>
+        <v>0.676022284687336</v>
       </c>
       <c r="AG20" s="26" t="n">
         <f aca="false">-AA20+($Q$45 + $Q$46)*1000*Q20/100</f>
@@ -6395,8 +6395,8 @@
         <v>1506</v>
       </c>
       <c r="S21" s="26" t="n">
-        <f aca="false">R21/$P21</f>
-        <v>4.65560573882237</v>
+        <f aca="false">R21/$P21/1000*100</f>
+        <v>0.465560573882237</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">R21/P21</f>
@@ -6407,16 +6407,16 @@
         <v>370.866666666667</v>
       </c>
       <c r="V21" s="26" t="n">
-        <f aca="false">U21/$P21</f>
-        <v>1.14648670761704</v>
+        <f aca="false">U21/$P21/1000*100</f>
+        <v>0.114648670761704</v>
       </c>
       <c r="W21" s="27" t="n">
         <f aca="false">R21-U21</f>
         <v>1135.13333333333</v>
       </c>
       <c r="X21" s="26" t="n">
-        <f aca="false">W21/$P21</f>
-        <v>3.50911903120534</v>
+        <f aca="false">W21/$P21/1000*100</f>
+        <v>0.350911903120534</v>
       </c>
       <c r="Y21" s="26"/>
       <c r="Z21" s="31" t="n">
@@ -6428,24 +6428,24 @@
         <v>241.4</v>
       </c>
       <c r="AB21" s="26" t="n">
-        <f aca="false">AA21/$P21</f>
-        <v>0.746257121747491</v>
+        <f aca="false">AA21/$P21/1000*100</f>
+        <v>0.0746257121747491</v>
       </c>
       <c r="AC21" s="27" t="n">
         <f aca="false">1000/100*Q21*($Q$41+$Q$47-$Q$49)-AA21</f>
         <v>982.985287701017</v>
       </c>
       <c r="AD21" s="26" t="n">
-        <f aca="false">AC21/$P21</f>
-        <v>3.03877287290758</v>
+        <f aca="false">AC21/$P21/1000*100</f>
+        <v>0.303877287290758</v>
       </c>
       <c r="AE21" s="27" t="n">
         <f aca="false">AC21+Q21/100*1000 *($Q$46+$Q$43)</f>
         <v>1945.40364672943</v>
       </c>
       <c r="AF21" s="26" t="n">
-        <f aca="false">AE21/$P21</f>
-        <v>6.01396572512585</v>
+        <f aca="false">AE21/$P21/1000*100</f>
+        <v>0.601396572512585</v>
       </c>
       <c r="AG21" s="26" t="n">
         <f aca="false">-Z21+($Q$45 + $Q$46)*1000*Q21/100</f>
@@ -6627,8 +6627,8 @@
         <v>13413.2</v>
       </c>
       <c r="S22" s="26" t="n">
-        <f aca="false">R22/$P22</f>
-        <v>7.39434833901146</v>
+        <f aca="false">R22/$P22/1000*100</f>
+        <v>0.739434833901146</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">R22/P22</f>
@@ -6639,16 +6639,16 @@
         <v>4132.13333333333</v>
       </c>
       <c r="V22" s="26" t="n">
-        <f aca="false">U22/$P22</f>
-        <v>2.2779376472361</v>
+        <f aca="false">U22/$P22/1000*100</f>
+        <v>0.22779376472361</v>
       </c>
       <c r="W22" s="27" t="n">
         <f aca="false">R22-U22</f>
         <v>9281.06666666667</v>
       </c>
       <c r="X22" s="26" t="n">
-        <f aca="false">W22/$P22</f>
-        <v>5.11641069177536</v>
+        <f aca="false">W22/$P22/1000*100</f>
+        <v>0.511641069177536</v>
       </c>
       <c r="Y22" s="26" t="n">
         <f aca="false">B22</f>
@@ -6663,24 +6663,24 @@
         <v>1011.5</v>
       </c>
       <c r="AB22" s="26" t="n">
-        <f aca="false">AA22/$P22</f>
-        <v>0.557613645133904</v>
+        <f aca="false">AA22/$P22/1000*100</f>
+        <v>0.0557613645133904</v>
       </c>
       <c r="AC22" s="27" t="n">
         <f aca="false">1000/100*Q22*($Q$41+$Q$47-$Q$49)-AA22</f>
         <v>5854.46870970442</v>
       </c>
       <c r="AD22" s="26" t="n">
-        <f aca="false">AC22/$P22</f>
-        <v>3.22741634952117</v>
+        <f aca="false">AC22/$P22/1000*100</f>
+        <v>0.322741634952117</v>
       </c>
       <c r="AE22" s="27" t="n">
         <f aca="false">AC22+Q22/100*1000 *($Q$46+$Q$43)</f>
         <v>11251.4090397713</v>
       </c>
       <c r="AF22" s="26" t="n">
-        <f aca="false">AE22/$P22</f>
-        <v>6.20260920173945</v>
+        <f aca="false">AE22/$P22/1000*100</f>
+        <v>0.620260920173945</v>
       </c>
       <c r="AG22" s="26" t="n">
         <f aca="false">-AA22+($Q$45 + $Q$46)*1000*Q22/100</f>
@@ -6859,8 +6859,8 @@
         <v>165.6</v>
       </c>
       <c r="S23" s="26" t="n">
-        <f aca="false">R23/$P23</f>
-        <v>5.00680272108844</v>
+        <f aca="false">R23/$P23/1000*100</f>
+        <v>0.500680272108844</v>
       </c>
       <c r="T23" s="26" t="n">
         <f aca="false">R23/P23</f>
@@ -6871,16 +6871,16 @@
         <v>34.6666666666667</v>
       </c>
       <c r="V23" s="26" t="n">
-        <f aca="false">U23/$P23</f>
-        <v>1.04812295288486</v>
+        <f aca="false">U23/$P23/1000*100</f>
+        <v>0.104812295288486</v>
       </c>
       <c r="W23" s="27" t="n">
         <f aca="false">R23-U23</f>
         <v>130.933333333333</v>
       </c>
       <c r="X23" s="26" t="n">
-        <f aca="false">W23/$P23</f>
-        <v>3.95867976820358</v>
+        <f aca="false">W23/$P23/1000*100</f>
+        <v>0.395867976820358</v>
       </c>
       <c r="Y23" s="26"/>
       <c r="Z23" s="26"/>
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="AB23" s="26" t="n">
-        <f aca="false">AA23/$P23</f>
+        <f aca="false">AA23/$P23/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC23" s="27" t="n">
@@ -6897,16 +6897,16 @@
         <v>125.189867073216</v>
       </c>
       <c r="AD23" s="26" t="n">
-        <f aca="false">AC23/$P23</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC23/$P23/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE23" s="27" t="n">
         <f aca="false">AC23+Q23/100*1000 *($Q$46+$Q$43)</f>
         <v>223.594370660335</v>
       </c>
       <c r="AF23" s="26" t="n">
-        <f aca="false">AE23/$P23</f>
-        <v>6.76022284687333</v>
+        <f aca="false">AE23/$P23/1000*100</f>
+        <v>0.676022284687333</v>
       </c>
       <c r="AG23" s="26" t="n">
         <f aca="false">-AA23+($Q$45 + $Q$46)*1000*Q23/100</f>
@@ -7085,8 +7085,8 @@
         <v>228.7</v>
       </c>
       <c r="S24" s="26" t="n">
-        <f aca="false">R24/$P24</f>
-        <v>4.23393068720379</v>
+        <f aca="false">R24/$P24/1000*100</f>
+        <v>0.423393068720379</v>
       </c>
       <c r="T24" s="26" t="n">
         <f aca="false">R24/P24</f>
@@ -7097,16 +7097,16 @@
         <v>54.8666666666667</v>
       </c>
       <c r="V24" s="26" t="n">
-        <f aca="false">U24/$P24</f>
-        <v>1.01574842022117</v>
+        <f aca="false">U24/$P24/1000*100</f>
+        <v>0.101574842022117</v>
       </c>
       <c r="W24" s="27" t="n">
         <f aca="false">R24-U24</f>
         <v>173.833333333333</v>
       </c>
       <c r="X24" s="26" t="n">
-        <f aca="false">W24/$P24</f>
-        <v>3.21818226698262</v>
+        <f aca="false">W24/$P24/1000*100</f>
+        <v>0.321818226698262</v>
       </c>
       <c r="Y24" s="26"/>
       <c r="Z24" s="26"/>
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="AB24" s="26" t="n">
-        <f aca="false">AA24/$P24</f>
+        <f aca="false">AA24/$P24/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC24" s="27" t="n">
@@ -7123,16 +7123,16 @@
         <v>204.452180191289</v>
       </c>
       <c r="AD24" s="26" t="n">
-        <f aca="false">AC24/$P24</f>
-        <v>3.78502999465508</v>
+        <f aca="false">AC24/$P24/1000*100</f>
+        <v>0.378502999465508</v>
       </c>
       <c r="AE24" s="27" t="n">
         <f aca="false">AC24+Q24/100*1000 *($Q$46+$Q$43)</f>
         <v>365.160197296711</v>
       </c>
       <c r="AF24" s="26" t="n">
-        <f aca="false">AE24/$P24</f>
-        <v>6.76022284687335</v>
+        <f aca="false">AE24/$P24/1000*100</f>
+        <v>0.676022284687335</v>
       </c>
       <c r="AG24" s="26" t="n">
         <f aca="false">-AA24+($Q$45 + $Q$46)*1000*Q24/100</f>
@@ -7311,8 +7311,8 @@
         <v>530.5</v>
       </c>
       <c r="S25" s="26" t="n">
-        <f aca="false">R25/$P25</f>
-        <v>10.5111947691698</v>
+        <f aca="false">R25/$P25/1000*100</f>
+        <v>1.05111947691698</v>
       </c>
       <c r="T25" s="26" t="n">
         <f aca="false">R25/P25</f>
@@ -7323,16 +7323,16 @@
         <v>206.4</v>
       </c>
       <c r="V25" s="26" t="n">
-        <f aca="false">U25/$P25</f>
-        <v>4.08955815335843</v>
+        <f aca="false">U25/$P25/1000*100</f>
+        <v>0.408955815335843</v>
       </c>
       <c r="W25" s="27" t="n">
         <f aca="false">R25-U25</f>
         <v>324.1</v>
       </c>
       <c r="X25" s="26" t="n">
-        <f aca="false">W25/$P25</f>
-        <v>6.42163661581137</v>
+        <f aca="false">W25/$P25/1000*100</f>
+        <v>0.642163661581137</v>
       </c>
       <c r="Y25" s="26"/>
       <c r="Z25" s="26"/>
@@ -7341,7 +7341,7 @@
         <v>0</v>
       </c>
       <c r="AB25" s="26" t="n">
-        <f aca="false">AA25/$P25</f>
+        <f aca="false">AA25/$P25/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC25" s="27" t="n">
@@ -7349,16 +7349,16 @@
         <v>191.030463830241</v>
       </c>
       <c r="AD25" s="26" t="n">
-        <f aca="false">AC25/$P25</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC25/$P25/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE25" s="27" t="n">
         <f aca="false">AC25+Q25/100*1000 *($Q$46+$Q$43)</f>
         <v>341.188447081697</v>
       </c>
       <c r="AF25" s="26" t="n">
-        <f aca="false">AE25/$P25</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE25/$P25/1000*100</f>
+        <v>0.676022284687334</v>
       </c>
       <c r="AG25" s="26" t="n">
         <f aca="false">-AA25+($Q$45 + $Q$46)*1000*Q25/100</f>
@@ -7537,8 +7537,8 @@
         <v>194.3</v>
       </c>
       <c r="S26" s="26" t="n">
-        <f aca="false">R26/$P26</f>
-        <v>14.1711034935453</v>
+        <f aca="false">R26/$P26/1000*100</f>
+        <v>1.41711034935453</v>
       </c>
       <c r="T26" s="26" t="n">
         <f aca="false">R26/P26</f>
@@ -7549,16 +7549,16 @@
         <v>46.2</v>
       </c>
       <c r="V26" s="26" t="n">
-        <f aca="false">U26/$P26</f>
-        <v>3.36955728976734</v>
+        <f aca="false">U26/$P26/1000*100</f>
+        <v>0.336955728976734</v>
       </c>
       <c r="W26" s="27" t="n">
         <f aca="false">R26-U26</f>
         <v>148.1</v>
       </c>
       <c r="X26" s="26" t="n">
-        <f aca="false">W26/$P26</f>
-        <v>10.801546203778</v>
+        <f aca="false">W26/$P26/1000*100</f>
+        <v>1.0801546203778</v>
       </c>
       <c r="Y26" s="26"/>
       <c r="Z26" s="26"/>
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="AB26" s="26" t="n">
-        <f aca="false">AA26/$P26</f>
+        <f aca="false">AA26/$P26/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC26" s="27" t="n">
@@ -7575,16 +7575,16 @@
         <v>51.8965462567157</v>
       </c>
       <c r="AD26" s="26" t="n">
-        <f aca="false">AC26/$P26</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC26/$P26/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE26" s="27" t="n">
         <f aca="false">AC26+Q26/100*1000 *($Q$46+$Q$43)</f>
         <v>92.6894154534804</v>
       </c>
       <c r="AF26" s="26" t="n">
-        <f aca="false">AE26/$P26</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE26/$P26/1000*100</f>
+        <v>0.676022284687334</v>
       </c>
       <c r="AG26" s="26" t="n">
         <f aca="false">-AA26+($Q$45 + $Q$46)*1000*Q26/100</f>
@@ -7763,8 +7763,8 @@
         <v>5691.6</v>
       </c>
       <c r="S27" s="26" t="n">
-        <f aca="false">R27/$P27</f>
-        <v>6.79873285265829</v>
+        <f aca="false">R27/$P27/1000*100</f>
+        <v>0.679873285265829</v>
       </c>
       <c r="T27" s="26" t="n">
         <f aca="false">R27/P27</f>
@@ -7775,16 +7775,16 @@
         <v>1046.46666666667</v>
       </c>
       <c r="V27" s="26" t="n">
-        <f aca="false">U27/$P27</f>
-        <v>1.2500258812774</v>
+        <f aca="false">U27/$P27/1000*100</f>
+        <v>0.12500258812774</v>
       </c>
       <c r="W27" s="27" t="n">
         <f aca="false">R27-U27</f>
         <v>4645.13333333333</v>
       </c>
       <c r="X27" s="26" t="n">
-        <f aca="false">W27/$P27</f>
-        <v>5.54870697138088</v>
+        <f aca="false">W27/$P27/1000*100</f>
+        <v>0.554870697138088</v>
       </c>
       <c r="Y27" s="26"/>
       <c r="Z27" s="26"/>
@@ -7793,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="AB27" s="26" t="n">
-        <f aca="false">AA27/$P27</f>
+        <f aca="false">AA27/$P27/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC27" s="27" t="n">
@@ -7801,16 +7801,16 @@
         <v>3168.66057020546</v>
       </c>
       <c r="AD27" s="26" t="n">
-        <f aca="false">AC27/$P27</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC27/$P27/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE27" s="27" t="n">
         <f aca="false">AC27+Q27/100*1000 *($Q$46+$Q$43)</f>
         <v>5659.3611175971</v>
       </c>
       <c r="AF27" s="26" t="n">
-        <f aca="false">AE27/$P27</f>
-        <v>6.76022284687335</v>
+        <f aca="false">AE27/$P27/1000*100</f>
+        <v>0.676022284687335</v>
       </c>
       <c r="AG27" s="26" t="n">
         <f aca="false">-AA27+($Q$45 + $Q$46)*1000*Q27/100</f>
@@ -7989,8 +7989,8 @@
         <v>2837.3</v>
       </c>
       <c r="S28" s="26" t="n">
-        <f aca="false">R28/$P28</f>
-        <v>5.1783957613554</v>
+        <f aca="false">R28/$P28/1000*100</f>
+        <v>0.51783957613554</v>
       </c>
       <c r="T28" s="26" t="n">
         <f aca="false">R28/P28</f>
@@ -8001,16 +8001,16 @@
         <v>698.666666666667</v>
       </c>
       <c r="V28" s="26" t="n">
-        <f aca="false">U28/$P28</f>
-        <v>1.27514626767243</v>
+        <f aca="false">U28/$P28/1000*100</f>
+        <v>0.127514626767243</v>
       </c>
       <c r="W28" s="27" t="n">
         <f aca="false">R28-U28</f>
         <v>2138.63333333333</v>
       </c>
       <c r="X28" s="26" t="n">
-        <f aca="false">W28/$P28</f>
-        <v>3.90324949368298</v>
+        <f aca="false">W28/$P28/1000*100</f>
+        <v>0.390324949368298</v>
       </c>
       <c r="Y28" s="26"/>
       <c r="Z28" s="26"/>
@@ -8019,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="AB28" s="26" t="n">
-        <f aca="false">AA28/$P28</f>
+        <f aca="false">AA28/$P28/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC28" s="27" t="n">
@@ -8027,16 +8027,16 @@
         <v>2073.85956940145</v>
       </c>
       <c r="AD28" s="26" t="n">
-        <f aca="false">AC28/$P28</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC28/$P28/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE28" s="27" t="n">
         <f aca="false">AC28+Q28/100*1000 *($Q$46+$Q$43)</f>
         <v>3704.00046025321</v>
       </c>
       <c r="AF28" s="26" t="n">
-        <f aca="false">AE28/$P28</f>
-        <v>6.76022284687333</v>
+        <f aca="false">AE28/$P28/1000*100</f>
+        <v>0.676022284687333</v>
       </c>
       <c r="AG28" s="26" t="n">
         <f aca="false">-AA28+($Q$45 + $Q$46)*1000*Q28/100</f>
@@ -8215,8 +8215,8 @@
         <v>1777.8</v>
       </c>
       <c r="S29" s="26" t="n">
-        <f aca="false">R29/$P29</f>
-        <v>8.39079646017699</v>
+        <f aca="false">R29/$P29/1000*100</f>
+        <v>0.839079646017699</v>
       </c>
       <c r="T29" s="26" t="n">
         <f aca="false">R29/P29</f>
@@ -8227,16 +8227,16 @@
         <v>488.133333333333</v>
       </c>
       <c r="V29" s="26" t="n">
-        <f aca="false">U29/$P29</f>
-        <v>2.30387413962635</v>
+        <f aca="false">U29/$P29/1000*100</f>
+        <v>0.230387413962635</v>
       </c>
       <c r="W29" s="27" t="n">
         <f aca="false">R29-U29</f>
         <v>1289.66666666667</v>
       </c>
       <c r="X29" s="26" t="n">
-        <f aca="false">W29/$P29</f>
-        <v>6.08692232055064</v>
+        <f aca="false">W29/$P29/1000*100</f>
+        <v>0.608692232055064</v>
       </c>
       <c r="Y29" s="26"/>
       <c r="Z29" s="26"/>
@@ -8245,7 +8245,7 @@
         <v>0</v>
       </c>
       <c r="AB29" s="26" t="n">
-        <f aca="false">AA29/$P29</f>
+        <f aca="false">AA29/$P29/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC29" s="27" t="n">
@@ -8253,16 +8253,16 @@
         <v>801.953230117544</v>
       </c>
       <c r="AD29" s="26" t="n">
-        <f aca="false">AC29/$P29</f>
-        <v>3.78502999465508</v>
+        <f aca="false">AC29/$P29/1000*100</f>
+        <v>0.378502999465508</v>
       </c>
       <c r="AE29" s="27" t="n">
         <f aca="false">AC29+Q29/100*1000 *($Q$46+$Q$43)</f>
         <v>1432.32221568129</v>
       </c>
       <c r="AF29" s="26" t="n">
-        <f aca="false">AE29/$P29</f>
-        <v>6.76022284687335</v>
+        <f aca="false">AE29/$P29/1000*100</f>
+        <v>0.676022284687335</v>
       </c>
       <c r="AG29" s="26" t="n">
         <f aca="false">-AA29+($Q$45 + $Q$46)*1000*Q29/100</f>
@@ -8441,8 +8441,8 @@
         <v>828.5</v>
       </c>
       <c r="S30" s="26" t="n">
-        <f aca="false">R30/$P30</f>
-        <v>3.84790443635283</v>
+        <f aca="false">R30/$P30/1000*100</f>
+        <v>0.384790443635283</v>
       </c>
       <c r="T30" s="26" t="n">
         <f aca="false">R30/P30</f>
@@ -8453,16 +8453,16 @@
         <v>217.666666666667</v>
       </c>
       <c r="V30" s="26" t="n">
-        <f aca="false">U30/$P30</f>
-        <v>1.01093606796958</v>
+        <f aca="false">U30/$P30/1000*100</f>
+        <v>0.101093606796958</v>
       </c>
       <c r="W30" s="27" t="n">
         <f aca="false">R30-U30</f>
         <v>610.833333333333</v>
       </c>
       <c r="X30" s="26" t="n">
-        <f aca="false">W30/$P30</f>
-        <v>2.83696836838325</v>
+        <f aca="false">W30/$P30/1000*100</f>
+        <v>0.283696836838325</v>
       </c>
       <c r="Y30" s="26"/>
       <c r="Z30" s="26"/>
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="AB30" s="26" t="n">
-        <f aca="false">AA30/$P30</f>
+        <f aca="false">AA30/$P30/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC30" s="27" t="n">
@@ -8479,16 +8479,16 @@
         <v>814.962378209173</v>
       </c>
       <c r="AD30" s="26" t="n">
-        <f aca="false">AC30/$P30</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC30/$P30/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE30" s="27" t="n">
         <f aca="false">AC30+Q30/100*1000 *($Q$46+$Q$43)</f>
         <v>1455.55710160599</v>
       </c>
       <c r="AF30" s="26" t="n">
-        <f aca="false">AE30/$P30</f>
-        <v>6.76022284687335</v>
+        <f aca="false">AE30/$P30/1000*100</f>
+        <v>0.676022284687335</v>
       </c>
       <c r="AG30" s="26" t="n">
         <f aca="false">-AA30+($Q$45 + $Q$46)*1000*Q30/100</f>
@@ -8667,8 +8667,8 @@
         <v>317.3</v>
       </c>
       <c r="S31" s="26" t="n">
-        <f aca="false">R31/$P31</f>
-        <v>3.26111533638924</v>
+        <f aca="false">R31/$P31/1000*100</f>
+        <v>0.326111533638924</v>
       </c>
       <c r="T31" s="26" t="n">
         <f aca="false">R31/P31</f>
@@ -8679,16 +8679,16 @@
         <v>70.3333333333333</v>
       </c>
       <c r="V31" s="26" t="n">
-        <f aca="false">U31/$P31</f>
-        <v>0.722865149677623</v>
+        <f aca="false">U31/$P31/1000*100</f>
+        <v>0.0722865149677623</v>
       </c>
       <c r="W31" s="27" t="n">
         <f aca="false">R31-U31</f>
         <v>246.966666666667</v>
       </c>
       <c r="X31" s="26" t="n">
-        <f aca="false">W31/$P31</f>
-        <v>2.53825018671161</v>
+        <f aca="false">W31/$P31/1000*100</f>
+        <v>0.253825018671161</v>
       </c>
       <c r="Y31" s="26"/>
       <c r="Z31" s="26"/>
@@ -8697,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="AB31" s="26" t="n">
-        <f aca="false">AA31/$P31</f>
+        <f aca="false">AA31/$P31/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC31" s="27" t="n">
@@ -8705,16 +8705,16 @@
         <v>368.275848419949</v>
       </c>
       <c r="AD31" s="26" t="n">
-        <f aca="false">AC31/$P31</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC31/$P31/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE31" s="27" t="n">
         <f aca="false">AC31+Q31/100*1000 *($Q$46+$Q$43)</f>
         <v>657.756162555082</v>
       </c>
       <c r="AF31" s="26" t="n">
-        <f aca="false">AE31/$P31</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE31/$P31/1000*100</f>
+        <v>0.676022284687334</v>
       </c>
       <c r="AG31" s="26" t="n">
         <f aca="false">-AA31+($Q$45 + $Q$46)*1000*Q31/100</f>
@@ -8894,8 +8894,8 @@
         <v>277.1</v>
       </c>
       <c r="S32" s="26" t="n">
-        <f aca="false">R32/$P32</f>
-        <v>5.38361407394455</v>
+        <f aca="false">R32/$P32/1000*100</f>
+        <v>0.538361407394455</v>
       </c>
       <c r="T32" s="26" t="n">
         <f aca="false">R32/P32</f>
@@ -8906,16 +8906,16 @@
         <v>94.8666666666667</v>
       </c>
       <c r="V32" s="26" t="n">
-        <f aca="false">U32/$P32</f>
-        <v>1.84310906465129</v>
+        <f aca="false">U32/$P32/1000*100</f>
+        <v>0.184310906465129</v>
       </c>
       <c r="W32" s="27" t="n">
         <f aca="false">R32-U32</f>
         <v>182.233333333333</v>
       </c>
       <c r="X32" s="26" t="n">
-        <f aca="false">W32/$P32</f>
-        <v>3.54050500929326</v>
+        <f aca="false">W32/$P32/1000*100</f>
+        <v>0.354050500929326</v>
       </c>
       <c r="Y32" s="26"/>
       <c r="Z32" s="26"/>
@@ -8924,7 +8924,7 @@
         <v>0</v>
       </c>
       <c r="AB32" s="26" t="n">
-        <f aca="false">AA32/$P32</f>
+        <f aca="false">AA32/$P32/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC32" s="27" t="n">
@@ -8932,16 +8932,16 @@
         <v>194.819278854891</v>
       </c>
       <c r="AD32" s="26" t="n">
-        <f aca="false">AC32/$P32</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC32/$P32/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE32" s="27" t="n">
         <f aca="false">AC32+Q32/100*1000 *($Q$46+$Q$43)</f>
         <v>347.955430151418</v>
       </c>
       <c r="AF32" s="26" t="n">
-        <f aca="false">AE32/$P32</f>
-        <v>6.76022284687334</v>
+        <f aca="false">AE32/$P32/1000*100</f>
+        <v>0.676022284687334</v>
       </c>
       <c r="AG32" s="26" t="n">
         <f aca="false">-AA32+($Q$45 + $Q$46)*1000*Q32/100</f>
@@ -9120,8 +9120,8 @@
         <v>9697.1</v>
       </c>
       <c r="S33" s="26" t="n">
-        <f aca="false">R33/$P33</f>
-        <v>7.99315844787438</v>
+        <f aca="false">R33/$P33/1000*100</f>
+        <v>0.799315844787438</v>
       </c>
       <c r="T33" s="26" t="n">
         <f aca="false">R33/P33</f>
@@ -9132,16 +9132,16 @@
         <v>2691.4</v>
       </c>
       <c r="V33" s="26" t="n">
-        <f aca="false">U33/$P33</f>
-        <v>2.21847631215612</v>
+        <f aca="false">U33/$P33/1000*100</f>
+        <v>0.221847631215612</v>
       </c>
       <c r="W33" s="27" t="n">
         <f aca="false">R33-U33</f>
         <v>7005.7</v>
       </c>
       <c r="X33" s="26" t="n">
-        <f aca="false">W33/$P33</f>
-        <v>5.77468213571826</v>
+        <f aca="false">W33/$P33/1000*100</f>
+        <v>0.577468213571826</v>
       </c>
       <c r="Y33" s="26" t="n">
         <f aca="false">B33</f>
@@ -9156,24 +9156,24 @@
         <v>927.6</v>
       </c>
       <c r="AB33" s="26" t="n">
-        <f aca="false">AA33/$P33</f>
-        <v>0.76460527129227</v>
+        <f aca="false">AA33/$P33/1000*100</f>
+        <v>0.076460527129227</v>
       </c>
       <c r="AC33" s="27" t="n">
         <f aca="false">1000/100*Q33*($Q$41+$Q$47-$Q$49)-AA33</f>
         <v>3664.30376376567</v>
       </c>
       <c r="AD33" s="26" t="n">
-        <f aca="false">AC33/$P33</f>
-        <v>3.0204247233628</v>
+        <f aca="false">AC33/$P33/1000*100</f>
+        <v>0.30204247233628</v>
       </c>
       <c r="AE33" s="27" t="n">
         <f aca="false">AC33+Q33/100*1000 *($Q$46+$Q$43)</f>
         <v>7273.73335225556</v>
       </c>
       <c r="AF33" s="26" t="n">
-        <f aca="false">AE33/$P33</f>
-        <v>5.99561757558107</v>
+        <f aca="false">AE33/$P33/1000*100</f>
+        <v>0.599561757558107</v>
       </c>
       <c r="AG33" s="26" t="n">
         <f aca="false">-AA33+($Q$45 + $Q$46)*1000*Q33/100</f>
@@ -9352,8 +9352,8 @@
         <v>2910.9</v>
       </c>
       <c r="S34" s="26" t="n">
-        <f aca="false">R34/$P34</f>
-        <v>5.26670984877818</v>
+        <f aca="false">R34/$P34/1000*100</f>
+        <v>0.526670984877818</v>
       </c>
       <c r="T34" s="26" t="n">
         <f aca="false">R34/P34</f>
@@ -9364,16 +9364,16 @@
         <v>749.066666666667</v>
       </c>
       <c r="V34" s="26" t="n">
-        <f aca="false">U34/$P34</f>
-        <v>1.35529107517427</v>
+        <f aca="false">U34/$P34/1000*100</f>
+        <v>0.135529107517427</v>
       </c>
       <c r="W34" s="27" t="n">
         <f aca="false">R34-U34</f>
         <v>2161.83333333333</v>
       </c>
       <c r="X34" s="26" t="n">
-        <f aca="false">W34/$P34</f>
-        <v>3.91141877360391</v>
+        <f aca="false">W34/$P34/1000*100</f>
+        <v>0.391141877360391</v>
       </c>
       <c r="Y34" s="26"/>
       <c r="Z34" s="26"/>
@@ -9382,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="AB34" s="26" t="n">
-        <f aca="false">AA34/$P34</f>
+        <f aca="false">AA34/$P34/1000*100</f>
         <v>0</v>
       </c>
       <c r="AC34" s="27" t="n">
@@ -9390,16 +9390,16 @@
         <v>2091.97850798587</v>
       </c>
       <c r="AD34" s="26" t="n">
-        <f aca="false">AC34/$P34</f>
-        <v>3.78502999465507</v>
+        <f aca="false">AC34/$P34/1000*100</f>
+        <v>0.378502999465507</v>
       </c>
       <c r="AE34" s="27" t="n">
         <f aca="false">AC34+Q34/100*1000 *($Q$46+$Q$43)</f>
         <v>3736.3616470212</v>
       </c>
       <c r="AF34" s="26" t="n">
-        <f aca="false">AE34/$P34</f>
-        <v>6.76022284687333</v>
+        <f aca="false">AE34/$P34/1000*100</f>
+        <v>0.676022284687333</v>
       </c>
       <c r="AG34" s="26" t="n">
         <f aca="false">-AA34+($Q$45 + $Q$46)*1000*Q34/100</f>
@@ -9556,8 +9556,8 @@
         <v>98422.2</v>
       </c>
       <c r="S35" s="26" t="n">
-        <f aca="false">R35/$P35</f>
-        <v>6.75995498226118</v>
+        <f aca="false">R35/$P35/1000*100</f>
+        <v>0.675995498226118</v>
       </c>
       <c r="T35" s="26"/>
       <c r="U35" s="27" t="n">
@@ -9565,16 +9565,16 @@
         <v>29317.6</v>
       </c>
       <c r="V35" s="26" t="n">
-        <f aca="false">U35/$P35</f>
-        <v>2.01362757780196</v>
+        <f aca="false">U35/$P35/1000*100</f>
+        <v>0.201362757780196</v>
       </c>
       <c r="W35" s="27" t="n">
         <f aca="false">R35-U35</f>
         <v>69104.6</v>
       </c>
       <c r="X35" s="26" t="n">
-        <f aca="false">W35/$P35</f>
-        <v>4.74632740445922</v>
+        <f aca="false">W35/$P35/1000*100</f>
+        <v>0.474632740445922</v>
       </c>
       <c r="Y35" s="23" t="n">
         <f aca="false">SUM(Y8:Y34)</f>
@@ -9589,24 +9589,24 @@
         <v>6549.520378624</v>
       </c>
       <c r="AB35" s="26" t="n">
-        <f aca="false">AA35/$P35</f>
-        <v>0.449842240011912</v>
+        <f aca="false">AA35/$P35/1000*100</f>
+        <v>0.0449842240011912</v>
       </c>
       <c r="AC35" s="27" t="n">
         <f aca="false">1000/100*Q35*($Q$41+$Q$47-$Q$49)-AA35</f>
         <v>48558.979621376</v>
       </c>
       <c r="AD35" s="26" t="n">
-        <f aca="false">AC35/$P35</f>
-        <v>3.33518775464316</v>
+        <f aca="false">AC35/$P35/1000*100</f>
+        <v>0.333518775464316</v>
       </c>
       <c r="AE35" s="27" t="n">
         <f aca="false">AC35+Q35/100*1000 *($Q$46+$Q$43)</f>
         <v>91876.579621376</v>
       </c>
       <c r="AF35" s="26" t="n">
-        <f aca="false">AE35/$P35</f>
-        <v>6.31038060686143</v>
+        <f aca="false">AE35/$P35/1000*100</f>
+        <v>0.631038060686143</v>
       </c>
       <c r="AG35" s="26" t="n">
         <f aca="false">SUM(AG8:AG34)</f>

--- a/combined.xlsx
+++ b/combined.xlsx
@@ -884,7 +884,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -993,10 +993,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1022,10 +1018,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1077,11 +1069,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1173,10 +1169,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.120686473519099"/>
-          <c:y val="0.0304360310102957"/>
-          <c:w val="0.693093744233253"/>
-          <c:h val="0.776528979859715"/>
+          <c:x val="0.120680906029432"/>
+          <c:y val="0.0304372795143162"/>
+          <c:w val="0.69308483646261"/>
+          <c:h val="0.776478792353762"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -2264,85 +2260,85 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>0.0454195610504591</c:v>
+                  <c:v>0.0623423551500831</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0368865393719426</c:v>
+                  <c:v>0.0506300299826416</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0876941594543474</c:v>
+                  <c:v>0.120367971571044</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.110487788191831</c:v>
+                  <c:v>0.151654238215776</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.224192814915871</c:v>
+                  <c:v>0.307724420190996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0328685740399784</c:v>
+                  <c:v>0.045115018038168</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0551431540391427</c:v>
+                  <c:v>0.0756888444911386</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0495161655717014</c:v>
+                  <c:v>0.0679653063205929</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0479235103188245</c:v>
+                  <c:v>0.0657792464576147</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0355228059055014</c:v>
+                  <c:v>0.0487581854705276</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0275318554936884</c:v>
+                  <c:v>0.0377899009464545</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.238720484738585</c:v>
+                  <c:v>0.327664928875891</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.0422363084526336</c:v>
+                  <c:v>0.0579730600843383</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.0494001193269466</c:v>
+                  <c:v>0.0678060226102924</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.0666324876790262</c:v>
+                  <c:v>0.0914589686766116</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.0925170068027211</c:v>
+                  <c:v>0.126987755102041</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.044061018957346</c:v>
+                  <c:v>0.0604776362559242</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.0707350901525659</c:v>
+                  <c:v>0.0970901525658807</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.334767704762599</c:v>
+                  <c:v>0.459498213113559</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0402075598813125</c:v>
+                  <c:v>0.0551884236629732</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.0369220548592746</c:v>
+                  <c:v>0.0506787781227243</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.15646017699115</c:v>
+                  <c:v>0.214755398230089</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.0489522181764138</c:v>
+                  <c:v>0.0671912387604964</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.00873604801743099</c:v>
+                  <c:v>0.0119909967316903</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.00990849216063414</c:v>
+                  <c:v>0.0136002797691904</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.130739588270447</c:v>
+                  <c:v>0.179451620747213</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.035679521185168</c:v>
+                  <c:v>0.0489732910196889</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2497,85 +2493,85 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>0.33002103075196</c:v>
+                  <c:v>0.356975983763671</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.262900426069118</c:v>
+                  <c:v>0.284373204986587</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.41573527445024</c:v>
+                  <c:v>0.449691064366367</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.534993500718342</c:v>
+                  <c:v>0.57868988164466</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.927694406548431</c:v>
+                  <c:v>1.00346521145975</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.274900801061637</c:v>
+                  <c:v>0.297353728254231</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.163965484576566</c:v>
+                  <c:v>0.17735760665507</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.220071846985339</c:v>
+                  <c:v>0.238046538722936</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.154420199916212</c:v>
+                  <c:v>0.167032696832898</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.327496500541426</c:v>
+                  <c:v>0.354245258835647</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.210409014832559</c:v>
+                  <c:v>0.22759448054403</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.473681591764751</c:v>
+                  <c:v>0.512370232362714</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.228304370014235</c:v>
+                  <c:v>0.246951465176869</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.159762088036082</c:v>
+                  <c:v>0.172810891520677</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.423598937143739</c:v>
+                  <c:v>0.458197003274568</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.205593348450491</c:v>
+                  <c:v>0.222385487528345</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.201421800947867</c:v>
+                  <c:v>0.217873222748815</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.485040618189023</c:v>
+                  <c:v>0.524657023974638</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.892713879366932</c:v>
+                  <c:v>0.965627598278754</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.178700266139166</c:v>
+                  <c:v>0.193295873170592</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.198572395881813</c:v>
+                  <c:v>0.214791088333689</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.410808259587021</c:v>
+                  <c:v>0.444361628318584</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.202125287954225</c:v>
+                  <c:v>0.218634168090956</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.181709798762565</c:v>
+                  <c:v>0.196551213796789</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.290649103378602</c:v>
+                  <c:v>0.314388296322201</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.346396851237455</c:v>
+                  <c:v>0.374689323469409</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.17470662097565</c:v>
+                  <c:v>0.188976041165338</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2583,11 +2579,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="38914575"/>
-        <c:axId val="51911800"/>
+        <c:axId val="49219474"/>
+        <c:axId val="88960972"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38914575"/>
+        <c:axId val="49219474"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,7 +2615,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51911800"/>
+        <c:crossAx val="88960972"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2627,7 +2623,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51911800"/>
+        <c:axId val="88960972"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2668,7 +2664,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38914575"/>
+        <c:crossAx val="49219474"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2731,9 +2727,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>351720</xdr:colOff>
+      <xdr:colOff>351360</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>86040</xdr:rowOff>
+      <xdr:rowOff>85680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2742,7 +2738,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="344880" y="8228880"/>
-        <a:ext cx="15606360" cy="8776080"/>
+        <a:ext cx="15607080" cy="8775720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2892,8 +2888,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="11.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="11.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="76" style="1" width="12.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16380" min="16354" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16354" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" s="11" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2953,10 +2948,10 @@
       <c r="AO1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="XFA1" s="0"/>
-      <c r="XFB1" s="0"/>
-      <c r="XFC1" s="0"/>
-      <c r="XFD1" s="0"/>
+      <c r="XFA1" s="1"/>
+      <c r="XFB1" s="1"/>
+      <c r="XFC1" s="1"/>
+      <c r="XFD1" s="1"/>
     </row>
     <row r="2" s="13" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
@@ -3026,10 +3021,10 @@
       <c r="AO2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="XFA2" s="0"/>
-      <c r="XFB2" s="0"/>
-      <c r="XFC2" s="0"/>
-      <c r="XFD2" s="0"/>
+      <c r="XFA2" s="1"/>
+      <c r="XFB2" s="1"/>
+      <c r="XFC2" s="1"/>
+      <c r="XFD2" s="1"/>
     </row>
     <row r="3" s="13" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
@@ -3101,10 +3096,10 @@
       <c r="AO3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="XFA3" s="0"/>
-      <c r="XFB3" s="0"/>
-      <c r="XFC3" s="0"/>
-      <c r="XFD3" s="0"/>
+      <c r="XFA3" s="1"/>
+      <c r="XFB3" s="1"/>
+      <c r="XFC3" s="1"/>
+      <c r="XFD3" s="1"/>
     </row>
     <row r="4" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
@@ -3166,10 +3161,10 @@
       <c r="XEX4" s="19"/>
       <c r="XEY4" s="19"/>
       <c r="XEZ4" s="19"/>
-      <c r="XFA4" s="0"/>
-      <c r="XFB4" s="0"/>
-      <c r="XFC4" s="0"/>
-      <c r="XFD4" s="0"/>
+      <c r="XFA4" s="1"/>
+      <c r="XFB4" s="1"/>
+      <c r="XFC4" s="1"/>
+      <c r="XFD4" s="1"/>
     </row>
     <row r="5" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
@@ -3231,10 +3226,10 @@
       <c r="XEX5" s="19"/>
       <c r="XEY5" s="19"/>
       <c r="XEZ5" s="19"/>
-      <c r="XFA5" s="0"/>
-      <c r="XFB5" s="0"/>
-      <c r="XFC5" s="0"/>
-      <c r="XFD5" s="0"/>
+      <c r="XFA5" s="1"/>
+      <c r="XFB5" s="1"/>
+      <c r="XFC5" s="1"/>
+      <c r="XFD5" s="1"/>
     </row>
     <row r="6" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
@@ -3301,10 +3296,10 @@
       <c r="XEX6" s="19"/>
       <c r="XEY6" s="19"/>
       <c r="XEZ6" s="19"/>
-      <c r="XFA6" s="0"/>
-      <c r="XFB6" s="0"/>
-      <c r="XFC6" s="0"/>
-      <c r="XFD6" s="0"/>
+      <c r="XFA6" s="1"/>
+      <c r="XFB6" s="1"/>
+      <c r="XFC6" s="1"/>
+      <c r="XFD6" s="1"/>
     </row>
     <row r="7" s="21" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
@@ -3371,10 +3366,10 @@
       <c r="XEX7" s="19"/>
       <c r="XEY7" s="19"/>
       <c r="XEZ7" s="19"/>
-      <c r="XFA7" s="0"/>
-      <c r="XFB7" s="0"/>
-      <c r="XFC7" s="0"/>
-      <c r="XFD7" s="0"/>
+      <c r="XFA7" s="1"/>
+      <c r="XFB7" s="1"/>
+      <c r="XFC7" s="1"/>
+      <c r="XFD7" s="1"/>
     </row>
     <row r="8" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
@@ -3410,22 +3405,22 @@
       </c>
       <c r="J8" s="23" t="n">
         <f aca="false">L8*$J$37/100</f>
-        <v>185.3</v>
+        <v>254.3406</v>
       </c>
       <c r="K8" s="24" t="n">
         <f aca="false">J8/$P8/10</f>
-        <v>0.0454195610504591</v>
+        <v>0.0623423551500831</v>
       </c>
       <c r="L8" s="23" t="n">
         <v>1090</v>
       </c>
       <c r="M8" s="23" t="n">
         <f aca="false">O8*$M$37/100</f>
-        <v>1346.4</v>
+        <v>1456.3692</v>
       </c>
       <c r="N8" s="24" t="n">
         <f aca="false">M8/$P8/10</f>
-        <v>0.33002103075196</v>
+        <v>0.356975983763671</v>
       </c>
       <c r="O8" s="23" t="n">
         <v>9900</v>
@@ -3439,38 +3434,38 @@
       </c>
       <c r="R8" s="23" t="n">
         <f aca="false">H8+F8+B8+D8+J8+M8</f>
-        <v>2951.1</v>
+        <v>3130.1098</v>
       </c>
       <c r="S8" s="26" t="n">
         <f aca="false">R8/$P8/1000*100</f>
-        <v>0.723354919676254</v>
+        <v>0.76723266678759</v>
       </c>
       <c r="T8" s="26" t="n">
         <f aca="false">R8/P8</f>
-        <v>7.23354919676254</v>
-      </c>
-      <c r="U8" s="27" t="n">
+        <v>7.6723266678759</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <f aca="false">3/5*H8+M8/3</f>
-        <v>1000.8</v>
+        <v>1037.4564</v>
       </c>
       <c r="V8" s="26" t="n">
         <f aca="false">U8/$P8/1000*100</f>
-        <v>0.245309750131136</v>
-      </c>
-      <c r="W8" s="27" t="n">
+        <v>0.254294734468373</v>
+      </c>
+      <c r="W8" s="2" t="n">
         <f aca="false">R8-U8</f>
-        <v>1950.3</v>
+        <v>2092.6534</v>
       </c>
       <c r="X8" s="26" t="n">
         <f aca="false">W8/$P8/1000*100</f>
-        <v>0.478045169545118</v>
+        <v>0.512937932319217</v>
       </c>
       <c r="Y8" s="23" t="n">
         <f aca="false">124*(1.08)^4*3/5</f>
         <v>101.220378624</v>
       </c>
       <c r="Z8" s="26"/>
-      <c r="AA8" s="0" t="n">
+      <c r="AA8" s="1" t="n">
         <f aca="false">Y8+Z8</f>
         <v>101.220378624</v>
       </c>
@@ -3478,33 +3473,33 @@
         <f aca="false">AA8/$P8/1000*100</f>
         <v>0.02481049739052</v>
       </c>
-      <c r="AC8" s="27" t="n">
+      <c r="AC8" s="2" t="n">
         <f aca="false">1000/100*Q8*($Q$41+$Q$47-$Q$49)-AA8</f>
-        <v>1442.97344841541</v>
+        <v>1584.90627054526</v>
       </c>
       <c r="AD8" s="26" t="n">
         <f aca="false">AC8/$P8/1000*100</f>
-        <v>0.353692502074988</v>
-      </c>
-      <c r="AE8" s="27" t="n">
+        <v>0.388482175468353</v>
+      </c>
+      <c r="AE8" s="2" t="n">
         <f aca="false">AC8+Q8/100*1000 *($Q$46+$Q$43)</f>
-        <v>2656.77477710631</v>
+        <v>2829.73991968701</v>
       </c>
       <c r="AF8" s="26" t="n">
         <f aca="false">AE8/$P8/1000*100</f>
-        <v>0.651211787296815</v>
+        <v>0.693607906309474</v>
       </c>
       <c r="AG8" s="26" t="n">
         <f aca="false">-Y8+($Q$45 + $Q$46)*1000*Q8/100</f>
-        <v>1162.76371179775</v>
+        <v>1304.6965339276</v>
       </c>
       <c r="AH8" s="26" t="n">
         <f aca="false">AG8/P8/10</f>
-        <v>0.285009268188109</v>
+        <v>0.319798941581474</v>
       </c>
       <c r="AI8" s="26" t="n">
         <f aca="false">AG8/P8</f>
-        <v>2.85009268188109</v>
+        <v>3.19798941581474</v>
       </c>
       <c r="AK8" s="26" t="n">
         <f aca="false">-Q8*($Q$47)*10</f>
@@ -3534,7 +3529,7 @@
         <f aca="false">AW8*1000</f>
         <v>1900</v>
       </c>
-      <c r="BA8" s="28" t="s">
+      <c r="BA8" s="27" t="s">
         <v>43</v>
       </c>
       <c r="BB8" s="23" t="n">
@@ -3543,15 +3538,15 @@
       <c r="BC8" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="BD8" s="28" t="n">
+      <c r="BD8" s="27" t="n">
         <f aca="false">BB8+BC8/10</f>
         <v>9.9</v>
       </c>
-      <c r="BE8" s="28" t="n">
+      <c r="BE8" s="27" t="n">
         <f aca="false">1000*BD8</f>
         <v>9900</v>
       </c>
-      <c r="BG8" s="28" t="s">
+      <c r="BG8" s="27" t="s">
         <v>42</v>
       </c>
       <c r="BH8" s="23" t="n">
@@ -3569,10 +3564,10 @@
       <c r="BL8" s="23" t="n">
         <v>1.17</v>
       </c>
-      <c r="BM8" s="28" t="s">
+      <c r="BM8" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="BO8" s="28" t="n">
+      <c r="BO8" s="27" t="n">
         <f aca="false">BH8*1000</f>
         <v>1090</v>
       </c>
@@ -3600,13 +3595,13 @@
       <c r="BY8" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="XFA8" s="0"/>
-      <c r="XFB8" s="0"/>
-      <c r="XFC8" s="0"/>
-      <c r="XFD8" s="0"/>
+      <c r="XFA8" s="1"/>
+      <c r="XFB8" s="1"/>
+      <c r="XFC8" s="1"/>
+      <c r="XFD8" s="1"/>
     </row>
     <row r="9" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="23" t="n">
@@ -3623,14 +3618,14 @@
         <f aca="false">D9/$P9/10</f>
         <v>0.0362947767082216</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="29" t="n">
         <v>61.1</v>
       </c>
       <c r="G9" s="24" t="n">
         <f aca="false">F9/$P9/10</f>
         <v>0.0120522329177844</v>
       </c>
-      <c r="H9" s="30" t="n">
+      <c r="H9" s="29" t="n">
         <v>722</v>
       </c>
       <c r="I9" s="24" t="n">
@@ -3639,22 +3634,22 @@
       </c>
       <c r="J9" s="23" t="n">
         <f aca="false">L9*$J$37/100</f>
-        <v>187</v>
+        <v>256.674</v>
       </c>
       <c r="K9" s="24" t="n">
         <f aca="false">J9/$P9/10</f>
-        <v>0.0368865393719426</v>
+        <v>0.0506300299826416</v>
       </c>
       <c r="L9" s="23" t="n">
         <v>1100</v>
       </c>
       <c r="M9" s="23" t="n">
         <f aca="false">O9*$M$37/100</f>
-        <v>1332.8</v>
+        <v>1441.6584</v>
       </c>
       <c r="N9" s="24" t="n">
         <f aca="false">M9/$P9/10</f>
-        <v>0.262900426069118</v>
+        <v>0.284373204986587</v>
       </c>
       <c r="O9" s="23" t="n">
         <v>9800</v>
@@ -3668,38 +3663,38 @@
       </c>
       <c r="R9" s="23" t="n">
         <f aca="false">H9+F9+B9+D9+J9+M9</f>
-        <v>2687.9</v>
+        <v>2866.4324</v>
       </c>
       <c r="S9" s="26" t="n">
         <f aca="false">R9/$P9/1000*100</f>
-        <v>0.530199621271895</v>
+        <v>0.565415890800063</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">R9/P9</f>
-        <v>5.30199621271895</v>
-      </c>
-      <c r="U9" s="27" t="n">
+        <v>5.65415890800063</v>
+      </c>
+      <c r="U9" s="2" t="n">
         <f aca="false">3/5*H9+M9/3</f>
-        <v>877.466666666667</v>
+        <v>913.7528</v>
       </c>
       <c r="V9" s="26" t="n">
         <f aca="false">U9/$P9/1000*100</f>
-        <v>0.173084003997686</v>
-      </c>
-      <c r="W9" s="27" t="n">
+        <v>0.180241596970175</v>
+      </c>
+      <c r="W9" s="2" t="n">
         <f aca="false">R9-U9</f>
-        <v>1810.43333333333</v>
+        <v>1952.6796</v>
       </c>
       <c r="X9" s="26" t="n">
         <f aca="false">W9/$P9/1000*100</f>
-        <v>0.35711561727421</v>
+        <v>0.385174293829888</v>
       </c>
       <c r="Y9" s="26"/>
-      <c r="Z9" s="31" t="n">
+      <c r="Z9" s="30" t="n">
         <f aca="false">F9</f>
         <v>61.1</v>
       </c>
-      <c r="AA9" s="0" t="n">
+      <c r="AA9" s="1" t="n">
         <f aca="false">Y9+Z9</f>
         <v>61.1</v>
       </c>
@@ -3707,33 +3702,33 @@
         <f aca="false">AA9/$P9/1000*100</f>
         <v>0.0120522329177844</v>
       </c>
-      <c r="AC9" s="27" t="n">
+      <c r="AC9" s="2" t="n">
         <f aca="false">1000/100*Q9*($Q$41+$Q$47-$Q$49)-AA9</f>
-        <v>1857.75880609034</v>
+        <v>2034.12853432534</v>
       </c>
       <c r="AD9" s="26" t="n">
         <f aca="false">AC9/$P9/1000*100</f>
-        <v>0.366450766547723</v>
-      </c>
-      <c r="AE9" s="27" t="n">
+        <v>0.401240439941088</v>
+      </c>
+      <c r="AE9" s="2" t="n">
         <f aca="false">AC9+Q9/100*1000 *($Q$46+$Q$43)</f>
-        <v>3366.06257445091</v>
+        <v>3580.99393939749</v>
       </c>
       <c r="AF9" s="26" t="n">
         <f aca="false">AE9/$P9/1000*100</f>
-        <v>0.66397005176955</v>
+        <v>0.70636617078221</v>
       </c>
       <c r="AG9" s="26" t="n">
         <f aca="false">-Z9+($Q$45 + $Q$46)*1000*Q9/100</f>
-        <v>1509.56228357741</v>
+        <v>1685.93201181242</v>
       </c>
       <c r="AH9" s="26" t="n">
         <f aca="false">AG9/P9/10</f>
-        <v>0.297767532660844</v>
+        <v>0.332557206054209</v>
       </c>
       <c r="AI9" s="26" t="n">
         <f aca="false">AG9/P9</f>
-        <v>2.97767532660844</v>
+        <v>3.32557206054209</v>
       </c>
       <c r="AK9" s="26" t="n">
         <f aca="false">-Q9*($Q$47)*10</f>
@@ -3763,7 +3758,7 @@
         <f aca="false">AW9*1000</f>
         <v>1100</v>
       </c>
-      <c r="BA9" s="28" t="s">
+      <c r="BA9" s="27" t="s">
         <v>50</v>
       </c>
       <c r="BB9" s="23" t="n">
@@ -3772,15 +3767,15 @@
       <c r="BC9" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="BD9" s="28" t="n">
+      <c r="BD9" s="27" t="n">
         <f aca="false">BB9+BC9/10</f>
         <v>9.8</v>
       </c>
-      <c r="BE9" s="28" t="n">
+      <c r="BE9" s="27" t="n">
         <f aca="false">1000*BD9</f>
         <v>9800</v>
       </c>
-      <c r="BG9" s="28" t="s">
+      <c r="BG9" s="27" t="s">
         <v>49</v>
       </c>
       <c r="BH9" s="23" t="n">
@@ -3798,10 +3793,10 @@
       <c r="BL9" s="23" t="n">
         <v>0.96</v>
       </c>
-      <c r="BM9" s="28" t="s">
+      <c r="BM9" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="BO9" s="28" t="n">
+      <c r="BO9" s="27" t="n">
         <f aca="false">BH9*1000</f>
         <v>1100</v>
       </c>
@@ -3829,10 +3824,10 @@
       <c r="BY9" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="XFA9" s="0"/>
-      <c r="XFB9" s="0"/>
-      <c r="XFC9" s="0"/>
-      <c r="XFD9" s="0"/>
+      <c r="XFA9" s="1"/>
+      <c r="XFB9" s="1"/>
+      <c r="XFC9" s="1"/>
+      <c r="XFD9" s="1"/>
     </row>
     <row r="10" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
@@ -3868,22 +3863,22 @@
       </c>
       <c r="J10" s="23" t="n">
         <f aca="false">L10*$J$37/100</f>
-        <v>45.9</v>
+        <v>63.0018</v>
       </c>
       <c r="K10" s="24" t="n">
         <f aca="false">J10/$P10/10</f>
-        <v>0.0876941594543474</v>
+        <v>0.120367971571044</v>
       </c>
       <c r="L10" s="23" t="n">
         <v>270</v>
       </c>
       <c r="M10" s="23" t="n">
         <f aca="false">O10*$M$37/100</f>
-        <v>217.6</v>
+        <v>235.3728</v>
       </c>
       <c r="N10" s="24" t="n">
         <f aca="false">M10/$P10/10</f>
-        <v>0.41573527445024</v>
+        <v>0.449691064366367</v>
       </c>
       <c r="O10" s="23" t="n">
         <v>1600</v>
@@ -3897,35 +3892,35 @@
       </c>
       <c r="R10" s="23" t="n">
         <f aca="false">H10+F10+B10+D10+J10+M10</f>
-        <v>359.7</v>
+        <v>394.5746</v>
       </c>
       <c r="S10" s="26" t="n">
         <f aca="false">R10/$P10/1000*100</f>
-        <v>0.687224164612827</v>
+        <v>0.753853766645651</v>
       </c>
       <c r="T10" s="26" t="n">
         <f aca="false">R10/P10</f>
-        <v>6.87224164612827</v>
-      </c>
-      <c r="U10" s="27" t="n">
+        <v>7.53853766645651</v>
+      </c>
+      <c r="U10" s="2" t="n">
         <f aca="false">3/5*H10+M10/3</f>
-        <v>96.5333333333333</v>
+        <v>102.4576</v>
       </c>
       <c r="V10" s="26" t="n">
         <f aca="false">U10/$P10/1000*100</f>
-        <v>0.184431580086994</v>
-      </c>
-      <c r="W10" s="27" t="n">
+        <v>0.195750176725703</v>
+      </c>
+      <c r="W10" s="2" t="n">
         <f aca="false">R10-U10</f>
-        <v>263.166666666667</v>
+        <v>292.117</v>
       </c>
       <c r="X10" s="26" t="n">
         <f aca="false">W10/$P10/1000*100</f>
-        <v>0.502792584525834</v>
+        <v>0.558103589919948</v>
       </c>
       <c r="Y10" s="26"/>
       <c r="Z10" s="26"/>
-      <c r="AA10" s="0" t="n">
+      <c r="AA10" s="1" t="n">
         <f aca="false">Y10+Z10</f>
         <v>0</v>
       </c>
@@ -3933,33 +3928,33 @@
         <f aca="false">AA10/$P10/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="27" t="n">
+      <c r="AC10" s="2" t="n">
         <f aca="false">1000/100*Q10*($Q$41+$Q$47-$Q$49)-AA10</f>
-        <v>198.112254950241</v>
+        <v>216.321517901062</v>
       </c>
       <c r="AD10" s="26" t="n">
         <f aca="false">AC10/$P10/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE10" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE10" s="2" t="n">
         <f aca="false">AC10+Q10/100*1000 *($Q$46+$Q$43)</f>
-        <v>353.836824028197</v>
+        <v>376.027376680613</v>
       </c>
       <c r="AF10" s="26" t="n">
         <f aca="false">AE10/$P10/1000*100</f>
-        <v>0.676022284687334</v>
+        <v>0.718418403699993</v>
       </c>
       <c r="AG10" s="26" t="n">
         <f aca="false">-AA10+($Q$45 + $Q$46)*1000*Q10/100</f>
-        <v>162.16276350151</v>
+        <v>180.372026452331</v>
       </c>
       <c r="AH10" s="26" t="n">
         <f aca="false">AG10/P10/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI10" s="26" t="n">
         <f aca="false">AG10/P10</f>
-        <v>3.09819765578628</v>
+        <v>3.44609438971993</v>
       </c>
       <c r="AK10" s="26" t="n">
         <f aca="false">-Q10*($Q$47)*10</f>
@@ -3989,7 +3984,7 @@
         <f aca="false">AW10*1000</f>
         <v>270</v>
       </c>
-      <c r="BA10" s="28" t="s">
+      <c r="BA10" s="27" t="s">
         <v>55</v>
       </c>
       <c r="BB10" s="23" t="n">
@@ -3998,15 +3993,15 @@
       <c r="BC10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="BD10" s="28" t="n">
+      <c r="BD10" s="27" t="n">
         <f aca="false">BB10+BC10/10</f>
         <v>1.6</v>
       </c>
-      <c r="BE10" s="28" t="n">
+      <c r="BE10" s="27" t="n">
         <f aca="false">1000*BD10</f>
         <v>1600</v>
       </c>
-      <c r="BG10" s="28" t="s">
+      <c r="BG10" s="27" t="s">
         <v>56</v>
       </c>
       <c r="BH10" s="23" t="n">
@@ -4024,10 +4019,10 @@
       <c r="BL10" s="23" t="n">
         <v>1.48</v>
       </c>
-      <c r="BM10" s="28" t="s">
+      <c r="BM10" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="BO10" s="28" t="n">
+      <c r="BO10" s="27" t="n">
         <f aca="false">BH10*1000</f>
         <v>270</v>
       </c>
@@ -4055,13 +4050,13 @@
       <c r="BY10" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="XFA10" s="0"/>
-      <c r="XFB10" s="0"/>
-      <c r="XFC10" s="0"/>
-      <c r="XFD10" s="0"/>
+      <c r="XFA10" s="1"/>
+      <c r="XFB10" s="1"/>
+      <c r="XFC10" s="1"/>
+      <c r="XFD10" s="1"/>
     </row>
     <row r="11" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>60</v>
       </c>
       <c r="B11" s="23" t="n">
@@ -4078,14 +4073,14 @@
         <f aca="false">D11/$P11/10</f>
         <v>0.0444687692412944</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="29" t="n">
         <v>0.3</v>
       </c>
       <c r="G11" s="24" t="n">
         <f aca="false">F11/$P11/10</f>
         <v>0.000513101183553397</v>
       </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="29" t="n">
         <v>36</v>
       </c>
       <c r="I11" s="24" t="n">
@@ -4094,22 +4089,22 @@
       </c>
       <c r="J11" s="23" t="n">
         <f aca="false">L11*$J$37/100</f>
-        <v>64.6</v>
+        <v>88.6692</v>
       </c>
       <c r="K11" s="24" t="n">
         <f aca="false">J11/$P11/10</f>
-        <v>0.110487788191831</v>
+        <v>0.151654238215776</v>
       </c>
       <c r="L11" s="23" t="n">
         <v>380</v>
       </c>
       <c r="M11" s="23" t="n">
         <f aca="false">O11*$M$37/100</f>
-        <v>312.8</v>
+        <v>338.3484</v>
       </c>
       <c r="N11" s="24" t="n">
         <f aca="false">M11/$P11/10</f>
-        <v>0.534993500718342</v>
+        <v>0.57868988164466</v>
       </c>
       <c r="O11" s="23" t="n">
         <v>2300</v>
@@ -4123,35 +4118,35 @@
       </c>
       <c r="R11" s="23" t="n">
         <f aca="false">H11+F11+B11+D11+J11+M11</f>
-        <v>485.7</v>
+        <v>535.3176</v>
       </c>
       <c r="S11" s="26" t="n">
         <f aca="false">R11/$P11/1000*100</f>
-        <v>0.830710816172949</v>
+        <v>0.915573647123213</v>
       </c>
       <c r="T11" s="26" t="n">
         <f aca="false">R11/P11</f>
-        <v>8.30710816172949</v>
-      </c>
-      <c r="U11" s="27" t="n">
+        <v>9.15573647123213</v>
+      </c>
+      <c r="U11" s="2" t="n">
         <f aca="false">3/5*H11+M11/3</f>
-        <v>125.866666666667</v>
+        <v>134.3828</v>
       </c>
       <c r="V11" s="26" t="n">
         <f aca="false">U11/$P11/1000*100</f>
-        <v>0.215274452121958</v>
-      </c>
-      <c r="W11" s="27" t="n">
+        <v>0.229839912430731</v>
+      </c>
+      <c r="W11" s="2" t="n">
         <f aca="false">R11-U11</f>
-        <v>359.833333333333</v>
+        <v>400.9348</v>
       </c>
       <c r="X11" s="26" t="n">
         <f aca="false">W11/$P11/1000*100</f>
-        <v>0.615436364050991</v>
+        <v>0.685733734692482</v>
       </c>
       <c r="Y11" s="26"/>
       <c r="Z11" s="26"/>
-      <c r="AA11" s="0" t="n">
+      <c r="AA11" s="1" t="n">
         <f aca="false">Y11+Z11</f>
         <v>0</v>
       </c>
@@ -4159,33 +4154,33 @@
         <f aca="false">AA11/$P11/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC11" s="27" t="n">
+      <c r="AC11" s="2" t="n">
         <f aca="false">1000/100*Q11*($Q$41+$Q$47-$Q$49)-AA11</f>
-        <v>221.303133727493</v>
+        <v>241.643959967125</v>
       </c>
       <c r="AD11" s="26" t="n">
         <f aca="false">AC11/$P11/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE11" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE11" s="2" t="n">
         <f aca="false">AC11+Q11/100*1000 *($Q$46+$Q$43)</f>
-        <v>395.25670941099</v>
+        <v>420.044872275312</v>
       </c>
       <c r="AF11" s="26" t="n">
         <f aca="false">AE11/$P11/1000*100</f>
-        <v>0.676022284687334</v>
+        <v>0.718418403699993</v>
       </c>
       <c r="AG11" s="26" t="n">
         <f aca="false">-AA11+($Q$45 + $Q$46)*1000*Q11/100</f>
-        <v>181.145420538512</v>
+        <v>201.486246778145</v>
       </c>
       <c r="AH11" s="26" t="n">
         <f aca="false">AG11/P11/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI11" s="26" t="n">
         <f aca="false">ROUND(AG11/P11 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK11" s="26" t="n">
         <f aca="false">-Q11*($Q$47)*10</f>
@@ -4215,7 +4210,7 @@
         <f aca="false">AW11*1000</f>
         <v>380</v>
       </c>
-      <c r="BA11" s="28" t="s">
+      <c r="BA11" s="27" t="s">
         <v>60</v>
       </c>
       <c r="BB11" s="23" t="n">
@@ -4224,15 +4219,15 @@
       <c r="BC11" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="BD11" s="28" t="n">
+      <c r="BD11" s="27" t="n">
         <f aca="false">BB11+BC11/10</f>
         <v>2.3</v>
       </c>
-      <c r="BE11" s="28" t="n">
+      <c r="BE11" s="27" t="n">
         <f aca="false">1000*BD11</f>
         <v>2300</v>
       </c>
-      <c r="BG11" s="28" t="s">
+      <c r="BG11" s="27" t="s">
         <v>61</v>
       </c>
       <c r="BH11" s="23" t="n">
@@ -4250,10 +4245,10 @@
       <c r="BL11" s="23" t="n">
         <v>2.39</v>
       </c>
-      <c r="BM11" s="28" t="s">
+      <c r="BM11" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="BO11" s="28" t="n">
+      <c r="BO11" s="27" t="n">
         <f aca="false">BH11*1000</f>
         <v>380</v>
       </c>
@@ -4281,10 +4276,10 @@
       <c r="BY11" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="XFA11" s="0"/>
-      <c r="XFB11" s="0"/>
-      <c r="XFC11" s="0"/>
-      <c r="XFD11" s="0"/>
+      <c r="XFA11" s="1"/>
+      <c r="XFB11" s="1"/>
+      <c r="XFC11" s="1"/>
+      <c r="XFD11" s="1"/>
     </row>
     <row r="12" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
@@ -4320,22 +4315,22 @@
       </c>
       <c r="J12" s="23" t="n">
         <f aca="false">L12*$J$37/100</f>
-        <v>49.3</v>
+        <v>67.6686</v>
       </c>
       <c r="K12" s="24" t="n">
         <f aca="false">J12/$P12/10</f>
-        <v>0.224192814915871</v>
+        <v>0.307724420190996</v>
       </c>
       <c r="L12" s="23" t="n">
         <v>290</v>
       </c>
       <c r="M12" s="23" t="n">
         <f aca="false">O12*$M$37/100</f>
-        <v>204</v>
+        <v>220.662</v>
       </c>
       <c r="N12" s="24" t="n">
         <f aca="false">M12/$P12/10</f>
-        <v>0.927694406548431</v>
+        <v>1.00346521145975</v>
       </c>
       <c r="O12" s="23" t="n">
         <v>1500</v>
@@ -4349,35 +4344,35 @@
       </c>
       <c r="R12" s="23" t="n">
         <f aca="false">H12+F12+B12+D12+J12+M12</f>
-        <v>333.1</v>
+        <v>368.1306</v>
       </c>
       <c r="S12" s="26" t="n">
         <f aca="false">R12/$P12/1000*100</f>
-        <v>1.51477944520237</v>
+        <v>1.67408185538881</v>
       </c>
       <c r="T12" s="26" t="n">
         <f aca="false">R12/P12</f>
-        <v>15.1477944520237</v>
-      </c>
-      <c r="U12" s="27" t="n">
+        <v>16.7408185538881</v>
+      </c>
+      <c r="U12" s="2" t="n">
         <f aca="false">3/5*H12+M12/3</f>
-        <v>95.6</v>
+        <v>101.154</v>
       </c>
       <c r="V12" s="26" t="n">
         <f aca="false">U12/$P12/1000*100</f>
-        <v>0.434743065029559</v>
-      </c>
-      <c r="W12" s="27" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="W12" s="2" t="n">
         <f aca="false">R12-U12</f>
-        <v>237.5</v>
+        <v>266.9766</v>
       </c>
       <c r="X12" s="26" t="n">
         <f aca="false">W12/$P12/1000*100</f>
-        <v>1.08003638017281</v>
+        <v>1.21408185538881</v>
       </c>
       <c r="Y12" s="26"/>
       <c r="Z12" s="26"/>
-      <c r="AA12" s="0" t="n">
+      <c r="AA12" s="1" t="n">
         <f aca="false">Y12+Z12</f>
         <v>0</v>
       </c>
@@ -4385,33 +4380,33 @@
         <f aca="false">AA12/$P12/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="27" t="n">
+      <c r="AC12" s="2" t="n">
         <f aca="false">1000/100*Q12*($Q$41+$Q$47-$Q$49)-AA12</f>
-        <v>83.2328095824651</v>
+        <v>90.8830587616661</v>
       </c>
       <c r="AD12" s="26" t="n">
         <f aca="false">AC12/$P12/1000*100</f>
-        <v>0.378502999465508</v>
-      </c>
-      <c r="AE12" s="27" t="n">
+        <v>0.413292672858873</v>
+      </c>
+      <c r="AE12" s="2" t="n">
         <f aca="false">AC12+Q12/100*1000 *($Q$46+$Q$43)</f>
-        <v>148.657300402745</v>
+        <v>157.980206973629</v>
       </c>
       <c r="AF12" s="26" t="n">
         <f aca="false">AE12/$P12/1000*100</f>
-        <v>0.676022284687335</v>
+        <v>0.718418403699994</v>
       </c>
       <c r="AG12" s="26" t="n">
         <f aca="false">-AA12+($Q$45 + $Q$46)*1000*Q12/100</f>
-        <v>68.1293664507404</v>
+        <v>75.7796156299414</v>
       </c>
       <c r="AH12" s="26" t="n">
         <f aca="false">AG12/P12/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971994</v>
       </c>
       <c r="AI12" s="26" t="n">
         <f aca="false">ROUND(AG12/P12 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK12" s="26" t="n">
         <f aca="false">-Q12*($Q$47)*10</f>
@@ -4441,7 +4436,7 @@
         <f aca="false">AW12*1000</f>
         <v>290</v>
       </c>
-      <c r="BA12" s="28" t="s">
+      <c r="BA12" s="27" t="s">
         <v>65</v>
       </c>
       <c r="BB12" s="23" t="n">
@@ -4450,15 +4445,15 @@
       <c r="BC12" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="BD12" s="28" t="n">
+      <c r="BD12" s="27" t="n">
         <f aca="false">BB12+BC12/10</f>
         <v>1.5</v>
       </c>
-      <c r="BE12" s="28" t="n">
+      <c r="BE12" s="27" t="n">
         <f aca="false">1000*BD12</f>
         <v>1500</v>
       </c>
-      <c r="BG12" s="28" t="s">
+      <c r="BG12" s="27" t="s">
         <v>66</v>
       </c>
       <c r="BH12" s="23" t="n">
@@ -4476,10 +4471,10 @@
       <c r="BL12" s="23" t="n">
         <v>5.29</v>
       </c>
-      <c r="BM12" s="28" t="s">
+      <c r="BM12" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="BO12" s="28" t="n">
+      <c r="BO12" s="27" t="n">
         <f aca="false">BH12*1000</f>
         <v>290</v>
       </c>
@@ -4507,13 +4502,13 @@
       <c r="BY12" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="XFA12" s="0"/>
-      <c r="XFB12" s="0"/>
-      <c r="XFC12" s="0"/>
-      <c r="XFD12" s="0"/>
+      <c r="XFA12" s="1"/>
+      <c r="XFB12" s="1"/>
+      <c r="XFC12" s="1"/>
+      <c r="XFD12" s="1"/>
     </row>
     <row r="13" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="28" t="s">
         <v>72</v>
       </c>
       <c r="B13" s="23" t="n">
@@ -4530,14 +4525,14 @@
         <f aca="false">D13/$P13/10</f>
         <v>0.115567312466769</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="29" t="n">
         <v>3.8</v>
       </c>
       <c r="G13" s="24" t="n">
         <f aca="false">F13/$P13/10</f>
         <v>0.00166979386834115</v>
       </c>
-      <c r="H13" s="30" t="n">
+      <c r="H13" s="29" t="n">
         <v>348</v>
       </c>
       <c r="I13" s="24" t="n">
@@ -4546,22 +4541,22 @@
       </c>
       <c r="J13" s="23" t="n">
         <f aca="false">L13*$J$37/100</f>
-        <v>74.8</v>
+        <v>102.6696</v>
       </c>
       <c r="K13" s="24" t="n">
         <f aca="false">J13/$P13/10</f>
-        <v>0.0328685740399784</v>
+        <v>0.045115018038168</v>
       </c>
       <c r="L13" s="23" t="n">
         <v>440</v>
       </c>
       <c r="M13" s="23" t="n">
         <f aca="false">O13*$M$37/100</f>
-        <v>625.6</v>
+        <v>676.6968</v>
       </c>
       <c r="N13" s="24" t="n">
         <f aca="false">M13/$P13/10</f>
-        <v>0.274900801061637</v>
+        <v>0.297353728254231</v>
       </c>
       <c r="O13" s="23" t="n">
         <v>4600</v>
@@ -4575,35 +4570,35 @@
       </c>
       <c r="R13" s="23" t="n">
         <f aca="false">H13+F13+B13+D13+J13+M13</f>
-        <v>1493.2</v>
+        <v>1572.1664</v>
       </c>
       <c r="S13" s="26" t="n">
         <f aca="false">R13/$P13/1000*100</f>
-        <v>0.656141106370264</v>
+        <v>0.690840477561046</v>
       </c>
       <c r="T13" s="26" t="n">
         <f aca="false">R13/P13</f>
-        <v>6.56141106370264</v>
-      </c>
-      <c r="U13" s="27" t="n">
+        <v>6.90840477561046</v>
+      </c>
+      <c r="U13" s="2" t="n">
         <f aca="false">3/5*H13+M13/3</f>
-        <v>417.333333333333</v>
+        <v>434.3656</v>
       </c>
       <c r="V13" s="26" t="n">
         <f aca="false">U13/$P13/1000*100</f>
-        <v>0.183384379224835</v>
-      </c>
-      <c r="W13" s="27" t="n">
+        <v>0.190868688289033</v>
+      </c>
+      <c r="W13" s="2" t="n">
         <f aca="false">R13-U13</f>
-        <v>1075.86666666667</v>
+        <v>1137.8008</v>
       </c>
       <c r="X13" s="26" t="n">
         <f aca="false">W13/$P13/1000*100</f>
-        <v>0.472756727145429</v>
+        <v>0.499971789272014</v>
       </c>
       <c r="Y13" s="26"/>
       <c r="Z13" s="26"/>
-      <c r="AA13" s="0" t="n">
+      <c r="AA13" s="1" t="n">
         <f aca="false">Y13+Z13</f>
         <v>0</v>
       </c>
@@ -4611,33 +4606,33 @@
         <f aca="false">AA13/$P13/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC13" s="27" t="n">
+      <c r="AC13" s="2" t="n">
         <f aca="false">1000/100*Q13*($Q$41+$Q$47-$Q$49)-AA13</f>
-        <v>861.370630973638</v>
+        <v>940.542534405121</v>
       </c>
       <c r="AD13" s="26" t="n">
         <f aca="false">AC13/$P13/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE13" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE13" s="2" t="n">
         <f aca="false">AC13+Q13/100*1000 *($Q$46+$Q$43)</f>
-        <v>1538.44419393151</v>
+        <v>1634.92631385218</v>
       </c>
       <c r="AF13" s="26" t="n">
         <f aca="false">AE13/$P13/1000*100</f>
-        <v>0.676022284687334</v>
+        <v>0.718418403699993</v>
       </c>
       <c r="AG13" s="26" t="n">
         <f aca="false">-AA13+($Q$45 + $Q$46)*1000*Q13/100</f>
-        <v>705.066135120251</v>
+        <v>784.238038551734</v>
       </c>
       <c r="AH13" s="26" t="n">
         <f aca="false">AG13/P13/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI13" s="26" t="n">
         <f aca="false">ROUND(AG13/P13 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK13" s="26" t="n">
         <f aca="false">-Q13*($Q$47)*10</f>
@@ -4667,7 +4662,7 @@
         <f aca="false">AW13*1000</f>
         <v>440</v>
       </c>
-      <c r="BA13" s="28" t="s">
+      <c r="BA13" s="27" t="s">
         <v>74</v>
       </c>
       <c r="BB13" s="23" t="n">
@@ -4676,15 +4671,15 @@
       <c r="BC13" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="BD13" s="28" t="n">
+      <c r="BD13" s="27" t="n">
         <f aca="false">BB13+BC13/10</f>
         <v>4.6</v>
       </c>
-      <c r="BE13" s="28" t="n">
+      <c r="BE13" s="27" t="n">
         <f aca="false">1000*BD13</f>
         <v>4600</v>
       </c>
-      <c r="BG13" s="28" t="s">
+      <c r="BG13" s="27" t="s">
         <v>73</v>
       </c>
       <c r="BH13" s="23" t="n">
@@ -4702,10 +4697,10 @@
       <c r="BL13" s="23" t="n">
         <v>0.79</v>
       </c>
-      <c r="BM13" s="28" t="s">
+      <c r="BM13" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="BO13" s="28" t="n">
+      <c r="BO13" s="27" t="n">
         <f aca="false">BH13*1000</f>
         <v>440</v>
       </c>
@@ -4733,10 +4728,10 @@
       <c r="BY13" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="XFA13" s="0"/>
-      <c r="XFB13" s="0"/>
-      <c r="XFC13" s="0"/>
-      <c r="XFD13" s="0"/>
+      <c r="XFA13" s="1"/>
+      <c r="XFB13" s="1"/>
+      <c r="XFC13" s="1"/>
+      <c r="XFD13" s="1"/>
     </row>
     <row r="14" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
@@ -4772,22 +4767,22 @@
       </c>
       <c r="J14" s="23" t="n">
         <f aca="false">L14*$J$37/100</f>
-        <v>192.1</v>
+        <v>263.6742</v>
       </c>
       <c r="K14" s="24" t="n">
         <f aca="false">J14/$P14/10</f>
-        <v>0.0551431540391427</v>
+        <v>0.0756888444911386</v>
       </c>
       <c r="L14" s="23" t="n">
         <v>1130</v>
       </c>
       <c r="M14" s="23" t="n">
         <f aca="false">O14*$M$37/100</f>
-        <v>571.2</v>
+        <v>617.8536</v>
       </c>
       <c r="N14" s="24" t="n">
         <f aca="false">M14/$P14/10</f>
-        <v>0.163965484576566</v>
+        <v>0.17735760665507</v>
       </c>
       <c r="O14" s="23" t="n">
         <v>4200</v>
@@ -4801,35 +4796,35 @@
       </c>
       <c r="R14" s="23" t="n">
         <f aca="false">H14+F14+B14+D14+J14+M14</f>
-        <v>1776.1</v>
+        <v>1894.3278</v>
       </c>
       <c r="S14" s="26" t="n">
         <f aca="false">R14/$P14/1000*100</f>
-        <v>0.509837354965754</v>
+        <v>0.543775167496254</v>
       </c>
       <c r="T14" s="26" t="n">
         <f aca="false">R14/P14</f>
-        <v>5.09837354965754</v>
-      </c>
-      <c r="U14" s="27" t="n">
+        <v>5.43775167496254</v>
+      </c>
+      <c r="U14" s="2" t="n">
         <f aca="false">3/5*H14+M14/3</f>
-        <v>510.2</v>
+        <v>525.7512</v>
       </c>
       <c r="V14" s="26" t="n">
         <f aca="false">U14/$P14/1000*100</f>
-        <v>0.146455164970175</v>
-      </c>
-      <c r="W14" s="27" t="n">
+        <v>0.15091920566301</v>
+      </c>
+      <c r="W14" s="2" t="n">
         <f aca="false">R14-U14</f>
-        <v>1265.9</v>
+        <v>1368.5766</v>
       </c>
       <c r="X14" s="26" t="n">
         <f aca="false">W14/$P14/1000*100</f>
-        <v>0.363382189995579</v>
+        <v>0.392855961833244</v>
       </c>
       <c r="Y14" s="26"/>
       <c r="Z14" s="26"/>
-      <c r="AA14" s="0" t="n">
+      <c r="AA14" s="1" t="n">
         <f aca="false">Y14+Z14</f>
         <v>0</v>
       </c>
@@ -4837,33 +4832,33 @@
         <f aca="false">AA14/$P14/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="27" t="n">
+      <c r="AC14" s="2" t="n">
         <f aca="false">1000/100*Q14*($Q$41+$Q$47-$Q$49)-AA14</f>
-        <v>1318.57575911801</v>
+        <v>1439.77115273154</v>
       </c>
       <c r="AD14" s="26" t="n">
         <f aca="false">AC14/$P14/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE14" s="27" t="n">
+        <v>0.413292672858873</v>
+      </c>
+      <c r="AE14" s="2" t="n">
         <f aca="false">AC14+Q14/100*1000 *($Q$46+$Q$43)</f>
-        <v>2355.03179227388</v>
+        <v>2502.72545623352</v>
       </c>
       <c r="AF14" s="26" t="n">
         <f aca="false">AE14/$P14/1000*100</f>
-        <v>0.676022284687335</v>
+        <v>0.718418403699994</v>
       </c>
       <c r="AG14" s="26" t="n">
         <f aca="false">-AA14+($Q$45 + $Q$46)*1000*Q14/100</f>
-        <v>1079.30672455564</v>
+        <v>1200.50211816918</v>
       </c>
       <c r="AH14" s="26" t="n">
         <f aca="false">AG14/P14/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971994</v>
       </c>
       <c r="AI14" s="26" t="n">
         <f aca="false">ROUND(AG14/P14 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK14" s="26" t="n">
         <f aca="false">-Q14*($Q$47)*10</f>
@@ -4893,7 +4888,7 @@
         <f aca="false">AW14*1000</f>
         <v>1130</v>
       </c>
-      <c r="BA14" s="28" t="s">
+      <c r="BA14" s="27" t="s">
         <v>81</v>
       </c>
       <c r="BB14" s="23" t="n">
@@ -4902,15 +4897,15 @@
       <c r="BC14" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="BD14" s="28" t="n">
+      <c r="BD14" s="27" t="n">
         <f aca="false">BB14+BC14/10</f>
         <v>4.2</v>
       </c>
-      <c r="BE14" s="28" t="n">
+      <c r="BE14" s="27" t="n">
         <f aca="false">1000*BD14</f>
         <v>4200</v>
       </c>
-      <c r="BG14" s="28" t="s">
+      <c r="BG14" s="27" t="s">
         <v>80</v>
       </c>
       <c r="BH14" s="23" t="n">
@@ -4928,10 +4923,10 @@
       <c r="BL14" s="23" t="n">
         <v>1.49</v>
       </c>
-      <c r="BM14" s="28" t="s">
+      <c r="BM14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="BO14" s="28" t="n">
+      <c r="BO14" s="27" t="n">
         <f aca="false">BH14*1000</f>
         <v>1130</v>
       </c>
@@ -4959,13 +4954,13 @@
       <c r="BY14" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="XFA14" s="0"/>
-      <c r="XFB14" s="0"/>
-      <c r="XFC14" s="0"/>
-      <c r="XFD14" s="0"/>
+      <c r="XFA14" s="1"/>
+      <c r="XFB14" s="1"/>
+      <c r="XFC14" s="1"/>
+      <c r="XFD14" s="1"/>
     </row>
     <row r="15" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="28" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="23" t="n">
@@ -4982,14 +4977,14 @@
         <f aca="false">D15/$P15/10</f>
         <v>0.0679633645101783</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="29" t="n">
         <v>0.1</v>
       </c>
       <c r="G15" s="24" t="n">
         <f aca="false">F15/$P15/10</f>
         <v>0.000323635069096087</v>
       </c>
-      <c r="H15" s="30" t="n">
+      <c r="H15" s="29" t="n">
         <v>29</v>
       </c>
       <c r="I15" s="24" t="n">
@@ -4998,22 +4993,22 @@
       </c>
       <c r="J15" s="23" t="n">
         <f aca="false">L15*$J$37/100</f>
-        <v>15.3</v>
+        <v>21.0006</v>
       </c>
       <c r="K15" s="24" t="n">
         <f aca="false">J15/$P15/10</f>
-        <v>0.0495161655717014</v>
+        <v>0.0679653063205929</v>
       </c>
       <c r="L15" s="23" t="n">
         <v>90</v>
       </c>
       <c r="M15" s="23" t="n">
         <f aca="false">O15*$M$37/100</f>
-        <v>68</v>
+        <v>73.554</v>
       </c>
       <c r="N15" s="24" t="n">
         <f aca="false">M15/$P15/10</f>
-        <v>0.220071846985339</v>
+        <v>0.238046538722936</v>
       </c>
       <c r="O15" s="23" t="n">
         <v>500</v>
@@ -5027,35 +5022,35 @@
       </c>
       <c r="R15" s="23" t="n">
         <f aca="false">H15+F15+B15+D15+J15+M15</f>
-        <v>156.4</v>
+        <v>167.6546</v>
       </c>
       <c r="S15" s="26" t="n">
         <f aca="false">R15/$P15/1000*100</f>
-        <v>0.506165248066281</v>
+        <v>0.542589080552769</v>
       </c>
       <c r="T15" s="26" t="n">
         <f aca="false">R15/P15</f>
-        <v>5.0616524806628</v>
-      </c>
-      <c r="U15" s="27" t="n">
+        <v>5.42589080552769</v>
+      </c>
+      <c r="U15" s="2" t="n">
         <f aca="false">3/5*H15+M15/3</f>
-        <v>40.0666666666667</v>
+        <v>41.918</v>
       </c>
       <c r="V15" s="26" t="n">
         <f aca="false">U15/$P15/1000*100</f>
-        <v>0.129669784351166</v>
-      </c>
-      <c r="W15" s="27" t="n">
+        <v>0.135661348263698</v>
+      </c>
+      <c r="W15" s="2" t="n">
         <f aca="false">R15-U15</f>
-        <v>116.333333333333</v>
+        <v>125.7366</v>
       </c>
       <c r="X15" s="26" t="n">
         <f aca="false">W15/$P15/1000*100</f>
-        <v>0.376495463715115</v>
+        <v>0.406927732289071</v>
       </c>
       <c r="Y15" s="26"/>
       <c r="Z15" s="26"/>
-      <c r="AA15" s="0" t="n">
+      <c r="AA15" s="1" t="n">
         <f aca="false">Y15+Z15</f>
         <v>0</v>
       </c>
@@ -5063,33 +5058,33 @@
         <f aca="false">AA15/$P15/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="27" t="n">
+      <c r="AC15" s="2" t="n">
         <f aca="false">1000/100*Q15*($Q$41+$Q$47-$Q$49)-AA15</f>
-        <v>116.953641804847</v>
+        <v>127.703302986663</v>
       </c>
       <c r="AD15" s="26" t="n">
         <f aca="false">AC15/$P15/1000*100</f>
-        <v>0.378502999465506</v>
-      </c>
-      <c r="AE15" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE15" s="2" t="n">
         <f aca="false">AC15+Q15/100*1000 *($Q$46+$Q$43)</f>
-        <v>208.884125745539</v>
+        <v>221.984102559261</v>
       </c>
       <c r="AF15" s="26" t="n">
         <f aca="false">AE15/$P15/1000*100</f>
-        <v>0.676022284687333</v>
+        <v>0.718418403699992</v>
       </c>
       <c r="AG15" s="26" t="n">
         <f aca="false">-AA15+($Q$45 + $Q$46)*1000*Q15/100</f>
-        <v>95.7312093661401</v>
+        <v>106.480870547956</v>
       </c>
       <c r="AH15" s="26" t="n">
         <f aca="false">AG15/P15/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI15" s="26" t="n">
         <f aca="false">ROUND(AG15/P15 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK15" s="26" t="n">
         <f aca="false">-Q15*($Q$47)*10</f>
@@ -5119,7 +5114,7 @@
         <f aca="false">AW15*1000</f>
         <v>900</v>
       </c>
-      <c r="BA15" s="28" t="s">
+      <c r="BA15" s="27" t="s">
         <v>85</v>
       </c>
       <c r="BB15" s="23" t="n">
@@ -5128,15 +5123,15 @@
       <c r="BC15" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="BD15" s="28" t="n">
+      <c r="BD15" s="27" t="n">
         <f aca="false">BB15+BC15/10</f>
         <v>0.5</v>
       </c>
-      <c r="BE15" s="28" t="n">
+      <c r="BE15" s="27" t="n">
         <f aca="false">1000*BD15</f>
         <v>500</v>
       </c>
-      <c r="BG15" s="28" t="s">
+      <c r="BG15" s="27" t="s">
         <v>86</v>
       </c>
       <c r="BH15" s="23" t="n">
@@ -5154,10 +5149,10 @@
       <c r="BL15" s="23" t="n">
         <v>1.3</v>
       </c>
-      <c r="BM15" s="28" t="s">
+      <c r="BM15" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="BO15" s="28" t="n">
+      <c r="BO15" s="27" t="n">
         <f aca="false">BH15*1000</f>
         <v>90</v>
       </c>
@@ -5185,10 +5180,10 @@
       <c r="BY15" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="XFA15" s="0"/>
-      <c r="XFB15" s="0"/>
-      <c r="XFC15" s="0"/>
-      <c r="XFD15" s="0"/>
+      <c r="XFA15" s="1"/>
+      <c r="XFB15" s="1"/>
+      <c r="XFC15" s="1"/>
+      <c r="XFD15" s="1"/>
     </row>
     <row r="16" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
@@ -5224,22 +5219,22 @@
       </c>
       <c r="J16" s="23" t="n">
         <f aca="false">L16*$J$37/100</f>
-        <v>122.4</v>
+        <v>168.0048</v>
       </c>
       <c r="K16" s="24" t="n">
         <f aca="false">J16/$P16/10</f>
-        <v>0.0479235103188245</v>
+        <v>0.0657792464576147</v>
       </c>
       <c r="L16" s="23" t="n">
         <v>720</v>
       </c>
       <c r="M16" s="23" t="n">
         <f aca="false">O16*$M$37/100</f>
-        <v>394.4</v>
+        <v>426.6132</v>
       </c>
       <c r="N16" s="24" t="n">
         <f aca="false">M16/$P16/10</f>
-        <v>0.154420199916212</v>
+        <v>0.167032696832898</v>
       </c>
       <c r="O16" s="23" t="n">
         <v>2900</v>
@@ -5253,35 +5248,35 @@
       </c>
       <c r="R16" s="23" t="n">
         <f aca="false">H16+F16+B16+D16+J16+M16</f>
-        <v>980.1</v>
+        <v>1057.918</v>
       </c>
       <c r="S16" s="26" t="n">
         <f aca="false">R16/$P16/1000*100</f>
-        <v>0.38374046130294</v>
+        <v>0.414208694358416</v>
       </c>
       <c r="T16" s="26" t="n">
         <f aca="false">R16/P16</f>
-        <v>3.8374046130294</v>
-      </c>
-      <c r="U16" s="27" t="n">
+        <v>4.14208694358416</v>
+      </c>
+      <c r="U16" s="2" t="n">
         <f aca="false">3/5*H16+M16/3</f>
-        <v>222.666666666667</v>
+        <v>233.4044</v>
       </c>
       <c r="V16" s="26" t="n">
         <f aca="false">U16/$P16/1000*100</f>
-        <v>0.0871811135429595</v>
-      </c>
-      <c r="W16" s="27" t="n">
+        <v>0.0913852791818548</v>
+      </c>
+      <c r="W16" s="2" t="n">
         <f aca="false">R16-U16</f>
-        <v>757.433333333333</v>
+        <v>824.5136</v>
       </c>
       <c r="X16" s="26" t="n">
         <f aca="false">W16/$P16/1000*100</f>
-        <v>0.29655934775998</v>
+        <v>0.322823415176561</v>
       </c>
       <c r="Y16" s="26"/>
       <c r="Z16" s="26"/>
-      <c r="AA16" s="0" t="n">
+      <c r="AA16" s="1" t="n">
         <f aca="false">Y16+Z16</f>
         <v>0</v>
       </c>
@@ -5289,33 +5284,33 @@
         <f aca="false">AA16/$P16/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="27" t="n">
+      <c r="AC16" s="2" t="n">
         <f aca="false">1000/100*Q16*($Q$41+$Q$47-$Q$49)-AA16</f>
-        <v>966.723155844868</v>
+        <v>1055.57841696866</v>
       </c>
       <c r="AD16" s="26" t="n">
         <f aca="false">AC16/$P16/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE16" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE16" s="2" t="n">
         <f aca="false">AC16+Q16/100*1000 *($Q$46+$Q$43)</f>
-        <v>1726.60823665138</v>
+        <v>1834.89089233804</v>
       </c>
       <c r="AF16" s="26" t="n">
         <f aca="false">AE16/$P16/1000*100</f>
-        <v>0.676022284687334</v>
+        <v>0.718418403699993</v>
       </c>
       <c r="AG16" s="26" t="n">
         <f aca="false">-AA16+($Q$45 + $Q$46)*1000*Q16/100</f>
-        <v>791.301368671407</v>
+        <v>880.156629795199</v>
       </c>
       <c r="AH16" s="26" t="n">
         <f aca="false">AG16/P16/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI16" s="26" t="n">
         <f aca="false">ROUND(AG16/P16 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK16" s="26" t="n">
         <f aca="false">-Q16*($Q$47)*10</f>
@@ -5345,7 +5340,7 @@
         <f aca="false">AW16*1000</f>
         <v>720</v>
       </c>
-      <c r="BA16" s="28" t="s">
+      <c r="BA16" s="27" t="s">
         <v>90</v>
       </c>
       <c r="BB16" s="23" t="n">
@@ -5354,15 +5349,15 @@
       <c r="BC16" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="BD16" s="28" t="n">
+      <c r="BD16" s="27" t="n">
         <f aca="false">BB16+BC16/10</f>
         <v>2.9</v>
       </c>
-      <c r="BE16" s="28" t="n">
+      <c r="BE16" s="27" t="n">
         <f aca="false">1000*BD16</f>
         <v>2900</v>
       </c>
-      <c r="BG16" s="28" t="s">
+      <c r="BG16" s="27" t="s">
         <v>91</v>
       </c>
       <c r="BH16" s="23" t="n">
@@ -5380,10 +5375,10 @@
       <c r="BL16" s="23" t="n">
         <v>1.36</v>
       </c>
-      <c r="BM16" s="28" t="s">
+      <c r="BM16" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="BO16" s="28" t="n">
+      <c r="BO16" s="27" t="n">
         <f aca="false">BH16*1000</f>
         <v>720</v>
       </c>
@@ -5411,13 +5406,13 @@
       <c r="BY16" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="XFA16" s="0"/>
-      <c r="XFB16" s="0"/>
-      <c r="XFC16" s="0"/>
-      <c r="XFD16" s="0"/>
+      <c r="XFA16" s="1"/>
+      <c r="XFB16" s="1"/>
+      <c r="XFC16" s="1"/>
+      <c r="XFD16" s="1"/>
     </row>
     <row r="17" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>95</v>
       </c>
       <c r="B17" s="23" t="n">
@@ -5434,14 +5429,14 @@
         <f aca="false">D17/$P17/10</f>
         <v>0.0656779628101934</v>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="29" t="n">
         <v>3100</v>
       </c>
       <c r="G17" s="24" t="n">
         <f aca="false">F17/$P17/10</f>
         <v>0.120403125199054</v>
       </c>
-      <c r="H17" s="30" t="n">
+      <c r="H17" s="29" t="n">
         <v>6670</v>
       </c>
       <c r="I17" s="24" t="n">
@@ -5450,22 +5445,22 @@
       </c>
       <c r="J17" s="23" t="n">
         <f aca="false">L17*$J$37/100</f>
-        <v>914.6</v>
+        <v>1255.3692</v>
       </c>
       <c r="K17" s="24" t="n">
         <f aca="false">J17/$P17/10</f>
-        <v>0.0355228059055014</v>
+        <v>0.0487581854705276</v>
       </c>
       <c r="L17" s="23" t="n">
         <v>5380</v>
       </c>
       <c r="M17" s="23" t="n">
         <f aca="false">O17*$M$37/100</f>
-        <v>8432</v>
+        <v>9120.696</v>
       </c>
       <c r="N17" s="24" t="n">
         <f aca="false">M17/$P17/10</f>
-        <v>0.327496500541426</v>
+        <v>0.354245258835647</v>
       </c>
       <c r="O17" s="23" t="n">
         <v>62000</v>
@@ -5479,31 +5474,31 @@
       </c>
       <c r="R17" s="23" t="n">
         <f aca="false">H17+F17+B17+D17+J17+M17</f>
-        <v>21891.6</v>
+        <v>22921.0652</v>
       </c>
       <c r="S17" s="26" t="n">
         <f aca="false">R17/$P17/1000*100</f>
-        <v>0.850263566325032</v>
+        <v>0.890247704184281</v>
       </c>
       <c r="T17" s="26" t="n">
         <f aca="false">R17/P17</f>
-        <v>8.50263566325032</v>
-      </c>
-      <c r="U17" s="27" t="n">
+        <v>8.90247704184281</v>
+      </c>
+      <c r="U17" s="2" t="n">
         <f aca="false">3/5*H17+M17/3</f>
-        <v>6812.66666666667</v>
+        <v>7042.232</v>
       </c>
       <c r="V17" s="26" t="n">
         <f aca="false">U17/$P17/1000*100</f>
-        <v>0.264602050840673</v>
-      </c>
-      <c r="W17" s="27" t="n">
+        <v>0.273518303605413</v>
+      </c>
+      <c r="W17" s="2" t="n">
         <f aca="false">R17-U17</f>
-        <v>15078.9333333333</v>
+        <v>15878.8332</v>
       </c>
       <c r="X17" s="26" t="n">
         <f aca="false">W17/$P17/1000*100</f>
-        <v>0.58566151548436</v>
+        <v>0.616729400578867</v>
       </c>
       <c r="Y17" s="26" t="n">
         <f aca="false">B17</f>
@@ -5513,7 +5508,7 @@
         <f aca="false">F17</f>
         <v>3100</v>
       </c>
-      <c r="AA17" s="0" t="n">
+      <c r="AA17" s="1" t="n">
         <f aca="false">Y17+Z17</f>
         <v>4184</v>
       </c>
@@ -5521,33 +5516,33 @@
         <f aca="false">AA17/$P17/1000*100</f>
         <v>0.162505379300916</v>
       </c>
-      <c r="AC17" s="27" t="n">
+      <c r="AC17" s="2" t="n">
         <f aca="false">1000/100*Q17*($Q$41+$Q$47-$Q$49)-AA17</f>
-        <v>5561.25616675849</v>
+        <v>6456.98032126972</v>
       </c>
       <c r="AD17" s="26" t="n">
         <f aca="false">AC17/$P17/1000*100</f>
-        <v>0.215997620164591</v>
-      </c>
-      <c r="AE17" s="27" t="n">
+        <v>0.250787293557956</v>
+      </c>
+      <c r="AE17" s="2" t="n">
         <f aca="false">AC17+Q17/100*1000 *($Q$46+$Q$43)</f>
-        <v>13221.4376002792</v>
+        <v>14313.0036931191</v>
       </c>
       <c r="AF17" s="26" t="n">
         <f aca="false">AE17/$P17/1000*100</f>
-        <v>0.513516905386417</v>
+        <v>0.555913024399076</v>
       </c>
       <c r="AG17" s="26" t="n">
         <f aca="false">-AA17+($Q$45 + $Q$46)*1000*Q17/100</f>
-        <v>3792.87993319044</v>
+        <v>4688.60408770167</v>
       </c>
       <c r="AH17" s="26" t="n">
         <f aca="false">AG17/P17/10</f>
-        <v>0.147314386277712</v>
+        <v>0.182104059671077</v>
       </c>
       <c r="AI17" s="26" t="n">
         <f aca="false">ROUND(AG17/P17 *100/1000, 2)</f>
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="AK17" s="26" t="n">
         <f aca="false">-Q17*($Q$47)*10</f>
@@ -5577,7 +5572,7 @@
         <f aca="false">AW17*1000</f>
         <v>5380</v>
       </c>
-      <c r="BA17" s="28" t="s">
+      <c r="BA17" s="27" t="s">
         <v>97</v>
       </c>
       <c r="BB17" s="23" t="n">
@@ -5586,15 +5581,15 @@
       <c r="BC17" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="BD17" s="28" t="n">
+      <c r="BD17" s="27" t="n">
         <f aca="false">BB17+BC17/10</f>
         <v>62</v>
       </c>
-      <c r="BE17" s="28" t="n">
+      <c r="BE17" s="27" t="n">
         <f aca="false">1000*BD17</f>
         <v>62000</v>
       </c>
-      <c r="BG17" s="28" t="s">
+      <c r="BG17" s="27" t="s">
         <v>96</v>
       </c>
       <c r="BH17" s="23" t="n">
@@ -5612,10 +5607,10 @@
       <c r="BL17" s="23" t="n">
         <v>0.98</v>
       </c>
-      <c r="BM17" s="28" t="s">
+      <c r="BM17" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="BO17" s="28" t="n">
+      <c r="BO17" s="27" t="n">
         <f aca="false">BH17*1000</f>
         <v>5380</v>
       </c>
@@ -5643,10 +5638,10 @@
       <c r="BY17" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="XFA17" s="0"/>
-      <c r="XFB17" s="0"/>
-      <c r="XFC17" s="0"/>
-      <c r="XFD17" s="0"/>
+      <c r="XFA17" s="1"/>
+      <c r="XFB17" s="1"/>
+      <c r="XFC17" s="1"/>
+      <c r="XFD17" s="1"/>
     </row>
     <row r="18" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
@@ -5682,22 +5677,22 @@
       </c>
       <c r="J18" s="23" t="n">
         <f aca="false">L18*$J$37/100</f>
-        <v>1026.8</v>
+        <v>1409.3736</v>
       </c>
       <c r="K18" s="24" t="n">
         <f aca="false">J18/$P18/10</f>
-        <v>0.0275318554936884</v>
+        <v>0.0377899009464545</v>
       </c>
       <c r="L18" s="23" t="n">
         <v>6040</v>
       </c>
       <c r="M18" s="23" t="n">
         <f aca="false">O18*$M$37/100</f>
-        <v>7847.2</v>
+        <v>8488.1316</v>
       </c>
       <c r="N18" s="24" t="n">
         <f aca="false">M18/$P18/10</f>
-        <v>0.210409014832559</v>
+        <v>0.22759448054403</v>
       </c>
       <c r="O18" s="23" t="n">
         <v>57700</v>
@@ -5711,35 +5706,35 @@
       </c>
       <c r="R18" s="23" t="n">
         <f aca="false">H18+F18+B18+D18+J18+M18</f>
-        <v>22491.2</v>
+        <v>23514.7052</v>
       </c>
       <c r="S18" s="26" t="n">
         <f aca="false">R18/$P18/1000*100</f>
-        <v>0.603062396065101</v>
+        <v>0.630505907229338</v>
       </c>
       <c r="T18" s="26" t="n">
         <f aca="false">R18/P18</f>
-        <v>6.030623960651</v>
-      </c>
-      <c r="U18" s="27" t="n">
+        <v>6.30505907229338</v>
+      </c>
+      <c r="U18" s="2" t="n">
         <f aca="false">3/5*H18+M18/3</f>
-        <v>7622.13333333333</v>
+        <v>7835.7772</v>
       </c>
       <c r="V18" s="26" t="n">
         <f aca="false">U18/$P18/1000*100</f>
-        <v>0.204374243754343</v>
-      </c>
-      <c r="W18" s="27" t="n">
+        <v>0.210102732324833</v>
+      </c>
+      <c r="W18" s="2" t="n">
         <f aca="false">R18-U18</f>
-        <v>14869.0666666667</v>
+        <v>15678.928</v>
       </c>
       <c r="X18" s="26" t="n">
         <f aca="false">W18/$P18/1000*100</f>
-        <v>0.398688152310758</v>
+        <v>0.420403174904505</v>
       </c>
       <c r="Y18" s="26"/>
       <c r="Z18" s="26"/>
-      <c r="AA18" s="0" t="n">
+      <c r="AA18" s="1" t="n">
         <f aca="false">Y18+Z18</f>
         <v>0</v>
       </c>
@@ -5747,33 +5742,33 @@
         <f aca="false">AA18/$P18/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC18" s="27" t="n">
+      <c r="AC18" s="2" t="n">
         <f aca="false">1000/100*Q18*($Q$41+$Q$47-$Q$49)-AA18</f>
-        <v>14116.2617950061</v>
+        <v>15413.7419684182</v>
       </c>
       <c r="AD18" s="26" t="n">
         <f aca="false">AC18/$P18/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE18" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE18" s="2" t="n">
         <f aca="false">AC18+Q18/100*1000 *($Q$46+$Q$43)</f>
-        <v>25212.2375869684</v>
+        <v>26793.3999976231</v>
       </c>
       <c r="AF18" s="26" t="n">
         <f aca="false">AE18/$P18/1000*100</f>
-        <v>0.676022284687333</v>
+        <v>0.718418403699992</v>
       </c>
       <c r="AG18" s="26" t="n">
         <f aca="false">-AA18+($Q$45 + $Q$46)*1000*Q18/100</f>
-        <v>11554.7219608596</v>
+        <v>12852.2021342717</v>
       </c>
       <c r="AH18" s="26" t="n">
         <f aca="false">AG18/P18/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI18" s="26" t="n">
         <f aca="false">ROUND(AG18/P18 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK18" s="26" t="n">
         <f aca="false">-Q18*($Q$47)*10</f>
@@ -5803,7 +5798,7 @@
         <f aca="false">AW18*1000</f>
         <v>6400</v>
       </c>
-      <c r="BA18" s="28" t="s">
+      <c r="BA18" s="27" t="s">
         <v>104</v>
       </c>
       <c r="BB18" s="23" t="n">
@@ -5812,15 +5807,15 @@
       <c r="BC18" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="BD18" s="28" t="n">
+      <c r="BD18" s="27" t="n">
         <f aca="false">BB18+BC18/10</f>
         <v>57.7</v>
       </c>
-      <c r="BE18" s="28" t="n">
+      <c r="BE18" s="27" t="n">
         <f aca="false">1000*BD18</f>
         <v>57700</v>
       </c>
-      <c r="BG18" s="28" t="s">
+      <c r="BG18" s="27" t="s">
         <v>103</v>
       </c>
       <c r="BH18" s="23" t="n">
@@ -5838,10 +5833,10 @@
       <c r="BL18" s="23" t="n">
         <v>0.73</v>
       </c>
-      <c r="BM18" s="28" t="s">
+      <c r="BM18" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="BO18" s="28" t="n">
+      <c r="BO18" s="27" t="n">
         <f aca="false">BH18*1000</f>
         <v>6040</v>
       </c>
@@ -5869,13 +5864,13 @@
       <c r="BY18" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="XFA18" s="0"/>
-      <c r="XFB18" s="0"/>
-      <c r="XFC18" s="0"/>
-      <c r="XFD18" s="0"/>
+      <c r="XFA18" s="1"/>
+      <c r="XFB18" s="1"/>
+      <c r="XFC18" s="1"/>
+      <c r="XFD18" s="1"/>
     </row>
     <row r="19" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="28" t="s">
         <v>109</v>
       </c>
       <c r="B19" s="23" t="n">
@@ -5892,14 +5887,14 @@
         <f aca="false">D19/$P19/10</f>
         <v>0.0298538818339129</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="29" t="n">
         <v>22.7</v>
       </c>
       <c r="G19" s="24" t="n">
         <f aca="false">F19/$P19/10</f>
         <v>0.0125496873635152</v>
       </c>
-      <c r="H19" s="30" t="n">
+      <c r="H19" s="29" t="n">
         <v>118</v>
       </c>
       <c r="I19" s="24" t="n">
@@ -5908,22 +5903,22 @@
       </c>
       <c r="J19" s="23" t="n">
         <f aca="false">L19*$J$37/100</f>
-        <v>431.8</v>
+        <v>592.6836</v>
       </c>
       <c r="K19" s="24" t="n">
         <f aca="false">J19/$P19/10</f>
-        <v>0.238720484738585</v>
+        <v>0.327664928875891</v>
       </c>
       <c r="L19" s="23" t="n">
         <v>2540</v>
       </c>
       <c r="M19" s="23" t="n">
         <f aca="false">O19*$M$37/100</f>
-        <v>856.8</v>
+        <v>926.7804</v>
       </c>
       <c r="N19" s="24" t="n">
         <f aca="false">M19/$P19/10</f>
-        <v>0.473681591764751</v>
+        <v>0.512370232362714</v>
       </c>
       <c r="O19" s="23" t="n">
         <v>6300</v>
@@ -5937,38 +5932,38 @@
       </c>
       <c r="R19" s="23" t="n">
         <f aca="false">H19+F19+B19+D19+J19+M19</f>
-        <v>1574.3</v>
+        <v>1805.164</v>
       </c>
       <c r="S19" s="26" t="n">
         <f aca="false">R19/$P19/1000*100</f>
-        <v>0.870351225391279</v>
+        <v>0.997984310126547</v>
       </c>
       <c r="T19" s="26" t="n">
         <f aca="false">R19/P19</f>
-        <v>8.70351225391279</v>
-      </c>
-      <c r="U19" s="27" t="n">
+        <v>9.97984310126547</v>
+      </c>
+      <c r="U19" s="2" t="n">
         <f aca="false">3/5*H19+M19/3</f>
-        <v>356.4</v>
+        <v>379.7268</v>
       </c>
       <c r="V19" s="26" t="n">
         <f aca="false">U19/$P19/1000*100</f>
-        <v>0.197035620103825</v>
-      </c>
-      <c r="W19" s="27" t="n">
+        <v>0.209931833636479</v>
+      </c>
+      <c r="W19" s="2" t="n">
         <f aca="false">R19-U19</f>
-        <v>1217.9</v>
+        <v>1425.4372</v>
       </c>
       <c r="X19" s="26" t="n">
         <f aca="false">W19/$P19/1000*100</f>
-        <v>0.673315605287454</v>
+        <v>0.788052476490068</v>
       </c>
       <c r="Y19" s="26"/>
-      <c r="Z19" s="31" t="n">
+      <c r="Z19" s="30" t="n">
         <f aca="false">F19</f>
         <v>22.7</v>
       </c>
-      <c r="AA19" s="0" t="n">
+      <c r="AA19" s="1" t="n">
         <f aca="false">Y19+Z19</f>
         <v>22.7</v>
       </c>
@@ -5976,33 +5971,33 @@
         <f aca="false">AA19/$P19/1000*100</f>
         <v>0.0125496873635152</v>
       </c>
-      <c r="AC19" s="27" t="n">
+      <c r="AC19" s="2" t="n">
         <f aca="false">1000/100*Q19*($Q$41+$Q$47-$Q$49)-AA19</f>
-        <v>661.940010463206</v>
+        <v>724.867919593859</v>
       </c>
       <c r="AD19" s="26" t="n">
         <f aca="false">AC19/$P19/1000*100</f>
-        <v>0.365953312101993</v>
-      </c>
-      <c r="AE19" s="27" t="n">
+        <v>0.400742985495358</v>
+      </c>
+      <c r="AE19" s="2" t="n">
         <f aca="false">AC19+Q19/100*1000 *($Q$46+$Q$43)</f>
-        <v>1200.0958687653</v>
+        <v>1276.78239279659</v>
       </c>
       <c r="AF19" s="26" t="n">
         <f aca="false">AE19/$P19/1000*100</f>
-        <v>0.663472597323821</v>
+        <v>0.70586871633648</v>
       </c>
       <c r="AG19" s="26" t="n">
         <f aca="false">-Z19+($Q$45 + $Q$46)*1000*Q19/100</f>
-        <v>537.70509017628</v>
+        <v>600.632999306933</v>
       </c>
       <c r="AH19" s="26" t="n">
         <f aca="false">AG19/P19/10</f>
-        <v>0.297270078215114</v>
+        <v>0.332059751608479</v>
       </c>
       <c r="AI19" s="26" t="n">
         <f aca="false">ROUND(AG19/P19 *100/1000, 2)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="AK19" s="26" t="n">
         <f aca="false">-Q19*($Q$47)*10</f>
@@ -6032,7 +6027,7 @@
         <f aca="false">AW19*1000</f>
         <v>2540</v>
       </c>
-      <c r="BA19" s="28" t="s">
+      <c r="BA19" s="27" t="s">
         <v>111</v>
       </c>
       <c r="BB19" s="23" t="n">
@@ -6041,15 +6036,15 @@
       <c r="BC19" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="BD19" s="28" t="n">
+      <c r="BD19" s="27" t="n">
         <f aca="false">BB19+BC19/10</f>
         <v>6.3</v>
       </c>
-      <c r="BE19" s="28" t="n">
+      <c r="BE19" s="27" t="n">
         <f aca="false">1000*BD19</f>
         <v>6300</v>
       </c>
-      <c r="BG19" s="28" t="s">
+      <c r="BG19" s="27" t="s">
         <v>110</v>
       </c>
       <c r="BH19" s="23" t="n">
@@ -6067,10 +6062,10 @@
       <c r="BL19" s="23" t="n">
         <v>5.88</v>
       </c>
-      <c r="BM19" s="28" t="s">
+      <c r="BM19" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="BO19" s="28" t="n">
+      <c r="BO19" s="27" t="n">
         <f aca="false">BH19*1000</f>
         <v>2540</v>
       </c>
@@ -6098,10 +6093,10 @@
       <c r="BY19" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="XFA19" s="0"/>
-      <c r="XFB19" s="0"/>
-      <c r="XFC19" s="0"/>
-      <c r="XFD19" s="0"/>
+      <c r="XFA19" s="1"/>
+      <c r="XFB19" s="1"/>
+      <c r="XFC19" s="1"/>
+      <c r="XFD19" s="1"/>
     </row>
     <row r="20" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
@@ -6137,22 +6132,22 @@
       </c>
       <c r="J20" s="23" t="n">
         <f aca="false">L20*$J$37/100</f>
-        <v>62.9</v>
+        <v>86.3358</v>
       </c>
       <c r="K20" s="24" t="n">
         <f aca="false">J20/$P20/10</f>
-        <v>0.0422363084526336</v>
+        <v>0.0579730600843383</v>
       </c>
       <c r="L20" s="23" t="n">
         <v>370</v>
       </c>
       <c r="M20" s="23" t="n">
         <f aca="false">O20*$M$37/100</f>
-        <v>340</v>
+        <v>367.77</v>
       </c>
       <c r="N20" s="24" t="n">
         <f aca="false">M20/$P20/10</f>
-        <v>0.228304370014235</v>
+        <v>0.246951465176869</v>
       </c>
       <c r="O20" s="23" t="n">
         <v>2500</v>
@@ -6166,35 +6161,35 @@
       </c>
       <c r="R20" s="23" t="n">
         <f aca="false">H20+F20+B20+D20+J20+M20</f>
-        <v>869.8</v>
+        <v>921.0058</v>
       </c>
       <c r="S20" s="26" t="n">
         <f aca="false">R20/$P20/1000*100</f>
-        <v>0.584056297171712</v>
+        <v>0.61844014396605</v>
       </c>
       <c r="T20" s="26" t="n">
         <f aca="false">R20/P20</f>
-        <v>5.84056297171712</v>
-      </c>
-      <c r="U20" s="27" t="n">
+        <v>6.1844014396605</v>
+      </c>
+      <c r="U20" s="2" t="n">
         <f aca="false">3/5*H20+M20/3</f>
-        <v>238.133333333333</v>
+        <v>247.39</v>
       </c>
       <c r="V20" s="26" t="n">
         <f aca="false">U20/$P20/1000*100</f>
-        <v>0.159902590135461</v>
-      </c>
-      <c r="W20" s="27" t="n">
+        <v>0.166118288523005</v>
+      </c>
+      <c r="W20" s="2" t="n">
         <f aca="false">R20-U20</f>
-        <v>631.666666666667</v>
+        <v>673.6158</v>
       </c>
       <c r="X20" s="26" t="n">
         <f aca="false">W20/$P20/1000*100</f>
-        <v>0.424153707036251</v>
+        <v>0.452321855443045</v>
       </c>
       <c r="Y20" s="26"/>
       <c r="Z20" s="26"/>
-      <c r="AA20" s="0" t="n">
+      <c r="AA20" s="1" t="n">
         <f aca="false">Y20+Z20</f>
         <v>0</v>
       </c>
@@ -6202,33 +6197,33 @@
         <f aca="false">AA20/$P20/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC20" s="27" t="n">
+      <c r="AC20" s="2" t="n">
         <f aca="false">1000/100*Q20*($Q$41+$Q$47-$Q$49)-AA20</f>
-        <v>563.681806924014</v>
+        <v>615.491980128349</v>
       </c>
       <c r="AD20" s="26" t="n">
         <f aca="false">AC20/$P20/1000*100</f>
-        <v>0.378502999465508</v>
-      </c>
-      <c r="AE20" s="27" t="n">
+        <v>0.413292672858874</v>
+      </c>
+      <c r="AE20" s="2" t="n">
         <f aca="false">AC20+Q20/100*1000 *($Q$46+$Q$43)</f>
-        <v>1006.75942724777</v>
+        <v>1069.89742352618</v>
       </c>
       <c r="AF20" s="26" t="n">
         <f aca="false">AE20/$P20/1000*100</f>
-        <v>0.676022284687336</v>
+        <v>0.718418403699996</v>
       </c>
       <c r="AG20" s="26" t="n">
         <f aca="false">-AA20+($Q$45 + $Q$46)*1000*Q20/100</f>
-        <v>461.395987690318</v>
+        <v>513.206160894653</v>
       </c>
       <c r="AH20" s="26" t="n">
         <f aca="false">AG20/P20/10</f>
-        <v>0.309819765578629</v>
+        <v>0.344609438971994</v>
       </c>
       <c r="AI20" s="26" t="n">
         <f aca="false">ROUND(AG20/P20 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK20" s="26" t="n">
         <f aca="false">-Q20*($Q$47)*10</f>
@@ -6258,7 +6253,7 @@
         <f aca="false">AW20*1000</f>
         <v>370</v>
       </c>
-      <c r="BA20" s="28" t="s">
+      <c r="BA20" s="27" t="s">
         <v>115</v>
       </c>
       <c r="BB20" s="23" t="n">
@@ -6267,15 +6262,15 @@
       <c r="BC20" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="BD20" s="28" t="n">
+      <c r="BD20" s="27" t="n">
         <f aca="false">BB20+BC20/10</f>
         <v>2.5</v>
       </c>
-      <c r="BE20" s="28" t="n">
+      <c r="BE20" s="27" t="n">
         <f aca="false">1000*BD20</f>
         <v>2500</v>
       </c>
-      <c r="BG20" s="28" t="s">
+      <c r="BG20" s="27" t="s">
         <v>116</v>
       </c>
       <c r="BH20" s="23" t="n">
@@ -6293,10 +6288,10 @@
       <c r="BL20" s="23" t="n">
         <v>0.95</v>
       </c>
-      <c r="BM20" s="28" t="s">
+      <c r="BM20" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="BO20" s="28" t="n">
+      <c r="BO20" s="27" t="n">
         <f aca="false">BH20*1000</f>
         <v>370</v>
       </c>
@@ -6324,13 +6319,13 @@
       <c r="BY20" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="XFA20" s="0"/>
-      <c r="XFB20" s="0"/>
-      <c r="XFC20" s="0"/>
-      <c r="XFD20" s="0"/>
+      <c r="XFA20" s="1"/>
+      <c r="XFB20" s="1"/>
+      <c r="XFC20" s="1"/>
+      <c r="XFD20" s="1"/>
     </row>
     <row r="21" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>120</v>
       </c>
       <c r="B21" s="23" t="n">
@@ -6347,14 +6342,14 @@
         <f aca="false">D21/$P21/10</f>
         <v>0.0494619467603971</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="29" t="n">
         <v>241.4</v>
       </c>
       <c r="G21" s="24" t="n">
         <f aca="false">F21/$P21/10</f>
         <v>0.0746257121747491</v>
       </c>
-      <c r="H21" s="30" t="n">
+      <c r="H21" s="29" t="n">
         <v>331</v>
       </c>
       <c r="I21" s="24" t="n">
@@ -6363,22 +6358,22 @@
       </c>
       <c r="J21" s="23" t="n">
         <f aca="false">L21*$J$37/100</f>
-        <v>159.8</v>
+        <v>219.3396</v>
       </c>
       <c r="K21" s="24" t="n">
         <f aca="false">J21/$P21/10</f>
-        <v>0.0494001193269466</v>
+        <v>0.0678060226102924</v>
       </c>
       <c r="L21" s="23" t="n">
         <v>940</v>
       </c>
       <c r="M21" s="23" t="n">
         <f aca="false">O21*$M$37/100</f>
-        <v>516.8</v>
+        <v>559.0104</v>
       </c>
       <c r="N21" s="24" t="n">
         <f aca="false">M21/$P21/10</f>
-        <v>0.159762088036082</v>
+        <v>0.172810891520677</v>
       </c>
       <c r="O21" s="23" t="n">
         <v>3800</v>
@@ -6392,38 +6387,38 @@
       </c>
       <c r="R21" s="23" t="n">
         <f aca="false">H21+F21+B21+D21+J21+M21</f>
-        <v>1506</v>
+        <v>1607.75</v>
       </c>
       <c r="S21" s="26" t="n">
         <f aca="false">R21/$P21/1000*100</f>
-        <v>0.465560573882237</v>
+        <v>0.497015280650177</v>
       </c>
       <c r="T21" s="26" t="n">
         <f aca="false">R21/P21</f>
-        <v>4.65560573882237</v>
-      </c>
-      <c r="U21" s="27" t="n">
+        <v>4.97015280650177</v>
+      </c>
+      <c r="U21" s="2" t="n">
         <f aca="false">3/5*H21+M21/3</f>
-        <v>370.866666666667</v>
+        <v>384.9368</v>
       </c>
       <c r="V21" s="26" t="n">
         <f aca="false">U21/$P21/1000*100</f>
-        <v>0.114648670761704</v>
-      </c>
-      <c r="W21" s="27" t="n">
+        <v>0.118998271923235</v>
+      </c>
+      <c r="W21" s="2" t="n">
         <f aca="false">R21-U21</f>
-        <v>1135.13333333333</v>
+        <v>1222.8132</v>
       </c>
       <c r="X21" s="26" t="n">
         <f aca="false">W21/$P21/1000*100</f>
-        <v>0.350911903120534</v>
+        <v>0.378017008726942</v>
       </c>
       <c r="Y21" s="26"/>
-      <c r="Z21" s="31" t="n">
+      <c r="Z21" s="30" t="n">
         <f aca="false">F21</f>
         <v>241.4</v>
       </c>
-      <c r="AA21" s="0" t="n">
+      <c r="AA21" s="1" t="n">
         <f aca="false">Y21+Z21</f>
         <v>241.4</v>
       </c>
@@ -6431,33 +6426,33 @@
         <f aca="false">AA21/$P21/1000*100</f>
         <v>0.0746257121747491</v>
       </c>
-      <c r="AC21" s="27" t="n">
+      <c r="AC21" s="2" t="n">
         <f aca="false">1000/100*Q21*($Q$41+$Q$47-$Q$49)-AA21</f>
-        <v>982.985287701017</v>
+        <v>1095.52327109061</v>
       </c>
       <c r="AD21" s="26" t="n">
         <f aca="false">AC21/$P21/1000*100</f>
-        <v>0.303877287290758</v>
-      </c>
-      <c r="AE21" s="27" t="n">
+        <v>0.338666960684123</v>
+      </c>
+      <c r="AE21" s="2" t="n">
         <f aca="false">AC21+Q21/100*1000 *($Q$46+$Q$43)</f>
-        <v>1945.40364672943</v>
+        <v>2082.54703647278</v>
       </c>
       <c r="AF21" s="26" t="n">
         <f aca="false">AE21/$P21/1000*100</f>
-        <v>0.601396572512585</v>
+        <v>0.643792691525244</v>
       </c>
       <c r="AG21" s="26" t="n">
         <f aca="false">-Z21+($Q$45 + $Q$46)*1000*Q21/100</f>
-        <v>760.808075891402</v>
+        <v>873.346059280994</v>
       </c>
       <c r="AH21" s="26" t="n">
         <f aca="false">AG21/P21/10</f>
-        <v>0.235194053403879</v>
+        <v>0.269983726797244</v>
       </c>
       <c r="AI21" s="26" t="n">
         <f aca="false">ROUND(AG21/P21 *100/1000, 2)</f>
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="AK21" s="26" t="n">
         <f aca="false">-Q21*($Q$47)*10</f>
@@ -6487,7 +6482,7 @@
         <f aca="false">AW21*1000</f>
         <v>940</v>
       </c>
-      <c r="BA21" s="28" t="s">
+      <c r="BA21" s="27" t="s">
         <v>122</v>
       </c>
       <c r="BB21" s="23" t="n">
@@ -6496,18 +6491,18 @@
       <c r="BC21" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="BD21" s="28" t="n">
+      <c r="BD21" s="27" t="n">
         <f aca="false">BB21+BC21/10</f>
         <v>3.8</v>
       </c>
-      <c r="BE21" s="28" t="n">
+      <c r="BE21" s="27" t="n">
         <f aca="false">1000*BD21</f>
         <v>3800</v>
       </c>
-      <c r="BF21" s="28" t="s">
+      <c r="BF21" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="BG21" s="28" t="s">
+      <c r="BG21" s="27" t="s">
         <v>121</v>
       </c>
       <c r="BH21" s="23" t="n">
@@ -6525,10 +6520,10 @@
       <c r="BL21" s="23" t="n">
         <v>1.22</v>
       </c>
-      <c r="BM21" s="28" t="s">
+      <c r="BM21" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="BO21" s="28" t="n">
+      <c r="BO21" s="27" t="n">
         <f aca="false">BH21*1000</f>
         <v>940</v>
       </c>
@@ -6556,10 +6551,10 @@
       <c r="BY21" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="XFA21" s="0"/>
-      <c r="XFB21" s="0"/>
-      <c r="XFC21" s="0"/>
-      <c r="XFD21" s="0"/>
+      <c r="XFA21" s="1"/>
+      <c r="XFB21" s="1"/>
+      <c r="XFC21" s="1"/>
+      <c r="XFD21" s="1"/>
     </row>
     <row r="22" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
@@ -6595,22 +6590,22 @@
       </c>
       <c r="J22" s="23" t="n">
         <f aca="false">L22*$J$37/100</f>
-        <v>1208.7</v>
+        <v>1659.0474</v>
       </c>
       <c r="K22" s="24" t="n">
         <f aca="false">J22/$P22/10</f>
-        <v>0.0666324876790262</v>
+        <v>0.0914589686766116</v>
       </c>
       <c r="L22" s="23" t="n">
         <v>7110</v>
       </c>
       <c r="M22" s="23" t="n">
         <f aca="false">O22*$M$37/100</f>
-        <v>7684</v>
+        <v>8311.602</v>
       </c>
       <c r="N22" s="24" t="n">
         <f aca="false">M22/$P22/10</f>
-        <v>0.423598937143739</v>
+        <v>0.458197003274568</v>
       </c>
       <c r="O22" s="23" t="n">
         <v>56500</v>
@@ -6624,31 +6619,31 @@
       </c>
       <c r="R22" s="23" t="n">
         <f aca="false">H22+F22+B22+D22+J22+M22</f>
-        <v>13413.2</v>
+        <v>14491.1494</v>
       </c>
       <c r="S22" s="26" t="n">
         <f aca="false">R22/$P22/1000*100</f>
-        <v>0.739434833901146</v>
+        <v>0.798859381029559</v>
       </c>
       <c r="T22" s="26" t="n">
         <f aca="false">R22/P22</f>
-        <v>7.39434833901146</v>
-      </c>
-      <c r="U22" s="27" t="n">
+        <v>7.98859381029559</v>
+      </c>
+      <c r="U22" s="2" t="n">
         <f aca="false">3/5*H22+M22/3</f>
-        <v>4132.13333333333</v>
+        <v>4341.334</v>
       </c>
       <c r="V22" s="26" t="n">
         <f aca="false">U22/$P22/1000*100</f>
-        <v>0.22779376472361</v>
-      </c>
-      <c r="W22" s="27" t="n">
+        <v>0.239326453433886</v>
+      </c>
+      <c r="W22" s="2" t="n">
         <f aca="false">R22-U22</f>
-        <v>9281.06666666667</v>
+        <v>10149.8154</v>
       </c>
       <c r="X22" s="26" t="n">
         <f aca="false">W22/$P22/1000*100</f>
-        <v>0.511641069177536</v>
+        <v>0.559532927595674</v>
       </c>
       <c r="Y22" s="26" t="n">
         <f aca="false">B22</f>
@@ -6658,7 +6653,7 @@
         <f aca="false">F22</f>
         <v>544.5</v>
       </c>
-      <c r="AA22" s="0" t="n">
+      <c r="AA22" s="1" t="n">
         <f aca="false">Y22+Z22</f>
         <v>1011.5</v>
       </c>
@@ -6666,33 +6661,33 @@
         <f aca="false">AA22/$P22/1000*100</f>
         <v>0.0557613645133904</v>
       </c>
-      <c r="AC22" s="27" t="n">
+      <c r="AC22" s="2" t="n">
         <f aca="false">1000/100*Q22*($Q$41+$Q$47-$Q$49)-AA22</f>
-        <v>5854.46870970442</v>
+        <v>6485.54642712539</v>
       </c>
       <c r="AD22" s="26" t="n">
         <f aca="false">AC22/$P22/1000*100</f>
-        <v>0.322741634952117</v>
-      </c>
-      <c r="AE22" s="27" t="n">
+        <v>0.357531308345483</v>
+      </c>
+      <c r="AE22" s="2" t="n">
         <f aca="false">AC22+Q22/100*1000 *($Q$46+$Q$43)</f>
-        <v>11251.4090397713</v>
+        <v>12020.4661594372</v>
       </c>
       <c r="AF22" s="26" t="n">
         <f aca="false">AE22/$P22/1000*100</f>
-        <v>0.620260920173945</v>
+        <v>0.662657039186604</v>
       </c>
       <c r="AG22" s="26" t="n">
         <f aca="false">-AA22+($Q$45 + $Q$46)*1000*Q22/100</f>
-        <v>4608.56858364321</v>
+        <v>5239.64630106418</v>
       </c>
       <c r="AH22" s="26" t="n">
         <f aca="false">AG22/P22/10</f>
-        <v>0.254058401065238</v>
+        <v>0.288848074458604</v>
       </c>
       <c r="AI22" s="26" t="n">
         <f aca="false">ROUND(AG22/P22 *100/1000, 2)</f>
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AK22" s="26" t="n">
         <f aca="false">-Q22*($Q$47)*10</f>
@@ -6722,7 +6717,7 @@
         <f aca="false">AW22*1000</f>
         <v>7110</v>
       </c>
-      <c r="BA22" s="28" t="s">
+      <c r="BA22" s="27" t="s">
         <v>129</v>
       </c>
       <c r="BB22" s="23" t="n">
@@ -6731,15 +6726,15 @@
       <c r="BC22" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="BD22" s="28" t="n">
+      <c r="BD22" s="27" t="n">
         <f aca="false">BB22+BC22/10</f>
         <v>56.5</v>
       </c>
-      <c r="BE22" s="28" t="n">
+      <c r="BE22" s="27" t="n">
         <f aca="false">1000*BD22</f>
         <v>56500</v>
       </c>
-      <c r="BG22" s="28" t="s">
+      <c r="BG22" s="27" t="s">
         <v>128</v>
       </c>
       <c r="BH22" s="23" t="n">
@@ -6757,10 +6752,10 @@
       <c r="BL22" s="23" t="n">
         <v>1.78</v>
       </c>
-      <c r="BM22" s="28" t="s">
+      <c r="BM22" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="BO22" s="28" t="n">
+      <c r="BO22" s="27" t="n">
         <f aca="false">BH22*1000</f>
         <v>7110</v>
       </c>
@@ -6788,13 +6783,13 @@
       <c r="BY22" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="XFA22" s="0"/>
-      <c r="XFB22" s="0"/>
-      <c r="XFC22" s="0"/>
-      <c r="XFD22" s="0"/>
+      <c r="XFA22" s="1"/>
+      <c r="XFB22" s="1"/>
+      <c r="XFC22" s="1"/>
+      <c r="XFD22" s="1"/>
     </row>
     <row r="23" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="28" t="s">
         <v>134</v>
       </c>
       <c r="B23" s="23" t="n">
@@ -6811,14 +6806,14 @@
         <f aca="false">D23/$P23/10</f>
         <v>0.0604686318972033</v>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="24" t="n">
         <f aca="false">F23/$P23/10</f>
         <v>0</v>
       </c>
-      <c r="H23" s="30" t="n">
+      <c r="H23" s="29" t="n">
         <v>20</v>
       </c>
       <c r="I23" s="24" t="n">
@@ -6827,22 +6822,22 @@
       </c>
       <c r="J23" s="23" t="n">
         <f aca="false">L23*$J$37/100</f>
-        <v>30.6</v>
+        <v>42.0012</v>
       </c>
       <c r="K23" s="24" t="n">
         <f aca="false">J23/$P23/10</f>
-        <v>0.0925170068027211</v>
+        <v>0.126987755102041</v>
       </c>
       <c r="L23" s="23" t="n">
         <v>180</v>
       </c>
       <c r="M23" s="23" t="n">
         <f aca="false">O23*$M$37/100</f>
-        <v>68</v>
+        <v>73.554</v>
       </c>
       <c r="N23" s="24" t="n">
         <f aca="false">M23/$P23/10</f>
-        <v>0.205593348450491</v>
+        <v>0.222385487528345</v>
       </c>
       <c r="O23" s="23" t="n">
         <v>500</v>
@@ -6856,35 +6851,35 @@
       </c>
       <c r="R23" s="23" t="n">
         <f aca="false">H23+F23+B23+D23+J23+M23</f>
-        <v>165.6</v>
+        <v>182.5552</v>
       </c>
       <c r="S23" s="26" t="n">
         <f aca="false">R23/$P23/1000*100</f>
-        <v>0.500680272108844</v>
+        <v>0.551943159486017</v>
       </c>
       <c r="T23" s="26" t="n">
         <f aca="false">R23/P23</f>
-        <v>5.00680272108844</v>
-      </c>
-      <c r="U23" s="27" t="n">
+        <v>5.51943159486017</v>
+      </c>
+      <c r="U23" s="2" t="n">
         <f aca="false">3/5*H23+M23/3</f>
-        <v>34.6666666666667</v>
+        <v>36.518</v>
       </c>
       <c r="V23" s="26" t="n">
         <f aca="false">U23/$P23/1000*100</f>
-        <v>0.104812295288486</v>
-      </c>
-      <c r="W23" s="27" t="n">
+        <v>0.110409674981104</v>
+      </c>
+      <c r="W23" s="2" t="n">
         <f aca="false">R23-U23</f>
-        <v>130.933333333333</v>
+        <v>146.0372</v>
       </c>
       <c r="X23" s="26" t="n">
         <f aca="false">W23/$P23/1000*100</f>
-        <v>0.395867976820358</v>
+        <v>0.441533484504913</v>
       </c>
       <c r="Y23" s="26"/>
       <c r="Z23" s="26"/>
-      <c r="AA23" s="0" t="n">
+      <c r="AA23" s="1" t="n">
         <f aca="false">Y23+Z23</f>
         <v>0</v>
       </c>
@@ -6892,33 +6887,33 @@
         <f aca="false">AA23/$P23/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC23" s="27" t="n">
+      <c r="AC23" s="2" t="n">
         <f aca="false">1000/100*Q23*($Q$41+$Q$47-$Q$49)-AA23</f>
-        <v>125.189867073216</v>
+        <v>136.696551548072</v>
       </c>
       <c r="AD23" s="26" t="n">
         <f aca="false">AC23/$P23/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE23" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE23" s="2" t="n">
         <f aca="false">AC23+Q23/100*1000 *($Q$46+$Q$43)</f>
-        <v>223.594370660335</v>
+        <v>237.616887023773</v>
       </c>
       <c r="AF23" s="26" t="n">
         <f aca="false">AE23/$P23/1000*100</f>
-        <v>0.676022284687333</v>
+        <v>0.718418403699992</v>
       </c>
       <c r="AG23" s="26" t="n">
         <f aca="false">-AA23+($Q$45 + $Q$46)*1000*Q23/100</f>
-        <v>102.472887465131</v>
+        <v>113.979571939987</v>
       </c>
       <c r="AH23" s="26" t="n">
         <f aca="false">AG23/P23/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI23" s="26" t="n">
         <f aca="false">ROUND(AG23/P23 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK23" s="26" t="n">
         <f aca="false">-Q23*($Q$47)*10</f>
@@ -6948,7 +6943,7 @@
         <f aca="false">AW23*1000</f>
         <v>180</v>
       </c>
-      <c r="BA23" s="28" t="s">
+      <c r="BA23" s="27" t="s">
         <v>134</v>
       </c>
       <c r="BB23" s="23" t="n">
@@ -6957,15 +6952,15 @@
       <c r="BC23" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="BD23" s="28" t="n">
+      <c r="BD23" s="27" t="n">
         <f aca="false">BB23+BC23/10</f>
         <v>0.5</v>
       </c>
-      <c r="BE23" s="28" t="n">
+      <c r="BE23" s="27" t="n">
         <f aca="false">1000*BD23</f>
         <v>500</v>
       </c>
-      <c r="BG23" s="28" t="s">
+      <c r="BG23" s="27" t="s">
         <v>135</v>
       </c>
       <c r="BH23" s="23" t="n">
@@ -6983,10 +6978,10 @@
       <c r="BL23" s="23" t="n">
         <v>2.26</v>
       </c>
-      <c r="BM23" s="28" t="s">
+      <c r="BM23" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="BO23" s="28" t="n">
+      <c r="BO23" s="27" t="n">
         <f aca="false">BH23*1000</f>
         <v>180</v>
       </c>
@@ -7014,10 +7009,10 @@
       <c r="BY23" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="XFA23" s="0"/>
-      <c r="XFB23" s="0"/>
-      <c r="XFC23" s="0"/>
-      <c r="XFD23" s="0"/>
+      <c r="XFA23" s="1"/>
+      <c r="XFB23" s="1"/>
+      <c r="XFC23" s="1"/>
+      <c r="XFD23" s="1"/>
     </row>
     <row r="24" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
@@ -7053,22 +7048,22 @@
       </c>
       <c r="J24" s="23" t="n">
         <f aca="false">L24*$J$37/100</f>
-        <v>23.8</v>
+        <v>32.6676</v>
       </c>
       <c r="K24" s="24" t="n">
         <f aca="false">J24/$P24/10</f>
-        <v>0.044061018957346</v>
+        <v>0.0604776362559242</v>
       </c>
       <c r="L24" s="23" t="n">
         <v>140</v>
       </c>
       <c r="M24" s="23" t="n">
         <f aca="false">O24*$M$37/100</f>
-        <v>108.8</v>
+        <v>117.6864</v>
       </c>
       <c r="N24" s="24" t="n">
         <f aca="false">M24/$P24/10</f>
-        <v>0.201421800947867</v>
+        <v>0.217873222748815</v>
       </c>
       <c r="O24" s="23" t="n">
         <v>800</v>
@@ -7082,35 +7077,35 @@
       </c>
       <c r="R24" s="23" t="n">
         <f aca="false">H24+F24+B24+D24+J24+M24</f>
-        <v>228.7</v>
+        <v>246.454</v>
       </c>
       <c r="S24" s="26" t="n">
         <f aca="false">R24/$P24/1000*100</f>
-        <v>0.423393068720379</v>
+        <v>0.456261107819905</v>
       </c>
       <c r="T24" s="26" t="n">
         <f aca="false">R24/P24</f>
-        <v>4.23393068720379</v>
-      </c>
-      <c r="U24" s="27" t="n">
+        <v>4.56261107819905</v>
+      </c>
+      <c r="U24" s="2" t="n">
         <f aca="false">3/5*H24+M24/3</f>
-        <v>54.8666666666667</v>
+        <v>57.8288</v>
       </c>
       <c r="V24" s="26" t="n">
         <f aca="false">U24/$P24/1000*100</f>
-        <v>0.101574842022117</v>
-      </c>
-      <c r="W24" s="27" t="n">
+        <v>0.1070586492891</v>
+      </c>
+      <c r="W24" s="2" t="n">
         <f aca="false">R24-U24</f>
-        <v>173.833333333333</v>
+        <v>188.6252</v>
       </c>
       <c r="X24" s="26" t="n">
         <f aca="false">W24/$P24/1000*100</f>
-        <v>0.321818226698262</v>
+        <v>0.349202458530806</v>
       </c>
       <c r="Y24" s="26"/>
       <c r="Z24" s="26"/>
-      <c r="AA24" s="0" t="n">
+      <c r="AA24" s="1" t="n">
         <f aca="false">Y24+Z24</f>
         <v>0</v>
       </c>
@@ -7118,33 +7113,33 @@
         <f aca="false">AA24/$P24/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="27" t="n">
+      <c r="AC24" s="2" t="n">
         <f aca="false">1000/100*Q24*($Q$41+$Q$47-$Q$49)-AA24</f>
-        <v>204.452180191289</v>
+        <v>223.244170171449</v>
       </c>
       <c r="AD24" s="26" t="n">
         <f aca="false">AC24/$P24/1000*100</f>
-        <v>0.378502999465508</v>
-      </c>
-      <c r="AE24" s="27" t="n">
+        <v>0.413292672858873</v>
+      </c>
+      <c r="AE24" s="2" t="n">
         <f aca="false">AC24+Q24/100*1000 *($Q$46+$Q$43)</f>
-        <v>365.160197296711</v>
+        <v>388.060884942589</v>
       </c>
       <c r="AF24" s="26" t="n">
         <f aca="false">AE24/$P24/1000*100</f>
-        <v>0.676022284687335</v>
+        <v>0.718418403699994</v>
       </c>
       <c r="AG24" s="26" t="n">
         <f aca="false">-AA24+($Q$45 + $Q$46)*1000*Q24/100</f>
-        <v>167.352244574952</v>
+        <v>186.144234555112</v>
       </c>
       <c r="AH24" s="26" t="n">
         <f aca="false">AG24/P24/10</f>
-        <v>0.309819765578629</v>
+        <v>0.344609438971994</v>
       </c>
       <c r="AI24" s="26" t="n">
         <f aca="false">ROUND(AG24/P24 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK24" s="26" t="n">
         <f aca="false">-Q24*($Q$47)*10</f>
@@ -7174,7 +7169,7 @@
         <f aca="false">AW24*1000</f>
         <v>140</v>
       </c>
-      <c r="BA24" s="28" t="s">
+      <c r="BA24" s="27" t="s">
         <v>138</v>
       </c>
       <c r="BB24" s="23" t="n">
@@ -7183,15 +7178,15 @@
       <c r="BC24" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="BD24" s="28" t="n">
+      <c r="BD24" s="27" t="n">
         <f aca="false">BB24+BC24/10</f>
         <v>0.8</v>
       </c>
-      <c r="BE24" s="28" t="n">
+      <c r="BE24" s="27" t="n">
         <f aca="false">1000*BD24</f>
         <v>800</v>
       </c>
-      <c r="BG24" s="28" t="s">
+      <c r="BG24" s="27" t="s">
         <v>139</v>
       </c>
       <c r="BH24" s="23" t="n">
@@ -7209,10 +7204,10 @@
       <c r="BL24" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="BM24" s="28" t="s">
+      <c r="BM24" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="BO24" s="28" t="n">
+      <c r="BO24" s="27" t="n">
         <f aca="false">BH24*1000</f>
         <v>140</v>
       </c>
@@ -7240,13 +7235,13 @@
       <c r="BY24" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="XFA24" s="0"/>
-      <c r="XFB24" s="0"/>
-      <c r="XFC24" s="0"/>
-      <c r="XFD24" s="0"/>
+      <c r="XFA24" s="1"/>
+      <c r="XFB24" s="1"/>
+      <c r="XFC24" s="1"/>
+      <c r="XFD24" s="1"/>
     </row>
     <row r="25" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="28" t="s">
         <v>143</v>
       </c>
       <c r="B25" s="23" t="n">
@@ -7263,14 +7258,14 @@
         <f aca="false">D25/$P25/10</f>
         <v>0.0634040023776501</v>
       </c>
-      <c r="F25" s="30" t="n">
+      <c r="F25" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="24" t="n">
         <f aca="false">F25/$P25/10</f>
         <v>0</v>
       </c>
-      <c r="H25" s="30" t="n">
+      <c r="H25" s="29" t="n">
         <v>208</v>
       </c>
       <c r="I25" s="24" t="n">
@@ -7279,22 +7274,22 @@
       </c>
       <c r="J25" s="23" t="n">
         <f aca="false">L25*$J$37/100</f>
-        <v>35.7</v>
+        <v>49.0014</v>
       </c>
       <c r="K25" s="24" t="n">
         <f aca="false">J25/$P25/10</f>
-        <v>0.0707350901525659</v>
+        <v>0.0970901525658807</v>
       </c>
       <c r="L25" s="23" t="n">
         <v>210</v>
       </c>
       <c r="M25" s="23" t="n">
         <f aca="false">O25*$M$37/100</f>
-        <v>244.8</v>
+        <v>264.7944</v>
       </c>
       <c r="N25" s="24" t="n">
         <f aca="false">M25/$P25/10</f>
-        <v>0.485040618189023</v>
+        <v>0.524657023974638</v>
       </c>
       <c r="O25" s="23" t="n">
         <v>1800</v>
@@ -7308,35 +7303,35 @@
       </c>
       <c r="R25" s="23" t="n">
         <f aca="false">H25+F25+B25+D25+J25+M25</f>
-        <v>530.5</v>
+        <v>563.7958</v>
       </c>
       <c r="S25" s="26" t="n">
         <f aca="false">R25/$P25/1000*100</f>
-        <v>1.05111947691698</v>
+        <v>1.11709094511591</v>
       </c>
       <c r="T25" s="26" t="n">
         <f aca="false">R25/P25</f>
-        <v>10.5111947691698</v>
-      </c>
-      <c r="U25" s="27" t="n">
+        <v>11.1709094511591</v>
+      </c>
+      <c r="U25" s="2" t="n">
         <f aca="false">3/5*H25+M25/3</f>
-        <v>206.4</v>
+        <v>213.0648</v>
       </c>
       <c r="V25" s="26" t="n">
         <f aca="false">U25/$P25/1000*100</f>
-        <v>0.408955815335843</v>
-      </c>
-      <c r="W25" s="27" t="n">
+        <v>0.422161283931048</v>
+      </c>
+      <c r="W25" s="2" t="n">
         <f aca="false">R25-U25</f>
-        <v>324.1</v>
+        <v>350.731</v>
       </c>
       <c r="X25" s="26" t="n">
         <f aca="false">W25/$P25/1000*100</f>
-        <v>0.642163661581137</v>
+        <v>0.694929661184862</v>
       </c>
       <c r="Y25" s="26"/>
       <c r="Z25" s="26"/>
-      <c r="AA25" s="0" t="n">
+      <c r="AA25" s="1" t="n">
         <f aca="false">Y25+Z25</f>
         <v>0</v>
       </c>
@@ -7344,33 +7339,33 @@
         <f aca="false">AA25/$P25/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC25" s="27" t="n">
+      <c r="AC25" s="2" t="n">
         <f aca="false">1000/100*Q25*($Q$41+$Q$47-$Q$49)-AA25</f>
-        <v>191.030463830241</v>
+        <v>208.588811991873</v>
       </c>
       <c r="AD25" s="26" t="n">
         <f aca="false">AC25/$P25/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE25" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE25" s="2" t="n">
         <f aca="false">AC25+Q25/100*1000 *($Q$46+$Q$43)</f>
-        <v>341.188447081697</v>
+        <v>362.585768347386</v>
       </c>
       <c r="AF25" s="26" t="n">
         <f aca="false">AE25/$P25/1000*100</f>
-        <v>0.676022284687334</v>
+        <v>0.718418403699993</v>
       </c>
       <c r="AG25" s="26" t="n">
         <f aca="false">-AA25+($Q$45 + $Q$46)*1000*Q25/100</f>
-        <v>156.366035687534</v>
+        <v>173.924383849165</v>
       </c>
       <c r="AH25" s="26" t="n">
         <f aca="false">AG25/P25/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI25" s="26" t="n">
         <f aca="false">ROUND(AG25/P25 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK25" s="26" t="n">
         <f aca="false">-Q25*($Q$47)*10</f>
@@ -7400,7 +7395,7 @@
         <f aca="false">AW25*1000</f>
         <v>210</v>
       </c>
-      <c r="BA25" s="28" t="s">
+      <c r="BA25" s="27" t="s">
         <v>143</v>
       </c>
       <c r="BB25" s="23" t="n">
@@ -7409,15 +7404,15 @@
       <c r="BC25" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="BD25" s="28" t="n">
+      <c r="BD25" s="27" t="n">
         <f aca="false">BB25+BC25/10</f>
         <v>1.8</v>
       </c>
-      <c r="BE25" s="28" t="n">
+      <c r="BE25" s="27" t="n">
         <f aca="false">1000*BD25</f>
         <v>1800</v>
       </c>
-      <c r="BG25" s="28" t="s">
+      <c r="BG25" s="27" t="s">
         <v>144</v>
       </c>
       <c r="BH25" s="23" t="n">
@@ -7435,10 +7430,10 @@
       <c r="BL25" s="23" t="n">
         <v>2.01</v>
       </c>
-      <c r="BM25" s="28" t="s">
+      <c r="BM25" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="BO25" s="28" t="n">
+      <c r="BO25" s="27" t="n">
         <f aca="false">BH25*1000</f>
         <v>210</v>
       </c>
@@ -7466,10 +7461,10 @@
       <c r="BY25" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="XFA25" s="0"/>
-      <c r="XFB25" s="0"/>
-      <c r="XFC25" s="0"/>
-      <c r="XFD25" s="0"/>
+      <c r="XFA25" s="1"/>
+      <c r="XFB25" s="1"/>
+      <c r="XFC25" s="1"/>
+      <c r="XFD25" s="1"/>
     </row>
     <row r="26" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
@@ -7505,22 +7500,22 @@
       </c>
       <c r="J26" s="23" t="n">
         <f aca="false">L26*$J$37/100</f>
-        <v>45.9</v>
+        <v>63.0018</v>
       </c>
       <c r="K26" s="24" t="n">
         <f aca="false">J26/$P26/10</f>
-        <v>0.334767704762599</v>
+        <v>0.459498213113559</v>
       </c>
       <c r="L26" s="23" t="n">
         <v>270</v>
       </c>
       <c r="M26" s="23" t="n">
         <f aca="false">O26*$M$37/100</f>
-        <v>122.4</v>
+        <v>132.3972</v>
       </c>
       <c r="N26" s="24" t="n">
         <f aca="false">M26/$P26/10</f>
-        <v>0.892713879366932</v>
+        <v>0.965627598278754</v>
       </c>
       <c r="O26" s="23" t="n">
         <v>900</v>
@@ -7534,35 +7529,35 @@
       </c>
       <c r="R26" s="23" t="n">
         <f aca="false">H26+F26+B26+D26+J26+M26</f>
-        <v>194.3</v>
+        <v>221.399</v>
       </c>
       <c r="S26" s="26" t="n">
         <f aca="false">R26/$P26/1000*100</f>
-        <v>1.41711034935453</v>
+        <v>1.61475457661731</v>
       </c>
       <c r="T26" s="26" t="n">
         <f aca="false">R26/P26</f>
-        <v>14.1711034935453</v>
-      </c>
-      <c r="U26" s="27" t="n">
+        <v>16.1475457661731</v>
+      </c>
+      <c r="U26" s="2" t="n">
         <f aca="false">3/5*H26+M26/3</f>
-        <v>46.2</v>
+        <v>49.5324</v>
       </c>
       <c r="V26" s="26" t="n">
         <f aca="false">U26/$P26/1000*100</f>
-        <v>0.336955728976734</v>
-      </c>
-      <c r="W26" s="27" t="n">
+        <v>0.361260301947342</v>
+      </c>
+      <c r="W26" s="2" t="n">
         <f aca="false">R26-U26</f>
-        <v>148.1</v>
+        <v>171.8666</v>
       </c>
       <c r="X26" s="26" t="n">
         <f aca="false">W26/$P26/1000*100</f>
-        <v>1.0801546203778</v>
+        <v>1.25349427466997</v>
       </c>
       <c r="Y26" s="26"/>
       <c r="Z26" s="26"/>
-      <c r="AA26" s="0" t="n">
+      <c r="AA26" s="1" t="n">
         <f aca="false">Y26+Z26</f>
         <v>0</v>
       </c>
@@ -7570,33 +7565,33 @@
         <f aca="false">AA26/$P26/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC26" s="27" t="n">
+      <c r="AC26" s="2" t="n">
         <f aca="false">1000/100*Q26*($Q$41+$Q$47-$Q$49)-AA26</f>
-        <v>51.8965462567157</v>
+        <v>56.66655837568</v>
       </c>
       <c r="AD26" s="26" t="n">
         <f aca="false">AC26/$P26/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE26" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE26" s="2" t="n">
         <f aca="false">AC26+Q26/100*1000 *($Q$46+$Q$43)</f>
-        <v>92.6894154534804</v>
+        <v>98.5023473313061</v>
       </c>
       <c r="AF26" s="26" t="n">
         <f aca="false">AE26/$P26/1000*100</f>
-        <v>0.676022284687334</v>
+        <v>0.718418403699994</v>
       </c>
       <c r="AG26" s="26" t="n">
         <f aca="false">-AA26+($Q$45 + $Q$46)*1000*Q26/100</f>
-        <v>42.4793880584857</v>
+        <v>47.24940017745</v>
       </c>
       <c r="AH26" s="26" t="n">
         <f aca="false">AG26/P26/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI26" s="26" t="n">
         <f aca="false">ROUND(AG26/P26 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK26" s="26" t="n">
         <f aca="false">-Q26*($Q$47)*10</f>
@@ -7626,7 +7621,7 @@
         <f aca="false">AW26*1000</f>
         <v>270</v>
       </c>
-      <c r="BA26" s="28" t="s">
+      <c r="BA26" s="27" t="s">
         <v>149</v>
       </c>
       <c r="BB26" s="23" t="n">
@@ -7635,15 +7630,15 @@
       <c r="BC26" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="BD26" s="28" t="n">
+      <c r="BD26" s="27" t="n">
         <f aca="false">BB26+BC26/10</f>
         <v>0.9</v>
       </c>
-      <c r="BE26" s="28" t="n">
+      <c r="BE26" s="27" t="n">
         <f aca="false">1000*BD26</f>
         <v>900</v>
       </c>
-      <c r="BG26" s="28" t="s">
+      <c r="BG26" s="27" t="s">
         <v>150</v>
       </c>
       <c r="BH26" s="23" t="n">
@@ -7661,10 +7656,10 @@
       <c r="BL26" s="23" t="n">
         <v>7.59</v>
       </c>
-      <c r="BM26" s="28" t="s">
+      <c r="BM26" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="BO26" s="28" t="n">
+      <c r="BO26" s="27" t="n">
         <f aca="false">BH26*1000</f>
         <v>270</v>
       </c>
@@ -7692,13 +7687,13 @@
       <c r="BY26" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="XFA26" s="0"/>
-      <c r="XFB26" s="0"/>
-      <c r="XFC26" s="0"/>
-      <c r="XFD26" s="0"/>
+      <c r="XFA26" s="1"/>
+      <c r="XFB26" s="1"/>
+      <c r="XFC26" s="1"/>
+      <c r="XFD26" s="1"/>
     </row>
     <row r="27" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="28" t="s">
         <v>155</v>
       </c>
       <c r="B27" s="23" t="n">
@@ -7715,14 +7710,14 @@
         <f aca="false">D27/$P27/10</f>
         <v>0.0778827363119896</v>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="29" t="n">
         <v>1961</v>
       </c>
       <c r="G27" s="24" t="n">
         <f aca="false">F27/$P27/10</f>
         <v>0.23424546918376</v>
       </c>
-      <c r="H27" s="30" t="n">
+      <c r="H27" s="29" t="n">
         <v>913</v>
       </c>
       <c r="I27" s="24" t="n">
@@ -7731,22 +7726,22 @@
       </c>
       <c r="J27" s="23" t="n">
         <f aca="false">L27*$J$37/100</f>
-        <v>336.6</v>
+        <v>462.0132</v>
       </c>
       <c r="K27" s="24" t="n">
         <f aca="false">J27/$P27/10</f>
-        <v>0.0402075598813125</v>
+        <v>0.0551884236629732</v>
       </c>
       <c r="L27" s="23" t="n">
         <v>1980</v>
       </c>
       <c r="M27" s="23" t="n">
         <f aca="false">O27*$M$37/100</f>
-        <v>1496</v>
+        <v>1618.188</v>
       </c>
       <c r="N27" s="24" t="n">
         <f aca="false">M27/$P27/10</f>
-        <v>0.178700266139166</v>
+        <v>0.193295873170592</v>
       </c>
       <c r="O27" s="23" t="n">
         <v>11000</v>
@@ -7760,35 +7755,35 @@
       </c>
       <c r="R27" s="23" t="n">
         <f aca="false">H27+F27+B27+D27+J27+M27</f>
-        <v>5691.6</v>
+        <v>5939.2012</v>
       </c>
       <c r="S27" s="26" t="n">
         <f aca="false">R27/$P27/1000*100</f>
-        <v>0.679873285265829</v>
+        <v>0.709449756078915</v>
       </c>
       <c r="T27" s="26" t="n">
         <f aca="false">R27/P27</f>
-        <v>6.79873285265829</v>
-      </c>
-      <c r="U27" s="27" t="n">
+        <v>7.09449756078915</v>
+      </c>
+      <c r="U27" s="2" t="n">
         <f aca="false">3/5*H27+M27/3</f>
-        <v>1046.46666666667</v>
+        <v>1087.196</v>
       </c>
       <c r="V27" s="26" t="n">
         <f aca="false">U27/$P27/1000*100</f>
-        <v>0.12500258812774</v>
-      </c>
-      <c r="W27" s="27" t="n">
+        <v>0.129867790471549</v>
+      </c>
+      <c r="W27" s="2" t="n">
         <f aca="false">R27-U27</f>
-        <v>4645.13333333333</v>
+        <v>4852.0052</v>
       </c>
       <c r="X27" s="26" t="n">
         <f aca="false">W27/$P27/1000*100</f>
-        <v>0.554870697138088</v>
+        <v>0.579581965607366</v>
       </c>
       <c r="Y27" s="26"/>
       <c r="Z27" s="26"/>
-      <c r="AA27" s="0" t="n">
+      <c r="AA27" s="1" t="n">
         <f aca="false">Y27+Z27</f>
         <v>0</v>
       </c>
@@ -7796,33 +7791,33 @@
         <f aca="false">AA27/$P27/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="27" t="n">
+      <c r="AC27" s="2" t="n">
         <f aca="false">1000/100*Q27*($Q$41+$Q$47-$Q$49)-AA27</f>
-        <v>3168.66057020546</v>
+        <v>3459.90440839842</v>
       </c>
       <c r="AD27" s="26" t="n">
         <f aca="false">AC27/$P27/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE27" s="27" t="n">
+        <v>0.413292672858873</v>
+      </c>
+      <c r="AE27" s="2" t="n">
         <f aca="false">AC27+Q27/100*1000 *($Q$46+$Q$43)</f>
-        <v>5659.3611175971</v>
+        <v>6014.28277167872</v>
       </c>
       <c r="AF27" s="26" t="n">
         <f aca="false">AE27/$P27/1000*100</f>
-        <v>0.676022284687335</v>
+        <v>0.718418403699994</v>
       </c>
       <c r="AG27" s="26" t="n">
         <f aca="false">-AA27+($Q$45 + $Q$46)*1000*Q27/100</f>
-        <v>2593.67475672742</v>
+        <v>2884.91859492038</v>
       </c>
       <c r="AH27" s="26" t="n">
         <f aca="false">AG27/P27/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971994</v>
       </c>
       <c r="AI27" s="26" t="n">
         <f aca="false">ROUND(AG27/P27 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK27" s="26" t="n">
         <f aca="false">-Q27*($Q$47)*10</f>
@@ -7852,7 +7847,7 @@
         <f aca="false">AW27*1000</f>
         <v>1980</v>
       </c>
-      <c r="BA27" s="28" t="s">
+      <c r="BA27" s="27" t="s">
         <v>157</v>
       </c>
       <c r="BB27" s="23" t="n">
@@ -7861,15 +7856,15 @@
       <c r="BC27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="BD27" s="28" t="n">
+      <c r="BD27" s="27" t="n">
         <f aca="false">BB27+BC27/10</f>
         <v>11</v>
       </c>
-      <c r="BE27" s="28" t="n">
+      <c r="BE27" s="27" t="n">
         <f aca="false">1000*BD27</f>
         <v>11000</v>
       </c>
-      <c r="BG27" s="28" t="s">
+      <c r="BG27" s="27" t="s">
         <v>156</v>
       </c>
       <c r="BH27" s="23" t="n">
@@ -7887,10 +7882,10 @@
       <c r="BL27" s="23" t="n">
         <v>0.99</v>
       </c>
-      <c r="BM27" s="28" t="s">
+      <c r="BM27" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="BO27" s="28" t="n">
+      <c r="BO27" s="27" t="n">
         <f aca="false">BH27*1000</f>
         <v>1980</v>
       </c>
@@ -7918,10 +7913,10 @@
       <c r="BY27" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="XFA27" s="0"/>
-      <c r="XFB27" s="0"/>
-      <c r="XFC27" s="0"/>
-      <c r="XFD27" s="0"/>
+      <c r="XFA27" s="1"/>
+      <c r="XFB27" s="1"/>
+      <c r="XFC27" s="1"/>
+      <c r="XFD27" s="1"/>
     </row>
     <row r="28" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
@@ -7957,22 +7952,22 @@
       </c>
       <c r="J28" s="23" t="n">
         <f aca="false">L28*$J$37/100</f>
-        <v>202.3</v>
+        <v>277.6746</v>
       </c>
       <c r="K28" s="24" t="n">
         <f aca="false">J28/$P28/10</f>
-        <v>0.0369220548592746</v>
+        <v>0.0506787781227243</v>
       </c>
       <c r="L28" s="23" t="n">
         <v>1190</v>
       </c>
       <c r="M28" s="23" t="n">
         <f aca="false">O28*$M$37/100</f>
-        <v>1088</v>
+        <v>1176.864</v>
       </c>
       <c r="N28" s="24" t="n">
         <f aca="false">M28/$P28/10</f>
-        <v>0.198572395881813</v>
+        <v>0.214791088333689</v>
       </c>
       <c r="O28" s="23" t="n">
         <v>8000</v>
@@ -7986,35 +7981,35 @@
       </c>
       <c r="R28" s="23" t="n">
         <f aca="false">H28+F28+B28+D28+J28+M28</f>
-        <v>2837.3</v>
+        <v>3001.5386</v>
       </c>
       <c r="S28" s="26" t="n">
         <f aca="false">R28/$P28/1000*100</f>
-        <v>0.51783957613554</v>
+        <v>0.547814991850866</v>
       </c>
       <c r="T28" s="26" t="n">
         <f aca="false">R28/P28</f>
-        <v>5.1783957613554</v>
-      </c>
-      <c r="U28" s="27" t="n">
+        <v>5.47814991850866</v>
+      </c>
+      <c r="U28" s="2" t="n">
         <f aca="false">3/5*H28+M28/3</f>
-        <v>698.666666666667</v>
+        <v>728.288</v>
       </c>
       <c r="V28" s="26" t="n">
         <f aca="false">U28/$P28/1000*100</f>
-        <v>0.127514626767243</v>
-      </c>
-      <c r="W28" s="27" t="n">
+        <v>0.132920857584535</v>
+      </c>
+      <c r="W28" s="2" t="n">
         <f aca="false">R28-U28</f>
-        <v>2138.63333333333</v>
+        <v>2273.2506</v>
       </c>
       <c r="X28" s="26" t="n">
         <f aca="false">W28/$P28/1000*100</f>
-        <v>0.390324949368298</v>
+        <v>0.414894134266332</v>
       </c>
       <c r="Y28" s="26"/>
       <c r="Z28" s="26"/>
-      <c r="AA28" s="0" t="n">
+      <c r="AA28" s="1" t="n">
         <f aca="false">Y28+Z28</f>
         <v>0</v>
       </c>
@@ -8022,33 +8017,33 @@
         <f aca="false">AA28/$P28/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC28" s="27" t="n">
+      <c r="AC28" s="2" t="n">
         <f aca="false">1000/100*Q28*($Q$41+$Q$47-$Q$49)-AA28</f>
-        <v>2073.85956940145</v>
+        <v>2264.47601678777</v>
       </c>
       <c r="AD28" s="26" t="n">
         <f aca="false">AC28/$P28/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE28" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE28" s="2" t="n">
         <f aca="false">AC28+Q28/100*1000 *($Q$46+$Q$43)</f>
-        <v>3704.00046025321</v>
+        <v>3936.29345989667</v>
       </c>
       <c r="AF28" s="26" t="n">
         <f aca="false">AE28/$P28/1000*100</f>
-        <v>0.676022284687333</v>
+        <v>0.718418403699992</v>
       </c>
       <c r="AG28" s="26" t="n">
         <f aca="false">-AA28+($Q$45 + $Q$46)*1000*Q28/100</f>
-        <v>1697.53657577951</v>
+        <v>1888.15302316584</v>
       </c>
       <c r="AH28" s="26" t="n">
         <f aca="false">AG28/P28/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI28" s="26" t="n">
         <f aca="false">ROUND(AG28/P28 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK28" s="26" t="n">
         <f aca="false">-Q28*($Q$47)*10</f>
@@ -8078,7 +8073,7 @@
         <f aca="false">AW28*1000</f>
         <v>1190</v>
       </c>
-      <c r="BA28" s="28" t="s">
+      <c r="BA28" s="27" t="s">
         <v>162</v>
       </c>
       <c r="BB28" s="23" t="n">
@@ -8087,15 +8082,15 @@
       <c r="BC28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="BD28" s="28" t="n">
+      <c r="BD28" s="27" t="n">
         <f aca="false">BB28+BC28/10</f>
         <v>8</v>
       </c>
-      <c r="BE28" s="28" t="n">
+      <c r="BE28" s="27" t="n">
         <f aca="false">1000*BD28</f>
         <v>8000</v>
       </c>
-      <c r="BG28" s="28" t="s">
+      <c r="BG28" s="27" t="s">
         <v>161</v>
       </c>
       <c r="BH28" s="23" t="n">
@@ -8113,10 +8108,10 @@
       <c r="BL28" s="23" t="n">
         <v>0.76</v>
       </c>
-      <c r="BM28" s="28" t="s">
+      <c r="BM28" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="BO28" s="28" t="n">
+      <c r="BO28" s="27" t="n">
         <f aca="false">BH28*1000</f>
         <v>1190</v>
       </c>
@@ -8144,13 +8139,13 @@
       <c r="BY28" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="XFA28" s="0"/>
-      <c r="XFB28" s="0"/>
-      <c r="XFC28" s="0"/>
-      <c r="XFD28" s="0"/>
+      <c r="XFA28" s="1"/>
+      <c r="XFB28" s="1"/>
+      <c r="XFC28" s="1"/>
+      <c r="XFD28" s="1"/>
     </row>
     <row r="29" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="28" t="s">
         <v>166</v>
       </c>
       <c r="B29" s="23" t="n">
@@ -8167,14 +8162,14 @@
         <f aca="false">D29/$P29/10</f>
         <v>0.039646017699115</v>
       </c>
-      <c r="F29" s="30" t="n">
+      <c r="F29" s="29" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="24" t="n">
         <f aca="false">F29/$P29/10</f>
         <v>0.0117522123893805</v>
       </c>
-      <c r="H29" s="30" t="n">
+      <c r="H29" s="29" t="n">
         <v>330</v>
       </c>
       <c r="I29" s="24" t="n">
@@ -8183,22 +8178,22 @@
       </c>
       <c r="J29" s="23" t="n">
         <f aca="false">L29*$J$37/100</f>
-        <v>331.5</v>
+        <v>455.013</v>
       </c>
       <c r="K29" s="24" t="n">
         <f aca="false">J29/$P29/10</f>
-        <v>0.15646017699115</v>
+        <v>0.214755398230089</v>
       </c>
       <c r="L29" s="23" t="n">
         <v>1950</v>
       </c>
       <c r="M29" s="23" t="n">
         <f aca="false">O29*$M$37/100</f>
-        <v>870.4</v>
+        <v>941.4912</v>
       </c>
       <c r="N29" s="24" t="n">
         <f aca="false">M29/$P29/10</f>
-        <v>0.410808259587021</v>
+        <v>0.444361628318584</v>
       </c>
       <c r="O29" s="23" t="n">
         <v>6400</v>
@@ -8212,35 +8207,35 @@
       </c>
       <c r="R29" s="23" t="n">
         <f aca="false">H29+F29+B29+D29+J29+M29</f>
-        <v>1777.8</v>
+        <v>1972.4042</v>
       </c>
       <c r="S29" s="26" t="n">
         <f aca="false">R29/$P29/1000*100</f>
-        <v>0.839079646017699</v>
+        <v>0.930928235988201</v>
       </c>
       <c r="T29" s="26" t="n">
         <f aca="false">R29/P29</f>
-        <v>8.39079646017699</v>
-      </c>
-      <c r="U29" s="27" t="n">
+        <v>9.30928235988201</v>
+      </c>
+      <c r="U29" s="2" t="n">
         <f aca="false">3/5*H29+M29/3</f>
-        <v>488.133333333333</v>
+        <v>511.8304</v>
       </c>
       <c r="V29" s="26" t="n">
         <f aca="false">U29/$P29/1000*100</f>
-        <v>0.230387413962635</v>
-      </c>
-      <c r="W29" s="27" t="n">
+        <v>0.24157187020649</v>
+      </c>
+      <c r="W29" s="2" t="n">
         <f aca="false">R29-U29</f>
-        <v>1289.66666666667</v>
+        <v>1460.5738</v>
       </c>
       <c r="X29" s="26" t="n">
         <f aca="false">W29/$P29/1000*100</f>
-        <v>0.608692232055064</v>
+        <v>0.689356365781711</v>
       </c>
       <c r="Y29" s="26"/>
       <c r="Z29" s="26"/>
-      <c r="AA29" s="0" t="n">
+      <c r="AA29" s="1" t="n">
         <f aca="false">Y29+Z29</f>
         <v>0</v>
       </c>
@@ -8248,33 +8243,33 @@
         <f aca="false">AA29/$P29/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC29" s="27" t="n">
+      <c r="AC29" s="2" t="n">
         <f aca="false">1000/100*Q29*($Q$41+$Q$47-$Q$49)-AA29</f>
-        <v>801.953230117544</v>
+        <v>875.663850619736</v>
       </c>
       <c r="AD29" s="26" t="n">
         <f aca="false">AC29/$P29/1000*100</f>
-        <v>0.378502999465508</v>
-      </c>
-      <c r="AE29" s="27" t="n">
+        <v>0.413292672858873</v>
+      </c>
+      <c r="AE29" s="2" t="n">
         <f aca="false">AC29+Q29/100*1000 *($Q$46+$Q$43)</f>
-        <v>1432.32221568129</v>
+        <v>1522.14899283936</v>
       </c>
       <c r="AF29" s="26" t="n">
         <f aca="false">AE29/$P29/1000*100</f>
-        <v>0.676022284687335</v>
+        <v>0.718418403699994</v>
       </c>
       <c r="AG29" s="26" t="n">
         <f aca="false">-AA29+($Q$45 + $Q$46)*1000*Q29/100</f>
-        <v>656.430628319719</v>
+        <v>730.141248821911</v>
       </c>
       <c r="AH29" s="26" t="n">
         <f aca="false">AG29/P29/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971994</v>
       </c>
       <c r="AI29" s="26" t="n">
         <f aca="false">ROUND(AG29/P29 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK29" s="26" t="n">
         <f aca="false">-Q29*($Q$47)*10</f>
@@ -8304,7 +8299,7 @@
         <f aca="false">AW29*1000</f>
         <v>1950</v>
       </c>
-      <c r="BA29" s="28" t="s">
+      <c r="BA29" s="27" t="s">
         <v>168</v>
       </c>
       <c r="BB29" s="23" t="n">
@@ -8313,15 +8308,15 @@
       <c r="BC29" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="BD29" s="28" t="n">
+      <c r="BD29" s="27" t="n">
         <f aca="false">BB29+BC29/10</f>
         <v>6.4</v>
       </c>
-      <c r="BE29" s="28" t="n">
+      <c r="BE29" s="27" t="n">
         <f aca="false">1000*BD29</f>
         <v>6400</v>
       </c>
-      <c r="BG29" s="28" t="s">
+      <c r="BG29" s="27" t="s">
         <v>167</v>
       </c>
       <c r="BH29" s="23" t="n">
@@ -8339,10 +8334,10 @@
       <c r="BL29" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="BM29" s="28" t="s">
+      <c r="BM29" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="BO29" s="28" t="n">
+      <c r="BO29" s="27" t="n">
         <f aca="false">BH29*1000</f>
         <v>1950</v>
       </c>
@@ -8370,10 +8365,10 @@
       <c r="BY29" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="XFA29" s="0"/>
-      <c r="XFB29" s="0"/>
-      <c r="XFC29" s="0"/>
-      <c r="XFD29" s="0"/>
+      <c r="XFA29" s="1"/>
+      <c r="XFB29" s="1"/>
+      <c r="XFC29" s="1"/>
+      <c r="XFD29" s="1"/>
     </row>
     <row r="30" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
@@ -8409,22 +8404,22 @@
       </c>
       <c r="J30" s="23" t="n">
         <f aca="false">L30*$J$37/100</f>
-        <v>105.4</v>
+        <v>144.6708</v>
       </c>
       <c r="K30" s="24" t="n">
         <f aca="false">J30/$P30/10</f>
-        <v>0.0489522181764138</v>
+        <v>0.0671912387604964</v>
       </c>
       <c r="L30" s="23" t="n">
         <v>620</v>
       </c>
       <c r="M30" s="23" t="n">
         <f aca="false">O30*$M$37/100</f>
-        <v>435.2</v>
+        <v>470.7456</v>
       </c>
       <c r="N30" s="24" t="n">
         <f aca="false">M30/$P30/10</f>
-        <v>0.202125287954225</v>
+        <v>0.218634168090956</v>
       </c>
       <c r="O30" s="23" t="n">
         <v>3200</v>
@@ -8438,35 +8433,35 @@
       </c>
       <c r="R30" s="23" t="n">
         <f aca="false">H30+F30+B30+D30+J30+M30</f>
-        <v>828.5</v>
+        <v>903.3164</v>
       </c>
       <c r="S30" s="26" t="n">
         <f aca="false">R30/$P30/1000*100</f>
-        <v>0.384790443635283</v>
+        <v>0.419538344356097</v>
       </c>
       <c r="T30" s="26" t="n">
         <f aca="false">R30/P30</f>
-        <v>3.84790443635283</v>
-      </c>
-      <c r="U30" s="27" t="n">
+        <v>4.19538344356097</v>
+      </c>
+      <c r="U30" s="2" t="n">
         <f aca="false">3/5*H30+M30/3</f>
-        <v>217.666666666667</v>
+        <v>229.5152</v>
       </c>
       <c r="V30" s="26" t="n">
         <f aca="false">U30/$P30/1000*100</f>
-        <v>0.101093606796958</v>
-      </c>
-      <c r="W30" s="27" t="n">
+        <v>0.106596566842535</v>
+      </c>
+      <c r="W30" s="2" t="n">
         <f aca="false">R30-U30</f>
-        <v>610.833333333333</v>
+        <v>673.8012</v>
       </c>
       <c r="X30" s="26" t="n">
         <f aca="false">W30/$P30/1000*100</f>
-        <v>0.283696836838325</v>
+        <v>0.312941777513562</v>
       </c>
       <c r="Y30" s="26"/>
       <c r="Z30" s="26"/>
-      <c r="AA30" s="0" t="n">
+      <c r="AA30" s="1" t="n">
         <f aca="false">Y30+Z30</f>
         <v>0</v>
       </c>
@@ -8474,33 +8469,33 @@
         <f aca="false">AA30/$P30/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="27" t="n">
+      <c r="AC30" s="2" t="n">
         <f aca="false">1000/100*Q30*($Q$41+$Q$47-$Q$49)-AA30</f>
-        <v>814.962378209173</v>
+        <v>889.868719785896</v>
       </c>
       <c r="AD30" s="26" t="n">
         <f aca="false">AC30/$P30/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE30" s="27" t="n">
+        <v>0.413292672858873</v>
+      </c>
+      <c r="AE30" s="2" t="n">
         <f aca="false">AC30+Q30/100*1000 *($Q$46+$Q$43)</f>
-        <v>1455.55710160599</v>
+        <v>1546.84103337453</v>
       </c>
       <c r="AF30" s="26" t="n">
         <f aca="false">AE30/$P30/1000*100</f>
-        <v>0.676022284687335</v>
+        <v>0.718418403699994</v>
       </c>
       <c r="AG30" s="26" t="n">
         <f aca="false">-AA30+($Q$45 + $Q$46)*1000*Q30/100</f>
-        <v>667.079133662656</v>
+        <v>741.985475239379</v>
       </c>
       <c r="AH30" s="26" t="n">
         <f aca="false">AG30/P30/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971994</v>
       </c>
       <c r="AI30" s="26" t="n">
         <f aca="false">ROUND(AG30/P30 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK30" s="26" t="n">
         <f aca="false">-Q30*($Q$47)*10</f>
@@ -8530,7 +8525,7 @@
         <f aca="false">AW30*1000</f>
         <v>620</v>
       </c>
-      <c r="BA30" s="28" t="s">
+      <c r="BA30" s="27" t="s">
         <v>171</v>
       </c>
       <c r="BB30" s="23" t="n">
@@ -8539,15 +8534,15 @@
       <c r="BC30" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="BD30" s="28" t="n">
+      <c r="BD30" s="27" t="n">
         <f aca="false">BB30+BC30/10</f>
         <v>3.2</v>
       </c>
-      <c r="BE30" s="28" t="n">
+      <c r="BE30" s="27" t="n">
         <f aca="false">1000*BD30</f>
         <v>3200</v>
       </c>
-      <c r="BG30" s="28" t="s">
+      <c r="BG30" s="27" t="s">
         <v>172</v>
       </c>
       <c r="BH30" s="23" t="n">
@@ -8565,10 +8560,10 @@
       <c r="BL30" s="23" t="n">
         <v>0.92</v>
       </c>
-      <c r="BM30" s="28" t="s">
+      <c r="BM30" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="BO30" s="28" t="n">
+      <c r="BO30" s="27" t="n">
         <f aca="false">BH30*1000</f>
         <v>620</v>
       </c>
@@ -8596,13 +8591,13 @@
       <c r="BY30" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="XFA30" s="0"/>
-      <c r="XFB30" s="0"/>
-      <c r="XFC30" s="0"/>
-      <c r="XFD30" s="0"/>
+      <c r="XFA30" s="1"/>
+      <c r="XFB30" s="1"/>
+      <c r="XFC30" s="1"/>
+      <c r="XFD30" s="1"/>
     </row>
     <row r="31" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="28" t="s">
         <v>176</v>
       </c>
       <c r="B31" s="23" t="n">
@@ -8619,14 +8614,14 @@
         <f aca="false">D31/$P31/10</f>
         <v>0.0380275031346996</v>
       </c>
-      <c r="F31" s="30" t="n">
+      <c r="F31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="24" t="n">
         <f aca="false">F31/$P31/10</f>
         <v>0</v>
       </c>
-      <c r="H31" s="30" t="n">
+      <c r="H31" s="29" t="n">
         <v>19</v>
       </c>
       <c r="I31" s="24" t="n">
@@ -8635,22 +8630,22 @@
       </c>
       <c r="J31" s="23" t="n">
         <f aca="false">L31*$J$37/100</f>
-        <v>8.5</v>
+        <v>11.667</v>
       </c>
       <c r="K31" s="24" t="n">
         <f aca="false">J31/$P31/10</f>
-        <v>0.00873604801743099</v>
+        <v>0.0119909967316903</v>
       </c>
       <c r="L31" s="23" t="n">
         <v>50</v>
       </c>
       <c r="M31" s="23" t="n">
         <f aca="false">O31*$M$37/100</f>
-        <v>176.8</v>
+        <v>191.2404</v>
       </c>
       <c r="N31" s="24" t="n">
         <f aca="false">M31/$P31/10</f>
-        <v>0.181709798762565</v>
+        <v>0.196551213796789</v>
       </c>
       <c r="O31" s="23" t="n">
         <v>1300</v>
@@ -8664,35 +8659,35 @@
       </c>
       <c r="R31" s="23" t="n">
         <f aca="false">H31+F31+B31+D31+J31+M31</f>
-        <v>317.3</v>
+        <v>334.9074</v>
       </c>
       <c r="S31" s="26" t="n">
         <f aca="false">R31/$P31/1000*100</f>
-        <v>0.326111533638924</v>
+        <v>0.344207897387408</v>
       </c>
       <c r="T31" s="26" t="n">
         <f aca="false">R31/P31</f>
-        <v>3.26111533638924</v>
-      </c>
-      <c r="U31" s="27" t="n">
+        <v>3.44207897387408</v>
+      </c>
+      <c r="U31" s="2" t="n">
         <f aca="false">3/5*H31+M31/3</f>
-        <v>70.3333333333333</v>
+        <v>75.1468</v>
       </c>
       <c r="V31" s="26" t="n">
         <f aca="false">U31/$P31/1000*100</f>
-        <v>0.0722865149677623</v>
-      </c>
-      <c r="W31" s="27" t="n">
+        <v>0.0772336533125039</v>
+      </c>
+      <c r="W31" s="2" t="n">
         <f aca="false">R31-U31</f>
-        <v>246.966666666667</v>
+        <v>259.7606</v>
       </c>
       <c r="X31" s="26" t="n">
         <f aca="false">W31/$P31/1000*100</f>
-        <v>0.253825018671161</v>
+        <v>0.266974244074904</v>
       </c>
       <c r="Y31" s="26"/>
       <c r="Z31" s="26"/>
-      <c r="AA31" s="0" t="n">
+      <c r="AA31" s="1" t="n">
         <f aca="false">Y31+Z31</f>
         <v>0</v>
       </c>
@@ -8700,33 +8695,33 @@
         <f aca="false">AA31/$P31/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC31" s="27" t="n">
+      <c r="AC31" s="2" t="n">
         <f aca="false">1000/100*Q31*($Q$41+$Q$47-$Q$49)-AA31</f>
-        <v>368.275848419949</v>
+        <v>402.125504838226</v>
       </c>
       <c r="AD31" s="26" t="n">
         <f aca="false">AC31/$P31/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE31" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE31" s="2" t="n">
         <f aca="false">AC31+Q31/100*1000 *($Q$46+$Q$43)</f>
-        <v>657.756162555082</v>
+        <v>699.006738432019</v>
       </c>
       <c r="AF31" s="26" t="n">
         <f aca="false">AE31/$P31/1000*100</f>
-        <v>0.676022284687334</v>
+        <v>0.718418403699993</v>
       </c>
       <c r="AG31" s="26" t="n">
         <f aca="false">-AA31+($Q$45 + $Q$46)*1000*Q31/100</f>
-        <v>301.448435512694</v>
+        <v>335.29809193097</v>
       </c>
       <c r="AH31" s="26" t="n">
         <f aca="false">AG31/P31/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI31" s="26" t="n">
         <f aca="false">ROUND(AG31/P31 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK31" s="26" t="n">
         <f aca="false">-Q31*($Q$47)*10</f>
@@ -8736,7 +8731,7 @@
         <f aca="false">AK31/P31/10</f>
         <v>-0.16483976132851</v>
       </c>
-      <c r="AM31" s="32"/>
+      <c r="AM31" s="31"/>
       <c r="AO31" s="23" t="n">
         <v>136.8</v>
       </c>
@@ -8757,7 +8752,7 @@
         <f aca="false">AW31*1000</f>
         <v>400</v>
       </c>
-      <c r="BA31" s="28" t="s">
+      <c r="BA31" s="27" t="s">
         <v>176</v>
       </c>
       <c r="BB31" s="23" t="n">
@@ -8766,15 +8761,15 @@
       <c r="BC31" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="BD31" s="28" t="n">
+      <c r="BD31" s="27" t="n">
         <f aca="false">BB31+BC31/10</f>
         <v>1.3</v>
       </c>
-      <c r="BE31" s="28" t="n">
+      <c r="BE31" s="27" t="n">
         <f aca="false">1000*BD31</f>
         <v>1300</v>
       </c>
-      <c r="BG31" s="28" t="s">
+      <c r="BG31" s="27" t="s">
         <v>177</v>
       </c>
       <c r="BH31" s="23" t="n">
@@ -8792,10 +8787,10 @@
       <c r="BL31" s="23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BM31" s="28" t="s">
+      <c r="BM31" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="BO31" s="28" t="n">
+      <c r="BO31" s="27" t="n">
         <f aca="false">BH31*1000</f>
         <v>50</v>
       </c>
@@ -8823,10 +8818,10 @@
       <c r="BY31" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="XFA31" s="0"/>
-      <c r="XFB31" s="0"/>
-      <c r="XFC31" s="0"/>
-      <c r="XFD31" s="0"/>
+      <c r="XFA31" s="1"/>
+      <c r="XFB31" s="1"/>
+      <c r="XFC31" s="1"/>
+      <c r="XFD31" s="1"/>
     </row>
     <row r="32" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
@@ -8862,22 +8857,22 @@
       </c>
       <c r="J32" s="23" t="n">
         <f aca="false">L32*$J$37/100</f>
-        <v>5.1</v>
+        <v>7.0002</v>
       </c>
       <c r="K32" s="24" t="n">
         <f aca="false">J32/$P32/10</f>
-        <v>0.00990849216063414</v>
+        <v>0.0136002797691904</v>
       </c>
       <c r="L32" s="23" t="n">
         <v>30</v>
       </c>
       <c r="M32" s="23" t="n">
         <f aca="false">O32*$M$37/100</f>
-        <v>149.6</v>
+        <v>161.8188</v>
       </c>
       <c r="N32" s="24" t="n">
         <f aca="false">M32/$P32/10</f>
-        <v>0.290649103378602</v>
+        <v>0.314388296322201</v>
       </c>
       <c r="O32" s="23" t="n">
         <v>1100</v>
@@ -8891,35 +8886,35 @@
       </c>
       <c r="R32" s="23" t="n">
         <f aca="false">H32+F32+B32+D32+J32+M32</f>
-        <v>277.1</v>
+        <v>291.219</v>
       </c>
       <c r="S32" s="26" t="n">
         <f aca="false">R32/$P32/1000*100</f>
-        <v>0.538361407394455</v>
+        <v>0.565792387946611</v>
       </c>
       <c r="T32" s="26" t="n">
         <f aca="false">R32/P32</f>
-        <v>5.38361407394455</v>
-      </c>
-      <c r="U32" s="27" t="n">
+        <v>5.65792387946611</v>
+      </c>
+      <c r="U32" s="2" t="n">
         <f aca="false">3/5*H32+M32/3</f>
-        <v>94.8666666666667</v>
+        <v>98.9396</v>
       </c>
       <c r="V32" s="26" t="n">
         <f aca="false">U32/$P32/1000*100</f>
-        <v>0.184310906465129</v>
-      </c>
-      <c r="W32" s="27" t="n">
+        <v>0.192223970779662</v>
+      </c>
+      <c r="W32" s="2" t="n">
         <f aca="false">R32-U32</f>
-        <v>182.233333333333</v>
+        <v>192.2794</v>
       </c>
       <c r="X32" s="26" t="n">
         <f aca="false">W32/$P32/1000*100</f>
-        <v>0.354050500929326</v>
+        <v>0.373568417166949</v>
       </c>
       <c r="Y32" s="26"/>
       <c r="Z32" s="26"/>
-      <c r="AA32" s="0" t="n">
+      <c r="AA32" s="1" t="n">
         <f aca="false">Y32+Z32</f>
         <v>0</v>
       </c>
@@ -8927,33 +8922,33 @@
         <f aca="false">AA32/$P32/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC32" s="27" t="n">
+      <c r="AC32" s="2" t="n">
         <f aca="false">1000/100*Q32*($Q$41+$Q$47-$Q$49)-AA32</f>
-        <v>194.819278854891</v>
+        <v>212.72587164719</v>
       </c>
       <c r="AD32" s="26" t="n">
         <f aca="false">AC32/$P32/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE32" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE32" s="2" t="n">
         <f aca="false">AC32+Q32/100*1000 *($Q$46+$Q$43)</f>
-        <v>347.955430151418</v>
+        <v>369.777136568424</v>
       </c>
       <c r="AF32" s="26" t="n">
         <f aca="false">AE32/$P32/1000*100</f>
-        <v>0.676022284687334</v>
+        <v>0.718418403699994</v>
       </c>
       <c r="AG32" s="26" t="n">
         <f aca="false">-AA32+($Q$45 + $Q$46)*1000*Q32/100</f>
-        <v>159.467331540976</v>
+        <v>177.373924333275</v>
       </c>
       <c r="AH32" s="26" t="n">
         <f aca="false">AG32/P32/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971994</v>
       </c>
       <c r="AI32" s="26" t="n">
         <f aca="false">ROUND(AG32/P32 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK32" s="26" t="n">
         <f aca="false">-Q32*($Q$47)*10</f>
@@ -8983,7 +8978,7 @@
         <f aca="false">AW32*1000</f>
         <v>300</v>
       </c>
-      <c r="BA32" s="28" t="s">
+      <c r="BA32" s="27" t="s">
         <v>180</v>
       </c>
       <c r="BB32" s="23" t="n">
@@ -8992,15 +8987,15 @@
       <c r="BC32" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="BD32" s="28" t="n">
+      <c r="BD32" s="27" t="n">
         <f aca="false">BB32+BC32/10</f>
         <v>1.1</v>
       </c>
-      <c r="BE32" s="28" t="n">
+      <c r="BE32" s="27" t="n">
         <f aca="false">1000*BD32</f>
         <v>1100</v>
       </c>
-      <c r="BG32" s="28" t="s">
+      <c r="BG32" s="27" t="s">
         <v>181</v>
       </c>
       <c r="BH32" s="23" t="n">
@@ -9018,10 +9013,10 @@
       <c r="BL32" s="23" t="n">
         <v>0.22</v>
       </c>
-      <c r="BM32" s="28" t="s">
+      <c r="BM32" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="BO32" s="28" t="n">
+      <c r="BO32" s="27" t="n">
         <f aca="false">BH32*1000</f>
         <v>30</v>
       </c>
@@ -9049,13 +9044,13 @@
       <c r="BY32" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="XFA32" s="0"/>
-      <c r="XFB32" s="0"/>
-      <c r="XFC32" s="0"/>
-      <c r="XFD32" s="0"/>
+      <c r="XFA32" s="1"/>
+      <c r="XFB32" s="1"/>
+      <c r="XFC32" s="1"/>
+      <c r="XFD32" s="1"/>
     </row>
     <row r="33" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="28" t="s">
         <v>185</v>
       </c>
       <c r="B33" s="23" t="n">
@@ -9072,14 +9067,14 @@
         <f aca="false">D33/$P33/10</f>
         <v>0.0684155212562079</v>
       </c>
-      <c r="F33" s="30" t="n">
+      <c r="F33" s="29" t="n">
         <v>240.6</v>
       </c>
       <c r="G33" s="24" t="n">
         <f aca="false">F33/$P33/10</f>
         <v>0.019832258330414</v>
       </c>
-      <c r="H33" s="30" t="n">
+      <c r="H33" s="29" t="n">
         <v>2151</v>
       </c>
       <c r="I33" s="24" t="n">
@@ -9088,22 +9083,22 @@
       </c>
       <c r="J33" s="23" t="n">
         <f aca="false">L33*$J$37/100</f>
-        <v>1586.1</v>
+        <v>2177.0622</v>
       </c>
       <c r="K33" s="24" t="n">
         <f aca="false">J33/$P33/10</f>
-        <v>0.130739588270447</v>
+        <v>0.179451620747213</v>
       </c>
       <c r="L33" s="23" t="n">
         <v>9330</v>
       </c>
       <c r="M33" s="23" t="n">
         <f aca="false">O33*$M$37/100</f>
-        <v>4202.4</v>
+        <v>4545.6372</v>
       </c>
       <c r="N33" s="24" t="n">
         <f aca="false">M33/$P33/10</f>
-        <v>0.346396851237455</v>
+        <v>0.374689323469409</v>
       </c>
       <c r="O33" s="23" t="n">
         <v>30900</v>
@@ -9117,31 +9112,31 @@
       </c>
       <c r="R33" s="23" t="n">
         <f aca="false">H33+F33+B33+D33+J33+M33</f>
-        <v>9697.1</v>
+        <v>10631.2994</v>
       </c>
       <c r="S33" s="26" t="n">
         <f aca="false">R33/$P33/1000*100</f>
-        <v>0.799315844787438</v>
+        <v>0.876320349496157</v>
       </c>
       <c r="T33" s="26" t="n">
         <f aca="false">R33/P33</f>
-        <v>7.99315844787438</v>
-      </c>
-      <c r="U33" s="27" t="n">
+        <v>8.76320349496157</v>
+      </c>
+      <c r="U33" s="2" t="n">
         <f aca="false">3/5*H33+M33/3</f>
-        <v>2691.4</v>
+        <v>2805.8124</v>
       </c>
       <c r="V33" s="26" t="n">
         <f aca="false">U33/$P33/1000*100</f>
-        <v>0.221847631215612</v>
-      </c>
-      <c r="W33" s="27" t="n">
+        <v>0.23127845529293</v>
+      </c>
+      <c r="W33" s="2" t="n">
         <f aca="false">R33-U33</f>
-        <v>7005.7</v>
+        <v>7825.487</v>
       </c>
       <c r="X33" s="26" t="n">
         <f aca="false">W33/$P33/1000*100</f>
-        <v>0.577468213571826</v>
+        <v>0.645041894203227</v>
       </c>
       <c r="Y33" s="26" t="n">
         <f aca="false">B33</f>
@@ -9151,7 +9146,7 @@
         <f aca="false">F33</f>
         <v>240.6</v>
       </c>
-      <c r="AA33" s="0" t="n">
+      <c r="AA33" s="1" t="n">
         <f aca="false">Y33+Z33</f>
         <v>927.6</v>
       </c>
@@ -9159,33 +9154,33 @@
         <f aca="false">AA33/$P33/1000*100</f>
         <v>0.076460527129227</v>
       </c>
-      <c r="AC33" s="27" t="n">
+      <c r="AC33" s="2" t="n">
         <f aca="false">1000/100*Q33*($Q$41+$Q$47-$Q$49)-AA33</f>
-        <v>3664.30376376567</v>
+        <v>4086.36338395562</v>
       </c>
       <c r="AD33" s="26" t="n">
         <f aca="false">AC33/$P33/1000*100</f>
-        <v>0.30204247233628</v>
-      </c>
-      <c r="AE33" s="27" t="n">
+        <v>0.336832145729645</v>
+      </c>
+      <c r="AE33" s="2" t="n">
         <f aca="false">AC33+Q33/100*1000 *($Q$46+$Q$43)</f>
-        <v>7273.73335225556</v>
+        <v>7788.07246908739</v>
       </c>
       <c r="AF33" s="26" t="n">
         <f aca="false">AE33/$P33/1000*100</f>
-        <v>0.599561757558107</v>
+        <v>0.641957876570766</v>
       </c>
       <c r="AG33" s="26" t="n">
         <f aca="false">-AA33+($Q$45 + $Q$46)*1000*Q33/100</f>
-        <v>2831.05594105852</v>
+        <v>3253.11556124848</v>
       </c>
       <c r="AH33" s="26" t="n">
         <f aca="false">AG33/P33/10</f>
-        <v>0.233359238449401</v>
+        <v>0.268148911842766</v>
       </c>
       <c r="AI33" s="26" t="n">
         <f aca="false">ROUND(AG33/P33 *100/1000, 2)</f>
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="AK33" s="26" t="n">
         <f aca="false">-Q33*($Q$47)*10</f>
@@ -9215,7 +9210,7 @@
         <f aca="false">AW33*1000</f>
         <v>9330</v>
       </c>
-      <c r="BA33" s="28" t="s">
+      <c r="BA33" s="27" t="s">
         <v>187</v>
       </c>
       <c r="BB33" s="23" t="n">
@@ -9224,15 +9219,15 @@
       <c r="BC33" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="BD33" s="28" t="n">
+      <c r="BD33" s="27" t="n">
         <f aca="false">BB33+BC33/10</f>
         <v>30.9</v>
       </c>
-      <c r="BE33" s="28" t="n">
+      <c r="BE33" s="27" t="n">
         <f aca="false">1000*BD33</f>
         <v>30900</v>
       </c>
-      <c r="BG33" s="28" t="s">
+      <c r="BG33" s="27" t="s">
         <v>186</v>
       </c>
       <c r="BH33" s="23" t="n">
@@ -9250,10 +9245,10 @@
       <c r="BL33" s="23" t="n">
         <v>3.24</v>
       </c>
-      <c r="BM33" s="28" t="s">
+      <c r="BM33" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="BO33" s="28" t="n">
+      <c r="BO33" s="27" t="n">
         <f aca="false">BH33*1000</f>
         <v>9330</v>
       </c>
@@ -9281,10 +9276,10 @@
       <c r="BY33" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="XFA33" s="0"/>
-      <c r="XFB33" s="0"/>
-      <c r="XFC33" s="0"/>
-      <c r="XFD33" s="0"/>
+      <c r="XFA33" s="1"/>
+      <c r="XFB33" s="1"/>
+      <c r="XFC33" s="1"/>
+      <c r="XFD33" s="1"/>
     </row>
     <row r="34" s="23" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="s">
@@ -9320,22 +9315,22 @@
       </c>
       <c r="J34" s="23" t="n">
         <f aca="false">L34*$J$37/100</f>
-        <v>197.2</v>
+        <v>270.6744</v>
       </c>
       <c r="K34" s="24" t="n">
         <f aca="false">J34/$P34/10</f>
-        <v>0.035679521185168</v>
+        <v>0.0489732910196889</v>
       </c>
       <c r="L34" s="23" t="n">
         <v>1160</v>
       </c>
       <c r="M34" s="23" t="n">
         <f aca="false">O34*$M$37/100</f>
-        <v>965.6</v>
+        <v>1044.4668</v>
       </c>
       <c r="N34" s="24" t="n">
         <f aca="false">M34/$P34/10</f>
-        <v>0.17470662097565</v>
+        <v>0.188976041165338</v>
       </c>
       <c r="O34" s="23" t="n">
         <v>7100</v>
@@ -9349,35 +9344,35 @@
       </c>
       <c r="R34" s="23" t="n">
         <f aca="false">H34+F34+B34+D34+J34+M34</f>
-        <v>2910.9</v>
+        <v>3063.2412</v>
       </c>
       <c r="S34" s="26" t="n">
         <f aca="false">R34/$P34/1000*100</f>
-        <v>0.526670984877818</v>
+        <v>0.554234174902026</v>
       </c>
       <c r="T34" s="26" t="n">
         <f aca="false">R34/P34</f>
-        <v>5.26670984877818</v>
-      </c>
-      <c r="U34" s="27" t="n">
+        <v>5.54234174902026</v>
+      </c>
+      <c r="U34" s="2" t="n">
         <f aca="false">3/5*H34+M34/3</f>
-        <v>749.066666666667</v>
+        <v>775.3556</v>
       </c>
       <c r="V34" s="26" t="n">
         <f aca="false">U34/$P34/1000*100</f>
-        <v>0.135529107517427</v>
-      </c>
-      <c r="W34" s="27" t="n">
+        <v>0.140285580913989</v>
+      </c>
+      <c r="W34" s="2" t="n">
         <f aca="false">R34-U34</f>
-        <v>2161.83333333333</v>
+        <v>2287.8856</v>
       </c>
       <c r="X34" s="26" t="n">
         <f aca="false">W34/$P34/1000*100</f>
-        <v>0.391141877360391</v>
+        <v>0.413948593988037</v>
       </c>
       <c r="Y34" s="26"/>
       <c r="Z34" s="26"/>
-      <c r="AA34" s="0" t="n">
+      <c r="AA34" s="1" t="n">
         <f aca="false">Y34+Z34</f>
         <v>0</v>
       </c>
@@ -9385,33 +9380,33 @@
         <f aca="false">AA34/$P34/1000*100</f>
         <v>0</v>
       </c>
-      <c r="AC34" s="27" t="n">
+      <c r="AC34" s="2" t="n">
         <f aca="false">1000/100*Q34*($Q$41+$Q$47-$Q$49)-AA34</f>
-        <v>2091.97850798587</v>
+        <v>2284.26033703753</v>
       </c>
       <c r="AD34" s="26" t="n">
         <f aca="false">AC34/$P34/1000*100</f>
-        <v>0.378502999465507</v>
-      </c>
-      <c r="AE34" s="27" t="n">
+        <v>0.413292672858872</v>
+      </c>
+      <c r="AE34" s="2" t="n">
         <f aca="false">AC34+Q34/100*1000 *($Q$46+$Q$43)</f>
-        <v>3736.3616470212</v>
+        <v>3970.68414888178</v>
       </c>
       <c r="AF34" s="26" t="n">
         <f aca="false">AE34/$P34/1000*100</f>
-        <v>0.676022284687333</v>
+        <v>0.718418403699993</v>
       </c>
       <c r="AG34" s="26" t="n">
         <f aca="false">-AA34+($Q$45 + $Q$46)*1000*Q34/100</f>
-        <v>1712.36764795776</v>
+        <v>1904.64947700943</v>
       </c>
       <c r="AH34" s="26" t="n">
         <f aca="false">AG34/P34/10</f>
-        <v>0.309819765578628</v>
+        <v>0.344609438971993</v>
       </c>
       <c r="AI34" s="26" t="n">
         <f aca="false">ROUND(AG34/P34 *100/1000, 2)</f>
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="AK34" s="26" t="n">
         <f aca="false">-Q34*($Q$47)*10</f>
@@ -9441,7 +9436,7 @@
         <f aca="false">AW34*1000</f>
         <v>1160</v>
       </c>
-      <c r="BA34" s="28" t="s">
+      <c r="BA34" s="27" t="s">
         <v>193</v>
       </c>
       <c r="BB34" s="23" t="n">
@@ -9450,15 +9445,15 @@
       <c r="BC34" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="BD34" s="28" t="n">
+      <c r="BD34" s="27" t="n">
         <f aca="false">BB34+BC34/10</f>
         <v>7.1</v>
       </c>
-      <c r="BE34" s="28" t="n">
+      <c r="BE34" s="27" t="n">
         <f aca="false">1000*BD34</f>
         <v>7100</v>
       </c>
-      <c r="BG34" s="28" t="s">
+      <c r="BG34" s="27" t="s">
         <v>192</v>
       </c>
       <c r="BH34" s="23" t="n">
@@ -9476,10 +9471,10 @@
       <c r="BL34" s="23" t="n">
         <v>1.08</v>
       </c>
-      <c r="BM34" s="28" t="s">
+      <c r="BM34" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="BO34" s="28" t="n">
+      <c r="BO34" s="27" t="n">
         <f aca="false">BH34*1000</f>
         <v>1160</v>
       </c>
@@ -9507,74 +9502,92 @@
       <c r="BY34" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="XFA34" s="0"/>
-      <c r="XFB34" s="0"/>
-      <c r="XFC34" s="0"/>
-      <c r="XFD34" s="0"/>
+      <c r="XFA34" s="1"/>
+      <c r="XFB34" s="1"/>
+      <c r="XFC34" s="1"/>
+      <c r="XFD34" s="1"/>
     </row>
-    <row r="35" s="38" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="33" t="s">
+    <row r="35" s="36" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="B35" s="34" t="n">
+      <c r="B35" s="33" t="n">
         <v>5880</v>
       </c>
-      <c r="C35" s="35"/>
-      <c r="D35" s="36" t="n">
+      <c r="C35" s="24" t="n">
+        <f aca="false">B35/$P35/10</f>
+        <v>0.0403857415254848</v>
+      </c>
+      <c r="D35" s="34" t="n">
         <v>9616</v>
       </c>
-      <c r="E35" s="35"/>
-      <c r="F35" s="34" t="n">
+      <c r="E35" s="24" t="n">
+        <f aca="false">D35/$P35/10</f>
+        <v>0.0660457977056228</v>
+      </c>
+      <c r="F35" s="33" t="n">
         <v>8334.6</v>
       </c>
-      <c r="G35" s="35"/>
-      <c r="H35" s="34" t="n">
+      <c r="G35" s="24" t="n">
+        <f aca="false">F35/$P35/10</f>
+        <v>0.0572447281153582</v>
+      </c>
+      <c r="H35" s="33" t="n">
         <v>26264</v>
       </c>
-      <c r="I35" s="35"/>
+      <c r="I35" s="24" t="n">
+        <f aca="false">H35/$P35/10</f>
+        <v>0.180389645480499</v>
+      </c>
       <c r="J35" s="23" t="n">
         <f aca="false">SUM(J8:J34)</f>
-        <v>7650</v>
-      </c>
-      <c r="K35" s="26"/>
+        <v>10500.3</v>
+      </c>
+      <c r="K35" s="24" t="n">
+        <f aca="false">J35/$P35/10</f>
+        <v>0.0721194560782395</v>
+      </c>
       <c r="L35" s="23"/>
       <c r="M35" s="23" t="n">
         <f aca="false">SUM(M8:M34)</f>
-        <v>40677.6</v>
-      </c>
-      <c r="N35" s="26"/>
+        <v>44000.0028</v>
+      </c>
+      <c r="N35" s="24" t="n">
+        <f aca="false">M35/$P35/10</f>
+        <v>0.302206248333573</v>
+      </c>
       <c r="O35" s="23"/>
       <c r="P35" s="2" t="n">
         <f aca="false">SUM(P8:P34)</f>
         <v>14559.594</v>
       </c>
-      <c r="Q35" s="37" t="n">
+      <c r="Q35" s="35" t="n">
         <v>100</v>
       </c>
       <c r="R35" s="23" t="n">
         <f aca="false">H35+F35+B35+D35+J35+M35</f>
-        <v>98422.2</v>
+        <v>104594.9028</v>
       </c>
       <c r="S35" s="26" t="n">
         <f aca="false">R35/$P35/1000*100</f>
-        <v>0.675995498226118</v>
+        <v>0.718391617238778</v>
       </c>
       <c r="T35" s="26"/>
-      <c r="U35" s="27" t="n">
+      <c r="U35" s="2" t="n">
         <f aca="false">3/5*H35+M35/3</f>
-        <v>29317.6</v>
+        <v>30425.0676</v>
       </c>
       <c r="V35" s="26" t="n">
         <f aca="false">U35/$P35/1000*100</f>
-        <v>0.201362757780196</v>
-      </c>
-      <c r="W35" s="27" t="n">
+        <v>0.20896920339949</v>
+      </c>
+      <c r="W35" s="2" t="n">
         <f aca="false">R35-U35</f>
-        <v>69104.6</v>
+        <v>74169.8352</v>
       </c>
       <c r="X35" s="26" t="n">
         <f aca="false">W35/$P35/1000*100</f>
-        <v>0.474632740445922</v>
+        <v>0.509422413839287</v>
       </c>
       <c r="Y35" s="23" t="n">
         <f aca="false">SUM(Y8:Y34)</f>
@@ -9584,7 +9597,7 @@
         <f aca="false">SUM(Z8:Z34)</f>
         <v>4210.3</v>
       </c>
-      <c r="AA35" s="0" t="n">
+      <c r="AA35" s="1" t="n">
         <f aca="false">Y35+Z35</f>
         <v>6549.520378624</v>
       </c>
@@ -9592,51 +9605,51 @@
         <f aca="false">AA35/$P35/1000*100</f>
         <v>0.0449842240011912</v>
       </c>
-      <c r="AC35" s="27" t="n">
+      <c r="AC35" s="2" t="n">
         <f aca="false">1000/100*Q35*($Q$41+$Q$47-$Q$49)-AA35</f>
-        <v>48558.979621376</v>
+        <v>53624.214821376</v>
       </c>
       <c r="AD35" s="26" t="n">
         <f aca="false">AC35/$P35/1000*100</f>
-        <v>0.333518775464316</v>
-      </c>
-      <c r="AE35" s="27" t="n">
+        <v>0.368308448857681</v>
+      </c>
+      <c r="AE35" s="2" t="n">
         <f aca="false">AC35+Q35/100*1000 *($Q$46+$Q$43)</f>
-        <v>91876.579621376</v>
+        <v>98049.282421376</v>
       </c>
       <c r="AF35" s="26" t="n">
         <f aca="false">AE35/$P35/1000*100</f>
-        <v>0.631038060686143</v>
+        <v>0.673434179698802</v>
       </c>
       <c r="AG35" s="26" t="n">
         <f aca="false">SUM(AG8:AG34)</f>
-        <v>38558.979621376</v>
+        <v>43624.214821376</v>
       </c>
       <c r="AH35" s="23"/>
-      <c r="AI35" s="38" t="n">
+      <c r="AI35" s="36" t="n">
         <f aca="false">ROUND(AG35/P35 *100/1000, 2)</f>
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="AK35" s="26" t="n">
         <f aca="false">-Q35*($Q$47)*10</f>
         <v>-24000</v>
       </c>
       <c r="AL35" s="26"/>
-      <c r="AO35" s="38" t="n">
+      <c r="AO35" s="36" t="n">
         <v>18796</v>
       </c>
-      <c r="AX35" s="38" t="n">
+      <c r="AX35" s="36" t="n">
         <f aca="false">SUM(AX8:AX34)</f>
         <v>47600</v>
       </c>
-      <c r="BD35" s="38" t="n">
+      <c r="BD35" s="36" t="n">
         <f aca="false">SUM(BD8:BD34)</f>
         <v>299.1</v>
       </c>
-      <c r="XFA35" s="0"/>
-      <c r="XFB35" s="0"/>
-      <c r="XFC35" s="0"/>
-      <c r="XFD35" s="0"/>
+      <c r="XFA35" s="1"/>
+      <c r="XFB35" s="1"/>
+      <c r="XFC35" s="1"/>
+      <c r="XFD35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="n">
@@ -9666,7 +9679,7 @@
       </c>
       <c r="M36" s="1" t="n">
         <f aca="false">SUM(M8:M34)</f>
-        <v>40677.6</v>
+        <v>44000.0028</v>
       </c>
       <c r="O36" s="1" t="n">
         <f aca="false">SUM(O8:O34)</f>
@@ -9679,362 +9692,362 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="1" t="n">
         <f aca="false">SUM(R8:R34)</f>
-        <v>98426.1</v>
+        <v>104598.8028</v>
       </c>
       <c r="T36" s="2"/>
       <c r="Y36" s="2"/>
       <c r="Z36" s=